--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="6" name="Dow_Jones" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="141">
   <si>
     <t>Ticker</t>
   </si>
@@ -194,157 +195,253 @@
     <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Last Run</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Russell 2000</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Small ($300M–$2B)</t>
+  </si>
+  <si>
+    <t>Price min</t>
+  </si>
+  <si>
+    <t>&gt; $7</t>
+  </si>
+  <si>
+    <t>YTD perf min</t>
+  </si>
+  <si>
+    <t>&gt; +10%</t>
+  </si>
+  <si>
+    <t>P/E max</t>
+  </si>
+  <si>
+    <t>&lt; 28</t>
+  </si>
+  <si>
+    <t>EPS Q/Q</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Sectors</t>
+  </si>
+  <si>
+    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Beta range</t>
+  </si>
+  <si>
+    <t>0.7 – 1.2</t>
+  </si>
+  <si>
+    <t>RSI min</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>&gt; 0</t>
+  </si>
+  <si>
+    <t>Ranked by</t>
+  </si>
+  <si>
+    <t>Alpha (highest first)</t>
+  </si>
+  <si>
+    <t>Top N</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>2 of 2 qualified</t>
+  </si>
+  <si>
+    <t>Dow Jones 30</t>
+  </si>
+  <si>
+    <t>&gt; $10</t>
+  </si>
+  <si>
+    <t>&gt; +5%</t>
+  </si>
+  <si>
+    <t>&lt; 35</t>
+  </si>
+  <si>
+    <t>All sectors</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>1 of 1 qualified</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 (large-cap subset)</t>
+  </si>
+  <si>
+    <t>Large (approx. S&amp;P 100)</t>
+  </si>
+  <si>
+    <t>&gt; +8%</t>
+  </si>
+  <si>
+    <t>&lt; 40</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Signal Type</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Earnings quality vs peers</t>
+  </si>
+  <si>
+    <t>Finviz</t>
+  </si>
+  <si>
+    <t>P(EPS_Fwd_Growth)</t>
+  </si>
+  <si>
+    <t>Earnings acceleration</t>
+  </si>
+  <si>
+    <t>P(MA_Slope_50)</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Medium-term price trend</t>
+  </si>
+  <si>
+    <t>Yahoo Finance prices</t>
+  </si>
+  <si>
+    <t>P(RSI_14)</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Short-term momentum strength</t>
+  </si>
+  <si>
+    <t>P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Long-term trend confirmation</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Criteria</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>WSR</t>
-  </si>
-  <si>
-    <t>Last Run</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>Russell 2000</t>
-  </si>
-  <si>
-    <t>Cap</t>
-  </si>
-  <si>
-    <t>Small ($300M–$2B)</t>
-  </si>
-  <si>
-    <t>Price min</t>
-  </si>
-  <si>
-    <t>&gt; $7</t>
-  </si>
-  <si>
-    <t>YTD perf min</t>
-  </si>
-  <si>
-    <t>&gt; +10%</t>
-  </si>
-  <si>
-    <t>P/E max</t>
-  </si>
-  <si>
-    <t>&lt; 28</t>
-  </si>
-  <si>
-    <t>EPS Q/Q</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>Sectors</t>
-  </si>
-  <si>
-    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>Beta range</t>
-  </si>
-  <si>
-    <t>0.7 – 1.2</t>
-  </si>
-  <si>
-    <t>RSI min</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>Alpha</t>
-  </si>
-  <si>
-    <t>&gt; 0</t>
-  </si>
-  <si>
-    <t>Ranked by</t>
-  </si>
-  <si>
-    <t>Alpha (highest first)</t>
-  </si>
-  <si>
-    <t>Top N</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Results</t>
-  </si>
-  <si>
-    <t>2 of 2 qualified</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>Dow Jones 30</t>
-  </si>
-  <si>
-    <t>&gt; $10</t>
-  </si>
-  <si>
-    <t>&gt; +5%</t>
-  </si>
-  <si>
-    <t>&lt; 35</t>
-  </si>
-  <si>
-    <t>All sectors</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>1 of 1 qualified</t>
-  </si>
-  <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>S&amp;P 500 (large-cap subset)</t>
-  </si>
-  <si>
-    <t>Large (approx. S&amp;P 100)</t>
-  </si>
-  <si>
-    <t>&gt; +8%</t>
-  </si>
-  <si>
-    <t>&lt; 40</t>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Score Range</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>≥ 70</t>
+  </si>
+  <si>
+    <t>Strong Buy candidate</t>
+  </si>
+  <si>
+    <t>50 – 70</t>
+  </si>
+  <si>
+    <t>Hold / Monitor</t>
+  </si>
+  <si>
+    <t>30 – 50</t>
+  </si>
+  <si>
+    <t>Weak / Neutral</t>
+  </si>
+  <si>
+    <t>&lt; 30</t>
+  </si>
+  <si>
+    <t>Consider reducing position</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
   </si>
 </sst>
 </file>
@@ -360,12 +457,32 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -380,8 +497,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1017,6 +1138,2166 @@
       <c r="O1" t="s">
         <v>57</v>
       </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.69</v>
+      </c>
+      <c r="C2" s="1">
+        <v>85.41666666666666</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-0.8191330343796712</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.11940253782009777</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="H2" s="1">
+        <v>39.81</v>
+      </c>
+      <c r="I2" s="1">
+        <v>17.35</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.0023737785663199627</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>364</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.09774252789480942</v>
+      </c>
+      <c r="N2" s="1">
+        <v>44.375</v>
+      </c>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.64</v>
+      </c>
+      <c r="C3" s="2">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.181818181818183</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.15463133361194895</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>79.25</v>
+      </c>
+      <c r="I3" s="2">
+        <v>39.15</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.027035824145518757</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>375</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.18368744448733576</v>
+      </c>
+      <c r="N3" s="2">
+        <v>77.29166666666666</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-3.95</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.721518987341772</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-0.2997874815980858</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="H4" s="3">
+        <v>50.03</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-27.2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-0.01432968093560943</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>50</v>
+      </c>
+      <c r="M4" s="3">
+        <v>-0.29503284527302254</v>
+      </c>
+      <c r="N4" s="3">
+        <v>24.583333333333332</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="C5" s="4">
+        <v>56.25</v>
+      </c>
+      <c r="D5" s="4">
+        <v>27.981481481481477</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.58</v>
+      </c>
+      <c r="F5" s="4">
+        <v>-0.1324852835010605</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="H5" s="4">
+        <v>55.13</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-2.42</v>
+      </c>
+      <c r="J5" s="4">
+        <v>-0.004872619589082648</v>
+      </c>
+      <c r="K5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>312</v>
+      </c>
+      <c r="M5" s="4">
+        <v>-0.1100328341882616</v>
+      </c>
+      <c r="N5" s="4">
+        <v>51.66666666666667</v>
+      </c>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.09</v>
+      </c>
+      <c r="C6" s="1">
+        <v>70.83333333333334</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.5663430420711975</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-2.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.015574698750199387</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>41.72</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-11.59</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.020971830186022736</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>139</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.03142348650041038</v>
+      </c>
+      <c r="N6" s="1">
+        <v>49.375</v>
+      </c>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>79.16666666666666</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.05216692912061721</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.29</v>
+      </c>
+      <c r="H7" s="4">
+        <v>68.67</v>
+      </c>
+      <c r="I7" s="4">
+        <v>10.03</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.011374279129554401</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>434</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0.08624182278357084</v>
+      </c>
+      <c r="N7" s="4">
+        <v>61.875</v>
+      </c>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>13.19</v>
+      </c>
+      <c r="C8" s="4">
+        <v>97.91666666666666</v>
+      </c>
+      <c r="D8" s="4">
+        <v>-0.044730856709628494</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.013480296772397392</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="4">
+        <v>80.84</v>
+      </c>
+      <c r="I8" s="4">
+        <v>12.36</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.016806327810061392</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>69</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.0002729736472215638</v>
+      </c>
+      <c r="N8" s="4">
+        <v>62.708333333333336</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="C9" s="4">
+        <v>50</v>
+      </c>
+      <c r="D9" s="4">
+        <v>67.1111111111111</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-0.18257434339651085</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="H9" s="4">
+        <v>52.98</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-10.4</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.0017804758732523362</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>189</v>
+      </c>
+      <c r="M9" s="4">
+        <v>-0.16672555564629987</v>
+      </c>
+      <c r="N9" s="4">
+        <v>52.29166666666667</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.79</v>
+      </c>
+      <c r="C10" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.6435935198821797</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-0.09935027283030967</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H10" s="1">
+        <v>62.08</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-5.15</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-0.0009973918374701378</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>56</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.08746368201765142</v>
+      </c>
+      <c r="N10" s="1">
+        <v>46.875</v>
+      </c>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="C11" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-1653.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.2373041633607682</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.41</v>
+      </c>
+      <c r="H11" s="3">
+        <v>49.11</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-0.49</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-0.012954170042827666</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>28</v>
+      </c>
+      <c r="M11" s="3">
+        <v>-0.22647415839812401</v>
+      </c>
+      <c r="N11" s="3">
+        <v>22.916666666666668</v>
+      </c>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C12" s="1">
+        <v>60.416666666666664</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7.5114503816793885</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-0.1266387692870606</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="H12" s="1">
+        <v>55.45</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-9.56</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-0.01441421206345179</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.13641218839969071</v>
+      </c>
+      <c r="N12" s="1">
+        <v>40.208333333333336</v>
+      </c>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.08</v>
+      </c>
+      <c r="C13" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1166</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6.17</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.31134277324890075</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.66</v>
+      </c>
+      <c r="H13" s="2">
+        <v>71.41</v>
+      </c>
+      <c r="I13" s="2">
+        <v>76.95</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.036955400678864</v>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>249</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.32877643977413284</v>
+      </c>
+      <c r="N13" s="2">
+        <v>75.625</v>
+      </c>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-3.83</v>
+      </c>
+      <c r="C14" s="1">
+        <v>10.416666666666668</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12.668407310704959</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2.52</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.1367064575621085</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2.06</v>
+      </c>
+      <c r="H14" s="1">
+        <v>64.5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>18.73</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.019616079754584414</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>27</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0.16470598258748126</v>
+      </c>
+      <c r="N14" s="1">
+        <v>49.791666666666664</v>
+      </c>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-6.51</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4.411674347158218</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4.53</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.02551684943171327</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="H15" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.014393856469644214</v>
+      </c>
+      <c r="K15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>43</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0.04770515228200867</v>
+      </c>
+      <c r="N15" s="1">
+        <v>36.25</v>
+      </c>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-0.01</v>
+      </c>
+      <c r="C16" s="4">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="D16" s="4">
+        <v>18685</v>
+      </c>
+      <c r="E16" s="4">
+        <v>11.11</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-0.07710107317789963</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.23</v>
+      </c>
+      <c r="H16" s="4">
+        <v>66.28</v>
+      </c>
+      <c r="I16" s="4">
+        <v>22.53</v>
+      </c>
+      <c r="J16" s="4">
+        <v>-0.003388255450886434</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>32</v>
+      </c>
+      <c r="M16" s="4">
+        <v>-0.07102570454031876</v>
+      </c>
+      <c r="N16" s="4">
+        <v>63.125</v>
+      </c>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8.81</v>
+      </c>
+      <c r="C17" s="1">
+        <v>93.75</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-0.27922814982973904</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4.52</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.11848178357699889</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="H17" s="1">
+        <v>56.37</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15.34</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.002480406015349057</v>
+      </c>
+      <c r="K17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>94</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.09655762718920702</v>
+      </c>
+      <c r="N17" s="1">
+        <v>49.166666666666664</v>
+      </c>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <v>27.92</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="4">
+        <v>-0.5508595988538683</v>
+      </c>
+      <c r="E18" s="4">
+        <v>-1.85</v>
+      </c>
+      <c r="F18" s="4">
+        <v>-0.06458700033216558</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1.14</v>
+      </c>
+      <c r="H18" s="4">
+        <v>69.94</v>
+      </c>
+      <c r="I18" s="4">
+        <v>4.92</v>
+      </c>
+      <c r="J18" s="4">
+        <v>-0.0006200222082913154</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>4</v>
+      </c>
+      <c r="M18" s="4">
+        <v>-0.06088894985711635</v>
+      </c>
+      <c r="N18" s="4">
+        <v>53.54166666666667</v>
+      </c>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="C19" s="1">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="D19" s="1">
+        <v>15.426356589147288</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="F19" s="1">
+        <v>-0.04129758439236603</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="H19" s="1">
+        <v>46.23</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-4.53</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-0.027338011861329586</v>
+      </c>
+      <c r="K19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>-7</v>
+      </c>
+      <c r="M19" s="1">
+        <v>-0.03310904405475701</v>
+      </c>
+      <c r="N19" s="1">
+        <v>43.958333333333336</v>
+      </c>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-18.39</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-4.206090266449157</v>
+      </c>
+      <c r="E20" s="3">
+        <v>8.76</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-0.061258483063819674</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3.67</v>
+      </c>
+      <c r="H20" s="3">
+        <v>71</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-29.81</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.023188818679715038</v>
+      </c>
+      <c r="K20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-44</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.009268622424619233</v>
+      </c>
+      <c r="N20" s="3">
+        <v>27.916666666666664</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-2.25</v>
+      </c>
+      <c r="C21" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10.44</v>
+      </c>
+      <c r="E21" s="3">
+        <v>12.21</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-0.43969939957864956</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.31</v>
+      </c>
+      <c r="H21" s="3">
+        <v>54.4</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-55.05</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-0.03547797069677966</v>
+      </c>
+      <c r="K21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>17</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-0.4050962129906889</v>
+      </c>
+      <c r="N21" s="3">
+        <v>25.625</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-2.38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1.4705882352941178</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5.89</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-0.17120120712554815</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3.13</v>
+      </c>
+      <c r="H22" s="1">
+        <v>73.51</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.03109288839166161</v>
+      </c>
+      <c r="K22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>43</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-0.11493801061229914</v>
+      </c>
+      <c r="N22" s="1">
+        <v>46.04166666666667</v>
+      </c>
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1.13</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20.833333333333336</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5.7522123893805315</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.4662787098315891</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="H23" s="3">
+        <v>49.67</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-33.89</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-0.012401909198076783</v>
+      </c>
+      <c r="K23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>37</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-0.4226945435185089</v>
+      </c>
+      <c r="N23" s="3">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-0.99</v>
+      </c>
+      <c r="C24" s="3">
+        <v>22.916666666666664</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.04040404040404</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-0.40154728528252626</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="H24" s="3">
+        <v>53.77</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-29.95</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-0.01464141824677345</v>
+      </c>
+      <c r="K24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>60</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-0.34237847768173857</v>
+      </c>
+      <c r="N24" s="3">
+        <v>23.125000000000004</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="C25" s="4">
+        <v>45.83333333333333</v>
+      </c>
+      <c r="D25" s="4">
+        <v>89.71052631578947</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="F25" s="4">
+        <v>-0.3170927581740075</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2.32</v>
+      </c>
+      <c r="H25" s="4">
+        <v>63.79</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-19.66</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-0.009812260461178298</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>70</v>
+      </c>
+      <c r="M25" s="4">
+        <v>-0.2822254251235433</v>
+      </c>
+      <c r="N25" s="4">
+        <v>51.87499999999999</v>
+      </c>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="C26" s="4">
+        <v>62.5</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2990.236842105264</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2.07</v>
+      </c>
+      <c r="F26" s="4">
+        <v>-0.1547367590902501</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H26" s="4">
+        <v>55.52</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="J26" s="4">
+        <v>-0.006328987029654367</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4">
+        <v>116</v>
+      </c>
+      <c r="M26" s="4">
+        <v>-0.14945382984017974</v>
+      </c>
+      <c r="N26" s="4">
+        <v>61.875</v>
+      </c>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="C27" s="2">
+        <v>81.25</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10.491228070175438</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.16421433169186833</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1.39</v>
+      </c>
+      <c r="H27" s="2">
+        <v>74.94</v>
+      </c>
+      <c r="I27" s="2">
+        <v>20.62</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.024434924341505217</v>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>412</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0.17451604372950547</v>
+      </c>
+      <c r="N27" s="2">
+        <v>75.62500000000001</v>
+      </c>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-3.07</v>
+      </c>
+      <c r="C28" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8.671009771986972</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.00989392080333086</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="H28" s="1">
+        <v>63.26</v>
+      </c>
+      <c r="I28" s="1">
+        <v>13.66</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.0168781609811</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>44</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0.0281200267160735</v>
+      </c>
+      <c r="N28" s="1">
+        <v>43.74999999999999</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>89.58333333333334</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1.2283783783783782</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-0.84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.09024617250147376</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>42.46</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-14.49</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.010836343223542119</v>
+      </c>
+      <c r="K29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>149</v>
+      </c>
+      <c r="M29" s="1">
+        <v>-0.08760470787643859</v>
+      </c>
+      <c r="N29" s="1">
+        <v>49.583333333333336</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <v>5.41</v>
+      </c>
+      <c r="C30" s="4">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.6598890942698706</v>
+      </c>
+      <c r="E30" s="4">
+        <v>-0.09</v>
+      </c>
+      <c r="F30" s="4">
+        <v>-0.11560724672853408</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H30" s="4">
+        <v>70.08</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-14.71</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.016935392611379864</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4">
+        <v>-63</v>
+      </c>
+      <c r="M30" s="4">
+        <v>-0.10424894884088287</v>
+      </c>
+      <c r="N30" s="4">
+        <v>54.375</v>
+      </c>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>-0.74</v>
+      </c>
+      <c r="C31" s="4">
+        <v>27.083333333333332</v>
+      </c>
+      <c r="D31" s="4">
+        <v>36.608108108108105</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="F31" s="4">
+        <v>-0.012600547693719072</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="H31" s="4">
+        <v>63.53</v>
+      </c>
+      <c r="I31" s="4">
+        <v>-1.24</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0.004536771046019471</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
+        <v>93</v>
+      </c>
+      <c r="M31" s="4">
+        <v>-0.011279815381201486</v>
+      </c>
+      <c r="N31" s="4">
+        <v>50.833333333333336</v>
+      </c>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <v>-0.18</v>
+      </c>
+      <c r="C32" s="4">
+        <v>35.41666666666667</v>
+      </c>
+      <c r="D32" s="4">
+        <v>105.33333333333334</v>
+      </c>
+      <c r="E32" s="4">
+        <v>-4.72</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.1381086728940456</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1.36</v>
+      </c>
+      <c r="H32" s="4">
+        <v>75</v>
+      </c>
+      <c r="I32" s="4">
+        <v>13.25</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0.02243554574533957</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4">
+        <v>-11</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0.14761794554417218</v>
+      </c>
+      <c r="N32" s="4">
+        <v>68.54166666666666</v>
+      </c>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>-4.08</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="D33" s="1">
+        <v>14.372549019607844</v>
+      </c>
+      <c r="E33" s="1">
+        <v>13.14</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.0749569552980534</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>62.34</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-7.11</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.04408771991281714</v>
+      </c>
+      <c r="K33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>20</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0.04854230904770174</v>
+      </c>
+      <c r="N33" s="1">
+        <v>48.333333333333336</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>-0.48</v>
+      </c>
+      <c r="C34" s="1">
+        <v>29.166666666666668</v>
+      </c>
+      <c r="D34" s="1">
+        <v>86.47916666666667</v>
+      </c>
+      <c r="E34" s="1">
+        <v>-1.38</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-0.27528167947146365</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="H34" s="1">
+        <v>56.83</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-32.31</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-0.010654340748782016</v>
+      </c>
+      <c r="K34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>3</v>
+      </c>
+      <c r="M34" s="1">
+        <v>-0.27765899763399526</v>
+      </c>
+      <c r="N34" s="1">
+        <v>42.708333333333336</v>
+      </c>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3.52</v>
+      </c>
+      <c r="C35" s="1">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.1988636363636365</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.04837859130682097</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="H35" s="1">
+        <v>43.38</v>
+      </c>
+      <c r="I35" s="1">
+        <v>4.13</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.007072343136519611</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>28</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0.03200151063160295</v>
+      </c>
+      <c r="N35" s="1">
+        <v>47.083333333333336</v>
+      </c>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
+        <v>-0.02</v>
+      </c>
+      <c r="C36" s="4">
+        <v>39.58333333333333</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1215</v>
+      </c>
+      <c r="E36" s="4">
+        <v>5.89</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-0.048296298967170956</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1.38</v>
+      </c>
+      <c r="H36" s="4">
+        <v>57.58</v>
+      </c>
+      <c r="I36" s="4">
+        <v>-8.94</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0.017724750523772582</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="4">
+        <v>31</v>
+      </c>
+      <c r="M36" s="4">
+        <v>-0.038258733392037336</v>
+      </c>
+      <c r="N36" s="4">
+        <v>62.08333333333333</v>
+      </c>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="C37" s="4">
+        <v>52.083333333333336</v>
+      </c>
+      <c r="D37" s="4">
+        <v>31.03191489361702</v>
+      </c>
+      <c r="E37" s="4">
+        <v>-0.72</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-0.15913082613344948</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2.78</v>
+      </c>
+      <c r="H37" s="4">
+        <v>62.2</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-5.66</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0.010883126809017934</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
+        <v>134</v>
+      </c>
+      <c r="M37" s="4">
+        <v>-0.11211275580782354</v>
+      </c>
+      <c r="N37" s="4">
+        <v>57.70833333333334</v>
+      </c>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>3.41</v>
+      </c>
+      <c r="C38" s="2">
+        <v>72.91666666666666</v>
+      </c>
+      <c r="D38" s="2">
+        <v>8.926686217008797</v>
+      </c>
+      <c r="E38" s="2">
+        <v>-1.19</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.7532144984691509</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="H38" s="2">
+        <v>68.52</v>
+      </c>
+      <c r="I38" s="2">
+        <v>72.37</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.04794036718733313</v>
+      </c>
+      <c r="K38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>234</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0.7817423164195307</v>
+      </c>
+      <c r="N38" s="2">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>-0.38</v>
+      </c>
+      <c r="C39" s="2">
+        <v>31.25</v>
+      </c>
+      <c r="D39" s="2">
+        <v>325.07894736842104</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3.31</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.4244393059541854</v>
+      </c>
+      <c r="G39" s="2">
+        <v>3.47</v>
+      </c>
+      <c r="H39" s="2">
+        <v>73.96</v>
+      </c>
+      <c r="I39" s="2">
+        <v>120.27</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.04318873970246332</v>
+      </c>
+      <c r="K39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>211</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0.489683482192554</v>
+      </c>
+      <c r="N39" s="2">
+        <v>74.58333333333333</v>
+      </c>
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="C40" s="1">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="D40" s="1">
+        <v>228.28125</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="F40" s="1">
+        <v>-0.20047544049218177</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="H40" s="1">
+        <v>45.97</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-3.8</v>
+      </c>
+      <c r="J40" s="1">
+        <v>-0.01178367415794677</v>
+      </c>
+      <c r="K40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>11</v>
+      </c>
+      <c r="M40" s="1">
+        <v>-0.18251348104194265</v>
+      </c>
+      <c r="N40" s="1">
+        <v>46.041666666666664</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C41" s="3">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="D41" s="3">
+        <v>-23.77054794520548</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16.88</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.1549289351552015</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="H41" s="3">
+        <v>70.81</v>
+      </c>
+      <c r="I41" s="3">
+        <v>31.67</v>
+      </c>
+      <c r="J41" s="3">
+        <v>-0.012185710379580567</v>
+      </c>
+      <c r="K41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="3">
+        <v>83</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0.18002284909303556</v>
+      </c>
+      <c r="N41" s="3">
+        <v>25.625</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="C42" s="4">
+        <v>77.08333333333334</v>
+      </c>
+      <c r="D42" s="4">
+        <v>6.178278688524591</v>
+      </c>
+      <c r="E42" s="4">
+        <v>-0.19</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.11548747115132582</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="H42" s="4">
+        <v>61.04</v>
+      </c>
+      <c r="I42" s="4">
+        <v>56.14</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0.017137808683028773</v>
+      </c>
+      <c r="K42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4">
+        <v>300</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0.13793992046412473</v>
+      </c>
+      <c r="N42" s="4">
+        <v>64.58333333333334</v>
+      </c>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-0.76</v>
+      </c>
+      <c r="C43" s="1">
+        <v>25</v>
+      </c>
+      <c r="D43" s="1">
+        <v>13.236842105263158</v>
+      </c>
+      <c r="E43" s="1">
+        <v>7.72</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-0.38174499445726107</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2.61</v>
+      </c>
+      <c r="H43" s="1">
+        <v>56.14</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-31.84</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-0.01874205106563216</v>
+      </c>
+      <c r="K43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>64</v>
+      </c>
+      <c r="M43" s="1">
+        <v>-0.3392174139941949</v>
+      </c>
+      <c r="N43" s="1">
+        <v>31.666666666666664</v>
+      </c>
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="C44" s="4">
+        <v>47.91666666666667</v>
+      </c>
+      <c r="D44" s="4">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1.41</v>
+      </c>
+      <c r="H44" s="4">
+        <v>63.64</v>
+      </c>
+      <c r="I44" s="4">
+        <v>-3.37</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4">
+        <v>45</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="4">
+        <v>55.83333333333333</v>
+      </c>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C45" s="2">
+        <v>54.166666666666664</v>
+      </c>
+      <c r="D45" s="2">
+        <v>14.789473684210527</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2.01</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.31067145981052635</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="H45" s="2">
+        <v>83.89</v>
+      </c>
+      <c r="I45" s="2">
+        <v>36.93</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.026608906205351935</v>
+      </c>
+      <c r="K45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2">
+        <v>11</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.305388530560456</v>
+      </c>
+      <c r="N45" s="2">
+        <v>72.08333333333333</v>
+      </c>
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="C46" s="4">
+        <v>64.58333333333334</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1.1030927835051547</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0.04356416389380155</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="H46" s="4">
+        <v>70.05</v>
+      </c>
+      <c r="I46" s="4">
+        <v>22.64</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0.008830482815401951</v>
+      </c>
+      <c r="K46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4">
+        <v>23</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0.03669635586871012</v>
+      </c>
+      <c r="N46" s="4">
+        <v>52.91666666666667</v>
+      </c>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="4">
+        <v>2.84</v>
+      </c>
+      <c r="C47" s="4">
+        <v>68.75</v>
+      </c>
+      <c r="D47" s="4">
+        <v>2.0880281690140845</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0.18093353280757316</v>
+      </c>
+      <c r="G47" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="H47" s="4">
+        <v>72.82</v>
+      </c>
+      <c r="I47" s="4">
+        <v>19.81</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0.004465546501666247</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>248</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0.17776377525753095</v>
+      </c>
+      <c r="N47" s="4">
+        <v>56.666666666666664</v>
+      </c>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2">
+        <v>8.72</v>
+      </c>
+      <c r="C48" s="2">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0.8061926605504586</v>
+      </c>
+      <c r="E48" s="2">
+        <v>6.35</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.873048360184754</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="H48" s="2">
+        <v>72.13</v>
+      </c>
+      <c r="I48" s="2">
+        <v>52.56</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0.05270914285945323</v>
+      </c>
+      <c r="K48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2">
+        <v>115</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.8719917743347398</v>
+      </c>
+      <c r="N48" s="2">
+        <v>71.875</v>
+      </c>
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="4">
+        <v>10.45</v>
+      </c>
+      <c r="C49" s="4">
+        <v>95.83333333333334</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="E49" s="4">
+        <v>-0.36</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0.177434564940825</v>
+      </c>
+      <c r="G49" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H49" s="4">
+        <v>68.18</v>
+      </c>
+      <c r="I49" s="4">
+        <v>14.22</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0.010713778808231215</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <v>133</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0.18271749419089534</v>
+      </c>
+      <c r="N49" s="4">
+        <v>57.91666666666667</v>
+      </c>
+      <c r="O49" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1026,15 +3307,399 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>44.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>77.29166666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>24.583333333333332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>51.66666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>49.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>61.875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>62.708333333333336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>52.29166666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>46.875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>22.916666666666668</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>40.208333333333336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>75.625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>49.791666666666664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>63.125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>49.166666666666664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>53.54166666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>43.958333333333336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>27.916666666666664</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>25.625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>46.04166666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>24.16666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>23.125000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>51.87499999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>61.875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>75.62500000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>43.74999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>49.583333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>54.375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>50.833333333333336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>68.54166666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>48.333333333333336</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>42.708333333333336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>47.083333333333336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>62.08333333333333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>57.70833333333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>73.33333333333333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>74.58333333333333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>46.041666666666664</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>25.625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>64.58333333333334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>31.666666666666664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>55.83333333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B45">
+        <v>72.08333333333333</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>59</v>
+      </c>
+      <c r="B46">
+        <v>52.91666666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47">
+        <v>56.666666666666664</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48">
+        <v>71.875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49">
+        <v>57.91666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1053,18 +3718,18 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -1072,109 +3737,109 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1193,18 +3858,18 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -1212,98 +3877,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1322,18 +3987,18 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -1341,98 +4006,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1451,18 +4116,18 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -1470,113 +4135,348 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
         <v>104</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="144">
   <si>
     <t>Ticker</t>
   </si>
@@ -198,12 +198,18 @@
     <t>WSR</t>
   </si>
   <si>
+    <t>BLX</t>
+  </si>
+  <si>
     <t>MD</t>
   </si>
   <si>
     <t>CSCO</t>
   </si>
   <si>
+    <t>JPM</t>
+  </si>
+  <si>
     <t>DELL</t>
   </si>
   <si>
@@ -300,37 +306,40 @@
     <t>Results</t>
   </si>
   <si>
+    <t>3 of 3 qualified</t>
+  </si>
+  <si>
+    <t>Dow Jones 30</t>
+  </si>
+  <si>
+    <t>&gt; $10</t>
+  </si>
+  <si>
+    <t>&gt; +5%</t>
+  </si>
+  <si>
+    <t>&lt; 35</t>
+  </si>
+  <si>
+    <t>All sectors</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
     <t>2 of 2 qualified</t>
   </si>
   <si>
-    <t>Dow Jones 30</t>
-  </si>
-  <si>
-    <t>&gt; $10</t>
-  </si>
-  <si>
-    <t>&gt; +5%</t>
-  </si>
-  <si>
-    <t>&lt; 35</t>
-  </si>
-  <si>
-    <t>All sectors</t>
-  </si>
-  <si>
-    <t>64</t>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
   </si>
   <si>
     <t>1 of 1 qualified</t>
-  </si>
-  <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
   </si>
   <si>
     <t>S&amp;P 500 (large-cap subset)</t>
@@ -1089,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1147,7 +1156,7 @@
         <v>6.69</v>
       </c>
       <c r="C2" s="1">
-        <v>85.41666666666666</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1">
         <v>-0.8191330343796712</v>
@@ -1156,16 +1165,16 @@
         <v>-0.01</v>
       </c>
       <c r="F2" s="1">
-        <v>0.11940253782009777</v>
+        <v>0.11967941242595193</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>39.81</v>
+        <v>39.49</v>
       </c>
       <c r="I2" s="1">
-        <v>17.35</v>
+        <v>17.22</v>
       </c>
       <c r="J2" s="1">
         <v>0.0023737785663199627</v>
@@ -1177,12 +1186,14 @@
         <v>364</v>
       </c>
       <c r="M2" s="1">
-        <v>0.09774252789480942</v>
+        <v>0.09928072014955469</v>
       </c>
       <c r="N2" s="1">
-        <v>44.375</v>
-      </c>
-      <c r="O2" s="1"/>
+        <v>43.800000000000004</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1192,7 +1203,7 @@
         <v>2.64</v>
       </c>
       <c r="C3" s="2">
-        <v>66.66666666666666</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2">
         <v>23.181818181818183</v>
@@ -1201,19 +1212,19 @@
         <v>2.75</v>
       </c>
       <c r="F3" s="2">
-        <v>0.15463133361194895</v>
+        <v>0.15876698515967727</v>
       </c>
       <c r="G3" s="2">
         <v>2.1</v>
       </c>
       <c r="H3" s="2">
-        <v>79.25</v>
+        <v>78.96</v>
       </c>
       <c r="I3" s="2">
-        <v>39.15</v>
+        <v>38.57</v>
       </c>
       <c r="J3" s="2">
-        <v>0.027035824145518757</v>
+        <v>0.02705586046568028</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -1222,12 +1233,14 @@
         <v>375</v>
       </c>
       <c r="M3" s="2">
-        <v>0.18368744448733576</v>
+        <v>0.18613108455484428</v>
       </c>
       <c r="N3" s="2">
-        <v>77.29166666666666</v>
-      </c>
-      <c r="O3" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1237,7 +1250,7 @@
         <v>-3.95</v>
       </c>
       <c r="C4" s="3">
-        <v>8.333333333333332</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3">
         <v>9.721518987341772</v>
@@ -1246,19 +1259,19 @@
         <v>4.7</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.2997874815980858</v>
+        <v>-0.3033310828445169</v>
       </c>
       <c r="G4" s="3">
         <v>1.18</v>
       </c>
       <c r="H4" s="3">
-        <v>50.03</v>
+        <v>48.95</v>
       </c>
       <c r="I4" s="3">
-        <v>-27.2</v>
+        <v>-27.88</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.01432968093560943</v>
+        <v>-0.01446289471733941</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
@@ -1267,12 +1280,14 @@
         <v>50</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.29503284527302254</v>
+        <v>-0.2988533211253077</v>
       </c>
       <c r="N4" s="3">
-        <v>24.583333333333332</v>
-      </c>
-      <c r="O4" s="3"/>
+        <v>24.6</v>
+      </c>
+      <c r="O4" s="3">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1282,28 +1297,28 @@
         <v>1.08</v>
       </c>
       <c r="C5" s="4">
-        <v>56.25</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4">
-        <v>27.981481481481477</v>
+        <v>27.944444444444443</v>
       </c>
       <c r="E5" s="4">
         <v>0.58</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.1324852835010605</v>
+        <v>-0.12866175509386943</v>
       </c>
       <c r="G5" s="4">
         <v>1.85</v>
       </c>
       <c r="H5" s="4">
-        <v>55.13</v>
+        <v>54.34</v>
       </c>
       <c r="I5" s="4">
-        <v>-2.42</v>
+        <v>-2.85</v>
       </c>
       <c r="J5" s="4">
-        <v>-0.004872619589082648</v>
+        <v>-0.004851686507586286</v>
       </c>
       <c r="K5" s="4" t="b">
         <v>0</v>
@@ -1312,12 +1327,14 @@
         <v>312</v>
       </c>
       <c r="M5" s="4">
-        <v>-0.1100328341882616</v>
+        <v>-0.107516769197604</v>
       </c>
       <c r="N5" s="4">
-        <v>51.66666666666667</v>
-      </c>
-      <c r="O5" s="4"/>
+        <v>50.800000000000004</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1327,7 +1344,7 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>70.83333333333334</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1">
         <v>1.5663430420711975</v>
@@ -1336,19 +1353,19 @@
         <v>-2.3</v>
       </c>
       <c r="F6" s="1">
-        <v>0.015574698750199387</v>
+        <v>0.016374056771371423</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>41.72</v>
+        <v>41.41</v>
       </c>
       <c r="I6" s="1">
-        <v>-11.59</v>
+        <v>-11.78</v>
       </c>
       <c r="J6" s="1">
-        <v>0.020971830186022736</v>
+        <v>0.02093980443525671</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -1357,12 +1374,14 @@
         <v>139</v>
       </c>
       <c r="M6" s="1">
-        <v>0.03142348650041038</v>
+        <v>0.03129992916873525</v>
       </c>
       <c r="N6" s="1">
-        <v>49.375</v>
-      </c>
-      <c r="O6" s="1"/>
+        <v>49.6</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1372,7 +1391,7 @@
         <v>4.9</v>
       </c>
       <c r="C7" s="4">
-        <v>79.16666666666666</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4">
         <v>5.9</v>
@@ -1381,19 +1400,19 @@
         <v>0.37</v>
       </c>
       <c r="F7" s="4">
-        <v>0.05216692912061721</v>
+        <v>0.05439778654196077</v>
       </c>
       <c r="G7" s="4">
         <v>2.29</v>
       </c>
       <c r="H7" s="4">
-        <v>68.67</v>
+        <v>67.39</v>
       </c>
       <c r="I7" s="4">
-        <v>10.03</v>
+        <v>9.64</v>
       </c>
       <c r="J7" s="4">
-        <v>0.011374279129554401</v>
+        <v>0.011349021721240592</v>
       </c>
       <c r="K7" s="4" t="b">
         <v>0</v>
@@ -1402,12 +1421,14 @@
         <v>434</v>
       </c>
       <c r="M7" s="4">
-        <v>0.08624182278357084</v>
+        <v>0.086488412196293</v>
       </c>
       <c r="N7" s="4">
-        <v>61.875</v>
-      </c>
-      <c r="O7" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1417,7 +1438,7 @@
         <v>13.19</v>
       </c>
       <c r="C8" s="4">
-        <v>97.91666666666666</v>
+        <v>96</v>
       </c>
       <c r="D8" s="4">
         <v>-0.044730856709628494</v>
@@ -1426,19 +1447,19 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="4">
-        <v>0.013480296772397392</v>
+        <v>0.018164476427022368</v>
       </c>
       <c r="G8" s="4">
         <v>0.5</v>
       </c>
       <c r="H8" s="4">
-        <v>80.84</v>
+        <v>80.91</v>
       </c>
       <c r="I8" s="4">
-        <v>12.36</v>
+        <v>12.46</v>
       </c>
       <c r="J8" s="4">
-        <v>0.016806327810061392</v>
+        <v>0.016899589420790572</v>
       </c>
       <c r="K8" s="4" t="b">
         <v>0</v>
@@ -1447,12 +1468,14 @@
         <v>69</v>
       </c>
       <c r="M8" s="4">
-        <v>0.0002729736472215638</v>
+        <v>0.005726249429219177</v>
       </c>
       <c r="N8" s="4">
-        <v>62.708333333333336</v>
-      </c>
-      <c r="O8" s="4"/>
+        <v>63.599999999999994</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1462,7 +1485,7 @@
         <v>0.63</v>
       </c>
       <c r="C9" s="4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4">
         <v>67.1111111111111</v>
@@ -1471,19 +1494,19 @@
         <v>1.75</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.18257434339651085</v>
+        <v>-0.17753265067641916</v>
       </c>
       <c r="G9" s="4">
         <v>1.6</v>
       </c>
       <c r="H9" s="4">
-        <v>52.98</v>
+        <v>52.36</v>
       </c>
       <c r="I9" s="4">
-        <v>-10.4</v>
+        <v>-10.8</v>
       </c>
       <c r="J9" s="4">
-        <v>0.0017804758732523362</v>
+        <v>0.001840994302116228</v>
       </c>
       <c r="K9" s="4" t="b">
         <v>0</v>
@@ -1492,12 +1515,14 @@
         <v>189</v>
       </c>
       <c r="M9" s="4">
-        <v>-0.16672555564629987</v>
+        <v>-0.16260677827905534</v>
       </c>
       <c r="N9" s="4">
-        <v>52.29166666666667</v>
-      </c>
-      <c r="O9" s="4"/>
+        <v>52</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1507,7 +1532,7 @@
         <v>6.79</v>
       </c>
       <c r="C10" s="1">
-        <v>87.5</v>
+        <v>86</v>
       </c>
       <c r="D10" s="1">
         <v>0.6435935198821797</v>
@@ -1516,19 +1541,19 @@
         <v>0.88</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.09935027283030967</v>
+        <v>-0.0974824182303593</v>
       </c>
       <c r="G10" s="1">
         <v>1.45</v>
       </c>
       <c r="H10" s="1">
-        <v>62.08</v>
+        <v>62.54</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.15</v>
+        <v>-5.04</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.0009973918374701378</v>
+        <v>-0.0010052609990238268</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -1537,12 +1562,14 @@
         <v>56</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.08746368201765142</v>
+        <v>-0.08628801393233643</v>
       </c>
       <c r="N10" s="1">
-        <v>46.875</v>
-      </c>
-      <c r="O10" s="1"/>
+        <v>48.4</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -1552,7 +1579,7 @@
         <v>0.02</v>
       </c>
       <c r="C11" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>-1653.5</v>
@@ -1561,16 +1588,16 @@
         <v>10.01</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.2373041633607682</v>
+        <v>-0.23513531228157736</v>
       </c>
       <c r="G11" s="3">
         <v>1.41</v>
       </c>
       <c r="H11" s="3">
-        <v>49.11</v>
+        <v>47.58</v>
       </c>
       <c r="I11" s="3">
-        <v>-0.49</v>
+        <v>-1.59</v>
       </c>
       <c r="J11" s="3">
         <v>-0.012954170042827666</v>
@@ -1582,12 +1609,14 @@
         <v>28</v>
       </c>
       <c r="M11" s="3">
-        <v>-0.22647415839812401</v>
+        <v>-0.22493596614337874</v>
       </c>
       <c r="N11" s="3">
-        <v>22.916666666666668</v>
-      </c>
-      <c r="O11" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1597,7 +1626,7 @@
         <v>1.31</v>
       </c>
       <c r="C12" s="1">
-        <v>60.416666666666664</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="D12" s="1">
         <v>7.5114503816793885</v>
@@ -1606,19 +1635,19 @@
         <v>0.13</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.1266387692870606</v>
+        <v>-0.13422061465190438</v>
       </c>
       <c r="G12" s="1">
         <v>0.63</v>
       </c>
       <c r="H12" s="1">
-        <v>55.45</v>
+        <v>54.75</v>
       </c>
       <c r="I12" s="1">
-        <v>-9.56</v>
+        <v>-10.23</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.01441421206345179</v>
+        <v>-0.014605975442797736</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
@@ -1627,12 +1656,14 @@
         <v>10</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.13641218839969071</v>
+        <v>-0.14342490263027874</v>
       </c>
       <c r="N12" s="1">
-        <v>40.208333333333336</v>
-      </c>
-      <c r="O12" s="1"/>
+        <v>40.2</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -1642,7 +1673,7 @@
         <v>-0.08</v>
       </c>
       <c r="C13" s="2">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="D13" s="2">
         <v>1166</v>
@@ -1651,19 +1682,19 @@
         <v>6.17</v>
       </c>
       <c r="F13" s="2">
-        <v>0.31134277324890075</v>
+        <v>0.31368202773667075</v>
       </c>
       <c r="G13" s="2">
         <v>1.66</v>
       </c>
       <c r="H13" s="2">
-        <v>71.41</v>
+        <v>70.84</v>
       </c>
       <c r="I13" s="2">
-        <v>76.95</v>
+        <v>75.58</v>
       </c>
       <c r="J13" s="2">
-        <v>0.036955400678864</v>
+        <v>0.03695105739468107</v>
       </c>
       <c r="K13" s="2" t="b">
         <v>0</v>
@@ -1672,57 +1703,61 @@
         <v>249</v>
       </c>
       <c r="M13" s="2">
-        <v>0.32877643977413284</v>
+        <v>0.33010048737377096</v>
       </c>
       <c r="N13" s="2">
-        <v>75.625</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>75.2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>-3.83</v>
       </c>
-      <c r="C14" s="1">
-        <v>10.416666666666668</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14" s="4">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4">
         <v>12.668407310704959</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="4">
         <v>2.52</v>
       </c>
-      <c r="F14" s="1">
-        <v>0.1367064575621085</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="F14" s="4">
+        <v>0.15078708560651521</v>
+      </c>
+      <c r="G14" s="4">
         <v>2.06</v>
       </c>
-      <c r="H14" s="1">
-        <v>64.5</v>
-      </c>
-      <c r="I14" s="1">
-        <v>18.73</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.019616079754584414</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="H14" s="4">
+        <v>64.43</v>
+      </c>
+      <c r="I14" s="4">
+        <v>18.63</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.019829962781969673</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
         <v>27</v>
       </c>
-      <c r="M14" s="1">
-        <v>0.16470598258748126</v>
-      </c>
-      <c r="N14" s="1">
-        <v>49.791666666666664</v>
-      </c>
-      <c r="O14" s="1"/>
+      <c r="M14" s="4">
+        <v>0.177156126841858</v>
+      </c>
+      <c r="N14" s="4">
+        <v>50.199999999999996</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1732,7 +1767,7 @@
         <v>-6.51</v>
       </c>
       <c r="C15" s="1">
-        <v>4.166666666666666</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1">
         <v>4.411674347158218</v>
@@ -1741,19 +1776,19 @@
         <v>4.53</v>
       </c>
       <c r="F15" s="1">
-        <v>0.02551684943171327</v>
+        <v>0.022359621987671996</v>
       </c>
       <c r="G15" s="1">
         <v>1.84</v>
       </c>
       <c r="H15" s="1">
-        <v>63.5</v>
+        <v>62</v>
       </c>
       <c r="I15" s="1">
-        <v>1.17</v>
+        <v>0.41</v>
       </c>
       <c r="J15" s="1">
-        <v>0.014393856469644214</v>
+        <v>0.014271758714584973</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>0</v>
@@ -1762,12 +1797,14 @@
         <v>43</v>
       </c>
       <c r="M15" s="1">
-        <v>0.04770515228200867</v>
+        <v>0.04325584334398136</v>
       </c>
       <c r="N15" s="1">
-        <v>36.25</v>
-      </c>
-      <c r="O15" s="1"/>
+        <v>36.400000000000006</v>
+      </c>
+      <c r="O15" s="1">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1777,7 +1814,7 @@
         <v>-0.01</v>
       </c>
       <c r="C16" s="4">
-        <v>41.66666666666667</v>
+        <v>40</v>
       </c>
       <c r="D16" s="4">
         <v>18685</v>
@@ -1786,19 +1823,19 @@
         <v>11.11</v>
       </c>
       <c r="F16" s="4">
-        <v>-0.07710107317789963</v>
+        <v>-0.08136562225678619</v>
       </c>
       <c r="G16" s="4">
         <v>1.23</v>
       </c>
       <c r="H16" s="4">
-        <v>66.28</v>
+        <v>66.22</v>
       </c>
       <c r="I16" s="4">
-        <v>22.53</v>
+        <v>22.47</v>
       </c>
       <c r="J16" s="4">
-        <v>-0.003388255450886434</v>
+        <v>-0.003532875449604242</v>
       </c>
       <c r="K16" s="4" t="b">
         <v>0</v>
@@ -1807,12 +1844,14 @@
         <v>32</v>
       </c>
       <c r="M16" s="4">
-        <v>-0.07102570454031876</v>
+        <v>-0.07564403783779672</v>
       </c>
       <c r="N16" s="4">
-        <v>63.125</v>
-      </c>
-      <c r="O16" s="4"/>
+        <v>62.6</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1822,7 +1861,7 @@
         <v>8.81</v>
       </c>
       <c r="C17" s="1">
-        <v>93.75</v>
+        <v>92</v>
       </c>
       <c r="D17" s="1">
         <v>-0.27922814982973904</v>
@@ -1831,19 +1870,19 @@
         <v>4.52</v>
       </c>
       <c r="F17" s="1">
-        <v>0.11848178357699889</v>
+        <v>0.11748865655087395</v>
       </c>
       <c r="G17" s="1">
         <v>0.17</v>
       </c>
       <c r="H17" s="1">
-        <v>56.37</v>
+        <v>56.43</v>
       </c>
       <c r="I17" s="1">
-        <v>15.34</v>
+        <v>15.38</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.002480406015349057</v>
+        <v>-0.0025026903760530404</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
@@ -1852,12 +1891,14 @@
         <v>94</v>
       </c>
       <c r="M17" s="1">
-        <v>0.09655762718920702</v>
+        <v>0.09684119973452066</v>
       </c>
       <c r="N17" s="1">
-        <v>49.166666666666664</v>
-      </c>
-      <c r="O17" s="1"/>
+        <v>48.99999999999999</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1876,19 +1917,19 @@
         <v>-1.85</v>
       </c>
       <c r="F18" s="4">
-        <v>-0.06458700033216558</v>
+        <v>-0.0675655590646727</v>
       </c>
       <c r="G18" s="4">
         <v>1.14</v>
       </c>
       <c r="H18" s="4">
-        <v>69.94</v>
+        <v>69.08</v>
       </c>
       <c r="I18" s="4">
-        <v>4.92</v>
+        <v>4.38</v>
       </c>
       <c r="J18" s="4">
-        <v>-0.0006200222082913154</v>
+        <v>-0.0007267240423029835</v>
       </c>
       <c r="K18" s="4" t="b">
         <v>0</v>
@@ -1897,12 +1938,14 @@
         <v>4</v>
       </c>
       <c r="M18" s="4">
-        <v>-0.06088894985711635</v>
+        <v>-0.0640828555052878</v>
       </c>
       <c r="N18" s="4">
-        <v>53.54166666666667</v>
-      </c>
-      <c r="O18" s="4"/>
+        <v>54.2</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1912,7 +1955,7 @@
         <v>1.29</v>
       </c>
       <c r="C19" s="1">
-        <v>58.333333333333336</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="D19" s="1">
         <v>15.426356589147288</v>
@@ -1921,19 +1964,19 @@
         <v>3.37</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.04129758439236603</v>
+        <v>-0.055505071827900376</v>
       </c>
       <c r="G19" s="1">
         <v>1.31</v>
       </c>
       <c r="H19" s="1">
-        <v>46.23</v>
+        <v>43.15</v>
       </c>
       <c r="I19" s="1">
-        <v>-4.53</v>
+        <v>-6.89</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.027338011861329586</v>
+        <v>-0.027605050492327275</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>1</v>
@@ -1942,12 +1985,14 @@
         <v>-7</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.03310904405475701</v>
+        <v>-0.047793371089262404</v>
       </c>
       <c r="N19" s="1">
-        <v>43.958333333333336</v>
-      </c>
-      <c r="O19" s="1"/>
+        <v>42.8</v>
+      </c>
+      <c r="O19" s="1">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -1957,7 +2002,7 @@
         <v>-18.39</v>
       </c>
       <c r="C20" s="3">
-        <v>2.083333333333333</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3">
         <v>-4.206090266449157</v>
@@ -1966,19 +2011,19 @@
         <v>8.76</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.061258483063819674</v>
+        <v>-0.05948272480163863</v>
       </c>
       <c r="G20" s="3">
         <v>3.67</v>
       </c>
       <c r="H20" s="3">
-        <v>71</v>
+        <v>69.53</v>
       </c>
       <c r="I20" s="3">
-        <v>-29.81</v>
+        <v>-30.43</v>
       </c>
       <c r="J20" s="3">
-        <v>0.023188818679715038</v>
+        <v>0.023095206533151898</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
@@ -1987,12 +2032,14 @@
         <v>-44</v>
       </c>
       <c r="M20" s="3">
-        <v>0.009268622424619233</v>
+        <v>0.006937407366630399</v>
       </c>
       <c r="N20" s="3">
-        <v>27.916666666666664</v>
-      </c>
-      <c r="O20" s="3"/>
+        <v>27.400000000000002</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
@@ -2002,7 +2049,7 @@
         <v>-2.25</v>
       </c>
       <c r="C21" s="3">
-        <v>18.75</v>
+        <v>18</v>
       </c>
       <c r="D21" s="3">
         <v>10.44</v>
@@ -2011,19 +2058,19 @@
         <v>12.21</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.43969939957864956</v>
+        <v>-0.4405830197438053</v>
       </c>
       <c r="G21" s="3">
         <v>2.31</v>
       </c>
       <c r="H21" s="3">
-        <v>54.4</v>
+        <v>53.95</v>
       </c>
       <c r="I21" s="3">
-        <v>-55.05</v>
+        <v>-55.29</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.03547797069677966</v>
+        <v>-0.03561172296348668</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
@@ -2032,12 +2079,14 @@
         <v>17</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.4050962129906889</v>
+        <v>-0.40799486500956095</v>
       </c>
       <c r="N21" s="3">
-        <v>25.625</v>
-      </c>
-      <c r="O21" s="3"/>
+        <v>25.799999999999994</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2047,7 +2096,7 @@
         <v>-2.38</v>
       </c>
       <c r="C22" s="1">
-        <v>16.666666666666664</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1">
         <v>1.4705882352941178</v>
@@ -2056,19 +2105,19 @@
         <v>5.89</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.17120120712554815</v>
+        <v>-0.1655971450178095</v>
       </c>
       <c r="G22" s="1">
         <v>3.13</v>
       </c>
       <c r="H22" s="1">
-        <v>73.51</v>
+        <v>72.8</v>
       </c>
       <c r="I22" s="1">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="J22" s="1">
-        <v>0.03109288839166161</v>
+        <v>0.031117144788648583</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
@@ -2077,12 +2126,14 @@
         <v>43</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.11493801061229914</v>
+        <v>-0.11261029800716793</v>
       </c>
       <c r="N22" s="1">
-        <v>46.04166666666667</v>
-      </c>
-      <c r="O22" s="1"/>
+        <v>46.400000000000006</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -2092,7 +2143,7 @@
         <v>-1.13</v>
       </c>
       <c r="C23" s="3">
-        <v>20.833333333333336</v>
+        <v>20</v>
       </c>
       <c r="D23" s="3">
         <v>5.7522123893805315</v>
@@ -2101,7 +2152,7 @@
         <v>1.42</v>
       </c>
       <c r="F23" s="3">
-        <v>-0.4662787098315891</v>
+        <v>-0.46051095944106835</v>
       </c>
       <c r="G23" s="3">
         <v>2.65</v>
@@ -2113,7 +2164,7 @@
         <v>-33.89</v>
       </c>
       <c r="J23" s="3">
-        <v>-0.012401909198076783</v>
+        <v>-0.012349525627281642</v>
       </c>
       <c r="K23" s="3" t="b">
         <v>0</v>
@@ -2122,12 +2173,14 @@
         <v>37</v>
       </c>
       <c r="M23" s="3">
-        <v>-0.4226945435185089</v>
+        <v>-0.41946481034831784</v>
       </c>
       <c r="N23" s="3">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="O23" s="3"/>
+        <v>24.599999999999998</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -2137,7 +2190,7 @@
         <v>-0.99</v>
       </c>
       <c r="C24" s="3">
-        <v>22.916666666666664</v>
+        <v>22</v>
       </c>
       <c r="D24" s="3">
         <v>3.04040404040404</v>
@@ -2146,19 +2199,19 @@
         <v>3.54</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.40154728528252626</v>
+        <v>-0.400598246421679</v>
       </c>
       <c r="G24" s="3">
         <v>3.24</v>
       </c>
       <c r="H24" s="3">
-        <v>53.77</v>
+        <v>52.34</v>
       </c>
       <c r="I24" s="3">
-        <v>-29.95</v>
+        <v>-30.64</v>
       </c>
       <c r="J24" s="3">
-        <v>-0.01464141824677345</v>
+        <v>-0.014752019382312919</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
@@ -2167,12 +2220,14 @@
         <v>60</v>
       </c>
       <c r="M24" s="3">
-        <v>-0.34237847768173857</v>
+        <v>-0.34487498947152073</v>
       </c>
       <c r="N24" s="3">
-        <v>23.125000000000004</v>
-      </c>
-      <c r="O24" s="3"/>
+        <v>23.200000000000003</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -2182,7 +2237,7 @@
         <v>0.38</v>
       </c>
       <c r="C25" s="4">
-        <v>45.83333333333333</v>
+        <v>44</v>
       </c>
       <c r="D25" s="4">
         <v>89.71052631578947</v>
@@ -2191,19 +2246,19 @@
         <v>2.21</v>
       </c>
       <c r="F25" s="4">
-        <v>-0.3170927581740075</v>
+        <v>-0.31542297047728074</v>
       </c>
       <c r="G25" s="4">
         <v>2.32</v>
       </c>
       <c r="H25" s="4">
-        <v>63.79</v>
+        <v>63.1</v>
       </c>
       <c r="I25" s="4">
-        <v>-19.66</v>
+        <v>-19.91</v>
       </c>
       <c r="J25" s="4">
-        <v>-0.009812260461178298</v>
+        <v>-0.009865523158916659</v>
       </c>
       <c r="K25" s="4" t="b">
         <v>0</v>
@@ -2212,12 +2267,14 @@
         <v>70</v>
       </c>
       <c r="M25" s="4">
-        <v>-0.2822254251235433</v>
+        <v>-0.28258605120308034</v>
       </c>
       <c r="N25" s="4">
-        <v>51.87499999999999</v>
-      </c>
-      <c r="O25" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="O25" s="4">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -2227,7 +2284,7 @@
         <v>1.9</v>
       </c>
       <c r="C26" s="4">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="D26" s="4">
         <v>2990.236842105264</v>
@@ -2236,19 +2293,19 @@
         <v>2.07</v>
       </c>
       <c r="F26" s="4">
-        <v>-0.1547367590902501</v>
+        <v>-0.15608369211525974</v>
       </c>
       <c r="G26" s="4">
         <v>1.2</v>
       </c>
       <c r="H26" s="4">
-        <v>55.52</v>
+        <v>54.45</v>
       </c>
       <c r="I26" s="4">
-        <v>0.85</v>
+        <v>0.38</v>
       </c>
       <c r="J26" s="4">
-        <v>-0.006328987029654367</v>
+        <v>-0.006401082366864428</v>
       </c>
       <c r="K26" s="4" t="b">
         <v>0</v>
@@ -2257,12 +2314,14 @@
         <v>116</v>
       </c>
       <c r="M26" s="4">
-        <v>-0.14945382984017974</v>
+        <v>-0.15110840131613845</v>
       </c>
       <c r="N26" s="4">
-        <v>61.875</v>
-      </c>
-      <c r="O26" s="4"/>
+        <v>60.400000000000006</v>
+      </c>
+      <c r="O26" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
@@ -2272,7 +2331,7 @@
         <v>5.13</v>
       </c>
       <c r="C27" s="2">
-        <v>81.25</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2">
         <v>10.491228070175438</v>
@@ -2281,19 +2340,19 @@
         <v>0.39</v>
       </c>
       <c r="F27" s="2">
-        <v>0.16421433169186833</v>
+        <v>0.1639470722757364</v>
       </c>
       <c r="G27" s="2">
         <v>1.39</v>
       </c>
       <c r="H27" s="2">
-        <v>74.94</v>
+        <v>74.36</v>
       </c>
       <c r="I27" s="2">
-        <v>20.62</v>
+        <v>19.93</v>
       </c>
       <c r="J27" s="2">
-        <v>0.024434924341505217</v>
+        <v>0.024386229289761436</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
@@ -2302,12 +2361,14 @@
         <v>412</v>
       </c>
       <c r="M27" s="2">
-        <v>0.17451604372950547</v>
+        <v>0.1736488893340229</v>
       </c>
       <c r="N27" s="2">
-        <v>75.62500000000001</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>75.2</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2317,7 +2378,7 @@
         <v>-3.07</v>
       </c>
       <c r="C28" s="1">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1">
         <v>8.671009771986972</v>
@@ -2326,19 +2387,19 @@
         <v>2.29</v>
       </c>
       <c r="F28" s="1">
-        <v>0.00989392080333086</v>
+        <v>0.0041394910754501135</v>
       </c>
       <c r="G28" s="1">
         <v>1.69</v>
       </c>
       <c r="H28" s="1">
-        <v>63.26</v>
+        <v>62.1</v>
       </c>
       <c r="I28" s="1">
-        <v>13.66</v>
+        <v>12.57</v>
       </c>
       <c r="J28" s="1">
-        <v>0.0168781609811</v>
+        <v>0.016701733911623943</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -2347,57 +2408,61 @@
         <v>44</v>
       </c>
       <c r="M28" s="1">
-        <v>0.0281200267160735</v>
+        <v>0.02130424433241851</v>
       </c>
       <c r="N28" s="1">
-        <v>43.74999999999999</v>
-      </c>
-      <c r="O28" s="1"/>
+        <v>43.800000000000004</v>
+      </c>
+      <c r="O28" s="1">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>7.4</v>
       </c>
-      <c r="C29" s="1">
-        <v>89.58333333333334</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C29" s="4">
+        <v>88</v>
+      </c>
+      <c r="D29" s="4">
         <v>1.2283783783783782</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="4">
         <v>-0.84</v>
       </c>
-      <c r="F29" s="1">
-        <v>-0.09024617250147376</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="F29" s="4">
+        <v>-0.09146541819570014</v>
+      </c>
+      <c r="G29" s="4">
         <v>1.1</v>
       </c>
-      <c r="H29" s="1">
-        <v>42.46</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="H29" s="4">
+        <v>42.45</v>
+      </c>
+      <c r="I29" s="4">
         <v>-14.49</v>
       </c>
-      <c r="J29" s="1">
-        <v>0.010836343223542119</v>
-      </c>
-      <c r="K29" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="J29" s="4">
+        <v>0.010778051501450026</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
         <v>149</v>
       </c>
-      <c r="M29" s="1">
-        <v>-0.08760470787643859</v>
-      </c>
-      <c r="N29" s="1">
-        <v>49.583333333333336</v>
-      </c>
-      <c r="O29" s="1"/>
+      <c r="M29" s="4">
+        <v>-0.0889777727961395</v>
+      </c>
+      <c r="N29" s="4">
+        <v>50.4</v>
+      </c>
+      <c r="O29" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -2407,7 +2472,7 @@
         <v>5.41</v>
       </c>
       <c r="C30" s="4">
-        <v>83.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="D30" s="4">
         <v>0.6598890942698706</v>
@@ -2416,19 +2481,19 @@
         <v>-0.09</v>
       </c>
       <c r="F30" s="4">
-        <v>-0.11560724672853408</v>
+        <v>-0.11776489135020235</v>
       </c>
       <c r="G30" s="4">
         <v>1.43</v>
       </c>
       <c r="H30" s="4">
-        <v>70.08</v>
+        <v>68.13</v>
       </c>
       <c r="I30" s="4">
-        <v>-14.71</v>
+        <v>-15.24</v>
       </c>
       <c r="J30" s="4">
-        <v>0.016935392611379864</v>
+        <v>0.01682745320942556</v>
       </c>
       <c r="K30" s="4" t="b">
         <v>0</v>
@@ -2437,12 +2502,14 @@
         <v>-63</v>
       </c>
       <c r="M30" s="4">
-        <v>-0.10424894884088287</v>
+        <v>-0.1070680161320916</v>
       </c>
       <c r="N30" s="4">
-        <v>54.375</v>
-      </c>
-      <c r="O30" s="4"/>
+        <v>53.39999999999999</v>
+      </c>
+      <c r="O30" s="4">
+        <v>-0.6</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -2452,7 +2519,7 @@
         <v>-0.74</v>
       </c>
       <c r="C31" s="4">
-        <v>27.083333333333332</v>
+        <v>26</v>
       </c>
       <c r="D31" s="4">
         <v>36.608108108108105</v>
@@ -2461,19 +2528,19 @@
         <v>1.22</v>
       </c>
       <c r="F31" s="4">
-        <v>-0.012600547693719072</v>
+        <v>-0.020539826332099193</v>
       </c>
       <c r="G31" s="4">
         <v>1.05</v>
       </c>
       <c r="H31" s="4">
-        <v>63.53</v>
+        <v>62.82</v>
       </c>
       <c r="I31" s="4">
-        <v>-1.24</v>
+        <v>-1.92</v>
       </c>
       <c r="J31" s="4">
-        <v>0.004536771046019471</v>
+        <v>0.004328291007456379</v>
       </c>
       <c r="K31" s="4" t="b">
         <v>0</v>
@@ -2482,12 +2549,14 @@
         <v>93</v>
       </c>
       <c r="M31" s="4">
-        <v>-0.011279815381201486</v>
+        <v>-0.01929600363231887</v>
       </c>
       <c r="N31" s="4">
-        <v>50.833333333333336</v>
-      </c>
-      <c r="O31" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="O31" s="4">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -2497,7 +2566,7 @@
         <v>-0.18</v>
       </c>
       <c r="C32" s="4">
-        <v>35.41666666666667</v>
+        <v>34</v>
       </c>
       <c r="D32" s="4">
         <v>105.33333333333334</v>
@@ -2506,19 +2575,19 @@
         <v>-4.72</v>
       </c>
       <c r="F32" s="4">
-        <v>0.1381086728940456</v>
+        <v>0.13313544243322997</v>
       </c>
       <c r="G32" s="4">
         <v>1.36</v>
       </c>
       <c r="H32" s="4">
-        <v>75</v>
+        <v>74.22</v>
       </c>
       <c r="I32" s="4">
-        <v>13.25</v>
+        <v>12.57</v>
       </c>
       <c r="J32" s="4">
-        <v>0.02243554574533957</v>
+        <v>0.022292434755870626</v>
       </c>
       <c r="K32" s="4" t="b">
         <v>0</v>
@@ -2527,12 +2596,14 @@
         <v>-11</v>
       </c>
       <c r="M32" s="4">
-        <v>0.14761794554417218</v>
+        <v>0.14209096587164827</v>
       </c>
       <c r="N32" s="4">
-        <v>68.54166666666666</v>
-      </c>
-      <c r="O32" s="4"/>
+        <v>68.39999999999999</v>
+      </c>
+      <c r="O32" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2542,7 +2613,7 @@
         <v>-4.08</v>
       </c>
       <c r="C33" s="1">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="D33" s="1">
         <v>14.372549019607844</v>
@@ -2551,19 +2622,19 @@
         <v>13.14</v>
       </c>
       <c r="F33" s="1">
-        <v>0.0749569552980534</v>
+        <v>0.0794475694006667</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>62.34</v>
+        <v>61.98</v>
       </c>
       <c r="I33" s="1">
-        <v>-7.11</v>
+        <v>-7.32</v>
       </c>
       <c r="J33" s="1">
-        <v>0.04408771991281714</v>
+        <v>0.044189170511191735</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
@@ -2572,12 +2643,14 @@
         <v>20</v>
       </c>
       <c r="M33" s="1">
-        <v>0.04854230904770174</v>
+        <v>0.05457111540506032</v>
       </c>
       <c r="N33" s="1">
-        <v>48.333333333333336</v>
-      </c>
-      <c r="O33" s="1"/>
+        <v>48.2</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2587,7 +2660,7 @@
         <v>-0.48</v>
       </c>
       <c r="C34" s="1">
-        <v>29.166666666666668</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="D34" s="1">
         <v>86.47916666666667</v>
@@ -2596,19 +2669,19 @@
         <v>-1.38</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.27528167947146365</v>
+        <v>-0.28006059158760466</v>
       </c>
       <c r="G34" s="1">
         <v>0.91</v>
       </c>
       <c r="H34" s="1">
-        <v>56.83</v>
+        <v>55.97</v>
       </c>
       <c r="I34" s="1">
-        <v>-32.31</v>
+        <v>-32.6</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.010654340748782016</v>
+        <v>-0.010815020008760702</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
@@ -2617,12 +2690,14 @@
         <v>3</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.27765899763399526</v>
+        <v>-0.2822994724472092</v>
       </c>
       <c r="N34" s="1">
-        <v>42.708333333333336</v>
-      </c>
-      <c r="O34" s="1"/>
+        <v>42.2</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2632,7 +2707,7 @@
         <v>3.52</v>
       </c>
       <c r="C35" s="1">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1">
         <v>1.1988636363636365</v>
@@ -2641,19 +2716,19 @@
         <v>0.4</v>
       </c>
       <c r="F35" s="1">
-        <v>0.04837859130682097</v>
+        <v>0.04342695466623904</v>
       </c>
       <c r="G35" s="1">
         <v>0.38</v>
       </c>
       <c r="H35" s="1">
-        <v>43.38</v>
+        <v>41.35</v>
       </c>
       <c r="I35" s="1">
-        <v>4.13</v>
+        <v>3.54</v>
       </c>
       <c r="J35" s="1">
-        <v>0.007072343136519611</v>
+        <v>0.006968933733247495</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -2662,12 +2737,14 @@
         <v>28</v>
       </c>
       <c r="M35" s="1">
-        <v>0.03200151063160295</v>
+        <v>0.028003553188963082</v>
       </c>
       <c r="N35" s="1">
-        <v>47.083333333333336</v>
-      </c>
-      <c r="O35" s="1"/>
+        <v>46.599999999999994</v>
+      </c>
+      <c r="O35" s="1">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -2677,7 +2754,7 @@
         <v>-0.02</v>
       </c>
       <c r="C36" s="4">
-        <v>39.58333333333333</v>
+        <v>38</v>
       </c>
       <c r="D36" s="4">
         <v>1215</v>
@@ -2686,19 +2763,19 @@
         <v>5.89</v>
       </c>
       <c r="F36" s="4">
-        <v>-0.048296298967170956</v>
+        <v>-0.06133460065223531</v>
       </c>
       <c r="G36" s="4">
         <v>1.38</v>
       </c>
       <c r="H36" s="4">
-        <v>57.58</v>
+        <v>55.75</v>
       </c>
       <c r="I36" s="4">
-        <v>-8.94</v>
+        <v>-10.45</v>
       </c>
       <c r="J36" s="4">
-        <v>0.017724750523772582</v>
+        <v>0.01739455982384013</v>
       </c>
       <c r="K36" s="4" t="b">
         <v>1</v>
@@ -2707,12 +2784,14 @@
         <v>31</v>
       </c>
       <c r="M36" s="4">
-        <v>-0.038258733392037336</v>
+        <v>-0.05188154813390489</v>
       </c>
       <c r="N36" s="4">
-        <v>62.08333333333333</v>
-      </c>
-      <c r="O36" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="O36" s="4">
+        <v>-0.6</v>
+      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -2722,7 +2801,7 @@
         <v>0.94</v>
       </c>
       <c r="C37" s="4">
-        <v>52.083333333333336</v>
+        <v>50</v>
       </c>
       <c r="D37" s="4">
         <v>31.03191489361702</v>
@@ -2731,19 +2810,19 @@
         <v>-0.72</v>
       </c>
       <c r="F37" s="4">
-        <v>-0.15913082613344948</v>
+        <v>-0.16146366087670874</v>
       </c>
       <c r="G37" s="4">
         <v>2.78</v>
       </c>
       <c r="H37" s="4">
-        <v>62.2</v>
+        <v>60.56</v>
       </c>
       <c r="I37" s="4">
-        <v>-5.66</v>
+        <v>-6.56</v>
       </c>
       <c r="J37" s="4">
-        <v>0.010883126809017934</v>
+        <v>0.010724473081475675</v>
       </c>
       <c r="K37" s="4" t="b">
         <v>0</v>
@@ -2752,12 +2831,14 @@
         <v>134</v>
       </c>
       <c r="M37" s="4">
-        <v>-0.11211275580782354</v>
+        <v>-0.1171835727645294</v>
       </c>
       <c r="N37" s="4">
-        <v>57.70833333333334</v>
-      </c>
-      <c r="O37" s="4"/>
+        <v>56.6</v>
+      </c>
+      <c r="O37" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
@@ -2767,7 +2848,7 @@
         <v>3.41</v>
       </c>
       <c r="C38" s="2">
-        <v>72.91666666666666</v>
+        <v>70</v>
       </c>
       <c r="D38" s="2">
         <v>8.926686217008797</v>
@@ -2776,19 +2857,19 @@
         <v>-1.19</v>
       </c>
       <c r="F38" s="2">
-        <v>0.7532144984691509</v>
+        <v>0.7522690315963407</v>
       </c>
       <c r="G38" s="2">
         <v>2.08</v>
       </c>
       <c r="H38" s="2">
-        <v>68.52</v>
+        <v>68.69</v>
       </c>
       <c r="I38" s="2">
-        <v>72.37</v>
+        <v>72.68</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04794036718733313</v>
+        <v>0.04788231480104818</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -2797,12 +2878,14 @@
         <v>234</v>
       </c>
       <c r="M38" s="2">
-        <v>0.7817423164195307</v>
+        <v>0.7791356019115956</v>
       </c>
       <c r="N38" s="2">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>73.4</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
@@ -2812,7 +2895,7 @@
         <v>-0.38</v>
       </c>
       <c r="C39" s="2">
-        <v>31.25</v>
+        <v>30</v>
       </c>
       <c r="D39" s="2">
         <v>325.07894736842104</v>
@@ -2821,19 +2904,19 @@
         <v>3.31</v>
       </c>
       <c r="F39" s="2">
-        <v>0.4244393059541854</v>
+        <v>0.4187112698573938</v>
       </c>
       <c r="G39" s="2">
         <v>3.47</v>
       </c>
       <c r="H39" s="2">
-        <v>73.96</v>
+        <v>73.66</v>
       </c>
       <c r="I39" s="2">
-        <v>120.27</v>
+        <v>118.84</v>
       </c>
       <c r="J39" s="2">
-        <v>0.04318873970246332</v>
+        <v>0.04296879405972401</v>
       </c>
       <c r="K39" s="2" t="b">
         <v>0</v>
@@ -2842,12 +2925,14 @@
         <v>211</v>
       </c>
       <c r="M39" s="2">
-        <v>0.489683482192554</v>
+        <v>0.48015611122654156</v>
       </c>
       <c r="N39" s="2">
-        <v>74.58333333333333</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>74.39999999999999</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2857,7 +2942,7 @@
         <v>-0.32</v>
       </c>
       <c r="C40" s="1">
-        <v>33.33333333333333</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1">
         <v>228.28125</v>
@@ -2866,19 +2951,19 @@
         <v>3.34</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.20047544049218177</v>
+        <v>-0.2007982514277325</v>
       </c>
       <c r="G40" s="1">
         <v>1.68</v>
       </c>
       <c r="H40" s="1">
-        <v>45.97</v>
+        <v>43.52</v>
       </c>
       <c r="I40" s="1">
-        <v>-3.8</v>
+        <v>-5.97</v>
       </c>
       <c r="J40" s="1">
-        <v>-0.01178367415794677</v>
+        <v>-0.011845693448925713</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -2887,12 +2972,14 @@
         <v>11</v>
       </c>
       <c r="M40" s="1">
-        <v>-0.18251348104194265</v>
+        <v>-0.18388226271072017</v>
       </c>
       <c r="N40" s="1">
-        <v>46.041666666666664</v>
-      </c>
-      <c r="O40" s="1"/>
+        <v>45.400000000000006</v>
+      </c>
+      <c r="O40" s="1">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
@@ -2902,7 +2989,7 @@
         <v>-2.92</v>
       </c>
       <c r="C41" s="3">
-        <v>14.583333333333334</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="D41" s="3">
         <v>-23.77054794520548</v>
@@ -2911,19 +2998,19 @@
         <v>16.88</v>
       </c>
       <c r="F41" s="3">
-        <v>0.1549289351552015</v>
+        <v>0.16678258034043136</v>
       </c>
       <c r="G41" s="3">
         <v>1.95</v>
       </c>
       <c r="H41" s="3">
-        <v>70.81</v>
+        <v>71.02</v>
       </c>
       <c r="I41" s="3">
-        <v>31.67</v>
+        <v>32.21</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.012185710379580567</v>
+        <v>-0.012003514083289334</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -2932,12 +3019,14 @@
         <v>83</v>
       </c>
       <c r="M41" s="3">
-        <v>0.18002284909303556</v>
+        <v>0.1904152116362574</v>
       </c>
       <c r="N41" s="3">
-        <v>25.625</v>
-      </c>
-      <c r="O41" s="3"/>
+        <v>25.800000000000004</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -2947,7 +3036,7 @@
         <v>4.88</v>
       </c>
       <c r="C42" s="4">
-        <v>77.08333333333334</v>
+        <v>74</v>
       </c>
       <c r="D42" s="4">
         <v>6.178278688524591</v>
@@ -2956,19 +3045,19 @@
         <v>-0.19</v>
       </c>
       <c r="F42" s="4">
-        <v>0.11548747115132582</v>
+        <v>0.11162120817244162</v>
       </c>
       <c r="G42" s="4">
         <v>1.85</v>
       </c>
       <c r="H42" s="4">
-        <v>61.04</v>
+        <v>59.95</v>
       </c>
       <c r="I42" s="4">
-        <v>56.14</v>
+        <v>55.15</v>
       </c>
       <c r="J42" s="4">
-        <v>0.017137808683028773</v>
+        <v>0.01700763705192206</v>
       </c>
       <c r="K42" s="4" t="b">
         <v>0</v>
@@ -2977,12 +3066,14 @@
         <v>300</v>
       </c>
       <c r="M42" s="4">
-        <v>0.13793992046412473</v>
+        <v>0.13276619406870704</v>
       </c>
       <c r="N42" s="4">
-        <v>64.58333333333334</v>
-      </c>
-      <c r="O42" s="4"/>
+        <v>64.39999999999999</v>
+      </c>
+      <c r="O42" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2992,7 +3083,7 @@
         <v>-0.76</v>
       </c>
       <c r="C43" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43" s="1">
         <v>13.236842105263158</v>
@@ -3001,19 +3092,19 @@
         <v>7.72</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.38174499445726107</v>
+        <v>-0.3845729028929534</v>
       </c>
       <c r="G43" s="1">
         <v>2.61</v>
       </c>
       <c r="H43" s="1">
-        <v>56.14</v>
+        <v>54.93</v>
       </c>
       <c r="I43" s="1">
-        <v>-31.84</v>
+        <v>-32.36</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.01874205106563216</v>
+        <v>-0.01893993006080149</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>1</v>
@@ -3022,12 +3113,14 @@
         <v>64</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.3392174139941949</v>
+        <v>-0.3445218119600272</v>
       </c>
       <c r="N43" s="1">
-        <v>31.666666666666664</v>
-      </c>
-      <c r="O43" s="1"/>
+        <v>31.599999999999998</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -3037,7 +3130,7 @@
         <v>0.54</v>
       </c>
       <c r="C44" s="4">
-        <v>47.91666666666667</v>
+        <v>46</v>
       </c>
       <c r="D44" s="4">
         <v>41.629629629629626</v>
@@ -3052,10 +3145,10 @@
         <v>1.41</v>
       </c>
       <c r="H44" s="4">
-        <v>63.64</v>
+        <v>62.96</v>
       </c>
       <c r="I44" s="4">
-        <v>-3.37</v>
+        <v>-3.92</v>
       </c>
       <c r="J44" s="4">
         <v>0</v>
@@ -3070,9 +3163,11 @@
         <v>0</v>
       </c>
       <c r="N44" s="4">
-        <v>55.83333333333333</v>
-      </c>
-      <c r="O44" s="4"/>
+        <v>55.199999999999996</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
@@ -3082,7 +3177,7 @@
         <v>0.95</v>
       </c>
       <c r="C45" s="2">
-        <v>54.166666666666664</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2">
         <v>14.789473684210527</v>
@@ -3091,7 +3186,7 @@
         <v>2.01</v>
       </c>
       <c r="F45" s="2">
-        <v>0.31067145981052635</v>
+        <v>0.31197289663961014</v>
       </c>
       <c r="G45" s="2">
         <v>0.8</v>
@@ -3103,7 +3198,7 @@
         <v>36.93</v>
       </c>
       <c r="J45" s="2">
-        <v>0.026608906205351935</v>
+        <v>0.026610161244824973</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
@@ -3112,192 +3207,296 @@
         <v>11</v>
       </c>
       <c r="M45" s="2">
-        <v>0.305388530560456</v>
+        <v>0.30699760584048885</v>
       </c>
       <c r="N45" s="2">
-        <v>72.08333333333333</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="4">
-        <v>1.94</v>
+        <v>6.11</v>
       </c>
       <c r="C46" s="4">
-        <v>64.58333333333334</v>
+        <v>82</v>
       </c>
       <c r="D46" s="4">
-        <v>1.1030927835051547</v>
+        <v>0.6121112929623567</v>
       </c>
       <c r="E46" s="4">
-        <v>0.54</v>
+        <v>-2.35</v>
       </c>
       <c r="F46" s="4">
-        <v>0.04356416389380155</v>
+        <v>0.2268171383624703</v>
       </c>
       <c r="G46" s="4">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="H46" s="4">
-        <v>70.05</v>
+        <v>70.66</v>
       </c>
       <c r="I46" s="4">
-        <v>22.64</v>
+        <v>21.83</v>
       </c>
       <c r="J46" s="4">
-        <v>0.008830482815401951</v>
+        <v>0.014065204785143063</v>
       </c>
       <c r="K46" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M46" s="4">
-        <v>0.03669635586871012</v>
+        <v>0.2235831993430415</v>
       </c>
       <c r="N46" s="4">
-        <v>52.91666666666667</v>
-      </c>
-      <c r="O46" s="4"/>
+        <v>58.8</v>
+      </c>
+      <c r="O46" s="4">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B47" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="C47" s="4">
+        <v>62</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1.1030927835051547</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0.04217143679343387</v>
+      </c>
+      <c r="G47" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="H47" s="4">
+        <v>69.66</v>
+      </c>
+      <c r="I47" s="4">
+        <v>22.32</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0.008776966289988017</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>23</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0.0357035587545762</v>
+      </c>
+      <c r="N47" s="4">
+        <v>53.2</v>
+      </c>
+      <c r="O47" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="4">
         <v>2.84</v>
       </c>
-      <c r="C47" s="4">
-        <v>68.75</v>
-      </c>
-      <c r="D47" s="4">
+      <c r="C48" s="4">
+        <v>66</v>
+      </c>
+      <c r="D48" s="4">
         <v>2.0880281690140845</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E48" s="4">
         <v>0.95</v>
       </c>
-      <c r="F47" s="4">
-        <v>0.18093353280757316</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="F48" s="4">
+        <v>0.1842640237296823</v>
+      </c>
+      <c r="G48" s="4">
         <v>0.88</v>
       </c>
-      <c r="H47" s="4">
-        <v>72.82</v>
-      </c>
-      <c r="I47" s="4">
-        <v>19.81</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0.004465546501666247</v>
-      </c>
-      <c r="K47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4">
+      <c r="H48" s="4">
+        <v>73.46</v>
+      </c>
+      <c r="I48" s="4">
+        <v>20.33</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0.004501832495174733</v>
+      </c>
+      <c r="K48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
         <v>248</v>
       </c>
-      <c r="M47" s="4">
-        <v>0.17776377525753095</v>
-      </c>
-      <c r="N47" s="4">
-        <v>56.666666666666664</v>
-      </c>
-      <c r="O47" s="4"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" s="2">
-        <v>8.72</v>
-      </c>
-      <c r="C48" s="2">
-        <v>91.66666666666666</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0.8061926605504586</v>
-      </c>
-      <c r="E48" s="2">
-        <v>6.35</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0.873048360184754</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0.96</v>
-      </c>
-      <c r="H48" s="2">
-        <v>72.13</v>
-      </c>
-      <c r="I48" s="2">
-        <v>52.56</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0.05270914285945323</v>
-      </c>
-      <c r="K48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>115</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0.8719917743347398</v>
-      </c>
-      <c r="N48" s="2">
-        <v>71.875</v>
-      </c>
-      <c r="O48" s="2"/>
+      <c r="M48" s="4">
+        <v>0.18127884925020954</v>
+      </c>
+      <c r="N48" s="4">
+        <v>57.400000000000006</v>
+      </c>
+      <c r="O48" s="4">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B49" s="4">
+        <v>20.88</v>
+      </c>
+      <c r="C49" s="4">
+        <v>98</v>
+      </c>
+      <c r="D49" s="4">
+        <v>-0.7054597701149425</v>
+      </c>
+      <c r="E49" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0.002233231868567248</v>
+      </c>
+      <c r="G49" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="H49" s="4">
+        <v>63.33</v>
+      </c>
+      <c r="I49" s="4">
+        <v>3.52</v>
+      </c>
+      <c r="J49" s="4">
+        <v>-0.0010066168117376939</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <v>318</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0.0034770545683475707</v>
+      </c>
+      <c r="N49" s="4">
+        <v>50.4</v>
+      </c>
+      <c r="O49" s="4">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="2">
+        <v>8.72</v>
+      </c>
+      <c r="C50" s="2">
+        <v>90</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0.8061926605504586</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6.35</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.8831681458235491</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="H50" s="2">
+        <v>72.55</v>
+      </c>
+      <c r="I50" s="2">
+        <v>53.49</v>
+      </c>
+      <c r="J50" s="2">
+        <v>0.05283941505704367</v>
+      </c>
+      <c r="K50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>115</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0.8821730876637248</v>
+      </c>
+      <c r="N50" s="2">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="O50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="4">
         <v>10.45</v>
       </c>
-      <c r="C49" s="4">
-        <v>95.83333333333334</v>
-      </c>
-      <c r="D49" s="4">
+      <c r="C51" s="4">
+        <v>94</v>
+      </c>
+      <c r="D51" s="4">
         <v>0.4545454545454546</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E51" s="4">
         <v>-0.36</v>
       </c>
-      <c r="F49" s="4">
-        <v>0.177434564940825</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="F51" s="4">
+        <v>0.1777696584470837</v>
+      </c>
+      <c r="G51" s="4">
         <v>1.2</v>
       </c>
-      <c r="H49" s="4">
-        <v>68.18</v>
-      </c>
-      <c r="I49" s="4">
-        <v>14.22</v>
-      </c>
-      <c r="J49" s="4">
-        <v>0.010713778808231215</v>
-      </c>
-      <c r="K49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4">
+      <c r="H51" s="4">
+        <v>68.11</v>
+      </c>
+      <c r="I51" s="4">
+        <v>14.17</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0.0106861724220283</v>
+      </c>
+      <c r="K51" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4">
         <v>133</v>
       </c>
-      <c r="M49" s="4">
-        <v>0.18271749419089534</v>
-      </c>
-      <c r="N49" s="4">
-        <v>57.91666666666667</v>
-      </c>
-      <c r="O49" s="4"/>
+      <c r="M51" s="4">
+        <v>0.182744949246205</v>
+      </c>
+      <c r="N51" s="4">
+        <v>57.80000000000001</v>
+      </c>
+      <c r="O51" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3307,15 +3506,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3323,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>44.375</v>
+        <v>43.800000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3331,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>77.29166666666666</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3339,7 +3538,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24.583333333333332</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3347,7 +3546,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51.66666666666667</v>
+        <v>50.800000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3355,7 +3554,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>49.375</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3363,7 +3562,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>61.875</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3371,7 +3570,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>62.708333333333336</v>
+        <v>63.599999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3379,7 +3578,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>52.29166666666667</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3387,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>46.875</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3395,7 +3594,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>22.916666666666668</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3403,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>40.208333333333336</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3411,7 +3610,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>75.625</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3419,7 +3618,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>49.791666666666664</v>
+        <v>50.199999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3427,7 +3626,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>36.25</v>
+        <v>36.400000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3435,7 +3634,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>63.125</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3443,7 +3642,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>49.166666666666664</v>
+        <v>48.99999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3451,7 +3650,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>53.54166666666667</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3459,7 +3658,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>43.958333333333336</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3467,7 +3666,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.916666666666664</v>
+        <v>27.400000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3475,7 +3674,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.625</v>
+        <v>25.799999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3483,7 +3682,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>46.04166666666667</v>
+        <v>46.400000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3491,7 +3690,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>24.16666666666667</v>
+        <v>24.599999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3499,7 +3698,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>23.125000000000004</v>
+        <v>23.200000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3507,7 +3706,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>51.87499999999999</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3515,7 +3714,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>61.875</v>
+        <v>60.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3523,7 +3722,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>75.62500000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3531,7 +3730,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>43.74999999999999</v>
+        <v>43.800000000000004</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3539,7 +3738,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49.583333333333336</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3547,7 +3746,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>54.375</v>
+        <v>53.39999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -3555,7 +3754,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>50.833333333333336</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3563,7 +3762,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>68.54166666666666</v>
+        <v>68.39999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3571,7 +3770,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>48.333333333333336</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3579,7 +3778,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>42.708333333333336</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3587,7 +3786,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>47.083333333333336</v>
+        <v>46.599999999999994</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -3595,7 +3794,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>62.08333333333333</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3603,7 +3802,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>57.70833333333334</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -3611,7 +3810,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>73.33333333333333</v>
+        <v>73.4</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -3619,7 +3818,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>74.58333333333333</v>
+        <v>74.39999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3627,7 +3826,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>46.041666666666664</v>
+        <v>45.400000000000006</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -3635,7 +3834,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>25.625</v>
+        <v>25.800000000000004</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -3643,7 +3842,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>64.58333333333334</v>
+        <v>64.39999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -3651,7 +3850,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>31.666666666666664</v>
+        <v>31.599999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3659,7 +3858,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>55.83333333333333</v>
+        <v>55.199999999999996</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -3667,7 +3866,7 @@
         <v>58</v>
       </c>
       <c r="B45">
-        <v>72.08333333333333</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -3675,7 +3874,7 @@
         <v>59</v>
       </c>
       <c r="B46">
-        <v>52.91666666666667</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -3683,7 +3882,7 @@
         <v>60</v>
       </c>
       <c r="B47">
-        <v>56.666666666666664</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -3691,7 +3890,7 @@
         <v>61</v>
       </c>
       <c r="B48">
-        <v>71.875</v>
+        <v>57.400000000000006</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -3699,7 +3898,23 @@
         <v>62</v>
       </c>
       <c r="B49">
-        <v>57.91666666666667</v>
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50">
+        <v>72.39999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51">
+        <v>57.80000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3718,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3729,10 +3944,10 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3740,106 +3955,109 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3858,117 +4076,120 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3987,117 +4208,117 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4116,128 +4337,128 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4253,16 +4474,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4270,213 +4491,213 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
         <v>129</v>
       </c>
-      <c r="B10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="172">
   <si>
     <t>Ticker</t>
   </si>
@@ -192,34 +192,118 @@
     <t>Composite_Score</t>
   </si>
   <si>
+    <t>Earnings_Date</t>
+  </si>
+  <si>
     <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2027-03-04</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2027-02-26</t>
+  </si>
+  <si>
+    <t>2027-02-12</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>2027-02-24</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
+    <t>2027-02-18</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
     <t>WSR</t>
   </si>
   <si>
     <t>BLX</t>
   </si>
   <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
     <t>MD</t>
   </si>
   <si>
     <t>CSCO</t>
   </si>
   <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
     <t>JPM</t>
   </si>
   <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
     <t>DELL</t>
   </si>
   <si>
     <t>ETN</t>
   </si>
   <si>
+    <t>2027-02-03</t>
+  </si>
+  <si>
     <t>_date_</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -1098,10 +1182,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1147,8 +1231,11 @@
       <c r="O1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1165,19 +1252,19 @@
         <v>-0.01</v>
       </c>
       <c r="F2" s="1">
-        <v>0.11967941242595193</v>
+        <v>0.12180671561557217</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>39.49</v>
+        <v>40.62</v>
       </c>
       <c r="I2" s="1">
-        <v>17.22</v>
+        <v>17.71</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0023737785663199627</v>
+        <v>0.002404876827358358</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -1186,16 +1273,19 @@
         <v>364</v>
       </c>
       <c r="M2" s="1">
-        <v>0.09928072014955469</v>
+        <v>0.10271827784503751</v>
       </c>
       <c r="N2" s="1">
         <v>43.800000000000004</v>
       </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1212,19 +1302,19 @@
         <v>2.75</v>
       </c>
       <c r="F3" s="2">
-        <v>0.15876698515967727</v>
+        <v>0.16600313720455306</v>
       </c>
       <c r="G3" s="2">
         <v>2.1</v>
       </c>
       <c r="H3" s="2">
-        <v>78.96</v>
+        <v>79.17</v>
       </c>
       <c r="I3" s="2">
-        <v>38.57</v>
+        <v>39</v>
       </c>
       <c r="J3" s="2">
-        <v>0.02705586046568028</v>
+        <v>0.02714173332106283</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -1233,16 +1323,19 @@
         <v>375</v>
       </c>
       <c r="M3" s="2">
-        <v>0.18613108455484428</v>
+        <v>0.1916095781162459</v>
       </c>
       <c r="N3" s="2">
         <v>77</v>
       </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,19 +1352,19 @@
         <v>4.7</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.3033310828445169</v>
+        <v>-0.3021002404144685</v>
       </c>
       <c r="G4" s="3">
         <v>1.18</v>
       </c>
       <c r="H4" s="3">
-        <v>48.95</v>
+        <v>48.5</v>
       </c>
       <c r="I4" s="3">
-        <v>-27.88</v>
+        <v>-28.15</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.01446289471733941</v>
+        <v>-0.014479168880212931</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
@@ -1280,16 +1373,19 @@
         <v>50</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.2988533211253077</v>
+        <v>-0.2979100955380096</v>
       </c>
       <c r="N4" s="3">
         <v>24.6</v>
       </c>
-      <c r="O4" s="3">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1306,19 +1402,19 @@
         <v>0.58</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.12866175509386943</v>
+        <v>-0.12558638884002832</v>
       </c>
       <c r="G5" s="4">
         <v>1.85</v>
       </c>
       <c r="H5" s="4">
-        <v>54.34</v>
+        <v>54.26</v>
       </c>
       <c r="I5" s="4">
-        <v>-2.85</v>
+        <v>-2.89</v>
       </c>
       <c r="J5" s="4">
-        <v>-0.004851686507586286</v>
+        <v>-0.004849132590616535</v>
       </c>
       <c r="K5" s="4" t="b">
         <v>0</v>
@@ -1327,16 +1423,19 @@
         <v>312</v>
       </c>
       <c r="M5" s="4">
-        <v>-0.107516769197604</v>
+        <v>-0.10579959359008384</v>
       </c>
       <c r="N5" s="4">
-        <v>50.800000000000004</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1353,19 +1452,19 @@
         <v>-2.3</v>
       </c>
       <c r="F6" s="1">
-        <v>0.016374056771371423</v>
+        <v>0.014610241897089274</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>41.41</v>
+        <v>40.85</v>
       </c>
       <c r="I6" s="1">
-        <v>-11.78</v>
+        <v>-12.14</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02093980443525671</v>
+        <v>0.020856540179318855</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -1374,16 +1473,19 @@
         <v>139</v>
       </c>
       <c r="M6" s="1">
-        <v>0.03129992916873525</v>
+        <v>0.028577391485285375</v>
       </c>
       <c r="N6" s="1">
         <v>49.6</v>
       </c>
-      <c r="O6" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1400,19 +1502,19 @@
         <v>0.37</v>
       </c>
       <c r="F7" s="4">
-        <v>0.05439778654196077</v>
+        <v>0.06350472870759938</v>
       </c>
       <c r="G7" s="4">
         <v>2.29</v>
       </c>
       <c r="H7" s="4">
-        <v>67.39</v>
+        <v>68.37</v>
       </c>
       <c r="I7" s="4">
-        <v>9.64</v>
+        <v>9.94</v>
       </c>
       <c r="J7" s="4">
-        <v>0.011349021721240592</v>
+        <v>0.011455554262271794</v>
       </c>
       <c r="K7" s="4" t="b">
         <v>0</v>
@@ -1421,16 +1523,19 @@
         <v>434</v>
       </c>
       <c r="M7" s="4">
-        <v>0.086488412196293</v>
+        <v>0.09353410032222098</v>
       </c>
       <c r="N7" s="4">
+        <v>61.6</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1447,19 +1552,19 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="4">
-        <v>0.018164476427022368</v>
+        <v>0.008845260747195292</v>
       </c>
       <c r="G8" s="4">
         <v>0.5</v>
       </c>
       <c r="H8" s="4">
-        <v>80.91</v>
+        <v>80.5</v>
       </c>
       <c r="I8" s="4">
-        <v>12.46</v>
+        <v>11.86</v>
       </c>
       <c r="J8" s="4">
-        <v>0.016899589420790572</v>
+        <v>0.0166585638880483</v>
       </c>
       <c r="K8" s="4" t="b">
         <v>0</v>
@@ -1468,16 +1573,19 @@
         <v>69</v>
       </c>
       <c r="M8" s="4">
-        <v>0.005726249429219177</v>
+        <v>-0.002794030576301454</v>
       </c>
       <c r="N8" s="4">
-        <v>63.599999999999994</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>62.99999999999999</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="4">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -1494,19 +1602,19 @@
         <v>1.75</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.17753265067641916</v>
+        <v>-0.17610346672917965</v>
       </c>
       <c r="G9" s="4">
         <v>1.6</v>
       </c>
       <c r="H9" s="4">
-        <v>52.36</v>
+        <v>52.06</v>
       </c>
       <c r="I9" s="4">
-        <v>-10.8</v>
+        <v>-10.99</v>
       </c>
       <c r="J9" s="4">
-        <v>0.001840994302116228</v>
+        <v>0.0018145549127325065</v>
       </c>
       <c r="K9" s="4" t="b">
         <v>0</v>
@@ -1515,16 +1623,19 @@
         <v>189</v>
       </c>
       <c r="M9" s="4">
-        <v>-0.16260677827905534</v>
+        <v>-0.16213631714098353</v>
       </c>
       <c r="N9" s="4">
         <v>52</v>
       </c>
-      <c r="O9" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1541,19 +1652,19 @@
         <v>0.88</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.0974824182303593</v>
+        <v>-0.09625307728316178</v>
       </c>
       <c r="G10" s="1">
         <v>1.45</v>
       </c>
       <c r="H10" s="1">
-        <v>62.54</v>
+        <v>60.93</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.04</v>
+        <v>-5.42</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.0010052609990238268</v>
+        <v>-0.0010288684836846146</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -1562,16 +1673,19 @@
         <v>56</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.08628801393233643</v>
+        <v>-0.0857777150920147</v>
       </c>
       <c r="N10" s="1">
-        <v>48.4</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.00000000000001</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="1">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1588,19 +1702,19 @@
         <v>10.01</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.23513531228157736</v>
+        <v>-0.23176875548911732</v>
       </c>
       <c r="G11" s="3">
         <v>1.41</v>
       </c>
       <c r="H11" s="3">
-        <v>47.58</v>
+        <v>47.54</v>
       </c>
       <c r="I11" s="3">
-        <v>-1.59</v>
+        <v>-1.62</v>
       </c>
       <c r="J11" s="3">
-        <v>-0.012954170042827666</v>
+        <v>-0.012928365562974076</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>1</v>
@@ -1609,16 +1723,19 @@
         <v>28</v>
       </c>
       <c r="M11" s="3">
-        <v>-0.22493596614337874</v>
+        <v>-0.22222453660385</v>
       </c>
       <c r="N11" s="3">
         <v>22</v>
       </c>
-      <c r="O11" s="3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1635,19 +1752,19 @@
         <v>0.13</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.13422061465190438</v>
+        <v>-0.13213082696331171</v>
       </c>
       <c r="G12" s="1">
         <v>0.63</v>
       </c>
       <c r="H12" s="1">
-        <v>54.75</v>
+        <v>54.73</v>
       </c>
       <c r="I12" s="1">
-        <v>-10.23</v>
+        <v>-10.24</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.014605975442797736</v>
+        <v>-0.014581685102632282</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
@@ -1656,16 +1773,19 @@
         <v>10</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.14342490263027874</v>
+        <v>-0.1407439025426993</v>
       </c>
       <c r="N12" s="1">
-        <v>40.2</v>
-      </c>
-      <c r="O12" s="1">
+        <v>40.400000000000006</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P12" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1682,19 +1802,19 @@
         <v>6.17</v>
       </c>
       <c r="F13" s="2">
-        <v>0.31368202773667075</v>
+        <v>0.3190176654298967</v>
       </c>
       <c r="G13" s="2">
         <v>1.66</v>
       </c>
       <c r="H13" s="2">
-        <v>70.84</v>
+        <v>70.69</v>
       </c>
       <c r="I13" s="2">
-        <v>75.58</v>
+        <v>75.24</v>
       </c>
       <c r="J13" s="2">
-        <v>0.03695105739468107</v>
+        <v>0.03700547750273439</v>
       </c>
       <c r="K13" s="2" t="b">
         <v>0</v>
@@ -1703,16 +1823,19 @@
         <v>249</v>
       </c>
       <c r="M13" s="2">
-        <v>0.33010048737377096</v>
+        <v>0.3343815299769124</v>
       </c>
       <c r="N13" s="2">
         <v>75.2</v>
       </c>
-      <c r="O13" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -1729,19 +1852,19 @@
         <v>2.52</v>
       </c>
       <c r="F14" s="4">
-        <v>0.15078708560651521</v>
+        <v>0.1580303166649597</v>
       </c>
       <c r="G14" s="4">
         <v>2.06</v>
       </c>
       <c r="H14" s="4">
-        <v>64.43</v>
+        <v>64.17</v>
       </c>
       <c r="I14" s="4">
-        <v>18.63</v>
+        <v>18.3</v>
       </c>
       <c r="J14" s="4">
-        <v>0.019829962781969673</v>
+        <v>0.019907417632426136</v>
       </c>
       <c r="K14" s="4" t="b">
         <v>0</v>
@@ -1750,16 +1873,19 @@
         <v>27</v>
       </c>
       <c r="M14" s="4">
-        <v>0.177156126841858</v>
+        <v>0.1827056142707728</v>
       </c>
       <c r="N14" s="4">
         <v>50.199999999999996</v>
       </c>
-      <c r="O14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1776,19 +1902,19 @@
         <v>4.53</v>
       </c>
       <c r="F15" s="1">
-        <v>0.022359621987671996</v>
+        <v>0.019977546439078106</v>
       </c>
       <c r="G15" s="1">
         <v>1.84</v>
       </c>
       <c r="H15" s="1">
-        <v>62</v>
+        <v>60.37</v>
       </c>
       <c r="I15" s="1">
-        <v>0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="J15" s="1">
-        <v>0.014271758714584973</v>
+        <v>0.014163228691075109</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>0</v>
@@ -1797,16 +1923,19 @@
         <v>43</v>
       </c>
       <c r="M15" s="1">
-        <v>0.04325584334398136</v>
+        <v>0.039531555862552636</v>
       </c>
       <c r="N15" s="1">
-        <v>36.400000000000006</v>
-      </c>
-      <c r="O15" s="1">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>35.8</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P15" s="1">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -1823,19 +1952,19 @@
         <v>11.11</v>
       </c>
       <c r="F16" s="4">
-        <v>-0.08136562225678619</v>
+        <v>-0.07720150533687542</v>
       </c>
       <c r="G16" s="4">
         <v>1.23</v>
       </c>
       <c r="H16" s="4">
-        <v>66.22</v>
+        <v>65.26</v>
       </c>
       <c r="I16" s="4">
-        <v>22.47</v>
+        <v>21.48</v>
       </c>
       <c r="J16" s="4">
-        <v>-0.003532875449604242</v>
+        <v>-0.0034812260130050077</v>
       </c>
       <c r="K16" s="4" t="b">
         <v>0</v>
@@ -1844,16 +1973,19 @@
         <v>32</v>
       </c>
       <c r="M16" s="4">
-        <v>-0.07564403783779672</v>
+        <v>-0.07184743132806692</v>
       </c>
       <c r="N16" s="4">
-        <v>62.6</v>
-      </c>
-      <c r="O16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>62.2</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P16" s="4">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1870,19 +2002,19 @@
         <v>4.52</v>
       </c>
       <c r="F17" s="1">
-        <v>0.11748865655087395</v>
+        <v>0.11892421787726136</v>
       </c>
       <c r="G17" s="1">
         <v>0.17</v>
       </c>
       <c r="H17" s="1">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="I17" s="1">
-        <v>15.38</v>
+        <v>15.37</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.0025026903760530404</v>
+        <v>-0.0024820169527348685</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
@@ -1891,16 +2023,19 @@
         <v>94</v>
       </c>
       <c r="M17" s="1">
-        <v>0.09684119973452066</v>
+        <v>0.09960299428025676</v>
       </c>
       <c r="N17" s="1">
         <v>48.99999999999999</v>
       </c>
-      <c r="O17" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -1917,19 +2052,19 @@
         <v>-1.85</v>
       </c>
       <c r="F18" s="4">
-        <v>-0.0675655590646727</v>
+        <v>-0.06216288328514526</v>
       </c>
       <c r="G18" s="4">
         <v>1.14</v>
       </c>
       <c r="H18" s="4">
-        <v>69.08</v>
+        <v>68.57</v>
       </c>
       <c r="I18" s="4">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="J18" s="4">
-        <v>-0.0007267240423029835</v>
+        <v>-0.0006459754597089684</v>
       </c>
       <c r="K18" s="4" t="b">
         <v>0</v>
@@ -1938,16 +2073,19 @@
         <v>4</v>
       </c>
       <c r="M18" s="4">
-        <v>-0.0640828555052878</v>
+        <v>-0.058903881714566175</v>
       </c>
       <c r="N18" s="4">
-        <v>54.2</v>
-      </c>
-      <c r="O18" s="4">
+        <v>54.4</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P18" s="4">
         <v>0.2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1964,19 +2102,19 @@
         <v>3.37</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.055505071827900376</v>
+        <v>-0.05935038914566073</v>
       </c>
       <c r="G19" s="1">
         <v>1.31</v>
       </c>
       <c r="H19" s="1">
-        <v>43.15</v>
+        <v>42.55</v>
       </c>
       <c r="I19" s="1">
-        <v>-6.89</v>
+        <v>-7.32</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.027605050492327275</v>
+        <v>-0.0277028045198283</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>1</v>
@@ -1985,16 +2123,19 @@
         <v>-7</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.047793371089262404</v>
+        <v>-0.052134028525092746</v>
       </c>
       <c r="N19" s="1">
         <v>42.8</v>
       </c>
-      <c r="O19" s="1">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2011,19 +2152,19 @@
         <v>8.76</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.05948272480163863</v>
+        <v>-0.046129321572840026</v>
       </c>
       <c r="G20" s="3">
         <v>3.67</v>
       </c>
       <c r="H20" s="3">
-        <v>69.53</v>
+        <v>69.32</v>
       </c>
       <c r="I20" s="3">
-        <v>-30.43</v>
+        <v>-30.52</v>
       </c>
       <c r="J20" s="3">
-        <v>0.023095206533151898</v>
+        <v>0.02327639229910378</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
@@ -2032,16 +2173,19 @@
         <v>-44</v>
       </c>
       <c r="M20" s="3">
-        <v>0.006937407366630399</v>
+        <v>0.01602449409463258</v>
       </c>
       <c r="N20" s="3">
-        <v>27.400000000000002</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>27.6</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -2058,19 +2202,19 @@
         <v>12.21</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.4405830197438053</v>
+        <v>-0.43978668983249797</v>
       </c>
       <c r="G21" s="3">
         <v>2.31</v>
       </c>
       <c r="H21" s="3">
-        <v>53.95</v>
+        <v>52.84</v>
       </c>
       <c r="I21" s="3">
-        <v>-55.29</v>
+        <v>-55.91</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.03561172296348668</v>
+        <v>-0.035698987635985606</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
@@ -2079,16 +2223,19 @@
         <v>17</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.40799486500956095</v>
+        <v>-0.4092917465649365</v>
       </c>
       <c r="N21" s="3">
         <v>25.799999999999994</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -2105,19 +2252,19 @@
         <v>5.89</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.1655971450178095</v>
+        <v>-0.15052865140437732</v>
       </c>
       <c r="G22" s="1">
         <v>3.13</v>
       </c>
       <c r="H22" s="1">
-        <v>72.8</v>
+        <v>74.05</v>
       </c>
       <c r="I22" s="1">
-        <v>0.29</v>
+        <v>1.2</v>
       </c>
       <c r="J22" s="1">
-        <v>0.031117144788648583</v>
+        <v>0.031426437562972816</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
@@ -2126,16 +2273,19 @@
         <v>43</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.11261029800716793</v>
+        <v>-0.1009452703662812</v>
       </c>
       <c r="N22" s="1">
-        <v>46.400000000000006</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>47.400000000000006</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -2152,19 +2302,19 @@
         <v>1.42</v>
       </c>
       <c r="F23" s="3">
-        <v>-0.46051095944106835</v>
+        <v>-0.4583078229640903</v>
       </c>
       <c r="G23" s="3">
         <v>2.65</v>
       </c>
       <c r="H23" s="3">
-        <v>49.67</v>
+        <v>49.05</v>
       </c>
       <c r="I23" s="3">
-        <v>-33.89</v>
+        <v>-34.15</v>
       </c>
       <c r="J23" s="3">
-        <v>-0.012349525627281642</v>
+        <v>-0.012412428446676022</v>
       </c>
       <c r="K23" s="3" t="b">
         <v>0</v>
@@ -2173,16 +2323,19 @@
         <v>37</v>
       </c>
       <c r="M23" s="3">
-        <v>-0.41946481034831784</v>
+        <v>-0.419898161596551</v>
       </c>
       <c r="N23" s="3">
         <v>24.599999999999998</v>
       </c>
-      <c r="O23" s="3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -2199,16 +2352,16 @@
         <v>3.54</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.400598246421679</v>
+        <v>-0.39542114325217326</v>
       </c>
       <c r="G24" s="3">
         <v>3.24</v>
       </c>
       <c r="H24" s="3">
-        <v>52.34</v>
+        <v>51.83</v>
       </c>
       <c r="I24" s="3">
-        <v>-30.64</v>
+        <v>-30.9</v>
       </c>
       <c r="J24" s="3">
         <v>-0.014752019382312919</v>
@@ -2220,16 +2373,19 @@
         <v>60</v>
       </c>
       <c r="M24" s="3">
-        <v>-0.34487498947152073</v>
+        <v>-0.34327711812290784</v>
       </c>
       <c r="N24" s="3">
         <v>23.200000000000003</v>
       </c>
-      <c r="O24" s="3">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
@@ -2246,19 +2402,19 @@
         <v>2.21</v>
       </c>
       <c r="F25" s="4">
-        <v>-0.31542297047728074</v>
+        <v>-0.31406975227847667</v>
       </c>
       <c r="G25" s="4">
         <v>2.32</v>
       </c>
       <c r="H25" s="4">
-        <v>63.1</v>
+        <v>62.37</v>
       </c>
       <c r="I25" s="4">
-        <v>-19.91</v>
+        <v>-20.18</v>
       </c>
       <c r="J25" s="4">
-        <v>-0.009865523158916659</v>
+        <v>-0.009931549509908096</v>
       </c>
       <c r="K25" s="4" t="b">
         <v>0</v>
@@ -2267,16 +2423,19 @@
         <v>70</v>
       </c>
       <c r="M25" s="4">
-        <v>-0.28258605120308034</v>
+        <v>-0.28334202318444524</v>
       </c>
       <c r="N25" s="4">
         <v>51</v>
       </c>
-      <c r="O25" s="4">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
@@ -2293,19 +2452,19 @@
         <v>2.07</v>
       </c>
       <c r="F26" s="4">
-        <v>-0.15608369211525974</v>
+        <v>-0.14998950535265979</v>
       </c>
       <c r="G26" s="4">
         <v>1.2</v>
       </c>
       <c r="H26" s="4">
-        <v>54.45</v>
+        <v>54.33</v>
       </c>
       <c r="I26" s="4">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J26" s="4">
-        <v>-0.006401082366864428</v>
+        <v>-0.006306767977628789</v>
       </c>
       <c r="K26" s="4" t="b">
         <v>0</v>
@@ -2314,16 +2473,19 @@
         <v>116</v>
       </c>
       <c r="M26" s="4">
-        <v>-0.15110840131613845</v>
+        <v>-0.1453337888232611</v>
       </c>
       <c r="N26" s="4">
-        <v>60.400000000000006</v>
-      </c>
-      <c r="O26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>60.6</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P26" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -2340,7 +2502,7 @@
         <v>0.39</v>
       </c>
       <c r="F27" s="2">
-        <v>0.1639470722757364</v>
+        <v>0.16645374549769174</v>
       </c>
       <c r="G27" s="2">
         <v>1.39</v>
@@ -2352,7 +2514,7 @@
         <v>19.93</v>
       </c>
       <c r="J27" s="2">
-        <v>0.024386229289761436</v>
+        <v>0.024392011769108306</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
@@ -2361,16 +2523,19 @@
         <v>412</v>
       </c>
       <c r="M27" s="2">
-        <v>0.1736488893340229</v>
+        <v>0.1755323927300192</v>
       </c>
       <c r="N27" s="2">
         <v>75.2</v>
       </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -2387,19 +2552,19 @@
         <v>2.29</v>
       </c>
       <c r="F28" s="1">
-        <v>0.0041394910754501135</v>
+        <v>0.015812694343517494</v>
       </c>
       <c r="G28" s="1">
         <v>1.69</v>
       </c>
       <c r="H28" s="1">
-        <v>62.1</v>
+        <v>62.03</v>
       </c>
       <c r="I28" s="1">
-        <v>12.57</v>
+        <v>12.51</v>
       </c>
       <c r="J28" s="1">
-        <v>0.016701733911623943</v>
+        <v>0.016891229929873873</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -2408,63 +2573,69 @@
         <v>44</v>
       </c>
       <c r="M28" s="1">
-        <v>0.02130424433241851</v>
+        <v>0.031874916369942996</v>
       </c>
       <c r="N28" s="1">
-        <v>43.800000000000004</v>
-      </c>
-      <c r="O28" s="1">
+        <v>44.800000000000004</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>88</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1.2283783783783782</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-0.84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.09305921798036683</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>41.45</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-15.14</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.010710945690364857</v>
+      </c>
+      <c r="K29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>149</v>
+      </c>
+      <c r="M29" s="1">
+        <v>-0.09073135971566748</v>
+      </c>
+      <c r="N29" s="1">
+        <v>49.599999999999994</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P29" s="1">
         <v>-0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="C29" s="4">
-        <v>88</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1.2283783783783782</v>
-      </c>
-      <c r="E29" s="4">
-        <v>-0.84</v>
-      </c>
-      <c r="F29" s="4">
-        <v>-0.09146541819570014</v>
-      </c>
-      <c r="G29" s="4">
-        <v>1.1</v>
-      </c>
-      <c r="H29" s="4">
-        <v>42.45</v>
-      </c>
-      <c r="I29" s="4">
-        <v>-14.49</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0.010778051501450026</v>
-      </c>
-      <c r="K29" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4">
-        <v>149</v>
-      </c>
-      <c r="M29" s="4">
-        <v>-0.0889777727961395</v>
-      </c>
-      <c r="N29" s="4">
-        <v>50.4</v>
-      </c>
-      <c r="O29" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
@@ -2481,19 +2652,19 @@
         <v>-0.09</v>
       </c>
       <c r="F30" s="4">
-        <v>-0.11776489135020235</v>
+        <v>-0.11302898548426081</v>
       </c>
       <c r="G30" s="4">
         <v>1.43</v>
       </c>
       <c r="H30" s="4">
-        <v>68.13</v>
+        <v>67.76</v>
       </c>
       <c r="I30" s="4">
-        <v>-15.24</v>
+        <v>-15.34</v>
       </c>
       <c r="J30" s="4">
-        <v>0.01682745320942556</v>
+        <v>0.0168881689085666</v>
       </c>
       <c r="K30" s="4" t="b">
         <v>0</v>
@@ -2502,16 +2673,19 @@
         <v>-63</v>
       </c>
       <c r="M30" s="4">
-        <v>-0.1070680161320916</v>
+        <v>-0.1030191949460536</v>
       </c>
       <c r="N30" s="4">
-        <v>53.39999999999999</v>
-      </c>
-      <c r="O30" s="4">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>53.199999999999996</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P30" s="4">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>30</v>
       </c>
@@ -2528,19 +2702,19 @@
         <v>1.22</v>
       </c>
       <c r="F31" s="4">
-        <v>-0.020539826332099193</v>
+        <v>-0.016987291083692936</v>
       </c>
       <c r="G31" s="4">
         <v>1.05</v>
       </c>
       <c r="H31" s="4">
-        <v>62.82</v>
+        <v>62.25</v>
       </c>
       <c r="I31" s="4">
-        <v>-1.92</v>
+        <v>-2.43</v>
       </c>
       <c r="J31" s="4">
-        <v>0.004328291007456379</v>
+        <v>0.004369199174233781</v>
       </c>
       <c r="K31" s="4" t="b">
         <v>0</v>
@@ -2549,16 +2723,19 @@
         <v>93</v>
       </c>
       <c r="M31" s="4">
-        <v>-0.01929600363231887</v>
+        <v>-0.015823361951343262</v>
       </c>
       <c r="N31" s="4">
         <v>50</v>
       </c>
-      <c r="O31" s="4">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -2575,19 +2752,19 @@
         <v>-4.72</v>
       </c>
       <c r="F32" s="4">
-        <v>0.13313544243322997</v>
+        <v>0.12824337554007453</v>
       </c>
       <c r="G32" s="4">
         <v>1.36</v>
       </c>
       <c r="H32" s="4">
-        <v>74.22</v>
+        <v>71.41</v>
       </c>
       <c r="I32" s="4">
-        <v>12.57</v>
+        <v>11.65</v>
       </c>
       <c r="J32" s="4">
-        <v>0.022292434755870626</v>
+        <v>0.02214932376640168</v>
       </c>
       <c r="K32" s="4" t="b">
         <v>0</v>
@@ -2596,16 +2773,19 @@
         <v>-11</v>
       </c>
       <c r="M32" s="4">
-        <v>0.14209096587164827</v>
+        <v>0.1366236652929922</v>
       </c>
       <c r="N32" s="4">
-        <v>68.39999999999999</v>
-      </c>
-      <c r="O32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>67.19999999999999</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P32" s="4">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -2622,19 +2802,19 @@
         <v>13.14</v>
       </c>
       <c r="F33" s="1">
-        <v>0.0794475694006667</v>
+        <v>0.07059457453548217</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>61.98</v>
+        <v>60.46</v>
       </c>
       <c r="I33" s="1">
-        <v>-7.32</v>
+        <v>-8.24</v>
       </c>
       <c r="J33" s="1">
-        <v>0.044189170511191735</v>
+        <v>0.04398916632335539</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
@@ -2643,16 +2823,19 @@
         <v>20</v>
       </c>
       <c r="M33" s="1">
-        <v>0.05457111540506032</v>
+        <v>0.04731599188848867</v>
       </c>
       <c r="N33" s="1">
-        <v>48.2</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -2669,19 +2852,19 @@
         <v>-1.38</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.28006059158760466</v>
+        <v>-0.27623013916963984</v>
       </c>
       <c r="G34" s="1">
         <v>0.91</v>
       </c>
       <c r="H34" s="1">
-        <v>55.97</v>
+        <v>55.45</v>
       </c>
       <c r="I34" s="1">
-        <v>-32.6</v>
+        <v>-32.78</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.010815020008760702</v>
+        <v>-0.010753220837419914</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
@@ -2690,16 +2873,19 @@
         <v>3</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.2822994724472092</v>
+        <v>-0.27832521160786927</v>
       </c>
       <c r="N34" s="1">
-        <v>42.2</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P34" s="1">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -2716,19 +2902,19 @@
         <v>0.4</v>
       </c>
       <c r="F35" s="1">
-        <v>0.04342695466623904</v>
+        <v>0.04095073687320342</v>
       </c>
       <c r="G35" s="1">
         <v>0.38</v>
       </c>
       <c r="H35" s="1">
-        <v>41.35</v>
+        <v>40.8</v>
       </c>
       <c r="I35" s="1">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="J35" s="1">
-        <v>0.006968933733247495</v>
+        <v>0.0069113389259549875</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -2737,16 +2923,19 @@
         <v>28</v>
       </c>
       <c r="M35" s="1">
-        <v>0.028003553188963082</v>
+        <v>0.02651801563206746</v>
       </c>
       <c r="N35" s="1">
         <v>46.599999999999994</v>
       </c>
-      <c r="O35" s="1">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
@@ -2763,19 +2952,19 @@
         <v>5.89</v>
       </c>
       <c r="F36" s="4">
-        <v>-0.06133460065223531</v>
+        <v>-0.05131459596580723</v>
       </c>
       <c r="G36" s="4">
         <v>1.38</v>
       </c>
       <c r="H36" s="4">
-        <v>55.75</v>
+        <v>55.82</v>
       </c>
       <c r="I36" s="4">
-        <v>-10.45</v>
+        <v>-10.4</v>
       </c>
       <c r="J36" s="4">
-        <v>0.01739455982384013</v>
+        <v>0.017564761001367033</v>
       </c>
       <c r="K36" s="4" t="b">
         <v>1</v>
@@ -2784,16 +2973,19 @@
         <v>31</v>
       </c>
       <c r="M36" s="4">
-        <v>-0.05188154813390489</v>
+        <v>-0.042468734559949706</v>
       </c>
       <c r="N36" s="4">
-        <v>61</v>
-      </c>
-      <c r="O36" s="4">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+        <v>61.2</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="P36" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2810,19 +3002,19 @@
         <v>-0.72</v>
       </c>
       <c r="F37" s="4">
-        <v>-0.16146366087670874</v>
+        <v>-0.15726381840375436</v>
       </c>
       <c r="G37" s="4">
         <v>2.78</v>
       </c>
       <c r="H37" s="4">
-        <v>60.56</v>
+        <v>59.88</v>
       </c>
       <c r="I37" s="4">
-        <v>-6.56</v>
+        <v>-6.95</v>
       </c>
       <c r="J37" s="4">
-        <v>0.010724473081475675</v>
+        <v>0.01071865794972338</v>
       </c>
       <c r="K37" s="4" t="b">
         <v>0</v>
@@ -2831,16 +3023,19 @@
         <v>134</v>
       </c>
       <c r="M37" s="4">
-        <v>-0.1171835727645294</v>
+        <v>-0.11582794129210594</v>
       </c>
       <c r="N37" s="4">
         <v>56.6</v>
       </c>
-      <c r="O37" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
@@ -2857,19 +3052,19 @@
         <v>-1.19</v>
       </c>
       <c r="F38" s="2">
-        <v>0.7522690315963407</v>
+        <v>0.74731533337892</v>
       </c>
       <c r="G38" s="2">
         <v>2.08</v>
       </c>
       <c r="H38" s="2">
-        <v>68.69</v>
+        <v>67.47</v>
       </c>
       <c r="I38" s="2">
-        <v>72.68</v>
+        <v>70.51</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04788231480104818</v>
+        <v>0.047766385700810945</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -2878,16 +3073,19 @@
         <v>234</v>
       </c>
       <c r="M38" s="2">
-        <v>0.7791356019115956</v>
+        <v>0.7724562026376729</v>
       </c>
       <c r="N38" s="2">
-        <v>73.4</v>
-      </c>
-      <c r="O38" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72.80000000000001</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P38" s="2">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
@@ -2904,19 +3102,19 @@
         <v>3.31</v>
       </c>
       <c r="F39" s="2">
-        <v>0.4187112698573938</v>
+        <v>0.3944700233220165</v>
       </c>
       <c r="G39" s="2">
         <v>3.47</v>
       </c>
       <c r="H39" s="2">
-        <v>73.66</v>
+        <v>72.31</v>
       </c>
       <c r="I39" s="2">
-        <v>118.84</v>
+        <v>112.87</v>
       </c>
       <c r="J39" s="2">
-        <v>0.04296879405972401</v>
+        <v>0.04237675278565152</v>
       </c>
       <c r="K39" s="2" t="b">
         <v>0</v>
@@ -2925,16 +3123,19 @@
         <v>211</v>
       </c>
       <c r="M39" s="2">
-        <v>0.48015611122654156</v>
+        <v>0.45196812246009044</v>
       </c>
       <c r="N39" s="2">
-        <v>74.39999999999999</v>
-      </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P39" s="2">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -2951,19 +3152,19 @@
         <v>3.34</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.2007982514277325</v>
+        <v>-0.20392777540910845</v>
       </c>
       <c r="G40" s="1">
         <v>1.68</v>
       </c>
       <c r="H40" s="1">
-        <v>43.52</v>
+        <v>44.13</v>
       </c>
       <c r="I40" s="1">
-        <v>-5.97</v>
+        <v>-5.41</v>
       </c>
       <c r="J40" s="1">
-        <v>-0.011845693448925713</v>
+        <v>-0.011969732030883737</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -2972,16 +3173,19 @@
         <v>11</v>
       </c>
       <c r="M40" s="1">
-        <v>-0.18388226271072017</v>
+        <v>-0.18809833920915286</v>
       </c>
       <c r="N40" s="1">
-        <v>45.400000000000006</v>
-      </c>
-      <c r="O40" s="1">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+        <v>45.6</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -2998,19 +3202,19 @@
         <v>16.88</v>
       </c>
       <c r="F41" s="3">
-        <v>0.16678258034043136</v>
+        <v>0.15531506095359726</v>
       </c>
       <c r="G41" s="3">
         <v>1.95</v>
       </c>
       <c r="H41" s="3">
-        <v>71.02</v>
+        <v>70.88</v>
       </c>
       <c r="I41" s="3">
-        <v>32.21</v>
+        <v>31.85</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.012003514083289334</v>
+        <v>-0.012303602701941448</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -3019,16 +3223,19 @@
         <v>83</v>
       </c>
       <c r="M41" s="3">
-        <v>0.1904152116362574</v>
+        <v>0.17742971446824107</v>
       </c>
       <c r="N41" s="3">
         <v>25.800000000000004</v>
       </c>
-      <c r="O41" s="3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
@@ -3045,19 +3252,19 @@
         <v>-0.19</v>
       </c>
       <c r="F42" s="4">
-        <v>0.11162120817244162</v>
+        <v>0.11213940405695273</v>
       </c>
       <c r="G42" s="4">
         <v>1.85</v>
       </c>
       <c r="H42" s="4">
-        <v>59.95</v>
+        <v>58.87</v>
       </c>
       <c r="I42" s="4">
-        <v>55.15</v>
+        <v>54.14</v>
       </c>
       <c r="J42" s="4">
-        <v>0.01700763705192206</v>
+        <v>0.016960356829298147</v>
       </c>
       <c r="K42" s="4" t="b">
         <v>0</v>
@@ -3066,16 +3273,19 @@
         <v>300</v>
       </c>
       <c r="M42" s="4">
-        <v>0.13276619406870704</v>
+        <v>0.1319261993068972</v>
       </c>
       <c r="N42" s="4">
         <v>64.39999999999999</v>
       </c>
-      <c r="O42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O42" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -3092,19 +3302,19 @@
         <v>7.72</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.3845729028929534</v>
+        <v>-0.37991373552278257</v>
       </c>
       <c r="G43" s="1">
         <v>2.61</v>
       </c>
       <c r="H43" s="1">
-        <v>54.93</v>
+        <v>54.08</v>
       </c>
       <c r="I43" s="1">
-        <v>-32.36</v>
+        <v>-32.74</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.01893993006080149</v>
+        <v>-0.018925796809681986</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>1</v>
@@ -3113,16 +3323,19 @@
         <v>64</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.3445218119600272</v>
+        <v>-0.34243521746112304</v>
       </c>
       <c r="N43" s="1">
-        <v>31.599999999999998</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P43" s="1">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
@@ -3145,10 +3358,10 @@
         <v>1.41</v>
       </c>
       <c r="H44" s="4">
-        <v>62.96</v>
+        <v>62.46</v>
       </c>
       <c r="I44" s="4">
-        <v>-3.92</v>
+        <v>-4.31</v>
       </c>
       <c r="J44" s="4">
         <v>0</v>
@@ -3163,15 +3376,18 @@
         <v>0</v>
       </c>
       <c r="N44" s="4">
-        <v>55.199999999999996</v>
-      </c>
-      <c r="O44" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>55.599999999999994</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P44" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B45" s="2">
         <v>0.95</v>
@@ -3186,19 +3402,19 @@
         <v>2.01</v>
       </c>
       <c r="F45" s="2">
-        <v>0.31197289663961014</v>
+        <v>0.31318031069321284</v>
       </c>
       <c r="G45" s="2">
         <v>0.8</v>
       </c>
       <c r="H45" s="2">
-        <v>83.89</v>
+        <v>84.07</v>
       </c>
       <c r="I45" s="2">
-        <v>36.93</v>
+        <v>36.96</v>
       </c>
       <c r="J45" s="2">
-        <v>0.026610161244824973</v>
+        <v>0.026608906205351935</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
@@ -3207,18 +3423,21 @@
         <v>11</v>
       </c>
       <c r="M45" s="2">
-        <v>0.30699760584048885</v>
+        <v>0.30852459416381417</v>
       </c>
       <c r="N45" s="2">
         <v>72</v>
       </c>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B46" s="4">
         <v>6.11</v>
@@ -3233,19 +3452,19 @@
         <v>-2.35</v>
       </c>
       <c r="F46" s="4">
-        <v>0.2268171383624703</v>
+        <v>0.22139772405707542</v>
       </c>
       <c r="G46" s="4">
         <v>0.87</v>
       </c>
       <c r="H46" s="4">
-        <v>70.66</v>
+        <v>69.45</v>
       </c>
       <c r="I46" s="4">
-        <v>21.83</v>
+        <v>21.49</v>
       </c>
       <c r="J46" s="4">
-        <v>0.014065204785143063</v>
+        <v>0.01394367813026002</v>
       </c>
       <c r="K46" s="4" t="b">
         <v>0</v>
@@ -3254,18 +3473,21 @@
         <v>0</v>
       </c>
       <c r="M46" s="4">
-        <v>0.2235831993430415</v>
+        <v>0.21837150831296626</v>
       </c>
       <c r="N46" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="O46" s="4">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P46" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B47" s="4">
         <v>1.94</v>
@@ -3280,19 +3502,19 @@
         <v>0.54</v>
       </c>
       <c r="F47" s="4">
-        <v>0.04217143679343387</v>
+        <v>0.04059263864824124</v>
       </c>
       <c r="G47" s="4">
         <v>0.74</v>
       </c>
       <c r="H47" s="4">
-        <v>69.66</v>
+        <v>68.48</v>
       </c>
       <c r="I47" s="4">
-        <v>22.32</v>
+        <v>21.65</v>
       </c>
       <c r="J47" s="4">
-        <v>0.008776966289988017</v>
+        <v>0.008718581588879152</v>
       </c>
       <c r="K47" s="4" t="b">
         <v>0</v>
@@ -3301,18 +3523,21 @@
         <v>23</v>
       </c>
       <c r="M47" s="4">
-        <v>0.0357035587545762</v>
+        <v>0.03454020716002293</v>
       </c>
       <c r="N47" s="4">
-        <v>53.2</v>
-      </c>
-      <c r="O47" s="4">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P47" s="4">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B48" s="4">
         <v>2.84</v>
@@ -3327,19 +3552,19 @@
         <v>0.95</v>
       </c>
       <c r="F48" s="4">
-        <v>0.1842640237296823</v>
+        <v>0.18894345727710396</v>
       </c>
       <c r="G48" s="4">
         <v>0.88</v>
       </c>
       <c r="H48" s="4">
-        <v>73.46</v>
+        <v>73.31</v>
       </c>
       <c r="I48" s="4">
-        <v>20.33</v>
+        <v>20.2</v>
       </c>
       <c r="J48" s="4">
-        <v>0.004501832495174733</v>
+        <v>0.0045619145858679455</v>
       </c>
       <c r="K48" s="4" t="b">
         <v>0</v>
@@ -3348,18 +3573,21 @@
         <v>248</v>
       </c>
       <c r="M48" s="4">
-        <v>0.18127884925020954</v>
+        <v>0.18615002735946473</v>
       </c>
       <c r="N48" s="4">
-        <v>57.400000000000006</v>
-      </c>
-      <c r="O48" s="4">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>57.60000000000001</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P48" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B49" s="4">
         <v>20.88</v>
@@ -3374,19 +3602,19 @@
         <v>-0.3</v>
       </c>
       <c r="F49" s="4">
-        <v>0.002233231868567248</v>
+        <v>0.0027278534074316116</v>
       </c>
       <c r="G49" s="4">
         <v>1.05</v>
       </c>
       <c r="H49" s="4">
-        <v>63.33</v>
+        <v>62.28</v>
       </c>
       <c r="I49" s="4">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="J49" s="4">
-        <v>-0.0010066168117376939</v>
+        <v>-0.001030523403426859</v>
       </c>
       <c r="K49" s="4" t="b">
         <v>0</v>
@@ -3395,18 +3623,21 @@
         <v>318</v>
       </c>
       <c r="M49" s="4">
-        <v>0.0034770545683475707</v>
+        <v>0.0038917825397812855</v>
       </c>
       <c r="N49" s="4">
-        <v>50.4</v>
-      </c>
-      <c r="O49" s="4">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P49" s="4">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B50" s="2">
         <v>8.72</v>
@@ -3421,19 +3652,19 @@
         <v>6.35</v>
       </c>
       <c r="F50" s="2">
-        <v>0.8831681458235491</v>
+        <v>0.8930752718250653</v>
       </c>
       <c r="G50" s="2">
         <v>0.96</v>
       </c>
       <c r="H50" s="2">
-        <v>72.55</v>
+        <v>72.72</v>
       </c>
       <c r="I50" s="2">
-        <v>53.49</v>
+        <v>53.86</v>
       </c>
       <c r="J50" s="2">
-        <v>0.05283941505704367</v>
+        <v>0.05296561844851371</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
@@ -3442,18 +3673,21 @@
         <v>115</v>
       </c>
       <c r="M50" s="2">
-        <v>0.8821730876637248</v>
+        <v>0.8921441285191856</v>
       </c>
       <c r="N50" s="2">
-        <v>72.39999999999999</v>
-      </c>
-      <c r="O50" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72.8</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P50" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B51" s="4">
         <v>10.45</v>
@@ -3468,19 +3702,19 @@
         <v>-0.36</v>
       </c>
       <c r="F51" s="4">
-        <v>0.1777696584470837</v>
+        <v>0.18291586187730532</v>
       </c>
       <c r="G51" s="4">
         <v>1.2</v>
       </c>
       <c r="H51" s="4">
-        <v>68.11</v>
+        <v>67.86</v>
       </c>
       <c r="I51" s="4">
-        <v>14.17</v>
+        <v>13.98</v>
       </c>
       <c r="J51" s="4">
-        <v>0.0106861724220283</v>
+        <v>0.010745172978275826</v>
       </c>
       <c r="K51" s="4" t="b">
         <v>0</v>
@@ -3489,13 +3723,16 @@
         <v>133</v>
       </c>
       <c r="M51" s="4">
-        <v>0.182744949246205</v>
+        <v>0.18757157840670402</v>
       </c>
       <c r="N51" s="4">
-        <v>57.80000000000001</v>
-      </c>
-      <c r="O51" s="4">
-        <v>0</v>
+        <v>58.8</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="P51" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3511,10 +3748,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3546,7 +3783,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50.800000000000004</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3562,7 +3799,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3570,7 +3807,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>63.599999999999994</v>
+        <v>62.99999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3586,7 +3823,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.4</v>
+        <v>48.00000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3602,7 +3839,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>40.2</v>
+        <v>40.400000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3626,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>36.400000000000006</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3634,7 +3871,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3650,7 +3887,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3666,7 +3903,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.400000000000002</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3682,7 +3919,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>46.400000000000006</v>
+        <v>47.400000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3714,7 +3951,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>60.400000000000006</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3967,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>43.800000000000004</v>
+        <v>44.800000000000004</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3738,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>50.4</v>
+        <v>49.599999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3746,7 +3983,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>53.39999999999999</v>
+        <v>53.199999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -3762,7 +3999,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>68.39999999999999</v>
+        <v>67.19999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3770,7 +4007,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>48.2</v>
+        <v>48.400000000000006</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3778,7 +4015,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>42.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3794,7 +4031,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>61</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3810,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>73.4</v>
+        <v>72.80000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -3818,7 +4055,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>74.39999999999999</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3826,7 +4063,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>45.400000000000006</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -3850,7 +4087,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>31.599999999999998</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3858,12 +4095,12 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>55.199999999999996</v>
+        <v>55.599999999999994</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B45">
         <v>72</v>
@@ -3871,50 +4108,50 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46">
         <v>59</v>
-      </c>
-      <c r="B46">
-        <v>58.8</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B47">
-        <v>53.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B48">
-        <v>57.400000000000006</v>
+        <v>57.60000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B49">
-        <v>50.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B50">
-        <v>72.39999999999999</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B51">
-        <v>57.80000000000001</v>
+        <v>58.8</v>
       </c>
     </row>
   </sheetData>
@@ -3933,131 +4170,131 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -4076,120 +4313,120 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -4208,117 +4445,117 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4337,128 +4574,128 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -4474,16 +4711,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4491,209 +4728,209 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="181">
   <si>
     <t>Ticker</t>
   </si>
@@ -132,6 +132,24 @@
     <t>SHOP</t>
   </si>
   <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>UUUU</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>TESTNEW</t>
+  </si>
+  <si>
+    <t>NEWTEST</t>
+  </si>
+  <si>
+    <t>ANOTHERNEW</t>
+  </si>
+  <si>
     <t>VRT</t>
   </si>
   <si>
@@ -267,9 +285,18 @@
     <t>2027-03-05</t>
   </si>
   <si>
+    <t>2027-02-27</t>
+  </si>
+  <si>
     <t>2026-03-30</t>
   </si>
   <si>
+    <t>TRVI</t>
+  </si>
+  <si>
+    <t>2027-03-17</t>
+  </si>
+  <si>
     <t>WSR</t>
   </si>
   <si>
@@ -279,6 +306,9 @@
     <t>2026-04-27</t>
   </si>
   <si>
+    <t>OFG</t>
+  </si>
+  <si>
     <t>MD</t>
   </si>
   <si>
@@ -297,10 +327,7 @@
     <t>DELL</t>
   </si>
   <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>2027-02-03</t>
+    <t>UNP</t>
   </si>
   <si>
     <t>_date_</t>
@@ -366,7 +393,7 @@
     <t>RSI min</t>
   </si>
   <si>
-    <t>68</t>
+    <t>50</t>
   </si>
   <si>
     <t>Alpha</t>
@@ -390,7 +417,7 @@
     <t>Results</t>
   </si>
   <si>
-    <t>3 of 3 qualified</t>
+    <t>5 of 5 qualified</t>
   </si>
   <si>
     <t>Dow Jones 30</t>
@@ -408,9 +435,6 @@
     <t>All sectors</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
     <t>2 of 2 qualified</t>
   </si>
   <si>
@@ -421,6 +445,9 @@
   </si>
   <si>
     <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t>1 of 1 qualified</t>
@@ -935,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1121,6 +1148,36 @@
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1141,37 +1198,37 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1182,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1190,49 +1247,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1243,46 +1300,46 @@
         <v>6.69</v>
       </c>
       <c r="C2" s="1">
-        <v>84</v>
+        <v>81.81818181818183</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.8191330343796712</v>
+        <v>-0.9805680119581465</v>
       </c>
       <c r="E2" s="1">
         <v>-0.01</v>
       </c>
       <c r="F2" s="1">
-        <v>0.12180671561557217</v>
+        <v>0.10430950033267328</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H2" s="1">
-        <v>40.62</v>
+        <v>42.88</v>
       </c>
       <c r="I2" s="1">
-        <v>17.71</v>
+        <v>18.48</v>
       </c>
       <c r="J2" s="1">
-        <v>0.002404876827358358</v>
+        <v>0.0008132475398867927</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="M2" s="1">
-        <v>0.10271827784503751</v>
+        <v>0.08829513522031007</v>
       </c>
       <c r="N2" s="1">
-        <v>43.800000000000004</v>
+        <v>43.45454545454546</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P2" s="1">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1293,7 +1350,7 @@
         <v>2.64</v>
       </c>
       <c r="C3" s="2">
-        <v>64</v>
+        <v>61.81818181818181</v>
       </c>
       <c r="D3" s="2">
         <v>23.181818181818183</v>
@@ -1302,34 +1359,34 @@
         <v>2.75</v>
       </c>
       <c r="F3" s="2">
-        <v>0.16600313720455306</v>
+        <v>0.10010054590499808</v>
       </c>
       <c r="G3" s="2">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H3" s="2">
-        <v>79.17</v>
+        <v>80.14</v>
       </c>
       <c r="I3" s="2">
-        <v>39</v>
+        <v>40.45</v>
       </c>
       <c r="J3" s="2">
-        <v>0.02714173332106283</v>
+        <v>0.03286763369908954</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="M3" s="2">
-        <v>0.1916095781162459</v>
+        <v>0.12244157377780107</v>
       </c>
       <c r="N3" s="2">
-        <v>77</v>
+        <v>76.54545454545453</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P3" s="2">
         <v>0</v>
@@ -1343,7 +1400,7 @@
         <v>-3.95</v>
       </c>
       <c r="C4" s="3">
-        <v>8</v>
+        <v>7.2727272727272725</v>
       </c>
       <c r="D4" s="3">
         <v>9.721518987341772</v>
@@ -1352,87 +1409,87 @@
         <v>4.7</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.3021002404144685</v>
+        <v>-0.28681962046476495</v>
       </c>
       <c r="G4" s="3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H4" s="3">
-        <v>48.5</v>
+        <v>51.55</v>
       </c>
       <c r="I4" s="3">
-        <v>-28.15</v>
+        <v>-26.21</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.014479168880212931</v>
+        <v>-0.011693792711078415</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.2979100955380096</v>
+        <v>-0.28306316445075386</v>
       </c>
       <c r="N4" s="3">
-        <v>24.6</v>
+        <v>25.27272727272727</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>1.08</v>
       </c>
-      <c r="C5" s="4">
-        <v>54</v>
-      </c>
-      <c r="D5" s="4">
-        <v>27.944444444444443</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="C5" s="1">
+        <v>52.72727272727272</v>
+      </c>
+      <c r="D5" s="1">
+        <v>28.39814814814815</v>
+      </c>
+      <c r="E5" s="1">
         <v>0.58</v>
       </c>
-      <c r="F5" s="4">
-        <v>-0.12558638884002832</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1.85</v>
-      </c>
-      <c r="H5" s="4">
-        <v>54.26</v>
-      </c>
-      <c r="I5" s="4">
-        <v>-2.89</v>
-      </c>
-      <c r="J5" s="4">
-        <v>-0.004849132590616535</v>
-      </c>
-      <c r="K5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>312</v>
-      </c>
-      <c r="M5" s="4">
-        <v>-0.10579959359008384</v>
-      </c>
-      <c r="N5" s="4">
-        <v>51</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0.2</v>
+      <c r="F5" s="1">
+        <v>-0.14109408444493632</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="H5" s="1">
+        <v>55.03</v>
+      </c>
+      <c r="I5" s="1">
+        <v>-2.48</v>
+      </c>
+      <c r="J5" s="1">
+        <v>-0.004812047593288001</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>283</v>
+      </c>
+      <c r="M5" s="1">
+        <v>-0.12409117827625438</v>
+      </c>
+      <c r="N5" s="1">
+        <v>49.090909090909086</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="1">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1443,7 +1500,7 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>68</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="D6" s="1">
         <v>1.5663430420711975</v>
@@ -1452,37 +1509,37 @@
         <v>-2.3</v>
       </c>
       <c r="F6" s="1">
-        <v>0.014610241897089274</v>
+        <v>0.055496204330394164</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>40.85</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.14</v>
+        <v>-11.11</v>
       </c>
       <c r="J6" s="1">
-        <v>0.020856540179318855</v>
+        <v>0.017920172839522984</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="M6" s="1">
-        <v>0.028577391485285375</v>
+        <v>0.06735869700621877</v>
       </c>
       <c r="N6" s="1">
-        <v>49.6</v>
+        <v>47.63636363636364</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P6" s="1">
-        <v>0</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1493,46 +1550,46 @@
         <v>4.9</v>
       </c>
       <c r="C7" s="4">
-        <v>76</v>
+        <v>74.54545454545455</v>
       </c>
       <c r="D7" s="4">
-        <v>5.9</v>
+        <v>6.042857142857143</v>
       </c>
       <c r="E7" s="4">
         <v>0.37</v>
       </c>
       <c r="F7" s="4">
-        <v>0.06350472870759938</v>
+        <v>0.03291084305376221</v>
       </c>
       <c r="G7" s="4">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="H7" s="4">
-        <v>68.37</v>
+        <v>67.97</v>
       </c>
       <c r="I7" s="4">
-        <v>9.94</v>
+        <v>9.8</v>
       </c>
       <c r="J7" s="4">
-        <v>0.011455554262271794</v>
+        <v>0.010940497228009789</v>
       </c>
       <c r="K7" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="4">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="M7" s="4">
-        <v>0.09353410032222098</v>
+        <v>0.058612910518048844</v>
       </c>
       <c r="N7" s="4">
-        <v>61.6</v>
+        <v>61.09090909090909</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P7" s="4">
-        <v>0.6</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1540,49 +1597,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>13.19</v>
+        <v>13.24</v>
       </c>
       <c r="C8" s="4">
-        <v>96</v>
+        <v>96.36363636363636</v>
       </c>
       <c r="D8" s="4">
-        <v>-0.044730856709628494</v>
+        <v>-0.029456193353474363</v>
       </c>
       <c r="E8" s="4">
         <v>0.43</v>
       </c>
       <c r="F8" s="4">
-        <v>0.008845260747195292</v>
+        <v>-0.0024470741673631932</v>
       </c>
       <c r="G8" s="4">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H8" s="4">
-        <v>80.5</v>
+        <v>81.35</v>
       </c>
       <c r="I8" s="4">
-        <v>11.86</v>
+        <v>12.85</v>
       </c>
       <c r="J8" s="4">
-        <v>0.0166585638880483</v>
+        <v>0.019940840366897854</v>
       </c>
       <c r="K8" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="4">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="M8" s="4">
-        <v>-0.002794030576301454</v>
+        <v>-0.011541651885495385</v>
       </c>
       <c r="N8" s="4">
-        <v>62.99999999999999</v>
+        <v>65.81818181818181</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="P8" s="4">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1593,7 +1650,7 @@
         <v>0.63</v>
       </c>
       <c r="C9" s="4">
-        <v>48</v>
+        <v>47.27272727272727</v>
       </c>
       <c r="D9" s="4">
         <v>67.1111111111111</v>
@@ -1602,37 +1659,37 @@
         <v>1.75</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.17610346672917965</v>
+        <v>-0.1372570569392728</v>
       </c>
       <c r="G9" s="4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H9" s="4">
-        <v>52.06</v>
+        <v>55.21</v>
       </c>
       <c r="I9" s="4">
-        <v>-10.99</v>
+        <v>-9.04</v>
       </c>
       <c r="J9" s="4">
-        <v>0.0018145549127325065</v>
+        <v>0.0034091107992321877</v>
       </c>
       <c r="K9" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="4">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M9" s="4">
-        <v>-0.16213631714098353</v>
+        <v>-0.1249991478409207</v>
       </c>
       <c r="N9" s="4">
-        <v>52</v>
+        <v>51.63636363636364</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P9" s="4">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1643,7 +1700,7 @@
         <v>6.79</v>
       </c>
       <c r="C10" s="1">
-        <v>86</v>
+        <v>83.63636363636363</v>
       </c>
       <c r="D10" s="1">
         <v>0.6435935198821797</v>
@@ -1652,37 +1709,37 @@
         <v>0.88</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.09625307728316178</v>
+        <v>-0.10112809313957198</v>
       </c>
       <c r="G10" s="1">
         <v>1.45</v>
       </c>
       <c r="H10" s="1">
-        <v>60.93</v>
+        <v>64.13</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.42</v>
+        <v>-4.06</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.0010288684836846146</v>
+        <v>-0.001000620138271621</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.0857777150920147</v>
+        <v>-0.09223122363270353</v>
       </c>
       <c r="N10" s="1">
-        <v>48.00000000000001</v>
+        <v>48.54545454545455</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.4</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1693,7 +1750,7 @@
         <v>0.02</v>
       </c>
       <c r="C11" s="3">
-        <v>42</v>
+        <v>41.81818181818181</v>
       </c>
       <c r="D11" s="3">
         <v>-1653.5</v>
@@ -1702,19 +1759,19 @@
         <v>10.01</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.23176875548911732</v>
+        <v>-0.2434658818286352</v>
       </c>
       <c r="G11" s="3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H11" s="3">
-        <v>47.54</v>
+        <v>51.58</v>
       </c>
       <c r="I11" s="3">
-        <v>-1.62</v>
+        <v>1.04</v>
       </c>
       <c r="J11" s="3">
-        <v>-0.012928365562974076</v>
+        <v>-0.012373803280994666</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>1</v>
@@ -1723,16 +1780,16 @@
         <v>28</v>
       </c>
       <c r="M11" s="3">
-        <v>-0.22222453660385</v>
+        <v>-0.235162136955558</v>
       </c>
       <c r="N11" s="3">
-        <v>22</v>
+        <v>21.45454545454545</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P11" s="3">
-        <v>0</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1743,7 +1800,7 @@
         <v>1.31</v>
       </c>
       <c r="C12" s="1">
-        <v>57.99999999999999</v>
+        <v>56.36363636363636</v>
       </c>
       <c r="D12" s="1">
         <v>7.5114503816793885</v>
@@ -1752,37 +1809,37 @@
         <v>0.13</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.13213082696331171</v>
+        <v>-0.14896646233357083</v>
       </c>
       <c r="G12" s="1">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H12" s="1">
-        <v>54.73</v>
+        <v>55.23</v>
       </c>
       <c r="I12" s="1">
-        <v>-10.24</v>
+        <v>-9.72</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.014581685102632282</v>
+        <v>-0.012171326773475355</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.1407439025426993</v>
+        <v>-0.15588624972780185</v>
       </c>
       <c r="N12" s="1">
-        <v>40.400000000000006</v>
+        <v>39.818181818181806</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P12" s="1">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1793,7 +1850,7 @@
         <v>-0.08</v>
       </c>
       <c r="C13" s="2">
-        <v>36</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="D13" s="2">
         <v>1166</v>
@@ -1802,37 +1859,37 @@
         <v>6.17</v>
       </c>
       <c r="F13" s="2">
-        <v>0.3190176654298967</v>
+        <v>0.1716512034922168</v>
       </c>
       <c r="G13" s="2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H13" s="2">
-        <v>70.69</v>
+        <v>71.67</v>
       </c>
       <c r="I13" s="2">
-        <v>75.24</v>
+        <v>76.41</v>
       </c>
       <c r="J13" s="2">
-        <v>0.03700547750273439</v>
+        <v>0.03649024746281057</v>
       </c>
       <c r="K13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M13" s="2">
-        <v>0.3343815299769124</v>
+        <v>0.1845022372243601</v>
       </c>
       <c r="N13" s="2">
-        <v>75.2</v>
+        <v>75.27272727272728</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P13" s="2">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1843,7 +1900,7 @@
         <v>-3.83</v>
       </c>
       <c r="C14" s="4">
-        <v>10</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="D14" s="4">
         <v>12.668407310704959</v>
@@ -1852,37 +1909,37 @@
         <v>2.52</v>
       </c>
       <c r="F14" s="4">
-        <v>0.1580303166649597</v>
+        <v>0.10513123213847486</v>
       </c>
       <c r="G14" s="4">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H14" s="4">
-        <v>64.17</v>
+        <v>66.96</v>
       </c>
       <c r="I14" s="4">
-        <v>18.3</v>
+        <v>21.59</v>
       </c>
       <c r="J14" s="4">
-        <v>0.019907417632426136</v>
+        <v>0.02222577706122988</v>
       </c>
       <c r="K14" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M14" s="4">
-        <v>0.1827056142707728</v>
+        <v>0.1262860107436954</v>
       </c>
       <c r="N14" s="4">
-        <v>50.199999999999996</v>
+        <v>51.45454545454545</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P14" s="4">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1893,7 +1950,7 @@
         <v>-6.51</v>
       </c>
       <c r="C15" s="1">
-        <v>4</v>
+        <v>3.6363636363636362</v>
       </c>
       <c r="D15" s="1">
         <v>4.411674347158218</v>
@@ -1902,37 +1959,37 @@
         <v>4.53</v>
       </c>
       <c r="F15" s="1">
-        <v>0.019977546439078106</v>
+        <v>-0.014209620300817183</v>
       </c>
       <c r="G15" s="1">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H15" s="1">
-        <v>60.37</v>
+        <v>59.06</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.44</v>
+        <v>-0.97</v>
       </c>
       <c r="J15" s="1">
-        <v>0.014163228691075109</v>
+        <v>0.014295825738936294</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M15" s="1">
-        <v>0.039531555862552636</v>
+        <v>0.0020024530228097692</v>
       </c>
       <c r="N15" s="1">
-        <v>35.8</v>
+        <v>35.09090909090909</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="P15" s="1">
-        <v>-0.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1952,37 +2009,37 @@
         <v>11.11</v>
       </c>
       <c r="F16" s="4">
-        <v>-0.07720150533687542</v>
+        <v>-0.12328239891560946</v>
       </c>
       <c r="G16" s="4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H16" s="4">
-        <v>65.26</v>
+        <v>63.53</v>
       </c>
       <c r="I16" s="4">
-        <v>21.48</v>
+        <v>19.97</v>
       </c>
       <c r="J16" s="4">
-        <v>-0.0034812260130050077</v>
+        <v>-0.0015315852409681203</v>
       </c>
       <c r="K16" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M16" s="4">
-        <v>-0.07184743132806692</v>
+        <v>-0.1189328182678071</v>
       </c>
       <c r="N16" s="4">
-        <v>62.2</v>
+        <v>60.90909090909091</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P16" s="4">
-        <v>-0.4</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1993,46 +2050,46 @@
         <v>8.81</v>
       </c>
       <c r="C17" s="1">
-        <v>92</v>
+        <v>90.9090909090909</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.27922814982973904</v>
+        <v>-0.29057888762769585</v>
       </c>
       <c r="E17" s="1">
         <v>4.52</v>
       </c>
       <c r="F17" s="1">
-        <v>0.11892421787726136</v>
+        <v>0.08608519450555685</v>
       </c>
       <c r="G17" s="1">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H17" s="1">
-        <v>56.42</v>
+        <v>59.48</v>
       </c>
       <c r="I17" s="1">
-        <v>15.37</v>
+        <v>17.17</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.0024820169527348685</v>
+        <v>-0.0032161330507446675</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M17" s="1">
-        <v>0.09960299428025676</v>
+        <v>0.0698731211819299</v>
       </c>
       <c r="N17" s="1">
-        <v>48.99999999999999</v>
+        <v>48.727272727272734</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P17" s="1">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2052,37 +2109,37 @@
         <v>-1.85</v>
       </c>
       <c r="F18" s="4">
-        <v>-0.06216288328514526</v>
+        <v>-0.051911110773201034</v>
       </c>
       <c r="G18" s="4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H18" s="4">
-        <v>68.57</v>
+        <v>70.81</v>
       </c>
       <c r="I18" s="4">
-        <v>4.14</v>
+        <v>5.36</v>
       </c>
       <c r="J18" s="4">
-        <v>-0.0006459754597089684</v>
+        <v>0.0002956202940703527</v>
       </c>
       <c r="K18" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" s="4">
-        <v>-0.058903881714566175</v>
+        <v>-0.048945487604244886</v>
       </c>
       <c r="N18" s="4">
-        <v>54.4</v>
+        <v>54.72727272727273</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2093,46 +2150,46 @@
         <v>1.29</v>
       </c>
       <c r="C19" s="1">
-        <v>56.00000000000001</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="D19" s="1">
-        <v>15.426356589147288</v>
+        <v>15.51937984496124</v>
       </c>
       <c r="E19" s="1">
         <v>3.37</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.05935038914566073</v>
+        <v>-0.08208279820329009</v>
       </c>
       <c r="G19" s="1">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="H19" s="1">
-        <v>42.55</v>
+        <v>44.62</v>
       </c>
       <c r="I19" s="1">
-        <v>-7.32</v>
+        <v>-5.98</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.0277028045198283</v>
+        <v>-0.03346250635985272</v>
       </c>
       <c r="K19" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.052134028525092746</v>
+        <v>-0.07555842723158657</v>
       </c>
       <c r="N19" s="1">
-        <v>42.8</v>
+        <v>42.18181818181817</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P19" s="1">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2143,7 +2200,7 @@
         <v>-18.39</v>
       </c>
       <c r="C20" s="3">
-        <v>2</v>
+        <v>1.8181818181818181</v>
       </c>
       <c r="D20" s="3">
         <v>-4.206090266449157</v>
@@ -2152,37 +2209,37 @@
         <v>8.76</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.046129321572840026</v>
+        <v>0.02956439389881868</v>
       </c>
       <c r="G20" s="3">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="H20" s="3">
-        <v>69.32</v>
+        <v>72.93</v>
       </c>
       <c r="I20" s="3">
-        <v>-30.52</v>
+        <v>-24.8</v>
       </c>
       <c r="J20" s="3">
-        <v>0.02327639229910378</v>
+        <v>0.02863543498165481</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="3">
-        <v>-44</v>
+        <v>-46</v>
       </c>
       <c r="M20" s="3">
-        <v>0.01602449409463258</v>
+        <v>0.08195706988371065</v>
       </c>
       <c r="N20" s="3">
-        <v>27.6</v>
+        <v>28.90909090909091</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P20" s="3">
-        <v>0.2</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2193,7 +2250,7 @@
         <v>-2.25</v>
       </c>
       <c r="C21" s="3">
-        <v>18</v>
+        <v>16.363636363636363</v>
       </c>
       <c r="D21" s="3">
         <v>10.44</v>
@@ -2202,37 +2259,37 @@
         <v>12.21</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.43978668983249797</v>
+        <v>-0.41441940524372706</v>
       </c>
       <c r="G21" s="3">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="H21" s="3">
-        <v>52.84</v>
+        <v>57.81</v>
       </c>
       <c r="I21" s="3">
-        <v>-55.91</v>
+        <v>-52.31</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.035698987635985606</v>
+        <v>-0.03669065017046017</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.4092917465649365</v>
+        <v>-0.3895081706244954</v>
       </c>
       <c r="N21" s="3">
-        <v>25.799999999999994</v>
+        <v>26.181818181818183</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2243,7 +2300,7 @@
         <v>-2.38</v>
       </c>
       <c r="C22" s="1">
-        <v>16</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="D22" s="1">
         <v>1.4705882352941178</v>
@@ -2252,37 +2309,37 @@
         <v>5.89</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.15052865140437732</v>
+        <v>-0.06957505250534916</v>
       </c>
       <c r="G22" s="1">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H22" s="1">
-        <v>74.05</v>
+        <v>74.47</v>
       </c>
       <c r="I22" s="1">
-        <v>1.2</v>
+        <v>4.91</v>
       </c>
       <c r="J22" s="1">
-        <v>0.031426437562972816</v>
+        <v>0.03573372127307865</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.1009452703662812</v>
+        <v>-0.028451744562490555</v>
       </c>
       <c r="N22" s="1">
-        <v>47.400000000000006</v>
+        <v>47.27272727272727</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2293,7 +2350,7 @@
         <v>-1.13</v>
       </c>
       <c r="C23" s="3">
-        <v>20</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="D23" s="3">
         <v>5.7522123893805315</v>
@@ -2302,37 +2359,37 @@
         <v>1.42</v>
       </c>
       <c r="F23" s="3">
-        <v>-0.4583078229640903</v>
+        <v>-0.41334038753068125</v>
       </c>
       <c r="G23" s="3">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="H23" s="3">
-        <v>49.05</v>
+        <v>55.6</v>
       </c>
       <c r="I23" s="3">
-        <v>-34.15</v>
+        <v>-31.18</v>
       </c>
       <c r="J23" s="3">
-        <v>-0.012412428446676022</v>
+        <v>-0.012523736043624573</v>
       </c>
       <c r="K23" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M23" s="3">
-        <v>-0.419898161596551</v>
+        <v>-0.38052082446089985</v>
       </c>
       <c r="N23" s="3">
-        <v>24.599999999999998</v>
+        <v>24.545454545454547</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P23" s="3">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -2343,7 +2400,7 @@
         <v>-0.99</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" s="3">
         <v>3.04040404040404</v>
@@ -2352,86 +2409,86 @@
         <v>3.54</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.39542114325217326</v>
+        <v>-0.3392702913037773</v>
       </c>
       <c r="G24" s="3">
         <v>3.24</v>
       </c>
       <c r="H24" s="3">
-        <v>51.83</v>
+        <v>58.42</v>
       </c>
       <c r="I24" s="3">
-        <v>-30.9</v>
+        <v>-26.82</v>
       </c>
       <c r="J24" s="3">
-        <v>-0.014752019382312919</v>
+        <v>-0.015386569128688356</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M24" s="3">
-        <v>-0.34327711812290784</v>
+        <v>-0.29498365198069876</v>
       </c>
       <c r="N24" s="3">
-        <v>23.200000000000003</v>
+        <v>24.727272727272727</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="1">
         <v>0.38</v>
       </c>
-      <c r="C25" s="4">
-        <v>44</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="C25" s="1">
+        <v>43.63636363636363</v>
+      </c>
+      <c r="D25" s="1">
         <v>89.71052631578947</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="1">
         <v>2.21</v>
       </c>
-      <c r="F25" s="4">
-        <v>-0.31406975227847667</v>
-      </c>
-      <c r="G25" s="4">
-        <v>2.32</v>
-      </c>
-      <c r="H25" s="4">
-        <v>62.37</v>
-      </c>
-      <c r="I25" s="4">
-        <v>-20.18</v>
-      </c>
-      <c r="J25" s="4">
-        <v>-0.009931549509908096</v>
-      </c>
-      <c r="K25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4">
-        <v>70</v>
-      </c>
-      <c r="M25" s="4">
-        <v>-0.28334202318444524</v>
-      </c>
-      <c r="N25" s="4">
-        <v>51</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="P25" s="4">
+      <c r="F25" s="1">
+        <v>-0.3068078882008596</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="H25" s="1">
+        <v>62.81</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-19.36</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-0.009028858322843525</v>
+      </c>
+      <c r="K25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>62</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-0.281105820736573</v>
+      </c>
+      <c r="N25" s="1">
+        <v>49.09090909090909</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P25" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2443,7 +2500,7 @@
         <v>1.9</v>
       </c>
       <c r="C26" s="4">
-        <v>60</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="D26" s="4">
         <v>2990.236842105264</v>
@@ -2452,37 +2509,37 @@
         <v>2.07</v>
       </c>
       <c r="F26" s="4">
-        <v>-0.14998950535265979</v>
+        <v>-0.13772230852441927</v>
       </c>
       <c r="G26" s="4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H26" s="4">
-        <v>54.33</v>
+        <v>56.45</v>
       </c>
       <c r="I26" s="4">
-        <v>0.33</v>
+        <v>1.52</v>
       </c>
       <c r="J26" s="4">
-        <v>-0.006306767977628789</v>
+        <v>-0.007541191452759171</v>
       </c>
       <c r="K26" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="4">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="M26" s="4">
-        <v>-0.1453337888232611</v>
+        <v>-0.13396585251040816</v>
       </c>
       <c r="N26" s="4">
-        <v>60.6</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P26" s="4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -2493,7 +2550,7 @@
         <v>5.13</v>
       </c>
       <c r="C27" s="2">
-        <v>78</v>
+        <v>76.36363636363637</v>
       </c>
       <c r="D27" s="2">
         <v>10.491228070175438</v>
@@ -2502,37 +2559,37 @@
         <v>0.39</v>
       </c>
       <c r="F27" s="2">
-        <v>0.16645374549769174</v>
+        <v>0.20203619524294897</v>
       </c>
       <c r="G27" s="2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H27" s="2">
-        <v>74.36</v>
+        <v>75.4</v>
       </c>
       <c r="I27" s="2">
-        <v>19.93</v>
+        <v>20.9</v>
       </c>
       <c r="J27" s="2">
-        <v>0.024392011769108306</v>
+        <v>0.02418495433315183</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="M27" s="2">
-        <v>0.1755323927300192</v>
+        <v>0.2099445236934987</v>
       </c>
       <c r="N27" s="2">
-        <v>75.2</v>
+        <v>74.72727272727272</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P27" s="2">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -2543,7 +2600,7 @@
         <v>-3.07</v>
       </c>
       <c r="C28" s="1">
-        <v>12</v>
+        <v>10.909090909090908</v>
       </c>
       <c r="D28" s="1">
         <v>8.671009771986972</v>
@@ -2552,19 +2609,19 @@
         <v>2.29</v>
       </c>
       <c r="F28" s="1">
-        <v>0.015812694343517494</v>
+        <v>0.019795285552190303</v>
       </c>
       <c r="G28" s="1">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H28" s="1">
-        <v>62.03</v>
+        <v>65.91</v>
       </c>
       <c r="I28" s="1">
-        <v>12.51</v>
+        <v>16.01</v>
       </c>
       <c r="J28" s="1">
-        <v>0.016891229929873873</v>
+        <v>0.01788401274100739</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -2573,66 +2630,66 @@
         <v>44</v>
       </c>
       <c r="M28" s="1">
-        <v>0.031874916369942996</v>
+        <v>0.033832568551916076</v>
       </c>
       <c r="N28" s="1">
-        <v>44.800000000000004</v>
+        <v>46.36363636363636</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>7.4</v>
       </c>
-      <c r="C29" s="1">
-        <v>88</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1.2283783783783782</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="C29" s="4">
+        <v>87.27272727272727</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1.2256756756756755</v>
+      </c>
+      <c r="E29" s="4">
         <v>-0.84</v>
       </c>
-      <c r="F29" s="1">
-        <v>-0.09305921798036683</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>41.45</v>
-      </c>
-      <c r="I29" s="1">
-        <v>-15.14</v>
-      </c>
-      <c r="J29" s="1">
-        <v>0.010710945690364857</v>
-      </c>
-      <c r="K29" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>149</v>
-      </c>
-      <c r="M29" s="1">
-        <v>-0.09073135971566748</v>
-      </c>
-      <c r="N29" s="1">
-        <v>49.599999999999994</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P29" s="1">
-        <v>-0.8</v>
+      <c r="F29" s="4">
+        <v>-0.07112885577909608</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1.09</v>
+      </c>
+      <c r="H29" s="4">
+        <v>46.02</v>
+      </c>
+      <c r="I29" s="4">
+        <v>-12.97</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0.009745563359081855</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
+        <v>124</v>
+      </c>
+      <c r="M29" s="4">
+        <v>-0.06934948187772239</v>
+      </c>
+      <c r="N29" s="4">
+        <v>50.727272727272734</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2643,28 +2700,28 @@
         <v>5.41</v>
       </c>
       <c r="C30" s="4">
-        <v>80</v>
+        <v>78.18181818181819</v>
       </c>
       <c r="D30" s="4">
-        <v>0.6598890942698706</v>
+        <v>0.6487985212569316</v>
       </c>
       <c r="E30" s="4">
         <v>-0.09</v>
       </c>
       <c r="F30" s="4">
-        <v>-0.11302898548426081</v>
+        <v>-0.12041335842012785</v>
       </c>
       <c r="G30" s="4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H30" s="4">
-        <v>67.76</v>
+        <v>68.01</v>
       </c>
       <c r="I30" s="4">
-        <v>-15.34</v>
+        <v>-14.83</v>
       </c>
       <c r="J30" s="4">
-        <v>0.0168881689085666</v>
+        <v>0.022556054159840782</v>
       </c>
       <c r="K30" s="4" t="b">
         <v>0</v>
@@ -2673,16 +2730,16 @@
         <v>-63</v>
       </c>
       <c r="M30" s="4">
-        <v>-0.1030191949460536</v>
+        <v>-0.11210961354705062</v>
       </c>
       <c r="N30" s="4">
-        <v>53.199999999999996</v>
+        <v>55.27272727272727</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P30" s="4">
-        <v>-0.2</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2693,7 +2750,7 @@
         <v>-0.74</v>
       </c>
       <c r="C31" s="4">
-        <v>26</v>
+        <v>23.636363636363637</v>
       </c>
       <c r="D31" s="4">
         <v>36.608108108108105</v>
@@ -2702,34 +2759,34 @@
         <v>1.22</v>
       </c>
       <c r="F31" s="4">
-        <v>-0.016987291083692936</v>
+        <v>-0.0010403042744442093</v>
       </c>
       <c r="G31" s="4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H31" s="4">
-        <v>62.25</v>
+        <v>64.56</v>
       </c>
       <c r="I31" s="4">
-        <v>-2.43</v>
+        <v>-0.27</v>
       </c>
       <c r="J31" s="4">
-        <v>0.004369199174233781</v>
+        <v>0.00823459622246454</v>
       </c>
       <c r="K31" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="4">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M31" s="4">
-        <v>-0.015823361951343262</v>
+        <v>0.000541361415665742</v>
       </c>
       <c r="N31" s="4">
-        <v>50</v>
+        <v>51.09090909090909</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P31" s="4">
         <v>0</v>
@@ -2743,7 +2800,7 @@
         <v>-0.18</v>
       </c>
       <c r="C32" s="4">
-        <v>34</v>
+        <v>34.54545454545455</v>
       </c>
       <c r="D32" s="4">
         <v>105.33333333333334</v>
@@ -2752,19 +2809,19 @@
         <v>-4.72</v>
       </c>
       <c r="F32" s="4">
-        <v>0.12824337554007453</v>
+        <v>0.14162410826325136</v>
       </c>
       <c r="G32" s="4">
         <v>1.36</v>
       </c>
       <c r="H32" s="4">
-        <v>71.41</v>
+        <v>73.18</v>
       </c>
       <c r="I32" s="4">
-        <v>11.65</v>
+        <v>12.88</v>
       </c>
       <c r="J32" s="4">
-        <v>0.02214932376640168</v>
+        <v>0.023198173721221762</v>
       </c>
       <c r="K32" s="4" t="b">
         <v>0</v>
@@ -2773,16 +2830,16 @@
         <v>-11</v>
       </c>
       <c r="M32" s="4">
-        <v>0.1366236652929922</v>
+        <v>0.14874160386874613</v>
       </c>
       <c r="N32" s="4">
-        <v>67.19999999999999</v>
+        <v>66.9090909090909</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P32" s="4">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2793,7 +2850,7 @@
         <v>-4.08</v>
       </c>
       <c r="C33" s="1">
-        <v>6</v>
+        <v>5.454545454545454</v>
       </c>
       <c r="D33" s="1">
         <v>14.372549019607844</v>
@@ -2802,37 +2859,37 @@
         <v>13.14</v>
       </c>
       <c r="F33" s="1">
-        <v>0.07059457453548217</v>
+        <v>0.10301079749743129</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>60.46</v>
+        <v>62.92</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.24</v>
+        <v>-5.98</v>
       </c>
       <c r="J33" s="1">
-        <v>0.04398916632335539</v>
+        <v>0.04226725639991526</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33" s="1">
-        <v>0.04731599188848867</v>
+        <v>0.08323997637105696</v>
       </c>
       <c r="N33" s="1">
-        <v>48.400000000000006</v>
+        <v>48.909090909090914</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P33" s="1">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2843,7 +2900,7 @@
         <v>-0.48</v>
       </c>
       <c r="C34" s="1">
-        <v>28.000000000000004</v>
+        <v>25.454545454545453</v>
       </c>
       <c r="D34" s="1">
         <v>86.47916666666667</v>
@@ -2852,37 +2909,37 @@
         <v>-1.38</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.27623013916963984</v>
+        <v>-0.2995498692167092</v>
       </c>
       <c r="G34" s="1">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H34" s="1">
-        <v>55.45</v>
+        <v>56.71</v>
       </c>
       <c r="I34" s="1">
-        <v>-32.78</v>
+        <v>-31.88</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.010753220837419914</v>
+        <v>-0.010724557085192855</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.27832521160786927</v>
+        <v>-0.30212007596313784</v>
       </c>
       <c r="N34" s="1">
-        <v>42</v>
+        <v>39.27272727272727</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P34" s="1">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2893,7 +2950,7 @@
         <v>3.52</v>
       </c>
       <c r="C35" s="1">
-        <v>72</v>
+        <v>69.0909090909091</v>
       </c>
       <c r="D35" s="1">
         <v>1.1988636363636365</v>
@@ -2902,37 +2959,37 @@
         <v>0.4</v>
       </c>
       <c r="F35" s="1">
-        <v>0.04095073687320342</v>
+        <v>0.047018161284827026</v>
       </c>
       <c r="G35" s="1">
         <v>0.38</v>
       </c>
       <c r="H35" s="1">
-        <v>40.8</v>
+        <v>43.93</v>
       </c>
       <c r="I35" s="1">
-        <v>3.38</v>
+        <v>3.91</v>
       </c>
       <c r="J35" s="1">
-        <v>0.0069113389259549875</v>
+        <v>0.005992047525405495</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M35" s="1">
-        <v>0.02651801563206746</v>
+        <v>0.03476025218647494</v>
       </c>
       <c r="N35" s="1">
-        <v>46.599999999999994</v>
+        <v>45.81818181818183</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P35" s="1">
-        <v>0</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2943,7 +3000,7 @@
         <v>-0.02</v>
       </c>
       <c r="C36" s="4">
-        <v>38</v>
+        <v>38.18181818181819</v>
       </c>
       <c r="D36" s="4">
         <v>1215</v>
@@ -2952,37 +3009,37 @@
         <v>5.89</v>
       </c>
       <c r="F36" s="4">
-        <v>-0.05131459596580723</v>
+        <v>-0.03658281578765016</v>
       </c>
       <c r="G36" s="4">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="H36" s="4">
-        <v>55.82</v>
+        <v>58.26</v>
       </c>
       <c r="I36" s="4">
-        <v>-10.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J36" s="4">
-        <v>0.017564761001367033</v>
+        <v>0.018830414038394996</v>
       </c>
       <c r="K36" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M36" s="4">
-        <v>-0.042468734559949706</v>
+        <v>-0.028476779125836682</v>
       </c>
       <c r="N36" s="4">
-        <v>61.2</v>
+        <v>60.54545454545455</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P36" s="4">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2993,7 +3050,7 @@
         <v>0.94</v>
       </c>
       <c r="C37" s="4">
-        <v>50</v>
+        <v>49.09090909090909</v>
       </c>
       <c r="D37" s="4">
         <v>31.03191489361702</v>
@@ -3002,737 +3059,987 @@
         <v>-0.72</v>
       </c>
       <c r="F37" s="4">
-        <v>-0.15726381840375436</v>
+        <v>-0.11017649397603763</v>
       </c>
       <c r="G37" s="4">
         <v>2.78</v>
       </c>
       <c r="H37" s="4">
-        <v>59.88</v>
+        <v>60</v>
       </c>
       <c r="I37" s="4">
-        <v>-6.95</v>
+        <v>-6.72</v>
       </c>
       <c r="J37" s="4">
-        <v>0.01071865794972338</v>
+        <v>0.013590219442493048</v>
       </c>
       <c r="K37" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="4">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="M37" s="4">
-        <v>-0.11582794129210594</v>
+        <v>-0.07498443237109131</v>
       </c>
       <c r="N37" s="4">
-        <v>56.6</v>
+        <v>56.72727272727273</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P37" s="4">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="4">
+        <v>7.17</v>
+      </c>
+      <c r="C38" s="4">
+        <v>85.45454545454545</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2.0557880055788007</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0.05455663814864881</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="H38" s="4">
+        <v>75.06</v>
+      </c>
+      <c r="I38" s="4">
+        <v>11.41</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0.012918925710753417</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
+        <v>402</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0.06286038302172603</v>
+      </c>
+      <c r="N38" s="4">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4">
+        <v>-0.38</v>
+      </c>
+      <c r="C39" s="4">
+        <v>29.09090909090909</v>
+      </c>
+      <c r="D39" s="4">
+        <v>882.7368421052631</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="F39" s="4">
+        <v>-0.09166964128422896</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="H39" s="4">
+        <v>60.09</v>
+      </c>
+      <c r="I39" s="4">
+        <v>30.22</v>
+      </c>
+      <c r="J39" s="4">
+        <v>-0.005047418719858366</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>28</v>
+      </c>
+      <c r="M39" s="4">
+        <v>-0.08158652250977805</v>
+      </c>
+      <c r="N39" s="4">
+        <v>54.18181818181819</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P39" s="4">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4">
+        <v>11.94</v>
+      </c>
+      <c r="C40" s="4">
+        <v>92.72727272727272</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.9145728643216081</v>
+      </c>
+      <c r="E40" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.07936458381834273</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1.71</v>
+      </c>
+      <c r="H40" s="4">
+        <v>67.23</v>
+      </c>
+      <c r="I40" s="4">
+        <v>15.73</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.007845735865819117</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4">
+        <v>19</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.0934018668180685</v>
+      </c>
+      <c r="N40" s="4">
+        <v>59.81818181818182</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P40" s="4">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="2">
         <v>3.41</v>
       </c>
-      <c r="C38" s="2">
-        <v>70</v>
-      </c>
-      <c r="D38" s="2">
+      <c r="C41" s="2">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="D41" s="2">
         <v>8.926686217008797</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E41" s="2">
         <v>-1.19</v>
       </c>
-      <c r="F38" s="2">
-        <v>0.74731533337892</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="F41" s="2">
+        <v>0.6053426689601764</v>
+      </c>
+      <c r="G41" s="2">
         <v>2.08</v>
       </c>
-      <c r="H38" s="2">
-        <v>67.47</v>
-      </c>
-      <c r="I38" s="2">
-        <v>70.51</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0.047766385700810945</v>
-      </c>
-      <c r="K38" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>234</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0.7724562026376729</v>
-      </c>
-      <c r="N38" s="2">
-        <v>72.80000000000001</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P38" s="2">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2">
+      <c r="H41" s="2">
+        <v>61.03</v>
+      </c>
+      <c r="I41" s="2">
+        <v>63.89</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.046043236539078866</v>
+      </c>
+      <c r="K41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>235</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0.6266951557766607</v>
+      </c>
+      <c r="N41" s="2">
+        <v>70.9090909090909</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P41" s="2">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="2">
         <v>-0.38</v>
       </c>
-      <c r="C39" s="2">
-        <v>30</v>
-      </c>
-      <c r="D39" s="2">
-        <v>325.07894736842104</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="C42" s="2">
+        <v>29.09090909090909</v>
+      </c>
+      <c r="D42" s="2">
+        <v>322.6315789473684</v>
+      </c>
+      <c r="E42" s="2">
         <v>3.31</v>
       </c>
-      <c r="F39" s="2">
-        <v>0.3944700233220165</v>
-      </c>
-      <c r="G39" s="2">
-        <v>3.47</v>
-      </c>
-      <c r="H39" s="2">
-        <v>72.31</v>
-      </c>
-      <c r="I39" s="2">
-        <v>112.87</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0.04237675278565152</v>
-      </c>
-      <c r="K39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2">
+      <c r="F42" s="2">
+        <v>0.4415022596716921</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3.48</v>
+      </c>
+      <c r="H42" s="2">
+        <v>73.94</v>
+      </c>
+      <c r="I42" s="2">
+        <v>117.41</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.04355902893016545</v>
+      </c>
+      <c r="K42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2">
         <v>211</v>
       </c>
-      <c r="M39" s="2">
-        <v>0.45196812246009044</v>
-      </c>
-      <c r="N39" s="2">
-        <v>74</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P39" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1">
-        <v>-0.32</v>
-      </c>
-      <c r="C40" s="1">
-        <v>32</v>
-      </c>
-      <c r="D40" s="1">
-        <v>228.28125</v>
-      </c>
-      <c r="E40" s="1">
-        <v>3.34</v>
-      </c>
-      <c r="F40" s="1">
-        <v>-0.20392777540910845</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="H40" s="1">
-        <v>44.13</v>
-      </c>
-      <c r="I40" s="1">
-        <v>-5.41</v>
-      </c>
-      <c r="J40" s="1">
-        <v>-0.011969732030883737</v>
-      </c>
-      <c r="K40" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1">
-        <v>11</v>
-      </c>
-      <c r="M40" s="1">
-        <v>-0.18809833920915286</v>
-      </c>
-      <c r="N40" s="1">
-        <v>45.6</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3">
-        <v>-2.92</v>
-      </c>
-      <c r="C41" s="3">
-        <v>14.000000000000002</v>
-      </c>
-      <c r="D41" s="3">
-        <v>-23.77054794520548</v>
-      </c>
-      <c r="E41" s="3">
-        <v>16.88</v>
-      </c>
-      <c r="F41" s="3">
-        <v>0.15531506095359726</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="H41" s="3">
-        <v>70.88</v>
-      </c>
-      <c r="I41" s="3">
-        <v>31.85</v>
-      </c>
-      <c r="J41" s="3">
-        <v>-0.012303602701941448</v>
-      </c>
-      <c r="K41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" s="3">
-        <v>83</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0.17742971446824107</v>
-      </c>
-      <c r="N41" s="3">
-        <v>25.800000000000004</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="4">
-        <v>4.88</v>
-      </c>
-      <c r="C42" s="4">
-        <v>74</v>
-      </c>
-      <c r="D42" s="4">
-        <v>6.178278688524591</v>
-      </c>
-      <c r="E42" s="4">
-        <v>-0.19</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0.11213940405695273</v>
-      </c>
-      <c r="G42" s="4">
-        <v>1.85</v>
-      </c>
-      <c r="H42" s="4">
-        <v>58.87</v>
-      </c>
-      <c r="I42" s="4">
-        <v>54.14</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0.016960356829298147</v>
-      </c>
-      <c r="K42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4">
-        <v>300</v>
-      </c>
-      <c r="M42" s="4">
-        <v>0.1319261993068972</v>
-      </c>
-      <c r="N42" s="4">
-        <v>64.39999999999999</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="P42" s="4">
+      <c r="M42" s="2">
+        <v>0.49053389606510045</v>
+      </c>
+      <c r="N42" s="2">
+        <v>73.63636363636364</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="C43" s="1">
+        <v>32.72727272727273</v>
+      </c>
+      <c r="D43" s="1">
+        <v>228.28125</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-0.19222078820742267</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="H43" s="1">
+        <v>45.26</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-4.48</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-0.012866731081671965</v>
+      </c>
+      <c r="K43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>12</v>
+      </c>
+      <c r="M43" s="1">
+        <v>-0.17877662984148812</v>
+      </c>
+      <c r="N43" s="1">
+        <v>42.54545454545455</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C44" s="3">
+        <v>12.727272727272727</v>
+      </c>
+      <c r="D44" s="3">
+        <v>-23.77054794520548</v>
+      </c>
+      <c r="E44" s="3">
+        <v>16.88</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.254369990495335</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="H44" s="3">
+        <v>75.57</v>
+      </c>
+      <c r="I44" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-0.006854620607529632</v>
+      </c>
+      <c r="K44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="3">
+        <v>82</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0.2731522705653906</v>
+      </c>
+      <c r="N44" s="3">
+        <v>28.545454545454547</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="C45" s="4">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="D45" s="4">
+        <v>6.172131147540984</v>
+      </c>
+      <c r="E45" s="4">
+        <v>-0.19</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0.08580220575029152</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1.84</v>
+      </c>
+      <c r="H45" s="4">
+        <v>58.74</v>
+      </c>
+      <c r="I45" s="4">
+        <v>53.34</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.016994357881832428</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>304</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0.10240969549644596</v>
+      </c>
+      <c r="N45" s="4">
+        <v>63.27272727272727</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P45" s="4">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="1">
         <v>-0.76</v>
       </c>
-      <c r="C43" s="1">
-        <v>24</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="C46" s="1">
+        <v>21.818181818181817</v>
+      </c>
+      <c r="D46" s="1">
         <v>13.236842105263158</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E46" s="1">
         <v>7.72</v>
       </c>
-      <c r="F43" s="1">
-        <v>-0.37991373552278257</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="F46" s="1">
+        <v>-0.40986316316747196</v>
+      </c>
+      <c r="G46" s="1">
         <v>2.61</v>
       </c>
-      <c r="H43" s="1">
-        <v>54.08</v>
-      </c>
-      <c r="I43" s="1">
-        <v>-32.74</v>
-      </c>
-      <c r="J43" s="1">
-        <v>-0.018925796809681986</v>
-      </c>
-      <c r="K43" s="1" t="b">
+      <c r="H46" s="1">
+        <v>58.25</v>
+      </c>
+      <c r="I46" s="1">
+        <v>-30.35</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.020554168246811402</v>
+      </c>
+      <c r="K46" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L43" s="1">
-        <v>64</v>
-      </c>
-      <c r="M43" s="1">
-        <v>-0.34243521746112304</v>
-      </c>
-      <c r="N43" s="1">
-        <v>31</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P43" s="1">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="4">
-        <v>0.54</v>
-      </c>
-      <c r="C44" s="4">
-        <v>46</v>
-      </c>
-      <c r="D44" s="4">
-        <v>41.629629629629626</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4">
-        <v>1.41</v>
-      </c>
-      <c r="H44" s="4">
-        <v>62.46</v>
-      </c>
-      <c r="I44" s="4">
-        <v>-4.31</v>
-      </c>
-      <c r="J44" s="4">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4">
-        <v>45</v>
-      </c>
-      <c r="M44" s="4">
-        <v>0</v>
-      </c>
-      <c r="N44" s="4">
-        <v>55.599999999999994</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="P44" s="4">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="C45" s="2">
-        <v>52</v>
-      </c>
-      <c r="D45" s="2">
-        <v>14.789473684210527</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2.01</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0.31318031069321284</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="H45" s="2">
-        <v>84.07</v>
-      </c>
-      <c r="I45" s="2">
-        <v>36.96</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0.026608906205351935</v>
-      </c>
-      <c r="K45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
-        <v>11</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0.30852459416381417</v>
-      </c>
-      <c r="N45" s="2">
-        <v>72</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="P45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="4">
-        <v>6.11</v>
-      </c>
-      <c r="C46" s="4">
-        <v>82</v>
-      </c>
-      <c r="D46" s="4">
-        <v>0.6121112929623567</v>
-      </c>
-      <c r="E46" s="4">
-        <v>-2.35</v>
-      </c>
-      <c r="F46" s="4">
-        <v>0.22139772405707542</v>
-      </c>
-      <c r="G46" s="4">
-        <v>0.87</v>
-      </c>
-      <c r="H46" s="4">
-        <v>69.45</v>
-      </c>
-      <c r="I46" s="4">
-        <v>21.49</v>
-      </c>
-      <c r="J46" s="4">
-        <v>0.01394367813026002</v>
-      </c>
-      <c r="K46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4">
-        <v>0</v>
-      </c>
-      <c r="M46" s="4">
-        <v>0.21837150831296626</v>
-      </c>
-      <c r="N46" s="4">
-        <v>59</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P46" s="4">
-        <v>0.2</v>
+      <c r="L46" s="1">
+        <v>65</v>
+      </c>
+      <c r="M46" s="1">
+        <v>-0.3780321411540093</v>
+      </c>
+      <c r="N46" s="1">
+        <v>30.909090909090907</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0.36</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B47" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="C47" s="4">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="D47" s="4">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>-0.06230075509548687</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H47" s="4">
+        <v>63.91</v>
+      </c>
+      <c r="I47" s="4">
+        <v>-3.32</v>
+      </c>
+      <c r="J47" s="4">
+        <v>-0.0010169706067324617</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>47</v>
+      </c>
+      <c r="M47" s="4">
+        <v>-0.05379930201114591</v>
+      </c>
+      <c r="N47" s="4">
+        <v>53.63636363636364</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P47" s="4">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="C48" s="1">
+        <v>32.72727272727273</v>
+      </c>
+      <c r="D48" s="1">
+        <v>-107.84374999999999</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.4074879510791903</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H48" s="1">
+        <v>68.32</v>
+      </c>
+      <c r="I48" s="1">
+        <v>42.87</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0.031132398026786835</v>
+      </c>
+      <c r="K48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>20</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0.4102558660368827</v>
+      </c>
+      <c r="N48" s="1">
+        <v>44.36363636363636</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C49" s="2">
+        <v>50.90909090909091</v>
+      </c>
+      <c r="D49" s="2">
+        <v>14.789473684210527</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2.01</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.30057211822530927</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="H49" s="2">
+        <v>83.69</v>
+      </c>
+      <c r="I49" s="2">
+        <v>36.58</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.025767018199270773</v>
+      </c>
+      <c r="K49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2">
+        <v>11</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0.29661795400003443</v>
+      </c>
+      <c r="N49" s="2">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="4">
+        <v>6.11</v>
+      </c>
+      <c r="C50" s="4">
+        <v>80</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0.6121112929623567</v>
+      </c>
+      <c r="E50" s="4">
+        <v>-2.35</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0.20134588670534742</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="H50" s="4">
+        <v>70.62</v>
+      </c>
+      <c r="I50" s="4">
+        <v>22.01</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0.014330963999259223</v>
+      </c>
+      <c r="K50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0.198577971747655</v>
+      </c>
+      <c r="N50" s="4">
+        <v>59.09090909090909</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="1">
+        <v>4.84</v>
+      </c>
+      <c r="C51" s="1">
+        <v>70.9090909090909</v>
+      </c>
+      <c r="D51" s="1">
+        <v>-1.0661157024793388</v>
+      </c>
+      <c r="E51" s="1">
+        <v>-1.8</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0.0717368273552148</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H51" s="1">
+        <v>77.24</v>
+      </c>
+      <c r="I51" s="1">
+        <v>11.09</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.005967348131211193</v>
+      </c>
+      <c r="K51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>4</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0.06600328922856624</v>
+      </c>
+      <c r="N51" s="1">
+        <v>48.72727272727273</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="P51" s="1">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="4">
         <v>1.94</v>
       </c>
-      <c r="C47" s="4">
-        <v>62</v>
-      </c>
-      <c r="D47" s="4">
+      <c r="C52" s="4">
+        <v>60</v>
+      </c>
+      <c r="D52" s="4">
         <v>1.1030927835051547</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E52" s="4">
         <v>0.54</v>
       </c>
-      <c r="F47" s="4">
-        <v>0.04059263864824124</v>
-      </c>
-      <c r="G47" s="4">
-        <v>0.74</v>
-      </c>
-      <c r="H47" s="4">
-        <v>68.48</v>
-      </c>
-      <c r="I47" s="4">
-        <v>21.65</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0.008718581588879152</v>
-      </c>
-      <c r="K47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4">
+      <c r="F52" s="4">
+        <v>0.009706311380236698</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="H52" s="4">
+        <v>64.73</v>
+      </c>
+      <c r="I52" s="4">
+        <v>19.94</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0.00954844203468285</v>
+      </c>
+      <c r="K52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4">
         <v>23</v>
       </c>
-      <c r="M47" s="4">
-        <v>0.03454020716002293</v>
-      </c>
-      <c r="N47" s="4">
-        <v>53</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="P47" s="4">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="4">
+      <c r="M52" s="4">
+        <v>0.00436818967611563</v>
+      </c>
+      <c r="N52" s="4">
+        <v>51.45454545454545</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P52" s="4">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="4">
         <v>2.84</v>
       </c>
-      <c r="C48" s="4">
-        <v>66</v>
-      </c>
-      <c r="D48" s="4">
+      <c r="C53" s="4">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="D53" s="4">
         <v>2.0880281690140845</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E53" s="4">
         <v>0.95</v>
       </c>
-      <c r="F48" s="4">
-        <v>0.18894345727710396</v>
-      </c>
-      <c r="G48" s="4">
-        <v>0.88</v>
-      </c>
-      <c r="H48" s="4">
-        <v>73.31</v>
-      </c>
-      <c r="I48" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="J48" s="4">
-        <v>0.0045619145858679455</v>
-      </c>
-      <c r="K48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4">
-        <v>248</v>
-      </c>
-      <c r="M48" s="4">
-        <v>0.18615002735946473</v>
-      </c>
-      <c r="N48" s="4">
-        <v>57.60000000000001</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="P48" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="4">
+      <c r="F53" s="4">
+        <v>0.19597787342752854</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="H53" s="4">
+        <v>74.2</v>
+      </c>
+      <c r="I53" s="4">
+        <v>20.78</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0.005043934232289435</v>
+      </c>
+      <c r="K53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4">
+        <v>241</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0.19400079131489112</v>
+      </c>
+      <c r="N53" s="4">
+        <v>56.909090909090914</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="1">
         <v>20.88</v>
       </c>
-      <c r="C49" s="4">
-        <v>98</v>
-      </c>
-      <c r="D49" s="4">
-        <v>-0.7054597701149425</v>
-      </c>
-      <c r="E49" s="4">
+      <c r="C54" s="1">
+        <v>98.18181818181819</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-0.7102490421455938</v>
+      </c>
+      <c r="E54" s="1">
         <v>-0.3</v>
       </c>
-      <c r="F49" s="4">
-        <v>0.0027278534074316116</v>
-      </c>
-      <c r="G49" s="4">
-        <v>1.05</v>
-      </c>
-      <c r="H49" s="4">
-        <v>62.28</v>
-      </c>
-      <c r="I49" s="4">
-        <v>3.26</v>
-      </c>
-      <c r="J49" s="4">
-        <v>-0.001030523403426859</v>
-      </c>
-      <c r="K49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4">
-        <v>318</v>
-      </c>
-      <c r="M49" s="4">
-        <v>0.0038917825397812855</v>
-      </c>
-      <c r="N49" s="4">
-        <v>50</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="P49" s="4">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="2">
+      <c r="F54" s="1">
+        <v>0.010851585967919478</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="H54" s="1">
+        <v>62.51</v>
+      </c>
+      <c r="I54" s="1">
+        <v>3.46</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-0.0014535587902348485</v>
+      </c>
+      <c r="K54" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>290</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0.011642418812974453</v>
+      </c>
+      <c r="N54" s="1">
+        <v>49.27272727272727</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="2">
         <v>8.72</v>
       </c>
-      <c r="C50" s="2">
-        <v>90</v>
-      </c>
-      <c r="D50" s="2">
+      <c r="C55" s="2">
+        <v>89.0909090909091</v>
+      </c>
+      <c r="D55" s="2">
         <v>0.8061926605504586</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E55" s="2">
         <v>6.35</v>
       </c>
-      <c r="F50" s="2">
-        <v>0.8930752718250653</v>
-      </c>
-      <c r="G50" s="2">
+      <c r="F55" s="2">
+        <v>0.861098265684221</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="H55" s="2">
+        <v>73.46</v>
+      </c>
+      <c r="I55" s="2">
+        <v>54.97</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0.05707369021187975</v>
+      </c>
+      <c r="K55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2">
+        <v>115</v>
+      </c>
+      <c r="M55" s="2">
+        <v>0.8607028492616935</v>
+      </c>
+      <c r="N55" s="2">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B56" s="4">
+        <v>11.98</v>
+      </c>
+      <c r="C56" s="4">
+        <v>94.54545454545455</v>
+      </c>
+      <c r="D56" s="4">
+        <v>-0.2445742904841402</v>
+      </c>
+      <c r="E56" s="4">
+        <v>1.73</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0.07860082897154917</v>
+      </c>
+      <c r="G56" s="4">
         <v>0.96</v>
       </c>
-      <c r="H50" s="2">
-        <v>72.72</v>
-      </c>
-      <c r="I50" s="2">
-        <v>53.86</v>
-      </c>
-      <c r="J50" s="2">
-        <v>0.05296561844851371</v>
-      </c>
-      <c r="K50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2">
-        <v>115</v>
-      </c>
-      <c r="M50" s="2">
-        <v>0.8921441285191856</v>
-      </c>
-      <c r="N50" s="2">
-        <v>72.8</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P50" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="4">
-        <v>10.45</v>
-      </c>
-      <c r="C51" s="4">
-        <v>94</v>
-      </c>
-      <c r="D51" s="4">
-        <v>0.4545454545454546</v>
-      </c>
-      <c r="E51" s="4">
-        <v>-0.36</v>
-      </c>
-      <c r="F51" s="4">
-        <v>0.18291586187730532</v>
-      </c>
-      <c r="G51" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H51" s="4">
-        <v>67.86</v>
-      </c>
-      <c r="I51" s="4">
-        <v>13.98</v>
-      </c>
-      <c r="J51" s="4">
-        <v>0.010745172978275826</v>
-      </c>
-      <c r="K51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4">
-        <v>133</v>
-      </c>
-      <c r="M51" s="4">
-        <v>0.18757157840670402</v>
-      </c>
-      <c r="N51" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="P51" s="4">
-        <v>1</v>
+      <c r="H56" s="4">
+        <v>60.42</v>
+      </c>
+      <c r="I56" s="4">
+        <v>8.28</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0.0008121075722220841</v>
+      </c>
+      <c r="K56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="4">
+        <v>97</v>
+      </c>
+      <c r="M56" s="4">
+        <v>0.0778099961264942</v>
+      </c>
+      <c r="N56" s="4">
+        <v>51.63636363636364</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P56" s="4">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -3743,15 +4050,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3759,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>43.800000000000004</v>
+        <v>43.45454545454546</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3767,7 +4074,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>77</v>
+        <v>76.54545454545453</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3775,7 +4082,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24.6</v>
+        <v>25.27272727272727</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3783,7 +4090,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>49.090909090909086</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3791,7 +4098,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>49.6</v>
+        <v>47.63636363636364</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3799,7 +4106,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>61.6</v>
+        <v>61.09090909090909</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3807,7 +4114,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>62.99999999999999</v>
+        <v>65.81818181818181</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3815,7 +4122,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>52</v>
+        <v>51.63636363636364</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3823,7 +4130,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.00000000000001</v>
+        <v>48.54545454545455</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3831,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>21.45454545454545</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3839,7 +4146,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>40.400000000000006</v>
+        <v>39.818181818181806</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3847,7 +4154,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>75.2</v>
+        <v>75.27272727272728</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3855,7 +4162,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>50.199999999999996</v>
+        <v>51.45454545454545</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3863,7 +4170,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>35.8</v>
+        <v>35.09090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3871,7 +4178,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>62.2</v>
+        <v>60.90909090909091</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3879,7 +4186,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>48.99999999999999</v>
+        <v>48.727272727272734</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3887,7 +4194,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>54.4</v>
+        <v>54.72727272727273</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3895,7 +4202,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>42.8</v>
+        <v>42.18181818181817</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3903,7 +4210,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.6</v>
+        <v>28.90909090909091</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3911,7 +4218,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.799999999999994</v>
+        <v>26.181818181818183</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3919,7 +4226,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>47.400000000000006</v>
+        <v>47.27272727272727</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3927,7 +4234,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>24.599999999999998</v>
+        <v>24.545454545454547</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3935,7 +4242,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>23.200000000000003</v>
+        <v>24.727272727272727</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3943,7 +4250,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>51</v>
+        <v>49.09090909090909</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3951,7 +4258,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>60.6</v>
+        <v>58.18181818181818</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3959,7 +4266,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>75.2</v>
+        <v>74.72727272727272</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3967,7 +4274,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>44.800000000000004</v>
+        <v>46.36363636363636</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3975,7 +4282,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49.599999999999994</v>
+        <v>50.727272727272734</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3983,7 +4290,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>53.199999999999996</v>
+        <v>55.27272727272727</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -3991,7 +4298,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>50</v>
+        <v>51.09090909090909</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3999,7 +4306,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>67.19999999999999</v>
+        <v>66.9090909090909</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4007,7 +4314,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>48.400000000000006</v>
+        <v>48.909090909090914</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4015,7 +4322,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>42</v>
+        <v>39.27272727272727</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4023,7 +4330,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>46.599999999999994</v>
+        <v>45.81818181818183</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4031,7 +4338,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>61.2</v>
+        <v>60.54545454545455</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4039,7 +4346,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>56.6</v>
+        <v>56.72727272727273</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4047,7 +4354,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>72.80000000000001</v>
+        <v>64.54545454545455</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4055,7 +4362,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>74</v>
+        <v>54.18181818181819</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4063,95 +4370,135 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>45.6</v>
+        <v>59.81818181818182</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41">
-        <v>25.800000000000004</v>
+        <v>70.9090909090909</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42">
-        <v>64.39999999999999</v>
+        <v>73.63636363636364</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43">
-        <v>31</v>
+        <v>42.54545454545455</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>55.599999999999994</v>
+        <v>28.545454545454547</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>72</v>
+        <v>63.27272727272727</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>59</v>
+        <v>30.909090909090907</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B47">
-        <v>53</v>
+        <v>53.63636363636364</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B48">
-        <v>57.60000000000001</v>
+        <v>44.36363636363636</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B49">
-        <v>50</v>
+        <v>71.27272727272727</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B50">
-        <v>72.8</v>
+        <v>59.09090909090909</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B51">
-        <v>58.8</v>
+        <v>48.72727272727273</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52">
+        <v>51.45454545454545</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53">
+        <v>56.909090909090914</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54">
+        <v>49.27272727272727</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55">
+        <v>72.54545454545455</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>102</v>
+      </c>
+      <c r="B56">
+        <v>51.63636363636364</v>
       </c>
     </row>
   </sheetData>
@@ -4170,131 +4517,137 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4313,120 +4666,120 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -4445,117 +4798,117 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4574,128 +4927,128 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -4711,226 +5064,226 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" t="s">
         <v>154</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="6" name="Dow_Jones" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="121">
   <si>
     <t>Ticker</t>
   </si>
@@ -200,13 +201,187 @@
     <t>Composite_Score</t>
   </si>
   <si>
+    <t>Earnings_Date</t>
+  </si>
+  <si>
     <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2027-03-04</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2027-02-26</t>
+  </si>
+  <si>
+    <t>2027-02-12</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>2027-02-24</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
+    <t>2027-02-18</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-03-05</t>
+  </si>
+  <si>
+    <t>2027-02-27</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Signal Type</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Earnings quality vs peers</t>
+  </si>
+  <si>
+    <t>Finviz</t>
+  </si>
+  <si>
+    <t>P(EPS_Fwd_Growth)</t>
+  </si>
+  <si>
+    <t>Earnings acceleration</t>
+  </si>
+  <si>
+    <t>P(MA_Slope_50)</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Medium-term price trend</t>
+  </si>
+  <si>
+    <t>Yahoo Finance prices</t>
+  </si>
+  <si>
+    <t>P(RSI_14)</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Short-term momentum strength</t>
+  </si>
+  <si>
+    <t>P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Long-term trend confirmation</t>
+  </si>
+  <si>
     <t/>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Score Range</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>≥ 70</t>
+  </si>
+  <si>
+    <t>Strong Buy candidate</t>
+  </si>
+  <si>
+    <t>50 – 70</t>
+  </si>
+  <si>
+    <t>Hold / Monitor</t>
+  </si>
+  <si>
+    <t>30 – 50</t>
+  </si>
+  <si>
+    <t>Weak / Neutral</t>
+  </si>
+  <si>
+    <t>&lt; 30</t>
+  </si>
+  <si>
+    <t>Consider reducing position</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
   </si>
 </sst>
 </file>
@@ -222,12 +397,32 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -242,8 +437,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,7 +987,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -839,16 +1038,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -894,29 +1093,2700 @@
       <c r="O1" t="s">
         <v>60</v>
       </c>
+      <c r="P1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.69</v>
+      </c>
+      <c r="C2" s="1">
+        <v>84.78260869565217</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-0.9805680119581465</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.09996892429925061</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="H2" s="1">
+        <v>41.06</v>
+      </c>
+      <c r="I2" s="1">
+        <v>17.69</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.0007479023153258213</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>357</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.08156342940660632</v>
+      </c>
+      <c r="N2" s="1">
+        <v>45.434782608695656</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.64</v>
+      </c>
+      <c r="C3" s="2">
+        <v>67.3913043478261</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.181818181818183</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.12599842043116044</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.13</v>
+      </c>
+      <c r="H3" s="2">
+        <v>82.11</v>
+      </c>
+      <c r="I3" s="2">
+        <v>44.96</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.03363390125374692</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>361</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.15167522194805927</v>
+      </c>
+      <c r="N3" s="2">
+        <v>77.3913043478261</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-3.95</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.721518987341772</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-0.28808071658688233</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H4" s="3">
+        <v>51.41</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-26.3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-0.011637421455963387</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>46</v>
+      </c>
+      <c r="M4" s="3">
+        <v>-0.2837633782787312</v>
+      </c>
+      <c r="N4" s="3">
+        <v>25.434782608695652</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="C5" s="4">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="D5" s="4">
+        <v>28.39814814814815</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.58</v>
+      </c>
+      <c r="F5" s="4">
+        <v>-0.14718748257773764</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.86</v>
+      </c>
+      <c r="H5" s="4">
+        <v>55.23</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-2.35</v>
+      </c>
+      <c r="J5" s="4">
+        <v>-0.004825343870562308</v>
+      </c>
+      <c r="K5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>283</v>
+      </c>
+      <c r="M5" s="4">
+        <v>-0.12764584602505358</v>
+      </c>
+      <c r="N5" s="4">
+        <v>52.608695652173914</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.09</v>
+      </c>
+      <c r="C6" s="1">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.5663430420711975</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-2.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.041782884097026574</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>41.49</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-11.77</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.017751614246319332</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>144</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.05541658401750382</v>
+      </c>
+      <c r="N6" s="1">
+        <v>46.95652173913043</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6.042857142857143</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.03441707862937263</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="H7" s="4">
+        <v>68.73</v>
+      </c>
+      <c r="I7" s="4">
+        <v>10.28</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.011107263617018194</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>410</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0.06395676179040666</v>
+      </c>
+      <c r="N7" s="4">
+        <v>61.52173913043478</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>13.24</v>
+      </c>
+      <c r="C8" s="4">
+        <v>97.82608695652173</v>
+      </c>
+      <c r="D8" s="4">
+        <v>-0.031722054380664645</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-0.0022726769078958084</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="H8" s="4">
+        <v>81.59</v>
+      </c>
+      <c r="I8" s="4">
+        <v>13.2</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.019984041201728593</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>48</v>
+      </c>
+      <c r="M8" s="4">
+        <v>-0.012725180180261697</v>
+      </c>
+      <c r="N8" s="4">
+        <v>65.8695652173913</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="C9" s="4">
+        <v>54.347826086956516</v>
+      </c>
+      <c r="D9" s="4">
+        <v>67.1111111111111</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-0.1326937351573292</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="H9" s="4">
+        <v>56.62</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-8.06</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.0036242846020889314</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>181</v>
+      </c>
+      <c r="M9" s="4">
+        <v>-0.11860557857283605</v>
+      </c>
+      <c r="N9" s="4">
+        <v>55.65217391304348</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.79</v>
+      </c>
+      <c r="C10" s="1">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.6435935198821797</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-0.11941150605596082</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H10" s="1">
+        <v>61.49</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-5.1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-0.0013125148616111757</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>42</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.10918623111560288</v>
+      </c>
+      <c r="N10" s="1">
+        <v>48.69565217391304</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="1">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="C11" s="3">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-1653.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.2613708318770846</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="H11" s="3">
+        <v>50.91</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-0.012710329593127003</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>28</v>
+      </c>
+      <c r="M11" s="3">
+        <v>-0.2518272419327505</v>
+      </c>
+      <c r="N11" s="3">
+        <v>25</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="3">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C12" s="1">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7.5114503816793885</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-0.157856292551665</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H12" s="1">
+        <v>53.93</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-10.77</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-0.012330698631726643</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>14</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.1658092841719434</v>
+      </c>
+      <c r="N12" s="1">
+        <v>41.08695652173913</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.08</v>
+      </c>
+      <c r="C13" s="2">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1166</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6.17</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.1663195259495343</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="H13" s="2">
+        <v>70.76</v>
+      </c>
+      <c r="I13" s="2">
+        <v>74.53</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.03647987497816678</v>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>250</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.18108936753005134</v>
+      </c>
+      <c r="N13" s="2">
+        <v>76.95652173913044</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>-3.83</v>
+      </c>
+      <c r="C14" s="4">
+        <v>10.869565217391305</v>
+      </c>
+      <c r="D14" s="4">
+        <v>12.668407310704959</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2.52</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.09331850547452526</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.07</v>
+      </c>
+      <c r="H14" s="4">
+        <v>68.78</v>
+      </c>
+      <c r="I14" s="4">
+        <v>24.28</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.022103908627329315</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>24</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.11763193699937635</v>
+      </c>
+      <c r="N14" s="4">
+        <v>52.608695652173914</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P14" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-6.51</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4.3478260869565215</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4.411674347158218</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4.53</v>
+      </c>
+      <c r="F15" s="1">
+        <v>-0.03840923881066992</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="H15" s="1">
+        <v>57.02</v>
+      </c>
+      <c r="I15" s="1">
+        <v>-2.37</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.013897275697783682</v>
+      </c>
+      <c r="K15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>42</v>
+      </c>
+      <c r="M15" s="1">
+        <v>-0.019776515586017673</v>
+      </c>
+      <c r="N15" s="1">
+        <v>33.47826086956522</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="1">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-0.01</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="D16" s="4">
+        <v>18685</v>
+      </c>
+      <c r="E16" s="4">
+        <v>11.11</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-0.1397593578045052</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="H16" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>17.19</v>
+      </c>
+      <c r="J16" s="4">
+        <v>-0.001842040615125081</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>31</v>
+      </c>
+      <c r="M16" s="4">
+        <v>-0.1347603345003302</v>
+      </c>
+      <c r="N16" s="4">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P16" s="4">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>8.81</v>
+      </c>
+      <c r="C17" s="4">
+        <v>93.47826086956522</v>
+      </c>
+      <c r="D17" s="4">
+        <v>-0.2542565266742338</v>
+      </c>
+      <c r="E17" s="4">
+        <v>4.52</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.08708899278369829</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="H17" s="4">
+        <v>59.05</v>
+      </c>
+      <c r="I17" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="J17" s="4">
+        <v>-0.0031876764959356445</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>95</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0.06845626955904605</v>
+      </c>
+      <c r="N17" s="4">
+        <v>50.869565217391305</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <v>27.92</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="4">
+        <v>-0.5508595988538683</v>
+      </c>
+      <c r="E18" s="4">
+        <v>-1.85</v>
+      </c>
+      <c r="F18" s="4">
+        <v>-0.07398723892664896</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1.15</v>
+      </c>
+      <c r="H18" s="4">
+        <v>63.15</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="J18" s="4">
+        <v>-0.00012401714498254583</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>5</v>
+      </c>
+      <c r="M18" s="4">
+        <v>-0.07057881394652965</v>
+      </c>
+      <c r="N18" s="4">
+        <v>53.47826086956522</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P18" s="4">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="C19" s="1">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="D19" s="1">
+        <v>15.51937984496124</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="F19" s="1">
+        <v>-0.07071837006175516</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="H19" s="1">
+        <v>46.58</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-4.49</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-0.03319969783581741</v>
+      </c>
+      <c r="K19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>-8</v>
+      </c>
+      <c r="M19" s="1">
+        <v>-0.06321983510549267</v>
+      </c>
+      <c r="N19" s="1">
+        <v>43.913043478260875</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-18.39</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.1739130434782608</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-4.206090266449157</v>
+      </c>
+      <c r="E20" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.008381790563761982</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3.65</v>
+      </c>
+      <c r="H20" s="1">
+        <v>72.85</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-24.91</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.028378167283443965</v>
+      </c>
+      <c r="K20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>-46</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0.06859729854586982</v>
+      </c>
+      <c r="N20" s="1">
+        <v>30</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-2.25</v>
+      </c>
+      <c r="C21" s="3">
+        <v>19.565217391304348</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10.44</v>
+      </c>
+      <c r="E21" s="3">
+        <v>12.21</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-0.4329896693257033</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="H21" s="3">
+        <v>56.52</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-53.26</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-0.03706634906145761</v>
+      </c>
+      <c r="K21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>25</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-0.4043588994927011</v>
+      </c>
+      <c r="N21" s="3">
+        <v>25.8695652173913</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-2.38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>17.391304347826086</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1.4705882352941178</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5.89</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-0.08508151333094409</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3.08</v>
+      </c>
+      <c r="H22" s="1">
+        <v>73.98</v>
+      </c>
+      <c r="I22" s="1">
+        <v>3.85</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.03554625294757561</v>
+      </c>
+      <c r="K22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>48</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-0.03781802027328962</v>
+      </c>
+      <c r="N22" s="1">
+        <v>46.73913043478261</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1.13</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21.73913043478261</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5.7522123893805315</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.44182211533809623</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.66</v>
+      </c>
+      <c r="H23" s="3">
+        <v>49.4</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-33.99</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-0.0131462304015791</v>
+      </c>
+      <c r="K23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>39</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-0.4041022122247758</v>
+      </c>
+      <c r="N23" s="3">
+        <v>22.391304347826086</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-0.99</v>
+      </c>
+      <c r="C24" s="3">
+        <v>23.91304347826087</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.04040404040404</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-0.37303787031193114</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="H24" s="3">
+        <v>53.56</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-29.81</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-0.016038272851735914</v>
+      </c>
+      <c r="K24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>61</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-0.3221387239421494</v>
+      </c>
+      <c r="N24" s="3">
+        <v>22.60869565217391</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="C25" s="4">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4">
+        <v>89.71052631578947</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="F25" s="4">
+        <v>-0.32237288207287773</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="H25" s="4">
+        <v>61.11</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-20.43</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-0.009277359455133173</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>62</v>
+      </c>
+      <c r="M25" s="4">
+        <v>-0.2928331989118437</v>
+      </c>
+      <c r="N25" s="4">
+        <v>51.73913043478261</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="C26" s="4">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2990.236842105264</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2.07</v>
+      </c>
+      <c r="F26" s="4">
+        <v>-0.119567320339584</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.19</v>
+      </c>
+      <c r="H26" s="4">
+        <v>62.01</v>
+      </c>
+      <c r="I26" s="4">
+        <v>5.11</v>
+      </c>
+      <c r="J26" s="4">
+        <v>-0.007049404183546274</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4">
+        <v>101</v>
+      </c>
+      <c r="M26" s="4">
+        <v>-0.11524998203143288</v>
+      </c>
+      <c r="N26" s="4">
+        <v>66.08695652173913</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P26" s="4">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="C27" s="2">
+        <v>80.43478260869566</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10.491228070175438</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.2229490479703709</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>78.01</v>
+      </c>
+      <c r="I27" s="2">
+        <v>24.35</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.02468420475262018</v>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>386</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0.2320381812506891</v>
+      </c>
+      <c r="N27" s="2">
+        <v>76.08695652173913</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-3.07</v>
+      </c>
+      <c r="C28" s="1">
+        <v>13.043478260869565</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8.671009771986972</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.04116510893404747</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="H28" s="1">
+        <v>66.88</v>
+      </c>
+      <c r="I28" s="1">
+        <v>17.06</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.018451170252593203</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>44</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0.05729832050661221</v>
+      </c>
+      <c r="N28" s="1">
+        <v>47.173913043478265</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1.2256756756756755</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-0.84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.05617212154524295</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1.09</v>
+      </c>
+      <c r="H29" s="1">
+        <v>47.34</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-12.27</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.010107613393399483</v>
+      </c>
+      <c r="K29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>124</v>
+      </c>
+      <c r="M29" s="1">
+        <v>-0.054127066557171366</v>
+      </c>
+      <c r="N29" s="1">
+        <v>49.99999999999999</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <v>5.41</v>
+      </c>
+      <c r="C30" s="4">
+        <v>82.6086956521739</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.6487985212569316</v>
+      </c>
+      <c r="E30" s="4">
+        <v>-0.09</v>
+      </c>
+      <c r="F30" s="4">
+        <v>-0.12979399564621946</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="H30" s="4">
+        <v>67.38</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-15.19</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.022425463705878987</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4">
+        <v>-63</v>
+      </c>
+      <c r="M30" s="4">
+        <v>-0.12025040570188539</v>
+      </c>
+      <c r="N30" s="4">
+        <v>56.08695652173913</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>-0.74</v>
+      </c>
+      <c r="C31" s="4">
+        <v>28.26086956521739</v>
+      </c>
+      <c r="D31" s="4">
+        <v>36.608108108108105</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0.0016923626016362228</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="H31" s="4">
+        <v>65.35</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0.008364888116717522</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
+        <v>90</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0.0035101892576998583</v>
+      </c>
+      <c r="N31" s="4">
+        <v>53.26086956521739</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="P31" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <v>-0.18</v>
+      </c>
+      <c r="C32" s="4">
+        <v>39.130434782608695</v>
+      </c>
+      <c r="D32" s="4">
+        <v>105.33333333333334</v>
+      </c>
+      <c r="E32" s="4">
+        <v>-4.72</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.12212126696351888</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1.36</v>
+      </c>
+      <c r="H32" s="4">
+        <v>71.01</v>
+      </c>
+      <c r="I32" s="4">
+        <v>11.54</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0.02288485019404691</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4">
+        <v>-11</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0.13030148691580523</v>
+      </c>
+      <c r="N32" s="4">
+        <v>68.47826086956522</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4">
+        <v>-4.08</v>
+      </c>
+      <c r="C33" s="4">
+        <v>6.521739130434782</v>
+      </c>
+      <c r="D33" s="4">
+        <v>14.372549019607844</v>
+      </c>
+      <c r="E33" s="4">
+        <v>13.14</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0.10965664256424805</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4">
+        <v>63.5</v>
+      </c>
+      <c r="I33" s="4">
+        <v>-5.4</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0.042413988359607684</v>
+      </c>
+      <c r="K33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4">
+        <v>19</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0.08693380936345263</v>
+      </c>
+      <c r="N33" s="4">
+        <v>50</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P33" s="4">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>-0.48</v>
+      </c>
+      <c r="C34" s="1">
+        <v>30.434782608695656</v>
+      </c>
+      <c r="D34" s="1">
+        <v>85.89583333333333</v>
+      </c>
+      <c r="E34" s="1">
+        <v>-1.38</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-0.30901152829805545</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="H34" s="1">
+        <v>54.87</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-32.68</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-0.010910532801692763</v>
+      </c>
+      <c r="K34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2</v>
+      </c>
+      <c r="M34" s="1">
+        <v>-0.31196549661415884</v>
+      </c>
+      <c r="N34" s="1">
+        <v>40.869565217391305</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P34" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3.52</v>
+      </c>
+      <c r="C35" s="1">
+        <v>73.91304347826086</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.1988636363636365</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.03780598225516454</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="H35" s="1">
+        <v>41.11</v>
+      </c>
+      <c r="I35" s="1">
+        <v>3.29</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.005840482007137134</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>30</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0.023717825670671377</v>
+      </c>
+      <c r="N35" s="1">
+        <v>45.43478260869564</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="1">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
+        <v>-0.02</v>
+      </c>
+      <c r="C36" s="4">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1215</v>
+      </c>
+      <c r="E36" s="4">
+        <v>5.89</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-0.042474722199229806</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1.41</v>
+      </c>
+      <c r="H36" s="4">
+        <v>57.13</v>
+      </c>
+      <c r="I36" s="4">
+        <v>-9.3</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0.018793031669813467</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4">
+        <v>29</v>
+      </c>
+      <c r="M36" s="4">
+        <v>-0.03315836058690369</v>
+      </c>
+      <c r="N36" s="4">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P36" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="C37" s="4">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="D37" s="4">
+        <v>31.03191489361702</v>
+      </c>
+      <c r="E37" s="4">
+        <v>-0.72</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-0.11748082100577148</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2.78</v>
+      </c>
+      <c r="H37" s="4">
+        <v>60.16</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-6.59</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0.013611002135374714</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
+        <v>118</v>
+      </c>
+      <c r="M37" s="4">
+        <v>-0.07703417790835565</v>
+      </c>
+      <c r="N37" s="4">
+        <v>59.34782608695652</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4">
+        <v>7.17</v>
+      </c>
+      <c r="C38" s="4">
+        <v>89.13043478260869</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2.0557880055788007</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0.04783567841319197</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="H38" s="4">
+        <v>75.45</v>
+      </c>
+      <c r="I38" s="4">
+        <v>11.74</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0.01286416800260734</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
+        <v>402</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0.05737926835752605</v>
+      </c>
+      <c r="N38" s="4">
+        <v>64.78260869565219</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4">
+        <v>-0.38</v>
+      </c>
+      <c r="C39" s="4">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="D39" s="4">
+        <v>882.7368421052631</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="F39" s="4">
+        <v>-0.10456414799775396</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="H39" s="4">
+        <v>58.98</v>
+      </c>
+      <c r="I39" s="4">
+        <v>28.59</v>
+      </c>
+      <c r="J39" s="4">
+        <v>-0.005237698966110143</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>28</v>
+      </c>
+      <c r="M39" s="4">
+        <v>-0.0929755030653483</v>
+      </c>
+      <c r="N39" s="4">
+        <v>56.95652173913044</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4">
+        <v>11.94</v>
+      </c>
+      <c r="C40" s="4">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.9145728643216081</v>
+      </c>
+      <c r="E40" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.08168919683414534</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1.71</v>
+      </c>
+      <c r="H40" s="4">
+        <v>67.32</v>
+      </c>
+      <c r="I40" s="4">
+        <v>15.79</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.007987304885088326</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4">
+        <v>19</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.09782240840671008</v>
+      </c>
+      <c r="N40" s="4">
+        <v>60.000000000000014</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P40" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3.41</v>
+      </c>
+      <c r="C41" s="2">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8.926686217008797</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-1.19</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.6153054797879739</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="H41" s="2">
+        <v>60.93</v>
+      </c>
+      <c r="I41" s="2">
+        <v>63.79</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.04627481066076709</v>
+      </c>
+      <c r="K41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>235</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0.639846139644833</v>
+      </c>
+      <c r="N41" s="2">
+        <v>71.30434782608695</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P41" s="2">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>-0.38</v>
+      </c>
+      <c r="C42" s="2">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="D42" s="2">
+        <v>322.6315789473684</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3.31</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.4198218532481703</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3.48</v>
+      </c>
+      <c r="H42" s="2">
+        <v>73.18</v>
+      </c>
+      <c r="I42" s="2">
+        <v>114.18</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.04333575444785875</v>
+      </c>
+      <c r="K42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2">
+        <v>211</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0.4761744795861429</v>
+      </c>
+      <c r="N42" s="2">
+        <v>75.43478260869566</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P42" s="2">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="C43" s="1">
+        <v>36.95652173913043</v>
+      </c>
+      <c r="D43" s="1">
+        <v>228.28125</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-0.20299411633949566</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="H43" s="1">
+        <v>44.09</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-5.45</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-0.012991047223777473</v>
+      </c>
+      <c r="K43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>12</v>
+      </c>
+      <c r="M43" s="1">
+        <v>-0.1875425897629548</v>
+      </c>
+      <c r="N43" s="1">
+        <v>44.130434782608695</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C44" s="3">
+        <v>15.217391304347828</v>
+      </c>
+      <c r="D44" s="3">
+        <v>-23.77054794520548</v>
+      </c>
+      <c r="E44" s="3">
+        <v>16.88</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.24188821420172246</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="H44" s="3">
+        <v>74.63</v>
+      </c>
+      <c r="I44" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-0.006994511996842627</v>
+      </c>
+      <c r="K44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="3">
+        <v>82</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0.2634749057424781</v>
+      </c>
+      <c r="N44" s="3">
+        <v>29.565217391304344</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="C45" s="4">
+        <v>76.08695652173914</v>
+      </c>
+      <c r="D45" s="4">
+        <v>6.172131147540984</v>
+      </c>
+      <c r="E45" s="4">
+        <v>-0.19</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0.09383436891822006</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1.84</v>
+      </c>
+      <c r="H45" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="I45" s="4">
+        <v>54.98</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.017261853058808306</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>304</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0.1129215488068882</v>
+      </c>
+      <c r="N45" s="4">
+        <v>63.47826086956522</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P45" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>-0.76</v>
+      </c>
+      <c r="C46" s="1">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="D46" s="1">
+        <v>13.236842105263158</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7.72</v>
+      </c>
+      <c r="F46" s="1">
+        <v>-0.4166629597611616</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2.61</v>
+      </c>
+      <c r="H46" s="1">
+        <v>57.47</v>
+      </c>
+      <c r="I46" s="1">
+        <v>-30.83</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.020525779216574738</v>
+      </c>
+      <c r="K46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>65</v>
+      </c>
+      <c r="M46" s="1">
+        <v>-0.38007919830788095</v>
+      </c>
+      <c r="N46" s="1">
+        <v>32.173913043478265</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="C47" s="4">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="D47" s="4">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>-0.07112210226546752</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H47" s="4">
+        <v>63.64</v>
+      </c>
+      <c r="I47" s="4">
+        <v>-3.52</v>
+      </c>
+      <c r="J47" s="4">
+        <v>-0.001118055836978989</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>47</v>
+      </c>
+      <c r="M47" s="4">
+        <v>-0.06135128398912548</v>
+      </c>
+      <c r="N47" s="4">
+        <v>57.608695652173914</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P47" s="4">
+        <v>0.65</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>45.434782608695656</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>77.3913043478261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>25.434782608695652</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>52.608695652173914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>46.95652173913043</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>61.52173913043478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>65.8695652173913</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>55.65217391304348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>48.69565217391304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>41.08695652173913</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>76.95652173913044</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>52.608695652173914</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>33.47826086956522</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>63.04347826086957</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>50.869565217391305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>53.47826086956522</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>43.913043478260875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>25.8695652173913</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>46.73913043478261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>22.391304347826086</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>22.60869565217391</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>51.73913043478261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>66.08695652173913</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>76.08695652173913</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>47.173913043478265</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>49.99999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>56.08695652173913</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>53.26086956521739</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>68.47826086956522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>40.869565217391305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>45.43478260869564</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63.04347826086957</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>59.34782608695652</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>64.78260869565219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>56.95652173913044</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>60.000000000000014</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>71.30434782608695</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>75.43478260869566</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>44.130434782608695</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>29.565217391304344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>63.47826086956522</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>32.173913043478265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>57.608695652173914</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -932,7 +3802,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -948,7 +3818,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -964,7 +3834,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -980,6 +3850,241 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="6" name="Dow_Jones" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="121">
   <si>
     <t>Ticker</t>
   </si>
@@ -200,13 +201,187 @@
     <t>Composite_Score</t>
   </si>
   <si>
+    <t>Earnings_Date</t>
+  </si>
+  <si>
     <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2027-03-04</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2027-02-26</t>
+  </si>
+  <si>
+    <t>2027-02-12</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>2027-02-24</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
+    <t>2027-02-18</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-03-05</t>
+  </si>
+  <si>
+    <t>2027-02-27</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Signal Type</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Earnings quality vs peers</t>
+  </si>
+  <si>
+    <t>Finviz</t>
+  </si>
+  <si>
+    <t>P(EPS_Fwd_Growth)</t>
+  </si>
+  <si>
+    <t>Earnings acceleration</t>
+  </si>
+  <si>
+    <t>P(MA_Slope_50)</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Medium-term price trend</t>
+  </si>
+  <si>
+    <t>Yahoo Finance prices</t>
+  </si>
+  <si>
+    <t>P(RSI_14)</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Short-term momentum strength</t>
+  </si>
+  <si>
+    <t>P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Long-term trend confirmation</t>
+  </si>
+  <si>
     <t/>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Score Range</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>≥ 70</t>
+  </si>
+  <si>
+    <t>Strong Buy candidate</t>
+  </si>
+  <si>
+    <t>50 – 70</t>
+  </si>
+  <si>
+    <t>Hold / Monitor</t>
+  </si>
+  <si>
+    <t>30 – 50</t>
+  </si>
+  <si>
+    <t>Weak / Neutral</t>
+  </si>
+  <si>
+    <t>&lt; 30</t>
+  </si>
+  <si>
+    <t>Consider reducing position</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
   </si>
 </sst>
 </file>
@@ -222,12 +397,32 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -242,8 +437,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,10 +1044,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -893,6 +1092,2309 @@
       </c>
       <c r="O1" t="s">
         <v>60</v>
+      </c>
+      <c r="P1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.69</v>
+      </c>
+      <c r="C2" s="1">
+        <v>84.78260869565217</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-0.9805680119581465</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.1008274762122777</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="H2" s="1">
+        <v>41.04</v>
+      </c>
+      <c r="I2" s="1">
+        <v>17.69</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.000767312784949413</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>357</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.08129571015627968</v>
+      </c>
+      <c r="N2" s="1">
+        <v>45.652173913043484</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.64</v>
+      </c>
+      <c r="C3" s="2">
+        <v>67.3913043478261</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.181818181818183</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.13554675226258095</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.13</v>
+      </c>
+      <c r="H3" s="2">
+        <v>82.76</v>
+      </c>
+      <c r="I3" s="2">
+        <v>46.67</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.033931736160777805</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>361</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.16279477157526956</v>
+      </c>
+      <c r="N3" s="2">
+        <v>77.3913043478261</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-3.95</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.721518987341772</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-0.2926409604404942</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H4" s="3">
+        <v>51.36</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-26.33</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-0.011710159872109282</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>46</v>
+      </c>
+      <c r="M4" s="3">
+        <v>-0.2880594350693342</v>
+      </c>
+      <c r="N4" s="3">
+        <v>25.217391304347828</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="C5" s="4">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="D5" s="4">
+        <v>28.39814814814815</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.58</v>
+      </c>
+      <c r="F5" s="4">
+        <v>-0.15459476807109435</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.86</v>
+      </c>
+      <c r="H5" s="4">
+        <v>54.55</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-2.78</v>
+      </c>
+      <c r="J5" s="4">
+        <v>-0.004931709406969973</v>
+      </c>
+      <c r="K5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>283</v>
+      </c>
+      <c r="M5" s="4">
+        <v>-0.1338573374437384</v>
+      </c>
+      <c r="N5" s="4">
+        <v>51.73913043478261</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="4">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.09</v>
+      </c>
+      <c r="C6" s="1">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.5663430420711975</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-2.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.040289182066815615</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>41.93</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-11.58</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.01776532060850231</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>144</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.05475715692311045</v>
+      </c>
+      <c r="N6" s="1">
+        <v>46.95652173913043</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6.042857142857143</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.03386742167029862</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="H7" s="4">
+        <v>69.62</v>
+      </c>
+      <c r="I7" s="4">
+        <v>10.87</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.011160502632594714</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>410</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0.06521470052560407</v>
+      </c>
+      <c r="N7" s="4">
+        <v>61.95652173913042</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>13.24</v>
+      </c>
+      <c r="C8" s="4">
+        <v>97.82608695652173</v>
+      </c>
+      <c r="D8" s="4">
+        <v>-0.024169184290030232</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-0.010226989146141601</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="H8" s="4">
+        <v>81.17</v>
+      </c>
+      <c r="I8" s="4">
+        <v>12.61</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.01980807368851632</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4">
+        <v>48</v>
+      </c>
+      <c r="M8" s="4">
+        <v>-0.021319103202634304</v>
+      </c>
+      <c r="N8" s="4">
+        <v>65.8695652173913</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="C9" s="4">
+        <v>54.347826086956516</v>
+      </c>
+      <c r="D9" s="4">
+        <v>67.1111111111111</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-0.13310152654710197</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="H9" s="4">
+        <v>57.31</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-7.56</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.0036667583722992786</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>181</v>
+      </c>
+      <c r="M9" s="4">
+        <v>-0.11815128586226398</v>
+      </c>
+      <c r="N9" s="4">
+        <v>55.65217391304348</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.79</v>
+      </c>
+      <c r="C10" s="1">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.6435935198821797</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-0.12398974230389055</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H10" s="1">
+        <v>61.31</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-5.16</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-0.0013695809862560113</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>42</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.11313876116166943</v>
+      </c>
+      <c r="N10" s="1">
+        <v>48.47826086956522</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="C11" s="3">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-1653.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.25701617436476676</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="H11" s="3">
+        <v>52.4</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.71</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-0.012555010041612849</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>28</v>
+      </c>
+      <c r="M11" s="3">
+        <v>-0.2468885919653604</v>
+      </c>
+      <c r="N11" s="3">
+        <v>25.434782608695652</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C12" s="1">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7.5114503816793885</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-0.1505522723541079</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H12" s="1">
+        <v>55.4</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-9.57</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-0.012143051089573783</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>14</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.1589919243536132</v>
+      </c>
+      <c r="N12" s="1">
+        <v>41.52173913043479</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.08</v>
+      </c>
+      <c r="C13" s="2">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1166</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6.17</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.1534630938967733</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="H13" s="2">
+        <v>68.58</v>
+      </c>
+      <c r="I13" s="2">
+        <v>72.52</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.036242152949882776</v>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>250</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.16913673332442603</v>
+      </c>
+      <c r="N13" s="2">
+        <v>76.73913043478261</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>-3.83</v>
+      </c>
+      <c r="C14" s="4">
+        <v>10.869565217391305</v>
+      </c>
+      <c r="D14" s="4">
+        <v>12.668407310704959</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2.52</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.08438187589888259</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.07</v>
+      </c>
+      <c r="H14" s="4">
+        <v>67.8</v>
+      </c>
+      <c r="I14" s="4">
+        <v>22.8</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.02197442468749787</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>24</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.1101830977259417</v>
+      </c>
+      <c r="N14" s="4">
+        <v>51.95652173913044</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P14" s="4">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-6.51</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4.3478260869565215</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4.411674347158218</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4.53</v>
+      </c>
+      <c r="F15" s="1">
+        <v>-0.0412979929126466</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="H15" s="1">
+        <v>57.34</v>
+      </c>
+      <c r="I15" s="1">
+        <v>-2.19</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.013889694610936927</v>
+      </c>
+      <c r="K15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>42</v>
+      </c>
+      <c r="M15" s="1">
+        <v>-0.021525093942377005</v>
+      </c>
+      <c r="N15" s="1">
+        <v>33.69565217391305</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-0.01</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="D16" s="4">
+        <v>18685</v>
+      </c>
+      <c r="E16" s="4">
+        <v>11.11</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-0.14574757884685463</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="H16" s="4">
+        <v>57.77</v>
+      </c>
+      <c r="I16" s="4">
+        <v>16.75</v>
+      </c>
+      <c r="J16" s="4">
+        <v>-0.0019455263977864303</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>31</v>
+      </c>
+      <c r="M16" s="4">
+        <v>-0.14044265473287987</v>
+      </c>
+      <c r="N16" s="4">
+        <v>62.82608695652174</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P16" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>8.81</v>
+      </c>
+      <c r="C17" s="4">
+        <v>93.47826086956522</v>
+      </c>
+      <c r="D17" s="4">
+        <v>-0.2542565266742338</v>
+      </c>
+      <c r="E17" s="4">
+        <v>4.52</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.08860564312184951</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="H17" s="4">
+        <v>59.17</v>
+      </c>
+      <c r="I17" s="4">
+        <v>16.95</v>
+      </c>
+      <c r="J17" s="4">
+        <v>-0.003154923684622415</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>95</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0.06883274415157992</v>
+      </c>
+      <c r="N17" s="4">
+        <v>51.08695652173914</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <v>27.92</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="4">
+        <v>-0.5508595988538683</v>
+      </c>
+      <c r="E18" s="4">
+        <v>-1.85</v>
+      </c>
+      <c r="F18" s="4">
+        <v>-0.07768872066430293</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1.15</v>
+      </c>
+      <c r="H18" s="4">
+        <v>63.12</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="J18" s="4">
+        <v>-0.00017124448272952357</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>5</v>
+      </c>
+      <c r="M18" s="4">
+        <v>-0.07407172695022923</v>
+      </c>
+      <c r="N18" s="4">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="C19" s="1">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="D19" s="1">
+        <v>15.51937984496124</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="F19" s="1">
+        <v>-0.059362273386575806</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="H19" s="1">
+        <v>47.16</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-4.03</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-0.032972728826274986</v>
+      </c>
+      <c r="K19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>-8</v>
+      </c>
+      <c r="M19" s="1">
+        <v>-0.05140488721561365</v>
+      </c>
+      <c r="N19" s="1">
+        <v>44.1304347826087</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P19" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-18.39</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.1739130434782608</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-4.206090266449157</v>
+      </c>
+      <c r="E20" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="F20" s="1">
+        <v>-0.01879277749792678</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3.65</v>
+      </c>
+      <c r="H20" s="1">
+        <v>72.27</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-25.64</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.02783189594132707</v>
+      </c>
+      <c r="K20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>-46</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0.04510744478404205</v>
+      </c>
+      <c r="N20" s="1">
+        <v>30</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-2.25</v>
+      </c>
+      <c r="C21" s="3">
+        <v>19.565217391304348</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10.44</v>
+      </c>
+      <c r="E21" s="3">
+        <v>12.21</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-0.4257523619448244</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="H21" s="3">
+        <v>57.74</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-52.37</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-0.036738611374177825</v>
+      </c>
+      <c r="K21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>25</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-0.39536961474660526</v>
+      </c>
+      <c r="N21" s="3">
+        <v>26.739130434782606</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-2.38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>17.391304347826086</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1.4705882352941178</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5.89</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-0.11802123762200953</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3.08</v>
+      </c>
+      <c r="H22" s="1">
+        <v>72.74</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.03470869757352629</v>
+      </c>
+      <c r="K22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>48</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-0.06786559145352078</v>
+      </c>
+      <c r="N22" s="1">
+        <v>45.869565217391305</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1.13</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21.73913043478261</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5.7522123893805315</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.4479682759646458</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.66</v>
+      </c>
+      <c r="H23" s="3">
+        <v>49.03</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-34.14</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-0.013220085323303233</v>
+      </c>
+      <c r="K23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>39</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-0.4079402121955634</v>
+      </c>
+      <c r="N23" s="3">
+        <v>22.391304347826086</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-0.99</v>
+      </c>
+      <c r="C24" s="3">
+        <v>23.91304347826087</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.04040404040404</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-0.3834461650194826</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.24</v>
+      </c>
+      <c r="H24" s="3">
+        <v>52.77</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-30.24</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-0.0161972256448195</v>
+      </c>
+      <c r="K24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>61</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-0.32943239222264853</v>
+      </c>
+      <c r="N24" s="3">
+        <v>22.60869565217391</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="C25" s="4">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4">
+        <v>89.71052631578947</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="F25" s="4">
+        <v>-0.3271270914927164</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="H25" s="4">
+        <v>61.04</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-20.47</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-0.009321426722427306</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>62</v>
+      </c>
+      <c r="M25" s="4">
+        <v>-0.29577981263741093</v>
+      </c>
+      <c r="N25" s="4">
+        <v>51.52173913043478</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="C26" s="4">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2990.236842105264</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2.07</v>
+      </c>
+      <c r="F26" s="4">
+        <v>-0.1137240652607237</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.19</v>
+      </c>
+      <c r="H26" s="4">
+        <v>62.57</v>
+      </c>
+      <c r="I26" s="4">
+        <v>5.52</v>
+      </c>
+      <c r="J26" s="4">
+        <v>-0.0068792273359546295</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="4">
+        <v>101</v>
+      </c>
+      <c r="M26" s="4">
+        <v>-0.10914253988956368</v>
+      </c>
+      <c r="N26" s="4">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P26" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="C27" s="2">
+        <v>80.43478260869566</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10.491228070175438</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.23160151071424817</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>78.63</v>
+      </c>
+      <c r="I27" s="2">
+        <v>25.29</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.02489548308240803</v>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>386</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0.24124682728511138</v>
+      </c>
+      <c r="N27" s="2">
+        <v>76.08695652173913</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-3.07</v>
+      </c>
+      <c r="C28" s="1">
+        <v>13.043478260869565</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8.667752442996743</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.02300113273057261</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="H28" s="1">
+        <v>66.58</v>
+      </c>
+      <c r="I28" s="1">
+        <v>16.73</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.01811225760128193</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>44</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0.040121569643854826</v>
+      </c>
+      <c r="N28" s="1">
+        <v>46.95652173913044</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P28" s="1">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1.2256756756756755</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-0.84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.06157745009525035</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1.09</v>
+      </c>
+      <c r="H29" s="1">
+        <v>47.51</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-12.18</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.010030126685428955</v>
+      </c>
+      <c r="K29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>124</v>
+      </c>
+      <c r="M29" s="1">
+        <v>-0.05940725386680612</v>
+      </c>
+      <c r="N29" s="1">
+        <v>49.99999999999999</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <v>5.41</v>
+      </c>
+      <c r="C30" s="4">
+        <v>82.6086956521739</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.6487985212569316</v>
+      </c>
+      <c r="E30" s="4">
+        <v>-0.09</v>
+      </c>
+      <c r="F30" s="4">
+        <v>-0.13114399355140938</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="H30" s="4">
+        <v>67.82</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-14.94</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.02244117984151456</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4">
+        <v>-63</v>
+      </c>
+      <c r="M30" s="4">
+        <v>-0.12101641115200301</v>
+      </c>
+      <c r="N30" s="4">
+        <v>56.08695652173913</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>-0.74</v>
+      </c>
+      <c r="C31" s="4">
+        <v>28.26086956521739</v>
+      </c>
+      <c r="D31" s="4">
+        <v>36.608108108108105</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0.0027810480137657745</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="H31" s="4">
+        <v>65.81</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0.008421891102854916</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
+        <v>90</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0.0047101113279384155</v>
+      </c>
+      <c r="N31" s="4">
+        <v>53.26086956521739</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="P31" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <v>-0.18</v>
+      </c>
+      <c r="C32" s="4">
+        <v>39.130434782608695</v>
+      </c>
+      <c r="D32" s="4">
+        <v>105.33333333333334</v>
+      </c>
+      <c r="E32" s="4">
+        <v>-4.72</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.11290929379608892</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1.36</v>
+      </c>
+      <c r="H32" s="4">
+        <v>70.33</v>
+      </c>
+      <c r="I32" s="4">
+        <v>11.33</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0.022736747770421565</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4">
+        <v>-11</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0.12159007870986582</v>
+      </c>
+      <c r="N32" s="4">
+        <v>68.47826086956522</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>-4.08</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6.521739130434782</v>
+      </c>
+      <c r="D33" s="1">
+        <v>14.372549019607844</v>
+      </c>
+      <c r="E33" s="1">
+        <v>13.14</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.0948011949387904</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>62.13</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-6.76</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.04208599862763582</v>
+      </c>
+      <c r="K33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>19</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0.07068790351163234</v>
+      </c>
+      <c r="N33" s="1">
+        <v>49.130434782608695</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P33" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>-0.48</v>
+      </c>
+      <c r="C34" s="1">
+        <v>30.434782608695656</v>
+      </c>
+      <c r="D34" s="1">
+        <v>85.89583333333333</v>
+      </c>
+      <c r="E34" s="1">
+        <v>-1.38</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-0.3115998911395332</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="H34" s="1">
+        <v>53.46</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-33.19</v>
+      </c>
+      <c r="J34" s="1">
+        <v>-0.010947727472033765</v>
+      </c>
+      <c r="K34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2</v>
+      </c>
+      <c r="M34" s="1">
+        <v>-0.3147346190250637</v>
+      </c>
+      <c r="N34" s="1">
+        <v>40.65217391304348</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3.52</v>
+      </c>
+      <c r="C35" s="1">
+        <v>73.91304347826086</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.1988636363636365</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.02862922306194351</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="H35" s="1">
+        <v>38.34</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2.56</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.005678463488259859</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>30</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0.01367898237710552</v>
+      </c>
+      <c r="N35" s="1">
+        <v>45.21739130434782</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
+        <v>-0.02</v>
+      </c>
+      <c r="C36" s="4">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1215</v>
+      </c>
+      <c r="E36" s="4">
+        <v>5.89</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-0.036259160275768546</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1.41</v>
+      </c>
+      <c r="H36" s="4">
+        <v>57.49</v>
+      </c>
+      <c r="I36" s="4">
+        <v>-9.02</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0.018969747496321538</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4">
+        <v>29</v>
+      </c>
+      <c r="M36" s="4">
+        <v>-0.026372710790633747</v>
+      </c>
+      <c r="N36" s="4">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P36" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="C37" s="4">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="D37" s="4">
+        <v>31.03191489361702</v>
+      </c>
+      <c r="E37" s="4">
+        <v>-0.72</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-0.12542455724540152</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2.78</v>
+      </c>
+      <c r="H37" s="4">
+        <v>60.11</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-6.63</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0.01351706395763758</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
+        <v>118</v>
+      </c>
+      <c r="M37" s="4">
+        <v>-0.08250289850506021</v>
+      </c>
+      <c r="N37" s="4">
+        <v>59.1304347826087</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P37" s="4">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4">
+        <v>7.17</v>
+      </c>
+      <c r="C38" s="4">
+        <v>89.13043478260869</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2.0557880055788007</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0.052951277478668554</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="H38" s="4">
+        <v>76.19</v>
+      </c>
+      <c r="I38" s="4">
+        <v>12.39</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0.01301767497237266</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
+        <v>402</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0.06307885987807493</v>
+      </c>
+      <c r="N38" s="4">
+        <v>64.78260869565219</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4">
+        <v>-0.38</v>
+      </c>
+      <c r="C39" s="4">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="D39" s="4">
+        <v>882.7368421052631</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="F39" s="4">
+        <v>-0.08623749324450543</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="H39" s="4">
+        <v>60.23</v>
+      </c>
+      <c r="I39" s="4">
+        <v>30.43</v>
+      </c>
+      <c r="J39" s="4">
+        <v>-0.004777022686944814</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>28</v>
+      </c>
+      <c r="M39" s="4">
+        <v>-0.07393971461665483</v>
+      </c>
+      <c r="N39" s="4">
+        <v>57.826086956521735</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P39" s="4">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4">
+        <v>11.94</v>
+      </c>
+      <c r="C40" s="4">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.9145728643216081</v>
+      </c>
+      <c r="E40" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.08153386460991555</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1.71</v>
+      </c>
+      <c r="H40" s="4">
+        <v>68.02</v>
+      </c>
+      <c r="I40" s="4">
+        <v>16.38</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.008029978850508778</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4">
+        <v>19</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.09865430152319776</v>
+      </c>
+      <c r="N40" s="4">
+        <v>60.434782608695656</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3.41</v>
+      </c>
+      <c r="C41" s="2">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8.926686217008797</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-1.19</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.6135308078325732</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="H41" s="2">
+        <v>61.03</v>
+      </c>
+      <c r="I41" s="2">
+        <v>63.89</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.046290880944706556</v>
+      </c>
+      <c r="K41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>235</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0.6395731625739038</v>
+      </c>
+      <c r="N41" s="2">
+        <v>71.08695652173913</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P41" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>-0.38</v>
+      </c>
+      <c r="C42" s="2">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="D42" s="2">
+        <v>322.6315789473684</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3.31</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.43376294328765586</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3.48</v>
+      </c>
+      <c r="H42" s="2">
+        <v>73.97</v>
+      </c>
+      <c r="I42" s="2">
+        <v>117.52</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.0437033287774922</v>
+      </c>
+      <c r="K42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2">
+        <v>211</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0.49356390602700784</v>
+      </c>
+      <c r="N42" s="2">
+        <v>75.86956521739131</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P42" s="2">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="C43" s="1">
+        <v>36.95652173913043</v>
+      </c>
+      <c r="D43" s="1">
+        <v>228.28125</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-0.2024231122362621</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="H43" s="1">
+        <v>44.47</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-5.12</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-0.012928889152724788</v>
+      </c>
+      <c r="K43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>12</v>
+      </c>
+      <c r="M43" s="1">
+        <v>-0.18602607406579463</v>
+      </c>
+      <c r="N43" s="1">
+        <v>44.565217391304344</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C44" s="3">
+        <v>15.217391304347828</v>
+      </c>
+      <c r="D44" s="3">
+        <v>-23.77054794520548</v>
+      </c>
+      <c r="E44" s="3">
+        <v>16.88</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.23124094783320537</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="H44" s="3">
+        <v>73.93</v>
+      </c>
+      <c r="I44" s="3">
+        <v>39.23</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-0.007159582933150655</v>
+      </c>
+      <c r="K44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="3">
+        <v>82</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0.25414857468900554</v>
+      </c>
+      <c r="N44" s="3">
+        <v>28.913043478260867</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P44" s="3">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="C45" s="4">
+        <v>76.08695652173914</v>
+      </c>
+      <c r="D45" s="4">
+        <v>6.172131147540984</v>
+      </c>
+      <c r="E45" s="4">
+        <v>-0.19</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0.09983578644763577</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1.84</v>
+      </c>
+      <c r="H45" s="4">
+        <v>61.19</v>
+      </c>
+      <c r="I45" s="4">
+        <v>56.66</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.017431917254956325</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>304</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0.12009095124644853</v>
+      </c>
+      <c r="N45" s="4">
+        <v>64.13043478260869</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P45" s="4">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>-0.76</v>
+      </c>
+      <c r="C46" s="1">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="D46" s="1">
+        <v>13.236842105263158</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7.72</v>
+      </c>
+      <c r="F46" s="1">
+        <v>-0.4293418207008787</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2.61</v>
+      </c>
+      <c r="H46" s="1">
+        <v>55.73</v>
+      </c>
+      <c r="I46" s="1">
+        <v>-31.83</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.020809676287581447</v>
+      </c>
+      <c r="K46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>65</v>
+      </c>
+      <c r="M46" s="1">
+        <v>-0.3905194215031542</v>
+      </c>
+      <c r="N46" s="1">
+        <v>31.30434782608696</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P46" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="C47" s="4">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="D47" s="4">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>-0.07729216133870549</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H47" s="4">
+        <v>62.92</v>
+      </c>
+      <c r="I47" s="4">
+        <v>-4.06</v>
+      </c>
+      <c r="J47" s="4">
+        <v>-0.0012099495887365832</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>47</v>
+      </c>
+      <c r="M47" s="4">
+        <v>-0.06692344602502753</v>
+      </c>
+      <c r="N47" s="4">
+        <v>57.17391304347826</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P47" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -903,15 +3405,383 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>45.652173913043484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>77.3913043478261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>25.217391304347828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>51.73913043478261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>46.95652173913043</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>61.95652173913042</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>65.8695652173913</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>55.65217391304348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>48.47826086956522</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25.434782608695652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>41.52173913043479</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>76.73913043478261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>51.95652173913044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>33.69565217391305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>62.82608695652174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>51.08695652173914</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>54.34782608695652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>44.1304347826087</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>26.739130434782606</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>45.869565217391305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>22.391304347826086</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>22.60869565217391</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>51.52173913043478</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>66.73913043478261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>76.08695652173913</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>46.95652173913044</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>49.99999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>56.08695652173913</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>53.26086956521739</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>68.47826086956522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>49.130434782608695</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>40.65217391304348</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>45.21739130434782</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63.04347826086957</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>59.1304347826087</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>64.78260869565219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>57.826086956521735</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>60.434782608695656</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>71.08695652173913</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>75.86956521739131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>44.565217391304344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>28.913043478260867</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>64.13043478260869</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>31.30434782608696</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>57.17391304347826</v>
       </c>
     </row>
   </sheetData>
@@ -982,4 +3852,239 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="173">
   <si>
     <t>Ticker</t>
   </si>
@@ -283,6 +283,162 @@
   </si>
   <si>
     <t>_date_</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>Last Run</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Russell 2000</t>
+  </si>
+  <si>
+    <t>OFG</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Small ($300M–$2B)</t>
+  </si>
+  <si>
+    <t>Price min</t>
+  </si>
+  <si>
+    <t>&gt; $7</t>
+  </si>
+  <si>
+    <t>YTD perf min</t>
+  </si>
+  <si>
+    <t>&gt; +10%</t>
+  </si>
+  <si>
+    <t>P/E max</t>
+  </si>
+  <si>
+    <t>&lt; 28</t>
+  </si>
+  <si>
+    <t>EPS Q/Q</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Sectors</t>
+  </si>
+  <si>
+    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Beta range</t>
+  </si>
+  <si>
+    <t>0.7 – 1.2</t>
+  </si>
+  <si>
+    <t>RSI min</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>&gt; 0</t>
+  </si>
+  <si>
+    <t>Ranked by</t>
+  </si>
+  <si>
+    <t>Alpha (highest first)</t>
+  </si>
+  <si>
+    <t>Top N</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>3 of 3 qualified</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>Dow Jones 30</t>
+  </si>
+  <si>
+    <t>&gt; $10</t>
+  </si>
+  <si>
+    <t>&gt; +5%</t>
+  </si>
+  <si>
+    <t>&lt; 35</t>
+  </si>
+  <si>
+    <t>All sectors</t>
+  </si>
+  <si>
+    <t>2 of 2 qualified</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 (large-cap subset)</t>
+  </si>
+  <si>
+    <t>UNP</t>
+  </si>
+  <si>
+    <t>Large (approx. S&amp;P 100)</t>
+  </si>
+  <si>
+    <t>&gt; +8%</t>
+  </si>
+  <si>
+    <t>&lt; 40</t>
   </si>
   <si>
     <t>Component</t>
@@ -3792,12 +3948,139 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3808,12 +4091,128 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3824,12 +4223,128 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3840,12 +4355,139 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3861,16 +4503,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3878,209 +4520,209 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="204">
   <si>
     <t>Ticker</t>
   </si>
@@ -51,6 +51,12 @@
     <t>DIS</t>
   </si>
   <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
     <t>UROY</t>
   </si>
   <si>
@@ -78,6 +84,12 @@
     <t>ENPH</t>
   </si>
   <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
     <t>MSTR</t>
   </si>
   <si>
@@ -105,6 +117,12 @@
     <t>RIVN</t>
   </si>
   <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
     <t>CEG</t>
   </si>
   <si>
@@ -162,6 +180,63 @@
     <t>P</t>
   </si>
   <si>
+    <t>BAC</t>
+  </si>
+  <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>VRTX</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>GILD</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t>NKE</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>AXP</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
     <t>EPS_TTM</t>
   </si>
   <si>
@@ -222,6 +297,9 @@
     <t>2026-04-16</t>
   </si>
   <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
     <t>2026-04-21</t>
   </si>
   <si>
@@ -231,55 +309,97 @@
     <t>2026-05-06</t>
   </si>
   <si>
+    <t>2027-03-12</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
     <t>2027-03-10</t>
   </si>
   <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2027-02-26</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
     <t>2027-03-04</t>
   </si>
   <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2027-02-26</t>
-  </si>
-  <si>
-    <t>2027-02-12</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2027-03-02</t>
-  </si>
-  <si>
-    <t>2027-02-24</t>
-  </si>
-  <si>
-    <t>2027-03-03</t>
-  </si>
-  <si>
-    <t>2027-02-18</t>
-  </si>
-  <si>
-    <t>2027-02-05</t>
+    <t>2026-05-14</t>
   </si>
   <si>
     <t>2027-03-05</t>
   </si>
   <si>
-    <t>2027-02-27</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
+    <t>2027-03-30</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2027-03-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>OFG</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>UNP</t>
   </si>
   <si>
     <t>_date_</t>
@@ -291,24 +411,15 @@
     <t>Value</t>
   </si>
   <si>
-    <t>WSR</t>
-  </si>
-  <si>
     <t>Last Run</t>
   </si>
   <si>
-    <t>BLX</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
     <t>Russell 2000</t>
   </si>
   <si>
-    <t>OFG</t>
-  </si>
-  <si>
     <t>Cap</t>
   </si>
   <si>
@@ -381,12 +492,6 @@
     <t>3 of 3 qualified</t>
   </si>
   <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>JPM</t>
-  </si>
-  <si>
     <t>Dow Jones 30</t>
   </si>
   <si>
@@ -405,9 +510,6 @@
     <t>2 of 2 qualified</t>
   </si>
   <si>
-    <t>AAPL</t>
-  </si>
-  <si>
     <t>Nasdaq 100</t>
   </si>
   <si>
@@ -420,16 +522,7 @@
     <t>60</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
     <t>S&amp;P 500 (large-cap subset)</t>
-  </si>
-  <si>
-    <t>UNP</t>
   </si>
   <si>
     <t>Large (approx. S&amp;P 100)</t>
@@ -938,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1139,6 +1232,36 @@
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1159,37 +1282,132 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1200,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1208,49 +1426,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="I1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="J1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K1" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="L1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="M1" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="N1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="O1" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="P1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1258,49 +1476,49 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>6.69</v>
+        <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>84.78260869565217</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.9805680119581465</v>
+        <v>-1.2192242833052276</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F2" s="1">
-        <v>0.1008274762122777</v>
+        <v>-0.014335314934530014</v>
       </c>
       <c r="G2" s="1">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>41.04</v>
+        <v>42.57</v>
       </c>
       <c r="I2" s="1">
-        <v>17.69</v>
+        <v>15.73</v>
       </c>
       <c r="J2" s="1">
-        <v>0.000767312784949413</v>
+        <v>0.0019894812329862566</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08129571015627968</v>
+        <v>-0.06462152315541192</v>
       </c>
       <c r="N2" s="1">
-        <v>45.652173913043484</v>
+        <v>38.875</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="P2" s="1">
-        <v>0.43</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1308,49 +1526,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="C3" s="2">
-        <v>67.3913043478261</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2">
-        <v>23.181818181818183</v>
+        <v>22.675409836065572</v>
       </c>
       <c r="E3" s="2">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="F3" s="2">
-        <v>0.13554675226258095</v>
+        <v>0.946407952265454</v>
       </c>
       <c r="G3" s="2">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="H3" s="2">
-        <v>82.76</v>
+        <v>81.18</v>
       </c>
       <c r="I3" s="2">
-        <v>46.67</v>
+        <v>96.36</v>
       </c>
       <c r="J3" s="2">
-        <v>0.033931736160777805</v>
+        <v>0.07149503357864534</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>361</v>
+        <v>241</v>
       </c>
       <c r="M3" s="2">
-        <v>0.16279477157526956</v>
+        <v>1.0328757005477023</v>
       </c>
       <c r="N3" s="2">
-        <v>77.3913043478261</v>
+        <v>75.125</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="P3" s="2">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1361,46 +1579,46 @@
         <v>-3.95</v>
       </c>
       <c r="C4" s="3">
-        <v>8.695652173913043</v>
+        <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>9.721518987341772</v>
+        <v>9.969620253164557</v>
       </c>
       <c r="E4" s="3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.2926409604404942</v>
+        <v>-0.23155735253643348</v>
       </c>
       <c r="G4" s="3">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="H4" s="3">
-        <v>51.36</v>
+        <v>43.23</v>
       </c>
       <c r="I4" s="3">
-        <v>-26.33</v>
+        <v>-32.17</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.011710159872109282</v>
+        <v>-0.017970759965882977</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>46</v>
+        <v>-10</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.2880594350693342</v>
+        <v>-0.2266513810026889</v>
       </c>
       <c r="N4" s="3">
-        <v>25.217391304347828</v>
+        <v>27.125</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="P4" s="3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1408,49 +1626,49 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="C5" s="4">
-        <v>58.69565217391305</v>
+        <v>38.75</v>
       </c>
       <c r="D5" s="4">
-        <v>28.39814814814815</v>
+        <v>23.85321100917431</v>
       </c>
       <c r="E5" s="4">
-        <v>0.58</v>
+        <v>0.76</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.15459476807109435</v>
+        <v>-0.13845170247221328</v>
       </c>
       <c r="G5" s="4">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="H5" s="4">
-        <v>54.55</v>
+        <v>59.39</v>
       </c>
       <c r="I5" s="4">
-        <v>-2.78</v>
+        <v>-1.18</v>
       </c>
       <c r="J5" s="4">
-        <v>-0.004931709406969973</v>
+        <v>-0.0047306354230083</v>
       </c>
       <c r="K5" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="4">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="M5" s="4">
-        <v>-0.1338573374437384</v>
+        <v>-0.0900052335764856</v>
       </c>
       <c r="N5" s="4">
-        <v>51.73913043478261</v>
+        <v>51.75</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="P5" s="4">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1461,46 +1679,46 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>69.56521739130434</v>
+        <v>46.25</v>
       </c>
       <c r="D6" s="1">
-        <v>1.5663430420711975</v>
+        <v>1.4271844660194175</v>
       </c>
       <c r="E6" s="1">
-        <v>-2.3</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" s="1">
-        <v>0.040289182066815615</v>
+        <v>-0.00401738951894387</v>
       </c>
       <c r="G6" s="1">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="H6" s="1">
-        <v>41.93</v>
+        <v>35.35</v>
       </c>
       <c r="I6" s="1">
-        <v>-11.58</v>
+        <v>-14.83</v>
       </c>
       <c r="J6" s="1">
-        <v>0.01776532060850231</v>
+        <v>0.013847841186918867</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="M6" s="1">
-        <v>0.05475715692311045</v>
+        <v>0.029097918333832018</v>
       </c>
       <c r="N6" s="1">
-        <v>46.95652173913043</v>
+        <v>45.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="P6" s="1">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1511,46 +1729,46 @@
         <v>4.9</v>
       </c>
       <c r="C7" s="4">
-        <v>78.26086956521739</v>
+        <v>53.75</v>
       </c>
       <c r="D7" s="4">
         <v>6.042857142857143</v>
       </c>
       <c r="E7" s="4">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="F7" s="4">
-        <v>0.03386742167029862</v>
+        <v>0.045005243338854056</v>
       </c>
       <c r="G7" s="4">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H7" s="4">
-        <v>69.62</v>
+        <v>60.81</v>
       </c>
       <c r="I7" s="4">
-        <v>10.87</v>
+        <v>12.78</v>
       </c>
       <c r="J7" s="4">
-        <v>0.011160502632594714</v>
+        <v>0.005434054466258972</v>
       </c>
       <c r="K7" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="4">
-        <v>410</v>
+        <v>237</v>
       </c>
       <c r="M7" s="4">
-        <v>0.06521470052560407</v>
+        <v>0.12104780211189503</v>
       </c>
       <c r="N7" s="4">
-        <v>61.95652173913042</v>
+        <v>58.125</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="P7" s="4">
-        <v>0</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1561,46 +1779,46 @@
         <v>13.24</v>
       </c>
       <c r="C8" s="4">
-        <v>97.82608695652173</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4">
-        <v>-0.024169184290030232</v>
+        <v>-0.006042296072507558</v>
       </c>
       <c r="E8" s="4">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="F8" s="4">
-        <v>-0.010226989146141601</v>
+        <v>0.2804993788872671</v>
       </c>
       <c r="G8" s="4">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="H8" s="4">
-        <v>81.17</v>
+        <v>75.88</v>
       </c>
       <c r="I8" s="4">
-        <v>12.61</v>
+        <v>16.01</v>
       </c>
       <c r="J8" s="4">
-        <v>0.01980807368851632</v>
+        <v>0.027966217704146333</v>
       </c>
       <c r="K8" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="4">
-        <v>48</v>
+        <v>-62</v>
       </c>
       <c r="M8" s="4">
-        <v>-0.021319103202634304</v>
+        <v>0.2590357534271346</v>
       </c>
       <c r="N8" s="4">
-        <v>65.8695652173913</v>
+        <v>65.625</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="P8" s="4">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1608,49 +1826,49 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="C9" s="4">
-        <v>54.347826086956516</v>
+        <v>33.75</v>
       </c>
       <c r="D9" s="4">
-        <v>67.1111111111111</v>
+        <v>46.08988764044943</v>
       </c>
       <c r="E9" s="4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.13310152654710197</v>
+        <v>-0.14455703709857712</v>
       </c>
       <c r="G9" s="4">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="H9" s="4">
-        <v>57.31</v>
+        <v>41.22</v>
       </c>
       <c r="I9" s="4">
-        <v>-7.56</v>
+        <v>-18.46</v>
       </c>
       <c r="J9" s="4">
-        <v>0.0036667583722992786</v>
+        <v>0.00468654143378392</v>
       </c>
       <c r="K9" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="4">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="M9" s="4">
-        <v>-0.11815128586226398</v>
+        <v>-0.11328146857095545</v>
       </c>
       <c r="N9" s="4">
-        <v>55.65217391304348</v>
+        <v>50.875</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="P9" s="4">
-        <v>0</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1658,399 +1876,395 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>6.79</v>
+        <v>6.25</v>
       </c>
       <c r="C10" s="1">
-        <v>86.95652173913044</v>
+        <v>63.74999999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>0.6435935198821797</v>
+        <v>0.6272</v>
       </c>
       <c r="E10" s="1">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.12398974230389055</v>
+        <v>-0.08839620277587429</v>
       </c>
       <c r="G10" s="1">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>61.31</v>
+        <v>64.58</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.16</v>
+        <v>-1.21</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.0013695809862560113</v>
+        <v>-0.0024646974138411515</v>
       </c>
       <c r="K10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>-23</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.06263985222371526</v>
+      </c>
+      <c r="N10" s="1">
+        <v>49</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>-1.36</v>
+      </c>
+      <c r="C11" s="4">
+        <v>13.750000000000002</v>
+      </c>
+      <c r="D11" s="4">
+        <v>31.610294117647058</v>
+      </c>
+      <c r="E11" s="4">
+        <v>8.33</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.06635419575295845</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="H11" s="4">
+        <v>60.26</v>
+      </c>
+      <c r="I11" s="4">
+        <v>-2.33</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.015901187035988293</v>
+      </c>
+      <c r="K11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="1">
-        <v>42</v>
-      </c>
-      <c r="M10" s="1">
-        <v>-0.11313876116166943</v>
-      </c>
-      <c r="N10" s="1">
-        <v>48.47826086956522</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="1">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="C11" s="3">
-        <v>47.82608695652174</v>
-      </c>
-      <c r="D11" s="3">
-        <v>-1653.5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>10.01</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-0.25701617436476676</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1.42</v>
-      </c>
-      <c r="H11" s="3">
-        <v>52.4</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1.71</v>
-      </c>
-      <c r="J11" s="3">
-        <v>-0.012555010041612849</v>
-      </c>
-      <c r="K11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>28</v>
-      </c>
-      <c r="M11" s="3">
-        <v>-0.2468885919653604</v>
-      </c>
-      <c r="N11" s="3">
-        <v>25.434782608695652</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0.43</v>
-      </c>
+      <c r="L11" s="4">
+        <v>-3</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0.05347602047687894</v>
+      </c>
+      <c r="N11" s="4">
+        <v>53</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>1.31</v>
+        <v>-0.34</v>
       </c>
       <c r="C12" s="1">
-        <v>63.04347826086957</v>
+        <v>22.5</v>
       </c>
       <c r="D12" s="1">
-        <v>7.5114503816793885</v>
+        <v>65.85294117647058</v>
       </c>
       <c r="E12" s="1">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.1505522723541079</v>
+        <v>-0.3151835593916287</v>
       </c>
       <c r="G12" s="1">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="H12" s="1">
-        <v>55.4</v>
+        <v>59.32</v>
       </c>
       <c r="I12" s="1">
-        <v>-9.57</v>
+        <v>-34.38</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.012143051089573783</v>
+        <v>-0.011454434566654514</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="1">
+        <v>-5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.3256087489008359</v>
+      </c>
+      <c r="N12" s="1">
+        <v>41.875</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="3">
+        <v>28.749999999999996</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-1653.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>13.04</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-0.10808278596901545</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="H13" s="3">
+        <v>62.37</v>
+      </c>
+      <c r="I13" s="3">
+        <v>9.36</v>
+      </c>
+      <c r="J13" s="3">
+        <v>-0.009177233320267129</v>
+      </c>
+      <c r="K13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>22</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-0.08171318897513835</v>
+      </c>
+      <c r="N13" s="3">
+        <v>26</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C14" s="1">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7.557251908396947</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-0.83</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-0.11861693755356174</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="H14" s="1">
+        <v>54.02</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-9.7</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.0005773612701066432</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>-0.1437600416640027</v>
+      </c>
+      <c r="N14" s="1">
+        <v>47.625</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P14" s="1">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="1">
-        <v>-0.1589919243536132</v>
-      </c>
-      <c r="N12" s="1">
-        <v>41.52173913043479</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <v>-0.08</v>
-      </c>
-      <c r="C13" s="2">
-        <v>41.30434782608695</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1166</v>
-      </c>
-      <c r="E13" s="2">
-        <v>6.17</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.1534630938967733</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1.65</v>
-      </c>
-      <c r="H13" s="2">
-        <v>68.58</v>
-      </c>
-      <c r="I13" s="2">
-        <v>72.52</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.036242152949882776</v>
-      </c>
-      <c r="K13" s="2" t="b">
+      <c r="B15" s="2">
+        <v>-0.63</v>
+      </c>
+      <c r="C15" s="2">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2">
+        <v>62.25396825396826</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5.96</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.1796445417596797</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>85.92</v>
+      </c>
+      <c r="I15" s="2">
+        <v>172.99</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.10727136583311915</v>
+      </c>
+      <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L13" s="2">
-        <v>250</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0.16913673332442603</v>
-      </c>
-      <c r="N13" s="2">
-        <v>76.73913043478261</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P13" s="2">
+      <c r="L15" s="2">
+        <v>230</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1.2532341147658483</v>
+      </c>
+      <c r="N15" s="2">
+        <v>72.375</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P15" s="2">
+        <v>-4.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-3.83</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>11.890339425587467</v>
+      </c>
+      <c r="E16" s="1">
+        <v>4.46</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-0.00855633945060777</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.93</v>
+      </c>
+      <c r="H16" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="I16" s="1">
+        <v>5.07</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.004220961927641882</v>
+      </c>
+      <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4">
-        <v>-3.83</v>
-      </c>
-      <c r="C14" s="4">
-        <v>10.869565217391305</v>
-      </c>
-      <c r="D14" s="4">
-        <v>12.668407310704959</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2.52</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0.08438187589888259</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2.07</v>
-      </c>
-      <c r="H14" s="4">
-        <v>67.8</v>
-      </c>
-      <c r="I14" s="4">
-        <v>22.8</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0.02197442468749787</v>
-      </c>
-      <c r="K14" s="4" t="b">
+      <c r="L16" s="1">
+        <v>20</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0.04847557962917293</v>
+      </c>
+      <c r="N16" s="1">
+        <v>43.75</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P16" s="1">
+        <v>-8.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-6.21</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4.3784219001610305</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4.78</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-0.01958755294764694</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="H17" s="1">
+        <v>55.5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-2.23</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.0028009845159087795</v>
+      </c>
+      <c r="K17" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L14" s="4">
-        <v>24</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0.1101830977259417</v>
-      </c>
-      <c r="N14" s="4">
-        <v>51.95652173913044</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="P14" s="4">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <v>-6.51</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4.3478260869565215</v>
-      </c>
-      <c r="D15" s="1">
-        <v>4.411674347158218</v>
-      </c>
-      <c r="E15" s="1">
-        <v>4.53</v>
-      </c>
-      <c r="F15" s="1">
-        <v>-0.0412979929126466</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="H15" s="1">
-        <v>57.34</v>
-      </c>
-      <c r="I15" s="1">
-        <v>-2.19</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0.013889694610936927</v>
-      </c>
-      <c r="K15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>42</v>
-      </c>
-      <c r="M15" s="1">
-        <v>-0.021525093942377005</v>
-      </c>
-      <c r="N15" s="1">
-        <v>33.69565217391305</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P15" s="1">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>-0.01</v>
-      </c>
-      <c r="C16" s="4">
-        <v>45.65217391304348</v>
-      </c>
-      <c r="D16" s="4">
-        <v>18685</v>
-      </c>
-      <c r="E16" s="4">
-        <v>11.11</v>
-      </c>
-      <c r="F16" s="4">
-        <v>-0.14574757884685463</v>
-      </c>
-      <c r="G16" s="4">
-        <v>1.22</v>
-      </c>
-      <c r="H16" s="4">
-        <v>57.77</v>
-      </c>
-      <c r="I16" s="4">
-        <v>16.75</v>
-      </c>
-      <c r="J16" s="4">
-        <v>-0.0019455263977864303</v>
-      </c>
-      <c r="K16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
-        <v>31</v>
-      </c>
-      <c r="M16" s="4">
-        <v>-0.14044265473287987</v>
-      </c>
-      <c r="N16" s="4">
-        <v>62.82608695652174</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="P16" s="4">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4">
-        <v>8.81</v>
-      </c>
-      <c r="C17" s="4">
-        <v>93.47826086956522</v>
-      </c>
-      <c r="D17" s="4">
-        <v>-0.2542565266742338</v>
-      </c>
-      <c r="E17" s="4">
-        <v>4.52</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0.08860564312184951</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.18</v>
-      </c>
-      <c r="H17" s="4">
-        <v>59.17</v>
-      </c>
-      <c r="I17" s="4">
-        <v>16.95</v>
-      </c>
-      <c r="J17" s="4">
-        <v>-0.003154923684622415</v>
-      </c>
-      <c r="K17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>95</v>
-      </c>
-      <c r="M17" s="4">
-        <v>0.06883274415157992</v>
-      </c>
-      <c r="N17" s="4">
-        <v>51.08695652173914</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P17" s="4">
-        <v>0</v>
+      <c r="L17" s="1">
+        <v>41</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.025792683739490396</v>
+      </c>
+      <c r="N17" s="1">
+        <v>32.75</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="1">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2058,49 +2272,49 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>27.92</v>
+        <v>0.09</v>
       </c>
       <c r="C18" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4">
-        <v>-0.5508595988538683</v>
+        <v>1467.6666666666667</v>
       </c>
       <c r="E18" s="4">
-        <v>-1.85</v>
+        <v>8.29</v>
       </c>
       <c r="F18" s="4">
-        <v>-0.07768872066430293</v>
+        <v>-0.23696044869660288</v>
       </c>
       <c r="G18" s="4">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="H18" s="4">
-        <v>63.12</v>
+        <v>37.27</v>
       </c>
       <c r="I18" s="4">
-        <v>2.9</v>
+        <v>-0.64</v>
       </c>
       <c r="J18" s="4">
-        <v>-0.00017124448272952357</v>
+        <v>-0.0030434655943608487</v>
       </c>
       <c r="K18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="4">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M18" s="4">
-        <v>-0.07407172695022923</v>
+        <v>-0.22162928765365109</v>
       </c>
       <c r="N18" s="4">
-        <v>54.34782608695652</v>
+        <v>50.5</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="P18" s="4">
-        <v>0.22</v>
+        <v>-12.33</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2108,49 +2322,49 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>1.29</v>
+        <v>9.32</v>
       </c>
       <c r="C19" s="1">
-        <v>60.86956521739131</v>
+        <v>76.25</v>
       </c>
       <c r="D19" s="1">
-        <v>15.51937984496124</v>
+        <v>0.10193133047210293</v>
       </c>
       <c r="E19" s="1">
-        <v>3.37</v>
+        <v>2.93</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.059362273386575806</v>
+        <v>0.00518672020097773</v>
       </c>
       <c r="G19" s="1">
-        <v>1.33</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>47.16</v>
+        <v>56.59</v>
       </c>
       <c r="I19" s="1">
-        <v>-4.03</v>
+        <v>15.28</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.032972728826274986</v>
+        <v>-0.002850051217110792</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>-8</v>
+        <v>86</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.05140488721561365</v>
+        <v>-0.04387299513646803</v>
       </c>
       <c r="N19" s="1">
-        <v>44.1304347826087</v>
+        <v>49</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.22</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2158,99 +2372,99 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>-18.39</v>
+        <v>6.07</v>
       </c>
       <c r="C20" s="1">
-        <v>2.1739130434782608</v>
+        <v>61.25000000000001</v>
       </c>
       <c r="D20" s="1">
-        <v>-4.206090266449157</v>
+        <v>0.9456342668863262</v>
       </c>
       <c r="E20" s="1">
-        <v>8.76</v>
+        <v>-1.81</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.01879277749792678</v>
+        <v>-0.22839359236010615</v>
       </c>
       <c r="G20" s="1">
-        <v>3.65</v>
+        <v>1.05</v>
       </c>
       <c r="H20" s="1">
-        <v>72.27</v>
+        <v>36.95</v>
       </c>
       <c r="I20" s="1">
-        <v>-25.64</v>
+        <v>-11.45</v>
       </c>
       <c r="J20" s="1">
-        <v>0.02783189594132707</v>
+        <v>-0.002894402747055063</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>-46</v>
+        <v>2</v>
       </c>
       <c r="M20" s="1">
-        <v>0.04510744478404205</v>
+        <v>-0.22532736015151578</v>
       </c>
       <c r="N20" s="1">
-        <v>30</v>
+        <v>41.75</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="P20" s="1">
+        <v>-12.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="C21" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="D21" s="1">
+        <v>14.107843137254902</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3.69</v>
+      </c>
+      <c r="F21" s="1">
+        <v>-0.3951605166124976</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="H21" s="1">
+        <v>52.09</v>
+      </c>
+      <c r="I21" s="1">
+        <v>-1.23</v>
+      </c>
+      <c r="J21" s="1">
+        <v>-0.03197467631905114</v>
+      </c>
+      <c r="K21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3">
-        <v>-2.25</v>
-      </c>
-      <c r="C21" s="3">
-        <v>19.565217391304348</v>
-      </c>
-      <c r="D21" s="3">
-        <v>10.44</v>
-      </c>
-      <c r="E21" s="3">
-        <v>12.21</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-0.4257523619448244</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2.26</v>
-      </c>
-      <c r="H21" s="3">
-        <v>57.74</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-52.37</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-0.036738611374177825</v>
-      </c>
-      <c r="K21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="3">
-        <v>25</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-0.39536961474660526</v>
-      </c>
-      <c r="N21" s="3">
-        <v>26.739130434782606</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0.87</v>
+      <c r="L21" s="1">
+        <v>8</v>
+      </c>
+      <c r="M21" s="1">
+        <v>-0.37921610912782777</v>
+      </c>
+      <c r="N21" s="1">
+        <v>42.25</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P21" s="1">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2258,349 +2472,345 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <v>8.11</v>
+      </c>
+      <c r="C22" s="1">
+        <v>68.75</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.6929716399506783</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-0.1029051588163294</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="H22" s="1">
+        <v>56.44</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-0.015785479600669304</v>
+      </c>
+      <c r="K22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>162</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-0.08021504047276073</v>
+      </c>
+      <c r="N22" s="1">
+        <v>43.125</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>27.51</v>
+      </c>
+      <c r="C23" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-0.7539076699382044</v>
+      </c>
+      <c r="E23" s="1">
+        <v>-0.69</v>
+      </c>
+      <c r="F23" s="1">
+        <v>-0.1706652417288873</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="H23" s="1">
+        <v>42.84</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-9.45</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-0.005423791546682635</v>
+      </c>
+      <c r="K23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>75</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-0.15594732712765358</v>
+      </c>
+      <c r="N23" s="1">
+        <v>42.375</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-40.16</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-0.4108565737051793</v>
+      </c>
+      <c r="E24" s="1">
+        <v>9.26</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.2169152463573835</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3.58</v>
+      </c>
+      <c r="H24" s="1">
+        <v>68.85</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-17.27</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.03798572362457417</v>
+      </c>
+      <c r="K24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>3</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.3751328283206461</v>
+      </c>
+      <c r="N24" s="1">
+        <v>32</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-2.25</v>
+      </c>
+      <c r="C25" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7.142222222222222</v>
+      </c>
+      <c r="E25" s="1">
+        <v>13.04</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-0.3141625591989796</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="H25" s="1">
+        <v>58.83</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-46.26</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-0.010423562358953769</v>
+      </c>
+      <c r="K25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>34</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-0.2375067539842206</v>
+      </c>
+      <c r="N25" s="1">
+        <v>31.124999999999996</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="P25" s="1">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
         <v>-2.38</v>
       </c>
-      <c r="C22" s="1">
-        <v>17.391304347826086</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1.4705882352941178</v>
-      </c>
-      <c r="E22" s="1">
-        <v>5.89</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-0.11802123762200953</v>
-      </c>
-      <c r="G22" s="1">
-        <v>3.08</v>
-      </c>
-      <c r="H22" s="1">
-        <v>72.74</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1.33</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0.03470869757352629</v>
-      </c>
-      <c r="K22" s="1" t="b">
+      <c r="C26" s="1">
+        <v>11.25</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-14.344537815126051</v>
+      </c>
+      <c r="E26" s="1">
+        <v>5.04</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.2897593391764458</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3.05</v>
+      </c>
+      <c r="H26" s="1">
+        <v>72.67</v>
+      </c>
+      <c r="I26" s="1">
+        <v>12.86</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.043515570359671</v>
+      </c>
+      <c r="K26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>21</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0.4154748597286506</v>
+      </c>
+      <c r="N26" s="1">
+        <v>37.75</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P26" s="1">
+        <v>-8.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-1.13</v>
+      </c>
+      <c r="C27" s="1">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2.4513274336283186</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-0.15793305888820516</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.62</v>
+      </c>
+      <c r="H27" s="1">
+        <v>65.51</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-21.47</v>
+      </c>
+      <c r="J27" s="1">
+        <v>-0.006437350179720533</v>
+      </c>
+      <c r="K27" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L22" s="1">
-        <v>48</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.06786559145352078</v>
-      </c>
-      <c r="N22" s="1">
-        <v>45.869565217391305</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="P22" s="1">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3">
-        <v>-1.13</v>
-      </c>
-      <c r="C23" s="3">
-        <v>21.73913043478261</v>
-      </c>
-      <c r="D23" s="3">
-        <v>5.7522123893805315</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1.42</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-0.4479682759646458</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2.66</v>
-      </c>
-      <c r="H23" s="3">
-        <v>49.03</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-34.14</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-0.013220085323303233</v>
-      </c>
-      <c r="K23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>39</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-0.4079402121955634</v>
-      </c>
-      <c r="N23" s="3">
-        <v>22.391304347826086</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="L27" s="1">
+        <v>34</v>
+      </c>
+      <c r="M27" s="1">
+        <v>-0.05858713532987747</v>
+      </c>
+      <c r="N27" s="1">
+        <v>34.25</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="1">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
         <v>-0.99</v>
       </c>
-      <c r="C24" s="3">
-        <v>23.91304347826087</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="C28" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="D28" s="3">
         <v>3.04040404040404</v>
       </c>
-      <c r="E24" s="3">
-        <v>3.54</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-0.3834461650194826</v>
-      </c>
-      <c r="G24" s="3">
-        <v>3.24</v>
-      </c>
-      <c r="H24" s="3">
-        <v>52.77</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-30.24</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-0.0161972256448195</v>
-      </c>
-      <c r="K24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>61</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-0.32943239222264853</v>
-      </c>
-      <c r="N24" s="3">
-        <v>22.60869565217391</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0.38</v>
-      </c>
-      <c r="C25" s="4">
-        <v>50</v>
-      </c>
-      <c r="D25" s="4">
-        <v>89.71052631578947</v>
-      </c>
-      <c r="E25" s="4">
-        <v>2.21</v>
-      </c>
-      <c r="F25" s="4">
-        <v>-0.3271270914927164</v>
-      </c>
-      <c r="G25" s="4">
-        <v>2.3</v>
-      </c>
-      <c r="H25" s="4">
-        <v>61.04</v>
-      </c>
-      <c r="I25" s="4">
-        <v>-20.47</v>
-      </c>
-      <c r="J25" s="4">
-        <v>-0.009321426722427306</v>
-      </c>
-      <c r="K25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4">
-        <v>62</v>
-      </c>
-      <c r="M25" s="4">
-        <v>-0.29577981263741093</v>
-      </c>
-      <c r="N25" s="4">
-        <v>51.52173913043478</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P25" s="4">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4">
-        <v>1.9</v>
-      </c>
-      <c r="C26" s="4">
-        <v>65.21739130434783</v>
-      </c>
-      <c r="D26" s="4">
-        <v>2990.236842105264</v>
-      </c>
-      <c r="E26" s="4">
-        <v>2.07</v>
-      </c>
-      <c r="F26" s="4">
-        <v>-0.1137240652607237</v>
-      </c>
-      <c r="G26" s="4">
-        <v>1.19</v>
-      </c>
-      <c r="H26" s="4">
-        <v>62.57</v>
-      </c>
-      <c r="I26" s="4">
-        <v>5.52</v>
-      </c>
-      <c r="J26" s="4">
-        <v>-0.0068792273359546295</v>
-      </c>
-      <c r="K26" s="4" t="b">
+      <c r="E28" s="3">
+        <v>-0.07</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-0.2803939746279312</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3.13</v>
+      </c>
+      <c r="H28" s="3">
+        <v>61.5</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-22.76</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-0.018593477707233675</v>
+      </c>
+      <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L26" s="4">
-        <v>101</v>
-      </c>
-      <c r="M26" s="4">
-        <v>-0.10914253988956368</v>
-      </c>
-      <c r="N26" s="4">
-        <v>66.73913043478261</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="P26" s="4">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2">
-        <v>5.13</v>
-      </c>
-      <c r="C27" s="2">
-        <v>80.43478260869566</v>
-      </c>
-      <c r="D27" s="2">
-        <v>10.491228070175438</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.23160151071424817</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="H27" s="2">
-        <v>78.63</v>
-      </c>
-      <c r="I27" s="2">
-        <v>25.29</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0.02489548308240803</v>
-      </c>
-      <c r="K27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>386</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0.24124682728511138</v>
-      </c>
-      <c r="N27" s="2">
-        <v>76.08695652173913</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <v>-3.07</v>
-      </c>
-      <c r="C28" s="1">
-        <v>13.043478260869565</v>
-      </c>
-      <c r="D28" s="1">
-        <v>8.667752442996743</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2.29</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0.02300113273057261</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="H28" s="1">
-        <v>66.58</v>
-      </c>
-      <c r="I28" s="1">
-        <v>16.73</v>
-      </c>
-      <c r="J28" s="1">
-        <v>0.01811225760128193</v>
-      </c>
-      <c r="K28" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>44</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0.040121569643854826</v>
-      </c>
-      <c r="N28" s="1">
-        <v>46.95652173913044</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P28" s="1">
-        <v>-1.09</v>
+      <c r="L28" s="3">
+        <v>42</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-0.14977248254198183</v>
+      </c>
+      <c r="N28" s="3">
+        <v>29.5</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" s="3">
+        <v>6.89</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2608,49 +2818,49 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>7.4</v>
+        <v>0.44</v>
       </c>
       <c r="C29" s="1">
-        <v>91.30434782608695</v>
+        <v>31.25</v>
       </c>
       <c r="D29" s="1">
-        <v>1.2256756756756755</v>
+        <v>77.0909090909091</v>
       </c>
       <c r="E29" s="1">
-        <v>-0.84</v>
+        <v>0.86</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.06157745009525035</v>
+        <v>-0.355829360179417</v>
       </c>
       <c r="G29" s="1">
-        <v>1.09</v>
+        <v>2.13</v>
       </c>
       <c r="H29" s="1">
-        <v>47.51</v>
+        <v>41.93</v>
       </c>
       <c r="I29" s="1">
-        <v>-12.18</v>
+        <v>-31.17</v>
       </c>
       <c r="J29" s="1">
-        <v>0.010030126685428955</v>
+        <v>-0.015445277039866463</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.05940725386680612</v>
+        <v>-0.2865325122652749</v>
       </c>
       <c r="N29" s="1">
-        <v>49.99999999999999</v>
+        <v>41</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="P29" s="1">
-        <v>0.22</v>
+        <v>-10.52</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2658,349 +2868,345 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>5.41</v>
+        <v>1.95</v>
       </c>
       <c r="C30" s="4">
-        <v>82.6086956521739</v>
+        <v>42.5</v>
       </c>
       <c r="D30" s="4">
-        <v>0.6487985212569316</v>
+        <v>1974.0307692307692</v>
       </c>
       <c r="E30" s="4">
-        <v>-0.09</v>
+        <v>1.87</v>
       </c>
       <c r="F30" s="4">
-        <v>-0.13114399355140938</v>
+        <v>-0.11046671794470034</v>
       </c>
       <c r="G30" s="4">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="H30" s="4">
-        <v>67.82</v>
+        <v>56.88</v>
       </c>
       <c r="I30" s="4">
-        <v>-14.94</v>
+        <v>4.72</v>
       </c>
       <c r="J30" s="4">
-        <v>0.02244117984151456</v>
+        <v>-0.003350018743476765</v>
       </c>
       <c r="K30" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="4">
-        <v>-63</v>
+        <v>79</v>
       </c>
       <c r="M30" s="4">
-        <v>-0.12101641115200301</v>
+        <v>-0.09758854266862083</v>
       </c>
       <c r="N30" s="4">
-        <v>56.08695652173913</v>
+        <v>59.25</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="P30" s="4">
-        <v>0.43</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="4">
-        <v>-0.74</v>
-      </c>
-      <c r="C31" s="4">
-        <v>28.26086956521739</v>
-      </c>
-      <c r="D31" s="4">
-        <v>36.608108108108105</v>
-      </c>
-      <c r="E31" s="4">
-        <v>1.22</v>
-      </c>
-      <c r="F31" s="4">
-        <v>0.0027810480137657745</v>
-      </c>
-      <c r="G31" s="4">
-        <v>1.08</v>
-      </c>
-      <c r="H31" s="4">
-        <v>65.81</v>
-      </c>
-      <c r="I31" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="J31" s="4">
-        <v>0.008421891102854916</v>
-      </c>
-      <c r="K31" s="4" t="b">
+      <c r="B31" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="C31" s="2">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="D31" s="2">
+        <v>10.491228070175438</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.2820170759382124</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1.44</v>
+      </c>
+      <c r="H31" s="2">
+        <v>68.01</v>
+      </c>
+      <c r="I31" s="2">
+        <v>24.35</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.02612502060622656</v>
+      </c>
+      <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L31" s="4">
-        <v>90</v>
-      </c>
-      <c r="M31" s="4">
-        <v>0.0047101113279384155</v>
-      </c>
-      <c r="N31" s="4">
-        <v>53.26086956521739</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="P31" s="4">
-        <v>-0.22</v>
+      <c r="L31" s="2">
+        <v>237</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0.30899991937380755</v>
+      </c>
+      <c r="N31" s="2">
+        <v>70</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P31" s="2">
+        <v>-6.09</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4">
-        <v>-0.18</v>
-      </c>
-      <c r="C32" s="4">
-        <v>39.130434782608695</v>
-      </c>
-      <c r="D32" s="4">
-        <v>105.33333333333334</v>
-      </c>
-      <c r="E32" s="4">
-        <v>-4.72</v>
-      </c>
-      <c r="F32" s="4">
-        <v>0.11290929379608892</v>
-      </c>
-      <c r="G32" s="4">
-        <v>1.36</v>
-      </c>
-      <c r="H32" s="4">
-        <v>70.33</v>
-      </c>
-      <c r="I32" s="4">
-        <v>11.33</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0.022736747770421565</v>
-      </c>
-      <c r="K32" s="4" t="b">
+      <c r="B32" s="1">
+        <v>-2.92</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10</v>
+      </c>
+      <c r="D32" s="1">
+        <v>8.23972602739726</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="F32" s="1">
+        <v>-0.10305435736585863</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="H32" s="1">
+        <v>38.02</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-5.47</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.0026477925685757693</v>
+      </c>
+      <c r="K32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>37</v>
+      </c>
+      <c r="M32" s="1">
+        <v>-0.0644198315376201</v>
+      </c>
+      <c r="N32" s="1">
+        <v>35.875</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P32" s="1">
+        <v>-11.08</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4">
+        <v>16.79</v>
+      </c>
+      <c r="C33" s="4">
+        <v>88.75</v>
+      </c>
+      <c r="D33" s="4">
+        <v>-0.06075044669446097</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="F33" s="4">
+        <v>-0.07814918937625251</v>
+      </c>
+      <c r="G33" s="4">
+        <v>1.09</v>
+      </c>
+      <c r="H33" s="4">
+        <v>54.07</v>
+      </c>
+      <c r="I33" s="4">
+        <v>-11.27</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0.004672074264792407</v>
+      </c>
+      <c r="K33" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="4">
-        <v>-11</v>
-      </c>
-      <c r="M32" s="4">
-        <v>0.12159007870986582</v>
-      </c>
-      <c r="N32" s="4">
-        <v>68.47826086956522</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="P32" s="4">
+      <c r="L33" s="4">
+        <v>150</v>
+      </c>
+      <c r="M33" s="4">
+        <v>-0.07262997140078986</v>
+      </c>
+      <c r="N33" s="4">
+        <v>50.375</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4">
+        <v>12.78</v>
+      </c>
+      <c r="C34" s="4">
+        <v>83.75</v>
+      </c>
+      <c r="D34" s="4">
+        <v>-0.6267605633802817</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0.10653944803522034</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1.27</v>
+      </c>
+      <c r="H34" s="4">
+        <v>83.47</v>
+      </c>
+      <c r="I34" s="4">
+        <v>40.06</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0.02540855102647141</v>
+      </c>
+      <c r="K34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4">
+        <v>249</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0.12309710196160828</v>
+      </c>
+      <c r="N34" s="4">
+        <v>62.75</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="C35" s="4">
+        <v>67.5</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1.2310810810810813</v>
+      </c>
+      <c r="E35" s="4">
+        <v>-0.78</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0.20747532216979983</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1.15</v>
+      </c>
+      <c r="H35" s="4">
+        <v>60.66</v>
+      </c>
+      <c r="I35" s="4">
+        <v>-1.34</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.006523283987740831</v>
+      </c>
+      <c r="K35" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1">
-        <v>-4.08</v>
-      </c>
-      <c r="C33" s="1">
-        <v>6.521739130434782</v>
-      </c>
-      <c r="D33" s="1">
-        <v>14.372549019607844</v>
-      </c>
-      <c r="E33" s="1">
-        <v>13.14</v>
-      </c>
-      <c r="F33" s="1">
-        <v>0.0948011949387904</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>62.13</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-6.76</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.04208599862763582</v>
-      </c>
-      <c r="K33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>19</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0.07068790351163234</v>
-      </c>
-      <c r="N33" s="1">
-        <v>49.130434782608695</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P33" s="1">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1">
-        <v>-0.48</v>
-      </c>
-      <c r="C34" s="1">
-        <v>30.434782608695656</v>
-      </c>
-      <c r="D34" s="1">
-        <v>85.89583333333333</v>
-      </c>
-      <c r="E34" s="1">
-        <v>-1.38</v>
-      </c>
-      <c r="F34" s="1">
-        <v>-0.3115998911395332</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="H34" s="1">
-        <v>53.46</v>
-      </c>
-      <c r="I34" s="1">
-        <v>-33.19</v>
-      </c>
-      <c r="J34" s="1">
-        <v>-0.010947727472033765</v>
-      </c>
-      <c r="K34" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>2</v>
-      </c>
-      <c r="M34" s="1">
-        <v>-0.3147346190250637</v>
-      </c>
-      <c r="N34" s="1">
-        <v>40.65217391304348</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <v>3.52</v>
-      </c>
-      <c r="C35" s="1">
-        <v>73.91304347826086</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1.1988636363636365</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0.02862922306194351</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.38</v>
-      </c>
-      <c r="H35" s="1">
-        <v>38.34</v>
-      </c>
-      <c r="I35" s="1">
-        <v>2.56</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0.005678463488259859</v>
-      </c>
-      <c r="K35" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>30</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0.01367898237710552</v>
-      </c>
-      <c r="N35" s="1">
-        <v>45.21739130434782</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P35" s="1">
-        <v>-0.43</v>
+      <c r="L35" s="4">
+        <v>39</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.2166740187955709</v>
+      </c>
+      <c r="N35" s="4">
+        <v>56.875</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P35" s="4">
+        <v>6.88</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="4">
-        <v>-0.02</v>
-      </c>
-      <c r="C36" s="4">
-        <v>43.47826086956522</v>
-      </c>
-      <c r="D36" s="4">
-        <v>1215</v>
-      </c>
-      <c r="E36" s="4">
-        <v>5.89</v>
-      </c>
-      <c r="F36" s="4">
-        <v>-0.036259160275768546</v>
-      </c>
-      <c r="G36" s="4">
-        <v>1.41</v>
-      </c>
-      <c r="H36" s="4">
-        <v>57.49</v>
-      </c>
-      <c r="I36" s="4">
-        <v>-9.02</v>
-      </c>
-      <c r="J36" s="4">
-        <v>0.018969747496321538</v>
-      </c>
-      <c r="K36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4">
-        <v>29</v>
-      </c>
-      <c r="M36" s="4">
-        <v>-0.026372710790633747</v>
-      </c>
-      <c r="N36" s="4">
-        <v>63.04347826086957</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="P36" s="4">
-        <v>-0.22</v>
+      <c r="B36" s="1">
+        <v>5.33</v>
+      </c>
+      <c r="C36" s="1">
+        <v>58.75</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="E36" s="1">
+        <v>-0.23</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.031720219969567004</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="H36" s="1">
+        <v>40.92</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-21.43</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.012000240621086893</v>
+      </c>
+      <c r="K36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>-96</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0.05563683119657181</v>
+      </c>
+      <c r="N36" s="1">
+        <v>44</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P36" s="1">
+        <v>-12.09</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -3008,49 +3214,49 @@
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>0.94</v>
+        <v>-0.74</v>
       </c>
       <c r="C37" s="4">
-        <v>56.52173913043478</v>
+        <v>17.5</v>
       </c>
       <c r="D37" s="4">
-        <v>31.03191489361702</v>
+        <v>36.689189189189186</v>
       </c>
       <c r="E37" s="4">
-        <v>-0.72</v>
+        <v>0.47</v>
       </c>
       <c r="F37" s="4">
-        <v>-0.12542455724540152</v>
+        <v>0.05114789911445167</v>
       </c>
       <c r="G37" s="4">
-        <v>2.78</v>
+        <v>1.06</v>
       </c>
       <c r="H37" s="4">
-        <v>60.11</v>
+        <v>61.67</v>
       </c>
       <c r="I37" s="4">
-        <v>-6.63</v>
+        <v>2.31</v>
       </c>
       <c r="J37" s="4">
-        <v>0.01351706395763758</v>
+        <v>0.018836097329806758</v>
       </c>
       <c r="K37" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="4">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="M37" s="4">
-        <v>-0.08250289850506021</v>
+        <v>0.0548273777647601</v>
       </c>
       <c r="N37" s="4">
-        <v>59.1304347826087</v>
+        <v>57.25</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="P37" s="4">
-        <v>-0.22</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -3058,49 +3264,49 @@
         <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>7.17</v>
+        <v>-0.18</v>
       </c>
       <c r="C38" s="4">
-        <v>89.13043478260869</v>
+        <v>23.75</v>
       </c>
       <c r="D38" s="4">
-        <v>2.0557880055788007</v>
+        <v>100</v>
       </c>
       <c r="E38" s="4">
-        <v>0.78</v>
+        <v>-5.65</v>
       </c>
       <c r="F38" s="4">
-        <v>0.052951277478668554</v>
+        <v>0.1501734239706899</v>
       </c>
       <c r="G38" s="4">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="H38" s="4">
-        <v>76.19</v>
+        <v>59.09</v>
       </c>
       <c r="I38" s="4">
-        <v>12.39</v>
+        <v>11.12</v>
       </c>
       <c r="J38" s="4">
-        <v>0.01301767497237266</v>
+        <v>0.02030200149913848</v>
       </c>
       <c r="K38" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="4">
-        <v>402</v>
+        <v>-15</v>
       </c>
       <c r="M38" s="4">
-        <v>0.06307885987807493</v>
+        <v>0.1691840636639501</v>
       </c>
       <c r="N38" s="4">
-        <v>64.78260869565219</v>
+        <v>61.625</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="P38" s="4">
-        <v>0</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3108,199 +3314,199 @@
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>-0.38</v>
+        <v>-4.08</v>
       </c>
       <c r="C39" s="4">
-        <v>34.78260869565217</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4">
-        <v>882.7368421052631</v>
+        <v>14.436274509803921</v>
       </c>
       <c r="E39" s="4">
-        <v>0.68</v>
+        <v>12.76</v>
       </c>
       <c r="F39" s="4">
-        <v>-0.08623749324450543</v>
+        <v>0.618294122442242</v>
       </c>
       <c r="G39" s="4">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="H39" s="4">
-        <v>60.23</v>
+        <v>60.78</v>
       </c>
       <c r="I39" s="4">
-        <v>30.43</v>
+        <v>-2.22</v>
       </c>
       <c r="J39" s="4">
-        <v>-0.004777022686944814</v>
+        <v>0.027037108645637985</v>
       </c>
       <c r="K39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="4">
+        <v>24</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0.5569694782704349</v>
+      </c>
+      <c r="N39" s="4">
+        <v>51.375</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="P39" s="4">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-5.03</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.75</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6.938369781312127</v>
+      </c>
+      <c r="E40" s="1">
+        <v>-1.63</v>
+      </c>
+      <c r="F40" s="1">
+        <v>-0.060076700104974845</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1.06</v>
+      </c>
+      <c r="H40" s="1">
+        <v>65.41</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-19.94</v>
+      </c>
+      <c r="J40" s="1">
+        <v>-0.0023692515235434353</v>
+      </c>
+      <c r="K40" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L40" s="1">
+        <v>3</v>
+      </c>
+      <c r="M40" s="1">
+        <v>-0.05639722145466641</v>
+      </c>
+      <c r="N40" s="1">
+        <v>36.875</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P40" s="1">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3.61</v>
+      </c>
+      <c r="C41" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1.0858725761772854</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.0007778234141011253</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="H41" s="1">
+        <v>38.21</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-0.0006386141229999658</v>
+      </c>
+      <c r="K41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
         <v>28</v>
       </c>
-      <c r="M39" s="4">
-        <v>-0.07393971461665483</v>
-      </c>
-      <c r="N39" s="4">
-        <v>57.826086956521735</v>
-      </c>
-      <c r="O39" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P39" s="4">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4">
-        <v>11.94</v>
-      </c>
-      <c r="C40" s="4">
-        <v>95.65217391304348</v>
-      </c>
-      <c r="D40" s="4">
-        <v>0.9145728643216081</v>
-      </c>
-      <c r="E40" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F40" s="4">
-        <v>0.08153386460991555</v>
-      </c>
-      <c r="G40" s="4">
-        <v>1.71</v>
-      </c>
-      <c r="H40" s="4">
-        <v>68.02</v>
-      </c>
-      <c r="I40" s="4">
-        <v>16.38</v>
-      </c>
-      <c r="J40" s="4">
-        <v>0.008029978850508778</v>
-      </c>
-      <c r="K40" s="4" t="b">
+      <c r="M41" s="1">
+        <v>-0.03785670241413741</v>
+      </c>
+      <c r="N41" s="1">
+        <v>42.75</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P41" s="1">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4">
+        <v>-0.02</v>
+      </c>
+      <c r="C42" s="4">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1214</v>
+      </c>
+      <c r="E42" s="4">
+        <v>5.74</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.06294567604844832</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="H42" s="4">
+        <v>45.21</v>
+      </c>
+      <c r="I42" s="4">
+        <v>-16.43</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0.011841566107371212</v>
+      </c>
+      <c r="K42" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L40" s="4">
-        <v>19</v>
-      </c>
-      <c r="M40" s="4">
-        <v>0.09865430152319776</v>
-      </c>
-      <c r="N40" s="4">
-        <v>60.434782608695656</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="P40" s="4">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2">
-        <v>3.41</v>
-      </c>
-      <c r="C41" s="2">
-        <v>71.73913043478261</v>
-      </c>
-      <c r="D41" s="2">
-        <v>8.926686217008797</v>
-      </c>
-      <c r="E41" s="2">
-        <v>-1.19</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0.6135308078325732</v>
-      </c>
-      <c r="G41" s="2">
-        <v>2.08</v>
-      </c>
-      <c r="H41" s="2">
-        <v>61.03</v>
-      </c>
-      <c r="I41" s="2">
-        <v>63.89</v>
-      </c>
-      <c r="J41" s="2">
-        <v>0.046290880944706556</v>
-      </c>
-      <c r="K41" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="2">
-        <v>235</v>
-      </c>
-      <c r="M41" s="2">
-        <v>0.6395731625739038</v>
-      </c>
-      <c r="N41" s="2">
-        <v>71.08695652173913</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P41" s="2">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2">
-        <v>-0.38</v>
-      </c>
-      <c r="C42" s="2">
-        <v>34.78260869565217</v>
-      </c>
-      <c r="D42" s="2">
-        <v>322.6315789473684</v>
-      </c>
-      <c r="E42" s="2">
-        <v>3.31</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0.43376294328765586</v>
-      </c>
-      <c r="G42" s="2">
-        <v>3.48</v>
-      </c>
-      <c r="H42" s="2">
-        <v>73.97</v>
-      </c>
-      <c r="I42" s="2">
-        <v>117.52</v>
-      </c>
-      <c r="J42" s="2">
-        <v>0.0437033287774922</v>
-      </c>
-      <c r="K42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2">
-        <v>211</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0.49356390602700784</v>
-      </c>
-      <c r="N42" s="2">
-        <v>75.86956521739131</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P42" s="2">
-        <v>0.22</v>
+      <c r="L42" s="4">
+        <v>13</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0.08011657641655434</v>
+      </c>
+      <c r="N42" s="4">
+        <v>55.25</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="P42" s="4">
+        <v>-7.79</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3308,99 +3514,99 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>-0.32</v>
+        <v>1.02</v>
       </c>
       <c r="C43" s="1">
-        <v>36.95652173913043</v>
+        <v>37.5</v>
       </c>
       <c r="D43" s="1">
-        <v>228.28125</v>
+        <v>26.833333333333332</v>
       </c>
       <c r="E43" s="1">
-        <v>3.34</v>
+        <v>-1.14</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.2024231122362621</v>
+        <v>-0.24728372168166793</v>
       </c>
       <c r="G43" s="1">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="H43" s="1">
-        <v>44.47</v>
+        <v>34.69</v>
       </c>
       <c r="I43" s="1">
-        <v>-5.12</v>
+        <v>-25.64</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.012928889152724788</v>
+        <v>-0.002679959397422861</v>
       </c>
       <c r="K43" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="1">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.18602607406579463</v>
+        <v>-0.14732455168162217</v>
       </c>
       <c r="N43" s="1">
-        <v>44.565217391304344</v>
+        <v>44.75</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="P43" s="1">
-        <v>0.22</v>
+        <v>-14.38</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="3">
-        <v>-2.92</v>
-      </c>
-      <c r="C44" s="3">
-        <v>15.217391304347828</v>
-      </c>
-      <c r="D44" s="3">
-        <v>-23.77054794520548</v>
-      </c>
-      <c r="E44" s="3">
-        <v>16.88</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0.23124094783320537</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="H44" s="3">
-        <v>73.93</v>
-      </c>
-      <c r="I44" s="3">
-        <v>39.23</v>
-      </c>
-      <c r="J44" s="3">
-        <v>-0.007159582933150655</v>
-      </c>
-      <c r="K44" s="3" t="b">
+      <c r="B44" s="4">
+        <v>8.37</v>
+      </c>
+      <c r="C44" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0.835125448028674</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0.07936795076169952</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1.47</v>
+      </c>
+      <c r="H44" s="4">
+        <v>81.15</v>
+      </c>
+      <c r="I44" s="4">
+        <v>20.57</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0.028815159670616916</v>
+      </c>
+      <c r="K44" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="L44" s="3">
-        <v>82</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0.25414857468900554</v>
-      </c>
-      <c r="N44" s="3">
-        <v>28.913043478260867</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P44" s="3">
-        <v>-0.22</v>
+      <c r="L44" s="4">
+        <v>253</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0.1081905335224489</v>
+      </c>
+      <c r="N44" s="4">
+        <v>68.375</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P44" s="4">
+        <v>3.59</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3408,49 +3614,49 @@
         <v>44</v>
       </c>
       <c r="B45" s="4">
-        <v>4.88</v>
+        <v>-0.38</v>
       </c>
       <c r="C45" s="4">
-        <v>76.08695652173914</v>
+        <v>21.25</v>
       </c>
       <c r="D45" s="4">
-        <v>6.172131147540984</v>
+        <v>851.5</v>
       </c>
       <c r="E45" s="4">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="F45" s="4">
-        <v>0.09983578644763577</v>
+        <v>-0.0071507188784613596</v>
       </c>
       <c r="G45" s="4">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="H45" s="4">
-        <v>61.19</v>
+        <v>62.2</v>
       </c>
       <c r="I45" s="4">
-        <v>56.66</v>
+        <v>36.94</v>
       </c>
       <c r="J45" s="4">
-        <v>0.017431917254956325</v>
+        <v>0.0010386631373696439</v>
       </c>
       <c r="K45" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="4">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="M45" s="4">
-        <v>0.12009095124644853</v>
+        <v>0.02596458897431453</v>
       </c>
       <c r="N45" s="4">
-        <v>64.13043478260869</v>
+        <v>58.75</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="P45" s="4">
-        <v>0.22</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3458,49 +3664,49 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>-0.76</v>
+        <v>10.62</v>
       </c>
       <c r="C46" s="1">
-        <v>26.08695652173913</v>
+        <v>81.25</v>
       </c>
       <c r="D46" s="1">
-        <v>13.236842105263158</v>
+        <v>0.8549905838041432</v>
       </c>
       <c r="E46" s="1">
-        <v>7.72</v>
+        <v>-4.03</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.4293418207008787</v>
+        <v>-0.21640668943784197</v>
       </c>
       <c r="G46" s="1">
-        <v>2.61</v>
+        <v>1.49</v>
       </c>
       <c r="H46" s="1">
-        <v>55.73</v>
+        <v>30.83</v>
       </c>
       <c r="I46" s="1">
-        <v>-31.83</v>
+        <v>-15.8</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.020809676287581447</v>
+        <v>-0.020487821655474574</v>
       </c>
       <c r="K46" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L46" s="1">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.3905194215031542</v>
+        <v>-0.18635761379365645</v>
       </c>
       <c r="N46" s="1">
-        <v>31.30434782608696</v>
+        <v>40.25</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="P46" s="1">
-        <v>-0.43</v>
+        <v>-20.18</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3508,50 +3714,1694 @@
         <v>46</v>
       </c>
       <c r="B47" s="4">
-        <v>0.54</v>
+        <v>3.98</v>
       </c>
       <c r="C47" s="4">
-        <v>52.17391304347826</v>
+        <v>48.75</v>
       </c>
       <c r="D47" s="4">
-        <v>41.629629629629626</v>
+        <v>7.4874371859296485</v>
       </c>
       <c r="E47" s="4">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="F47" s="4">
-        <v>-0.07729216133870549</v>
+        <v>0.8265069097481523</v>
       </c>
       <c r="G47" s="4">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="H47" s="4">
-        <v>62.92</v>
+        <v>73.61</v>
       </c>
       <c r="I47" s="4">
-        <v>-4.06</v>
+        <v>83.86</v>
       </c>
       <c r="J47" s="4">
-        <v>-0.0012099495887365832</v>
+        <v>0.0337080873874883</v>
       </c>
       <c r="K47" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="4">
+        <v>289</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0.8939640183371402</v>
+      </c>
+      <c r="N47" s="4">
+        <v>69.875</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P47" s="4">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M47" s="4">
-        <v>-0.06692344602502753</v>
-      </c>
-      <c r="N47" s="4">
-        <v>57.17391304347826</v>
-      </c>
-      <c r="O47" s="4" t="s">
+      <c r="B48" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="C48" s="2">
+        <v>26.25</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1695.5000000000002</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.6929630608869305</v>
+      </c>
+      <c r="G48" s="2">
+        <v>3.81</v>
+      </c>
+      <c r="H48" s="2">
+        <v>72.58</v>
+      </c>
+      <c r="I48" s="2">
+        <v>141.2</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0.07665810200054786</v>
+      </c>
+      <c r="K48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2">
+        <v>228</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.8652853110097087</v>
+      </c>
+      <c r="N48" s="2">
+        <v>75</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P48" s="2">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>-0.13</v>
+      </c>
+      <c r="C49" s="1">
+        <v>25</v>
+      </c>
+      <c r="D49" s="1">
+        <v>560.4615384615385</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2.94</v>
+      </c>
+      <c r="F49" s="1">
+        <v>-0.40098393303826685</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H49" s="1">
+        <v>29.84</v>
+      </c>
+      <c r="I49" s="1">
+        <v>-24.84</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-0.018499486824224972</v>
+      </c>
+      <c r="K49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>12</v>
+      </c>
+      <c r="M49" s="1">
+        <v>-0.3672553787437729</v>
+      </c>
+      <c r="N49" s="1">
+        <v>38</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P49" s="1">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>-2.92</v>
+      </c>
+      <c r="C50" s="1">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1">
+        <v>-8.5</v>
+      </c>
+      <c r="E50" s="1">
+        <v>15.86</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0.05631395510647852</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2.42</v>
+      </c>
+      <c r="H50" s="1">
+        <v>70.19</v>
+      </c>
+      <c r="I50" s="1">
+        <v>55.91</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.04373138826321657</v>
+      </c>
+      <c r="K50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>92</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0.14339494983044476</v>
+      </c>
+      <c r="N50" s="1">
+        <v>39.625</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="P50" s="1">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="C51" s="4">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="D51" s="4">
+        <v>6.496226415094339</v>
+      </c>
+      <c r="E51" s="4">
+        <v>-0.19</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0.29360524694191664</v>
+      </c>
+      <c r="G51" s="4">
+        <v>1.83</v>
+      </c>
+      <c r="H51" s="4">
+        <v>69.93</v>
+      </c>
+      <c r="I51" s="4">
+        <v>68</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0.01160803399657271</v>
+      </c>
+      <c r="K51" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4">
+        <v>274</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0.3445047016045166</v>
+      </c>
+      <c r="N51" s="4">
+        <v>66.125</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P51" s="4">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>-0.71</v>
+      </c>
+      <c r="C52" s="1">
+        <v>18.75</v>
+      </c>
+      <c r="D52" s="1">
+        <v>12.042253521126762</v>
+      </c>
+      <c r="E52" s="1">
+        <v>6.95</v>
+      </c>
+      <c r="F52" s="1">
+        <v>-0.232571819467489</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2.58</v>
+      </c>
+      <c r="H52" s="1">
+        <v>66.33</v>
+      </c>
+      <c r="I52" s="1">
+        <v>-22.47</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.0054829565044803045</v>
+      </c>
+      <c r="K52" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>44</v>
+      </c>
+      <c r="M52" s="1">
+        <v>-0.1356788816760336</v>
+      </c>
+      <c r="N52" s="1">
+        <v>48.375</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P52" s="1">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="C53" s="4">
+        <v>32.5</v>
+      </c>
+      <c r="D53" s="4">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E53" s="4">
+        <v>-0.49</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0.007992566020441391</v>
+      </c>
+      <c r="G53" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H53" s="4">
+        <v>66.83</v>
+      </c>
+      <c r="I53" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0.002646039390808575</v>
+      </c>
+      <c r="K53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4">
+        <v>30</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0.03436216301431849</v>
+      </c>
+      <c r="N53" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="P53" s="4">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4">
+        <v>4.03</v>
+      </c>
+      <c r="C54" s="4">
+        <v>51.24999999999999</v>
+      </c>
+      <c r="D54" s="4">
+        <v>2.2655086848635233</v>
+      </c>
+      <c r="E54" s="4">
+        <v>-0.56</v>
+      </c>
+      <c r="F54" s="4">
+        <v>-0.11770767946243242</v>
+      </c>
+      <c r="G54" s="4">
+        <v>1.22</v>
+      </c>
+      <c r="H54" s="4">
+        <v>59.68</v>
+      </c>
+      <c r="I54" s="4">
+        <v>4.04</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0.0019598565372724946</v>
+      </c>
+      <c r="K54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4">
+        <v>82</v>
+      </c>
+      <c r="M54" s="4">
+        <v>-0.10421625774463483</v>
+      </c>
+      <c r="N54" s="4">
+        <v>51.5</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>8.65</v>
+      </c>
+      <c r="C55" s="1">
+        <v>73.75</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0.17803468208092474</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="F55" s="1">
+        <v>-0.06870407205682959</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="H55" s="1">
+        <v>37.03</v>
+      </c>
+      <c r="I55" s="1">
+        <v>8.41</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-0.007951173110002985</v>
+      </c>
+      <c r="K55" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>206</v>
+      </c>
+      <c r="M55" s="1">
+        <v>-0.11408430874396691</v>
+      </c>
+      <c r="N55" s="1">
+        <v>41.75</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>21.18</v>
+      </c>
+      <c r="C56" s="2">
+        <v>96.25</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2.2030217186024554</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.6272386446532731</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1.94</v>
+      </c>
+      <c r="H56" s="2">
+        <v>83.47</v>
+      </c>
+      <c r="I56" s="2">
+        <v>134.11</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.0397470916198297</v>
+      </c>
+      <c r="K56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2">
+        <v>482</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.6848838101747718</v>
+      </c>
+      <c r="N56" s="2">
+        <v>81.5</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4">
+        <v>20.1</v>
+      </c>
+      <c r="C57" s="4">
+        <v>93.75</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.02786069651741287</v>
+      </c>
+      <c r="E57" s="4">
+        <v>-1.94</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0.22913353888735302</v>
+      </c>
+      <c r="G57" s="4">
+        <v>1.63</v>
+      </c>
+      <c r="H57" s="4">
+        <v>76.2</v>
+      </c>
+      <c r="I57" s="4">
+        <v>54.91</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0.018500523939808115</v>
+      </c>
+      <c r="K57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" s="4">
+        <v>346</v>
+      </c>
+      <c r="M57" s="4">
+        <v>0.26776806471559156</v>
+      </c>
+      <c r="N57" s="4">
+        <v>67.75</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="P57" s="4"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4">
+        <v>34.32</v>
+      </c>
+      <c r="C58" s="4">
+        <v>100</v>
+      </c>
+      <c r="D58" s="4">
+        <v>-1.391025641025641</v>
+      </c>
+      <c r="E58" s="4">
+        <v>-1.33</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0.4090321367723118</v>
+      </c>
+      <c r="G58" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="H58" s="4">
+        <v>66.48</v>
+      </c>
+      <c r="I58" s="4">
+        <v>56.15</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0.027172825238733007</v>
+      </c>
+      <c r="K58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="4">
+        <v>349</v>
+      </c>
+      <c r="M58" s="4">
+        <v>0.427429530023854</v>
+      </c>
+      <c r="N58" s="4">
+        <v>64.625</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P58" s="4"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>6.37</v>
+      </c>
+      <c r="C59" s="1">
+        <v>65</v>
+      </c>
+      <c r="D59" s="1">
+        <v>-0.1240188383045526</v>
+      </c>
+      <c r="E59" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="F59" s="1">
+        <v>-0.09616610823235944</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="H59" s="1">
+        <v>49.87</v>
+      </c>
+      <c r="I59" s="1">
+        <v>3.88</v>
+      </c>
+      <c r="J59" s="1">
+        <v>-0.006356649066148242</v>
+      </c>
+      <c r="K59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>157</v>
+      </c>
+      <c r="M59" s="1">
+        <v>-0.13357414117716182</v>
+      </c>
+      <c r="N59" s="1">
+        <v>38.5</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P59" s="1"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4">
+        <v>17.74</v>
+      </c>
+      <c r="C60" s="4">
+        <v>91.25</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0.624577226606539</v>
+      </c>
+      <c r="E60" s="4">
+        <v>-0.29</v>
+      </c>
+      <c r="F60" s="4">
+        <v>-0.0272563686144133</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="H60" s="4">
+        <v>54.04</v>
+      </c>
+      <c r="I60" s="4">
+        <v>14.35</v>
+      </c>
+      <c r="J60" s="4">
+        <v>-0.010004394425515348</v>
+      </c>
+      <c r="K60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" s="4">
+        <v>140</v>
+      </c>
+      <c r="M60" s="4">
+        <v>-0.029096107939567517</v>
+      </c>
+      <c r="N60" s="4">
+        <v>52.125</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="P60" s="4"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>28.77</v>
+      </c>
+      <c r="C61" s="2">
+        <v>98.75</v>
+      </c>
+      <c r="D61" s="2">
+        <v>4.886687521724018</v>
+      </c>
+      <c r="E61" s="2">
+        <v>-8.91</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1.1069693915148988</v>
+      </c>
+      <c r="G61" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H61" s="2">
+        <v>81.22</v>
+      </c>
+      <c r="I61" s="2">
+        <v>278.28</v>
+      </c>
+      <c r="J61" s="2">
+        <v>0.08573239660165008</v>
+      </c>
+      <c r="K61" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2">
+        <v>352</v>
+      </c>
+      <c r="M61" s="2">
+        <v>1.3400030393677662</v>
+      </c>
+      <c r="N61" s="2">
+        <v>86</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>10.54</v>
+      </c>
+      <c r="C62" s="2">
+        <v>80</v>
+      </c>
+      <c r="D62" s="2">
+        <v>6.303605313092979</v>
+      </c>
+      <c r="E62" s="2">
+        <v>-4.18</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0.7439303990216621</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2.02</v>
+      </c>
+      <c r="H62" s="2">
+        <v>87.03</v>
+      </c>
+      <c r="I62" s="2">
+        <v>149.52</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0.07347561151398473</v>
+      </c>
+      <c r="K62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2">
+        <v>176</v>
+      </c>
+      <c r="M62" s="2">
+        <v>0.8064815360769055</v>
+      </c>
+      <c r="N62" s="2">
+        <v>81</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <v>16.87</v>
+      </c>
+      <c r="C63" s="1">
+        <v>90</v>
+      </c>
+      <c r="D63" s="1">
+        <v>-0.26615293420272673</v>
+      </c>
+      <c r="E63" s="1">
+        <v>-0.51</v>
+      </c>
+      <c r="F63" s="1">
+        <v>-0.12025934623584313</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H63" s="1">
+        <v>43.24</v>
+      </c>
+      <c r="I63" s="1">
+        <v>-1.85</v>
+      </c>
+      <c r="J63" s="1">
+        <v>-0.011059425947000838</v>
+      </c>
+      <c r="K63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1">
+        <v>102</v>
+      </c>
+      <c r="M63" s="1">
+        <v>-0.16318659715610817</v>
+      </c>
+      <c r="N63" s="1">
+        <v>41.25</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P63" s="1"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>15.41</v>
+      </c>
+      <c r="C64" s="1">
+        <v>86.25</v>
+      </c>
+      <c r="D64" s="1">
+        <v>-0.10837118754055808</v>
+      </c>
+      <c r="E64" s="1">
+        <v>-0.54</v>
+      </c>
+      <c r="F64" s="1">
+        <v>-0.20263557576689845</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="H64" s="1">
+        <v>44.84</v>
+      </c>
+      <c r="I64" s="1">
+        <v>-33.4</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0.005385096736302075</v>
+      </c>
+      <c r="K64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>-108</v>
+      </c>
+      <c r="M64" s="1">
+        <v>-0.20018259000002614</v>
+      </c>
+      <c r="N64" s="1">
+        <v>45.875</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P64" s="1"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P47" s="4">
+      <c r="B65" s="4">
+        <v>4.01</v>
+      </c>
+      <c r="C65" s="4">
+        <v>50</v>
+      </c>
+      <c r="D65" s="4">
+        <v>7.408977556109726</v>
+      </c>
+      <c r="E65" s="4">
+        <v>-1.22</v>
+      </c>
+      <c r="F65" s="4">
+        <v>-0.01086385820728189</v>
+      </c>
+      <c r="G65" s="4">
+        <v>1.16</v>
+      </c>
+      <c r="H65" s="4">
+        <v>62.31</v>
+      </c>
+      <c r="I65" s="4">
+        <v>-6.82</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0.0038187360476474243</v>
+      </c>
+      <c r="K65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4">
+        <v>-10</v>
+      </c>
+      <c r="M65" s="4">
+        <v>-0.0010519151397927473</v>
+      </c>
+      <c r="N65" s="4">
+        <v>54.625</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P65" s="4"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="C66" s="1">
+        <v>66.25</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0.9336283185840707</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="F66" s="1">
+        <v>-0.09950705320230185</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="H66" s="1">
+        <v>52.59</v>
+      </c>
+      <c r="I66" s="1">
+        <v>7.17</v>
+      </c>
+      <c r="J66" s="1">
+        <v>-0.012435834332819305</v>
+      </c>
+      <c r="K66" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L66" s="1">
+        <v>134</v>
+      </c>
+      <c r="M66" s="1">
+        <v>-0.1399813183556946</v>
+      </c>
+      <c r="N66" s="1">
+        <v>45.125</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="P66" s="1"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>8.24</v>
+      </c>
+      <c r="C67" s="1">
+        <v>70</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0.6286407766990291</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F67" s="1">
+        <v>-0.15866285769577249</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H67" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I67" s="1">
+        <v>-9.51</v>
+      </c>
+      <c r="J67" s="1">
+        <v>-0.009214174294287896</v>
+      </c>
+      <c r="K67" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>84</v>
+      </c>
+      <c r="M67" s="1">
+        <v>-0.1280005356098689</v>
+      </c>
+      <c r="N67" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P67" s="1"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>18.19</v>
+      </c>
+      <c r="C68" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="D68" s="1">
+        <v>-0.47278724573941733</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-0.22796179153608975</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="H68" s="1">
+        <v>43.08</v>
+      </c>
+      <c r="I68" s="1">
+        <v>-10.35</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.008899239591692868</v>
+      </c>
+      <c r="K68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>36</v>
+      </c>
+      <c r="M68" s="1">
+        <v>-0.23532074883670662</v>
+      </c>
+      <c r="N68" s="1">
+        <v>40.75</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P68" s="1"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="C69" s="1">
+        <v>41.25</v>
+      </c>
+      <c r="D69" s="1">
+        <v>13.717105263157896</v>
+      </c>
+      <c r="E69" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="F69" s="1">
+        <v>-0.39615735989600254</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1.12</v>
+      </c>
+      <c r="H69" s="1">
+        <v>36.52</v>
+      </c>
+      <c r="I69" s="1">
+        <v>-30.99</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-0.04018332221851326</v>
+      </c>
+      <c r="K69" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>-71</v>
+      </c>
+      <c r="M69" s="1">
+        <v>-0.3887984025953857</v>
+      </c>
+      <c r="N69" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P69" s="1"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <v>5.18</v>
+      </c>
+      <c r="C70" s="1">
+        <v>56.25</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0.7837837837837839</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-0.1780056798991328</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="H70" s="1">
+        <v>48.8</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-7.13</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.01438869771358164</v>
+      </c>
+      <c r="K70" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>27</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.17739243345741473</v>
+      </c>
+      <c r="N70" s="1">
+        <v>36.75</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P70" s="1"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <v>16.03</v>
+      </c>
+      <c r="C71" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="D71" s="1">
+        <v>-0.1041796631316283</v>
+      </c>
+      <c r="E71" s="1">
+        <v>-0.84</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-0.16681016959771852</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="H71" s="1">
+        <v>53.4</v>
+      </c>
+      <c r="I71" s="1">
+        <v>-4.25</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-0.004919159703157198</v>
+      </c>
+      <c r="K71" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>65</v>
+      </c>
+      <c r="M71" s="1">
+        <v>-0.16190419806397394</v>
+      </c>
+      <c r="N71" s="1">
+        <v>45.125</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P71" s="1"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>10.42</v>
+      </c>
+      <c r="C72" s="1">
+        <v>78.75</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.2168905950095969</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-1.33</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.20462654638870872</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.16</v>
+      </c>
+      <c r="H72" s="1">
+        <v>47.64</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-5.28</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.013622084813143599</v>
+      </c>
+      <c r="K72" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>90</v>
+      </c>
+      <c r="M72" s="1">
+        <v>-0.19481460332121958</v>
+      </c>
+      <c r="N72" s="1">
+        <v>41</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P72" s="1"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="C73" s="4">
+        <v>35</v>
+      </c>
+      <c r="D73" s="4">
+        <v>14.410526315789475</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0.22991924598990235</v>
+      </c>
+      <c r="G73" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="H73" s="4">
+        <v>82.09</v>
+      </c>
+      <c r="I73" s="4">
+        <v>33.69</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0.023133281810783026</v>
+      </c>
+      <c r="K73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4">
+        <v>10</v>
+      </c>
+      <c r="M73" s="4">
+        <v>0.21704107071382284</v>
+      </c>
+      <c r="N73" s="4">
+        <v>67.25</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="P73" s="4"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" s="4">
+        <v>6.21</v>
+      </c>
+      <c r="C74" s="4">
+        <v>62.5</v>
+      </c>
+      <c r="D74" s="4">
+        <v>0.5861513687600644</v>
+      </c>
+      <c r="E74" s="4">
+        <v>-2.11</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0.05194794945076753</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0.81</v>
+      </c>
+      <c r="H74" s="4">
+        <v>56.41</v>
+      </c>
+      <c r="I74" s="4">
+        <v>16.87</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0.00840303528987608</v>
+      </c>
+      <c r="K74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" s="4">
+        <v>0</v>
+      </c>
+      <c r="M74" s="4">
+        <v>0.04029626705812417</v>
+      </c>
+      <c r="N74" s="4">
+        <v>52.75</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="P74" s="4"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4.84</v>
+      </c>
+      <c r="C75" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="D75" s="1">
+        <v>-1.0661157024793388</v>
+      </c>
+      <c r="E75" s="1">
+        <v>-0.6</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0.06545859718074318</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H75" s="1">
+        <v>64.81</v>
+      </c>
+      <c r="I75" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0.009045496647137405</v>
+      </c>
+      <c r="K75" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>2</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0.048900943254355234</v>
+      </c>
+      <c r="N75" s="1">
+        <v>44.375</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P75" s="1"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="4">
+        <v>2.84</v>
+      </c>
+      <c r="C76" s="4">
+        <v>43.75</v>
+      </c>
+      <c r="D76" s="4">
+        <v>2.084507042253521</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0.06257216442292227</v>
+      </c>
+      <c r="G76" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="H76" s="4">
+        <v>63.92</v>
+      </c>
+      <c r="I76" s="4">
+        <v>21.49</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0.017268733582750783</v>
+      </c>
+      <c r="K76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="4">
+        <v>167</v>
+      </c>
+      <c r="M76" s="4">
+        <v>0.05705294644745962</v>
+      </c>
+      <c r="N76" s="4">
+        <v>57.625</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P76" s="4"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77" s="4">
+        <v>20.88</v>
+      </c>
+      <c r="C77" s="4">
+        <v>95</v>
+      </c>
+      <c r="D77" s="4">
+        <v>-0.7169540229885057</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="F77" s="4">
+        <v>-0.08077110017578727</v>
+      </c>
+      <c r="G77" s="4">
+        <v>1.02</v>
+      </c>
+      <c r="H77" s="4">
+        <v>59.36</v>
+      </c>
+      <c r="I77" s="4">
+        <v>3.19</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0.002342358304012036</v>
+      </c>
+      <c r="K77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" s="4">
+        <v>145</v>
+      </c>
+      <c r="M77" s="4">
+        <v>-0.07954460729235113</v>
+      </c>
+      <c r="N77" s="4">
+        <v>51.875</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="P77" s="4"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B78" s="4">
+        <v>8.27</v>
+      </c>
+      <c r="C78" s="4">
+        <v>71.25</v>
+      </c>
+      <c r="D78" s="4">
+        <v>0.19830713422007262</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="F78" s="4">
+        <v>-0.03651052120250399</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1.07</v>
+      </c>
+      <c r="H78" s="4">
+        <v>69.41</v>
+      </c>
+      <c r="I78" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0.0055376687472732155</v>
+      </c>
+      <c r="K78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" s="4">
+        <v>236</v>
+      </c>
+      <c r="M78" s="4">
+        <v>-0.03221779611047748</v>
+      </c>
+      <c r="N78" s="4">
+        <v>56.5</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="P78" s="4"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="2">
+        <v>8.72</v>
+      </c>
+      <c r="C79" s="2">
+        <v>75</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0.8061926605504586</v>
+      </c>
+      <c r="E79" s="2">
+        <v>6.04</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0.8852741091554643</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="H79" s="2">
+        <v>77.19</v>
+      </c>
+      <c r="I79" s="2">
+        <v>66.76</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.058820983234075884</v>
+      </c>
+      <c r="K79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2">
+        <v>144</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0.8846608627137462</v>
+      </c>
+      <c r="N79" s="2">
+        <v>71.25</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P79" s="2"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80" s="4">
+        <v>10.23</v>
+      </c>
+      <c r="C80" s="4">
+        <v>77.5</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0.5835777126099705</v>
+      </c>
+      <c r="E80" s="4">
+        <v>-0.63</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0.06831387848631416</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1.23</v>
+      </c>
+      <c r="H80" s="4">
+        <v>59.82</v>
+      </c>
+      <c r="I80" s="4">
+        <v>15.99</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0.01302611572609901</v>
+      </c>
+      <c r="K80" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" s="4">
+        <v>148</v>
+      </c>
+      <c r="M80" s="4">
+        <v>0.08241854664582982</v>
+      </c>
+      <c r="N80" s="4">
+        <v>59.125</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P80" s="4"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81" s="4">
+        <v>12.15</v>
+      </c>
+      <c r="C81" s="4">
+        <v>82.5</v>
+      </c>
+      <c r="D81" s="4">
+        <v>-0.2559670781893005</v>
+      </c>
+      <c r="E81" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0.0024896628309193924</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="H81" s="4">
+        <v>63.6</v>
+      </c>
+      <c r="I81" s="4">
+        <v>13.86</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0.0005514220814281436</v>
+      </c>
+      <c r="K81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4">
+        <v>95</v>
+      </c>
+      <c r="M81" s="4">
+        <v>0.0018764163892013297</v>
+      </c>
+      <c r="N81" s="4">
+        <v>52</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="P81" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3561,15 +5411,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3577,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>45.652173913043484</v>
+        <v>38.875</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3585,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>77.3913043478261</v>
+        <v>75.125</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3593,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25.217391304347828</v>
+        <v>27.125</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3601,7 +5451,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51.73913043478261</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3609,7 +5459,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>46.95652173913043</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3617,7 +5467,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>61.95652173913042</v>
+        <v>58.125</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3625,7 +5475,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>65.8695652173913</v>
+        <v>65.625</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3633,7 +5483,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>55.65217391304348</v>
+        <v>50.875</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3641,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.47826086956522</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3649,7 +5499,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>25.434782608695652</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3657,7 +5507,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>41.52173913043479</v>
+        <v>41.875</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3665,7 +5515,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>76.73913043478261</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3673,7 +5523,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>51.95652173913044</v>
+        <v>47.625</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3681,7 +5531,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>33.69565217391305</v>
+        <v>72.375</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3689,7 +5539,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>62.82608695652174</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3697,7 +5547,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>51.08695652173914</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3705,7 +5555,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>54.34782608695652</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3713,7 +5563,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>44.1304347826087</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3721,7 +5571,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>30</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3729,7 +5579,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>26.739130434782606</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3737,7 +5587,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>45.869565217391305</v>
+        <v>43.125</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3745,7 +5595,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>22.391304347826086</v>
+        <v>42.375</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3753,7 +5603,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22.60869565217391</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3761,7 +5611,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>51.52173913043478</v>
+        <v>31.124999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3769,7 +5619,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>66.73913043478261</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3777,7 +5627,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>76.08695652173913</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3785,7 +5635,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>46.95652173913044</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3793,7 +5643,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49.99999999999999</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3801,7 +5651,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>56.08695652173913</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -3809,7 +5659,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>53.26086956521739</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3817,7 +5667,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>68.47826086956522</v>
+        <v>35.875</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3825,7 +5675,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>49.130434782608695</v>
+        <v>50.375</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3833,7 +5683,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40.65217391304348</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3841,7 +5691,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>45.21739130434782</v>
+        <v>56.875</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -3849,7 +5699,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>63.04347826086957</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3857,7 +5707,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>59.1304347826087</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -3865,7 +5715,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>64.78260869565219</v>
+        <v>61.625</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -3873,7 +5723,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>57.826086956521735</v>
+        <v>51.375</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3881,7 +5731,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>60.434782608695656</v>
+        <v>36.875</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -3889,7 +5739,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>71.08695652173913</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -3897,7 +5747,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>75.86956521739131</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -3905,7 +5755,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>44.565217391304344</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3913,7 +5763,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>28.913043478260867</v>
+        <v>68.375</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -3921,7 +5771,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>64.13043478260869</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -3929,7 +5779,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>31.30434782608696</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -3937,7 +5787,279 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>57.17391304347826</v>
+        <v>69.875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>39.625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>66.125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>48.375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>64.625</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>52.125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>45.875</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>54.625</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>45.125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>45.125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73">
+        <v>67.25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74">
+        <v>52.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75">
+        <v>44.375</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76">
+        <v>57.625</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77">
+        <v>51.875</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>123</v>
+      </c>
+      <c r="B78">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79">
+        <v>71.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80">
+        <v>59.125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3956,131 +6078,131 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" t="s">
         <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4099,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4110,109 +6232,109 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4231,10 +6353,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4242,109 +6364,109 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4363,131 +6485,131 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4503,226 +6625,226 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C1" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
   <si>
     <t>Ticker</t>
   </si>
@@ -282,6 +282,96 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Last Run</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>Price min</t>
+  </si>
+  <si>
+    <t>&gt; $10</t>
+  </si>
+  <si>
+    <t>YTD perf min</t>
+  </si>
+  <si>
+    <t>&gt; +10%</t>
+  </si>
+  <si>
+    <t>P/E max</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>EPS Q/Q</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Sectors</t>
+  </si>
+  <si>
+    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Beta range</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>RSI min</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>&gt; 0</t>
+  </si>
+  <si>
+    <t>Ranked by</t>
+  </si>
+  <si>
+    <t>Alpha (highest first)</t>
+  </si>
+  <si>
+    <t>Top N</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>3 of 3 qualified</t>
   </si>
 </sst>
 </file>
@@ -898,7 +988,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1039,7 +1129,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1097,7 +1187,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1116,7 +1206,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1132,7 +1222,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1148,23 +1238,142 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1180,6 +1389,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="6" name="Dow_Jones" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="202">
   <si>
     <t>Ticker</t>
   </si>
@@ -275,103 +276,355 @@
     <t>Composite_Score</t>
   </si>
   <si>
+    <t>Earnings_Date</t>
+  </si>
+  <si>
     <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2027-04-14</t>
+  </si>
+  <si>
+    <t>2027-03-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>ATEN</t>
+  </si>
+  <si>
+    <t>Last Run</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Russell 2000</t>
+  </si>
+  <si>
+    <t>OMCL</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Small ($300M–$2B)</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Price min</t>
+  </si>
+  <si>
+    <t>&gt; $7</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
+    <t>YTD perf min</t>
+  </si>
+  <si>
+    <t>&gt; +10%</t>
+  </si>
+  <si>
+    <t>P/E max</t>
+  </si>
+  <si>
+    <t>&lt; 28</t>
+  </si>
+  <si>
+    <t>EPS Q/Q</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Sectors</t>
+  </si>
+  <si>
+    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Beta range</t>
+  </si>
+  <si>
+    <t>0.7 – 1.2</t>
+  </si>
+  <si>
+    <t>RSI min</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>&gt; 0</t>
+  </si>
+  <si>
+    <t>Ranked by</t>
+  </si>
+  <si>
+    <t>Alpha (highest first)</t>
+  </si>
+  <si>
+    <t>Top N</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>5 of 5 qualified</t>
+  </si>
+  <si>
+    <t>Dow Jones 30</t>
+  </si>
+  <si>
+    <t>&gt; $10</t>
+  </si>
+  <si>
+    <t>&gt; +5%</t>
+  </si>
+  <si>
+    <t>&lt; 35</t>
+  </si>
+  <si>
+    <t>All sectors</t>
+  </si>
+  <si>
+    <t>0 of 0 qualified</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>3 of 3 qualified</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 (large-cap subset)</t>
+  </si>
+  <si>
+    <t>Large (approx. S&amp;P 100)</t>
+  </si>
+  <si>
+    <t>&gt; +8%</t>
+  </si>
+  <si>
+    <t>&lt; 40</t>
+  </si>
+  <si>
+    <t>1 of 1 qualified</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Signal Type</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Earnings quality vs peers</t>
+  </si>
+  <si>
+    <t>Finviz</t>
+  </si>
+  <si>
+    <t>P(EPS_Fwd_Growth)</t>
+  </si>
+  <si>
+    <t>Earnings acceleration</t>
+  </si>
+  <si>
+    <t>P(MA_Slope_50)</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Medium-term price trend</t>
+  </si>
+  <si>
+    <t>Yahoo Finance prices</t>
+  </si>
+  <si>
+    <t>P(RSI_14)</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Short-term momentum strength</t>
+  </si>
+  <si>
+    <t>P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Long-term trend confirmation</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Criteria</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Last Run</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>Price min</t>
-  </si>
-  <si>
-    <t>&gt; $10</t>
-  </si>
-  <si>
-    <t>YTD perf min</t>
-  </si>
-  <si>
-    <t>&gt; +10%</t>
-  </si>
-  <si>
-    <t>P/E max</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>EPS Q/Q</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>Sectors</t>
-  </si>
-  <si>
-    <t>Technology, Consumer Staples, Materials, Real Estate, Financials, Industrials, Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>Beta range</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
-  </si>
-  <si>
-    <t>RSI min</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Alpha</t>
-  </si>
-  <si>
-    <t>&gt; 0</t>
-  </si>
-  <si>
-    <t>Ranked by</t>
-  </si>
-  <si>
-    <t>Alpha (highest first)</t>
-  </si>
-  <si>
-    <t>Top N</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Results</t>
-  </si>
-  <si>
-    <t>3 of 3 qualified</t>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+  </si>
+  <si>
+    <t>Score Range</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>≥ 70</t>
+  </si>
+  <si>
+    <t>Strong Buy candidate</t>
+  </si>
+  <si>
+    <t>50 – 70</t>
+  </si>
+  <si>
+    <t>Hold / Monitor</t>
+  </si>
+  <si>
+    <t>30 – 50</t>
+  </si>
+  <si>
+    <t>Weak / Neutral</t>
+  </si>
+  <si>
+    <t>&lt; 30</t>
+  </si>
+  <si>
+    <t>Consider reducing position</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
   </si>
 </sst>
 </file>
@@ -387,12 +640,32 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -407,8 +680,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1135,10 +1412,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1183,6 +1460,3659 @@
       </c>
       <c r="O1" t="s">
         <v>85</v>
+      </c>
+      <c r="P1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5.93</v>
+      </c>
+      <c r="C2" s="1">
+        <v>63.013698630136986</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-1.5446880269814502</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="F2" s="1">
+        <v>-0.050408902280218</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="H2" s="1">
+        <v>49.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>17.1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>-0.0016926625628907066</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>325</v>
+      </c>
+      <c r="M2" s="1">
+        <v>-0.11423085751745321</v>
+      </c>
+      <c r="N2" s="1">
+        <v>41.36986301369862</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.05</v>
+      </c>
+      <c r="C3" s="2">
+        <v>47.94520547945205</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.98032786885246</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.8859885294205656</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.43</v>
+      </c>
+      <c r="H3" s="2">
+        <v>76.2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>101.03</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.09871835961238663</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>171</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.9972877928220856</v>
+      </c>
+      <c r="N3" s="2">
+        <v>75.75342465753425</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-3.95</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6.8493150684931505</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9.977215189873418</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.62</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-0.24432660541346612</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>53.78</v>
+      </c>
+      <c r="I4" s="1">
+        <v>-25.47</v>
+      </c>
+      <c r="J4" s="1">
+        <v>-0.010825776730706725</v>
+      </c>
+      <c r="K4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>-64</v>
+      </c>
+      <c r="M4" s="1">
+        <v>-0.23654344014063255</v>
+      </c>
+      <c r="N4" s="1">
+        <v>32.87671232876712</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="C5" s="3">
+        <v>41.0958904109589</v>
+      </c>
+      <c r="D5" s="3">
+        <v>23.917431192660548</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-0.11193070522842519</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.81</v>
+      </c>
+      <c r="H5" s="3">
+        <v>70.19</v>
+      </c>
+      <c r="I5" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.007292648979306909</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>28</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-0.0488870665184733</v>
+      </c>
+      <c r="N5" s="3">
+        <v>62.1917808219178</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.09</v>
+      </c>
+      <c r="C6" s="1">
+        <v>49.31506849315068</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.4271844660194175</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>-0.03010880975809349</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H6" s="1">
+        <v>37.71</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-14.88</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-0.004594839874945752</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>160</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.011141966187924401</v>
+      </c>
+      <c r="N6" s="1">
+        <v>41.09589041095891</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>4.9</v>
+      </c>
+      <c r="C7" s="3">
+        <v>56.16438356164384</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.214285714285714</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.14</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.002395017639876429</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="H7" s="3">
+        <v>72.13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>21.78</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.018386371875611464</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.09968458355029597</v>
+      </c>
+      <c r="N7" s="3">
+        <v>63.01369863013699</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>13.24</v>
+      </c>
+      <c r="C8" s="3">
+        <v>84.93150684931507</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-0.012084592145015116</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.37619453788542767</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="H8" s="3">
+        <v>85.55</v>
+      </c>
+      <c r="I8" s="3">
+        <v>25.69</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.03155966068115684</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>-140</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.3497317759577936</v>
+      </c>
+      <c r="N8" s="3">
+        <v>67.12328767123287</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="C9" s="1">
+        <v>36.986301369863014</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46.10112359550562</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.14</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-0.16821378172750712</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H9" s="1">
+        <v>38.39</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-20.5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-0.003010889503415941</v>
+      </c>
+      <c r="K9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>54</v>
+      </c>
+      <c r="M9" s="1">
+        <v>-0.13007627189062265</v>
+      </c>
+      <c r="N9" s="1">
+        <v>49.45205479452054</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="C10" s="1">
+        <v>65.75342465753424</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.5312</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-0.15027436489102597</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.41</v>
+      </c>
+      <c r="H10" s="1">
+        <v>53.61</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-3.77</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.0016240548226396764</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>-83</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.11836338727240836</v>
+      </c>
+      <c r="N10" s="1">
+        <v>49.58904109589041</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-1.36</v>
+      </c>
+      <c r="C11" s="3">
+        <v>13.698630136986301</v>
+      </c>
+      <c r="D11" s="3">
+        <v>31.911764705882348</v>
+      </c>
+      <c r="E11" s="3">
+        <v>8.3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.10682310569657667</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="H11" s="3">
+        <v>61.24</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.021283661493117726</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>15</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.0920350916781929</v>
+      </c>
+      <c r="N11" s="3">
+        <v>54.52054794520548</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-0.34</v>
+      </c>
+      <c r="C12" s="1">
+        <v>21.91780821917808</v>
+      </c>
+      <c r="D12" s="1">
+        <v>65.85294117647058</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-0.34006166540284416</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44.51</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-39.51</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-0.009139416668990319</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>-15</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.3540713628939446</v>
+      </c>
+      <c r="N12" s="1">
+        <v>42.1917808219178</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="4">
+        <v>31.506849315068493</v>
+      </c>
+      <c r="D13" s="4">
+        <v>-1653.5</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2.73</v>
+      </c>
+      <c r="F13" s="4">
+        <v>-0.1884108124741753</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="H13" s="4">
+        <v>56.28</v>
+      </c>
+      <c r="I13" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="J13" s="4">
+        <v>-0.004604348070180763</v>
+      </c>
+      <c r="K13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4">
+        <v>21</v>
+      </c>
+      <c r="M13" s="4">
+        <v>-0.15494320180099097</v>
+      </c>
+      <c r="N13" s="4">
+        <v>29.58904109589041</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="C14" s="3">
+        <v>42.465753424657535</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7.580152671755725</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-0.17062662060495917</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="H14" s="3">
+        <v>52.04</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-8.36</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.009613205960270458</v>
+      </c>
+      <c r="K14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>14</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-0.20175928169629342</v>
+      </c>
+      <c r="N14" s="3">
+        <v>53.28767123287671</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>-0.63</v>
+      </c>
+      <c r="C15" s="2">
+        <v>20.54794520547945</v>
+      </c>
+      <c r="D15" s="2">
+        <v>62.85714285714286</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5.78</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.307455626469211</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2.22</v>
+      </c>
+      <c r="H15" s="2">
+        <v>74.77</v>
+      </c>
+      <c r="I15" s="2">
+        <v>174.21</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.1276636686580595</v>
+      </c>
+      <c r="K15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>206</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1.4024102427977805</v>
+      </c>
+      <c r="N15" s="2">
+        <v>70.68493150684931</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-3.53</v>
+      </c>
+      <c r="C16" s="1">
+        <v>8.21917808219178</v>
+      </c>
+      <c r="D16" s="1">
+        <v>12.218130311614733</v>
+      </c>
+      <c r="E16" s="1">
+        <v>4.52</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.028256571454628232</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.94</v>
+      </c>
+      <c r="H16" s="1">
+        <v>52.95</v>
+      </c>
+      <c r="I16" s="1">
+        <v>8.2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-0.00005125714893301769</v>
+      </c>
+      <c r="K16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>20</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0.10141832501926373</v>
+      </c>
+      <c r="N16" s="1">
+        <v>44.794520547945204</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>-6.21</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2.73972602739726</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4.355877616747182</v>
+      </c>
+      <c r="E17" s="4">
+        <v>4.89</v>
+      </c>
+      <c r="F17" s="4">
+        <v>-0.05371828874910933</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1.73</v>
+      </c>
+      <c r="H17" s="4">
+        <v>49.65</v>
+      </c>
+      <c r="I17" s="4">
+        <v>-5.85</v>
+      </c>
+      <c r="J17" s="4">
+        <v>-0.011094214309485508</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>32</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0.003098817742575699</v>
+      </c>
+      <c r="N17" s="4">
+        <v>28.767123287671232</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="C18" s="3">
+        <v>32.87671232876712</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1446.3333333333333</v>
+      </c>
+      <c r="E18" s="3">
+        <v>9.43</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-0.2104554191405284</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="H18" s="3">
+        <v>41.95</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-0.74</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-0.008154478936063782</v>
+      </c>
+      <c r="K18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>45</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-0.19255413901301122</v>
+      </c>
+      <c r="N18" s="3">
+        <v>53.287671232876704</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9.32</v>
+      </c>
+      <c r="C19" s="3">
+        <v>75.34246575342466</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.16523605150214582</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-0.43</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.0426229368382203</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="H19" s="3">
+        <v>68.84</v>
+      </c>
+      <c r="I19" s="3">
+        <v>22.42</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.004775952470250111</v>
+      </c>
+      <c r="K19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>71</v>
+      </c>
+      <c r="M19" s="3">
+        <v>-0.018864068817164847</v>
+      </c>
+      <c r="N19" s="3">
+        <v>57.3972602739726</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.07</v>
+      </c>
+      <c r="C20" s="1">
+        <v>64.38356164383562</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.9456342668863262</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-2.3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>-0.26177705897343784</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.03</v>
+      </c>
+      <c r="H20" s="1">
+        <v>30.71</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-16.69</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-0.010297530077944456</v>
+      </c>
+      <c r="K20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>-2</v>
+      </c>
+      <c r="M20" s="1">
+        <v>-0.25944210939158774</v>
+      </c>
+      <c r="N20" s="1">
+        <v>39.178082191780824</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="C21" s="1">
+        <v>39.726027397260275</v>
+      </c>
+      <c r="D21" s="1">
+        <v>13.990196078431373</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5.19</v>
+      </c>
+      <c r="F21" s="1">
+        <v>-0.2411038543599589</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H21" s="1">
+        <v>66.9</v>
+      </c>
+      <c r="I21" s="1">
+        <v>15.81</v>
+      </c>
+      <c r="J21" s="1">
+        <v>-0.018608099112600755</v>
+      </c>
+      <c r="K21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>12</v>
+      </c>
+      <c r="M21" s="1">
+        <v>-0.2177543585414582</v>
+      </c>
+      <c r="N21" s="1">
+        <v>49.726027397260275</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8.11</v>
+      </c>
+      <c r="C22" s="1">
+        <v>69.86301369863014</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.6929716399506783</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-0.1772264863526779</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="H22" s="1">
+        <v>49.57</v>
+      </c>
+      <c r="I22" s="1">
+        <v>-1.58</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-0.014086529086350441</v>
+      </c>
+      <c r="K22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>99</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-0.14920709137047705</v>
+      </c>
+      <c r="N22" s="1">
+        <v>42.73972602739725</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>27.51</v>
+      </c>
+      <c r="C23" s="1">
+        <v>97.26027397260275</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-0.7593602326426754</v>
+      </c>
+      <c r="E23" s="1">
+        <v>-0.52</v>
+      </c>
+      <c r="F23" s="1">
+        <v>-0.18511495942593814</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="H23" s="1">
+        <v>46.38</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-8.54</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-0.007086198171881758</v>
+      </c>
+      <c r="K23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>29</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-0.16643536277113757</v>
+      </c>
+      <c r="N23" s="1">
+        <v>45.61643835616439</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-40.16</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1.36986301369863</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-0.3107569721115539</v>
+      </c>
+      <c r="E24" s="1">
+        <v>9.38</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.12354297255472929</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3.57</v>
+      </c>
+      <c r="H24" s="1">
+        <v>56.24</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-19.13</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.03533322298691831</v>
+      </c>
+      <c r="K24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>31</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.32357032006655184</v>
+      </c>
+      <c r="N24" s="1">
+        <v>30.13698630136986</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>-2.28</v>
+      </c>
+      <c r="C25" s="4">
+        <v>12.32876712328767</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.8859649122807016</v>
+      </c>
+      <c r="E25" s="4">
+        <v>11.91</v>
+      </c>
+      <c r="F25" s="4">
+        <v>-0.41617070166858905</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2.23</v>
+      </c>
+      <c r="H25" s="4">
+        <v>49.25</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-50.66</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-0.004391759318720075</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>48</v>
+      </c>
+      <c r="M25" s="4">
+        <v>-0.3204377688127362</v>
+      </c>
+      <c r="N25" s="4">
+        <v>28.21917808219178</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>-0.17</v>
+      </c>
+      <c r="C26" s="1">
+        <v>26.027397260273972</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-2571.7647058823527</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4.67</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.39523858859064376</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3.06</v>
+      </c>
+      <c r="H26" s="1">
+        <v>67.45</v>
+      </c>
+      <c r="I26" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.04177717695071901</v>
+      </c>
+      <c r="K26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>-8</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0.5555717932110151</v>
+      </c>
+      <c r="N26" s="1">
+        <v>41.64383561643836</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-1.13</v>
+      </c>
+      <c r="C27" s="1">
+        <v>15.068493150684931</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1.0176991150442478</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-0.12039774153805113</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.63</v>
+      </c>
+      <c r="H27" s="1">
+        <v>64.78</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-16.38</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.006609947032577026</v>
+      </c>
+      <c r="K27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>39</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0.0064678524091359435</v>
+      </c>
+      <c r="N27" s="1">
+        <v>39.178082191780824</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>16.43835616438356</v>
+      </c>
+      <c r="D28" s="1">
+        <v>7.536363636363636</v>
+      </c>
+      <c r="E28" s="1">
+        <v>-0.68</v>
+      </c>
+      <c r="F28" s="1">
+        <v>-0.31970377447527576</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3.14</v>
+      </c>
+      <c r="H28" s="1">
+        <v>60.92</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-20.32</v>
+      </c>
+      <c r="J28" s="1">
+        <v>-0.012172220584618951</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>29</v>
+      </c>
+      <c r="M28" s="1">
+        <v>-0.15314403763663753</v>
+      </c>
+      <c r="N28" s="1">
+        <v>35.06849315068493</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="C29" s="1">
+        <v>34.24657534246575</v>
+      </c>
+      <c r="D29" s="1">
+        <v>77.04545454545456</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.42996257372803337</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2.11</v>
+      </c>
+      <c r="H29" s="1">
+        <v>37.19</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-34.98</v>
+      </c>
+      <c r="J29" s="1">
+        <v>-0.015962598634841656</v>
+      </c>
+      <c r="K29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>-4</v>
+      </c>
+      <c r="M29" s="1">
+        <v>-0.34356943919958083</v>
+      </c>
+      <c r="N29" s="1">
+        <v>40.54794520547945</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="C30" s="3">
+        <v>45.20547945205479</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1656.8153846153846</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.13</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-0.08655665746831766</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="H30" s="3">
+        <v>64.3</v>
+      </c>
+      <c r="I30" s="3">
+        <v>9.52</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.003953742187912844</v>
+      </c>
+      <c r="K30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="3">
+        <v>46</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-0.07021201039536717</v>
+      </c>
+      <c r="N30" s="3">
+        <v>67.67123287671232</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3">
+        <v>5.13</v>
+      </c>
+      <c r="C31" s="3">
+        <v>57.534246575342465</v>
+      </c>
+      <c r="D31" s="3">
+        <v>10.491228070175438</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.09393275512484683</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="H31" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="I31" s="3">
+        <v>20.63</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.02821015310502491</v>
+      </c>
+      <c r="K31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>237</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0.12740036579803116</v>
+      </c>
+      <c r="N31" s="3">
+        <v>68.21917808219179</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>-2.92</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10.95890410958904</v>
+      </c>
+      <c r="D32" s="1">
+        <v>8.178082191780822</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="F32" s="1">
+        <v>-0.16925677684924556</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H32" s="1">
+        <v>38.88</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-6.87</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.007147597187803493</v>
+      </c>
+      <c r="K32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>26</v>
+      </c>
+      <c r="M32" s="1">
+        <v>-0.12177946868496081</v>
+      </c>
+      <c r="N32" s="1">
+        <v>36.02739726027397</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3">
+        <v>16.79</v>
+      </c>
+      <c r="C33" s="3">
+        <v>87.67123287671232</v>
+      </c>
+      <c r="D33" s="3">
+        <v>-0.05777248362120303</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-0.09350920506704644</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="H33" s="3">
+        <v>47.34</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-12.69</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.003219819799583533</v>
+      </c>
+      <c r="K33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>84</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-0.08650435632149622</v>
+      </c>
+      <c r="N33" s="3">
+        <v>50.41095890410959</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3">
+        <v>13.11</v>
+      </c>
+      <c r="C34" s="3">
+        <v>83.56164383561644</v>
+      </c>
+      <c r="D34" s="3">
+        <v>-0.6453089244851258</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.18594673738751583</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="H34" s="3">
+        <v>75.58</v>
+      </c>
+      <c r="I34" s="3">
+        <v>39.18</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.027190257492783167</v>
+      </c>
+      <c r="K34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>151</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0.2061829670968831</v>
+      </c>
+      <c r="N34" s="3">
+        <v>62.054794520547944</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>17.37</v>
+      </c>
+      <c r="C35" s="1">
+        <v>90.41095890410958</v>
+      </c>
+      <c r="D35" s="1">
+        <v>-0.48244099021301096</v>
+      </c>
+      <c r="E35" s="1">
+        <v>-0.96</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-0.28524829078477276</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
+        <v>28.14</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-24.3</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-0.02296186682611087</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>45</v>
+      </c>
+      <c r="M35" s="1">
+        <v>-0.28524829078477276</v>
+      </c>
+      <c r="N35" s="1">
+        <v>33.28767123287671</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>11.51</v>
+      </c>
+      <c r="C36" s="1">
+        <v>80.82191780821918</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.38488271068635965</v>
+      </c>
+      <c r="E36" s="1">
+        <v>-0.97</v>
+      </c>
+      <c r="F36" s="1">
+        <v>-0.10500106605254855</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1.12</v>
+      </c>
+      <c r="H36" s="1">
+        <v>37.87</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-15.8</v>
+      </c>
+      <c r="J36" s="1">
+        <v>-0.009795192494873697</v>
+      </c>
+      <c r="K36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>-19</v>
+      </c>
+      <c r="M36" s="1">
+        <v>-0.09566126772514827</v>
+      </c>
+      <c r="N36" s="1">
+        <v>42.6027397260274</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>5.33</v>
+      </c>
+      <c r="C37" s="1">
+        <v>61.64383561643836</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.598499061913696</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="F37" s="1">
+        <v>-0.0002634502732824784</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="H37" s="1">
+        <v>38.15</v>
+      </c>
+      <c r="I37" s="1">
+        <v>-22.14</v>
+      </c>
+      <c r="J37" s="1">
+        <v>-0.0015935583132703091</v>
+      </c>
+      <c r="K37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>-134</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0.02931257776348506</v>
+      </c>
+      <c r="N37" s="1">
+        <v>40.95890410958904</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3">
+        <v>-0.74</v>
+      </c>
+      <c r="C38" s="3">
+        <v>17.80821917808219</v>
+      </c>
+      <c r="D38" s="3">
+        <v>36.648648648648646</v>
+      </c>
+      <c r="E38" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.2565848720671759</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>79.02</v>
+      </c>
+      <c r="I38" s="3">
+        <v>22.5</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0.0377154227246231</v>
+      </c>
+      <c r="K38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>-13</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0.26436803734000947</v>
+      </c>
+      <c r="N38" s="3">
+        <v>65.75342465753424</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3">
+        <v>-0.18</v>
+      </c>
+      <c r="C39" s="3">
+        <v>24.65753424657534</v>
+      </c>
+      <c r="D39" s="3">
+        <v>100</v>
+      </c>
+      <c r="E39" s="3">
+        <v>-7.97</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.09896104967906434</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H39" s="3">
+        <v>51.5</v>
+      </c>
+      <c r="I39" s="3">
+        <v>9.19</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.022209839983126898</v>
+      </c>
+      <c r="K39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="3">
+        <v>-14</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0.12231054549756504</v>
+      </c>
+      <c r="N39" s="3">
+        <v>60</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-4.08</v>
+      </c>
+      <c r="C40" s="1">
+        <v>5.47945205479452</v>
+      </c>
+      <c r="D40" s="1">
+        <v>16.730392156862745</v>
+      </c>
+      <c r="E40" s="1">
+        <v>12.27</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0.3007306296715609</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>52.62</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-7.6</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.026083250500902558</v>
+      </c>
+      <c r="K40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>39</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0.22289897694322525</v>
+      </c>
+      <c r="N40" s="1">
+        <v>48.76712328767123</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>-5.03</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4.10958904109589</v>
+      </c>
+      <c r="D41" s="1">
+        <v>7.34990059642147</v>
+      </c>
+      <c r="E41" s="1">
+        <v>-1.75</v>
+      </c>
+      <c r="F41" s="1">
+        <v>-0.0036852313264936487</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.11</v>
+      </c>
+      <c r="H41" s="1">
+        <v>77.84</v>
+      </c>
+      <c r="I41" s="1">
+        <v>-5.77</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.011545940693400493</v>
+      </c>
+      <c r="K41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>5</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0.004876250473623278</v>
+      </c>
+      <c r="N41" s="1">
+        <v>45.89041095890411</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3.61</v>
+      </c>
+      <c r="C42" s="1">
+        <v>50.68493150684932</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1.0831024930747921</v>
+      </c>
+      <c r="E42" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>-0.06171624363361932</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="H42" s="1">
+        <v>35.56</v>
+      </c>
+      <c r="I42" s="1">
+        <v>-1.09</v>
+      </c>
+      <c r="J42" s="1">
+        <v>-0.005639504742872616</v>
+      </c>
+      <c r="K42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>34</v>
+      </c>
+      <c r="M42" s="1">
+        <v>-0.11152850137975412</v>
+      </c>
+      <c r="N42" s="1">
+        <v>42.19178082191781</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3">
+        <v>-0.02</v>
+      </c>
+      <c r="C43" s="3">
+        <v>30.136986301369863</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1214</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5.23</v>
+      </c>
+      <c r="F43" s="3">
+        <v>-0.11788447075728632</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="H43" s="3">
+        <v>40.05</v>
+      </c>
+      <c r="I43" s="3">
+        <v>-19.91</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0.000778454819904717</v>
+      </c>
+      <c r="K43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>6</v>
+      </c>
+      <c r="M43" s="3">
+        <v>-0.0968699245206357</v>
+      </c>
+      <c r="N43" s="3">
+        <v>52.73972602739725</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="C44" s="1">
+        <v>39.726027397260275</v>
+      </c>
+      <c r="D44" s="1">
+        <v>26.862745098039216</v>
+      </c>
+      <c r="E44" s="1">
+        <v>-1.51</v>
+      </c>
+      <c r="F44" s="1">
+        <v>-0.4086948409687774</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2.59</v>
+      </c>
+      <c r="H44" s="1">
+        <v>31.13</v>
+      </c>
+      <c r="I44" s="1">
+        <v>-32.48</v>
+      </c>
+      <c r="J44" s="1">
+        <v>-0.014441649997011271</v>
+      </c>
+      <c r="K44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>-18</v>
+      </c>
+      <c r="M44" s="1">
+        <v>-0.2849425131307237</v>
+      </c>
+      <c r="N44" s="1">
+        <v>39.178082191780824</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3">
+        <v>8.37</v>
+      </c>
+      <c r="C45" s="3">
+        <v>72.6027397260274</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.818399044205496</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.19926338824723241</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="H45" s="3">
+        <v>67.29</v>
+      </c>
+      <c r="I45" s="3">
+        <v>17.93</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0.026503299137149217</v>
+      </c>
+      <c r="K45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
+        <v>162</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0.2350659485022668</v>
+      </c>
+      <c r="N45" s="3">
+        <v>64.24657534246575</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="C46" s="3">
+        <v>23.28767123287671</v>
+      </c>
+      <c r="D46" s="3">
+        <v>543.5000000000001</v>
+      </c>
+      <c r="E46" s="3">
+        <v>-0.94</v>
+      </c>
+      <c r="F46" s="3">
+        <v>-0.2297895477228808</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="H46" s="3">
+        <v>47.16</v>
+      </c>
+      <c r="I46" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="J46" s="3">
+        <v>-0.0031429740706628317</v>
+      </c>
+      <c r="K46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="3">
+        <v>34</v>
+      </c>
+      <c r="M46" s="3">
+        <v>-0.19009540483142962</v>
+      </c>
+      <c r="N46" s="3">
+        <v>54.38356164383562</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>10.62</v>
+      </c>
+      <c r="C47" s="1">
+        <v>79.45205479452055</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.8549905838041432</v>
+      </c>
+      <c r="E47" s="1">
+        <v>-4.11</v>
+      </c>
+      <c r="F47" s="1">
+        <v>-0.3826233814282752</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H47" s="1">
+        <v>29.61</v>
+      </c>
+      <c r="I47" s="1">
+        <v>-18.46</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-0.029377374403905726</v>
+      </c>
+      <c r="K47" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>17</v>
+      </c>
+      <c r="M47" s="1">
+        <v>-0.3460425046459574</v>
+      </c>
+      <c r="N47" s="1">
+        <v>38.630136986301366</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3">
+        <v>3.98</v>
+      </c>
+      <c r="C48" s="3">
+        <v>52.054794520547944</v>
+      </c>
+      <c r="D48" s="3">
+        <v>7.505025125628141</v>
+      </c>
+      <c r="E48" s="3">
+        <v>-1.16</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.3146369702297377</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="H48" s="3">
+        <v>70.58</v>
+      </c>
+      <c r="I48" s="3">
+        <v>84.25</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0.035975479556466974</v>
+      </c>
+      <c r="K48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>285</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0.4002517882309069</v>
+      </c>
+      <c r="N48" s="3">
+        <v>69.45205479452055</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="C49" s="2">
+        <v>28.767123287671232</v>
+      </c>
+      <c r="D49" s="2">
+        <v>1710.0000000000002</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2.02</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.5564190128886244</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="H49" s="2">
+        <v>67.15</v>
+      </c>
+      <c r="I49" s="2">
+        <v>132.83</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.06063028435871016</v>
+      </c>
+      <c r="K49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2">
+        <v>246</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0.7743476405279641</v>
+      </c>
+      <c r="N49" s="2">
+        <v>74.10958904109589</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>-0.13</v>
+      </c>
+      <c r="C50" s="1">
+        <v>27.397260273972602</v>
+      </c>
+      <c r="D50" s="1">
+        <v>385.61538461538464</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2.75</v>
+      </c>
+      <c r="F50" s="1">
+        <v>-0.4919013894666925</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H50" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="I50" s="1">
+        <v>-28.75</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-0.028664922179145992</v>
+      </c>
+      <c r="K50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>7</v>
+      </c>
+      <c r="M50" s="1">
+        <v>-0.4506506135206746</v>
+      </c>
+      <c r="N50" s="1">
+        <v>38.35616438356164</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>-2.92</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10.95890410958904</v>
+      </c>
+      <c r="D51" s="1">
+        <v>-9.537671232876713</v>
+      </c>
+      <c r="E51" s="1">
+        <v>17.05</v>
+      </c>
+      <c r="F51" s="1">
+        <v>-0.02754911794085696</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2.37</v>
+      </c>
+      <c r="H51" s="1">
+        <v>57.35</v>
+      </c>
+      <c r="I51" s="1">
+        <v>36.04</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.03197237848976752</v>
+      </c>
+      <c r="K51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>95</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0.07908024629696286</v>
+      </c>
+      <c r="N51" s="1">
+        <v>36.16438356164384</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="C52" s="3">
+        <v>60.273972602739725</v>
+      </c>
+      <c r="D52" s="3">
+        <v>6.496226415094339</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.10336795887267708</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="H52" s="3">
+        <v>64.51</v>
+      </c>
+      <c r="I52" s="3">
+        <v>62.55</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0.024303727713901203</v>
+      </c>
+      <c r="K52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>269</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0.16796823063719568</v>
+      </c>
+      <c r="N52" s="3">
+        <v>66.71232876712328</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3">
+        <v>-0.71</v>
+      </c>
+      <c r="C53" s="3">
+        <v>19.17808219178082</v>
+      </c>
+      <c r="D53" s="3">
+        <v>12.042253521126762</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6.97</v>
+      </c>
+      <c r="F53" s="3">
+        <v>-0.23047455346300746</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="H53" s="3">
+        <v>69.11</v>
+      </c>
+      <c r="I53" s="3">
+        <v>-14.62</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0.015672053898523407</v>
+      </c>
+      <c r="K53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" s="3">
+        <v>25</v>
+      </c>
+      <c r="M53" s="3">
+        <v>-0.10672222562495381</v>
+      </c>
+      <c r="N53" s="3">
+        <v>50.684931506849324</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="C54" s="3">
+        <v>35.61643835616438</v>
+      </c>
+      <c r="D54" s="3">
+        <v>41.629629629629626</v>
+      </c>
+      <c r="E54" s="3">
+        <v>-0.44</v>
+      </c>
+      <c r="F54" s="3">
+        <v>-0.014193589483792485</v>
+      </c>
+      <c r="G54" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="H54" s="3">
+        <v>72</v>
+      </c>
+      <c r="I54" s="3">
+        <v>14.47</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0.02402155512672836</v>
+      </c>
+      <c r="K54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3">
+        <v>21</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0.02160897077124191</v>
+      </c>
+      <c r="N54" s="3">
+        <v>66.02739726027396</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4.03</v>
+      </c>
+      <c r="C55" s="1">
+        <v>54.794520547945204</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2.2580645161290325</v>
+      </c>
+      <c r="E55" s="1">
+        <v>-0.7</v>
+      </c>
+      <c r="F55" s="1">
+        <v>-0.1786140637783561</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="H55" s="1">
+        <v>37.94</v>
+      </c>
+      <c r="I55" s="1">
+        <v>-3.39</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0.000645407993285332</v>
+      </c>
+      <c r="K55" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>10</v>
+      </c>
+      <c r="M55" s="1">
+        <v>-0.16304773323268895</v>
+      </c>
+      <c r="N55" s="1">
+        <v>47.53424657534247</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>8.65</v>
+      </c>
+      <c r="C56" s="1">
+        <v>73.97260273972603</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0.1757225433526011</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="F56" s="1">
+        <v>-0.07433092129348562</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="H56" s="1">
+        <v>51.95</v>
+      </c>
+      <c r="I56" s="1">
+        <v>10.47</v>
+      </c>
+      <c r="J56" s="1">
+        <v>-0.009476292611681675</v>
+      </c>
+      <c r="K56" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>199</v>
+      </c>
+      <c r="M56" s="1">
+        <v>-0.13192634431245398</v>
+      </c>
+      <c r="N56" s="1">
+        <v>46.98630136986301</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>21.18</v>
+      </c>
+      <c r="C57" s="2">
+        <v>95.8904109589041</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2.2587346553352217</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0.7920358149187916</v>
+      </c>
+      <c r="G57" s="2">
+        <v>2</v>
+      </c>
+      <c r="H57" s="2">
+        <v>81.34</v>
+      </c>
+      <c r="I57" s="2">
+        <v>167.2</v>
+      </c>
+      <c r="J57" s="2">
+        <v>0.0780708832930195</v>
+      </c>
+      <c r="K57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2">
+        <v>409</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0.8698674676471272</v>
+      </c>
+      <c r="N57" s="2">
+        <v>82.05479452054794</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3">
+        <v>20.1</v>
+      </c>
+      <c r="C58" s="3">
+        <v>94.52054794520548</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.09701492537313429</v>
+      </c>
+      <c r="E58" s="3">
+        <v>-1.9</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.027420771345217337</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1.62</v>
+      </c>
+      <c r="H58" s="3">
+        <v>63.7</v>
+      </c>
+      <c r="I58" s="3">
+        <v>47.84</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0.02102064106989931</v>
+      </c>
+      <c r="K58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>315</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0.07567639603678544</v>
+      </c>
+      <c r="N58" s="3">
+        <v>64.93150684931507</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3">
+        <v>34.32</v>
+      </c>
+      <c r="C59" s="3">
+        <v>100</v>
+      </c>
+      <c r="D59" s="3">
+        <v>-1.435897435897436</v>
+      </c>
+      <c r="E59" s="3">
+        <v>-2.43</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.18278205477471943</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="H59" s="3">
+        <v>54.92</v>
+      </c>
+      <c r="I59" s="3">
+        <v>46.04</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.020132843939223818</v>
+      </c>
+      <c r="K59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>374</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0.20146165142952</v>
+      </c>
+      <c r="N59" s="3">
+        <v>60.136986301369866</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>6.37</v>
+      </c>
+      <c r="C60" s="1">
+        <v>67.12328767123287</v>
+      </c>
+      <c r="D60" s="1">
+        <v>-0.1255886970172684</v>
+      </c>
+      <c r="E60" s="1">
+        <v>-0.23</v>
+      </c>
+      <c r="F60" s="1">
+        <v>-0.1578547915092008</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="H60" s="1">
+        <v>38.38</v>
+      </c>
+      <c r="I60" s="1">
+        <v>-0.71</v>
+      </c>
+      <c r="J60" s="1">
+        <v>-0.009825585144730604</v>
+      </c>
+      <c r="K60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>149</v>
+      </c>
+      <c r="M60" s="1">
+        <v>-0.20611041620076886</v>
+      </c>
+      <c r="N60" s="1">
+        <v>38.08219178082192</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3">
+        <v>17.74</v>
+      </c>
+      <c r="C61" s="3">
+        <v>91.78082191780823</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.6178128523111613</v>
+      </c>
+      <c r="E61" s="3">
+        <v>-0.38</v>
+      </c>
+      <c r="F61" s="3">
+        <v>-0.13776233282311112</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="H61" s="3">
+        <v>49.53</v>
+      </c>
+      <c r="I61" s="3">
+        <v>11.85</v>
+      </c>
+      <c r="J61" s="3">
+        <v>-0.007127990710515013</v>
+      </c>
+      <c r="K61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>155</v>
+      </c>
+      <c r="M61" s="3">
+        <v>-0.14087559893224455</v>
+      </c>
+      <c r="N61" s="3">
+        <v>54.79452054794521</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>28.77</v>
+      </c>
+      <c r="C62" s="2">
+        <v>98.63013698630137</v>
+      </c>
+      <c r="D62" s="2">
+        <v>4.887382690302398</v>
+      </c>
+      <c r="E62" s="2">
+        <v>-8.63</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1.0334773690205432</v>
+      </c>
+      <c r="G62" s="2">
+        <v>4.76</v>
+      </c>
+      <c r="H62" s="2">
+        <v>69.78</v>
+      </c>
+      <c r="I62" s="2">
+        <v>254.34</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0.1054338291002765</v>
+      </c>
+      <c r="K62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" s="2">
+        <v>413</v>
+      </c>
+      <c r="M62" s="2">
+        <v>1.3261243832790852</v>
+      </c>
+      <c r="N62" s="2">
+        <v>83.42465753424656</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>10.54</v>
+      </c>
+      <c r="C63" s="2">
+        <v>78.08219178082192</v>
+      </c>
+      <c r="D63" s="2">
+        <v>6.3927893738140416</v>
+      </c>
+      <c r="E63" s="2">
+        <v>-4.36</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0.8382498433922643</v>
+      </c>
+      <c r="G63" s="2">
+        <v>2.03</v>
+      </c>
+      <c r="H63" s="2">
+        <v>78.91</v>
+      </c>
+      <c r="I63" s="2">
+        <v>146.6</v>
+      </c>
+      <c r="J63" s="2">
+        <v>0.08437980976811785</v>
+      </c>
+      <c r="K63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="2">
+        <v>184</v>
+      </c>
+      <c r="M63" s="2">
+        <v>0.91841644570245</v>
+      </c>
+      <c r="N63" s="2">
+        <v>78.63013698630137</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>16.87</v>
+      </c>
+      <c r="C64" s="1">
+        <v>89.04109589041096</v>
+      </c>
+      <c r="D64" s="1">
+        <v>-0.2691167753408418</v>
+      </c>
+      <c r="E64" s="1">
+        <v>-0.69</v>
+      </c>
+      <c r="F64" s="1">
+        <v>-0.05261259868038751</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="H64" s="1">
+        <v>61.16</v>
+      </c>
+      <c r="I64" s="1">
+        <v>4.17</v>
+      </c>
+      <c r="J64" s="1">
+        <v>-0.0101707777934316</v>
+      </c>
+      <c r="K64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>71</v>
+      </c>
+      <c r="M64" s="1">
+        <v>-0.10631643906293908</v>
+      </c>
+      <c r="N64" s="1">
+        <v>48.21917808219178</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>15.41</v>
+      </c>
+      <c r="C65" s="1">
+        <v>86.3013698630137</v>
+      </c>
+      <c r="D65" s="1">
+        <v>-0.10837118754055808</v>
+      </c>
+      <c r="E65" s="1">
+        <v>-0.19</v>
+      </c>
+      <c r="F65" s="1">
+        <v>-0.16014256613872618</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="H65" s="1">
+        <v>39.88</v>
+      </c>
+      <c r="I65" s="1">
+        <v>-35.2</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-0.0039042812625143045</v>
+      </c>
+      <c r="K65" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>-153</v>
+      </c>
+      <c r="M65" s="1">
+        <v>-0.15858593308415947</v>
+      </c>
+      <c r="N65" s="1">
+        <v>43.150684931506845</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3">
+        <v>4.01</v>
+      </c>
+      <c r="C66" s="3">
+        <v>53.42465753424658</v>
+      </c>
+      <c r="D66" s="3">
+        <v>7.0074812967581055</v>
+      </c>
+      <c r="E66" s="3">
+        <v>-0.9</v>
+      </c>
+      <c r="F66" s="3">
+        <v>-0.04829196322026859</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1.15</v>
+      </c>
+      <c r="H66" s="3">
+        <v>48.99</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-11.69</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0.0010865312594037855</v>
+      </c>
+      <c r="K66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
+        <v>-32</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.03661721531101825</v>
+      </c>
+      <c r="N66" s="3">
+        <v>51.36986301369863</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="C67" s="3">
+        <v>68.4931506849315</v>
+      </c>
+      <c r="D67" s="3">
+        <v>84.9795918367347</v>
+      </c>
+      <c r="E67" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F67" s="3">
+        <v>-0.18245498169290972</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="H67" s="3">
+        <v>46.24</v>
+      </c>
+      <c r="I67" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-0.010157730080911484</v>
+      </c>
+      <c r="K67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3">
+        <v>132</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-0.23460218902089458</v>
+      </c>
+      <c r="N67" s="3">
+        <v>61.369863013698634</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>8.24</v>
+      </c>
+      <c r="C68" s="1">
+        <v>71.23287671232876</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0.6286407766990291</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-0.07</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-0.25541787806132454</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H68" s="1">
+        <v>37.66</v>
+      </c>
+      <c r="I68" s="1">
+        <v>-13.14</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.013656123551502256</v>
+      </c>
+      <c r="K68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>-11</v>
+      </c>
+      <c r="M68" s="1">
+        <v>-0.21728036822444008</v>
+      </c>
+      <c r="N68" s="1">
+        <v>38.630136986301366</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <v>18.19</v>
+      </c>
+      <c r="C69" s="1">
+        <v>93.15068493150685</v>
+      </c>
+      <c r="D69" s="1">
+        <v>-0.47663551401869164</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="F69" s="1">
+        <v>-0.23237970677791941</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="H69" s="1">
+        <v>35.06</v>
+      </c>
+      <c r="I69" s="1">
+        <v>-15.42</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-0.01113208174974412</v>
+      </c>
+      <c r="K69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1">
+        <v>-34</v>
+      </c>
+      <c r="M69" s="1">
+        <v>-0.24249782163260303</v>
+      </c>
+      <c r="N69" s="1">
+        <v>39.17808219178082</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="C70" s="1">
+        <v>43.83561643835616</v>
+      </c>
+      <c r="D70" s="1">
+        <v>13.532894736842104</v>
+      </c>
+      <c r="E70" s="1">
+        <v>-0.78</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-0.41807334802057516</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.11</v>
+      </c>
+      <c r="H70" s="1">
+        <v>31.88</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-32.53</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.03761723103276857</v>
+      </c>
+      <c r="K70" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>-65</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.4095118662204582</v>
+      </c>
+      <c r="N70" s="1">
+        <v>36.71232876712329</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5.18</v>
+      </c>
+      <c r="C71" s="1">
+        <v>58.9041095890411</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0.7837837837837839</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-0.23833306205712548</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="H71" s="1">
+        <v>51.82</v>
+      </c>
+      <c r="I71" s="1">
+        <v>-6.67</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-0.012878578894644761</v>
+      </c>
+      <c r="K71" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>-20</v>
+      </c>
+      <c r="M71" s="1">
+        <v>-0.23755474552984213</v>
+      </c>
+      <c r="N71" s="1">
+        <v>40.54794520547945</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>10.42</v>
+      </c>
+      <c r="C72" s="1">
+        <v>76.71232876712328</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.21305182341650677</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-1.31</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.26469596208705964</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H72" s="1">
+        <v>36.4</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-10.17</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.01325063782997437</v>
+      </c>
+      <c r="K72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1">
+        <v>62</v>
+      </c>
+      <c r="M72" s="1">
+        <v>-0.25379953070509265</v>
+      </c>
+      <c r="N72" s="1">
+        <v>38.630136986301366</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" s="3">
+        <v>13.11</v>
+      </c>
+      <c r="C73" s="3">
+        <v>83.56164383561644</v>
+      </c>
+      <c r="D73" s="3">
+        <v>-0.6414950419527079</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0.17290898537333294</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="H73" s="3">
+        <v>75.07</v>
+      </c>
+      <c r="I73" s="3">
+        <v>37.95</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0.026389290740785554</v>
+      </c>
+      <c r="K73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>144</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0.19314521508270022</v>
+      </c>
+      <c r="N73" s="3">
+        <v>61.64383561643836</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2.84</v>
+      </c>
+      <c r="C74" s="3">
+        <v>46.57534246575342</v>
+      </c>
+      <c r="D74" s="3">
+        <v>2.485915492957747</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0.10777142216624942</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="H74" s="3">
+        <v>78.87</v>
+      </c>
+      <c r="I74" s="3">
+        <v>33.75</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0.022654296415204802</v>
+      </c>
+      <c r="K74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" s="3">
+        <v>130</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0.10232320647526594</v>
+      </c>
+      <c r="N74" s="3">
+        <v>61.64383561643836</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1193,15 +5123,599 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>41.36986301369862</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>75.75342465753425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>32.87671232876712</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>62.1917808219178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>41.09589041095891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>63.01369863013699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>67.12328767123287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>49.45205479452054</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>49.58904109589041</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>54.52054794520548</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>42.1917808219178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>29.58904109589041</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>53.28767123287671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>70.68493150684931</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>44.794520547945204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>28.767123287671232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>53.287671232876704</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>57.3972602739726</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>39.178082191780824</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>49.726027397260275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>42.73972602739725</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>45.61643835616439</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>30.13698630136986</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>28.21917808219178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>41.64383561643836</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>39.178082191780824</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>35.06849315068493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>40.54794520547945</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>67.67123287671232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>68.21917808219179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>36.02739726027397</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>50.41095890410959</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>62.054794520547944</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>33.28767123287671</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>42.6027397260274</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>40.95890410958904</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>65.75342465753424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>48.76712328767123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>45.89041095890411</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>42.19178082191781</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>52.73972602739725</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>39.178082191780824</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>64.24657534246575</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>54.38356164383562</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>38.630136986301366</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>69.45205479452055</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>74.10958904109589</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>38.35616438356164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>36.16438356164384</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>66.71232876712328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>50.684931506849324</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>66.02739726027396</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>47.53424657534247</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>46.98630136986301</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>82.05479452054794</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>64.93150684931507</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>60.136986301369866</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>38.08219178082192</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>54.79452054794521</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>83.42465753424656</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>78.63013698630137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>48.21917808219178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>43.150684931506845</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>51.36986301369863</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>61.369863013698634</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>38.630136986301366</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>39.17808219178082</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>36.71232876712329</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>40.54794520547945</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>38.630136986301366</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73">
+        <v>61.64383561643836</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74">
+        <v>61.64383561643836</v>
       </c>
     </row>
   </sheetData>
@@ -1212,12 +5726,145 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1228,12 +5875,122 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1252,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,112 +6020,112 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1379,12 +6136,368 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="SignalsTriggered" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="227">
   <si>
     <t>Ticker</t>
   </si>
@@ -240,13 +241,13 @@
     <t>EPS_TTM</t>
   </si>
   <si>
-    <t>EPS_Percentile_In_Universe</t>
-  </si>
-  <si>
-    <t>EPS_Fwd_Grwth_Trnd</t>
-  </si>
-  <si>
-    <t>Institutional_Accumulation_%</t>
+    <t>EPS_Percentile</t>
+  </si>
+  <si>
+    <t>EPS_Growth</t>
+  </si>
+  <si>
+    <t>Inst_Accumulation</t>
   </si>
   <si>
     <t>Alpha_63D</t>
@@ -255,31 +256,43 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>RSI_14Day</t>
-  </si>
-  <si>
-    <t>SMA200_Dist_%</t>
-  </si>
-  <si>
-    <t>MA_Slope_50</t>
-  </si>
-  <si>
-    <t>Vol Expansion</t>
-  </si>
-  <si>
-    <t>LastQRtr_InstActivity</t>
+    <t>RSI</t>
+  </si>
+  <si>
+    <t>SMA200_Dist</t>
+  </si>
+  <si>
+    <t>MA_Slope</t>
+  </si>
+  <si>
+    <t>Volume_Expansion</t>
+  </si>
+  <si>
+    <t>Net_Inst</t>
   </si>
   <si>
     <t>RS_vs_SP100</t>
   </si>
   <si>
-    <t>Composite_Score</t>
+    <t>Return_63D</t>
+  </si>
+  <si>
+    <t>RS_Rank</t>
+  </si>
+  <si>
+    <t>Drawdown_%</t>
+  </si>
+  <si>
+    <t>Old_Score</t>
+  </si>
+  <si>
+    <t>New_Score</t>
   </si>
   <si>
     <t>Earnings_Date</t>
   </si>
   <si>
-    <t>Daily_Composite_Score_delta</t>
+    <t>Delta</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -366,12 +379,33 @@
     <t>2027-03-31</t>
   </si>
   <si>
+    <t>ATEN</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>OMCL</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
     <t>GOOG</t>
   </si>
   <si>
     <t>CSCO</t>
   </si>
   <si>
+    <t>DELL</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
@@ -381,42 +415,27 @@
     <t>Value</t>
   </si>
   <si>
-    <t>ATEN</t>
-  </si>
-  <si>
     <t>Last Run</t>
   </si>
   <si>
-    <t>WSR</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
     <t>Russell 2000</t>
   </si>
   <si>
-    <t>OMCL</t>
-  </si>
-  <si>
     <t>Cap</t>
   </si>
   <si>
     <t>Small ($300M–$2B)</t>
   </si>
   <si>
-    <t>MD</t>
-  </si>
-  <si>
     <t>Price min</t>
   </si>
   <si>
     <t>&gt; $7</t>
   </si>
   <si>
-    <t>SHO</t>
-  </si>
-  <si>
     <t>YTD perf min</t>
   </si>
   <si>
@@ -510,9 +529,6 @@
     <t>3 of 3 qualified</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>S&amp;P 500 (large-cap subset)</t>
   </si>
   <si>
@@ -540,46 +556,64 @@
     <t>Source</t>
   </si>
   <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>Earnings quality vs peers</t>
+    <t>EPS Percentile</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Earnings strength vs peers</t>
   </si>
   <si>
     <t>Finviz</t>
   </si>
   <si>
-    <t>P(EPS_Fwd_Growth)</t>
-  </si>
-  <si>
-    <t>Earnings acceleration</t>
-  </si>
-  <si>
-    <t>P(MA_Slope_50)</t>
+    <t>EPS Growth Trend</t>
+  </si>
+  <si>
+    <t>Forward growth momentum</t>
+  </si>
+  <si>
+    <t>Return 63D</t>
   </si>
   <si>
     <t>20%</t>
   </si>
   <si>
-    <t>Medium-term price trend</t>
-  </si>
-  <si>
-    <t>Yahoo Finance prices</t>
-  </si>
-  <si>
-    <t>P(RSI_14)</t>
+    <t>Price momentum</t>
+  </si>
+  <si>
+    <t>Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Relative Strength</t>
   </si>
   <si>
     <t>10%</t>
   </si>
   <si>
-    <t>Short-term momentum strength</t>
-  </si>
-  <si>
-    <t>P(SMA200_Dist)</t>
-  </si>
-  <si>
-    <t>Long-term trend confirmation</t>
+    <t>Market outperformance</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
+    <t>MA Slope</t>
+  </si>
+  <si>
+    <t>Trend confirmation</t>
+  </si>
+  <si>
+    <t>Drawdown</t>
+  </si>
+  <si>
+    <t>-10%</t>
+  </si>
+  <si>
+    <t>Risk penalty</t>
+  </si>
+  <si>
+    <t>Price history</t>
   </si>
   <si>
     <t/>
@@ -588,7 +622,7 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+    <t>Composite = Growth + Momentum + Strength + Trend - Risk</t>
   </si>
   <si>
     <t>Score Range</t>
@@ -621,10 +655,52 @@
     <t>Consider reducing position</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Triggers</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Volume Spike</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -654,17 +730,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1269,6 +1345,578 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <v>72.34177215189874</v>
+      </c>
+      <c r="C2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3">
+        <v>67.34177215189874</v>
+      </c>
+      <c r="C3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4">
+        <v>66.96202531645571</v>
+      </c>
+      <c r="C4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>64.9367088607595</v>
+      </c>
+      <c r="C5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6">
+        <v>64.24050632911393</v>
+      </c>
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>63.544303797468345</v>
+      </c>
+      <c r="C7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>63.037974683544306</v>
+      </c>
+      <c r="C8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>61.962025316455694</v>
+      </c>
+      <c r="C9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10">
+        <v>61.0126582278481</v>
+      </c>
+      <c r="C10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>60.822784810126585</v>
+      </c>
+      <c r="C11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12">
+        <v>58.037974683544306</v>
+      </c>
+      <c r="C12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13">
+        <v>56.962025316455694</v>
+      </c>
+      <c r="C13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14">
+        <v>56.77215189873419</v>
+      </c>
+      <c r="C14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15">
+        <v>56.582278481012665</v>
+      </c>
+      <c r="C15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16">
+        <v>56.32911392405063</v>
+      </c>
+      <c r="C16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>55.31645569620253</v>
+      </c>
+      <c r="C17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>55.316455696202524</v>
+      </c>
+      <c r="C18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>54.55696202531646</v>
+      </c>
+      <c r="C19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20">
+        <v>54.43037974683545</v>
+      </c>
+      <c r="C20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>53.92405063291139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
+        <v>53.41772151898734</v>
+      </c>
+      <c r="C22" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>52.65822784810126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>51.139240506329116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25">
+        <v>49.683544303797476</v>
+      </c>
+      <c r="C25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
+        <v>47.53164556962025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>46.455696202531655</v>
+      </c>
+      <c r="C27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28">
+        <v>46.45569620253164</v>
+      </c>
+      <c r="C28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>45.31645569620254</v>
+      </c>
+      <c r="C29" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30">
+        <v>44.936708860759495</v>
+      </c>
+      <c r="C30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>42.848101265822784</v>
+      </c>
+      <c r="C31" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32">
+        <v>42.21518987341772</v>
+      </c>
+      <c r="C32" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>42.151898734177216</v>
+      </c>
+      <c r="C33" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34">
+        <v>42.08860759493671</v>
+      </c>
+      <c r="C34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35">
+        <v>41.202531645569614</v>
+      </c>
+      <c r="C35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36">
+        <v>40.8860759493671</v>
+      </c>
+      <c r="C36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>40.75949367088608</v>
+      </c>
+      <c r="C37" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38">
+        <v>39.9367088607595</v>
+      </c>
+      <c r="C38" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39">
+        <v>38.79746835443038</v>
+      </c>
+      <c r="C39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40">
+        <v>38.54430379746835</v>
+      </c>
+      <c r="C40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41">
+        <v>37.40506329113924</v>
+      </c>
+      <c r="C41" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>36.64556962025316</v>
+      </c>
+      <c r="C42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43">
+        <v>36.582278481012665</v>
+      </c>
+      <c r="C43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44">
+        <v>35.189873417721515</v>
+      </c>
+      <c r="C44" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45">
+        <v>35.12658227848102</v>
+      </c>
+      <c r="C45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46">
+        <v>34.30379746835443</v>
+      </c>
+      <c r="C46" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47">
+        <v>33.98734177215189</v>
+      </c>
+      <c r="C47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48">
+        <v>33.037974683544306</v>
+      </c>
+      <c r="C48" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49">
+        <v>32.84810126582278</v>
+      </c>
+      <c r="C49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50">
+        <v>31.962025316455694</v>
+      </c>
+      <c r="C50" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51">
+        <v>31.39240506329114</v>
+      </c>
+      <c r="C51" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
@@ -1412,10 +2060,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1464,8 +2112,20 @@
       <c r="P1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S1" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1473,7 +2133,7 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>63.013698630136986</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="D2" s="1">
         <v>-1.5446880269814502</v>
@@ -1482,19 +2142,19 @@
         <v>-0.05</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.050408902280218</v>
+        <v>-0.01238980890086984</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>49.8</v>
+        <v>51.62</v>
       </c>
       <c r="I2" s="1">
-        <v>17.1</v>
+        <v>17.75</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0016926625628907066</v>
+        <v>-0.0010214726622593266</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -1503,19 +2163,31 @@
         <v>325</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.11423085751745321</v>
+        <v>-0.09931581803557199</v>
       </c>
       <c r="N2" s="1">
-        <v>41.36986301369862</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>87</v>
+        <v>1.744151017747948</v>
+      </c>
+      <c r="O2" s="1">
+        <v>41.77215189873418</v>
       </c>
       <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15.687871758897787</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>41.89873417721519</v>
+      </c>
+      <c r="R2" s="1">
+        <v>32.84810126582278</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T2" s="1">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1523,7 +2195,7 @@
         <v>3.05</v>
       </c>
       <c r="C3" s="2">
-        <v>47.94520547945205</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
         <v>23.98032786885246</v>
@@ -1532,19 +2204,19 @@
         <v>2.08</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8859885294205656</v>
+        <v>0.8977684935470766</v>
       </c>
       <c r="G3" s="2">
         <v>2.43</v>
       </c>
       <c r="H3" s="2">
-        <v>76.2</v>
+        <v>76.34</v>
       </c>
       <c r="I3" s="2">
-        <v>101.03</v>
+        <v>100.36</v>
       </c>
       <c r="J3" s="2">
-        <v>0.09871835961238663</v>
+        <v>0.10087590049150968</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -1553,119 +2225,155 @@
         <v>171</v>
       </c>
       <c r="M3" s="2">
-        <v>0.9972877928220856</v>
+        <v>1.04935897289174</v>
       </c>
       <c r="N3" s="2">
-        <v>75.75342465753425</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>88</v>
+        <v>116.61163011047915</v>
+      </c>
+      <c r="O3" s="2">
+        <v>94.9367088607595</v>
       </c>
       <c r="P3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+        <v>26.467189489392297</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>76.07594936708861</v>
+      </c>
+      <c r="R3" s="2">
+        <v>64.9367088607595</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>-3.95</v>
       </c>
-      <c r="C4" s="1">
-        <v>6.8493150684931505</v>
-      </c>
-      <c r="D4" s="1">
-        <v>9.977215189873418</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="3">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.865822784810128</v>
+      </c>
+      <c r="E4" s="3">
         <v>2.62</v>
       </c>
-      <c r="F4" s="1">
-        <v>-0.24432660541346612</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="F4" s="3">
+        <v>-0.25742575530792045</v>
+      </c>
+      <c r="G4" s="3">
         <v>1.1</v>
       </c>
-      <c r="H4" s="1">
-        <v>53.78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>-25.47</v>
-      </c>
-      <c r="J4" s="1">
-        <v>-0.010825776730706725</v>
-      </c>
-      <c r="K4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>-64</v>
-      </c>
-      <c r="M4" s="1">
-        <v>-0.23654344014063255</v>
-      </c>
-      <c r="N4" s="1">
-        <v>32.87671232876712</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="H4" s="3">
+        <v>52.47</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-25.95</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-0.011147903158076383</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>-69</v>
+      </c>
+      <c r="M4" s="3">
+        <v>-0.2468250224866153</v>
+      </c>
+      <c r="N4" s="3">
+        <v>-13.006769427356394</v>
+      </c>
+      <c r="O4" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="P4" s="3">
+        <v>48.360550359989794</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>31.0126582278481</v>
+      </c>
+      <c r="R4" s="3">
+        <v>14.810126582278478</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>1.09</v>
       </c>
-      <c r="C5" s="3">
-        <v>41.0958904109589</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="1">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="D5" s="1">
         <v>23.917431192660548</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>0.63</v>
       </c>
-      <c r="F5" s="3">
-        <v>-0.11193070522842519</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5" s="1">
+        <v>-0.13615623324950624</v>
+      </c>
+      <c r="G5" s="1">
         <v>1.81</v>
       </c>
-      <c r="H5" s="3">
-        <v>70.19</v>
-      </c>
-      <c r="I5" s="3">
-        <v>9.6</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.007292648979306909</v>
-      </c>
-      <c r="K5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="H5" s="1">
+        <v>70.53</v>
+      </c>
+      <c r="I5" s="1">
+        <v>9.77</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.00961777982348318</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
         <v>28</v>
       </c>
-      <c r="M5" s="3">
-        <v>-0.0488870665184733</v>
-      </c>
-      <c r="N5" s="3">
-        <v>62.1917808219178</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M5" s="1">
+        <v>-0.05029029739693458</v>
+      </c>
+      <c r="N5" s="1">
+        <v>6.646703081611673</v>
+      </c>
+      <c r="O5" s="1">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P5" s="1">
+        <v>29.9318207359553</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>61.77215189873418</v>
+      </c>
+      <c r="R5" s="1">
+        <v>45.31645569620254</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1673,7 +2381,7 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>49.31506849315068</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="D6" s="1">
         <v>1.4271844660194175</v>
@@ -1682,140 +2390,176 @@
         <v>-0.4</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.03010880975809349</v>
+        <v>-0.02516901345413544</v>
       </c>
       <c r="G6" s="1">
         <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>37.71</v>
+        <v>37.91</v>
       </c>
       <c r="I6" s="1">
-        <v>-14.88</v>
+        <v>-14.71</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.004594839874945752</v>
+        <v>-0.008179825383145704</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M6" s="1">
-        <v>0.011141966187924401</v>
+        <v>0.03101487049878182</v>
       </c>
       <c r="N6" s="1">
-        <v>41.09589041095891</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>91</v>
+        <v>14.777219871183316</v>
+      </c>
+      <c r="O6" s="1">
+        <v>60.75949367088608</v>
       </c>
       <c r="P6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+        <v>20.72548824337846</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>38.860759493670884</v>
+      </c>
+      <c r="R6" s="1">
+        <v>42.08860759493671</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>4.9</v>
       </c>
-      <c r="C7" s="3">
-        <v>56.16438356164384</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6.214285714285714</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" s="2">
+        <v>58.22784810126582</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6.242857142857143</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.14</v>
       </c>
-      <c r="F7" s="3">
-        <v>0.002395017639876429</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F7" s="2">
+        <v>0.002445248234289321</v>
+      </c>
+      <c r="G7" s="2">
         <v>2.25</v>
       </c>
-      <c r="H7" s="3">
-        <v>72.13</v>
-      </c>
-      <c r="I7" s="3">
-        <v>21.78</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.018386371875611464</v>
-      </c>
-      <c r="K7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0.09968458355029597</v>
-      </c>
-      <c r="N7" s="3">
-        <v>63.01369863013699</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="H7" s="2">
+        <v>76.18</v>
+      </c>
+      <c r="I7" s="2">
+        <v>26.19</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.02207931320336696</v>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.13495440850060358</v>
+      </c>
+      <c r="N7" s="2">
+        <v>25.171173671365487</v>
+      </c>
+      <c r="O7" s="2">
+        <v>70.88607594936708</v>
+      </c>
+      <c r="P7" s="2">
+        <v>15.539987609451147</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>64.43037974683543</v>
+      </c>
+      <c r="R7" s="2">
+        <v>54.55696202531646</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>13.24</v>
       </c>
-      <c r="C8" s="3">
-        <v>84.93150684931507</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8" s="2">
+        <v>86.07594936708861</v>
+      </c>
+      <c r="D8" s="2">
         <v>-0.012084592145015116</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>0.43</v>
       </c>
-      <c r="F8" s="3">
-        <v>0.37619453788542767</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="2">
+        <v>0.3224922725360976</v>
+      </c>
+      <c r="G8" s="2">
         <v>0.66</v>
       </c>
-      <c r="H8" s="3">
-        <v>85.55</v>
-      </c>
-      <c r="I8" s="3">
-        <v>25.69</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.03155966068115684</v>
-      </c>
-      <c r="K8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="H8" s="2">
+        <v>83.87</v>
+      </c>
+      <c r="I8" s="2">
+        <v>24.99</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.03278211098778094</v>
+      </c>
+      <c r="K8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
         <v>-140</v>
       </c>
-      <c r="M8" s="3">
-        <v>0.3497317759577936</v>
-      </c>
-      <c r="N8" s="3">
-        <v>67.12328767123287</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M8" s="2">
+        <v>0.28644978094366014</v>
+      </c>
+      <c r="N8" s="2">
+        <v>40.320710915671164</v>
+      </c>
+      <c r="O8" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="P8" s="2">
+        <v>27.294677507005353</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>66.07594936708861</v>
+      </c>
+      <c r="R8" s="2">
+        <v>55.316455696202524</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1823,28 +2567,28 @@
         <v>0.89</v>
       </c>
       <c r="C9" s="1">
-        <v>36.986301369863014</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="D9" s="1">
-        <v>46.10112359550562</v>
+        <v>46.2247191011236</v>
       </c>
       <c r="E9" s="1">
         <v>2.14</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.16821378172750712</v>
+        <v>-0.1346267787903565</v>
       </c>
       <c r="G9" s="1">
         <v>1.49</v>
       </c>
       <c r="H9" s="1">
-        <v>38.39</v>
+        <v>43.47</v>
       </c>
       <c r="I9" s="1">
-        <v>-20.5</v>
+        <v>-18.03</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.003010889503415941</v>
+        <v>-0.006101797654469959</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
@@ -1853,19 +2597,31 @@
         <v>54</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.13007627189062265</v>
+        <v>-0.0826831879659613</v>
       </c>
       <c r="N9" s="1">
-        <v>49.45205479452054</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>94</v>
+        <v>3.407414024709004</v>
+      </c>
+      <c r="O9" s="1">
+        <v>45.56962025316456</v>
       </c>
       <c r="P9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>34.04748479877408</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>48.9873417721519</v>
+      </c>
+      <c r="R9" s="1">
+        <v>41.202531645569614</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1873,28 +2629,28 @@
         <v>6.25</v>
       </c>
       <c r="C10" s="1">
-        <v>65.75342465753424</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="D10" s="1">
-        <v>0.5312</v>
+        <v>0.5408000000000002</v>
       </c>
       <c r="E10" s="1">
         <v>1.07</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.15027436489102597</v>
+        <v>-0.12925719658795642</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>53.61</v>
+        <v>55.02</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.77</v>
+        <v>-3.13</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0016240548226396764</v>
+        <v>0.0014049222467605465</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -1903,219 +2659,279 @@
         <v>-83</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.11836338727240836</v>
+        <v>-0.08579419202060534</v>
       </c>
       <c r="N10" s="1">
-        <v>49.58904109589041</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>95</v>
+        <v>3.0963136192446155</v>
+      </c>
+      <c r="O10" s="1">
+        <v>44.303797468354425</v>
       </c>
       <c r="P10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+        <v>20.24508080818123</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>48.22784810126583</v>
+      </c>
+      <c r="R10" s="1">
+        <v>38.79746835443038</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>-1.36</v>
       </c>
-      <c r="C11" s="3">
-        <v>13.698630136986301</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="D11" s="1">
         <v>31.911764705882348</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>8.3</v>
       </c>
-      <c r="F11" s="3">
-        <v>0.10682310569657667</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="1">
+        <v>0.13403760617326035</v>
+      </c>
+      <c r="G11" s="1">
         <v>0.81</v>
       </c>
-      <c r="H11" s="3">
-        <v>61.24</v>
-      </c>
-      <c r="I11" s="3">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.021283661493117726</v>
-      </c>
-      <c r="K11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
+      <c r="H11" s="1">
+        <v>63.55</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5.28</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.021033713114448644</v>
+      </c>
+      <c r="K11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
         <v>15</v>
       </c>
-      <c r="M11" s="3">
-        <v>0.0920350916781929</v>
-      </c>
-      <c r="N11" s="3">
-        <v>54.52054794520548</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="M11" s="1">
+        <v>0.11389621381278059</v>
+      </c>
+      <c r="N11" s="1">
+        <v>23.065354202583205</v>
+      </c>
+      <c r="O11" s="1">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="P11" s="1">
+        <v>23.11654999559394</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>53.54430379746836</v>
+      </c>
+      <c r="R11" s="1">
+        <v>46.455696202531655</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>-0.34</v>
       </c>
-      <c r="C12" s="1">
-        <v>21.91780821917808</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="D12" s="3">
         <v>65.85294117647058</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="3">
         <v>-0.32</v>
       </c>
-      <c r="F12" s="1">
-        <v>-0.34006166540284416</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F12" s="3">
+        <v>-0.3390113878920355</v>
+      </c>
+      <c r="G12" s="3">
         <v>0.82</v>
       </c>
-      <c r="H12" s="1">
-        <v>44.51</v>
-      </c>
-      <c r="I12" s="1">
-        <v>-39.51</v>
-      </c>
-      <c r="J12" s="1">
-        <v>-0.009139416668990319</v>
-      </c>
-      <c r="K12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="H12" s="3">
+        <v>46.63</v>
+      </c>
+      <c r="I12" s="3">
+        <v>-38.15</v>
+      </c>
+      <c r="J12" s="3">
+        <v>-0.01139281110627393</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>-15</v>
       </c>
-      <c r="M12" s="1">
-        <v>-0.3540713628939446</v>
-      </c>
-      <c r="N12" s="1">
-        <v>42.1917808219178</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="M12" s="3">
+        <v>-0.35809270697038476</v>
+      </c>
+      <c r="N12" s="3">
+        <v>-24.133537875733335</v>
+      </c>
+      <c r="O12" s="3">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="P12" s="3">
+        <v>49.67608188777989</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>39.493670886075954</v>
+      </c>
+      <c r="R12" s="3">
+        <v>20.696202531645564</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>0.02</v>
       </c>
-      <c r="C13" s="4">
-        <v>31.506849315068493</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="3">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="D13" s="3">
         <v>-1653.5</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>2.73</v>
       </c>
-      <c r="F13" s="4">
-        <v>-0.1884108124741753</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="3">
+        <v>-0.1759208009707229</v>
+      </c>
+      <c r="G13" s="3">
         <v>1.43</v>
       </c>
-      <c r="H13" s="4">
-        <v>56.28</v>
-      </c>
-      <c r="I13" s="4">
-        <v>7.78</v>
-      </c>
-      <c r="J13" s="4">
-        <v>-0.004604348070180763</v>
-      </c>
-      <c r="K13" s="4" t="b">
+      <c r="H13" s="3">
+        <v>53.88</v>
+      </c>
+      <c r="I13" s="3">
+        <v>5.67</v>
+      </c>
+      <c r="J13" s="3">
+        <v>-0.0026568641580235123</v>
+      </c>
+      <c r="K13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="3">
         <v>21</v>
       </c>
-      <c r="M13" s="4">
-        <v>-0.15494320180099097</v>
-      </c>
-      <c r="N13" s="4">
-        <v>29.58904109589041</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="M13" s="3">
+        <v>-0.13033764983911078</v>
+      </c>
+      <c r="N13" s="3">
+        <v>-1.3580321626059373</v>
+      </c>
+      <c r="O13" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="P13" s="3">
+        <v>39.74359086324119</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>28.481012658227847</v>
+      </c>
+      <c r="R13" s="3">
+        <v>15.88607594936709</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T13" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>1.31</v>
       </c>
-      <c r="C14" s="3">
-        <v>42.465753424657535</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="1">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="D14" s="1">
         <v>7.580152671755725</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>0.33</v>
       </c>
-      <c r="F14" s="3">
-        <v>-0.17062662060495917</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="1">
+        <v>-0.11661797016911667</v>
+      </c>
+      <c r="G14" s="1">
         <v>0.6</v>
       </c>
-      <c r="H14" s="3">
-        <v>52.04</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-8.36</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0.009613205960270458</v>
-      </c>
-      <c r="K14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="H14" s="1">
+        <v>57.94</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-4.21</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.010041979719406674</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>14</v>
       </c>
-      <c r="M14" s="3">
-        <v>-0.20175928169629342</v>
-      </c>
-      <c r="N14" s="3">
-        <v>53.28767123287671</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M14" s="1">
+        <v>-0.15902090145433723</v>
+      </c>
+      <c r="N14" s="1">
+        <v>-4.226357324128582</v>
+      </c>
+      <c r="O14" s="1">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="P14" s="1">
+        <v>33.10300785656511</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>53.92405063291139</v>
+      </c>
+      <c r="R14" s="1">
+        <v>35.189873417721515</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2123,7 +2939,7 @@
         <v>-0.63</v>
       </c>
       <c r="C15" s="2">
-        <v>20.54794520547945</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="D15" s="2">
         <v>62.85714285714286</v>
@@ -2132,19 +2948,19 @@
         <v>5.78</v>
       </c>
       <c r="F15" s="2">
-        <v>1.307455626469211</v>
+        <v>1.2291696989512908</v>
       </c>
       <c r="G15" s="2">
         <v>2.22</v>
       </c>
       <c r="H15" s="2">
-        <v>74.77</v>
+        <v>69.51</v>
       </c>
       <c r="I15" s="2">
-        <v>174.21</v>
+        <v>161.02</v>
       </c>
       <c r="J15" s="2">
-        <v>0.1276636686580595</v>
+        <v>0.12724079067001726</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2153,19 +2969,31 @@
         <v>206</v>
       </c>
       <c r="M15" s="2">
-        <v>1.4024102427977805</v>
+        <v>1.3584986393712135</v>
       </c>
       <c r="N15" s="2">
-        <v>70.68493150684931</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>99</v>
+        <v>147.5255967584265</v>
+      </c>
+      <c r="O15" s="2">
+        <v>100</v>
       </c>
       <c r="P15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24.171577948970977</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>69.49367088607595</v>
+      </c>
+      <c r="R15" s="2">
+        <v>61.962025316455694</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2173,7 +3001,7 @@
         <v>-3.53</v>
       </c>
       <c r="C16" s="1">
-        <v>8.21917808219178</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="D16" s="1">
         <v>12.218130311614733</v>
@@ -2182,19 +3010,19 @@
         <v>4.52</v>
       </c>
       <c r="F16" s="1">
-        <v>0.028256571454628232</v>
+        <v>-0.059777735429645346</v>
       </c>
       <c r="G16" s="1">
         <v>1.94</v>
       </c>
       <c r="H16" s="1">
-        <v>52.95</v>
+        <v>47.33</v>
       </c>
       <c r="I16" s="1">
-        <v>8.2</v>
+        <v>2.21</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.00005125714893301769</v>
+        <v>-0.0010320582236726678</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
@@ -2203,219 +3031,279 @@
         <v>20</v>
       </c>
       <c r="M16" s="1">
-        <v>0.10141832501926373</v>
+        <v>0.039869153090623</v>
       </c>
       <c r="N16" s="1">
-        <v>44.794520547945204</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>100</v>
+        <v>15.662648130367446</v>
+      </c>
+      <c r="O16" s="1">
+        <v>63.29113924050633</v>
       </c>
       <c r="P16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+        <v>30.2515696939809</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>40.63291139240506</v>
+      </c>
+      <c r="R16" s="1">
+        <v>36.64556962025316</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>-6.21</v>
       </c>
-      <c r="C17" s="4">
-        <v>2.73972602739726</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="3">
+        <v>2.5316455696202533</v>
+      </c>
+      <c r="D17" s="3">
         <v>4.355877616747182</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>4.89</v>
       </c>
-      <c r="F17" s="4">
-        <v>-0.05371828874910933</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="F17" s="3">
+        <v>-0.15592483762420115</v>
+      </c>
+      <c r="G17" s="3">
         <v>1.73</v>
       </c>
-      <c r="H17" s="4">
-        <v>49.65</v>
-      </c>
-      <c r="I17" s="4">
-        <v>-5.85</v>
-      </c>
-      <c r="J17" s="4">
-        <v>-0.011094214309485508</v>
-      </c>
-      <c r="K17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="H17" s="3">
+        <v>45.43</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-9.15</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-0.013558713931326748</v>
+      </c>
+      <c r="K17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
         <v>32</v>
       </c>
-      <c r="M17" s="4">
-        <v>0.003098817742575699</v>
-      </c>
-      <c r="N17" s="4">
-        <v>28.767123287671232</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="M17" s="3">
+        <v>-0.07853948802867361</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.8217840184377816</v>
+      </c>
+      <c r="O17" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P17" s="3">
+        <v>28.182703357372183</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>24.55696202531646</v>
+      </c>
+      <c r="R17" s="3">
+        <v>23.164556962025316</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
-        <v>32.87671232876712</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="C18" s="1">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>9.43</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.2104554191405284</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F18" s="1">
+        <v>-0.31769757444430774</v>
+      </c>
+      <c r="G18" s="1">
         <v>1.23</v>
       </c>
-      <c r="H18" s="3">
-        <v>41.95</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-0.74</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.008154478936063782</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="H18" s="1">
+        <v>34.31</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-9.92</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.008678430354633865</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>45</v>
       </c>
-      <c r="M18" s="3">
-        <v>-0.19255413901301122</v>
-      </c>
-      <c r="N18" s="3">
-        <v>53.287671232876704</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="M18" s="1">
+        <v>-0.2933158889553059</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-17.65585607422545</v>
+      </c>
+      <c r="O18" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P18" s="1">
+        <v>30.65938429567125</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>48.22784810126582</v>
+      </c>
+      <c r="R18" s="1">
+        <v>30.949367088607595</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="T18" s="1">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>9.32</v>
       </c>
-      <c r="C19" s="3">
-        <v>75.34246575342466</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.16523605150214582</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="C19" s="1">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.2027896995708155</v>
+      </c>
+      <c r="E19" s="1">
         <v>-0.43</v>
       </c>
-      <c r="F19" s="3">
-        <v>0.0426229368382203</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="F19" s="1">
+        <v>-0.04984014908398787</v>
+      </c>
+      <c r="G19" s="1">
         <v>0.21</v>
       </c>
-      <c r="H19" s="3">
-        <v>68.84</v>
-      </c>
-      <c r="I19" s="3">
-        <v>22.42</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.004775952470250111</v>
-      </c>
-      <c r="K19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
+      <c r="H19" s="1">
+        <v>53.67</v>
+      </c>
+      <c r="I19" s="1">
+        <v>15.22</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.0049513249802427125</v>
+      </c>
+      <c r="K19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
         <v>71</v>
       </c>
-      <c r="M19" s="3">
-        <v>-0.018864068817164847</v>
-      </c>
-      <c r="N19" s="3">
-        <v>57.3972602739726</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="M19" s="1">
+        <v>-0.13358593837229848</v>
+      </c>
+      <c r="N19" s="1">
+        <v>-1.6828610159247124</v>
+      </c>
+      <c r="O19" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P19" s="1">
+        <v>14.335419717590279</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>52.911392405063296</v>
+      </c>
+      <c r="R19" s="1">
+        <v>40.8860759493671</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="3">
         <v>6.07</v>
       </c>
-      <c r="C20" s="1">
-        <v>64.38356164383562</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="C20" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="D20" s="3">
         <v>0.9456342668863262</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="3">
         <v>-2.3</v>
       </c>
-      <c r="F20" s="1">
-        <v>-0.26177705897343784</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="F20" s="3">
+        <v>-0.27936579590574756</v>
+      </c>
+      <c r="G20" s="3">
         <v>1.03</v>
       </c>
-      <c r="H20" s="1">
-        <v>30.71</v>
-      </c>
-      <c r="I20" s="1">
-        <v>-16.69</v>
-      </c>
-      <c r="J20" s="1">
-        <v>-0.010297530077944456</v>
-      </c>
-      <c r="K20" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="H20" s="3">
+        <v>33.21</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-15.87</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-0.01222796653113952</v>
+      </c>
+      <c r="K20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2</v>
       </c>
-      <c r="M20" s="1">
-        <v>-0.25944210939158774</v>
-      </c>
-      <c r="N20" s="1">
-        <v>39.178082191780824</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M20" s="3">
+        <v>-0.276185576059356</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-15.942824784630464</v>
+      </c>
+      <c r="O20" s="3">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P20" s="3">
+        <v>25.74193342123896</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>37.72151898734177</v>
+      </c>
+      <c r="R20" s="3">
+        <v>27.405063291139236</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,7 +3311,7 @@
         <v>1.02</v>
       </c>
       <c r="C21" s="1">
-        <v>39.726027397260275</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="D21" s="1">
         <v>13.990196078431373</v>
@@ -2432,40 +3320,52 @@
         <v>5.19</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.2411038543599589</v>
+        <v>-0.06563929377820135</v>
       </c>
       <c r="G21" s="1">
         <v>1.3</v>
       </c>
       <c r="H21" s="1">
-        <v>66.9</v>
+        <v>75.01</v>
       </c>
       <c r="I21" s="1">
-        <v>15.81</v>
+        <v>31.41</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.018608099112600755</v>
+        <v>-0.00912194805209317</v>
       </c>
       <c r="K21" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.2177543585414582</v>
+        <v>-0.033837095314285914</v>
       </c>
       <c r="N21" s="1">
-        <v>49.726027397260275</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>103</v>
+        <v>8.29202328987655</v>
+      </c>
+      <c r="O21" s="1">
+        <v>53.16455696202531</v>
       </c>
       <c r="P21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>39.63614933355383</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>55.44303797468354</v>
+      </c>
+      <c r="R21" s="1">
+        <v>38.79746835443038</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T21" s="1">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -2473,49 +3373,61 @@
         <v>8.11</v>
       </c>
       <c r="C22" s="1">
-        <v>69.86301369863014</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="D22" s="1">
-        <v>0.6929716399506783</v>
+        <v>0.6954377311960543</v>
       </c>
       <c r="E22" s="1">
         <v>0.16</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.1772264863526779</v>
+        <v>-0.22745346460144902</v>
       </c>
       <c r="G22" s="1">
         <v>1.36</v>
       </c>
       <c r="H22" s="1">
-        <v>49.57</v>
+        <v>46.93</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.58</v>
+        <v>-3.08</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.014086529086350441</v>
+        <v>-0.014743973448483924</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.14920709137047705</v>
+        <v>-0.18929082644475048</v>
       </c>
       <c r="N22" s="1">
-        <v>42.73972602739725</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>93</v>
+        <v>-7.253349823169911</v>
+      </c>
+      <c r="O22" s="1">
+        <v>24.050632911392405</v>
       </c>
       <c r="P22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>20.966620085005058</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>40.75949367088608</v>
+      </c>
+      <c r="R22" s="1">
+        <v>30.253164556962027</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2523,7 +3435,7 @@
         <v>27.51</v>
       </c>
       <c r="C23" s="1">
-        <v>97.26027397260275</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
         <v>-0.7593602326426754</v>
@@ -2532,19 +3444,19 @@
         <v>-0.52</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.18511495942593814</v>
+        <v>-0.19121337686215006</v>
       </c>
       <c r="G23" s="1">
         <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>46.38</v>
+        <v>47.35</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.54</v>
+        <v>-8.12</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.007086198171881758</v>
+        <v>-0.0075053643476327555</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
@@ -2553,19 +3465,31 @@
         <v>29</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.16643536277113757</v>
+        <v>-0.1657716180910177</v>
       </c>
       <c r="N23" s="1">
-        <v>45.61643835616439</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>102</v>
+        <v>-4.901428987796632</v>
+      </c>
+      <c r="O23" s="1">
+        <v>26.582278481012654</v>
       </c>
       <c r="P23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>28.794141696367475</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>45.31645569620253</v>
+      </c>
+      <c r="R23" s="1">
+        <v>31.962025316455694</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T23" s="1">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -2573,7 +3497,7 @@
         <v>-40.16</v>
       </c>
       <c r="C24" s="1">
-        <v>1.36986301369863</v>
+        <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="1">
         <v>-0.3107569721115539</v>
@@ -2582,90 +3506,114 @@
         <v>9.38</v>
       </c>
       <c r="F24" s="1">
-        <v>0.12354297255472929</v>
+        <v>0.15592581430995772</v>
       </c>
       <c r="G24" s="1">
         <v>3.57</v>
       </c>
       <c r="H24" s="1">
-        <v>56.24</v>
+        <v>62.41</v>
       </c>
       <c r="I24" s="1">
-        <v>-19.13</v>
+        <v>-12.59</v>
       </c>
       <c r="J24" s="1">
-        <v>0.03533322298691831</v>
+        <v>0.035040529196603526</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M24" s="1">
-        <v>0.32357032006655184</v>
+        <v>0.42836464781749983</v>
       </c>
       <c r="N24" s="1">
-        <v>30.13698630136986</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>88</v>
+        <v>54.512197603055135</v>
+      </c>
+      <c r="O24" s="1">
+        <v>88.60759493670885</v>
       </c>
       <c r="P24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+        <v>40.33904155950217</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>31.39240506329114</v>
+      </c>
+      <c r="R24" s="1">
+        <v>31.0126582278481</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>-2.28</v>
       </c>
-      <c r="C25" s="4">
-        <v>12.32876712328767</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="C25" s="3">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="D25" s="3">
         <v>0.8859649122807016</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>11.91</v>
       </c>
-      <c r="F25" s="4">
-        <v>-0.41617070166858905</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F25" s="3">
+        <v>-0.3761670267637076</v>
+      </c>
+      <c r="G25" s="3">
         <v>2.23</v>
       </c>
-      <c r="H25" s="4">
-        <v>49.25</v>
-      </c>
-      <c r="I25" s="4">
-        <v>-50.66</v>
-      </c>
-      <c r="J25" s="4">
-        <v>-0.004391759318720075</v>
-      </c>
-      <c r="K25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4">
+      <c r="H25" s="3">
+        <v>50.29</v>
+      </c>
+      <c r="I25" s="3">
+        <v>-49.54</v>
+      </c>
+      <c r="J25" s="3">
+        <v>-0.003975544961099383</v>
+      </c>
+      <c r="K25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
         <v>48</v>
       </c>
-      <c r="M25" s="4">
-        <v>-0.3204377688127362</v>
-      </c>
-      <c r="N25" s="4">
-        <v>28.21917808219178</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="P25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M25" s="3">
+        <v>-0.24577801306165437</v>
+      </c>
+      <c r="N25" s="3">
+        <v>-12.902068484860301</v>
+      </c>
+      <c r="O25" s="3">
+        <v>16.455696202531644</v>
+      </c>
+      <c r="P25" s="3">
+        <v>55.620154465672535</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>28.101265822784814</v>
+      </c>
+      <c r="R25" s="3">
+        <v>11.962025316455694</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T25" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -2673,7 +3621,7 @@
         <v>-0.17</v>
       </c>
       <c r="C26" s="1">
-        <v>26.027397260273972</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="D26" s="1">
         <v>-2571.7647058823527</v>
@@ -2682,490 +3630,610 @@
         <v>4.67</v>
       </c>
       <c r="F26" s="1">
-        <v>0.39523858859064376</v>
+        <v>0.4878708588671728</v>
       </c>
       <c r="G26" s="1">
         <v>3.06</v>
       </c>
       <c r="H26" s="1">
-        <v>67.45</v>
+        <v>69.42</v>
       </c>
       <c r="I26" s="1">
-        <v>17.99</v>
+        <v>21.77</v>
       </c>
       <c r="J26" s="1">
-        <v>0.04177717695071901</v>
+        <v>0.044615350892172945</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="M26" s="1">
-        <v>0.5555717932110151</v>
+        <v>0.7062459549860587</v>
       </c>
       <c r="N26" s="1">
-        <v>41.64383561643836</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>95</v>
+        <v>82.300328319911</v>
+      </c>
+      <c r="O26" s="1">
+        <v>91.13924050632912</v>
       </c>
       <c r="P26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+        <v>50.63126652197354</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>41.01265822784811</v>
+      </c>
+      <c r="R26" s="1">
+        <v>33.037974683544306</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="3">
         <v>-1.13</v>
       </c>
-      <c r="C27" s="1">
-        <v>15.068493150684931</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C27" s="3">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="D27" s="3">
         <v>1.0176991150442478</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="3">
         <v>1.65</v>
       </c>
-      <c r="F27" s="1">
-        <v>-0.12039774153805113</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="F27" s="3">
+        <v>-0.20457969183921387</v>
+      </c>
+      <c r="G27" s="3">
         <v>2.63</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="3">
+        <v>60.75</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-18.72</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0.00800169742756051</v>
+      </c>
+      <c r="K27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>37</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-0.03178774685194008</v>
+      </c>
+      <c r="N27" s="3">
+        <v>8.496958136111138</v>
+      </c>
+      <c r="O27" s="3">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="P27" s="3">
+        <v>51.28834092723359</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>36.58227848101266</v>
+      </c>
+      <c r="R27" s="3">
+        <v>26.392405063291136</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.536363636363636</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-0.68</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-0.3879769225383227</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="H28" s="3">
+        <v>59.66</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-20.69</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-0.010456960261449664</v>
+      </c>
+      <c r="K28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>28</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-0.1611212401623927</v>
+      </c>
+      <c r="N28" s="3">
+        <v>-4.436391194934127</v>
+      </c>
+      <c r="O28" s="3">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="P28" s="3">
+        <v>45.17203183430412</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>34.68354430379746</v>
+      </c>
+      <c r="R28" s="3">
+        <v>21.898734177215193</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T28" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="C29" s="3">
+        <v>34.177215189873415</v>
+      </c>
+      <c r="D29" s="3">
+        <v>77.04545454545456</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-0.4139591068760087</v>
+      </c>
+      <c r="G29" s="3">
+        <v>2.11</v>
+      </c>
+      <c r="H29" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-32.51</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-0.015534149204213981</v>
+      </c>
+      <c r="K29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>-12</v>
+      </c>
+      <c r="M29" s="3">
+        <v>-0.29629097255952164</v>
+      </c>
+      <c r="N29" s="3">
+        <v>-17.953364434647018</v>
+      </c>
+      <c r="O29" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P29" s="3">
+        <v>48.25819923754261</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>41.13924050632911</v>
+      </c>
+      <c r="R29" s="3">
+        <v>24.36708860759493</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.95</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1656.8153846153846</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2.13</v>
+      </c>
+      <c r="F30" s="1">
+        <v>-0.17095955682866515</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="H30" s="1">
+        <v>54.01</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5.44</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.004296700252854999</v>
+      </c>
+      <c r="K30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>39</v>
+      </c>
+      <c r="M30" s="1">
+        <v>-0.14869801790392434</v>
+      </c>
+      <c r="N30" s="1">
+        <v>-3.1940689690872945</v>
+      </c>
+      <c r="O30" s="1">
+        <v>34.177215189873415</v>
+      </c>
+      <c r="P30" s="1">
+        <v>24.961328061128594</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>64.9367088607595</v>
+      </c>
+      <c r="R30" s="1">
+        <v>47.53164556962025</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T30" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="C31" s="2">
+        <v>59.49367088607595</v>
+      </c>
+      <c r="D31" s="2">
+        <v>10.688109161793372</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.14893465812358012</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1.43</v>
+      </c>
+      <c r="H31" s="2">
         <v>64.78</v>
       </c>
-      <c r="I27" s="1">
-        <v>-16.38</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0.006609947032577026</v>
-      </c>
-      <c r="K27" s="1" t="b">
+      <c r="I31" s="2">
+        <v>25.69</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.030128371718951562</v>
+      </c>
+      <c r="K31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>176</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0.19451780925519224</v>
+      </c>
+      <c r="N31" s="2">
+        <v>31.12751374682437</v>
+      </c>
+      <c r="O31" s="2">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P31" s="2">
+        <v>17.25839209766727</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="R31" s="2">
+        <v>60.822784810126585</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C32" s="3">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.178082191780822</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-0.13320749908480836</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1.61</v>
+      </c>
+      <c r="H32" s="3">
+        <v>43.93</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-4.28</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-0.006102937885637886</v>
+      </c>
+      <c r="K32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>26</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-0.06854302887484698</v>
+      </c>
+      <c r="N32" s="3">
+        <v>4.821429933820452</v>
+      </c>
+      <c r="O32" s="3">
+        <v>49.36708860759494</v>
+      </c>
+      <c r="P32" s="3">
+        <v>38.84187494148391</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>36.32911392405064</v>
+      </c>
+      <c r="R32" s="3">
+        <v>29.36708860759494</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>16.79</v>
+      </c>
+      <c r="C33" s="1">
+        <v>88.60759493670885</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-0.05777248362120303</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="F33" s="1">
+        <v>-0.10754673419165842</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1.09</v>
+      </c>
+      <c r="H33" s="1">
+        <v>50.21</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-11.71</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.0024125422671207788</v>
+      </c>
+      <c r="K33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>84</v>
+      </c>
+      <c r="M33" s="1">
+        <v>-0.09800607465248379</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.8751253560567682</v>
+      </c>
+      <c r="O33" s="1">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="P33" s="1">
+        <v>26.894390179645494</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>49.62025316455696</v>
+      </c>
+      <c r="R33" s="1">
+        <v>39.9367088607595</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T33" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>13.11</v>
+      </c>
+      <c r="C34" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-0.6453089244851258</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.58</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.15231508251016168</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1.26</v>
+      </c>
+      <c r="H34" s="2">
+        <v>75.21</v>
+      </c>
+      <c r="I34" s="2">
+        <v>38.55</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.02781949782545467</v>
+      </c>
+      <c r="K34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2">
+        <v>151</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.17987698784555506</v>
+      </c>
+      <c r="N34" s="2">
+        <v>29.66343160586064</v>
+      </c>
+      <c r="O34" s="2">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="P34" s="2">
+        <v>20.42247430615109</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>61.39240506329114</v>
+      </c>
+      <c r="R34" s="2">
+        <v>51.139240506329116</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T34" s="2">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>17.37</v>
+      </c>
+      <c r="C35" s="3">
+        <v>91.13924050632912</v>
+      </c>
+      <c r="D35" s="3">
+        <v>-0.47898675877950486</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-0.96</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-0.3181429691881079</v>
+      </c>
+      <c r="G35" s="3">
         <v>1</v>
       </c>
-      <c r="L27" s="1">
-        <v>39</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0.0064678524091359435</v>
-      </c>
-      <c r="N27" s="1">
-        <v>39.178082191780824</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <v>-1.1</v>
-      </c>
-      <c r="C28" s="1">
-        <v>16.43835616438356</v>
-      </c>
-      <c r="D28" s="1">
-        <v>7.536363636363636</v>
-      </c>
-      <c r="E28" s="1">
-        <v>-0.68</v>
-      </c>
-      <c r="F28" s="1">
-        <v>-0.31970377447527576</v>
-      </c>
-      <c r="G28" s="1">
-        <v>3.14</v>
-      </c>
-      <c r="H28" s="1">
-        <v>60.92</v>
-      </c>
-      <c r="I28" s="1">
-        <v>-20.32</v>
-      </c>
-      <c r="J28" s="1">
-        <v>-0.012172220584618951</v>
-      </c>
-      <c r="K28" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <v>29</v>
-      </c>
-      <c r="M28" s="1">
-        <v>-0.15314403763663753</v>
-      </c>
-      <c r="N28" s="1">
-        <v>35.06849315068493</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="C29" s="1">
-        <v>34.24657534246575</v>
-      </c>
-      <c r="D29" s="1">
-        <v>77.04545454545456</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="F29" s="1">
-        <v>-0.42996257372803337</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2.11</v>
-      </c>
-      <c r="H29" s="1">
-        <v>37.19</v>
-      </c>
-      <c r="I29" s="1">
-        <v>-34.98</v>
-      </c>
-      <c r="J29" s="1">
-        <v>-0.015962598634841656</v>
-      </c>
-      <c r="K29" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>-4</v>
-      </c>
-      <c r="M29" s="1">
-        <v>-0.34356943919958083</v>
-      </c>
-      <c r="N29" s="1">
-        <v>40.54794520547945</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="C30" s="3">
-        <v>45.20547945205479</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1656.8153846153846</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2.13</v>
-      </c>
-      <c r="F30" s="3">
-        <v>-0.08655665746831766</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1.21</v>
-      </c>
-      <c r="H30" s="3">
-        <v>64.3</v>
-      </c>
-      <c r="I30" s="3">
-        <v>9.52</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0.003953742187912844</v>
-      </c>
-      <c r="K30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="3">
-        <v>46</v>
-      </c>
-      <c r="M30" s="3">
-        <v>-0.07021201039536717</v>
-      </c>
-      <c r="N30" s="3">
-        <v>67.67123287671232</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3">
-        <v>5.13</v>
-      </c>
-      <c r="C31" s="3">
-        <v>57.534246575342465</v>
-      </c>
-      <c r="D31" s="3">
-        <v>10.491228070175438</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.09393275512484683</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1.43</v>
-      </c>
-      <c r="H31" s="3">
-        <v>58.34</v>
-      </c>
-      <c r="I31" s="3">
-        <v>20.63</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0.02821015310502491</v>
-      </c>
-      <c r="K31" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
-        <v>237</v>
-      </c>
-      <c r="M31" s="3">
-        <v>0.12740036579803116</v>
-      </c>
-      <c r="N31" s="3">
-        <v>68.21917808219179</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1">
-        <v>-2.92</v>
-      </c>
-      <c r="C32" s="1">
-        <v>10.95890410958904</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8.178082191780822</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="F32" s="1">
-        <v>-0.16925677684924556</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="H32" s="1">
-        <v>38.88</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-6.87</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.007147597187803493</v>
-      </c>
-      <c r="K32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1">
-        <v>26</v>
-      </c>
-      <c r="M32" s="1">
-        <v>-0.12177946868496081</v>
-      </c>
-      <c r="N32" s="1">
-        <v>36.02739726027397</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3">
-        <v>16.79</v>
-      </c>
-      <c r="C33" s="3">
-        <v>87.67123287671232</v>
-      </c>
-      <c r="D33" s="3">
-        <v>-0.05777248362120303</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0.37</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-0.09350920506704644</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1.09</v>
-      </c>
-      <c r="H33" s="3">
-        <v>47.34</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-12.69</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.003219819799583533</v>
-      </c>
-      <c r="K33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>84</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-0.08650435632149622</v>
-      </c>
-      <c r="N33" s="3">
-        <v>50.41095890410959</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3">
-        <v>13.11</v>
-      </c>
-      <c r="C34" s="3">
-        <v>83.56164383561644</v>
-      </c>
-      <c r="D34" s="3">
-        <v>-0.6453089244851258</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0.58</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.18594673738751583</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1.26</v>
-      </c>
-      <c r="H34" s="3">
-        <v>75.58</v>
-      </c>
-      <c r="I34" s="3">
-        <v>39.18</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0.027190257492783167</v>
-      </c>
-      <c r="K34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
-        <v>151</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0.2061829670968831</v>
-      </c>
-      <c r="N34" s="3">
-        <v>62.054794520547944</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <v>17.37</v>
-      </c>
-      <c r="C35" s="1">
-        <v>90.41095890410958</v>
-      </c>
-      <c r="D35" s="1">
-        <v>-0.48244099021301096</v>
-      </c>
-      <c r="E35" s="1">
-        <v>-0.96</v>
-      </c>
-      <c r="F35" s="1">
-        <v>-0.28524829078477276</v>
-      </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
-        <v>28.14</v>
-      </c>
-      <c r="I35" s="1">
-        <v>-24.3</v>
-      </c>
-      <c r="J35" s="1">
-        <v>-0.02296186682611087</v>
-      </c>
-      <c r="K35" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>45</v>
-      </c>
-      <c r="M35" s="1">
-        <v>-0.28524829078477276</v>
-      </c>
-      <c r="N35" s="1">
-        <v>33.28767123287671</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H35" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-25.05</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-0.024684340384122497</v>
+      </c>
+      <c r="K35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>44</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-0.3181429691881079</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-20.138564097505654</v>
+      </c>
+      <c r="O35" s="3">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="P35" s="3">
+        <v>30.4559601123391</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>32.911392405063296</v>
+      </c>
+      <c r="R35" s="3">
+        <v>21.582278481012658</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -3173,7 +4241,7 @@
         <v>11.51</v>
       </c>
       <c r="C36" s="1">
-        <v>80.82191780821918</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="D36" s="1">
         <v>0.38488271068635965</v>
@@ -3182,19 +4250,19 @@
         <v>-0.97</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.10500106605254855</v>
+        <v>-0.13120568027183452</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>37.87</v>
+        <v>38.9</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.8</v>
+        <v>-15.19</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.009795192494873697</v>
+        <v>-0.011964198390205084</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
@@ -3203,19 +4271,31 @@
         <v>-19</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.09566126772514827</v>
+        <v>-0.11848480088626834</v>
       </c>
       <c r="N36" s="1">
-        <v>42.6027397260274</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>100</v>
+        <v>-0.17274726732169896</v>
+      </c>
+      <c r="O36" s="1">
+        <v>40.50632911392405</v>
       </c>
       <c r="P36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>32.54334537649318</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>39.99999999999999</v>
+      </c>
+      <c r="R36" s="1">
+        <v>34.30379746835443</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T36" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -3223,7 +4303,7 @@
         <v>5.33</v>
       </c>
       <c r="C37" s="1">
-        <v>61.64383561643836</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="D37" s="1">
         <v>0.598499061913696</v>
@@ -3232,140 +4312,176 @@
         <v>0.52</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.0002634502732824784</v>
+        <v>-0.0008221176373724437</v>
       </c>
       <c r="G37" s="1">
         <v>1.38</v>
       </c>
       <c r="H37" s="1">
-        <v>38.15</v>
+        <v>38.49</v>
       </c>
       <c r="I37" s="1">
-        <v>-22.14</v>
+        <v>-21.87</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.0015935583132703091</v>
+        <v>-0.0017925280106526717</v>
       </c>
       <c r="K37" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1">
         <v>-134</v>
       </c>
       <c r="M37" s="1">
-        <v>0.02931257776348506</v>
+        <v>0.039460667083587087</v>
       </c>
       <c r="N37" s="1">
-        <v>40.95890410958904</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>88</v>
+        <v>15.621799529663857</v>
+      </c>
+      <c r="O37" s="1">
+        <v>62.0253164556962</v>
       </c>
       <c r="P37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+        <v>36.27914452259746</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>39.11392405063292</v>
+      </c>
+      <c r="R37" s="1">
+        <v>38.797468354430386</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>-0.74</v>
       </c>
-      <c r="C38" s="3">
-        <v>17.80821917808219</v>
-      </c>
-      <c r="D38" s="3">
+      <c r="C38" s="2">
+        <v>16.455696202531644</v>
+      </c>
+      <c r="D38" s="2">
         <v>36.648648648648646</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>-0.1</v>
       </c>
-      <c r="F38" s="3">
-        <v>0.2565848720671759</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="F38" s="2">
+        <v>0.27827678266224054</v>
+      </c>
+      <c r="G38" s="2">
         <v>1.1</v>
       </c>
-      <c r="H38" s="3">
-        <v>79.02</v>
-      </c>
-      <c r="I38" s="3">
-        <v>22.5</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0.0377154227246231</v>
-      </c>
-      <c r="K38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3">
+      <c r="H38" s="2">
+        <v>81.02</v>
+      </c>
+      <c r="I38" s="2">
+        <v>26.02</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.038804206935551595</v>
+      </c>
+      <c r="K38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
         <v>-13</v>
       </c>
-      <c r="M38" s="3">
-        <v>0.26436803734000947</v>
-      </c>
-      <c r="N38" s="3">
-        <v>65.75342465753424</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="M38" s="2">
+        <v>0.2888775154835457</v>
+      </c>
+      <c r="N38" s="2">
+        <v>40.56348436965971</v>
+      </c>
+      <c r="O38" s="2">
+        <v>86.07594936708861</v>
+      </c>
+      <c r="P38" s="2">
+        <v>28.305323956526895</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>64.55696202531647</v>
+      </c>
+      <c r="R38" s="2">
+        <v>53.92405063291139</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="2">
         <v>-0.18</v>
       </c>
-      <c r="C39" s="3">
-        <v>24.65753424657534</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="2">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="D39" s="2">
         <v>100</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>-7.97</v>
       </c>
-      <c r="F39" s="3">
-        <v>0.09896104967906434</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="F39" s="2">
+        <v>0.09070062691011735</v>
+      </c>
+      <c r="G39" s="2">
         <v>1.3</v>
       </c>
-      <c r="H39" s="3">
-        <v>51.5</v>
-      </c>
-      <c r="I39" s="3">
-        <v>9.19</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0.022209839983126898</v>
-      </c>
-      <c r="K39" s="3" t="b">
+      <c r="H39" s="2">
+        <v>51.1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>9.01</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.01990433112361712</v>
+      </c>
+      <c r="K39" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="2">
         <v>-14</v>
       </c>
-      <c r="M39" s="3">
-        <v>0.12231054549756504</v>
-      </c>
-      <c r="N39" s="3">
-        <v>60</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M39" s="2">
+        <v>0.12250282537403279</v>
+      </c>
+      <c r="N39" s="2">
+        <v>23.92601535870843</v>
+      </c>
+      <c r="O39" s="2">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="P39" s="2">
+        <v>18.299999237060547</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>57.46835443037974</v>
+      </c>
+      <c r="R39" s="2">
+        <v>53.41772151898734</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -3373,7 +4489,7 @@
         <v>-4.08</v>
       </c>
       <c r="C40" s="1">
-        <v>5.47945205479452</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="D40" s="1">
         <v>16.730392156862745</v>
@@ -3382,40 +4498,52 @@
         <v>12.27</v>
       </c>
       <c r="F40" s="1">
-        <v>0.3007306296715609</v>
+        <v>0.2721261109960245</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>52.62</v>
+        <v>49.27</v>
       </c>
       <c r="I40" s="1">
-        <v>-7.6</v>
+        <v>-10.63</v>
       </c>
       <c r="J40" s="1">
-        <v>0.026083250500902558</v>
+        <v>0.02361688973368183</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1">
         <v>39</v>
       </c>
       <c r="M40" s="1">
-        <v>0.22289897694322525</v>
+        <v>0.1661187827829731</v>
       </c>
       <c r="N40" s="1">
-        <v>48.76712328767123</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>107</v>
+        <v>28.28761109960246</v>
+      </c>
+      <c r="O40" s="1">
+        <v>74.68354430379746</v>
       </c>
       <c r="P40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>45.29877115964868</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>45.18987341772152</v>
+      </c>
+      <c r="R40" s="1">
+        <v>40.75949367088608</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T40" s="1">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -3423,7 +4551,7 @@
         <v>-5.03</v>
       </c>
       <c r="C41" s="1">
-        <v>4.10958904109589</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="D41" s="1">
         <v>7.34990059642147</v>
@@ -3432,19 +4560,19 @@
         <v>-1.75</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.0036852313264936487</v>
+        <v>-0.012992593659218676</v>
       </c>
       <c r="G41" s="1">
         <v>1.11</v>
       </c>
       <c r="H41" s="1">
-        <v>77.84</v>
+        <v>76.88</v>
       </c>
       <c r="I41" s="1">
-        <v>-5.77</v>
+        <v>-5.99</v>
       </c>
       <c r="J41" s="1">
-        <v>0.011545940693400493</v>
+        <v>0.016911260218543354</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -3453,19 +4581,31 @@
         <v>5</v>
       </c>
       <c r="M41" s="1">
-        <v>0.004876250473623278</v>
+        <v>-0.001331787555783004</v>
       </c>
       <c r="N41" s="1">
-        <v>45.89041095890411</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>99</v>
+        <v>11.542554065726831</v>
+      </c>
+      <c r="O41" s="1">
+        <v>56.9620253164557</v>
       </c>
       <c r="P41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46.4052282234621</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>44.30379746835443</v>
+      </c>
+      <c r="R41" s="1">
+        <v>30.063291139240505</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -3473,7 +4613,7 @@
         <v>3.61</v>
       </c>
       <c r="C42" s="1">
-        <v>50.68493150684932</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="D42" s="1">
         <v>1.0831024930747921</v>
@@ -3482,19 +4622,19 @@
         <v>-0.1</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.06171624363361932</v>
+        <v>-0.07152608902469655</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>35.56</v>
+        <v>37.51</v>
       </c>
       <c r="I42" s="1">
-        <v>-1.09</v>
+        <v>-0.72</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.005639504742872616</v>
+        <v>-0.006280195480516437</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -3503,319 +4643,403 @@
         <v>34</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.11152850137975412</v>
+        <v>-0.13937077908104945</v>
       </c>
       <c r="N42" s="1">
-        <v>42.19178082191781</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>103</v>
+        <v>-2.2613450867998</v>
+      </c>
+      <c r="O42" s="1">
+        <v>36.708860759493675</v>
       </c>
       <c r="P42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+        <v>9.169379043273572</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>42.15189873417721</v>
+      </c>
+      <c r="R42" s="1">
+        <v>38.54430379746835</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="1">
         <v>-0.02</v>
       </c>
-      <c r="C43" s="3">
-        <v>30.136986301369863</v>
-      </c>
-      <c r="D43" s="3">
+      <c r="C43" s="1">
+        <v>27.848101265822784</v>
+      </c>
+      <c r="D43" s="1">
         <v>1214</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="1">
         <v>5.23</v>
       </c>
-      <c r="F43" s="3">
-        <v>-0.11788447075728632</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F43" s="1">
+        <v>-0.10300963463207322</v>
+      </c>
+      <c r="G43" s="1">
         <v>1.27</v>
       </c>
-      <c r="H43" s="3">
-        <v>40.05</v>
-      </c>
-      <c r="I43" s="3">
-        <v>-19.91</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0.000778454819904717</v>
-      </c>
-      <c r="K43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="H43" s="1">
+        <v>42.05</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-18.73</v>
+      </c>
+      <c r="J43" s="1">
+        <v>-0.0015476646793928285</v>
+      </c>
+      <c r="K43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
         <v>6</v>
       </c>
-      <c r="M43" s="3">
-        <v>-0.0968699245206357</v>
-      </c>
-      <c r="N43" s="3">
-        <v>52.73972602739725</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="M43" s="1">
+        <v>-0.07438765601454933</v>
+      </c>
+      <c r="N43" s="1">
+        <v>4.236967219850214</v>
+      </c>
+      <c r="O43" s="1">
+        <v>48.10126582278481</v>
+      </c>
+      <c r="P43" s="1">
+        <v>38.87068031431492</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>49.87341772151898</v>
+      </c>
+      <c r="R43" s="1">
+        <v>42.151898734177216</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T43" s="1">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="3">
         <v>1.02</v>
       </c>
-      <c r="C44" s="1">
-        <v>39.726027397260275</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="C44" s="3">
+        <v>41.77215189873418</v>
+      </c>
+      <c r="D44" s="3">
         <v>26.862745098039216</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="3">
         <v>-1.51</v>
       </c>
-      <c r="F44" s="1">
-        <v>-0.4086948409687774</v>
-      </c>
-      <c r="G44" s="1">
+      <c r="F44" s="3">
+        <v>-0.4179675723306637</v>
+      </c>
+      <c r="G44" s="3">
         <v>2.59</v>
       </c>
-      <c r="H44" s="1">
-        <v>31.13</v>
-      </c>
-      <c r="I44" s="1">
-        <v>-32.48</v>
-      </c>
-      <c r="J44" s="1">
-        <v>-0.014441649997011271</v>
-      </c>
-      <c r="K44" s="1" t="b">
+      <c r="H44" s="3">
+        <v>32.04</v>
+      </c>
+      <c r="I44" s="3">
+        <v>-31.9</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-0.018572838403102806</v>
+      </c>
+      <c r="K44" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L44" s="3">
         <v>-18</v>
       </c>
-      <c r="M44" s="1">
-        <v>-0.2849425131307237</v>
-      </c>
-      <c r="N44" s="1">
-        <v>39.178082191780824</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="M44" s="3">
+        <v>-0.24941592047191197</v>
+      </c>
+      <c r="N44" s="3">
+        <v>-13.265859225886054</v>
+      </c>
+      <c r="O44" s="3">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="P44" s="3">
+        <v>44.155007607957295</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>38.60759493670886</v>
+      </c>
+      <c r="R44" s="3">
+        <v>26.518987341772146</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="2">
         <v>8.37</v>
       </c>
-      <c r="C45" s="3">
-        <v>72.6027397260274</v>
-      </c>
-      <c r="D45" s="3">
+      <c r="C45" s="2">
+        <v>73.41772151898735</v>
+      </c>
+      <c r="D45" s="2">
         <v>0.818399044205496</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="2">
         <v>0.94</v>
       </c>
-      <c r="F45" s="3">
-        <v>0.19926338824723241</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="F45" s="2">
+        <v>0.1791686078688256</v>
+      </c>
+      <c r="G45" s="2">
         <v>1.46</v>
       </c>
-      <c r="H45" s="3">
-        <v>67.29</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17.93</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0.026503299137149217</v>
-      </c>
-      <c r="K45" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="H45" s="2">
+        <v>65.55</v>
+      </c>
+      <c r="I45" s="2">
+        <v>17.34</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.025585314395313728</v>
+      </c>
+      <c r="K45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2">
         <v>162</v>
       </c>
-      <c r="M45" s="3">
-        <v>0.2350659485022668</v>
-      </c>
-      <c r="N45" s="3">
-        <v>64.24657534246575</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="M45" s="2">
+        <v>0.22793197884682925</v>
+      </c>
+      <c r="N45" s="2">
+        <v>34.468930705988065</v>
+      </c>
+      <c r="O45" s="2">
+        <v>82.27848101265823</v>
+      </c>
+      <c r="P45" s="2">
+        <v>19.641850851970627</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>62.27848101265823</v>
+      </c>
+      <c r="R45" s="2">
+        <v>56.962025316455694</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="1">
         <v>-0.3</v>
       </c>
-      <c r="C46" s="3">
-        <v>23.28767123287671</v>
-      </c>
-      <c r="D46" s="3">
+      <c r="C46" s="1">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="D46" s="1">
         <v>543.5000000000001</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="1">
         <v>-0.94</v>
       </c>
-      <c r="F46" s="3">
-        <v>-0.2297895477228808</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="F46" s="1">
+        <v>-0.25626706372444663</v>
+      </c>
+      <c r="G46" s="1">
         <v>1.51</v>
       </c>
-      <c r="H46" s="3">
-        <v>47.16</v>
-      </c>
-      <c r="I46" s="3">
-        <v>15.5</v>
-      </c>
-      <c r="J46" s="3">
-        <v>-0.0031429740706628317</v>
-      </c>
-      <c r="K46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="H46" s="1">
+        <v>44.66</v>
+      </c>
+      <c r="I46" s="1">
+        <v>11.33</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.0062409394148189405</v>
+      </c>
+      <c r="K46" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
         <v>34</v>
       </c>
-      <c r="M46" s="3">
-        <v>-0.19009540483142962</v>
-      </c>
-      <c r="N46" s="3">
-        <v>54.38356164383562</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="M46" s="1">
+        <v>-0.2022033263357904</v>
+      </c>
+      <c r="N46" s="1">
+        <v>-8.544599812273905</v>
+      </c>
+      <c r="O46" s="1">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="P46" s="1">
+        <v>40.6204924523832</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>51.139240506329116</v>
+      </c>
+      <c r="R46" s="1">
+        <v>31.39240506329114</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T46" s="1">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="3">
         <v>10.62</v>
       </c>
-      <c r="C47" s="1">
-        <v>79.45205479452055</v>
-      </c>
-      <c r="D47" s="1">
+      <c r="C47" s="3">
+        <v>81.0126582278481</v>
+      </c>
+      <c r="D47" s="3">
         <v>0.8549905838041432</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="3">
         <v>-4.11</v>
       </c>
-      <c r="F47" s="1">
-        <v>-0.3826233814282752</v>
-      </c>
-      <c r="G47" s="1">
+      <c r="F47" s="3">
+        <v>-0.4152563242428725</v>
+      </c>
+      <c r="G47" s="3">
         <v>1.47</v>
       </c>
-      <c r="H47" s="1">
-        <v>29.61</v>
-      </c>
-      <c r="I47" s="1">
-        <v>-18.46</v>
-      </c>
-      <c r="J47" s="1">
-        <v>-0.029377374403905726</v>
-      </c>
-      <c r="K47" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="H47" s="3">
+        <v>29.08</v>
+      </c>
+      <c r="I47" s="3">
+        <v>-19.09</v>
+      </c>
+      <c r="J47" s="3">
+        <v>-0.029842556362938727</v>
+      </c>
+      <c r="K47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>17</v>
       </c>
-      <c r="M47" s="1">
-        <v>-0.3460425046459574</v>
-      </c>
-      <c r="N47" s="1">
-        <v>38.630136986301366</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="M47" s="3">
+        <v>-0.3654328799827383</v>
+      </c>
+      <c r="N47" s="3">
+        <v>-24.867555176968693</v>
+      </c>
+      <c r="O47" s="3">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="P47" s="3">
+        <v>29.26623910493363</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>38.607594936708864</v>
+      </c>
+      <c r="R47" s="3">
+        <v>25.759493670886073</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T47" s="3">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="2">
         <v>3.98</v>
       </c>
-      <c r="C48" s="3">
-        <v>52.054794520547944</v>
-      </c>
-      <c r="D48" s="3">
+      <c r="C48" s="2">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="D48" s="2">
         <v>7.505025125628141</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>-1.16</v>
       </c>
-      <c r="F48" s="3">
-        <v>0.3146369702297377</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48" s="2">
+        <v>0.3550663954606283</v>
+      </c>
+      <c r="G48" s="2">
         <v>2.1</v>
       </c>
-      <c r="H48" s="3">
-        <v>70.58</v>
-      </c>
-      <c r="I48" s="3">
-        <v>84.25</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0.035975479556466974</v>
-      </c>
-      <c r="K48" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="H48" s="2">
+        <v>71.5</v>
+      </c>
+      <c r="I48" s="2">
+        <v>85.05</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0.039067879528610155</v>
+      </c>
+      <c r="K48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2">
         <v>285</v>
       </c>
-      <c r="M48" s="3">
-        <v>0.4002517882309069</v>
-      </c>
-      <c r="N48" s="3">
-        <v>69.45205479452055</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M48" s="2">
+        <v>0.47167445649498485</v>
+      </c>
+      <c r="N48" s="2">
+        <v>58.84317847080362</v>
+      </c>
+      <c r="O48" s="2">
+        <v>89.87341772151899</v>
+      </c>
+      <c r="P48" s="2">
+        <v>15.18684888660459</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>69.87341772151898</v>
+      </c>
+      <c r="R48" s="2">
+        <v>63.037974683544306</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
@@ -3823,7 +5047,7 @@
         <v>-0.06</v>
       </c>
       <c r="C49" s="2">
-        <v>28.767123287671232</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="D49" s="2">
         <v>1710.0000000000002</v>
@@ -3832,19 +5056,19 @@
         <v>2.02</v>
       </c>
       <c r="F49" s="2">
-        <v>0.5564190128886244</v>
+        <v>0.7888246191322793</v>
       </c>
       <c r="G49" s="2">
         <v>3.8</v>
       </c>
       <c r="H49" s="2">
-        <v>67.15</v>
+        <v>70.19</v>
       </c>
       <c r="I49" s="2">
-        <v>132.83</v>
+        <v>141.75</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06063028435871016</v>
+        <v>0.06629949146826043</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -3853,269 +5077,341 @@
         <v>246</v>
       </c>
       <c r="M49" s="2">
-        <v>0.7743476405279641</v>
+        <v>1.0856451381288232</v>
       </c>
       <c r="N49" s="2">
-        <v>74.10958904109589</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>103</v>
+        <v>120.24024663418746</v>
+      </c>
+      <c r="O49" s="2">
+        <v>97.46835443037975</v>
       </c>
       <c r="P49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+        <v>31.61869931071345</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>74.55696202531647</v>
+      </c>
+      <c r="R49" s="2">
+        <v>63.544303797468345</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T49" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="3">
         <v>-0.13</v>
       </c>
-      <c r="C50" s="1">
-        <v>27.397260273972602</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="C50" s="3">
+        <v>25.31645569620253</v>
+      </c>
+      <c r="D50" s="3">
         <v>385.61538461538464</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="3">
         <v>2.75</v>
       </c>
-      <c r="F50" s="1">
-        <v>-0.4919013894666925</v>
-      </c>
-      <c r="G50" s="1">
+      <c r="F50" s="3">
+        <v>-0.436916409525831</v>
+      </c>
+      <c r="G50" s="3">
         <v>1.53</v>
       </c>
-      <c r="H50" s="1">
-        <v>30.6</v>
-      </c>
-      <c r="I50" s="1">
-        <v>-28.75</v>
-      </c>
-      <c r="J50" s="1">
-        <v>-0.028664922179145992</v>
-      </c>
-      <c r="K50" s="1" t="b">
+      <c r="H50" s="3">
+        <v>39.39</v>
+      </c>
+      <c r="I50" s="3">
+        <v>-23.32</v>
+      </c>
+      <c r="J50" s="3">
+        <v>-0.030364906654603615</v>
+      </c>
+      <c r="K50" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50" s="3">
         <v>7</v>
       </c>
-      <c r="M50" s="1">
-        <v>-0.4506506135206746</v>
-      </c>
-      <c r="N50" s="1">
-        <v>38.35616438356164</v>
-      </c>
-      <c r="O50" s="1" t="s">
+      <c r="M50" s="3">
+        <v>-0.3807325255729137</v>
+      </c>
+      <c r="N50" s="3">
+        <v>-26.397519735986226</v>
+      </c>
+      <c r="O50" s="3">
+        <v>2.5316455696202533</v>
+      </c>
+      <c r="P50" s="3">
+        <v>47.64150593279924</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>39.24050632911393</v>
+      </c>
+      <c r="R50" s="3">
+        <v>21.77215189873418</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3">
+        <v>-3.88</v>
+      </c>
+      <c r="C51" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="D51" s="3">
+        <v>-6.131443298969073</v>
+      </c>
+      <c r="E51" s="3">
+        <v>17.05</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.06505664660412691</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2.37</v>
+      </c>
+      <c r="H51" s="3">
+        <v>56.45</v>
+      </c>
+      <c r="I51" s="3">
+        <v>34.3</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0.03187932043656487</v>
+      </c>
+      <c r="K51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
         <v>95</v>
       </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <v>-2.92</v>
-      </c>
-      <c r="C51" s="1">
-        <v>10.95890410958904</v>
-      </c>
-      <c r="D51" s="1">
-        <v>-9.537671232876713</v>
-      </c>
-      <c r="E51" s="1">
-        <v>17.05</v>
-      </c>
-      <c r="F51" s="1">
-        <v>-0.02754911794085696</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2.37</v>
-      </c>
-      <c r="H51" s="1">
-        <v>57.35</v>
-      </c>
-      <c r="I51" s="1">
-        <v>36.04</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0.03197237848976752</v>
-      </c>
-      <c r="K51" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>95</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0.07908024629696286</v>
-      </c>
-      <c r="N51" s="1">
-        <v>36.16438356164384</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="M51" s="3">
+        <v>0.21028668625600733</v>
+      </c>
+      <c r="N51" s="3">
+        <v>32.704401446905884</v>
+      </c>
+      <c r="O51" s="3">
+        <v>81.0126582278481</v>
+      </c>
+      <c r="P51" s="3">
+        <v>46.744012320672994</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>33.67088607594937</v>
+      </c>
+      <c r="R51" s="3">
+        <v>26.64556962025317</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="2">
         <v>5.3</v>
       </c>
-      <c r="C52" s="3">
-        <v>60.273972602739725</v>
-      </c>
-      <c r="D52" s="3">
+      <c r="C52" s="2">
+        <v>62.0253164556962</v>
+      </c>
+      <c r="D52" s="2">
         <v>6.496226415094339</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="2">
         <v>0.22</v>
       </c>
-      <c r="F52" s="3">
-        <v>0.10336795887267708</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="F52" s="2">
+        <v>0.09175586852112316</v>
+      </c>
+      <c r="G52" s="2">
         <v>1.83</v>
       </c>
-      <c r="H52" s="3">
-        <v>64.51</v>
-      </c>
-      <c r="I52" s="3">
-        <v>62.55</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0.024303727713901203</v>
-      </c>
-      <c r="K52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="H52" s="2">
+        <v>66.21</v>
+      </c>
+      <c r="I52" s="2">
+        <v>64.37</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0.027550206758726836</v>
+      </c>
+      <c r="K52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
         <v>269</v>
       </c>
-      <c r="M52" s="3">
-        <v>0.16796823063719568</v>
-      </c>
-      <c r="N52" s="3">
-        <v>66.71232876712328</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="M52" s="2">
+        <v>0.17974195093795586</v>
+      </c>
+      <c r="N52" s="2">
+        <v>29.649927915100726</v>
+      </c>
+      <c r="O52" s="2">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="P52" s="2">
+        <v>20.10180966623631</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>67.21518987341773</v>
+      </c>
+      <c r="R52" s="2">
+        <v>56.77215189873419</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="1">
         <v>-0.71</v>
       </c>
-      <c r="C53" s="3">
-        <v>19.17808219178082</v>
-      </c>
-      <c r="D53" s="3">
+      <c r="C53" s="1">
+        <v>17.72151898734177</v>
+      </c>
+      <c r="D53" s="1">
         <v>12.042253521126762</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="1">
         <v>6.97</v>
       </c>
-      <c r="F53" s="3">
-        <v>-0.23047455346300746</v>
-      </c>
-      <c r="G53" s="3">
+      <c r="F53" s="1">
+        <v>-0.1745555804193139</v>
+      </c>
+      <c r="G53" s="1">
         <v>2.59</v>
       </c>
-      <c r="H53" s="3">
-        <v>69.11</v>
-      </c>
-      <c r="I53" s="3">
-        <v>-14.62</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0.015672053898523407</v>
-      </c>
-      <c r="K53" s="3" t="b">
+      <c r="H53" s="1">
+        <v>69.25</v>
+      </c>
+      <c r="I53" s="1">
+        <v>-14.45</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.019469516135453818</v>
+      </c>
+      <c r="K53" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L53" s="3">
+      <c r="L53" s="1">
         <v>25</v>
       </c>
-      <c r="M53" s="3">
-        <v>-0.10672222562495381</v>
-      </c>
-      <c r="N53" s="3">
-        <v>50.684931506849324</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="M53" s="1">
+        <v>-0.0060039285605621995</v>
+      </c>
+      <c r="N53" s="1">
+        <v>11.075339965248917</v>
+      </c>
+      <c r="O53" s="1">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P53" s="1">
+        <v>48.21894075039502</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>48.734177215189874</v>
+      </c>
+      <c r="R53" s="1">
+        <v>35.12658227848102</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T53" s="1">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="2">
         <v>0.54</v>
       </c>
-      <c r="C54" s="3">
-        <v>35.61643835616438</v>
-      </c>
-      <c r="D54" s="3">
+      <c r="C54" s="2">
+        <v>35.44303797468354</v>
+      </c>
+      <c r="D54" s="2">
         <v>41.629629629629626</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="2">
         <v>-0.44</v>
       </c>
-      <c r="F54" s="3">
-        <v>-0.014193589483792485</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="F54" s="2">
+        <v>-0.00014858383710547596</v>
+      </c>
+      <c r="G54" s="2">
         <v>1.46</v>
       </c>
-      <c r="H54" s="3">
-        <v>72</v>
-      </c>
-      <c r="I54" s="3">
-        <v>14.47</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0.02402155512672836</v>
-      </c>
-      <c r="K54" s="3" t="b">
+      <c r="H54" s="2">
+        <v>66.62</v>
+      </c>
+      <c r="I54" s="2">
+        <v>11.42</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.029728045222307847</v>
+      </c>
+      <c r="K54" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="2">
         <v>21</v>
       </c>
-      <c r="M54" s="3">
-        <v>0.02160897077124191</v>
-      </c>
-      <c r="N54" s="3">
-        <v>66.02739726027396</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M54" s="2">
+        <v>0.048614787140898175</v>
+      </c>
+      <c r="N54" s="2">
+        <v>16.53721153539496</v>
+      </c>
+      <c r="O54" s="2">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="P54" s="2">
+        <v>25.062459708672506</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>65.69620253164557</v>
+      </c>
+      <c r="R54" s="2">
+        <v>52.65822784810126</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -4123,7 +5419,7 @@
         <v>4.03</v>
       </c>
       <c r="C55" s="1">
-        <v>54.794520547945204</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="D55" s="1">
         <v>2.2580645161290325</v>
@@ -4132,19 +5428,19 @@
         <v>-0.7</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.1786140637783561</v>
+        <v>-0.18622611726230834</v>
       </c>
       <c r="G55" s="1">
         <v>1.2</v>
       </c>
       <c r="H55" s="1">
-        <v>37.94</v>
+        <v>39.05</v>
       </c>
       <c r="I55" s="1">
-        <v>-3.39</v>
+        <v>-3.12</v>
       </c>
       <c r="J55" s="1">
-        <v>0.000645407993285332</v>
+        <v>0.0001009254578829784</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -4153,19 +5449,31 @@
         <v>10</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.16304773323268895</v>
+        <v>-0.16502465161969804</v>
       </c>
       <c r="N55" s="1">
-        <v>47.53424657534247</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>110</v>
+        <v>-4.826732340664665</v>
+      </c>
+      <c r="O55" s="1">
+        <v>27.848101265822784</v>
       </c>
       <c r="P55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18.39301096820415</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>47.21518987341773</v>
+      </c>
+      <c r="R55" s="1">
+        <v>36.582278481012665</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -4173,7 +5481,7 @@
         <v>8.65</v>
       </c>
       <c r="C56" s="1">
-        <v>73.97260273972603</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="D56" s="1">
         <v>0.1757225433526011</v>
@@ -4182,19 +5490,19 @@
         <v>0.84</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.07433092129348562</v>
+        <v>-0.09903570790419841</v>
       </c>
       <c r="G56" s="1">
         <v>0.26</v>
       </c>
       <c r="H56" s="1">
-        <v>51.95</v>
+        <v>51.35</v>
       </c>
       <c r="I56" s="1">
-        <v>10.47</v>
+        <v>10.14</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.009476292611681675</v>
+        <v>-0.008898279015999048</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
@@ -4203,19 +5511,31 @@
         <v>199</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.13192634431245398</v>
+        <v>-0.17748113078185646</v>
       </c>
       <c r="N56" s="1">
-        <v>46.98630136986301</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>111</v>
+        <v>-6.07238025688051</v>
+      </c>
+      <c r="O56" s="1">
+        <v>25.31645569620253</v>
       </c>
       <c r="P56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10.95912073621325</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>45.063291139240505</v>
+      </c>
+      <c r="R56" s="1">
+        <v>33.98734177215189</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
@@ -4223,28 +5543,28 @@
         <v>21.18</v>
       </c>
       <c r="C57" s="2">
-        <v>95.8904109589041</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.2587346553352217</v>
+        <v>2.31067044381492</v>
       </c>
       <c r="E57" s="2">
         <v>0.39</v>
       </c>
       <c r="F57" s="2">
-        <v>0.7920358149187916</v>
+        <v>0.6840401434964034</v>
       </c>
       <c r="G57" s="2">
         <v>2</v>
       </c>
       <c r="H57" s="2">
-        <v>81.34</v>
+        <v>79.04</v>
       </c>
       <c r="I57" s="2">
-        <v>167.2</v>
+        <v>160.72</v>
       </c>
       <c r="J57" s="2">
-        <v>0.0780708832930195</v>
+        <v>0.08503248308634306</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>1</v>
@@ -4253,269 +5573,341 @@
         <v>409</v>
       </c>
       <c r="M57" s="2">
-        <v>0.8698674676471272</v>
+        <v>0.7900474717094548</v>
       </c>
       <c r="N57" s="2">
-        <v>82.05479452054794</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>112</v>
+        <v>90.68047999225062</v>
+      </c>
+      <c r="O57" s="2">
+        <v>93.67088607594937</v>
       </c>
       <c r="P57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+        <v>30.30559414893712</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>81.51898734177216</v>
+      </c>
+      <c r="R57" s="2">
+        <v>67.34177215189874</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="2">
         <v>20.1</v>
       </c>
-      <c r="C58" s="3">
-        <v>94.52054794520548</v>
-      </c>
-      <c r="D58" s="3">
+      <c r="C58" s="2">
+        <v>94.9367088607595</v>
+      </c>
+      <c r="D58" s="2">
         <v>0.09701492537313429</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="2">
         <v>-1.9</v>
       </c>
-      <c r="F58" s="3">
-        <v>0.027420771345217337</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="F58" s="2">
+        <v>0.021818608106908055</v>
+      </c>
+      <c r="G58" s="2">
         <v>1.62</v>
       </c>
-      <c r="H58" s="3">
-        <v>63.7</v>
-      </c>
-      <c r="I58" s="3">
-        <v>47.84</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0.02102064106989931</v>
-      </c>
-      <c r="K58" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="H58" s="2">
+        <v>65.53</v>
+      </c>
+      <c r="I58" s="2">
+        <v>49.13</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0.02231951880965812</v>
+      </c>
+      <c r="K58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="2">
         <v>315</v>
       </c>
-      <c r="M58" s="3">
-        <v>0.07567639603678544</v>
-      </c>
-      <c r="N58" s="3">
-        <v>64.93150684931507</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="M58" s="2">
+        <v>0.08754315159899995</v>
+      </c>
+      <c r="N58" s="2">
+        <v>20.430047981205142</v>
+      </c>
+      <c r="O58" s="2">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P58" s="2">
+        <v>13.880000945060484</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>65.0632911392405</v>
+      </c>
+      <c r="R58" s="2">
+        <v>55.31645569620253</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="T58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="2">
         <v>34.32</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <v>100</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="2">
         <v>-1.435897435897436</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="2">
         <v>-2.43</v>
       </c>
-      <c r="F59" s="3">
-        <v>0.18278205477471943</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="2">
+        <v>0.17401162363333672</v>
+      </c>
+      <c r="G59" s="2">
         <v>1.24</v>
       </c>
-      <c r="H59" s="3">
-        <v>54.92</v>
-      </c>
-      <c r="I59" s="3">
-        <v>46.04</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0.020132843939223818</v>
-      </c>
-      <c r="K59" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="H59" s="2">
+        <v>56.61</v>
+      </c>
+      <c r="I59" s="2">
+        <v>47.17</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0.02141742119672486</v>
+      </c>
+      <c r="K59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2">
         <v>374</v>
       </c>
-      <c r="M59" s="3">
-        <v>0.20146165142952</v>
-      </c>
-      <c r="N59" s="3">
-        <v>60.136986301369866</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="M59" s="2">
+        <v>0.19945338240446908</v>
+      </c>
+      <c r="N59" s="2">
+        <v>31.621071061752055</v>
+      </c>
+      <c r="O59" s="2">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="P59" s="2">
+        <v>11.512523311327532</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>59.74683544303798</v>
+      </c>
+      <c r="R59" s="2">
+        <v>56.582278481012665</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="3">
         <v>6.37</v>
       </c>
-      <c r="C60" s="1">
-        <v>67.12328767123287</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C60" s="3">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="D60" s="3">
         <v>-0.1255886970172684</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="3">
         <v>-0.23</v>
       </c>
-      <c r="F60" s="1">
-        <v>-0.1578547915092008</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="F60" s="3">
+        <v>-0.16126001565497908</v>
+      </c>
+      <c r="G60" s="3">
         <v>0.38</v>
       </c>
-      <c r="H60" s="1">
-        <v>38.38</v>
-      </c>
-      <c r="I60" s="1">
-        <v>-0.71</v>
-      </c>
-      <c r="J60" s="1">
-        <v>-0.009825585144730604</v>
-      </c>
-      <c r="K60" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="H60" s="3">
+        <v>38.08</v>
+      </c>
+      <c r="I60" s="3">
+        <v>-0.86</v>
+      </c>
+      <c r="J60" s="3">
+        <v>-0.010130946048307181</v>
+      </c>
+      <c r="K60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
         <v>149</v>
       </c>
-      <c r="M60" s="1">
-        <v>-0.20611041620076886</v>
-      </c>
-      <c r="N60" s="1">
-        <v>38.08219178082192</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="M60" s="3">
+        <v>-0.22698455914707094</v>
+      </c>
+      <c r="N60" s="3">
+        <v>-11.02272309340195</v>
+      </c>
+      <c r="O60" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="P60" s="3">
+        <v>12.73975043749647</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>36.32911392405063</v>
+      </c>
+      <c r="R60" s="3">
+        <v>28.79746835443038</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="1">
         <v>17.74</v>
       </c>
-      <c r="C61" s="3">
-        <v>91.78082191780823</v>
-      </c>
-      <c r="D61" s="3">
+      <c r="C61" s="1">
+        <v>92.40506329113924</v>
+      </c>
+      <c r="D61" s="1">
         <v>0.6178128523111613</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="1">
         <v>-0.38</v>
       </c>
-      <c r="F61" s="3">
-        <v>-0.13776233282311112</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="F61" s="1">
+        <v>-0.14291277018514845</v>
+      </c>
+      <c r="G61" s="1">
         <v>0.96</v>
       </c>
-      <c r="H61" s="3">
-        <v>49.53</v>
-      </c>
-      <c r="I61" s="3">
-        <v>11.85</v>
-      </c>
-      <c r="J61" s="3">
-        <v>-0.007127990710515013</v>
-      </c>
-      <c r="K61" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="H61" s="1">
+        <v>49.51</v>
+      </c>
+      <c r="I61" s="1">
+        <v>11.77</v>
+      </c>
+      <c r="J61" s="1">
+        <v>-0.006832330097585761</v>
+      </c>
+      <c r="K61" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
         <v>155</v>
       </c>
-      <c r="M61" s="3">
-        <v>-0.14087559893224455</v>
-      </c>
-      <c r="N61" s="3">
-        <v>54.79452054794521</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="M61" s="1">
+        <v>-0.1471530633136705</v>
+      </c>
+      <c r="N61" s="1">
+        <v>-3.0395735100619077</v>
+      </c>
+      <c r="O61" s="1">
+        <v>35.44303797468354</v>
+      </c>
+      <c r="P61" s="1">
+        <v>16.149676494964734</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>54.050632911392405</v>
+      </c>
+      <c r="R61" s="1">
+        <v>42.848101265822784</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="4">
         <v>28.77</v>
       </c>
-      <c r="C62" s="2">
-        <v>98.63013698630137</v>
-      </c>
-      <c r="D62" s="2">
-        <v>4.887382690302398</v>
-      </c>
-      <c r="E62" s="2">
+      <c r="C62" s="4">
+        <v>98.73417721518987</v>
+      </c>
+      <c r="D62" s="4">
+        <v>4.831074035453597</v>
+      </c>
+      <c r="E62" s="4">
         <v>-8.63</v>
       </c>
-      <c r="F62" s="2">
-        <v>1.0334773690205432</v>
-      </c>
-      <c r="G62" s="2">
+      <c r="F62" s="4">
+        <v>0.702412030848552</v>
+      </c>
+      <c r="G62" s="4">
         <v>4.76</v>
       </c>
-      <c r="H62" s="2">
-        <v>69.78</v>
-      </c>
-      <c r="I62" s="2">
-        <v>254.34</v>
-      </c>
-      <c r="J62" s="2">
-        <v>0.1054338291002765</v>
-      </c>
-      <c r="K62" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" s="2">
+      <c r="H62" s="4">
+        <v>66.15</v>
+      </c>
+      <c r="I62" s="4">
+        <v>238.33</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0.1058386935433432</v>
+      </c>
+      <c r="K62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4">
         <v>413</v>
       </c>
-      <c r="M62" s="2">
-        <v>1.3261243832790852</v>
-      </c>
-      <c r="N62" s="2">
-        <v>83.42465753424656</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="P62" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M62" s="4">
+        <v>1.1009995849296252</v>
+      </c>
+      <c r="N62" s="4">
+        <v>121.77569131426769</v>
+      </c>
+      <c r="O62" s="4">
+        <v>98.73417721518987</v>
+      </c>
+      <c r="P62" s="4">
+        <v>25.85061584959845</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>82.27848101265823</v>
+      </c>
+      <c r="R62" s="4">
+        <v>72.34177215189874</v>
+      </c>
+      <c r="S62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="T62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
@@ -4523,7 +5915,7 @@
         <v>10.54</v>
       </c>
       <c r="C63" s="2">
-        <v>78.08219178082192</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="D63" s="2">
         <v>6.3927893738140416</v>
@@ -4532,19 +5924,19 @@
         <v>-4.36</v>
       </c>
       <c r="F63" s="2">
-        <v>0.8382498433922643</v>
+        <v>0.6347132974900617</v>
       </c>
       <c r="G63" s="2">
         <v>2.03</v>
       </c>
       <c r="H63" s="2">
-        <v>78.91</v>
+        <v>75.15</v>
       </c>
       <c r="I63" s="2">
-        <v>146.6</v>
+        <v>139.96</v>
       </c>
       <c r="J63" s="2">
-        <v>0.08437980976811785</v>
+        <v>0.0865727164624305</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
@@ -4553,19 +5945,31 @@
         <v>184</v>
       </c>
       <c r="M63" s="2">
-        <v>0.91841644570245</v>
+        <v>0.7439008455495046</v>
       </c>
       <c r="N63" s="2">
-        <v>78.63013698630137</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>103</v>
+        <v>86.06581737625561</v>
+      </c>
+      <c r="O63" s="2">
+        <v>92.40506329113924</v>
       </c>
       <c r="P63" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>20.9978319173529</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>77.84810126582278</v>
+      </c>
+      <c r="R63" s="2">
+        <v>66.96202531645571</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
@@ -4573,7 +5977,7 @@
         <v>16.87</v>
       </c>
       <c r="C64" s="1">
-        <v>89.04109589041096</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="D64" s="1">
         <v>-0.2691167753408418</v>
@@ -4582,19 +5986,19 @@
         <v>-0.69</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.05261259868038751</v>
+        <v>-0.07677209987055884</v>
       </c>
       <c r="G64" s="1">
         <v>0.31</v>
       </c>
       <c r="H64" s="1">
-        <v>61.16</v>
+        <v>59.81</v>
       </c>
       <c r="I64" s="1">
-        <v>4.17</v>
+        <v>3.83</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.0101707777934316</v>
+        <v>-0.008871724521789534</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>0</v>
@@ -4603,516 +6007,1020 @@
         <v>71</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.10631643906293908</v>
+        <v>-0.1499171563375643</v>
       </c>
       <c r="N64" s="1">
-        <v>48.21917808219178</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>94</v>
+        <v>-3.315982812451293</v>
+      </c>
+      <c r="O64" s="1">
+        <v>32.91139240506329</v>
       </c>
       <c r="P64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+        <v>15.211254913322609</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>48.22784810126582</v>
+      </c>
+      <c r="R64" s="1">
+        <v>37.40506329113924</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T64" s="1">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="3">
         <v>15.41</v>
       </c>
-      <c r="C65" s="1">
-        <v>86.3013698630137</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="C65" s="3">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="D65" s="3">
         <v>-0.10837118754055808</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="3">
         <v>-0.19</v>
       </c>
-      <c r="F65" s="1">
-        <v>-0.16014256613872618</v>
-      </c>
-      <c r="G65" s="1">
+      <c r="F65" s="3">
+        <v>-0.16453528787485666</v>
+      </c>
+      <c r="G65" s="3">
         <v>1.02</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="3">
+        <v>43.81</v>
+      </c>
+      <c r="I65" s="3">
+        <v>-33.37</v>
+      </c>
+      <c r="J65" s="3">
+        <v>-0.008021649911025294</v>
+      </c>
+      <c r="K65" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>-153</v>
+      </c>
+      <c r="M65" s="3">
+        <v>-0.16241514131059565</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-4.5657813097544215</v>
+      </c>
+      <c r="O65" s="3">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="P65" s="3">
+        <v>48.12800106814908</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>40.75949367088607</v>
+      </c>
+      <c r="R65" s="3">
+        <v>29.050632911392405</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T65" s="3">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>4.01</v>
+      </c>
+      <c r="C66" s="1">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="D66" s="1">
+        <v>7.0074812967581055</v>
+      </c>
+      <c r="E66" s="1">
+        <v>-0.9</v>
+      </c>
+      <c r="F66" s="1">
+        <v>-0.08084571247327066</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1.15</v>
+      </c>
+      <c r="H66" s="1">
+        <v>48.91</v>
+      </c>
+      <c r="I66" s="1">
+        <v>-11.66</v>
+      </c>
+      <c r="J66" s="1">
+        <v>-0.00043359092444813775</v>
+      </c>
+      <c r="K66" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>-32</v>
+      </c>
+      <c r="M66" s="1">
+        <v>-0.06494461324131295</v>
+      </c>
+      <c r="N66" s="1">
+        <v>5.181271497173847</v>
+      </c>
+      <c r="O66" s="1">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="P66" s="1">
+        <v>21.01837744312229</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>50.12658227848102</v>
+      </c>
+      <c r="R66" s="1">
+        <v>44.11392405063291</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>7.35</v>
+      </c>
+      <c r="C67" s="1">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="D67" s="1">
+        <v>84.9795918367347</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F67" s="1">
+        <v>-0.17464350704065426</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="H67" s="1">
+        <v>45.64</v>
+      </c>
+      <c r="I67" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="J67" s="1">
+        <v>-0.010596519517794166</v>
+      </c>
+      <c r="K67" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>132</v>
+      </c>
+      <c r="M67" s="1">
+        <v>-0.2456684169433987</v>
+      </c>
+      <c r="N67" s="1">
+        <v>-12.891108873034732</v>
+      </c>
+      <c r="O67" s="1">
+        <v>17.72151898734177</v>
+      </c>
+      <c r="P67" s="1">
+        <v>18.003852697255347</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>60.37974683544305</v>
+      </c>
+      <c r="R67" s="1">
+        <v>44.936708860759495</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3">
+        <v>8.24</v>
+      </c>
+      <c r="C68" s="3">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0.6286407766990291</v>
+      </c>
+      <c r="E68" s="3">
+        <v>-0.07</v>
+      </c>
+      <c r="F68" s="3">
+        <v>-0.27315144163343014</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="H68" s="3">
+        <v>36.26</v>
+      </c>
+      <c r="I68" s="3">
+        <v>-13.82</v>
+      </c>
+      <c r="J68" s="3">
+        <v>-0.014530824507100982</v>
+      </c>
+      <c r="K68" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>-11</v>
+      </c>
+      <c r="M68" s="3">
+        <v>-0.22120785080903493</v>
+      </c>
+      <c r="N68" s="3">
+        <v>-10.445052259598356</v>
+      </c>
+      <c r="O68" s="3">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="P68" s="3">
+        <v>29.145649851223904</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>36.708860759493675</v>
+      </c>
+      <c r="R68" s="3">
+        <v>27.72151898734177</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3">
+        <v>18.19</v>
+      </c>
+      <c r="C69" s="3">
+        <v>93.67088607594937</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-0.47663551401869164</v>
+      </c>
+      <c r="E69" s="3">
+        <v>1.57</v>
+      </c>
+      <c r="F69" s="3">
+        <v>-0.21780123079606967</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="H69" s="3">
+        <v>37.59</v>
+      </c>
+      <c r="I69" s="3">
+        <v>-14.56</v>
+      </c>
+      <c r="J69" s="3">
+        <v>-0.012052150714678567</v>
+      </c>
+      <c r="K69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="3">
+        <v>-34</v>
+      </c>
+      <c r="M69" s="3">
+        <v>-0.23158218346376636</v>
+      </c>
+      <c r="N69" s="3">
+        <v>-11.4824855250715</v>
+      </c>
+      <c r="O69" s="3">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P69" s="3">
+        <v>30.247870785107096</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>38.481012658227854</v>
+      </c>
+      <c r="R69" s="3">
+        <v>27.72151898734177</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="C70" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="D70" s="3">
+        <v>13.532894736842104</v>
+      </c>
+      <c r="E70" s="3">
+        <v>-0.78</v>
+      </c>
+      <c r="F70" s="3">
+        <v>-0.43529043335779305</v>
+      </c>
+      <c r="G70" s="3">
+        <v>1.11</v>
+      </c>
+      <c r="H70" s="3">
+        <v>31.64</v>
+      </c>
+      <c r="I70" s="3">
+        <v>-32.43</v>
+      </c>
+      <c r="J70" s="3">
+        <v>-0.036819047674802624</v>
+      </c>
+      <c r="K70" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>-65</v>
+      </c>
+      <c r="M70" s="3">
+        <v>-0.4236296272543574</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-30.687229904130596</v>
+      </c>
+      <c r="O70" s="3">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="P70" s="3">
+        <v>37.53319428279413</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>35.822784810126585</v>
+      </c>
+      <c r="R70" s="3">
+        <v>21.835443037974688</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3">
+        <v>5.18</v>
+      </c>
+      <c r="C71" s="3">
+        <v>60.75949367088608</v>
+      </c>
+      <c r="D71" s="3">
+        <v>0.7837837837837839</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="F71" s="3">
+        <v>-0.2817255110945516</v>
+      </c>
+      <c r="G71" s="3">
+        <v>1.01</v>
+      </c>
+      <c r="H71" s="3">
+        <v>50.24</v>
+      </c>
+      <c r="I71" s="3">
+        <v>-7.12</v>
+      </c>
+      <c r="J71" s="3">
+        <v>-0.011991913113487167</v>
+      </c>
+      <c r="K71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>-20</v>
+      </c>
+      <c r="M71" s="3">
+        <v>-0.28066543781242104</v>
+      </c>
+      <c r="N71" s="3">
+        <v>-16.39081095993696</v>
+      </c>
+      <c r="O71" s="3">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="P71" s="3">
+        <v>19.13407224404345</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>40.126582278481</v>
+      </c>
+      <c r="R71" s="3">
+        <v>26.202531645569618</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T71" s="3">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3">
+        <v>10.42</v>
+      </c>
+      <c r="C72" s="3">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="D72" s="3">
+        <v>0.21305182341650677</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1.31</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-0.30054631759780803</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="H72" s="3">
         <v>39.88</v>
       </c>
-      <c r="I65" s="1">
-        <v>-35.2</v>
-      </c>
-      <c r="J65" s="1">
-        <v>-0.0039042812625143045</v>
-      </c>
-      <c r="K65" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>-153</v>
-      </c>
-      <c r="M65" s="1">
-        <v>-0.15858593308415947</v>
-      </c>
-      <c r="N65" s="1">
-        <v>43.150684931506845</v>
-      </c>
-      <c r="O65" s="1" t="s">
+      <c r="I72" s="3">
+        <v>-9.12</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-0.013340396526671216</v>
+      </c>
+      <c r="K72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3">
+        <v>55</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-0.28570529164798086</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-16.894796343492946</v>
+      </c>
+      <c r="O72" s="3">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="P72" s="3">
+        <v>18.537307083411516</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="R72" s="3">
+        <v>27.468354430379748</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="C73" s="2">
+        <v>36.708860759493675</v>
+      </c>
+      <c r="D73" s="2">
+        <v>22.40983606557377</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0.2318061407146457</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1.17</v>
+      </c>
+      <c r="H73" s="2">
+        <v>61.8</v>
+      </c>
+      <c r="I73" s="2">
+        <v>41.61</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0.03293282383472466</v>
+      </c>
+      <c r="K73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2">
+        <v>10</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0.24982738651086445</v>
+      </c>
+      <c r="N73" s="2">
+        <v>36.658471472391575</v>
+      </c>
+      <c r="O73" s="2">
+        <v>83.54430379746836</v>
+      </c>
+      <c r="P73" s="2">
+        <v>9.507882188735834</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>65.56962025316456</v>
+      </c>
+      <c r="R73" s="2">
+        <v>61.0126582278481</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T73" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="C74" s="2">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="D74" s="2">
+        <v>14.25</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2.01</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0.171837599993916</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="H74" s="2">
+        <v>83.02</v>
+      </c>
+      <c r="I74" s="2">
+        <v>32.23</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0.021742148422753137</v>
+      </c>
+      <c r="K74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2">
+        <v>15</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0.1495760610691752</v>
+      </c>
+      <c r="N74" s="2">
+        <v>26.633338928222656</v>
+      </c>
+      <c r="O74" s="2">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="P74" s="2">
+        <v>3.6747023875523213</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>65.0632911392405</v>
+      </c>
+      <c r="R74" s="2">
+        <v>56.32911392405063</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T74" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="C75" s="1">
+        <v>34.177215189873415</v>
+      </c>
+      <c r="D75" s="1">
+        <v>29.204545454545453</v>
+      </c>
+      <c r="E75" s="1">
+        <v>-0.71</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0.0822037529066603</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="H75" s="1">
+        <v>60.47</v>
+      </c>
+      <c r="I75" s="1">
+        <v>14.82</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0.00564206762993544</v>
+      </c>
+      <c r="K75" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>6</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0.07796345977813823</v>
+      </c>
+      <c r="N75" s="1">
+        <v>19.47207879911897</v>
+      </c>
+      <c r="O75" s="1">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P75" s="1">
+        <v>37.05001195108517</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>58.10126582278481</v>
+      </c>
+      <c r="R75" s="1">
+        <v>46.45569620253164</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2.05</v>
+      </c>
+      <c r="C76" s="1">
+        <v>48.10126582278481</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0.7170731707317075</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2.63</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0.036085675669937756</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="H76" s="1">
+        <v>58.72</v>
+      </c>
+      <c r="I76" s="1">
+        <v>18.77</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0.018217078308452244</v>
+      </c>
+      <c r="K76" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>6</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0.006403623770283362</v>
+      </c>
+      <c r="N76" s="1">
+        <v>12.316095198333482</v>
+      </c>
+      <c r="O76" s="1">
+        <v>58.22784810126582</v>
+      </c>
+      <c r="P76" s="1">
+        <v>17.05597509098574</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>50.253164556962034</v>
+      </c>
+      <c r="R76" s="1">
+        <v>42.21518987341772</v>
+      </c>
+      <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3">
-        <v>4.01</v>
-      </c>
-      <c r="C66" s="3">
-        <v>53.42465753424658</v>
-      </c>
-      <c r="D66" s="3">
-        <v>7.0074812967581055</v>
-      </c>
-      <c r="E66" s="3">
-        <v>-0.9</v>
-      </c>
-      <c r="F66" s="3">
-        <v>-0.04829196322026859</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1.15</v>
-      </c>
-      <c r="H66" s="3">
-        <v>48.99</v>
-      </c>
-      <c r="I66" s="3">
-        <v>-11.69</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0.0010865312594037855</v>
-      </c>
-      <c r="K66" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3">
-        <v>-32</v>
-      </c>
-      <c r="M66" s="3">
-        <v>-0.03661721531101825</v>
-      </c>
-      <c r="N66" s="3">
-        <v>51.36986301369863</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3">
-        <v>7.35</v>
-      </c>
-      <c r="C67" s="3">
-        <v>68.4931506849315</v>
-      </c>
-      <c r="D67" s="3">
-        <v>84.9795918367347</v>
-      </c>
-      <c r="E67" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="F67" s="3">
-        <v>-0.18245498169290972</v>
-      </c>
-      <c r="G67" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="H67" s="3">
-        <v>46.24</v>
-      </c>
-      <c r="I67" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="J67" s="3">
-        <v>-0.010157730080911484</v>
-      </c>
-      <c r="K67" s="3" t="b">
+      <c r="T76" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="C77" s="2">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="D77" s="2">
+        <v>281.33333333333337</v>
+      </c>
+      <c r="E77" s="2">
+        <v>-0.34</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0.01240752414840536</v>
+      </c>
+      <c r="G77" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="H77" s="2">
+        <v>66.79</v>
+      </c>
+      <c r="I77" s="2">
+        <v>11.55</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0.008247007365014443</v>
+      </c>
+      <c r="K77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2">
+        <v>2</v>
+      </c>
+      <c r="M77" s="2">
+        <v>0.01028737758414433</v>
+      </c>
+      <c r="N77" s="2">
+        <v>12.70447057971958</v>
+      </c>
+      <c r="O77" s="2">
+        <v>59.49367088607595</v>
+      </c>
+      <c r="P77" s="2">
+        <v>8.54788795515236</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>62.91139240506329</v>
+      </c>
+      <c r="R77" s="2">
+        <v>54.43037974683545</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T77" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="1">
+        <v>13.11</v>
+      </c>
+      <c r="C78" s="1">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="D78" s="1">
+        <v>-0.6414950419527079</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0.57</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.13799643285872165</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="H78" s="1">
+        <v>74.84</v>
+      </c>
+      <c r="I78" s="1">
+        <v>37.38</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0.02693996293552387</v>
+      </c>
+      <c r="K78" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>144</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0.16555833819411503</v>
+      </c>
+      <c r="N78" s="1">
+        <v>28.23156664071665</v>
+      </c>
+      <c r="O78" s="1">
+        <v>73.41772151898735</v>
+      </c>
+      <c r="P78" s="1">
+        <v>20.806025084936465</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>60.50632911392405</v>
+      </c>
+      <c r="R78" s="1">
+        <v>49.683544303797476</v>
+      </c>
+      <c r="S78" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="2">
+        <v>3.07</v>
+      </c>
+      <c r="C79" s="2">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2.4527687296416936</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0.4238631562787893</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="H79" s="2">
+        <v>87.31</v>
+      </c>
+      <c r="I79" s="2">
+        <v>50.65</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.0276716970655234</v>
+      </c>
+      <c r="K79" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L67" s="3">
-        <v>132</v>
-      </c>
-      <c r="M67" s="3">
-        <v>-0.23460218902089458</v>
-      </c>
-      <c r="N67" s="3">
-        <v>61.369863013698634</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="P67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
-        <v>8.24</v>
-      </c>
-      <c r="C68" s="1">
-        <v>71.23287671232876</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0.6286407766990291</v>
-      </c>
-      <c r="E68" s="1">
-        <v>-0.07</v>
-      </c>
-      <c r="F68" s="1">
-        <v>-0.25541787806132454</v>
-      </c>
-      <c r="G68" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H68" s="1">
-        <v>37.66</v>
-      </c>
-      <c r="I68" s="1">
-        <v>-13.14</v>
-      </c>
-      <c r="J68" s="1">
-        <v>-0.013656123551502256</v>
-      </c>
-      <c r="K68" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>-11</v>
-      </c>
-      <c r="M68" s="1">
-        <v>-0.21728036822444008</v>
-      </c>
-      <c r="N68" s="1">
-        <v>38.630136986301366</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1">
-        <v>18.19</v>
-      </c>
-      <c r="C69" s="1">
-        <v>93.15068493150685</v>
-      </c>
-      <c r="D69" s="1">
-        <v>-0.47663551401869164</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="F69" s="1">
-        <v>-0.23237970677791941</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="H69" s="1">
-        <v>35.06</v>
-      </c>
-      <c r="I69" s="1">
-        <v>-15.42</v>
-      </c>
-      <c r="J69" s="1">
-        <v>-0.01113208174974412</v>
-      </c>
-      <c r="K69" s="1" t="b">
+      <c r="L79" s="2">
+        <v>130</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0.4164426433038757</v>
+      </c>
+      <c r="N79" s="2">
+        <v>53.31999715169271</v>
+      </c>
+      <c r="O79" s="2">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="P79" s="2">
+        <v>13.574555133673535</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="R79" s="2">
+        <v>58.037974683544306</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="T79" s="2">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="2">
+        <v>8.72</v>
+      </c>
+      <c r="C80" s="2">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.8119266055045871</v>
+      </c>
+      <c r="E80" s="2">
+        <v>5.52</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1.0587470216818125</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="H80" s="2">
+        <v>66.13</v>
+      </c>
+      <c r="I80" s="2">
+        <v>67.76</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0.0584419134804722</v>
+      </c>
+      <c r="K80" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L69" s="1">
-        <v>-34</v>
-      </c>
-      <c r="M69" s="1">
-        <v>-0.24249782163260303</v>
-      </c>
-      <c r="N69" s="1">
-        <v>39.17808219178082</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="C70" s="1">
-        <v>43.83561643835616</v>
-      </c>
-      <c r="D70" s="1">
-        <v>13.532894736842104</v>
-      </c>
-      <c r="E70" s="1">
-        <v>-0.78</v>
-      </c>
-      <c r="F70" s="1">
-        <v>-0.41807334802057516</v>
-      </c>
-      <c r="G70" s="1">
-        <v>1.11</v>
-      </c>
-      <c r="H70" s="1">
-        <v>31.88</v>
-      </c>
-      <c r="I70" s="1">
-        <v>-32.53</v>
-      </c>
-      <c r="J70" s="1">
-        <v>-0.03761723103276857</v>
-      </c>
-      <c r="K70" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" s="1">
-        <v>-65</v>
-      </c>
-      <c r="M70" s="1">
-        <v>-0.4095118662204582</v>
-      </c>
-      <c r="N70" s="1">
-        <v>36.71232876712329</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <v>5.18</v>
-      </c>
-      <c r="C71" s="1">
-        <v>58.9041095890411</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0.7837837837837839</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="F71" s="1">
-        <v>-0.23833306205712548</v>
-      </c>
-      <c r="G71" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="H71" s="1">
-        <v>51.82</v>
-      </c>
-      <c r="I71" s="1">
-        <v>-6.67</v>
-      </c>
-      <c r="J71" s="1">
-        <v>-0.012878578894644761</v>
-      </c>
-      <c r="K71" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="1">
-        <v>-20</v>
-      </c>
-      <c r="M71" s="1">
-        <v>-0.23755474552984213</v>
-      </c>
-      <c r="N71" s="1">
-        <v>40.54794520547945</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1">
-        <v>10.42</v>
-      </c>
-      <c r="C72" s="1">
-        <v>76.71232876712328</v>
-      </c>
-      <c r="D72" s="1">
-        <v>0.21305182341650677</v>
-      </c>
-      <c r="E72" s="1">
-        <v>-1.31</v>
-      </c>
-      <c r="F72" s="1">
-        <v>-0.26469596208705964</v>
-      </c>
-      <c r="G72" s="1">
-        <v>1.14</v>
-      </c>
-      <c r="H72" s="1">
-        <v>36.4</v>
-      </c>
-      <c r="I72" s="1">
-        <v>-10.17</v>
-      </c>
-      <c r="J72" s="1">
-        <v>-0.01325063782997437</v>
-      </c>
-      <c r="K72" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L72" s="1">
-        <v>62</v>
-      </c>
-      <c r="M72" s="1">
-        <v>-0.25379953070509265</v>
-      </c>
-      <c r="N72" s="1">
-        <v>38.630136986301366</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="3">
-        <v>13.11</v>
-      </c>
-      <c r="C73" s="3">
-        <v>83.56164383561644</v>
-      </c>
-      <c r="D73" s="3">
-        <v>-0.6414950419527079</v>
-      </c>
-      <c r="E73" s="3">
-        <v>0.57</v>
-      </c>
-      <c r="F73" s="3">
-        <v>0.17290898537333294</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1.26</v>
-      </c>
-      <c r="H73" s="3">
-        <v>75.07</v>
-      </c>
-      <c r="I73" s="3">
-        <v>37.95</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0.026389290740785554</v>
-      </c>
-      <c r="K73" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3">
-        <v>144</v>
-      </c>
-      <c r="M73" s="3">
-        <v>0.19314521508270022</v>
-      </c>
-      <c r="N73" s="3">
-        <v>61.64383561643836</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B74" s="3">
-        <v>2.84</v>
-      </c>
-      <c r="C74" s="3">
-        <v>46.57534246575342</v>
-      </c>
-      <c r="D74" s="3">
-        <v>2.485915492957747</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="F74" s="3">
-        <v>0.10777142216624942</v>
-      </c>
-      <c r="G74" s="3">
-        <v>0.93</v>
-      </c>
-      <c r="H74" s="3">
-        <v>78.87</v>
-      </c>
-      <c r="I74" s="3">
-        <v>33.75</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0.022654296415204802</v>
-      </c>
-      <c r="K74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L74" s="3">
-        <v>130</v>
-      </c>
-      <c r="M74" s="3">
-        <v>0.10232320647526594</v>
-      </c>
-      <c r="N74" s="3">
-        <v>61.64383561643836</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="P74" s="3">
-        <v>0</v>
+      <c r="L80" s="2">
+        <v>141</v>
+      </c>
+      <c r="M80" s="2">
+        <v>1.0598070949639429</v>
+      </c>
+      <c r="N80" s="2">
+        <v>117.65644231769943</v>
+      </c>
+      <c r="O80" s="2">
+        <v>96.20253164556962</v>
+      </c>
+      <c r="P80" s="2">
+        <v>16.957009573963198</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>68.60759493670886</v>
+      </c>
+      <c r="R80" s="2">
+        <v>64.24050632911393</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T80" s="2">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -5123,15 +7031,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5139,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41.36986301369862</v>
+        <v>32.84810126582278</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5147,7 +7055,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>75.75342465753425</v>
+        <v>64.9367088607595</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5155,7 +7063,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>32.87671232876712</v>
+        <v>14.810126582278478</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5163,7 +7071,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62.1917808219178</v>
+        <v>45.31645569620254</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5171,7 +7079,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>41.09589041095891</v>
+        <v>42.08860759493671</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5179,7 +7087,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>63.01369863013699</v>
+        <v>54.55696202531646</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5187,7 +7095,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>67.12328767123287</v>
+        <v>55.316455696202524</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5195,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>49.45205479452054</v>
+        <v>41.202531645569614</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5203,7 +7111,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>49.58904109589041</v>
+        <v>38.79746835443038</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5211,7 +7119,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>54.52054794520548</v>
+        <v>46.455696202531655</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5219,7 +7127,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>42.1917808219178</v>
+        <v>20.696202531645564</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5227,7 +7135,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>29.58904109589041</v>
+        <v>15.88607594936709</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -5235,7 +7143,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>53.28767123287671</v>
+        <v>35.189873417721515</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -5243,7 +7151,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>70.68493150684931</v>
+        <v>61.962025316455694</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5251,7 +7159,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>44.794520547945204</v>
+        <v>36.64556962025316</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5259,7 +7167,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28.767123287671232</v>
+        <v>23.164556962025316</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5267,7 +7175,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>53.287671232876704</v>
+        <v>30.949367088607595</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5275,7 +7183,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>57.3972602739726</v>
+        <v>40.8860759493671</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5283,7 +7191,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39.178082191780824</v>
+        <v>27.405063291139236</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -5291,7 +7199,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49.726027397260275</v>
+        <v>38.79746835443038</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -5299,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>42.73972602739725</v>
+        <v>30.253164556962027</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -5307,7 +7215,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>45.61643835616439</v>
+        <v>31.962025316455694</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -5315,7 +7223,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>30.13698630136986</v>
+        <v>31.0126582278481</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5323,7 +7231,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>28.21917808219178</v>
+        <v>11.962025316455694</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -5331,7 +7239,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>41.64383561643836</v>
+        <v>33.037974683544306</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -5339,7 +7247,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>39.178082191780824</v>
+        <v>26.392405063291136</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -5347,7 +7255,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>35.06849315068493</v>
+        <v>21.898734177215193</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -5355,7 +7263,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40.54794520547945</v>
+        <v>24.36708860759493</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5363,7 +7271,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>67.67123287671232</v>
+        <v>47.53164556962025</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -5371,7 +7279,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>68.21917808219179</v>
+        <v>60.822784810126585</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -5379,7 +7287,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>36.02739726027397</v>
+        <v>29.36708860759494</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -5387,7 +7295,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>50.41095890410959</v>
+        <v>39.9367088607595</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -5395,7 +7303,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>62.054794520547944</v>
+        <v>51.139240506329116</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -5403,7 +7311,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>33.28767123287671</v>
+        <v>21.582278481012658</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5411,7 +7319,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>42.6027397260274</v>
+        <v>34.30379746835443</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -5419,7 +7327,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>40.95890410958904</v>
+        <v>38.797468354430386</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -5427,7 +7335,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>65.75342465753424</v>
+        <v>53.92405063291139</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -5435,7 +7343,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>60</v>
+        <v>53.41772151898734</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -5443,7 +7351,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>48.76712328767123</v>
+        <v>40.75949367088608</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -5451,7 +7359,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>45.89041095890411</v>
+        <v>30.063291139240505</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -5459,7 +7367,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>42.19178082191781</v>
+        <v>38.54430379746835</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5467,7 +7375,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>52.73972602739725</v>
+        <v>42.151898734177216</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5475,7 +7383,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>39.178082191780824</v>
+        <v>26.518987341772146</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -5483,7 +7391,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>64.24657534246575</v>
+        <v>56.962025316455694</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -5491,7 +7399,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>54.38356164383562</v>
+        <v>31.39240506329114</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5499,7 +7407,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>38.630136986301366</v>
+        <v>25.759493670886073</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5507,7 +7415,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>69.45205479452055</v>
+        <v>63.037974683544306</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -5515,7 +7423,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>74.10958904109589</v>
+        <v>63.544303797468345</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -5523,7 +7431,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>38.35616438356164</v>
+        <v>21.77215189873418</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -5531,7 +7439,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>36.16438356164384</v>
+        <v>26.64556962025317</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5539,7 +7447,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>66.71232876712328</v>
+        <v>56.77215189873419</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5547,7 +7455,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>50.684931506849324</v>
+        <v>35.12658227848102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -5555,7 +7463,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>66.02739726027396</v>
+        <v>52.65822784810126</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -5563,7 +7471,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>47.53424657534247</v>
+        <v>36.582278481012665</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -5571,7 +7479,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>46.98630136986301</v>
+        <v>33.98734177215189</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5579,7 +7487,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>82.05479452054794</v>
+        <v>67.34177215189874</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -5587,7 +7495,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>64.93150684931507</v>
+        <v>55.31645569620253</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5595,7 +7503,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>60.136986301369866</v>
+        <v>56.582278481012665</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -5603,7 +7511,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>38.08219178082192</v>
+        <v>28.79746835443038</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -5611,7 +7519,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>54.79452054794521</v>
+        <v>42.848101265822784</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -5619,7 +7527,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>83.42465753424656</v>
+        <v>72.34177215189874</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -5627,7 +7535,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>78.63013698630137</v>
+        <v>66.96202531645571</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -5635,7 +7543,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>48.21917808219178</v>
+        <v>37.40506329113924</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -5643,7 +7551,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>43.150684931506845</v>
+        <v>29.050632911392405</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5651,7 +7559,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>51.36986301369863</v>
+        <v>44.11392405063291</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -5659,7 +7567,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>61.369863013698634</v>
+        <v>44.936708860759495</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -5667,7 +7575,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>38.630136986301366</v>
+        <v>27.72151898734177</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5675,7 +7583,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>39.17808219178082</v>
+        <v>27.72151898734177</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -5683,7 +7591,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>36.71232876712329</v>
+        <v>21.835443037974688</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -5691,7 +7599,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>40.54794520547945</v>
+        <v>26.202531645569618</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -5699,23 +7607,71 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>38.630136986301366</v>
+        <v>27.468354430379748</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B73">
-        <v>61.64383561643836</v>
+        <v>61.0126582278481</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B74">
-        <v>61.64383561643836</v>
+        <v>56.32911392405063</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75">
+        <v>46.45569620253164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76">
+        <v>42.21518987341772</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77">
+        <v>54.43037974683545</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78">
+        <v>49.683544303797476</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79">
+        <v>58.037974683544306</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80">
+        <v>64.24050632911393</v>
       </c>
     </row>
   </sheetData>
@@ -5734,137 +7690,137 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5883,114 +7839,114 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -6009,10 +7965,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6020,112 +7976,112 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -6144,125 +8100,125 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -6273,231 +8229,217 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>187</v>
+      <c r="A11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>187</v>
+      <c r="A12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>187</v>
+      <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" t="s">
         <v>198</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>187</v>
+      <c r="D14" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>200</v>
-      </c>
-      <c r="B16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="231">
   <si>
     <t>Ticker</t>
   </si>
@@ -256,13 +256,13 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>RSI</t>
+    <t>RSI_14Day</t>
   </si>
   <si>
     <t>SMA200_Dist</t>
   </si>
   <si>
-    <t>MA_Slope</t>
+    <t>MA_Slope_50</t>
   </si>
   <si>
     <t>Volume_Expansion</t>
@@ -283,16 +283,16 @@
     <t>Drawdown_%</t>
   </si>
   <si>
-    <t>Old_Score</t>
-  </si>
-  <si>
-    <t>New_Score</t>
+    <t>Composite_Score</t>
+  </si>
+  <si>
+    <t>New_Composite_Score</t>
   </si>
   <si>
     <t>Earnings_Date</t>
   </si>
   <si>
-    <t>Delta</t>
+    <t>Daily_Composite_Score_delta</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -304,16 +304,16 @@
     <t>2026-05-27</t>
   </si>
   <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
+    <t>2027-04-22</t>
+  </si>
+  <si>
+    <t>2027-04-16</t>
   </si>
   <si>
     <t>2026-05-20</t>
   </si>
   <si>
-    <t>2026-04-21</t>
+    <t>2027-04-21</t>
   </si>
   <si>
     <t>2026-05-04</t>
@@ -325,13 +325,13 @@
     <t>2026-05-28</t>
   </si>
   <si>
-    <t>2027-03-03</t>
+    <t>2026-06-02</t>
   </si>
   <si>
     <t>2027-03-10</t>
   </si>
   <si>
-    <t>2026-04-23</t>
+    <t>2027-04-23</t>
   </si>
   <si>
     <t>2026-05-11</t>
@@ -340,10 +340,10 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
+    <t>2027-04-29</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
   </si>
   <si>
     <t>2026-05-07</t>
@@ -352,7 +352,7 @@
     <t>2026-06-03</t>
   </si>
   <si>
-    <t>2026-04-27</t>
+    <t>2027-04-27</t>
   </si>
   <si>
     <t>2026-05-14</t>
@@ -364,7 +364,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>2026-04-15</t>
+    <t>2027-04-15</t>
   </si>
   <si>
     <t>2027-04-14</t>
@@ -409,6 +409,9 @@
     <t>_date_</t>
   </si>
   <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -664,43 +667,52 @@
     <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Momentum Breakout, Earnings Upcoming</t>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Volume Spike</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -725,7 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -735,7 +747,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1355,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1366,10 +1378,10 @@
         <v>61</v>
       </c>
       <c r="B2">
-        <v>72.34177215189874</v>
+        <v>72.08860759493672</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1377,29 +1389,29 @@
         <v>56</v>
       </c>
       <c r="B3">
-        <v>67.34177215189874</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="B4">
-        <v>66.96202531645571</v>
+        <v>67.34177215189875</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="B5">
-        <v>64.9367088607595</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="C5" t="s">
         <v>215</v>
@@ -1407,32 +1419,32 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>64.24050632911393</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B7">
-        <v>63.544303797468345</v>
+        <v>61.329113924050645</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8">
-        <v>63.037974683544306</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="C8" t="s">
         <v>215</v>
@@ -1443,7 +1455,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>61.962025316455694</v>
+        <v>60.8860759493671</v>
       </c>
       <c r="C9" t="s">
         <v>215</v>
@@ -1451,24 +1463,24 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>61.0126582278481</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B11">
-        <v>60.822784810126585</v>
+        <v>58.41772151898735</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1476,263 +1488,263 @@
         <v>126</v>
       </c>
       <c r="B12">
-        <v>58.037974683544306</v>
+        <v>57.59493670886076</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13">
-        <v>56.962025316455694</v>
+        <v>55.949367088607595</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="B14">
-        <v>56.77215189873419</v>
+        <v>55.8860759493671</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>56.582278481012665</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>56.32911392405063</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B17">
-        <v>55.31645569620253</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B18">
-        <v>55.316455696202524</v>
+        <v>53.98734177215191</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="B19">
-        <v>54.55696202531646</v>
+        <v>53.9873417721519</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="B20">
-        <v>54.43037974683545</v>
+        <v>53.164556962025316</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>53.92405063291139</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B22">
-        <v>53.41772151898734</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="C22" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>52.65822784810126</v>
+        <v>51.139240506329116</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>51.139240506329116</v>
+        <v>48.79746835443037</v>
       </c>
       <c r="C24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>49.683544303797476</v>
+        <v>47.21518987341773</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>47.53164556962025</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B27">
-        <v>46.455696202531655</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B28">
-        <v>46.45569620253164</v>
+        <v>46.39240506329114</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="B29">
-        <v>45.31645569620254</v>
+        <v>46.265822784810126</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B30">
-        <v>44.936708860759495</v>
+        <v>43.291139240506325</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B31">
-        <v>42.848101265822784</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="B32">
-        <v>42.21518987341772</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B33">
-        <v>42.151898734177216</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <v>42.08860759493671</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B35">
-        <v>41.202531645569614</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1740,7 +1752,7 @@
         <v>18</v>
       </c>
       <c r="B36">
-        <v>40.8860759493671</v>
+        <v>41.64556962025317</v>
       </c>
       <c r="C36" t="s">
         <v>223</v>
@@ -1748,167 +1760,167 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="B37">
-        <v>40.75949367088608</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>39.9367088607595</v>
+        <v>40.632911392405056</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="B39">
-        <v>38.79746835443038</v>
+        <v>39.43037974683544</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>38.54430379746835</v>
+        <v>37.848101265822784</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B41">
-        <v>37.40506329113924</v>
+        <v>37.215189873417714</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B42">
-        <v>36.64556962025316</v>
+        <v>36.075949367088604</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B43">
-        <v>36.582278481012665</v>
+        <v>35.69620253164557</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>35.189873417721515</v>
+        <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B45">
-        <v>35.12658227848102</v>
+        <v>34.49367088607595</v>
       </c>
       <c r="C45" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B46">
-        <v>34.30379746835443</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>33.98734177215189</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B48">
-        <v>33.037974683544306</v>
+        <v>33.10126582278481</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="B49">
-        <v>32.84810126582278</v>
+        <v>33.10126582278481</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="B50">
-        <v>31.962025316455694</v>
+        <v>32.53164556962025</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B51">
-        <v>31.39240506329114</v>
+        <v>29.367088607594937</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2133,58 +2145,58 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>64.55696202531645</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.5446880269814502</v>
+        <v>-1.7858347386172007</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.01238980890086984</v>
+        <v>-0.07686573814465407</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H2" s="1">
-        <v>51.62</v>
+        <v>38.58</v>
       </c>
       <c r="I2" s="1">
-        <v>17.75</v>
+        <v>10.1</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0010214726622593266</v>
+        <v>-0.004938737119039667</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.09931581803557199</v>
+        <v>-0.174727272655817</v>
       </c>
       <c r="N2" s="1">
-        <v>1.744151017747948</v>
+        <v>-4.747544585681353</v>
       </c>
       <c r="O2" s="1">
-        <v>41.77215189873418</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>41.89873417721519</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="R2" s="1">
-        <v>32.84810126582278</v>
+        <v>27.21518987341772</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2198,40 +2210,40 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>23.98032786885246</v>
+        <v>23.93770491803279</v>
       </c>
       <c r="E3" s="2">
-        <v>2.08</v>
+        <v>-0.5</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8977684935470766</v>
+        <v>1.2757885416333137</v>
       </c>
       <c r="G3" s="2">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="H3" s="2">
-        <v>76.34</v>
+        <v>75.98</v>
       </c>
       <c r="I3" s="2">
-        <v>100.36</v>
+        <v>117.23</v>
       </c>
       <c r="J3" s="2">
-        <v>0.10087590049150968</v>
+        <v>0.1019263706345017</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="M3" s="2">
-        <v>1.04935897289174</v>
+        <v>1.4505412818318189</v>
       </c>
       <c r="N3" s="2">
-        <v>116.61163011047915</v>
+        <v>157.77931086308223</v>
       </c>
       <c r="O3" s="2">
-        <v>94.9367088607595</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
@@ -2240,7 +2252,7 @@
         <v>76.07594936708861</v>
       </c>
       <c r="R3" s="2">
-        <v>64.9367088607595</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
@@ -2254,55 +2266,55 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>-3.95</v>
+        <v>-3.51</v>
       </c>
       <c r="C4" s="3">
-        <v>6.329113924050633</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="D4" s="3">
-        <v>9.865822784810128</v>
+        <v>11.643874643874645</v>
       </c>
       <c r="E4" s="3">
-        <v>2.62</v>
+        <v>-1.02</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.25742575530792045</v>
+        <v>0.3552253164787448</v>
       </c>
       <c r="G4" s="3">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="H4" s="3">
-        <v>52.47</v>
+        <v>86.92</v>
       </c>
       <c r="I4" s="3">
-        <v>-25.95</v>
+        <v>25.86</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.011147903158076383</v>
+        <v>0.01849873493881134</v>
       </c>
       <c r="K4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>-69</v>
+        <v>-93</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.2468250224866153</v>
+        <v>0.3901758645184459</v>
       </c>
       <c r="N4" s="3">
-        <v>-13.006769427356394</v>
+        <v>51.74276913174493</v>
       </c>
       <c r="O4" s="3">
-        <v>15.18987341772152</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>31.0126582278481</v>
+        <v>52.658227848101276</v>
       </c>
       <c r="R4" s="3">
-        <v>14.810126582278478</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
@@ -2312,64 +2324,64 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>1.09</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>43.037974683544306</v>
       </c>
-      <c r="D5" s="1">
-        <v>23.917431192660548</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-0.13615623324950624</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="D5" s="3">
+        <v>24.65137614678899</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-0.1389371359219536</v>
+      </c>
+      <c r="G5" s="3">
         <v>1.81</v>
       </c>
-      <c r="H5" s="1">
-        <v>70.53</v>
-      </c>
-      <c r="I5" s="1">
-        <v>9.77</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.00961777982348318</v>
-      </c>
-      <c r="K5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>28</v>
-      </c>
-      <c r="M5" s="1">
-        <v>-0.05029029739693458</v>
-      </c>
-      <c r="N5" s="1">
-        <v>6.646703081611673</v>
-      </c>
-      <c r="O5" s="1">
-        <v>51.89873417721519</v>
-      </c>
-      <c r="P5" s="1">
-        <v>29.9318207359553</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>61.77215189873418</v>
-      </c>
-      <c r="R5" s="1">
-        <v>45.31645569620254</v>
-      </c>
-      <c r="S5" s="1" t="s">
+      <c r="H5" s="3">
+        <v>60.04</v>
+      </c>
+      <c r="I5" s="3">
+        <v>5.74</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.010524757318544712</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>-83</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-0.04457065621476075</v>
+      </c>
+      <c r="N5" s="3">
+        <v>8.268117058424279</v>
+      </c>
+      <c r="O5" s="3">
+        <v>49.36708860759494</v>
+      </c>
+      <c r="P5" s="3">
+        <v>24.00425315042111</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>58.60759493670887</v>
+      </c>
+      <c r="R5" s="3">
+        <v>46.139240506329116</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T5" s="1">
+      <c r="T5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2384,49 +2396,49 @@
         <v>51.89873417721519</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4271844660194175</v>
+        <v>1.5210355987055018</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.4</v>
+        <v>0.97</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.02516901345413544</v>
+        <v>-0.2916956064449262</v>
       </c>
       <c r="G6" s="1">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="1">
-        <v>37.91</v>
+        <v>37.12</v>
       </c>
       <c r="I6" s="1">
-        <v>-14.71</v>
+        <v>-15</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.008179825383145704</v>
+        <v>-0.008074952972190496</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="M6" s="1">
-        <v>0.03101487049878182</v>
+        <v>-0.23344469304542448</v>
       </c>
       <c r="N6" s="1">
-        <v>14.777219871183316</v>
+        <v>-10.619286624642104</v>
       </c>
       <c r="O6" s="1">
-        <v>60.75949367088608</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>38.860759493670884</v>
+        <v>34.0506329113924</v>
       </c>
       <c r="R6" s="1">
-        <v>42.08860759493671</v>
+        <v>27.341772151898734</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
@@ -2440,31 +2452,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>4.9</v>
+        <v>6.53</v>
       </c>
       <c r="C7" s="2">
-        <v>58.22784810126582</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>6.242857142857143</v>
+        <v>5.033690658499234</v>
       </c>
       <c r="E7" s="2">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>0.002445248234289321</v>
+        <v>-0.0777818404677516</v>
       </c>
       <c r="G7" s="2">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>76.18</v>
+        <v>49.41</v>
       </c>
       <c r="I7" s="2">
-        <v>26.19</v>
+        <v>12.52</v>
       </c>
       <c r="J7" s="2">
-        <v>0.02207931320336696</v>
+        <v>0.016235396994504565</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2473,22 +2485,22 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.13495440850060358</v>
+        <v>0.06435038822703265</v>
       </c>
       <c r="N7" s="2">
-        <v>25.171173671365487</v>
+        <v>19.160221502603612</v>
       </c>
       <c r="O7" s="2">
-        <v>70.88607594936708</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>64.43037974683543</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="R7" s="2">
-        <v>54.55696202531646</v>
+        <v>52.848101265822784</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
@@ -2508,49 +2520,49 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>-0.012084592145015116</v>
+        <v>0.027945619335347373</v>
       </c>
       <c r="E8" s="2">
-        <v>0.43</v>
+        <v>1.61</v>
       </c>
       <c r="F8" s="2">
-        <v>0.3224922725360976</v>
+        <v>0.21031520551401806</v>
       </c>
       <c r="G8" s="2">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>83.87</v>
+        <v>57.75</v>
       </c>
       <c r="I8" s="2">
-        <v>24.99</v>
+        <v>16.44</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03278211098778094</v>
+        <v>0.030184188099335905</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-140</v>
+        <v>-222</v>
       </c>
       <c r="M8" s="2">
-        <v>0.28644978094366014</v>
+        <v>0.16953956613436683</v>
       </c>
       <c r="N8" s="2">
-        <v>40.320710915671164</v>
+        <v>29.679139293337027</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>66.07594936708861</v>
+        <v>60.253164556962034</v>
       </c>
       <c r="R8" s="2">
-        <v>55.316455696202524</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
@@ -2560,188 +2572,188 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>0.89</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>37.9746835443038</v>
       </c>
-      <c r="D9" s="1">
-        <v>46.2247191011236</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2.14</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-0.1346267787903565</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="D9" s="3">
+        <v>46.831460674157306</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-0.04329252548487092</v>
+      </c>
+      <c r="G9" s="3">
         <v>1.49</v>
       </c>
-      <c r="H9" s="1">
-        <v>43.47</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-18.03</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-0.006101797654469959</v>
-      </c>
-      <c r="K9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>54</v>
-      </c>
-      <c r="M9" s="1">
-        <v>-0.0826831879659613</v>
-      </c>
-      <c r="N9" s="1">
-        <v>3.407414024709004</v>
-      </c>
-      <c r="O9" s="1">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="P9" s="1">
-        <v>34.04748479877408</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>48.9873417721519</v>
-      </c>
-      <c r="R9" s="1">
-        <v>41.202531645569614</v>
-      </c>
-      <c r="S9" s="1" t="s">
+      <c r="H9" s="3">
+        <v>67.42</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-3.24</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-0.008274099887544748</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>-17</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.013793369646640796</v>
+      </c>
+      <c r="N9" s="3">
+        <v>14.104519644564428</v>
+      </c>
+      <c r="O9" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P9" s="3">
+        <v>29.51342870916754</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>50.75949367088608</v>
+      </c>
+      <c r="R9" s="3">
+        <v>42.46835443037975</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="T9" s="1">
-        <v>0.25</v>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>6.25</v>
       </c>
-      <c r="C10" s="1">
-        <v>67.08860759493672</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.5408000000000002</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1.07</v>
-      </c>
-      <c r="F10" s="1">
-        <v>-0.12925719658795642</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="H10" s="1">
-        <v>55.02</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-3.13</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.0014049222467605465</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>-83</v>
-      </c>
-      <c r="M10" s="1">
-        <v>-0.08579419202060534</v>
-      </c>
-      <c r="N10" s="1">
-        <v>3.0963136192446155</v>
-      </c>
-      <c r="O10" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="P10" s="1">
+      <c r="C10" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.5663999999999999</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-0.77</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-0.21355454778760147</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>45.26</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-5.97</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.0037374607650429233</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>-131</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-0.16695381706800005</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-3.970199026899659</v>
+      </c>
+      <c r="O10" s="3">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="P10" s="3">
         <v>20.24508080818123</v>
       </c>
-      <c r="Q10" s="1">
-        <v>48.22784810126583</v>
-      </c>
-      <c r="R10" s="1">
-        <v>38.79746835443038</v>
-      </c>
-      <c r="S10" s="1" t="s">
+      <c r="Q10" s="3">
+        <v>42.911392405063296</v>
+      </c>
+      <c r="R10" s="3">
+        <v>34.74683544303798</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T10" s="1">
+      <c r="T10" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>-1.36</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12.658227848101266</v>
-      </c>
-      <c r="D11" s="1">
-        <v>31.911764705882348</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8.3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.13403760617326035</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.81</v>
-      </c>
-      <c r="H11" s="1">
-        <v>63.55</v>
-      </c>
-      <c r="I11" s="1">
-        <v>5.28</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.021033713114448644</v>
-      </c>
-      <c r="K11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>15</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0.11389621381278059</v>
-      </c>
-      <c r="N11" s="1">
-        <v>23.065354202583205</v>
-      </c>
-      <c r="O11" s="1">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="P11" s="1">
+      <c r="B11" s="2">
+        <v>-0.95</v>
+      </c>
+      <c r="C11" s="2">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46.905263157894744</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-0.88</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.1504913086342657</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.86</v>
+      </c>
+      <c r="H11" s="2">
+        <v>50.83</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5.91</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.02519102707019821</v>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <v>25</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.13418105288240523</v>
+      </c>
+      <c r="N11" s="2">
+        <v>26.143287968140882</v>
+      </c>
+      <c r="O11" s="2">
+        <v>74.68354430379746</v>
+      </c>
+      <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
-      <c r="Q11" s="1">
-        <v>53.54430379746836</v>
-      </c>
-      <c r="R11" s="1">
-        <v>46.455696202531655</v>
-      </c>
-      <c r="S11" s="1" t="s">
+      <c r="Q11" s="2">
+        <v>54.17721518987342</v>
+      </c>
+      <c r="R11" s="2">
+        <v>51.139240506329116</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T11" s="1">
+      <c r="T11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2756,49 +2768,49 @@
         <v>20.253164556962027</v>
       </c>
       <c r="D12" s="3">
-        <v>65.85294117647058</v>
+        <v>65.70588235294117</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.32</v>
+        <v>3.81</v>
       </c>
       <c r="F12" s="3">
-        <v>-0.3390113878920355</v>
+        <v>0.0638417078712054</v>
       </c>
       <c r="G12" s="3">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="H12" s="3">
-        <v>46.63</v>
+        <v>72.99</v>
       </c>
       <c r="I12" s="3">
-        <v>-38.15</v>
+        <v>-12.63</v>
       </c>
       <c r="J12" s="3">
-        <v>-0.01139281110627393</v>
+        <v>0.022522005094730492</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="3">
-        <v>-15</v>
+        <v>-51</v>
       </c>
       <c r="M12" s="3">
-        <v>-0.35809270697038476</v>
+        <v>0.05335654345929508</v>
       </c>
       <c r="N12" s="3">
-        <v>-24.133537875733335</v>
+        <v>18.060837025829855</v>
       </c>
       <c r="O12" s="3">
-        <v>5.063291139240507</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P12" s="3">
-        <v>49.67608188777989</v>
+        <v>49.122344752707264</v>
       </c>
       <c r="Q12" s="3">
-        <v>39.493670886075954</v>
+        <v>56.835443037974684</v>
       </c>
       <c r="R12" s="3">
-        <v>20.696202531645564</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>101</v>
@@ -2808,127 +2820,127 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>0.02</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>29.11392405063291</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>-1653.5</v>
       </c>
-      <c r="E13" s="3">
-        <v>2.73</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-0.1759208009707229</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1.43</v>
-      </c>
-      <c r="H13" s="3">
-        <v>53.88</v>
-      </c>
-      <c r="I13" s="3">
-        <v>5.67</v>
-      </c>
-      <c r="J13" s="3">
-        <v>-0.0026568641580235123</v>
-      </c>
-      <c r="K13" s="3" t="b">
+      <c r="E13" s="1">
+        <v>6.41</v>
+      </c>
+      <c r="F13" s="1">
+        <v>-0.3545066796092178</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="H13" s="1">
+        <v>43.21</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-8.75</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-0.0065988750880665754</v>
+      </c>
+      <c r="K13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>12</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-0.3114010036935865</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-18.414917689458296</v>
+      </c>
+      <c r="O13" s="1">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P13" s="1">
+        <v>39.74359086324119</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>18.354430379746834</v>
+      </c>
+      <c r="R13" s="1">
+        <v>4.113924050632909</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="C14" s="2">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="D14" s="2">
+        <v>6.956521739130436</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4.73</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.6114695918111009</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="H14" s="2">
+        <v>83.09</v>
+      </c>
+      <c r="I14" s="2">
+        <v>44.77</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.026147583723401546</v>
+      </c>
+      <c r="K14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="3">
-        <v>21</v>
-      </c>
-      <c r="M13" s="3">
-        <v>-0.13033764983911078</v>
-      </c>
-      <c r="N13" s="3">
-        <v>-1.3580321626059373</v>
-      </c>
-      <c r="O13" s="3">
-        <v>39.24050632911392</v>
-      </c>
-      <c r="P13" s="3">
-        <v>39.74359086324119</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>28.481012658227847</v>
-      </c>
-      <c r="R13" s="3">
-        <v>15.88607594936709</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="T13" s="3">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1.31</v>
-      </c>
-      <c r="C14" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="D14" s="1">
-        <v>7.580152671755725</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-0.11661797016911667</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H14" s="1">
-        <v>57.94</v>
-      </c>
-      <c r="I14" s="1">
-        <v>-4.21</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.010041979719406674</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>14</v>
-      </c>
-      <c r="M14" s="1">
-        <v>-0.15902090145433723</v>
-      </c>
-      <c r="N14" s="1">
-        <v>-4.226357324128582</v>
-      </c>
-      <c r="O14" s="1">
-        <v>31.645569620253166</v>
-      </c>
-      <c r="P14" s="1">
+      <c r="L14" s="2">
+        <v>12</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.5730239889674298</v>
+      </c>
+      <c r="N14" s="2">
+        <v>70.02758157664331</v>
+      </c>
+      <c r="O14" s="2">
+        <v>88.60759493670885</v>
+      </c>
+      <c r="P14" s="2">
         <v>33.10300785656511</v>
       </c>
-      <c r="Q14" s="1">
-        <v>53.92405063291139</v>
-      </c>
-      <c r="R14" s="1">
-        <v>35.189873417721515</v>
-      </c>
-      <c r="S14" s="1" t="s">
+      <c r="Q14" s="2">
+        <v>63.164556962025316</v>
+      </c>
+      <c r="R14" s="2">
+        <v>52.65822784810126</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T14" s="1">
-        <v>0.76</v>
+      <c r="T14" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2942,49 +2954,49 @@
         <v>18.9873417721519</v>
       </c>
       <c r="D15" s="2">
-        <v>62.85714285714286</v>
+        <v>63.57142857142858</v>
       </c>
       <c r="E15" s="2">
-        <v>5.78</v>
+        <v>2.23</v>
       </c>
       <c r="F15" s="2">
-        <v>1.2291696989512908</v>
+        <v>1.242646766784784</v>
       </c>
       <c r="G15" s="2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H15" s="2">
-        <v>69.51</v>
+        <v>59.19</v>
       </c>
       <c r="I15" s="2">
-        <v>161.02</v>
+        <v>133.25</v>
       </c>
       <c r="J15" s="2">
-        <v>0.12724079067001726</v>
+        <v>0.1000170746601051</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="M15" s="2">
-        <v>1.3584986393712135</v>
+        <v>1.3871090320155484</v>
       </c>
       <c r="N15" s="2">
-        <v>147.5255967584265</v>
+        <v>151.43608588145517</v>
       </c>
       <c r="O15" s="2">
-        <v>100</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P15" s="2">
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>69.49367088607595</v>
+        <v>66.96202531645571</v>
       </c>
       <c r="R15" s="2">
-        <v>61.962025316455694</v>
+        <v>60.8860759493671</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>103</v>
@@ -3001,119 +3013,119 @@
         <v>-3.53</v>
       </c>
       <c r="C16" s="1">
-        <v>8.860759493670885</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="D16" s="1">
-        <v>12.218130311614733</v>
+        <v>12.69971671388102</v>
       </c>
       <c r="E16" s="1">
-        <v>4.52</v>
+        <v>5.41</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.059777735429645346</v>
+        <v>-0.21222349880346625</v>
       </c>
       <c r="G16" s="1">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="1">
-        <v>47.33</v>
+        <v>55.28</v>
       </c>
       <c r="I16" s="1">
-        <v>2.21</v>
+        <v>5.98</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0010320582236726678</v>
+        <v>0.0010619223984947054</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M16" s="1">
-        <v>0.039869153090623</v>
+        <v>-0.10620683641637307</v>
       </c>
       <c r="N16" s="1">
-        <v>15.662648130367446</v>
+        <v>2.1044990382630337</v>
       </c>
       <c r="O16" s="1">
-        <v>63.29113924050633</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P16" s="1">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="1">
-        <v>40.63291139240506</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="R16" s="1">
-        <v>36.64556962025316</v>
+        <v>29.367088607594937</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="1">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>-6.21</v>
       </c>
-      <c r="C17" s="3">
-        <v>2.5316455696202533</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4.355877616747182</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4.89</v>
-      </c>
-      <c r="F17" s="3">
-        <v>-0.15592483762420115</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.73</v>
-      </c>
-      <c r="H17" s="3">
-        <v>45.43</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-9.15</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-0.013558713931326748</v>
-      </c>
-      <c r="K17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>32</v>
-      </c>
-      <c r="M17" s="3">
-        <v>-0.07853948802867361</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3.8217840184377816</v>
-      </c>
-      <c r="O17" s="3">
-        <v>46.835443037974684</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="C17" s="1">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5.15780998389694</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-0.27930952257210306</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="H17" s="1">
+        <v>60.77</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.00950051872316976</v>
+      </c>
+      <c r="K17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>24</v>
+      </c>
+      <c r="M17" s="1">
+        <v>-0.19309817074084046</v>
+      </c>
+      <c r="N17" s="1">
+        <v>-6.584634394183697</v>
+      </c>
+      <c r="O17" s="1">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="P17" s="1">
         <v>28.182703357372183</v>
       </c>
-      <c r="Q17" s="3">
-        <v>24.55696202531646</v>
-      </c>
-      <c r="R17" s="3">
-        <v>23.164556962025316</v>
-      </c>
-      <c r="S17" s="3" t="s">
+      <c r="Q17" s="1">
+        <v>37.721518987341774</v>
+      </c>
+      <c r="R17" s="1">
+        <v>21.455696202531644</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3131,113 +3143,113 @@
         <v>1446.3333333333333</v>
       </c>
       <c r="E18" s="1">
-        <v>9.43</v>
+        <v>6.73</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.31769757444430774</v>
+        <v>-0.3488057381222238</v>
       </c>
       <c r="G18" s="1">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="H18" s="1">
-        <v>34.31</v>
+        <v>31.33</v>
       </c>
       <c r="I18" s="1">
-        <v>-9.92</v>
+        <v>-17.39</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.008678430354633865</v>
+        <v>-0.008703234626623722</v>
       </c>
       <c r="K18" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.2933158889553059</v>
+        <v>-0.33016544583438323</v>
       </c>
       <c r="N18" s="1">
-        <v>-17.65585607422545</v>
+        <v>-20.291361903537975</v>
       </c>
       <c r="O18" s="1">
-        <v>8.860759493670885</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P18" s="1">
-        <v>30.65938429567125</v>
+        <v>35.65728669277035</v>
       </c>
       <c r="Q18" s="1">
-        <v>48.22784810126582</v>
+        <v>42.151898734177216</v>
       </c>
       <c r="R18" s="1">
-        <v>30.949367088607595</v>
+        <v>27.15189873417722</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T18" s="1">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="3">
         <v>9.32</v>
       </c>
-      <c r="C19" s="1">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.2027896995708155</v>
-      </c>
-      <c r="E19" s="1">
-        <v>-0.43</v>
-      </c>
-      <c r="F19" s="1">
-        <v>-0.04984014908398787</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="H19" s="1">
-        <v>53.67</v>
-      </c>
-      <c r="I19" s="1">
-        <v>15.22</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.0049513249802427125</v>
-      </c>
-      <c r="K19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <v>71</v>
-      </c>
-      <c r="M19" s="1">
-        <v>-0.13358593837229848</v>
-      </c>
-      <c r="N19" s="1">
-        <v>-1.6828610159247124</v>
-      </c>
-      <c r="O19" s="1">
-        <v>37.9746835443038</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="C19" s="3">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.24463519313304713</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-1.48</v>
+      </c>
+      <c r="F19" s="3">
+        <v>-0.012259141732558751</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>56.43</v>
+      </c>
+      <c r="I19" s="3">
+        <v>14.92</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.006347842570531851</v>
+      </c>
+      <c r="K19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>80</v>
+      </c>
+      <c r="M19" s="3">
+        <v>-0.10546060317176154</v>
+      </c>
+      <c r="N19" s="3">
+        <v>2.1791223627242005</v>
+      </c>
+      <c r="O19" s="3">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="P19" s="3">
         <v>14.335419717590279</v>
       </c>
-      <c r="Q19" s="1">
-        <v>52.911392405063296</v>
-      </c>
-      <c r="R19" s="1">
-        <v>40.8860759493671</v>
-      </c>
-      <c r="S19" s="1" t="s">
+      <c r="Q19" s="3">
+        <v>51.0126582278481</v>
+      </c>
+      <c r="R19" s="3">
+        <v>41.64556962025317</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T19" s="1">
+      <c r="T19" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3249,52 +3261,52 @@
         <v>6.07</v>
       </c>
       <c r="C20" s="3">
-        <v>65.82278481012658</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="D20" s="3">
-        <v>0.9456342668863262</v>
+        <v>0.6820428336079079</v>
       </c>
       <c r="E20" s="3">
-        <v>-2.3</v>
+        <v>6.54</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.27936579590574756</v>
+        <v>-0.015484411673298337</v>
       </c>
       <c r="G20" s="3">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H20" s="3">
-        <v>33.21</v>
+        <v>68.83</v>
       </c>
       <c r="I20" s="3">
-        <v>-15.87</v>
+        <v>6.47</v>
       </c>
       <c r="J20" s="3">
-        <v>-0.01222796653113952</v>
+        <v>0.014425078428826888</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="M20" s="3">
-        <v>-0.276185576059356</v>
+        <v>-0.004999247261388007</v>
       </c>
       <c r="N20" s="3">
-        <v>-15.942824784630464</v>
+        <v>12.22525795376155</v>
       </c>
       <c r="O20" s="3">
-        <v>12.658227848101266</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P20" s="3">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="3">
-        <v>37.72151898734177</v>
+        <v>55.189873417721515</v>
       </c>
       <c r="R20" s="3">
-        <v>27.405063291139236</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>105</v>
@@ -3304,189 +3316,189 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>1.02</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>41.77215189873418</v>
       </c>
-      <c r="D21" s="1">
-        <v>13.990196078431373</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5.19</v>
-      </c>
-      <c r="F21" s="1">
-        <v>-0.06563929377820135</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="H21" s="1">
-        <v>75.01</v>
-      </c>
-      <c r="I21" s="1">
-        <v>31.41</v>
-      </c>
-      <c r="J21" s="1">
-        <v>-0.00912194805209317</v>
-      </c>
-      <c r="K21" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>18</v>
-      </c>
-      <c r="M21" s="1">
-        <v>-0.033837095314285914</v>
-      </c>
-      <c r="N21" s="1">
-        <v>8.29202328987655</v>
-      </c>
-      <c r="O21" s="1">
-        <v>53.16455696202531</v>
-      </c>
-      <c r="P21" s="1">
+      <c r="D21" s="2">
+        <v>13.549019607843137</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2.47</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.4212347088280941</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.59</v>
+      </c>
+      <c r="H21" s="2">
+        <v>77.36</v>
+      </c>
+      <c r="I21" s="2">
+        <v>81.08</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.061494802984585206</v>
+      </c>
+      <c r="K21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>37</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.4899707866395062</v>
+      </c>
+      <c r="N21" s="2">
+        <v>61.72226134385096</v>
+      </c>
+      <c r="O21" s="2">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
-      <c r="Q21" s="1">
-        <v>55.44303797468354</v>
-      </c>
-      <c r="R21" s="1">
-        <v>38.79746835443038</v>
-      </c>
-      <c r="S21" s="1" t="s">
+      <c r="Q21" s="2">
+        <v>70.50632911392405</v>
+      </c>
+      <c r="R21" s="2">
+        <v>55.822784810126585</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T21" s="1">
-        <v>-0.51</v>
+      <c r="T21" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="3">
         <v>8.11</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>70.88607594936708</v>
       </c>
-      <c r="D22" s="1">
-        <v>0.6954377311960543</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-0.22745346460144902</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="H22" s="1">
-        <v>46.93</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-3.08</v>
-      </c>
-      <c r="J22" s="1">
-        <v>-0.014743973448483924</v>
-      </c>
-      <c r="K22" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
-        <v>96</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.18929082644475048</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-7.253349823169911</v>
-      </c>
-      <c r="O22" s="1">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="D22" s="3">
+        <v>0.7016029593094947</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-0.84</v>
+      </c>
+      <c r="F22" s="3">
+        <v>-0.22557499416717403</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="H22" s="3">
+        <v>66.11</v>
+      </c>
+      <c r="I22" s="3">
+        <v>7.54</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.004467482710446037</v>
+      </c>
+      <c r="K22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>57</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-0.18130429998355269</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-5.405247318454922</v>
+      </c>
+      <c r="O22" s="3">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="P22" s="3">
         <v>20.966620085005058</v>
       </c>
-      <c r="Q22" s="1">
-        <v>40.75949367088608</v>
-      </c>
-      <c r="R22" s="1">
-        <v>30.253164556962027</v>
-      </c>
-      <c r="S22" s="1" t="s">
+      <c r="Q22" s="3">
+        <v>54.55696202531645</v>
+      </c>
+      <c r="R22" s="3">
+        <v>36.075949367088604</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T22" s="1">
-        <v>0.38</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="3">
         <v>27.51</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="3">
         <v>97.46835443037975</v>
       </c>
-      <c r="D23" s="1">
-        <v>-0.7593602326426754</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-0.52</v>
-      </c>
-      <c r="F23" s="1">
-        <v>-0.19121337686215006</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="H23" s="1">
-        <v>47.35</v>
-      </c>
-      <c r="I23" s="1">
-        <v>-8.12</v>
-      </c>
-      <c r="J23" s="1">
-        <v>-0.0075053643476327555</v>
-      </c>
-      <c r="K23" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>29</v>
-      </c>
-      <c r="M23" s="1">
-        <v>-0.1657716180910177</v>
-      </c>
-      <c r="N23" s="1">
-        <v>-4.901428987796632</v>
-      </c>
-      <c r="O23" s="1">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="P23" s="1">
+      <c r="D23" s="3">
+        <v>-0.772446383133406</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.17822260425121553</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="H23" s="3">
+        <v>55.36</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-5.11</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.00025809824374163577</v>
+      </c>
+      <c r="K23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>21</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-0.1514271840874447</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-2.417535728844126</v>
+      </c>
+      <c r="O23" s="3">
+        <v>35.44303797468354</v>
+      </c>
+      <c r="P23" s="3">
         <v>28.794141696367475</v>
       </c>
-      <c r="Q23" s="1">
-        <v>45.31645569620253</v>
-      </c>
-      <c r="R23" s="1">
-        <v>31.962025316455694</v>
-      </c>
-      <c r="S23" s="1" t="s">
+      <c r="Q23" s="3">
+        <v>46.9620253164557</v>
+      </c>
+      <c r="R23" s="3">
+        <v>35</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T23" s="1">
-        <v>-0.38</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3500,49 +3512,49 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.3107569721115539</v>
+        <v>-0.009462151394422375</v>
       </c>
       <c r="E24" s="1">
-        <v>9.38</v>
+        <v>9.47</v>
       </c>
       <c r="F24" s="1">
-        <v>0.15592581430995772</v>
+        <v>-0.18884719531315047</v>
       </c>
       <c r="G24" s="1">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="H24" s="1">
-        <v>62.41</v>
+        <v>45.8</v>
       </c>
       <c r="I24" s="1">
-        <v>-12.59</v>
+        <v>-23.4</v>
       </c>
       <c r="J24" s="1">
-        <v>0.035040529196603526</v>
+        <v>0.00898746435782413</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>33</v>
+        <v>-12</v>
       </c>
       <c r="M24" s="1">
-        <v>0.42836464781749983</v>
+        <v>0.10124235341636822</v>
       </c>
       <c r="N24" s="1">
-        <v>54.512197603055135</v>
+        <v>22.84941802153716</v>
       </c>
       <c r="O24" s="1">
-        <v>88.60759493670885</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P24" s="1">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="1">
-        <v>31.39240506329114</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="R24" s="1">
-        <v>31.0126582278481</v>
+        <v>23.037974683544306</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>92</v>
@@ -3552,251 +3564,251 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>-2.28</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>11.39240506329114</v>
       </c>
-      <c r="D25" s="3">
-        <v>0.8859649122807016</v>
-      </c>
-      <c r="E25" s="3">
-        <v>11.91</v>
-      </c>
-      <c r="F25" s="3">
-        <v>-0.3761670267637076</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2.23</v>
-      </c>
-      <c r="H25" s="3">
-        <v>50.29</v>
-      </c>
-      <c r="I25" s="3">
-        <v>-49.54</v>
-      </c>
-      <c r="J25" s="3">
-        <v>-0.003975544961099383</v>
-      </c>
-      <c r="K25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <v>48</v>
-      </c>
-      <c r="M25" s="3">
-        <v>-0.24577801306165437</v>
-      </c>
-      <c r="N25" s="3">
-        <v>-12.902068484860301</v>
-      </c>
-      <c r="O25" s="3">
-        <v>16.455696202531644</v>
-      </c>
-      <c r="P25" s="3">
+      <c r="D25" s="1">
+        <v>-7.149122807017544</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11.95</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-0.28106182439222227</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="H25" s="1">
+        <v>56.14</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-43.5</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.0009599595740895468</v>
+      </c>
+      <c r="K25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>41</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-0.1412596322334181</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-1.4007805434414595</v>
+      </c>
+      <c r="O25" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P25" s="1">
         <v>55.620154465672535</v>
       </c>
-      <c r="Q25" s="3">
-        <v>28.101265822784814</v>
-      </c>
-      <c r="R25" s="3">
-        <v>11.962025316455694</v>
-      </c>
-      <c r="S25" s="3" t="s">
+      <c r="Q25" s="1">
+        <v>17.088607594936708</v>
+      </c>
+      <c r="R25" s="1">
+        <v>9.113924050632914</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="T25" s="3">
-        <v>-0.38</v>
+      <c r="T25" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="3">
         <v>-0.17</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="3">
         <v>24.050632911392405</v>
       </c>
-      <c r="D26" s="1">
-        <v>-2571.7647058823527</v>
-      </c>
-      <c r="E26" s="1">
-        <v>4.67</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.4878708588671728</v>
-      </c>
-      <c r="G26" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="H26" s="1">
-        <v>69.42</v>
-      </c>
-      <c r="I26" s="1">
-        <v>21.77</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.044615350892172945</v>
-      </c>
-      <c r="K26" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>-11</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.7062459549860587</v>
-      </c>
-      <c r="N26" s="1">
-        <v>82.300328319911</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="D26" s="3">
+        <v>-2529.3529411764703</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.4993946026358366</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.16</v>
+      </c>
+      <c r="H26" s="3">
+        <v>75.54</v>
+      </c>
+      <c r="I26" s="3">
+        <v>50.65</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.08421282073972343</v>
+      </c>
+      <c r="K26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-29</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0.7510385485216842</v>
+      </c>
+      <c r="N26" s="3">
+        <v>87.82903753206877</v>
+      </c>
+      <c r="O26" s="3">
         <v>91.13924050632912</v>
       </c>
-      <c r="P26" s="1">
-        <v>50.63126652197354</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>41.01265822784811</v>
-      </c>
-      <c r="R26" s="1">
-        <v>33.037974683544306</v>
-      </c>
-      <c r="S26" s="1" t="s">
+      <c r="P26" s="3">
+        <v>47.81158046237125</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>43.79746835443038</v>
+      </c>
+      <c r="R26" s="3">
+        <v>33.79746835443038</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T26" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>-1.13</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1.0176991150442478</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8.19</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-0.14007239858826454</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.68</v>
+      </c>
+      <c r="H27" s="1">
+        <v>65.28</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-7.39</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.020234889150990233</v>
+      </c>
+      <c r="K27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>42</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0.055650670434061356</v>
+      </c>
+      <c r="N27" s="1">
+        <v>18.29024972330648</v>
+      </c>
+      <c r="O27" s="1">
+        <v>62.0253164556962</v>
+      </c>
+      <c r="P27" s="1">
+        <v>51.28834092723359</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>39.620253164556964</v>
+      </c>
+      <c r="R27" s="1">
+        <v>29.050632911392405</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="1">
         <v>13.924050632911392</v>
       </c>
-      <c r="D27" s="3">
-        <v>1.0176991150442478</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-0.20457969183921387</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="H27" s="3">
-        <v>60.75</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-18.72</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0.00800169742756051</v>
-      </c>
-      <c r="K27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>37</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-0.03178774685194008</v>
-      </c>
-      <c r="N27" s="3">
-        <v>8.496958136111138</v>
-      </c>
-      <c r="O27" s="3">
-        <v>54.43037974683544</v>
-      </c>
-      <c r="P27" s="3">
-        <v>51.28834092723359</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>36.58227848101266</v>
-      </c>
-      <c r="R27" s="3">
-        <v>26.392405063291136</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T27" s="3">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-1.1</v>
-      </c>
-      <c r="C28" s="3">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="D28" s="3">
-        <v>7.536363636363636</v>
-      </c>
-      <c r="E28" s="3">
-        <v>-0.68</v>
-      </c>
-      <c r="F28" s="3">
-        <v>-0.3879769225383227</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="D28" s="1">
+        <v>7.899999999999999</v>
+      </c>
+      <c r="E28" s="1">
+        <v>-4.03</v>
+      </c>
+      <c r="F28" s="1">
+        <v>-0.4201050546548008</v>
+      </c>
+      <c r="G28" s="1">
         <v>3.14</v>
       </c>
-      <c r="H28" s="3">
-        <v>59.66</v>
-      </c>
-      <c r="I28" s="3">
-        <v>-20.69</v>
-      </c>
-      <c r="J28" s="3">
-        <v>-0.010456960261449664</v>
-      </c>
-      <c r="K28" s="3" t="b">
+      <c r="H28" s="1">
+        <v>64.22</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-14.65</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.008355306124368026</v>
+      </c>
+      <c r="K28" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L28" s="3">
-        <v>28</v>
-      </c>
-      <c r="M28" s="3">
-        <v>-0.1611212401623927</v>
-      </c>
-      <c r="N28" s="3">
-        <v>-4.436391194934127</v>
-      </c>
-      <c r="O28" s="3">
-        <v>30.37974683544304</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="L28" s="1">
+        <v>-3</v>
+      </c>
+      <c r="M28" s="1">
+        <v>-0.17079114530493333</v>
+      </c>
+      <c r="N28" s="1">
+        <v>-4.3539318505929865</v>
+      </c>
+      <c r="O28" s="1">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="P28" s="1">
         <v>45.17203183430412</v>
       </c>
-      <c r="Q28" s="3">
-        <v>34.68354430379746</v>
-      </c>
-      <c r="R28" s="3">
-        <v>21.898734177215193</v>
-      </c>
-      <c r="S28" s="3" t="s">
+      <c r="Q28" s="1">
+        <v>41.139240506329116</v>
+      </c>
+      <c r="R28" s="1">
+        <v>24.367088607594937</v>
+      </c>
+      <c r="S28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T28" s="3">
-        <v>-0.38</v>
+      <c r="T28" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3810,49 +3822,49 @@
         <v>34.177215189873415</v>
       </c>
       <c r="D29" s="3">
-        <v>77.04545454545456</v>
+        <v>79.00000000000001</v>
       </c>
       <c r="E29" s="3">
-        <v>0.62</v>
+        <v>1.51</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.4139591068760087</v>
+        <v>-0.23183302379674658</v>
       </c>
       <c r="G29" s="3">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>42.5</v>
+        <v>64.04</v>
       </c>
       <c r="I29" s="3">
-        <v>-32.51</v>
+        <v>-21.51</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.015534149204213981</v>
+        <v>-0.005570205553820807</v>
       </c>
       <c r="K29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3">
-        <v>-12</v>
+        <v>-69</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.29629097255952164</v>
+        <v>-0.10135097778186264</v>
       </c>
       <c r="N29" s="3">
-        <v>-17.953364434647018</v>
+        <v>2.59008490171409</v>
       </c>
       <c r="O29" s="3">
-        <v>7.59493670886076</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.13924050632911</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R29" s="3">
-        <v>24.36708860759493</v>
+        <v>37.215189873417714</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
@@ -3862,65 +3874,65 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="3">
         <v>1.95</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="3">
         <v>46.835443037974684</v>
       </c>
-      <c r="D30" s="1">
-        <v>1656.8153846153846</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2.13</v>
-      </c>
-      <c r="F30" s="1">
-        <v>-0.17095955682866515</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.21</v>
-      </c>
-      <c r="H30" s="1">
-        <v>54.01</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5.44</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0.004296700252854999</v>
-      </c>
-      <c r="K30" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <v>39</v>
-      </c>
-      <c r="M30" s="1">
-        <v>-0.14869801790392434</v>
-      </c>
-      <c r="N30" s="1">
-        <v>-3.1940689690872945</v>
-      </c>
-      <c r="O30" s="1">
-        <v>34.177215189873415</v>
-      </c>
-      <c r="P30" s="1">
+      <c r="D30" s="3">
+        <v>1500.169230769231</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-0.13347720537409605</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H30" s="3">
+        <v>56.23</v>
+      </c>
+      <c r="I30" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.007093702256404355</v>
+      </c>
+      <c r="K30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>24</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-0.11134185828228538</v>
+      </c>
+      <c r="N30" s="3">
+        <v>1.590996851671801</v>
+      </c>
+      <c r="O30" s="3">
+        <v>40.50632911392405</v>
+      </c>
+      <c r="P30" s="3">
         <v>24.961328061128594</v>
       </c>
-      <c r="Q30" s="1">
-        <v>64.9367088607595</v>
-      </c>
-      <c r="R30" s="1">
-        <v>47.53164556962025</v>
-      </c>
-      <c r="S30" s="1" t="s">
+      <c r="Q30" s="3">
+        <v>63.164556962025316</v>
+      </c>
+      <c r="R30" s="3">
+        <v>48.79746835443037</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T30" s="1">
-        <v>0.38</v>
+      <c r="T30" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3931,306 +3943,306 @@
         <v>5.13</v>
       </c>
       <c r="C31" s="2">
-        <v>59.49367088607595</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="D31" s="2">
-        <v>10.688109161793372</v>
+        <v>11.124756335282651</v>
       </c>
       <c r="E31" s="2">
-        <v>0.9</v>
+        <v>0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>0.14893465812358012</v>
+        <v>0.22310480281016756</v>
       </c>
       <c r="G31" s="2">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H31" s="2">
-        <v>64.78</v>
+        <v>65.92</v>
       </c>
       <c r="I31" s="2">
-        <v>25.69</v>
+        <v>26.81</v>
       </c>
       <c r="J31" s="2">
-        <v>0.030128371718951562</v>
+        <v>0.027222409406160743</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="M31" s="2">
-        <v>0.19451780925519224</v>
+        <v>0.270870551797759</v>
       </c>
       <c r="N31" s="2">
-        <v>31.12751374682437</v>
+        <v>39.812237859676245</v>
       </c>
       <c r="O31" s="2">
-        <v>78.48101265822784</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>68.35443037974683</v>
+        <v>67.59493670886076</v>
       </c>
       <c r="R31" s="2">
-        <v>60.822784810126585</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>-2.92</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>10.126582278481013</v>
       </c>
-      <c r="D32" s="3">
-        <v>8.178082191780822</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1.69</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-0.13320749908480836</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1.61</v>
-      </c>
-      <c r="H32" s="3">
-        <v>43.93</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-4.28</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-0.006102937885637886</v>
-      </c>
-      <c r="K32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>26</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-0.06854302887484698</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4.821429933820452</v>
-      </c>
-      <c r="O32" s="3">
-        <v>49.36708860759494</v>
-      </c>
-      <c r="P32" s="3">
-        <v>38.84187494148391</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>36.32911392405064</v>
-      </c>
-      <c r="R32" s="3">
-        <v>29.36708860759494</v>
-      </c>
-      <c r="S32" s="3" t="s">
+      <c r="D32" s="1">
+        <v>8.041095890410958</v>
+      </c>
+      <c r="E32" s="1">
+        <v>-2.98</v>
+      </c>
+      <c r="F32" s="1">
+        <v>-0.13387834243600763</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H32" s="1">
+        <v>63.34</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5.62</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.002650891559893463</v>
+      </c>
+      <c r="K32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>23</v>
+      </c>
+      <c r="M32" s="1">
+        <v>-0.06397724635660551</v>
+      </c>
+      <c r="N32" s="1">
+        <v>6.327458044239788</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P32" s="1">
+        <v>35.692921425886716</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>40.50632911392406</v>
+      </c>
+      <c r="R32" s="1">
+        <v>28.22784810126582</v>
+      </c>
+      <c r="S32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T32" s="3">
-        <v>-0.38</v>
+      <c r="T32" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="3">
         <v>16.79</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="3">
         <v>88.60759493670885</v>
       </c>
-      <c r="D33" s="1">
-        <v>-0.05777248362120303</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="F33" s="1">
-        <v>-0.10754673419165842</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="D33" s="3">
+        <v>-0.06611078022632516</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-0.44</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.008670304785823923</v>
+      </c>
+      <c r="G33" s="3">
         <v>1.09</v>
       </c>
-      <c r="H33" s="1">
-        <v>50.21</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-11.71</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.0024125422671207788</v>
-      </c>
-      <c r="K33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>84</v>
-      </c>
-      <c r="M33" s="1">
-        <v>-0.09800607465248379</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1.8751253560567682</v>
-      </c>
-      <c r="O33" s="1">
-        <v>43.037974683544306</v>
-      </c>
-      <c r="P33" s="1">
-        <v>26.894390179645494</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>49.62025316455696</v>
-      </c>
-      <c r="R33" s="1">
-        <v>39.9367088607595</v>
-      </c>
-      <c r="S33" s="1" t="s">
+      <c r="H33" s="3">
+        <v>69.59</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1.79</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.006795185819069533</v>
+      </c>
+      <c r="K33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0.019155469197734254</v>
+      </c>
+      <c r="N33" s="3">
+        <v>14.640729599673765</v>
+      </c>
+      <c r="O33" s="3">
+        <v>56.9620253164557</v>
+      </c>
+      <c r="P33" s="3">
+        <v>26.22927244204992</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>53.417721518987335</v>
+      </c>
+      <c r="R33" s="3">
+        <v>43.291139240506325</v>
+      </c>
+      <c r="S33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T33" s="1">
-        <v>0.38</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>13.11</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>84.81012658227847</v>
       </c>
-      <c r="D34" s="2">
-        <v>-0.6453089244851258</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0.58</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.15231508251016168</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1.26</v>
-      </c>
-      <c r="H34" s="2">
-        <v>75.21</v>
-      </c>
-      <c r="I34" s="2">
-        <v>38.55</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0.02781949782545467</v>
-      </c>
-      <c r="K34" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2">
-        <v>151</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0.17987698784555506</v>
-      </c>
-      <c r="N34" s="2">
-        <v>29.66343160586064</v>
-      </c>
-      <c r="O34" s="2">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="D34" s="3">
+        <v>-0.7360793287566743</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.06359957185168871</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H34" s="3">
+        <v>52.9</v>
+      </c>
+      <c r="I34" s="3">
+        <v>26.81</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.023628206004680925</v>
+      </c>
+      <c r="K34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>35</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0.0927250285514396</v>
+      </c>
+      <c r="N34" s="3">
+        <v>21.99768553504431</v>
+      </c>
+      <c r="O34" s="3">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P34" s="3">
         <v>20.42247430615109</v>
       </c>
-      <c r="Q34" s="2">
-        <v>61.39240506329114</v>
-      </c>
-      <c r="R34" s="2">
-        <v>51.139240506329116</v>
-      </c>
-      <c r="S34" s="2" t="s">
+      <c r="Q34" s="3">
+        <v>53.79746835443038</v>
+      </c>
+      <c r="R34" s="3">
+        <v>47.21518987341773</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T34" s="2">
-        <v>0.89</v>
+      <c r="T34" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>17.37</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>91.13924050632912</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="1">
         <v>-0.47898675877950486</v>
       </c>
-      <c r="E35" s="3">
-        <v>-0.96</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-0.3181429691881079</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3">
-        <v>26.9</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-25.05</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-0.024684340384122497</v>
-      </c>
-      <c r="K35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>44</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-0.3181429691881079</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-20.138564097505654</v>
-      </c>
-      <c r="O35" s="3">
-        <v>6.329113924050633</v>
-      </c>
-      <c r="P35" s="3">
-        <v>30.4559601123391</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>32.911392405063296</v>
-      </c>
-      <c r="R35" s="3">
-        <v>21.582278481012658</v>
-      </c>
-      <c r="S35" s="3" t="s">
+      <c r="E35" s="1">
+        <v>9.42</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-0.35331368354013404</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="H35" s="1">
+        <v>35.98</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-22.28</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-0.022884000834602305</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>18</v>
+      </c>
+      <c r="M35" s="1">
+        <v>-0.3556437200761141</v>
+      </c>
+      <c r="N35" s="1">
+        <v>-22.83918932771106</v>
+      </c>
+      <c r="O35" s="1">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="P35" s="1">
+        <v>28.919768290867083</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>33.164556962025316</v>
+      </c>
+      <c r="R35" s="1">
+        <v>21.455696202531644</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T35" s="3">
-        <v>-0.38</v>
+      <c r="T35" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4241,58 +4253,58 @@
         <v>11.51</v>
       </c>
       <c r="C36" s="1">
-        <v>82.27848101265823</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="D36" s="1">
-        <v>0.38488271068635965</v>
+        <v>0.3588184187662903</v>
       </c>
       <c r="E36" s="1">
-        <v>-0.97</v>
+        <v>3.24</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.13120568027183452</v>
+        <v>-0.26545011191909035</v>
       </c>
       <c r="G36" s="1">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="H36" s="1">
-        <v>38.9</v>
+        <v>48.45</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.19</v>
+        <v>-10.98</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.011964198390205084</v>
+        <v>-0.0051308850552891794</v>
       </c>
       <c r="K36" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-19</v>
+        <v>-55</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.11848480088626834</v>
+        <v>-0.25496494750718</v>
       </c>
       <c r="N36" s="1">
-        <v>-0.17274726732169896</v>
+        <v>-12.771312070817654</v>
       </c>
       <c r="O36" s="1">
-        <v>40.50632911392405</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="1">
-        <v>39.99999999999999</v>
+        <v>42.91139240506329</v>
       </c>
       <c r="R36" s="1">
-        <v>34.30379746835443</v>
+        <v>27.658227848101266</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4303,52 +4315,52 @@
         <v>5.33</v>
       </c>
       <c r="C37" s="1">
-        <v>63.29113924050633</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="D37" s="1">
-        <v>0.598499061913696</v>
+        <v>0.6022514071294557</v>
       </c>
       <c r="E37" s="1">
-        <v>0.52</v>
+        <v>-5.1</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.0008221176373724437</v>
+        <v>-0.1996223398726307</v>
       </c>
       <c r="G37" s="1">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H37" s="1">
-        <v>38.49</v>
+        <v>42.61</v>
       </c>
       <c r="I37" s="1">
-        <v>-21.87</v>
+        <v>-21.16</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.0017925280106526717</v>
+        <v>-0.001732836675708791</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-134</v>
+        <v>-214</v>
       </c>
       <c r="M37" s="1">
-        <v>0.039460667083587087</v>
+        <v>-0.15884670049297944</v>
       </c>
       <c r="N37" s="1">
-        <v>15.621799529663857</v>
+        <v>-3.1594873693975916</v>
       </c>
       <c r="O37" s="1">
-        <v>62.0253164556962</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P37" s="1">
-        <v>36.27914452259746</v>
+        <v>34.65975433248125</v>
       </c>
       <c r="Q37" s="1">
-        <v>39.11392405063292</v>
+        <v>37.72151898734178</v>
       </c>
       <c r="R37" s="1">
-        <v>38.797468354430386</v>
+        <v>29.55696202531646</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
@@ -4368,49 +4380,49 @@
         <v>16.455696202531644</v>
       </c>
       <c r="D38" s="2">
-        <v>36.648648648648646</v>
+        <v>36.729729729729726</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.1</v>
+        <v>-0.57</v>
       </c>
       <c r="F38" s="2">
-        <v>0.27827678266224054</v>
+        <v>0.8146071669737149</v>
       </c>
       <c r="G38" s="2">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>81.02</v>
+        <v>83.8</v>
       </c>
       <c r="I38" s="2">
-        <v>26.02</v>
+        <v>55.45</v>
       </c>
       <c r="J38" s="2">
-        <v>0.038804206935551595</v>
+        <v>0.05262778917701331</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-13</v>
+        <v>-45</v>
       </c>
       <c r="M38" s="2">
-        <v>0.2888775154835457</v>
+        <v>0.8379075323335157</v>
       </c>
       <c r="N38" s="2">
-        <v>40.56348436965971</v>
+        <v>96.51593591325192</v>
       </c>
       <c r="O38" s="2">
-        <v>86.07594936708861</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P38" s="2">
-        <v>28.305323956526895</v>
+        <v>26.865173556258448</v>
       </c>
       <c r="Q38" s="2">
-        <v>64.55696202531647</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="R38" s="2">
-        <v>53.92405063291139</v>
+        <v>55.949367088607595</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
@@ -4420,64 +4432,64 @@
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
-        <v>-0.18</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="B39" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="C39" s="3">
         <v>22.78481012658228</v>
       </c>
-      <c r="D39" s="2">
-        <v>100</v>
-      </c>
-      <c r="E39" s="2">
-        <v>-7.97</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0.09070062691011735</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="H39" s="2">
-        <v>51.1</v>
-      </c>
-      <c r="I39" s="2">
-        <v>9.01</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0.01990433112361712</v>
-      </c>
-      <c r="K39" s="2" t="b">
+      <c r="D39" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="E39" s="3">
+        <v>6.03</v>
+      </c>
+      <c r="F39" s="3">
+        <v>-0.16106483974385025</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="H39" s="3">
+        <v>31.09</v>
+      </c>
+      <c r="I39" s="3">
+        <v>-10.83</v>
+      </c>
+      <c r="J39" s="3">
+        <v>-0.00005971426348136263</v>
+      </c>
+      <c r="K39" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L39" s="2">
-        <v>-14</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0.12250282537403279</v>
-      </c>
-      <c r="N39" s="2">
-        <v>23.92601535870843</v>
-      </c>
-      <c r="O39" s="2">
-        <v>69.62025316455697</v>
-      </c>
-      <c r="P39" s="2">
-        <v>18.299999237060547</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>57.46835443037974</v>
-      </c>
-      <c r="R39" s="2">
-        <v>53.41772151898734</v>
-      </c>
-      <c r="S39" s="2" t="s">
+      <c r="L39" s="3">
+        <v>-4</v>
+      </c>
+      <c r="M39" s="3">
+        <v>-0.13426941958007943</v>
+      </c>
+      <c r="N39" s="3">
+        <v>-0.7017592781075979</v>
+      </c>
+      <c r="O39" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="P39" s="3">
+        <v>23.417722010155686</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>42.025316455696206</v>
+      </c>
+      <c r="R39" s="3">
+        <v>37.848101265822784</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4486,247 +4498,247 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>-4.08</v>
+        <v>-6.41</v>
       </c>
       <c r="C40" s="1">
-        <v>5.063291139240507</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>16.730392156862745</v>
+        <v>10.182527301092042</v>
       </c>
       <c r="E40" s="1">
-        <v>12.27</v>
+        <v>2.22</v>
       </c>
       <c r="F40" s="1">
-        <v>0.2721261109960245</v>
+        <v>0.10138764021048279</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>49.27</v>
+        <v>41.02</v>
       </c>
       <c r="I40" s="1">
-        <v>-10.63</v>
+        <v>-21.96</v>
       </c>
       <c r="J40" s="1">
-        <v>0.02361688973368183</v>
+        <v>-0.008086445195954525</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M40" s="1">
-        <v>0.1661187827829731</v>
+        <v>-0.015114186588520706</v>
       </c>
       <c r="N40" s="1">
-        <v>28.28761109960246</v>
+        <v>11.213764021048283</v>
       </c>
       <c r="O40" s="1">
-        <v>74.68354430379746</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P40" s="1">
-        <v>45.29877115964868</v>
+        <v>39.97107065255327</v>
       </c>
       <c r="Q40" s="1">
-        <v>45.18987341772152</v>
+        <v>25.44303797468354</v>
       </c>
       <c r="R40" s="1">
-        <v>40.75949367088608</v>
+        <v>25.886075949367083</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="3">
         <v>-5.03</v>
       </c>
-      <c r="C41" s="1">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="D41" s="1">
-        <v>7.34990059642147</v>
-      </c>
-      <c r="E41" s="1">
-        <v>-1.75</v>
-      </c>
-      <c r="F41" s="1">
-        <v>-0.012992593659218676</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.11</v>
-      </c>
-      <c r="H41" s="1">
-        <v>76.88</v>
-      </c>
-      <c r="I41" s="1">
-        <v>-5.99</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0.016911260218543354</v>
-      </c>
-      <c r="K41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>5</v>
-      </c>
-      <c r="M41" s="1">
-        <v>-0.001331787555783004</v>
-      </c>
-      <c r="N41" s="1">
-        <v>11.542554065726831</v>
-      </c>
-      <c r="O41" s="1">
-        <v>56.9620253164557</v>
-      </c>
-      <c r="P41" s="1">
+      <c r="C41" s="3">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="D41" s="3">
+        <v>7.121272365805169</v>
+      </c>
+      <c r="E41" s="3">
+        <v>-1.06</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.07749513392864157</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.15</v>
+      </c>
+      <c r="H41" s="3">
+        <v>64.49</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-5.63</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0.030257333663119494</v>
+      </c>
+      <c r="K41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0.0949704079484921</v>
+      </c>
+      <c r="N41" s="3">
+        <v>22.222223474749555</v>
+      </c>
+      <c r="O41" s="3">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="P41" s="3">
         <v>46.4052282234621</v>
       </c>
-      <c r="Q41" s="1">
-        <v>44.30379746835443</v>
-      </c>
-      <c r="R41" s="1">
-        <v>30.063291139240505</v>
-      </c>
-      <c r="S41" s="1" t="s">
+      <c r="Q41" s="3">
+        <v>45.82278481012659</v>
+      </c>
+      <c r="R41" s="3">
+        <v>35.69620253164557</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T41" s="1">
+      <c r="T41" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="3">
         <v>3.61</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="3">
         <v>53.16455696202531</v>
       </c>
-      <c r="D42" s="1">
-        <v>1.0831024930747921</v>
-      </c>
-      <c r="E42" s="1">
-        <v>-0.1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>-0.07152608902469655</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="H42" s="1">
-        <v>37.51</v>
-      </c>
-      <c r="I42" s="1">
-        <v>-0.72</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-0.006280195480516437</v>
-      </c>
-      <c r="K42" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>34</v>
-      </c>
-      <c r="M42" s="1">
-        <v>-0.13937077908104945</v>
-      </c>
-      <c r="N42" s="1">
-        <v>-2.2613450867998</v>
-      </c>
-      <c r="O42" s="1">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="P42" s="1">
-        <v>9.169379043273572</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>42.15189873417721</v>
-      </c>
-      <c r="R42" s="1">
-        <v>38.54430379746835</v>
-      </c>
-      <c r="S42" s="1" t="s">
+      <c r="D42" s="3">
+        <v>1.0637119113573408</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2.81</v>
+      </c>
+      <c r="F42" s="3">
+        <v>-0.12197523617098611</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="H42" s="3">
+        <v>40.62</v>
+      </c>
+      <c r="I42" s="3">
+        <v>-1.39</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-0.005248683020322596</v>
+      </c>
+      <c r="K42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>17</v>
+      </c>
+      <c r="M42" s="3">
+        <v>-0.19770142359033838</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-7.044959679133483</v>
+      </c>
+      <c r="O42" s="3">
+        <v>24.050632911392405</v>
+      </c>
+      <c r="P42" s="3">
+        <v>10.38279059078273</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>39.493670886075954</v>
+      </c>
+      <c r="R42" s="3">
+        <v>33.164556962025316</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T42" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="3">
         <v>-0.02</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="3">
         <v>27.848101265822784</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="3">
         <v>1214</v>
       </c>
-      <c r="E43" s="1">
-        <v>5.23</v>
-      </c>
-      <c r="F43" s="1">
-        <v>-0.10300963463207322</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="H43" s="1">
-        <v>42.05</v>
-      </c>
-      <c r="I43" s="1">
-        <v>-18.73</v>
-      </c>
-      <c r="J43" s="1">
-        <v>-0.0015476646793928285</v>
-      </c>
-      <c r="K43" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>6</v>
-      </c>
-      <c r="M43" s="1">
-        <v>-0.07438765601454933</v>
-      </c>
-      <c r="N43" s="1">
-        <v>4.236967219850214</v>
-      </c>
-      <c r="O43" s="1">
-        <v>48.10126582278481</v>
-      </c>
-      <c r="P43" s="1">
-        <v>38.87068031431492</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>49.87341772151898</v>
-      </c>
-      <c r="R43" s="1">
-        <v>42.151898734177216</v>
-      </c>
-      <c r="S43" s="1" t="s">
+      <c r="E43" s="3">
+        <v>10.72</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.0485243428195096</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>66.87</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="J43" s="3">
+        <v>-0.003428224080707113</v>
+      </c>
+      <c r="K43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>10</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0.08347489085921067</v>
+      </c>
+      <c r="N43" s="3">
+        <v>21.072671765821408</v>
+      </c>
+      <c r="O43" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P43" s="3">
+        <v>33.21399316212126</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>55.82278481012658</v>
+      </c>
+      <c r="R43" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T43" s="1">
-        <v>-0.38</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4740,49 +4752,49 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="3">
-        <v>26.862745098039216</v>
+        <v>26.69607843137255</v>
       </c>
       <c r="E44" s="3">
-        <v>-1.51</v>
+        <v>-0.99</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.4179675723306637</v>
+        <v>-0.3292213160718403</v>
       </c>
       <c r="G44" s="3">
         <v>2.59</v>
       </c>
       <c r="H44" s="3">
-        <v>32.04</v>
+        <v>58.82</v>
       </c>
       <c r="I44" s="3">
-        <v>-31.9</v>
+        <v>-14.98</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.018572838403102806</v>
+        <v>-0.013507900808196884</v>
       </c>
       <c r="K44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-18</v>
+        <v>-115</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.24941592047191197</v>
+        <v>-0.1439834114614248</v>
       </c>
       <c r="N44" s="3">
-        <v>-13.265859225886054</v>
+        <v>-1.6731584662421262</v>
       </c>
       <c r="O44" s="3">
-        <v>13.924050632911392</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P44" s="3">
-        <v>44.155007607957295</v>
+        <v>43.36598203964858</v>
       </c>
       <c r="Q44" s="3">
-        <v>38.60759493670886</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="R44" s="3">
-        <v>26.518987341772146</v>
+        <v>33.35443037974684</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
@@ -4802,49 +4814,49 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.818399044205496</v>
+        <v>0.7228195937873358</v>
       </c>
       <c r="E45" s="2">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>0.1791686078688256</v>
+        <v>0.10908432565781392</v>
       </c>
       <c r="G45" s="2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="2">
-        <v>65.55</v>
+        <v>59.69</v>
       </c>
       <c r="I45" s="2">
-        <v>17.34</v>
+        <v>16.9</v>
       </c>
       <c r="J45" s="2">
-        <v>0.025585314395313728</v>
+        <v>0.024427320861098265</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.22793197884682925</v>
+        <v>0.1615101477173655</v>
       </c>
       <c r="N45" s="2">
-        <v>34.468930705988065</v>
+        <v>28.876197451636905</v>
       </c>
       <c r="O45" s="2">
-        <v>82.27848101265823</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>62.27848101265823</v>
+        <v>60.63291139240506</v>
       </c>
       <c r="R45" s="2">
-        <v>56.962025316455694</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
@@ -4867,114 +4879,114 @@
         <v>543.5000000000001</v>
       </c>
       <c r="E46" s="1">
-        <v>-0.94</v>
+        <v>5.16</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.25626706372444663</v>
+        <v>-0.3262460642111287</v>
       </c>
       <c r="G46" s="1">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="H46" s="1">
-        <v>44.66</v>
+        <v>44.28</v>
       </c>
       <c r="I46" s="1">
-        <v>11.33</v>
+        <v>1.57</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.0062409394148189405</v>
+        <v>-0.004423731687799573</v>
       </c>
       <c r="K46" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.2022033263357904</v>
+        <v>-0.2726552238835871</v>
       </c>
       <c r="N46" s="1">
-        <v>-8.544599812273905</v>
+        <v>-14.540339708458358</v>
       </c>
       <c r="O46" s="1">
-        <v>22.78481012658228</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P46" s="1">
-        <v>40.6204924523832</v>
+        <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="1">
-        <v>51.139240506329116</v>
+        <v>47.46835443037975</v>
       </c>
       <c r="R46" s="1">
-        <v>31.39240506329114</v>
+        <v>27.721518987341767</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="1">
         <v>10.62</v>
       </c>
-      <c r="C47" s="3">
-        <v>81.0126582278481</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="C47" s="1">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="D47" s="1">
         <v>0.8549905838041432</v>
       </c>
-      <c r="E47" s="3">
-        <v>-4.11</v>
-      </c>
-      <c r="F47" s="3">
-        <v>-0.4152563242428725</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1.47</v>
-      </c>
-      <c r="H47" s="3">
-        <v>29.08</v>
-      </c>
-      <c r="I47" s="3">
-        <v>-19.09</v>
-      </c>
-      <c r="J47" s="3">
-        <v>-0.029842556362938727</v>
-      </c>
-      <c r="K47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>17</v>
-      </c>
-      <c r="M47" s="3">
-        <v>-0.3654328799827383</v>
-      </c>
-      <c r="N47" s="3">
-        <v>-24.867555176968693</v>
-      </c>
-      <c r="O47" s="3">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="P47" s="3">
-        <v>29.26623910493363</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>38.607594936708864</v>
-      </c>
-      <c r="R47" s="3">
-        <v>25.759493670886073</v>
-      </c>
-      <c r="S47" s="3" t="s">
+      <c r="E47" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="F47" s="1">
+        <v>-0.48840806761074906</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="H47" s="1">
+        <v>28.35</v>
+      </c>
+      <c r="I47" s="1">
+        <v>-23.95</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-0.03146335978104784</v>
+      </c>
+      <c r="K47" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>9</v>
+      </c>
+      <c r="M47" s="1">
+        <v>-0.43947730035516763</v>
+      </c>
+      <c r="N47" s="1">
+        <v>-31.22254735561642</v>
+      </c>
+      <c r="O47" s="1">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="P47" s="1">
+        <v>33.84253937304741</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>37.21518987341773</v>
+      </c>
+      <c r="R47" s="1">
+        <v>23.607594936708868</v>
+      </c>
+      <c r="S47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T47" s="3">
-        <v>-0.13</v>
+      <c r="T47" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -4988,49 +5000,49 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D48" s="2">
-        <v>7.505025125628141</v>
+        <v>7.922110552763819</v>
       </c>
       <c r="E48" s="2">
-        <v>-1.16</v>
+        <v>4.31</v>
       </c>
       <c r="F48" s="2">
-        <v>0.3550663954606283</v>
+        <v>-0.009801022322729891</v>
       </c>
       <c r="G48" s="2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H48" s="2">
-        <v>71.5</v>
+        <v>45.38</v>
       </c>
       <c r="I48" s="2">
-        <v>85.05</v>
+        <v>49.43</v>
       </c>
       <c r="J48" s="2">
-        <v>0.039067879528610155</v>
+        <v>0.01848470606497522</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="M48" s="2">
-        <v>0.47167445649498485</v>
+        <v>0.11136087754823376</v>
       </c>
       <c r="N48" s="2">
-        <v>58.84317847080362</v>
+        <v>23.861270434723732</v>
       </c>
       <c r="O48" s="2">
-        <v>89.87341772151899</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P48" s="2">
-        <v>15.18684888660459</v>
+        <v>16.492575418924176</v>
       </c>
       <c r="Q48" s="2">
-        <v>69.87341772151898</v>
+        <v>58.607594936708864</v>
       </c>
       <c r="R48" s="2">
-        <v>63.037974683544306</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>94</v>
@@ -5050,116 +5062,116 @@
         <v>26.582278481012654</v>
       </c>
       <c r="D49" s="2">
-        <v>1710.0000000000002</v>
+        <v>1715.8333333333335</v>
       </c>
       <c r="E49" s="2">
-        <v>2.02</v>
+        <v>5.72</v>
       </c>
       <c r="F49" s="2">
-        <v>0.7888246191322793</v>
+        <v>0.38199906720470367</v>
       </c>
       <c r="G49" s="2">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="H49" s="2">
-        <v>70.19</v>
+        <v>56.18</v>
       </c>
       <c r="I49" s="2">
-        <v>141.75</v>
+        <v>106.21</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06629949146826043</v>
+        <v>0.06592975996614166</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="M49" s="2">
-        <v>1.0856451381288232</v>
+        <v>0.7035441091699532</v>
       </c>
       <c r="N49" s="2">
-        <v>120.24024663418746</v>
+        <v>83.07959359689566</v>
       </c>
       <c r="O49" s="2">
-        <v>97.46835443037975</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P49" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q49" s="2">
-        <v>74.55696202531647</v>
+        <v>70.12658227848101</v>
       </c>
       <c r="R49" s="2">
-        <v>63.544303797468345</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T49" s="2">
-        <v>0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="1">
         <v>-0.13</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="1">
         <v>25.31645569620253</v>
       </c>
-      <c r="D50" s="3">
-        <v>385.61538461538464</v>
-      </c>
-      <c r="E50" s="3">
-        <v>2.75</v>
-      </c>
-      <c r="F50" s="3">
-        <v>-0.436916409525831</v>
-      </c>
-      <c r="G50" s="3">
-        <v>1.53</v>
-      </c>
-      <c r="H50" s="3">
-        <v>39.39</v>
-      </c>
-      <c r="I50" s="3">
-        <v>-23.32</v>
-      </c>
-      <c r="J50" s="3">
-        <v>-0.030364906654603615</v>
-      </c>
-      <c r="K50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" s="3">
-        <v>7</v>
-      </c>
-      <c r="M50" s="3">
-        <v>-0.3807325255729137</v>
-      </c>
-      <c r="N50" s="3">
-        <v>-26.397519735986226</v>
-      </c>
-      <c r="O50" s="3">
-        <v>2.5316455696202533</v>
-      </c>
-      <c r="P50" s="3">
-        <v>47.64150593279924</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>39.24050632911393</v>
-      </c>
-      <c r="R50" s="3">
-        <v>21.77215189873418</v>
-      </c>
-      <c r="S50" s="3" t="s">
+      <c r="D50" s="1">
+        <v>300.1538461538462</v>
+      </c>
+      <c r="E50" s="1">
+        <v>6.03</v>
+      </c>
+      <c r="F50" s="1">
+        <v>-0.3612154407216672</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H50" s="1">
+        <v>47.89</v>
+      </c>
+      <c r="I50" s="1">
+        <v>-19.43</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-0.027130684693928847</v>
+      </c>
+      <c r="K50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="M50" s="1">
+        <v>-0.29830445425020535</v>
+      </c>
+      <c r="N50" s="1">
+        <v>-17.105262745120182</v>
+      </c>
+      <c r="O50" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P50" s="1">
+        <v>45.04950372346088</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>40.379746835443036</v>
+      </c>
+      <c r="R50" s="1">
+        <v>23.860759493670876</v>
+      </c>
+      <c r="S50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T50" s="3">
+      <c r="T50" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5171,28 +5183,28 @@
         <v>-3.88</v>
       </c>
       <c r="C51" s="3">
-        <v>7.59493670886076</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="D51" s="3">
-        <v>-6.131443298969073</v>
+        <v>13.440721649484537</v>
       </c>
       <c r="E51" s="3">
-        <v>17.05</v>
+        <v>37.01</v>
       </c>
       <c r="F51" s="3">
-        <v>0.06505664660412691</v>
+        <v>0.1951512945193788</v>
       </c>
       <c r="G51" s="3">
         <v>2.37</v>
       </c>
       <c r="H51" s="3">
-        <v>56.45</v>
+        <v>60.82</v>
       </c>
       <c r="I51" s="3">
-        <v>34.3</v>
+        <v>45.35</v>
       </c>
       <c r="J51" s="3">
-        <v>0.03187932043656487</v>
+        <v>0.03804757318712313</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>0</v>
@@ -5201,22 +5213,22 @@
         <v>95</v>
       </c>
       <c r="M51" s="3">
-        <v>0.21028668625600733</v>
+        <v>0.3547587972340136</v>
       </c>
       <c r="N51" s="3">
-        <v>32.704401446905884</v>
+        <v>48.201062403301705</v>
       </c>
       <c r="O51" s="3">
-        <v>81.0126582278481</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P51" s="3">
         <v>46.744012320672994</v>
       </c>
       <c r="Q51" s="3">
-        <v>33.67088607594937</v>
+        <v>54.30379746835443</v>
       </c>
       <c r="R51" s="3">
-        <v>26.64556962025317</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="S51" s="3" t="s">
         <v>113</v>
@@ -5233,52 +5245,52 @@
         <v>5.3</v>
       </c>
       <c r="C52" s="2">
-        <v>62.0253164556962</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="D52" s="2">
-        <v>6.496226415094339</v>
+        <v>6.598113207547171</v>
       </c>
       <c r="E52" s="2">
-        <v>0.22</v>
+        <v>-0.82</v>
       </c>
       <c r="F52" s="2">
-        <v>0.09175586852112316</v>
+        <v>0.1329396604551625</v>
       </c>
       <c r="G52" s="2">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H52" s="2">
-        <v>66.21</v>
+        <v>66.07</v>
       </c>
       <c r="I52" s="2">
-        <v>64.37</v>
+        <v>64.97</v>
       </c>
       <c r="J52" s="2">
-        <v>0.027550206758726836</v>
+        <v>0.03866798658816369</v>
       </c>
       <c r="K52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="2">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="M52" s="2">
-        <v>0.17974195093795586</v>
+        <v>0.23313123150230552</v>
       </c>
       <c r="N52" s="2">
-        <v>29.649927915100726</v>
+        <v>36.03830583013091</v>
       </c>
       <c r="O52" s="2">
-        <v>75.9493670886076</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P52" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q52" s="2">
-        <v>67.21518987341773</v>
+        <v>68.22784810126582</v>
       </c>
       <c r="R52" s="2">
-        <v>56.77215189873419</v>
+        <v>58.41772151898735</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>94</v>
@@ -5288,65 +5300,65 @@
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="3">
         <v>-0.71</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="3">
         <v>17.72151898734177</v>
       </c>
-      <c r="D53" s="1">
-        <v>12.042253521126762</v>
-      </c>
-      <c r="E53" s="1">
-        <v>6.97</v>
-      </c>
-      <c r="F53" s="1">
-        <v>-0.1745555804193139</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2.59</v>
-      </c>
-      <c r="H53" s="1">
-        <v>69.25</v>
-      </c>
-      <c r="I53" s="1">
-        <v>-14.45</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0.019469516135453818</v>
-      </c>
-      <c r="K53" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1">
-        <v>25</v>
-      </c>
-      <c r="M53" s="1">
-        <v>-0.0060039285605621995</v>
-      </c>
-      <c r="N53" s="1">
-        <v>11.075339965248917</v>
-      </c>
-      <c r="O53" s="1">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="P53" s="1">
-        <v>48.21894075039502</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>48.734177215189874</v>
-      </c>
-      <c r="R53" s="1">
-        <v>35.12658227848102</v>
-      </c>
-      <c r="S53" s="1" t="s">
+      <c r="D53" s="3">
+        <v>6.873239436619719</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6.07</v>
+      </c>
+      <c r="F53" s="3">
+        <v>-0.018297005399717625</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="H53" s="3">
+        <v>63.25</v>
+      </c>
+      <c r="I53" s="3">
+        <v>-11.25</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0.027709444384052366</v>
+      </c>
+      <c r="K53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3">
+        <v>-15</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0.17043595401466805</v>
+      </c>
+      <c r="N53" s="3">
+        <v>29.76877808136716</v>
+      </c>
+      <c r="O53" s="3">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P53" s="3">
+        <v>47.39629233644822</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>46.58227848101265</v>
+      </c>
+      <c r="R53" s="3">
+        <v>40.632911392405056</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T53" s="1">
-        <v>-0.76</v>
+      <c r="T53" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5354,55 +5366,55 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="C54" s="2">
-        <v>35.44303797468354</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="D54" s="2">
-        <v>41.629629629629626</v>
+        <v>33.96969696969697</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.44</v>
+        <v>-1.41</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.00014858383710547596</v>
+        <v>0.06307025705197225</v>
       </c>
       <c r="G54" s="2">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="H54" s="2">
-        <v>66.62</v>
+        <v>52.55</v>
       </c>
       <c r="I54" s="2">
-        <v>11.42</v>
+        <v>5.98</v>
       </c>
       <c r="J54" s="2">
-        <v>0.029728045222307847</v>
+        <v>0.029239188458194603</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L54" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M54" s="2">
-        <v>0.048614787140898175</v>
+        <v>0.11083600603956367</v>
       </c>
       <c r="N54" s="2">
-        <v>16.53721153539496</v>
+        <v>23.808783283856716</v>
       </c>
       <c r="O54" s="2">
-        <v>64.55696202531645</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P54" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q54" s="2">
-        <v>65.69620253164557</v>
+        <v>61.0126582278481</v>
       </c>
       <c r="R54" s="2">
-        <v>52.65822784810126</v>
+        <v>53.98734177215191</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>93</v>
@@ -5412,127 +5424,127 @@
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="3">
         <v>4.03</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="3">
         <v>56.9620253164557</v>
       </c>
-      <c r="D55" s="1">
-        <v>2.2580645161290325</v>
-      </c>
-      <c r="E55" s="1">
-        <v>-0.7</v>
-      </c>
-      <c r="F55" s="1">
-        <v>-0.18622611726230834</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H55" s="1">
-        <v>39.05</v>
-      </c>
-      <c r="I55" s="1">
-        <v>-3.12</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0.0001009254578829784</v>
-      </c>
-      <c r="K55" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
-        <v>10</v>
-      </c>
-      <c r="M55" s="1">
-        <v>-0.16502465161969804</v>
-      </c>
-      <c r="N55" s="1">
-        <v>-4.826732340664665</v>
-      </c>
-      <c r="O55" s="1">
-        <v>27.848101265822784</v>
-      </c>
-      <c r="P55" s="1">
+      <c r="D55" s="3">
+        <v>2.307692307692308</v>
+      </c>
+      <c r="E55" s="3">
+        <v>-1.23</v>
+      </c>
+      <c r="F55" s="3">
+        <v>-0.11386647194367264</v>
+      </c>
+      <c r="G55" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H55" s="3">
+        <v>51.14</v>
+      </c>
+      <c r="I55" s="3">
+        <v>-0.47</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0.008848473543211676</v>
+      </c>
+      <c r="K55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" s="3">
+        <v>-63</v>
+      </c>
+      <c r="M55" s="3">
+        <v>-0.09173112485186197</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.552070194714145</v>
+      </c>
+      <c r="O55" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="P55" s="3">
         <v>18.39301096820415</v>
       </c>
-      <c r="Q55" s="1">
-        <v>47.21518987341773</v>
-      </c>
-      <c r="R55" s="1">
-        <v>36.582278481012665</v>
-      </c>
-      <c r="S55" s="1" t="s">
+      <c r="Q55" s="3">
+        <v>48.860759493670884</v>
+      </c>
+      <c r="R55" s="3">
+        <v>42.08860759493671</v>
+      </c>
+      <c r="S55" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="T55" s="1">
-        <v>0.38</v>
+      <c r="T55" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="3">
         <v>8.65</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="3">
         <v>74.68354430379746</v>
       </c>
-      <c r="D56" s="1">
-        <v>0.1757225433526011</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="F56" s="1">
-        <v>-0.09903570790419841</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="D56" s="3">
+        <v>0.18843930635838138</v>
+      </c>
+      <c r="E56" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="F56" s="3">
+        <v>-0.13402437999435216</v>
+      </c>
+      <c r="G56" s="3">
         <v>0.26</v>
       </c>
-      <c r="H56" s="1">
-        <v>51.35</v>
-      </c>
-      <c r="I56" s="1">
-        <v>10.14</v>
-      </c>
-      <c r="J56" s="1">
-        <v>-0.008898279015999048</v>
-      </c>
-      <c r="K56" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>199</v>
-      </c>
-      <c r="M56" s="1">
-        <v>-0.17748113078185646</v>
-      </c>
-      <c r="N56" s="1">
-        <v>-6.07238025688051</v>
-      </c>
-      <c r="O56" s="1">
-        <v>25.31645569620253</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="H56" s="3">
+        <v>42.79</v>
+      </c>
+      <c r="I56" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="J56" s="3">
+        <v>-0.004299484933438593</v>
+      </c>
+      <c r="K56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3">
+        <v>164</v>
+      </c>
+      <c r="M56" s="3">
+        <v>-0.22023573182561473</v>
+      </c>
+      <c r="N56" s="3">
+        <v>-9.298390502661121</v>
+      </c>
+      <c r="O56" s="3">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="P56" s="3">
         <v>10.95912073621325</v>
       </c>
-      <c r="Q56" s="1">
-        <v>45.063291139240505</v>
-      </c>
-      <c r="R56" s="1">
-        <v>33.98734177215189</v>
-      </c>
-      <c r="S56" s="1" t="s">
+      <c r="Q56" s="3">
+        <v>43.164556962025316</v>
+      </c>
+      <c r="R56" s="3">
+        <v>33.10126582278481</v>
+      </c>
+      <c r="S56" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="T56" s="1">
-        <v>0.13</v>
+      <c r="T56" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5546,55 +5558,55 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.31067044381492</v>
+        <v>2.4466477809254012</v>
       </c>
       <c r="E57" s="2">
-        <v>0.39</v>
+        <v>-1.3</v>
       </c>
       <c r="F57" s="2">
-        <v>0.6840401434964034</v>
+        <v>1.095782612173617</v>
       </c>
       <c r="G57" s="2">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="H57" s="2">
-        <v>79.04</v>
+        <v>78.01</v>
       </c>
       <c r="I57" s="2">
-        <v>160.72</v>
+        <v>186.65</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08503248308634306</v>
+        <v>0.08877660888261664</v>
       </c>
       <c r="K57" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="M57" s="2">
-        <v>0.7900474717094548</v>
+        <v>1.227429676456491</v>
       </c>
       <c r="N57" s="2">
-        <v>90.68047999225062</v>
+        <v>135.46815032554946</v>
       </c>
       <c r="O57" s="2">
-        <v>93.67088607594937</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P57" s="2">
         <v>30.30559414893712</v>
       </c>
       <c r="Q57" s="2">
-        <v>81.51898734177216</v>
+        <v>81.13924050632912</v>
       </c>
       <c r="R57" s="2">
-        <v>67.34177215189874</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="S57" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T57" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5608,49 +5620,49 @@
         <v>94.9367088607595</v>
       </c>
       <c r="D58" s="2">
-        <v>0.09701492537313429</v>
+        <v>0.10597014925373129</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.9</v>
+        <v>-0.36</v>
       </c>
       <c r="F58" s="2">
-        <v>0.021818608106908055</v>
+        <v>-0.018054104889669326</v>
       </c>
       <c r="G58" s="2">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H58" s="2">
-        <v>65.53</v>
+        <v>52.28</v>
       </c>
       <c r="I58" s="2">
-        <v>49.13</v>
+        <v>37.81</v>
       </c>
       <c r="J58" s="2">
-        <v>0.02231951880965812</v>
+        <v>0.02444271069944749</v>
       </c>
       <c r="K58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="2">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="M58" s="2">
-        <v>0.08754315159899995</v>
+        <v>0.051846991189732794</v>
       </c>
       <c r="N58" s="2">
-        <v>20.430047981205142</v>
+        <v>17.909881798873624</v>
       </c>
       <c r="O58" s="2">
-        <v>67.08860759493672</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P58" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q58" s="2">
-        <v>65.0632911392405</v>
+        <v>61.139240506329116</v>
       </c>
       <c r="R58" s="2">
-        <v>55.31645569620253</v>
+        <v>53.164556962025316</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>105</v>
@@ -5660,188 +5672,188 @@
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="3">
         <v>34.32</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>100</v>
       </c>
-      <c r="D59" s="2">
-        <v>-1.435897435897436</v>
-      </c>
-      <c r="E59" s="2">
-        <v>-2.43</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0.17401162363333672</v>
-      </c>
-      <c r="G59" s="2">
-        <v>1.24</v>
-      </c>
-      <c r="H59" s="2">
-        <v>56.61</v>
-      </c>
-      <c r="I59" s="2">
-        <v>47.17</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0.02141742119672486</v>
-      </c>
-      <c r="K59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>374</v>
-      </c>
-      <c r="M59" s="2">
-        <v>0.19945338240446908</v>
-      </c>
-      <c r="N59" s="2">
-        <v>31.621071061752055</v>
-      </c>
-      <c r="O59" s="2">
-        <v>79.74683544303798</v>
-      </c>
-      <c r="P59" s="2">
-        <v>11.512523311327532</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>59.74683544303798</v>
-      </c>
-      <c r="R59" s="2">
-        <v>56.582278481012665</v>
-      </c>
-      <c r="S59" s="2" t="s">
+      <c r="D59" s="3">
+        <v>-1.487762237762238</v>
+      </c>
+      <c r="E59" s="3">
+        <v>-0.04</v>
+      </c>
+      <c r="F59" s="3">
+        <v>-0.0293120434254574</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="H59" s="3">
+        <v>40.31</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.019107989063646694</v>
+      </c>
+      <c r="K59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>363</v>
+      </c>
+      <c r="M59" s="3">
+        <v>-0.01882687901354707</v>
+      </c>
+      <c r="N59" s="3">
+        <v>10.842494778545639</v>
+      </c>
+      <c r="O59" s="3">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P59" s="3">
+        <v>15.763835424420858</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>54.050632911392405</v>
+      </c>
+      <c r="R59" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="S59" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T59" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="1">
         <v>6.37</v>
       </c>
-      <c r="C60" s="3">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="D60" s="3">
-        <v>-0.1255886970172684</v>
-      </c>
-      <c r="E60" s="3">
-        <v>-0.23</v>
-      </c>
-      <c r="F60" s="3">
-        <v>-0.16126001565497908</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0.38</v>
-      </c>
-      <c r="H60" s="3">
-        <v>38.08</v>
-      </c>
-      <c r="I60" s="3">
-        <v>-0.86</v>
-      </c>
-      <c r="J60" s="3">
-        <v>-0.010130946048307181</v>
-      </c>
-      <c r="K60" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>149</v>
-      </c>
-      <c r="M60" s="3">
-        <v>-0.22698455914707094</v>
-      </c>
-      <c r="N60" s="3">
-        <v>-11.02272309340195</v>
-      </c>
-      <c r="O60" s="3">
-        <v>20.253164556962027</v>
-      </c>
-      <c r="P60" s="3">
-        <v>12.73975043749647</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>36.32911392405063</v>
-      </c>
-      <c r="R60" s="3">
-        <v>28.79746835443038</v>
-      </c>
-      <c r="S60" s="3" t="s">
+      <c r="C60" s="1">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="D60" s="1">
+        <v>-0.13029827315541603</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="F60" s="1">
+        <v>-0.2043800203536123</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="H60" s="1">
+        <v>34.95</v>
+      </c>
+      <c r="I60" s="1">
+        <v>-4.3</v>
+      </c>
+      <c r="J60" s="1">
+        <v>-0.006745998671544878</v>
+      </c>
+      <c r="K60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+      <c r="M60" s="1">
+        <v>-0.2777761712369845</v>
+      </c>
+      <c r="N60" s="1">
+        <v>-15.052434443798099</v>
+      </c>
+      <c r="O60" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P60" s="1">
+        <v>15.426125992360493</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>32.278481012658226</v>
+      </c>
+      <c r="R60" s="1">
+        <v>24.746835443037973</v>
+      </c>
+      <c r="S60" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="1">
-        <v>17.74</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B61" s="3">
+        <v>17.65</v>
+      </c>
+      <c r="C61" s="3">
         <v>92.40506329113924</v>
       </c>
-      <c r="D61" s="1">
-        <v>0.6178128523111613</v>
-      </c>
-      <c r="E61" s="1">
-        <v>-0.38</v>
-      </c>
-      <c r="F61" s="1">
-        <v>-0.14291277018514845</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.96</v>
-      </c>
-      <c r="H61" s="1">
-        <v>49.51</v>
-      </c>
-      <c r="I61" s="1">
-        <v>11.77</v>
-      </c>
-      <c r="J61" s="1">
-        <v>-0.006832330097585761</v>
-      </c>
-      <c r="K61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>155</v>
-      </c>
-      <c r="M61" s="1">
-        <v>-0.1471530633136705</v>
-      </c>
-      <c r="N61" s="1">
-        <v>-3.0395735100619077</v>
-      </c>
-      <c r="O61" s="1">
-        <v>35.44303797468354</v>
-      </c>
-      <c r="P61" s="1">
-        <v>16.149676494964734</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>54.050632911392405</v>
-      </c>
-      <c r="R61" s="1">
-        <v>42.848101265822784</v>
-      </c>
-      <c r="S61" s="1" t="s">
+      <c r="D61" s="3">
+        <v>0.49291784702549596</v>
+      </c>
+      <c r="E61" s="3">
+        <v>-0.19</v>
+      </c>
+      <c r="F61" s="3">
+        <v>-0.2580972328873807</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="H61" s="3">
+        <v>40.6</v>
+      </c>
+      <c r="I61" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="J61" s="3">
+        <v>-0.007351672799078714</v>
+      </c>
+      <c r="K61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" s="3">
+        <v>169</v>
+      </c>
+      <c r="M61" s="3">
+        <v>-0.26625236076331094</v>
+      </c>
+      <c r="N61" s="3">
+        <v>-13.900053396430746</v>
+      </c>
+      <c r="O61" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="P61" s="3">
+        <v>20.131624188012864</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="R61" s="3">
+        <v>33.10126582278481</v>
+      </c>
+      <c r="S61" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="T61" s="1">
+      <c r="T61" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5856,37 +5868,37 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D62" s="4">
-        <v>4.831074035453597</v>
+        <v>5.210288494960027</v>
       </c>
       <c r="E62" s="4">
-        <v>-8.63</v>
+        <v>-3.33</v>
       </c>
       <c r="F62" s="4">
-        <v>0.702412030848552</v>
+        <v>1.0942936261123775</v>
       </c>
       <c r="G62" s="4">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="H62" s="4">
-        <v>66.15</v>
+        <v>72.22</v>
       </c>
       <c r="I62" s="4">
-        <v>238.33</v>
+        <v>247.16</v>
       </c>
       <c r="J62" s="4">
-        <v>0.1058386935433432</v>
+        <v>0.09185172560782784</v>
       </c>
       <c r="K62" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="4">
-        <v>413</v>
+        <v>475</v>
       </c>
       <c r="M62" s="4">
-        <v>1.1009995849296252</v>
+        <v>1.5404956227525608</v>
       </c>
       <c r="N62" s="4">
-        <v>121.77569131426769</v>
+        <v>166.7747449551564</v>
       </c>
       <c r="O62" s="4">
         <v>98.73417721518987</v>
@@ -5895,10 +5907,10 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q62" s="4">
-        <v>82.27848101265823</v>
+        <v>83.1645569620253</v>
       </c>
       <c r="R62" s="4">
-        <v>72.34177215189874</v>
+        <v>72.08860759493672</v>
       </c>
       <c r="S62" s="4" t="s">
         <v>105</v>
@@ -5915,52 +5927,52 @@
         <v>10.54</v>
       </c>
       <c r="C63" s="2">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="D63" s="2">
-        <v>6.3927893738140416</v>
+        <v>6.5379506641366225</v>
       </c>
       <c r="E63" s="2">
-        <v>-4.36</v>
+        <v>-1.41</v>
       </c>
       <c r="F63" s="2">
-        <v>0.6347132974900617</v>
+        <v>0.905309725030915</v>
       </c>
       <c r="G63" s="2">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="H63" s="2">
-        <v>75.15</v>
+        <v>74.43</v>
       </c>
       <c r="I63" s="2">
-        <v>139.96</v>
+        <v>139.26</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0865727164624305</v>
+        <v>0.08083435181170055</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="M63" s="2">
-        <v>0.7439008455495046</v>
+        <v>1.0299666797058487</v>
       </c>
       <c r="N63" s="2">
-        <v>86.06581737625561</v>
+        <v>115.72185065048521</v>
       </c>
       <c r="O63" s="2">
-        <v>92.40506329113924</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="P63" s="2">
         <v>20.9978319173529</v>
       </c>
       <c r="Q63" s="2">
-        <v>77.84810126582278</v>
+        <v>76.32911392405063</v>
       </c>
       <c r="R63" s="2">
-        <v>66.96202531645571</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>107</v>
@@ -5970,313 +5982,313 @@
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="3">
         <v>16.87</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="3">
         <v>89.87341772151899</v>
       </c>
-      <c r="D64" s="1">
-        <v>-0.2691167753408418</v>
-      </c>
-      <c r="E64" s="1">
-        <v>-0.69</v>
-      </c>
-      <c r="F64" s="1">
-        <v>-0.07677209987055884</v>
-      </c>
-      <c r="G64" s="1">
+      <c r="D64" s="3">
+        <v>-0.28986366330764674</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0.14</v>
+      </c>
+      <c r="F64" s="3">
+        <v>-0.14607450972796582</v>
+      </c>
+      <c r="G64" s="3">
         <v>0.31</v>
       </c>
-      <c r="H64" s="1">
-        <v>59.81</v>
-      </c>
-      <c r="I64" s="1">
-        <v>3.83</v>
-      </c>
-      <c r="J64" s="1">
-        <v>-0.008871724521789534</v>
-      </c>
-      <c r="K64" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>71</v>
-      </c>
-      <c r="M64" s="1">
-        <v>-0.1499171563375643</v>
-      </c>
-      <c r="N64" s="1">
-        <v>-3.315982812451293</v>
-      </c>
-      <c r="O64" s="1">
-        <v>32.91139240506329</v>
-      </c>
-      <c r="P64" s="1">
+      <c r="H64" s="3">
+        <v>58.11</v>
+      </c>
+      <c r="I64" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="J64" s="3">
+        <v>-0.005642858388220164</v>
+      </c>
+      <c r="K64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>56</v>
+      </c>
+      <c r="M64" s="3">
+        <v>-0.22646077021927824</v>
+      </c>
+      <c r="N64" s="3">
+        <v>-9.920894342027472</v>
+      </c>
+      <c r="O64" s="3">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P64" s="3">
         <v>15.211254913322609</v>
       </c>
-      <c r="Q64" s="1">
-        <v>48.22784810126582</v>
-      </c>
-      <c r="R64" s="1">
-        <v>37.40506329113924</v>
-      </c>
-      <c r="S64" s="1" t="s">
+      <c r="Q64" s="3">
+        <v>45.443037974683556</v>
+      </c>
+      <c r="R64" s="3">
+        <v>32.53164556962025</v>
+      </c>
+      <c r="S64" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="T64" s="1">
-        <v>-0.38</v>
+      <c r="T64" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="3">
-        <v>15.41</v>
-      </c>
-      <c r="C65" s="3">
+      <c r="B65" s="1">
+        <v>16.51</v>
+      </c>
+      <c r="C65" s="1">
         <v>87.34177215189874</v>
       </c>
-      <c r="D65" s="3">
-        <v>-0.10837118754055808</v>
-      </c>
-      <c r="E65" s="3">
-        <v>-0.19</v>
-      </c>
-      <c r="F65" s="3">
-        <v>-0.16453528787485666</v>
-      </c>
-      <c r="G65" s="3">
-        <v>1.02</v>
-      </c>
-      <c r="H65" s="3">
-        <v>43.81</v>
-      </c>
-      <c r="I65" s="3">
-        <v>-33.37</v>
-      </c>
-      <c r="J65" s="3">
-        <v>-0.008021649911025294</v>
-      </c>
-      <c r="K65" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3">
-        <v>-153</v>
-      </c>
-      <c r="M65" s="3">
-        <v>-0.16241514131059565</v>
-      </c>
-      <c r="N65" s="3">
-        <v>-4.5657813097544215</v>
-      </c>
-      <c r="O65" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="P65" s="3">
-        <v>48.12800106814908</v>
-      </c>
-      <c r="Q65" s="3">
-        <v>40.75949367088607</v>
-      </c>
-      <c r="R65" s="3">
-        <v>29.050632911392405</v>
-      </c>
-      <c r="S65" s="3" t="s">
+      <c r="D65" s="1">
+        <v>-0.11265899454875838</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="F65" s="1">
+        <v>-0.3120644091099978</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="H65" s="1">
+        <v>40.09</v>
+      </c>
+      <c r="I65" s="1">
+        <v>-39.8</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-0.032455254246706575</v>
+      </c>
+      <c r="K65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>-196</v>
+      </c>
+      <c r="M65" s="1">
+        <v>-0.3167244821819579</v>
+      </c>
+      <c r="N65" s="1">
+        <v>-18.947265538295447</v>
+      </c>
+      <c r="O65" s="1">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="P65" s="1">
+        <v>54.054827155660476</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>32.911392405063296</v>
+      </c>
+      <c r="R65" s="1">
+        <v>18.10126582278481</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T65" s="3">
-        <v>-0.38</v>
+      <c r="T65" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="3">
         <v>4.01</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="3">
         <v>55.69620253164557</v>
       </c>
-      <c r="D66" s="1">
-        <v>7.0074812967581055</v>
-      </c>
-      <c r="E66" s="1">
-        <v>-0.9</v>
-      </c>
-      <c r="F66" s="1">
-        <v>-0.08084571247327066</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1.15</v>
-      </c>
-      <c r="H66" s="1">
-        <v>48.91</v>
-      </c>
-      <c r="I66" s="1">
-        <v>-11.66</v>
-      </c>
-      <c r="J66" s="1">
-        <v>-0.00043359092444813775</v>
-      </c>
-      <c r="K66" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>-32</v>
-      </c>
-      <c r="M66" s="1">
-        <v>-0.06494461324131295</v>
-      </c>
-      <c r="N66" s="1">
-        <v>5.181271497173847</v>
-      </c>
-      <c r="O66" s="1">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="P66" s="1">
+      <c r="D66" s="3">
+        <v>7.241895261845387</v>
+      </c>
+      <c r="E66" s="3">
+        <v>-0.68</v>
+      </c>
+      <c r="F66" s="3">
+        <v>-0.20779259712788334</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H66" s="3">
+        <v>37.79</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-15.88</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-0.005770708881856257</v>
+      </c>
+      <c r="K66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3">
+        <v>-77</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.1938123779120029</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-6.656055111299941</v>
+      </c>
+      <c r="O66" s="3">
+        <v>25.31645569620253</v>
+      </c>
+      <c r="P66" s="3">
         <v>21.01837744312229</v>
       </c>
-      <c r="Q66" s="1">
-        <v>50.12658227848102</v>
-      </c>
-      <c r="R66" s="1">
-        <v>44.11392405063291</v>
-      </c>
-      <c r="S66" s="1" t="s">
+      <c r="Q66" s="3">
+        <v>41.0126582278481</v>
+      </c>
+      <c r="R66" s="3">
+        <v>34.49367088607595</v>
+      </c>
+      <c r="S66" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T66" s="1">
-        <v>0.76</v>
+      <c r="T66" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="3">
         <v>7.35</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="3">
         <v>69.62025316455697</v>
       </c>
-      <c r="D67" s="1">
-        <v>84.9795918367347</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F67" s="1">
-        <v>-0.17464350704065426</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H67" s="1">
-        <v>45.64</v>
-      </c>
-      <c r="I67" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="J67" s="1">
-        <v>-0.010596519517794166</v>
-      </c>
-      <c r="K67" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>132</v>
-      </c>
-      <c r="M67" s="1">
-        <v>-0.2456684169433987</v>
-      </c>
-      <c r="N67" s="1">
-        <v>-12.891108873034732</v>
-      </c>
-      <c r="O67" s="1">
-        <v>17.72151898734177</v>
-      </c>
-      <c r="P67" s="1">
+      <c r="D67" s="3">
+        <v>485.7265306122449</v>
+      </c>
+      <c r="E67" s="3">
+        <v>-0.41</v>
+      </c>
+      <c r="F67" s="3">
+        <v>-0.1478430284292418</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="H67" s="3">
+        <v>52.18</v>
+      </c>
+      <c r="I67" s="3">
+        <v>4.49</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-0.007153378496309148</v>
+      </c>
+      <c r="K67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3">
+        <v>146</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-0.2247342341165841</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-9.748240731758063</v>
+      </c>
+      <c r="O67" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="P67" s="3">
         <v>18.003852697255347</v>
       </c>
-      <c r="Q67" s="1">
-        <v>60.37974683544305</v>
-      </c>
-      <c r="R67" s="1">
-        <v>44.936708860759495</v>
-      </c>
-      <c r="S67" s="1" t="s">
+      <c r="Q67" s="3">
+        <v>60.8860759493671</v>
+      </c>
+      <c r="R67" s="3">
+        <v>46.265822784810126</v>
+      </c>
+      <c r="S67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="T67" s="1">
-        <v>0.38</v>
+      <c r="T67" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="1">
         <v>8.24</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="1">
         <v>72.15189873417721</v>
       </c>
-      <c r="D68" s="3">
-        <v>0.6286407766990291</v>
-      </c>
-      <c r="E68" s="3">
-        <v>-0.07</v>
-      </c>
-      <c r="F68" s="3">
-        <v>-0.27315144163343014</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1.49</v>
-      </c>
-      <c r="H68" s="3">
-        <v>36.26</v>
-      </c>
-      <c r="I68" s="3">
-        <v>-13.82</v>
-      </c>
-      <c r="J68" s="3">
-        <v>-0.014530824507100982</v>
-      </c>
-      <c r="K68" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3">
-        <v>-11</v>
-      </c>
-      <c r="M68" s="3">
-        <v>-0.22120785080903493</v>
-      </c>
-      <c r="N68" s="3">
-        <v>-10.445052259598356</v>
-      </c>
-      <c r="O68" s="3">
-        <v>21.518987341772153</v>
-      </c>
-      <c r="P68" s="3">
-        <v>29.145649851223904</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="R68" s="3">
-        <v>27.72151898734177</v>
-      </c>
-      <c r="S68" s="3" t="s">
+      <c r="D68" s="1">
+        <v>0.6262135922330098</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-0.24</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-0.33748303889174613</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H68" s="1">
+        <v>40.09</v>
+      </c>
+      <c r="I68" s="1">
+        <v>-14.22</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.011059197669783964</v>
+      </c>
+      <c r="K68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>-69</v>
+      </c>
+      <c r="M68" s="1">
+        <v>-0.28389219856420456</v>
+      </c>
+      <c r="N68" s="1">
+        <v>-15.664037176520102</v>
+      </c>
+      <c r="O68" s="1">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="P68" s="1">
+        <v>29.40035337282439</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>36.58227848101265</v>
+      </c>
+      <c r="R68" s="1">
+        <v>24.620253164556964</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T68" s="3">
-        <v>0.13</v>
+      <c r="T68" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6290,116 +6302,116 @@
         <v>93.67088607594937</v>
       </c>
       <c r="D69" s="3">
-        <v>-0.47663551401869164</v>
+        <v>-0.47608576140736675</v>
       </c>
       <c r="E69" s="3">
-        <v>1.57</v>
+        <v>-1.55</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.21780123079606967</v>
+        <v>-0.1681544085078506</v>
       </c>
       <c r="G69" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H69" s="3">
-        <v>37.59</v>
+        <v>62.29</v>
       </c>
       <c r="I69" s="3">
-        <v>-14.56</v>
+        <v>-6.51</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.012052150714678567</v>
+        <v>-0.0006359513945416026</v>
       </c>
       <c r="K69" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-34</v>
+        <v>-60</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.23158218346376636</v>
+        <v>-0.182134627723731</v>
       </c>
       <c r="N69" s="3">
-        <v>-11.4824855250715</v>
+        <v>-5.488280092472756</v>
       </c>
       <c r="O69" s="3">
-        <v>18.9873417721519</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P69" s="3">
-        <v>30.247870785107096</v>
+        <v>31.450467124868602</v>
       </c>
       <c r="Q69" s="3">
-        <v>38.481012658227854</v>
+        <v>48.481012658227854</v>
       </c>
       <c r="R69" s="3">
-        <v>27.72151898734177</v>
+        <v>32.0253164556962</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T69" s="3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="1">
         <v>1.52</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="1">
         <v>45.56962025316456</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="1">
         <v>13.532894736842104</v>
       </c>
-      <c r="E70" s="3">
-        <v>-0.78</v>
-      </c>
-      <c r="F70" s="3">
-        <v>-0.43529043335779305</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1.11</v>
-      </c>
-      <c r="H70" s="3">
-        <v>31.64</v>
-      </c>
-      <c r="I70" s="3">
-        <v>-32.43</v>
-      </c>
-      <c r="J70" s="3">
-        <v>-0.036819047674802624</v>
-      </c>
-      <c r="K70" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>-65</v>
-      </c>
-      <c r="M70" s="3">
-        <v>-0.4236296272543574</v>
-      </c>
-      <c r="N70" s="3">
-        <v>-30.687229904130596</v>
-      </c>
-      <c r="O70" s="3">
-        <v>1.2658227848101267</v>
-      </c>
-      <c r="P70" s="3">
-        <v>37.53319428279413</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>35.822784810126585</v>
-      </c>
-      <c r="R70" s="3">
-        <v>21.835443037974688</v>
-      </c>
-      <c r="S70" s="3" t="s">
+      <c r="E70" s="1">
+        <v>-0.71</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-0.4000754419052832</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H70" s="1">
+        <v>57.58</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-24.28</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.018169950028812467</v>
+      </c>
+      <c r="K70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1">
+        <v>-99</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.3837651861534227</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-25.65133593544192</v>
+      </c>
+      <c r="O70" s="1">
+        <v>2.5316455696202533</v>
+      </c>
+      <c r="P70" s="1">
+        <v>36.83258048205344</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>41.645569620253156</v>
+      </c>
+      <c r="R70" s="1">
+        <v>22.91139240506329</v>
+      </c>
+      <c r="S70" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="T70" s="3">
+      <c r="T70" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6411,119 +6423,119 @@
         <v>5.18</v>
       </c>
       <c r="C71" s="3">
-        <v>60.75949367088608</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="D71" s="3">
-        <v>0.7837837837837839</v>
+        <v>0.7683397683397685</v>
       </c>
       <c r="E71" s="3">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.2817255110945516</v>
+        <v>-0.20331765997996998</v>
       </c>
       <c r="G71" s="3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H71" s="3">
-        <v>50.24</v>
+        <v>58.35</v>
       </c>
       <c r="I71" s="3">
-        <v>-7.12</v>
+        <v>-2.85</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.011991913113487167</v>
+        <v>0.0031967856605229932</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-20</v>
+        <v>-67</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.28066543781242104</v>
+        <v>-0.2009876234439899</v>
       </c>
       <c r="N71" s="3">
-        <v>-16.39081095993696</v>
+        <v>-7.373579664498636</v>
       </c>
       <c r="O71" s="3">
-        <v>11.39240506329114</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P71" s="3">
         <v>19.13407224404345</v>
       </c>
       <c r="Q71" s="3">
-        <v>40.126582278481</v>
+        <v>47.34177215189873</v>
       </c>
       <c r="R71" s="3">
-        <v>26.202531645569618</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T71" s="3">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="1">
         <v>10.42</v>
       </c>
-      <c r="C72" s="3">
-        <v>78.48101265822784</v>
-      </c>
-      <c r="D72" s="3">
-        <v>0.21305182341650677</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1.31</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-0.30054631759780803</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1.14</v>
-      </c>
-      <c r="H72" s="3">
-        <v>39.88</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-9.12</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-0.013340396526671216</v>
-      </c>
-      <c r="K72" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3">
-        <v>55</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-0.28570529164798086</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-16.894796343492946</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="C72" s="1">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.21976967370441466</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-0.66</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.30326078534406276</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.12</v>
+      </c>
+      <c r="H72" s="1">
+        <v>40.27</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-10.32</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.0033509170299639633</v>
+      </c>
+      <c r="K72" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>2</v>
+      </c>
+      <c r="M72" s="1">
+        <v>-0.2892805661281823</v>
+      </c>
+      <c r="N72" s="1">
+        <v>-16.202873932917885</v>
+      </c>
+      <c r="O72" s="1">
         <v>10.126582278481013</v>
       </c>
-      <c r="P72" s="3">
-        <v>18.537307083411516</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>39.24050632911392</v>
-      </c>
-      <c r="R72" s="3">
-        <v>27.468354430379748</v>
-      </c>
-      <c r="S72" s="3" t="s">
+      <c r="P72" s="1">
+        <v>19.739671794345924</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>40.75949367088607</v>
+      </c>
+      <c r="R72" s="1">
+        <v>28.734177215189874</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6535,52 +6547,52 @@
         <v>0.61</v>
       </c>
       <c r="C73" s="2">
-        <v>36.708860759493675</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="D73" s="2">
-        <v>22.40983606557377</v>
+        <v>20.426229508196723</v>
       </c>
       <c r="E73" s="2">
-        <v>0.1</v>
+        <v>3.07</v>
       </c>
       <c r="F73" s="2">
-        <v>0.2318061407146457</v>
+        <v>0.41667914403818085</v>
       </c>
       <c r="G73" s="2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>61.8</v>
+        <v>71.02</v>
       </c>
       <c r="I73" s="2">
-        <v>41.61</v>
+        <v>49.38</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03293282383472466</v>
+        <v>0.032868509631875445</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M73" s="2">
-        <v>0.24982738651086445</v>
+        <v>0.4376494728620015</v>
       </c>
       <c r="N73" s="2">
-        <v>36.658471472391575</v>
+        <v>56.49012996610049</v>
       </c>
       <c r="O73" s="2">
-        <v>83.54430379746836</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>65.56962025316456</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="R73" s="2">
-        <v>61.0126582278481</v>
+        <v>61.329113924050645</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
@@ -6603,46 +6615,46 @@
         <v>14.25</v>
       </c>
       <c r="E74" s="2">
-        <v>2.01</v>
+        <v>1.29</v>
       </c>
       <c r="F74" s="2">
-        <v>0.171837599993916</v>
+        <v>0.15446813736025394</v>
       </c>
       <c r="G74" s="2">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="H74" s="2">
-        <v>83.02</v>
+        <v>84.5</v>
       </c>
       <c r="I74" s="2">
-        <v>32.23</v>
+        <v>29.69</v>
       </c>
       <c r="J74" s="2">
-        <v>0.021742148422753137</v>
+        <v>0.014660665616865597</v>
       </c>
       <c r="K74" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.1495760610691752</v>
+        <v>0.1288377354644732</v>
       </c>
       <c r="N74" s="2">
-        <v>26.633338928222656</v>
+        <v>25.60895622634767</v>
       </c>
       <c r="O74" s="2">
-        <v>72.15189873417721</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>65.0632911392405</v>
+        <v>63.0379746835443</v>
       </c>
       <c r="R74" s="2">
-        <v>56.32911392405063</v>
+        <v>55.8860759493671</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
@@ -6652,127 +6664,127 @@
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="3">
         <v>0.44</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="3">
         <v>34.177215189873415</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="3">
         <v>29.204545454545453</v>
       </c>
-      <c r="E75" s="1">
-        <v>-0.71</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0.0822037529066603</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.96</v>
-      </c>
-      <c r="H75" s="1">
-        <v>60.47</v>
-      </c>
-      <c r="I75" s="1">
-        <v>14.82</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0.00564206762993544</v>
-      </c>
-      <c r="K75" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="1">
-        <v>6</v>
-      </c>
-      <c r="M75" s="1">
-        <v>0.07796345977813823</v>
-      </c>
-      <c r="N75" s="1">
-        <v>19.47207879911897</v>
-      </c>
-      <c r="O75" s="1">
-        <v>65.82278481012658</v>
-      </c>
-      <c r="P75" s="1">
+      <c r="E75" s="3">
+        <v>-0.35</v>
+      </c>
+      <c r="F75" s="3">
+        <v>-0.04979081023370874</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="H75" s="3">
+        <v>57.83</v>
+      </c>
+      <c r="I75" s="3">
+        <v>15.62</v>
+      </c>
+      <c r="J75" s="3">
+        <v>0.02491621190012164</v>
+      </c>
+      <c r="K75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3">
+        <v>-0.05328586503767885</v>
+      </c>
+      <c r="N75" s="3">
+        <v>7.396596176132468</v>
+      </c>
+      <c r="O75" s="3">
+        <v>48.10126582278481</v>
+      </c>
+      <c r="P75" s="3">
         <v>37.05001195108517</v>
       </c>
-      <c r="Q75" s="1">
-        <v>58.10126582278481</v>
-      </c>
-      <c r="R75" s="1">
-        <v>46.45569620253164</v>
-      </c>
-      <c r="S75" s="1" t="s">
+      <c r="Q75" s="3">
+        <v>61.0126582278481</v>
+      </c>
+      <c r="R75" s="3">
+        <v>42.53164556962026</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T75" s="1">
+      <c r="T75" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="3">
         <v>2.05</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="3">
         <v>48.10126582278481</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="3">
         <v>0.7170731707317075</v>
       </c>
-      <c r="E76" s="1">
-        <v>2.63</v>
-      </c>
-      <c r="F76" s="1">
-        <v>0.036085675669937756</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="H76" s="1">
-        <v>58.72</v>
-      </c>
-      <c r="I76" s="1">
-        <v>18.77</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0.018217078308452244</v>
-      </c>
-      <c r="K76" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="1">
-        <v>6</v>
-      </c>
-      <c r="M76" s="1">
-        <v>0.006403623770283362</v>
-      </c>
-      <c r="N76" s="1">
-        <v>12.316095198333482</v>
-      </c>
-      <c r="O76" s="1">
-        <v>58.22784810126582</v>
-      </c>
-      <c r="P76" s="1">
-        <v>17.05597509098574</v>
-      </c>
-      <c r="Q76" s="1">
-        <v>50.253164556962034</v>
-      </c>
-      <c r="R76" s="1">
-        <v>42.21518987341772</v>
-      </c>
-      <c r="S76" s="1" t="s">
+      <c r="E76" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-0.005997696179985912</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="H76" s="3">
+        <v>43.42</v>
+      </c>
+      <c r="I76" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.008843483003461172</v>
+      </c>
+      <c r="K76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
+        <v>-0.042113262487676995</v>
+      </c>
+      <c r="N76" s="3">
+        <v>8.513856431132655</v>
+      </c>
+      <c r="O76" s="3">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="P76" s="3">
+        <v>16.982798273104898</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>43.797468354430386</v>
+      </c>
+      <c r="R76" s="3">
+        <v>39.43037974683544</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T76" s="1">
-        <v>0.76</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6789,46 +6801,46 @@
         <v>281.33333333333337</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.34</v>
+        <v>2.54</v>
       </c>
       <c r="F77" s="2">
-        <v>0.01240752414840536</v>
+        <v>0.038696449727504856</v>
       </c>
       <c r="G77" s="2">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2">
-        <v>66.79</v>
+        <v>66.57</v>
       </c>
       <c r="I77" s="2">
-        <v>11.55</v>
+        <v>15.35</v>
       </c>
       <c r="J77" s="2">
-        <v>0.008247007365014443</v>
+        <v>0.018449106123646638</v>
       </c>
       <c r="K77" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M77" s="2">
-        <v>0.01028737758414433</v>
+        <v>0.038696449727504856</v>
       </c>
       <c r="N77" s="2">
-        <v>12.70447057971958</v>
+        <v>16.59482765265084</v>
       </c>
       <c r="O77" s="2">
-        <v>59.49367088607595</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>62.91139240506329</v>
+        <v>63.41772151898735</v>
       </c>
       <c r="R77" s="2">
-        <v>54.43037974683545</v>
+        <v>53.9873417721519</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
@@ -6838,64 +6850,64 @@
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="3">
         <v>13.11</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="3">
         <v>84.81012658227847</v>
       </c>
-      <c r="D78" s="1">
-        <v>-0.6414950419527079</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.57</v>
-      </c>
-      <c r="F78" s="1">
-        <v>0.13799643285872165</v>
-      </c>
-      <c r="G78" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="H78" s="1">
-        <v>74.84</v>
-      </c>
-      <c r="I78" s="1">
-        <v>37.38</v>
-      </c>
-      <c r="J78" s="1">
-        <v>0.02693996293552387</v>
-      </c>
-      <c r="K78" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" s="1">
-        <v>144</v>
-      </c>
-      <c r="M78" s="1">
-        <v>0.16555833819411503</v>
-      </c>
-      <c r="N78" s="1">
-        <v>28.23156664071665</v>
-      </c>
-      <c r="O78" s="1">
-        <v>73.41772151898735</v>
-      </c>
-      <c r="P78" s="1">
+      <c r="D78" s="3">
+        <v>-0.7337909992372235</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.05350237860146659</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="H78" s="3">
+        <v>52.46</v>
+      </c>
+      <c r="I78" s="3">
+        <v>25.62</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0.02293384813930577</v>
+      </c>
+      <c r="K78" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="3">
+        <v>58</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0.08146281703322744</v>
+      </c>
+      <c r="N78" s="3">
+        <v>20.871464383223103</v>
+      </c>
+      <c r="O78" s="3">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="P78" s="3">
         <v>20.806025084936465</v>
       </c>
-      <c r="Q78" s="1">
-        <v>60.50632911392405</v>
-      </c>
-      <c r="R78" s="1">
-        <v>49.683544303797476</v>
-      </c>
-      <c r="S78" s="1" t="s">
+      <c r="Q78" s="3">
+        <v>53.29113924050633</v>
+      </c>
+      <c r="R78" s="3">
+        <v>46.39240506329114</v>
+      </c>
+      <c r="S78" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T78" s="1">
+      <c r="T78" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6910,55 +6922,55 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="2">
-        <v>2.4527687296416936</v>
+        <v>2.8338762214983713</v>
       </c>
       <c r="E79" s="2">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4238631562787893</v>
+        <v>0.38939267242051206</v>
       </c>
       <c r="G79" s="2">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="H79" s="2">
-        <v>87.31</v>
+        <v>75.71</v>
       </c>
       <c r="I79" s="2">
-        <v>50.65</v>
+        <v>52.72</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0276716970655234</v>
+        <v>0.046187919958216896</v>
       </c>
       <c r="K79" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="M79" s="2">
-        <v>0.4164426433038757</v>
+        <v>0.38822765415252203</v>
       </c>
       <c r="N79" s="2">
-        <v>53.31999715169271</v>
+        <v>51.54794809515255</v>
       </c>
       <c r="O79" s="2">
-        <v>87.34177215189874</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>64.55696202531645</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="R79" s="2">
-        <v>58.037974683544306</v>
+        <v>57.59493670886076</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6966,61 +6978,61 @@
         <v>127</v>
       </c>
       <c r="B80" s="2">
-        <v>8.72</v>
+        <v>12.58</v>
       </c>
       <c r="C80" s="2">
-        <v>75.9493670886076</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8119266055045871</v>
+        <v>0.6200317965023846</v>
       </c>
       <c r="E80" s="2">
-        <v>5.52</v>
+        <v>-1.21</v>
       </c>
       <c r="F80" s="2">
-        <v>1.0587470216818125</v>
+        <v>1.7012179705803887</v>
       </c>
       <c r="G80" s="2">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="H80" s="2">
-        <v>66.13</v>
+        <v>89.38</v>
       </c>
       <c r="I80" s="2">
-        <v>67.76</v>
+        <v>172.87</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0584419134804722</v>
+        <v>0.08913157090404351</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L80" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>1.0598070949639429</v>
+        <v>1.7151981897962691</v>
       </c>
       <c r="N80" s="2">
-        <v>117.65644231769943</v>
+        <v>184.24500165952725</v>
       </c>
       <c r="O80" s="2">
-        <v>96.20253164556962</v>
+        <v>100</v>
       </c>
       <c r="P80" s="2">
-        <v>16.957009573963198</v>
+        <v>13.090769137273101</v>
       </c>
       <c r="Q80" s="2">
-        <v>68.60759493670886</v>
+        <v>73.16455696202533</v>
       </c>
       <c r="R80" s="2">
-        <v>64.24050632911393</v>
+        <v>67.34177215189875</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7039,7 +7051,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7047,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32.84810126582278</v>
+        <v>27.21518987341772</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7055,7 +7067,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>64.9367088607595</v>
+        <v>65.37974683544304</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7063,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>14.810126582278478</v>
+        <v>41.265822784810126</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7071,7 +7083,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>45.31645569620254</v>
+        <v>46.139240506329116</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7079,7 +7091,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42.08860759493671</v>
+        <v>27.341772151898734</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7087,7 +7099,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.55696202531646</v>
+        <v>52.848101265822784</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7095,7 +7107,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.316455696202524</v>
+        <v>52.40506329113924</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7103,7 +7115,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41.202531645569614</v>
+        <v>42.46835443037975</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7111,7 +7123,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.79746835443038</v>
+        <v>34.74683544303798</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7119,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>46.455696202531655</v>
+        <v>51.139240506329116</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7127,7 +7139,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>20.696202531645564</v>
+        <v>42.53164556962026</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7135,7 +7147,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>15.88607594936709</v>
+        <v>4.113924050632909</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7143,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>35.189873417721515</v>
+        <v>52.65822784810126</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7151,7 +7163,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>61.962025316455694</v>
+        <v>60.8860759493671</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7159,7 +7171,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36.64556962025316</v>
+        <v>29.367088607594937</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7167,7 +7179,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>23.164556962025316</v>
+        <v>21.455696202531644</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7175,7 +7187,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>30.949367088607595</v>
+        <v>27.15189873417722</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7183,7 +7195,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>40.8860759493671</v>
+        <v>41.64556962025317</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7191,7 +7203,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.405063291139236</v>
+        <v>41.89873417721519</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7199,7 +7211,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>38.79746835443038</v>
+        <v>55.822784810126585</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7207,7 +7219,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.253164556962027</v>
+        <v>36.075949367088604</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7215,7 +7227,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>31.962025316455694</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7223,7 +7235,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>31.0126582278481</v>
+        <v>23.037974683544306</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7231,7 +7243,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11.962025316455694</v>
+        <v>9.113924050632914</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7239,7 +7251,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33.037974683544306</v>
+        <v>33.79746835443038</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7247,7 +7259,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>26.392405063291136</v>
+        <v>29.050632911392405</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7255,7 +7267,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21.898734177215193</v>
+        <v>24.367088607594937</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7263,7 +7275,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>24.36708860759493</v>
+        <v>37.215189873417714</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7271,7 +7283,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>47.53164556962025</v>
+        <v>48.79746835443037</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7279,7 +7291,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>60.822784810126585</v>
+        <v>60.88607594936709</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7287,7 +7299,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>29.36708860759494</v>
+        <v>28.22784810126582</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7295,7 +7307,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>39.9367088607595</v>
+        <v>43.291139240506325</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7303,7 +7315,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>51.139240506329116</v>
+        <v>47.21518987341773</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7311,7 +7323,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>21.582278481012658</v>
+        <v>21.455696202531644</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7319,7 +7331,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>34.30379746835443</v>
+        <v>27.658227848101266</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7327,7 +7339,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>38.797468354430386</v>
+        <v>29.55696202531646</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7335,7 +7347,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>53.92405063291139</v>
+        <v>55.949367088607595</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7343,7 +7355,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>53.41772151898734</v>
+        <v>37.848101265822784</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7351,7 +7363,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>40.75949367088608</v>
+        <v>25.886075949367083</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7359,7 +7371,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>30.063291139240505</v>
+        <v>35.69620253164557</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7367,7 +7379,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.54430379746835</v>
+        <v>33.164556962025316</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7375,7 +7387,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>42.151898734177216</v>
+        <v>46.835443037974684</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7383,7 +7395,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>26.518987341772146</v>
+        <v>33.35443037974684</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7391,7 +7403,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>56.962025316455694</v>
+        <v>55.063291139240505</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7399,7 +7411,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>31.39240506329114</v>
+        <v>27.721518987341767</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7407,7 +7419,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.759493670886073</v>
+        <v>23.607594936708868</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7415,7 +7427,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>63.037974683544306</v>
+        <v>55.063291139240505</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7423,7 +7435,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>63.544303797468345</v>
+        <v>61.13924050632911</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7431,7 +7443,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>21.77215189873418</v>
+        <v>23.860759493670876</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7439,7 +7451,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>26.64556962025317</v>
+        <v>43.164556962025316</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7447,7 +7459,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>56.77215189873419</v>
+        <v>58.41772151898735</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7455,7 +7467,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>35.12658227848102</v>
+        <v>40.632911392405056</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7463,7 +7475,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>52.65822784810126</v>
+        <v>53.98734177215191</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7471,7 +7483,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>36.582278481012665</v>
+        <v>42.08860759493671</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7479,7 +7491,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>33.98734177215189</v>
+        <v>33.10126582278481</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7487,7 +7499,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>67.34177215189874</v>
+        <v>67.40506329113924</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7495,7 +7507,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>55.31645569620253</v>
+        <v>53.164556962025316</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7503,7 +7515,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>56.582278481012665</v>
+        <v>46.835443037974684</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7511,7 +7523,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>28.79746835443038</v>
+        <v>24.746835443037973</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7519,7 +7531,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>42.848101265822784</v>
+        <v>33.10126582278481</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7527,7 +7539,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>72.34177215189874</v>
+        <v>72.08860759493672</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7535,7 +7547,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>66.96202531645571</v>
+        <v>66.45569620253164</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7543,7 +7555,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>37.40506329113924</v>
+        <v>32.53164556962025</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7551,7 +7563,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>29.050632911392405</v>
+        <v>18.10126582278481</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7559,7 +7571,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>44.11392405063291</v>
+        <v>34.49367088607595</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7567,7 +7579,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>44.936708860759495</v>
+        <v>46.265822784810126</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7575,7 +7587,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>27.72151898734177</v>
+        <v>24.620253164556964</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7583,7 +7595,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.72151898734177</v>
+        <v>32.0253164556962</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7591,7 +7603,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>21.835443037974688</v>
+        <v>22.91139240506329</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7599,7 +7611,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>26.202531645569618</v>
+        <v>33.164556962025316</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7607,7 +7619,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>27.468354430379748</v>
+        <v>28.734177215189874</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7615,7 +7627,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>61.0126582278481</v>
+        <v>61.329113924050645</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7623,7 +7635,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>56.32911392405063</v>
+        <v>55.8860759493671</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7631,7 +7643,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>46.45569620253164</v>
+        <v>42.53164556962026</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7639,7 +7651,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>42.21518987341772</v>
+        <v>39.43037974683544</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7647,7 +7659,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>54.43037974683545</v>
+        <v>53.9873417721519</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7655,7 +7667,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>49.683544303797476</v>
+        <v>46.39240506329114</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7663,7 +7675,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>58.037974683544306</v>
+        <v>57.59493670886076</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7671,7 +7683,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>64.24050632911393</v>
+        <v>67.34177215189875</v>
       </c>
     </row>
   </sheetData>
@@ -7690,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7701,7 +7713,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7712,10 +7724,10 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7723,10 +7735,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7734,10 +7746,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7745,82 +7757,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7839,15 +7851,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7855,98 +7867,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7965,10 +7977,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7976,7 +7988,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7987,10 +7999,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7998,90 +8010,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8100,10 +8112,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8111,7 +8123,7 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8119,106 +8131,106 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -8234,212 +8246,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" t="s">
         <v>182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" t="s">
         <v>192</v>
-      </c>
-      <c r="B6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" t="s">
         <v>199</v>
       </c>
-      <c r="B9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" t="s">
-        <v>198</v>
-      </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -337,7 +337,7 @@
     <t>2026-05-11</t>
   </si>
   <si>
-    <t>2026-04-30</t>
+    <t>2027-04-30</t>
   </si>
   <si>
     <t>2027-04-29</t>
@@ -1689,7 +1689,7 @@
         <v>43.291139240506325</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1914,13 +1914,13 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B51">
-        <v>29.367088607594937</v>
+        <v>32.0253164556962</v>
       </c>
       <c r="C51" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4091,7 +4091,7 @@
         <v>0.006795185819069533</v>
       </c>
       <c r="K33" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="3">
         <v>5</v>
@@ -6323,7 +6323,7 @@
         <v>-0.0006359513945416026</v>
       </c>
       <c r="K69" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="3">
         <v>-60</v>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="234">
   <si>
     <t>Ticker</t>
   </si>
@@ -418,15 +418,24 @@
     <t>Value</t>
   </si>
   <si>
+    <t>RAPP</t>
+  </si>
+  <si>
     <t>Last Run</t>
   </si>
   <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
     <t>Index</t>
   </si>
   <si>
     <t>Russell 2000</t>
   </si>
   <si>
+    <t>OFG</t>
+  </si>
+  <si>
     <t>Cap</t>
   </si>
   <si>
@@ -496,7 +505,7 @@
     <t>Results</t>
   </si>
   <si>
-    <t>5 of 5 qualified</t>
+    <t>3 of 3 qualified</t>
   </si>
   <si>
     <t>Dow Jones 30</t>
@@ -514,37 +523,37 @@
     <t>All sectors</t>
   </si>
   <si>
+    <t>1 of 1 qualified</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 (large-cap subset)</t>
+  </si>
+  <si>
+    <t>Large (approx. S&amp;P 100)</t>
+  </si>
+  <si>
+    <t>&gt; +8%</t>
+  </si>
+  <si>
+    <t>&lt; 40</t>
+  </si>
+  <si>
     <t>0 of 0 qualified</t>
-  </si>
-  <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>3 of 3 qualified</t>
-  </si>
-  <si>
-    <t>S&amp;P 500 (large-cap subset)</t>
-  </si>
-  <si>
-    <t>Large (approx. S&amp;P 100)</t>
-  </si>
-  <si>
-    <t>&gt; +8%</t>
-  </si>
-  <si>
-    <t>&lt; 40</t>
-  </si>
-  <si>
-    <t>1 of 1 qualified</t>
   </si>
   <si>
     <t>Component</t>
@@ -1367,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1381,7 +1390,7 @@
         <v>72.08860759493672</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1392,7 +1401,7 @@
         <v>67.40506329113924</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1403,7 +1412,7 @@
         <v>67.34177215189875</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1414,7 +1423,7 @@
         <v>66.45569620253164</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1425,7 +1434,7 @@
         <v>65.37974683544304</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1436,7 +1445,7 @@
         <v>61.329113924050645</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1447,7 +1456,7 @@
         <v>61.13924050632911</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1458,7 +1467,7 @@
         <v>60.8860759493671</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1469,7 +1478,7 @@
         <v>60.88607594936709</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1480,7 +1489,7 @@
         <v>58.41772151898735</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1491,7 +1500,7 @@
         <v>57.59493670886076</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1502,7 +1511,7 @@
         <v>55.949367088607595</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1513,7 +1522,7 @@
         <v>55.8860759493671</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1524,7 +1533,7 @@
         <v>55.822784810126585</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1535,7 +1544,7 @@
         <v>55.063291139240505</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1546,7 +1555,7 @@
         <v>55.063291139240505</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1557,7 +1566,7 @@
         <v>53.98734177215191</v>
       </c>
       <c r="C18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1568,7 +1577,7 @@
         <v>53.9873417721519</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1579,7 +1588,7 @@
         <v>53.164556962025316</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1590,7 +1599,7 @@
         <v>52.65822784810126</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1601,7 +1610,7 @@
         <v>52.40506329113924</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1612,7 +1621,7 @@
         <v>51.139240506329116</v>
       </c>
       <c r="C23" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1623,7 +1632,7 @@
         <v>48.79746835443037</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1634,7 +1643,7 @@
         <v>47.21518987341773</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1645,7 +1654,7 @@
         <v>46.835443037974684</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1656,7 +1665,7 @@
         <v>46.835443037974684</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1667,7 +1676,7 @@
         <v>46.39240506329114</v>
       </c>
       <c r="C28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1678,7 +1687,7 @@
         <v>46.265822784810126</v>
       </c>
       <c r="C29" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1689,7 +1698,7 @@
         <v>43.291139240506325</v>
       </c>
       <c r="C30" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1700,7 +1709,7 @@
         <v>43.164556962025316</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1711,7 +1720,7 @@
         <v>42.53164556962026</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1722,7 +1731,7 @@
         <v>42.53164556962026</v>
       </c>
       <c r="C33" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1733,7 +1742,7 @@
         <v>42.08860759493671</v>
       </c>
       <c r="C34" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1744,7 +1753,7 @@
         <v>41.89873417721519</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1755,7 +1764,7 @@
         <v>41.64556962025317</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1766,7 +1775,7 @@
         <v>41.265822784810126</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1777,7 +1786,7 @@
         <v>40.632911392405056</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1788,7 +1797,7 @@
         <v>39.43037974683544</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1799,7 +1808,7 @@
         <v>37.848101265822784</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1810,7 +1819,7 @@
         <v>37.215189873417714</v>
       </c>
       <c r="C41" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1821,7 +1830,7 @@
         <v>36.075949367088604</v>
       </c>
       <c r="C42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1832,7 +1841,7 @@
         <v>35.69620253164557</v>
       </c>
       <c r="C43" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1843,7 +1852,7 @@
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1854,7 +1863,7 @@
         <v>34.49367088607595</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1865,7 +1874,7 @@
         <v>33.79746835443038</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1876,7 +1885,7 @@
         <v>33.164556962025316</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1887,7 +1896,7 @@
         <v>33.10126582278481</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1898,7 +1907,7 @@
         <v>33.10126582278481</v>
       </c>
       <c r="C49" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1909,7 +1918,7 @@
         <v>32.53164556962025</v>
       </c>
       <c r="C50" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1920,7 +1929,7 @@
         <v>32.0253164556962</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -7710,13 +7719,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7724,21 +7733,21 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7746,10 +7755,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7757,82 +7766,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7857,108 +7866,111 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -7985,115 +7997,115 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -8123,114 +8135,114 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -8246,212 +8258,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" t="s">
         <v>183</v>
       </c>
-      <c r="B3" t="s">
-        <v>180</v>
-      </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" t="s">
         <v>193</v>
       </c>
-      <c r="B6" t="s">
-        <v>190</v>
-      </c>
       <c r="C6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" t="s">
         <v>202</v>
       </c>
-      <c r="B11" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" t="s">
-        <v>199</v>
-      </c>
       <c r="D11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="226">
   <si>
     <t>Ticker</t>
   </si>
@@ -256,13 +256,13 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>RSI</t>
+    <t>RSI_14Day</t>
   </si>
   <si>
     <t>SMA200_Dist</t>
   </si>
   <si>
-    <t>MA_Slope</t>
+    <t>MA_Slope_50</t>
   </si>
   <si>
     <t>Volume_Expansion</t>
@@ -283,141 +283,147 @@
     <t>Drawdown_%</t>
   </si>
   <si>
-    <t>Old_Score</t>
-  </si>
-  <si>
-    <t>New_Score</t>
+    <t>Composite_Score</t>
+  </si>
+  <si>
+    <t>New_Composite_Score</t>
   </si>
   <si>
     <t>Earnings_Date</t>
   </si>
   <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
+    <t>Daily_Composite_Score_delta</t>
+  </si>
+  <si>
+    <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>2027-05-05</t>
   </si>
   <si>
     <t>2026-05-27</t>
   </si>
   <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
+    <t>2027-04-22</t>
+  </si>
+  <si>
+    <t>2027-04-16</t>
   </si>
   <si>
     <t>2026-05-20</t>
   </si>
   <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
+    <t>2027-04-21</t>
+  </si>
+  <si>
+    <t>2027-05-04</t>
+  </si>
+  <si>
+    <t>2027-05-06</t>
   </si>
   <si>
     <t>2026-05-28</t>
   </si>
   <si>
-    <t>2027-03-03</t>
+    <t>2026-06-02</t>
   </si>
   <si>
     <t>2027-03-10</t>
   </si>
   <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
+    <t>2027-04-23</t>
+  </si>
+  <si>
+    <t>2027-05-11</t>
+  </si>
+  <si>
+    <t>2027-04-30</t>
+  </si>
+  <si>
+    <t>2027-04-29</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
+  </si>
+  <si>
+    <t>2027-05-07</t>
   </si>
   <si>
     <t>2026-06-03</t>
   </si>
   <si>
-    <t>2026-04-27</t>
+    <t>2027-04-27</t>
+  </si>
+  <si>
+    <t>2027-05-14</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2027-05-13</t>
+  </si>
+  <si>
+    <t>2027-04-15</t>
+  </si>
+  <si>
+    <t>2027-04-14</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>ATEN</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>OMCL</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>_date_</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Last Run</t>
   </si>
   <si>
     <t>2026-05-14</t>
   </si>
   <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2027-04-14</t>
-  </si>
-  <si>
-    <t>2027-03-18</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2027-03-31</t>
-  </si>
-  <si>
-    <t>ATEN</t>
-  </si>
-  <si>
-    <t>WSR</t>
-  </si>
-  <si>
-    <t>2027-02-25</t>
-  </si>
-  <si>
-    <t>OMCL</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>SHO</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>_date_</t>
-  </si>
-  <si>
-    <t>Criteria</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Last Run</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
@@ -664,40 +670,31 @@
     <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
     <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Volume Spike</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
@@ -725,7 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -735,7 +732,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1355,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1366,32 +1363,32 @@
         <v>61</v>
       </c>
       <c r="B2">
-        <v>72.34177215189874</v>
+        <v>72.59493670886076</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3">
-        <v>67.34177215189874</v>
+        <v>68.54430379746836</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B4">
-        <v>66.96202531645571</v>
+        <v>67.27848101265823</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1399,10 +1396,10 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>64.9367088607595</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1410,32 +1407,32 @@
         <v>127</v>
       </c>
       <c r="B6">
-        <v>64.24050632911393</v>
+        <v>64.30379746835445</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="B7">
-        <v>63.544303797468345</v>
+        <v>63.0379746835443</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8">
-        <v>63.037974683544306</v>
+        <v>61.70886075949366</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1443,304 +1440,304 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>61.962025316455694</v>
+        <v>61.139240506329116</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10">
-        <v>61.0126582278481</v>
+        <v>60.94936708860761</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B11">
-        <v>60.822784810126585</v>
+        <v>60.25316455696203</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="B12">
-        <v>58.037974683544306</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="B13">
-        <v>56.962025316455694</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>56.77215189873419</v>
+        <v>57.53164556962025</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>56.582278481012665</v>
+        <v>56.58227848101266</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="B16">
-        <v>56.32911392405063</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>55.31645569620253</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="B18">
-        <v>55.316455696202524</v>
+        <v>53.41772151898735</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="B19">
-        <v>54.55696202531646</v>
+        <v>52.21518987341773</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>54.43037974683545</v>
+        <v>52.025316455696206</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>53.92405063291139</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B22">
-        <v>53.41772151898734</v>
+        <v>51.83544303797468</v>
       </c>
       <c r="C22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
-        <v>52.65822784810126</v>
+        <v>50.75949367088607</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>51.139240506329116</v>
+        <v>50.506329113924046</v>
       </c>
       <c r="C24" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>49.683544303797476</v>
+        <v>50.063291139240505</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="B26">
-        <v>47.53164556962025</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27">
-        <v>46.455696202531655</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28">
-        <v>46.45569620253164</v>
+        <v>48.60759493670886</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B29">
-        <v>45.31645569620254</v>
+        <v>47.53164556962025</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B30">
-        <v>44.936708860759495</v>
+        <v>47.34177215189874</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31">
-        <v>42.848101265822784</v>
+        <v>45.949367088607595</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="B32">
-        <v>42.21518987341772</v>
+        <v>45.31645569620254</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B33">
-        <v>42.151898734177216</v>
+        <v>44.683544303797476</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>42.08860759493671</v>
+        <v>43.924050632911396</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="B35">
-        <v>41.202531645569614</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B36">
-        <v>40.8860759493671</v>
+        <v>43.607594936708864</v>
       </c>
       <c r="C36" t="s">
         <v>223</v>
@@ -1748,145 +1745,145 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B37">
-        <v>40.75949367088608</v>
+        <v>43.22784810126582</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B38">
-        <v>39.9367088607595</v>
+        <v>42.21518987341773</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B39">
-        <v>38.79746835443038</v>
+        <v>41.139240506329116</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B40">
-        <v>38.54430379746835</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>37.40506329113924</v>
+        <v>38.54430379746835</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>36.64556962025316</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B43">
-        <v>36.582278481012665</v>
+        <v>38.41772151898734</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B44">
-        <v>35.189873417721515</v>
+        <v>37.911392405063296</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B45">
-        <v>35.12658227848102</v>
+        <v>36.39240506329114</v>
       </c>
       <c r="C45" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B46">
-        <v>34.30379746835443</v>
+        <v>36.07594936708861</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B47">
-        <v>33.98734177215189</v>
+        <v>34.936708860759495</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B48">
-        <v>33.037974683544306</v>
+        <v>34.87341772151899</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B49">
-        <v>32.84810126582278</v>
+        <v>33.73417721518988</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1894,21 +1891,21 @@
         <v>22</v>
       </c>
       <c r="B50">
-        <v>31.962025316455694</v>
+        <v>31.51898734177215</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B51">
-        <v>31.39240506329114</v>
+        <v>28.101265822784814</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2133,58 +2130,58 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>64.55696202531645</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.5446880269814502</v>
+        <v>-1.8853288364249579</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.01238980890086984</v>
+        <v>-0.08553141804598512</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H2" s="1">
-        <v>51.62</v>
+        <v>43.27</v>
       </c>
       <c r="I2" s="1">
-        <v>17.75</v>
+        <v>9.72</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0010214726622593266</v>
+        <v>-0.012152836818527623</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.09931581803557199</v>
+        <v>-0.1786283083249839</v>
       </c>
       <c r="N2" s="1">
-        <v>1.744151017747948</v>
+        <v>-5.835255505557358</v>
       </c>
       <c r="O2" s="1">
-        <v>41.77215189873418</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>41.89873417721519</v>
+        <v>32.53164556962025</v>
       </c>
       <c r="R2" s="1">
-        <v>32.84810126582278</v>
+        <v>25.379746835443036</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2198,49 +2195,49 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>23.98032786885246</v>
+        <v>24.422950819672135</v>
       </c>
       <c r="E3" s="2">
-        <v>2.08</v>
+        <v>-0.89</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8977684935470766</v>
+        <v>1.3618073050886133</v>
       </c>
       <c r="G3" s="2">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="H3" s="2">
-        <v>76.34</v>
+        <v>60.45</v>
       </c>
       <c r="I3" s="2">
-        <v>100.36</v>
+        <v>101.46</v>
       </c>
       <c r="J3" s="2">
-        <v>0.10087590049150968</v>
+        <v>0.0782117922997919</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="M3" s="2">
-        <v>1.04935897289174</v>
+        <v>1.5250006774600346</v>
       </c>
       <c r="N3" s="2">
-        <v>116.61163011047915</v>
+        <v>164.5276430729445</v>
       </c>
       <c r="O3" s="2">
-        <v>94.9367088607595</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>76.07594936708861</v>
+        <v>74.05063291139241</v>
       </c>
       <c r="R3" s="2">
-        <v>64.9367088607595</v>
+        <v>65</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
@@ -2254,55 +2251,55 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>-3.95</v>
+        <v>-3.51</v>
       </c>
       <c r="C4" s="3">
-        <v>6.329113924050633</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="D4" s="3">
-        <v>9.865822784810128</v>
+        <v>12.64102564102564</v>
       </c>
       <c r="E4" s="3">
-        <v>2.62</v>
+        <v>-1.7</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.25742575530792045</v>
+        <v>0.1432166928258231</v>
       </c>
       <c r="G4" s="3">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="H4" s="3">
-        <v>52.47</v>
+        <v>61.67</v>
       </c>
       <c r="I4" s="3">
-        <v>-25.95</v>
+        <v>13.25</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.011147903158076383</v>
+        <v>0.0511211768659595</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>-69</v>
+        <v>-92</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.2468250224866153</v>
+        <v>0.18264596400281086</v>
       </c>
       <c r="N4" s="3">
-        <v>-13.006769427356394</v>
+        <v>30.292171727222122</v>
       </c>
       <c r="O4" s="3">
-        <v>15.18987341772152</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P4" s="3">
-        <v>48.360550359989794</v>
+        <v>43.93055527298539</v>
       </c>
       <c r="Q4" s="3">
-        <v>31.0126582278481</v>
+        <v>56.20253164556962</v>
       </c>
       <c r="R4" s="3">
-        <v>14.810126582278478</v>
+        <v>43.607594936708864</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
@@ -2312,64 +2309,64 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>1.09</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>43.037974683544306</v>
       </c>
-      <c r="D5" s="1">
-        <v>23.917431192660548</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-0.13615623324950624</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="D5" s="3">
+        <v>25.027522935779817</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-0.83</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-0.17006017171642437</v>
+      </c>
+      <c r="G5" s="3">
         <v>1.81</v>
       </c>
-      <c r="H5" s="1">
-        <v>70.53</v>
-      </c>
-      <c r="I5" s="1">
-        <v>9.77</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.00961777982348318</v>
-      </c>
-      <c r="K5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>28</v>
-      </c>
-      <c r="M5" s="1">
-        <v>-0.05029029739693458</v>
-      </c>
-      <c r="N5" s="1">
-        <v>6.646703081611673</v>
-      </c>
-      <c r="O5" s="1">
-        <v>51.89873417721519</v>
-      </c>
-      <c r="P5" s="1">
-        <v>29.9318207359553</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>61.77215189873418</v>
-      </c>
-      <c r="R5" s="1">
-        <v>45.31645569620254</v>
-      </c>
-      <c r="S5" s="1" t="s">
+      <c r="H5" s="3">
+        <v>48.89</v>
+      </c>
+      <c r="I5" s="3">
+        <v>-2.23</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.007618231687685116</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>-82</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-0.08134431156820199</v>
+      </c>
+      <c r="N5" s="3">
+        <v>3.893144170120827</v>
+      </c>
+      <c r="O5" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P5" s="3">
+        <v>23.613581273496347</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>56.07594936708862</v>
+      </c>
+      <c r="R5" s="3">
+        <v>45.25316455696203</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T5" s="1">
+      <c r="T5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2384,49 +2381,49 @@
         <v>51.89873417721519</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4271844660194175</v>
+        <v>1.4563106796116505</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.02516901345413544</v>
+        <v>-0.3321050615919351</v>
       </c>
       <c r="G6" s="1">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="1">
-        <v>37.91</v>
+        <v>29.04</v>
       </c>
       <c r="I6" s="1">
-        <v>-14.71</v>
+        <v>-19.02</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.008179825383145704</v>
+        <v>-0.013842094592377854</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="M6" s="1">
-        <v>0.03101487049878182</v>
+        <v>-0.27734218495722995</v>
       </c>
       <c r="N6" s="1">
-        <v>14.777219871183316</v>
+        <v>-15.706643168781968</v>
       </c>
       <c r="O6" s="1">
-        <v>60.75949367088608</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P6" s="1">
-        <v>20.72548824337846</v>
+        <v>25.4661882776573</v>
       </c>
       <c r="Q6" s="1">
-        <v>38.860759493670884</v>
+        <v>32.53164556962025</v>
       </c>
       <c r="R6" s="1">
-        <v>42.08860759493671</v>
+        <v>24.493670886075954</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
@@ -2440,55 +2437,55 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>4.9</v>
+        <v>6.53</v>
       </c>
       <c r="C7" s="2">
-        <v>58.22784810126582</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>6.242857142857143</v>
+        <v>5.099540581929555</v>
       </c>
       <c r="E7" s="2">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>0.002445248234289321</v>
+        <v>-0.11334325945951962</v>
       </c>
       <c r="G7" s="2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="H7" s="2">
-        <v>76.18</v>
+        <v>45.24</v>
       </c>
       <c r="I7" s="2">
-        <v>26.19</v>
+        <v>8.42</v>
       </c>
       <c r="J7" s="2">
-        <v>0.02207931320336696</v>
+        <v>0.01702949611879757</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M7" s="2">
-        <v>0.13495440850060358</v>
+        <v>0.018087644463772756</v>
       </c>
       <c r="N7" s="2">
-        <v>25.171173671365487</v>
+        <v>13.836339773318308</v>
       </c>
       <c r="O7" s="2">
-        <v>70.88607594936708</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>64.43037974683543</v>
+        <v>60.25316455696203</v>
       </c>
       <c r="R7" s="2">
-        <v>54.55696202531646</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
@@ -2508,49 +2505,49 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>-0.012084592145015116</v>
+        <v>0.03398791540785493</v>
       </c>
       <c r="E8" s="2">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="F8" s="2">
-        <v>0.3224922725360976</v>
+        <v>0.36843904917242454</v>
       </c>
       <c r="G8" s="2">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="2">
-        <v>83.87</v>
+        <v>67.94</v>
       </c>
       <c r="I8" s="2">
-        <v>24.99</v>
+        <v>23.2</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03278211098778094</v>
+        <v>0.040487285904518604</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-140</v>
+        <v>-220</v>
       </c>
       <c r="M8" s="2">
-        <v>0.28644978094366014</v>
+        <v>0.3279145204627427</v>
       </c>
       <c r="N8" s="2">
-        <v>40.320710915671164</v>
+        <v>44.819027373215306</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>66.07594936708861</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="R8" s="2">
-        <v>55.316455696202524</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
@@ -2560,188 +2557,188 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>0.89</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>37.9746835443038</v>
       </c>
-      <c r="D9" s="1">
-        <v>46.2247191011236</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2.14</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-0.1346267787903565</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H9" s="1">
-        <v>43.47</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-18.03</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-0.006101797654469959</v>
-      </c>
-      <c r="K9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>54</v>
-      </c>
-      <c r="M9" s="1">
-        <v>-0.0826831879659613</v>
-      </c>
-      <c r="N9" s="1">
-        <v>3.407414024709004</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="D9" s="3">
+        <v>46.82022471910113</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-0.19</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-0.333713517588887</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.56</v>
+      </c>
+      <c r="H9" s="3">
+        <v>39.31</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-20.21</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-0.00895957584565531</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>-16</v>
+      </c>
+      <c r="M9" s="3">
+        <v>-0.2723790957580172</v>
+      </c>
+      <c r="N9" s="3">
+        <v>-15.210334248860697</v>
+      </c>
+      <c r="O9" s="3">
+        <v>16.455696202531644</v>
+      </c>
+      <c r="P9" s="3">
+        <v>27.71785589333756</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>44.55696202531645</v>
+      </c>
+      <c r="R9" s="3">
+        <v>31.708860759493664</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="C10" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.5616</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-2.1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-0.15434190880290874</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="H10" s="3">
+        <v>44.51</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-6.9</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.004467231752215964</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>-131</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-0.11272212256053282</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0.7553630708877476</v>
+      </c>
+      <c r="O10" s="3">
+        <v>41.77215189873418</v>
+      </c>
+      <c r="P10" s="3">
+        <v>18.508072317589463</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>44.177215189873415</v>
+      </c>
+      <c r="R10" s="3">
+        <v>38.291139240506325</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-0.95</v>
+      </c>
+      <c r="C11" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46.70526315789474</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-1.64</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.08111962352263938</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="H11" s="3">
+        <v>39.3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-4.71</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.01395318334517921</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>25</v>
+      </c>
+      <c r="M11" s="3">
+        <v>-0.09754848651305092</v>
+      </c>
+      <c r="N11" s="3">
+        <v>2.272726675635934</v>
+      </c>
+      <c r="O11" s="3">
         <v>45.56962025316456</v>
       </c>
-      <c r="P9" s="1">
-        <v>34.04748479877408</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>48.9873417721519</v>
-      </c>
-      <c r="R9" s="1">
-        <v>41.202531645569614</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="C10" s="1">
-        <v>67.08860759493672</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.5408000000000002</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1.07</v>
-      </c>
-      <c r="F10" s="1">
-        <v>-0.12925719658795642</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="H10" s="1">
-        <v>55.02</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-3.13</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.0014049222467605465</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>-83</v>
-      </c>
-      <c r="M10" s="1">
-        <v>-0.08579419202060534</v>
-      </c>
-      <c r="N10" s="1">
-        <v>3.0963136192446155</v>
-      </c>
-      <c r="O10" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="P10" s="1">
-        <v>20.24508080818123</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>48.22784810126583</v>
-      </c>
-      <c r="R10" s="1">
-        <v>38.79746835443038</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>-1.36</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12.658227848101266</v>
-      </c>
-      <c r="D11" s="1">
-        <v>31.911764705882348</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8.3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.13403760617326035</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.81</v>
-      </c>
-      <c r="H11" s="1">
-        <v>63.55</v>
-      </c>
-      <c r="I11" s="1">
-        <v>5.28</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.021033713114448644</v>
-      </c>
-      <c r="K11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>15</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0.11389621381278059</v>
-      </c>
-      <c r="N11" s="1">
-        <v>23.065354202583205</v>
-      </c>
-      <c r="O11" s="1">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="P11" s="1">
-        <v>23.11654999559394</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>53.54430379746836</v>
-      </c>
-      <c r="R11" s="1">
-        <v>46.455696202531655</v>
-      </c>
-      <c r="S11" s="1" t="s">
+      <c r="P11" s="3">
+        <v>21.111699887088218</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>47.721518987341774</v>
+      </c>
+      <c r="R11" s="3">
+        <v>41.139240506329116</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T11" s="1">
+      <c r="T11" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2750,55 +2747,55 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>-0.34</v>
+        <v>-0.15</v>
       </c>
       <c r="C12" s="3">
-        <v>20.253164556962027</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="D12" s="3">
-        <v>65.85294117647058</v>
+        <v>169</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.32</v>
+        <v>3.03</v>
       </c>
       <c r="F12" s="3">
-        <v>-0.3390113878920355</v>
+        <v>0.10777865138818392</v>
       </c>
       <c r="G12" s="3">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="3">
-        <v>46.63</v>
+        <v>50.22</v>
       </c>
       <c r="I12" s="3">
-        <v>-38.15</v>
+        <v>-20.3</v>
       </c>
       <c r="J12" s="3">
-        <v>-0.01139281110627393</v>
+        <v>0.033289015557999055</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="3">
-        <v>-15</v>
+        <v>-53</v>
       </c>
       <c r="M12" s="3">
-        <v>-0.35809270697038476</v>
+        <v>0.1044928787901016</v>
       </c>
       <c r="N12" s="3">
-        <v>-24.133537875733335</v>
+        <v>22.476863205951197</v>
       </c>
       <c r="O12" s="3">
-        <v>5.063291139240507</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P12" s="3">
-        <v>49.67608188777989</v>
+        <v>49.122344752707264</v>
       </c>
       <c r="Q12" s="3">
-        <v>39.493670886075954</v>
+        <v>58.22784810126583</v>
       </c>
       <c r="R12" s="3">
-        <v>20.696202531645564</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>101</v>
@@ -2808,127 +2805,127 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>0.02</v>
       </c>
-      <c r="C13" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="C13" s="1">
+        <v>27.848101265822784</v>
+      </c>
+      <c r="D13" s="1">
         <v>-1653.5</v>
       </c>
-      <c r="E13" s="3">
-        <v>2.73</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-0.1759208009707229</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1.43</v>
-      </c>
-      <c r="H13" s="3">
-        <v>53.88</v>
-      </c>
-      <c r="I13" s="3">
-        <v>5.67</v>
-      </c>
-      <c r="J13" s="3">
-        <v>-0.0026568641580235123</v>
-      </c>
-      <c r="K13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="3">
-        <v>21</v>
-      </c>
-      <c r="M13" s="3">
-        <v>-0.13033764983911078</v>
-      </c>
-      <c r="N13" s="3">
-        <v>-1.3580321626059373</v>
-      </c>
-      <c r="O13" s="3">
-        <v>39.24050632911392</v>
-      </c>
-      <c r="P13" s="3">
-        <v>39.74359086324119</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>28.481012658227847</v>
-      </c>
-      <c r="R13" s="3">
-        <v>15.88607594936709</v>
-      </c>
-      <c r="S13" s="3" t="s">
+      <c r="E13" s="1">
+        <v>6.42</v>
+      </c>
+      <c r="F13" s="1">
+        <v>-0.3877702428136644</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H13" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-23.59</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-0.013183592823452281</v>
+      </c>
+      <c r="K13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>12</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-0.34395994150590026</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-22.368418823648987</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="P13" s="1">
+        <v>48.90109995677025</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>13.797468354430382</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0.6329113924050613</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T13" s="3">
-        <v>-0.38</v>
+      <c r="T13" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>1.31</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B14" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="C14" s="2">
         <v>44.303797468354425</v>
       </c>
-      <c r="D14" s="1">
-        <v>7.580152671755725</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-0.11661797016911667</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H14" s="1">
-        <v>57.94</v>
-      </c>
-      <c r="I14" s="1">
-        <v>-4.21</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.010041979719406674</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>14</v>
-      </c>
-      <c r="M14" s="1">
-        <v>-0.15902090145433723</v>
-      </c>
-      <c r="N14" s="1">
-        <v>-4.226357324128582</v>
-      </c>
-      <c r="O14" s="1">
-        <v>31.645569620253166</v>
-      </c>
-      <c r="P14" s="1">
-        <v>33.10300785656511</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>53.92405063291139</v>
-      </c>
-      <c r="R14" s="1">
-        <v>35.189873417721515</v>
-      </c>
-      <c r="S14" s="1" t="s">
+      <c r="D14" s="2">
+        <v>6.768115942028986</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.370679366253922</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="H14" s="2">
+        <v>60.11</v>
+      </c>
+      <c r="I14" s="2">
+        <v>34.08</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.0472651748130161</v>
+      </c>
+      <c r="K14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.34877421560003996</v>
+      </c>
+      <c r="N14" s="2">
+        <v>46.90499688694502</v>
+      </c>
+      <c r="O14" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="P14" s="2">
+        <v>31.5531883466271</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>63.037974683544306</v>
+      </c>
+      <c r="R14" s="2">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T14" s="1">
-        <v>0.76</v>
+      <c r="T14" s="2">
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2939,52 +2936,52 @@
         <v>-0.63</v>
       </c>
       <c r="C15" s="2">
-        <v>18.9873417721519</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="D15" s="2">
-        <v>62.85714285714286</v>
+        <v>68.11111111111111</v>
       </c>
       <c r="E15" s="2">
-        <v>5.78</v>
+        <v>1.71</v>
       </c>
       <c r="F15" s="2">
-        <v>1.2291696989512908</v>
+        <v>1.4688497883323033</v>
       </c>
       <c r="G15" s="2">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="H15" s="2">
-        <v>69.51</v>
+        <v>62.43</v>
       </c>
       <c r="I15" s="2">
-        <v>161.02</v>
+        <v>132.83</v>
       </c>
       <c r="J15" s="2">
-        <v>0.12724079067001726</v>
+        <v>0.07800167121544431</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="M15" s="2">
-        <v>1.3584986393712135</v>
+        <v>1.6013759497882898</v>
       </c>
       <c r="N15" s="2">
-        <v>147.5255967584265</v>
+        <v>172.16517030577003</v>
       </c>
       <c r="O15" s="2">
-        <v>100</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P15" s="2">
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>69.49367088607595</v>
+        <v>68.22784810126582</v>
       </c>
       <c r="R15" s="2">
-        <v>61.962025316455694</v>
+        <v>61.139240506329116</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>103</v>
@@ -3001,243 +2998,243 @@
         <v>-3.53</v>
       </c>
       <c r="C16" s="1">
-        <v>8.860759493670885</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="D16" s="1">
-        <v>12.218130311614733</v>
+        <v>13.059490084985837</v>
       </c>
       <c r="E16" s="1">
-        <v>4.52</v>
+        <v>4.79</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.059777735429645346</v>
+        <v>-0.2610273537516778</v>
       </c>
       <c r="G16" s="1">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="H16" s="1">
-        <v>47.33</v>
+        <v>41.93</v>
       </c>
       <c r="I16" s="1">
-        <v>2.21</v>
+        <v>-9.59</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0010320582236726678</v>
+        <v>-0.0004547213608892286</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M16" s="1">
-        <v>0.039869153090623</v>
+        <v>-0.1712162360707613</v>
       </c>
       <c r="N16" s="1">
-        <v>15.662648130367446</v>
+        <v>-5.094048280135099</v>
       </c>
       <c r="O16" s="1">
-        <v>63.29113924050633</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P16" s="1">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="1">
-        <v>40.63291139240506</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="R16" s="1">
-        <v>36.64556962025316</v>
+        <v>26.518987341772156</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="1">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>-6.21</v>
       </c>
-      <c r="C17" s="3">
-        <v>2.5316455696202533</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4.355877616747182</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4.89</v>
-      </c>
-      <c r="F17" s="3">
-        <v>-0.15592483762420115</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.73</v>
-      </c>
-      <c r="H17" s="3">
-        <v>45.43</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-9.15</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-0.013558713931326748</v>
-      </c>
-      <c r="K17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>32</v>
-      </c>
-      <c r="M17" s="3">
-        <v>-0.07853948802867361</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3.8217840184377816</v>
-      </c>
-      <c r="O17" s="3">
-        <v>46.835443037974684</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="C17" s="1">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4.777777777777778</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-0.17759584973496417</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="H17" s="1">
+        <v>44.73</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-10.32</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.00710766206262125</v>
+      </c>
+      <c r="K17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>25</v>
+      </c>
+      <c r="M17" s="1">
+        <v>-0.09873730738098874</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2.1538445888421474</v>
+      </c>
+      <c r="O17" s="1">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="P17" s="1">
         <v>28.182703357372183</v>
       </c>
-      <c r="Q17" s="3">
-        <v>24.55696202531646</v>
-      </c>
-      <c r="R17" s="3">
-        <v>23.164556962025316</v>
-      </c>
-      <c r="S17" s="3" t="s">
+      <c r="Q17" s="1">
+        <v>33.41772151898734</v>
+      </c>
+      <c r="R17" s="1">
+        <v>25.443037974683545</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
+      <c r="T17" s="1">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
-        <v>30.37974683544304</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18" s="3">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="D18" s="3">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="1">
-        <v>9.43</v>
-      </c>
-      <c r="F18" s="1">
-        <v>-0.31769757444430774</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.23</v>
-      </c>
-      <c r="H18" s="1">
-        <v>34.31</v>
-      </c>
-      <c r="I18" s="1">
-        <v>-9.92</v>
-      </c>
-      <c r="J18" s="1">
-        <v>-0.008678430354633865</v>
-      </c>
-      <c r="K18" s="1" t="b">
+      <c r="E18" s="3">
+        <v>5.96</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.036696473844244015</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1.05</v>
+      </c>
+      <c r="H18" s="3">
+        <v>62.11</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.010037053654593404</v>
+      </c>
+      <c r="K18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L18" s="1">
-        <v>45</v>
-      </c>
-      <c r="M18" s="1">
-        <v>-0.2933158889553059</v>
-      </c>
-      <c r="N18" s="1">
-        <v>-17.65585607422545</v>
-      </c>
-      <c r="O18" s="1">
-        <v>8.860759493670885</v>
-      </c>
-      <c r="P18" s="1">
-        <v>30.65938429567125</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>48.22784810126582</v>
-      </c>
-      <c r="R18" s="1">
-        <v>30.949367088607595</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="L18" s="3">
+        <v>37</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.04217276150771454</v>
+      </c>
+      <c r="N18" s="3">
+        <v>16.24485147771248</v>
+      </c>
+      <c r="O18" s="3">
+        <v>63.29113924050633</v>
+      </c>
+      <c r="P18" s="3">
+        <v>44.14111512367286</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>62.78481012658227</v>
+      </c>
+      <c r="R18" s="3">
+        <v>47.34177215189874</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="1">
-        <v>-0.38</v>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="3">
         <v>9.32</v>
       </c>
-      <c r="C19" s="1">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.2027896995708155</v>
-      </c>
-      <c r="E19" s="1">
-        <v>-0.43</v>
-      </c>
-      <c r="F19" s="1">
-        <v>-0.04984014908398787</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="H19" s="1">
-        <v>53.67</v>
-      </c>
-      <c r="I19" s="1">
-        <v>15.22</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.0049513249802427125</v>
-      </c>
-      <c r="K19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <v>71</v>
-      </c>
-      <c r="M19" s="1">
-        <v>-0.13358593837229848</v>
-      </c>
-      <c r="N19" s="1">
-        <v>-1.6828610159247124</v>
-      </c>
-      <c r="O19" s="1">
-        <v>37.9746835443038</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="C19" s="3">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.3015021459227468</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-2.17</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.07253092317815768</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="H19" s="3">
+        <v>57.57</v>
+      </c>
+      <c r="I19" s="3">
+        <v>15.33</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.006009652808137184</v>
+      </c>
+      <c r="K19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>80</v>
+      </c>
+      <c r="M19" s="3">
+        <v>-0.018375452035452877</v>
+      </c>
+      <c r="N19" s="3">
+        <v>10.190030123395736</v>
+      </c>
+      <c r="O19" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P19" s="3">
         <v>14.335419717590279</v>
       </c>
-      <c r="Q19" s="1">
-        <v>52.911392405063296</v>
-      </c>
-      <c r="R19" s="1">
-        <v>40.8860759493671</v>
-      </c>
-      <c r="S19" s="1" t="s">
+      <c r="Q19" s="3">
+        <v>53.41772151898735</v>
+      </c>
+      <c r="R19" s="3">
+        <v>45.31645569620254</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T19" s="1">
+      <c r="T19" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3249,52 +3246,52 @@
         <v>6.07</v>
       </c>
       <c r="C20" s="3">
-        <v>65.82278481012658</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="D20" s="3">
-        <v>0.9456342668863262</v>
+        <v>0.6820428336079079</v>
       </c>
       <c r="E20" s="3">
-        <v>-2.3</v>
+        <v>5.04</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.27936579590574756</v>
+        <v>-0.042081260853274155</v>
       </c>
       <c r="G20" s="3">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H20" s="3">
-        <v>33.21</v>
+        <v>47.92</v>
       </c>
       <c r="I20" s="3">
-        <v>-15.87</v>
+        <v>-2.7</v>
       </c>
       <c r="J20" s="3">
-        <v>-0.01222796653113952</v>
+        <v>0.006295515639365568</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="M20" s="3">
-        <v>-0.276185576059356</v>
+        <v>-0.032223943059027205</v>
       </c>
       <c r="N20" s="3">
-        <v>-15.942824784630464</v>
+        <v>8.805181021038317</v>
       </c>
       <c r="O20" s="3">
-        <v>12.658227848101266</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P20" s="3">
-        <v>25.74193342123896</v>
+        <v>24.948764656842595</v>
       </c>
       <c r="Q20" s="3">
-        <v>37.72151898734177</v>
+        <v>47.974683544303794</v>
       </c>
       <c r="R20" s="3">
-        <v>27.405063291139236</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>105</v>
@@ -3304,189 +3301,189 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>1.02</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>41.77215189873418</v>
       </c>
-      <c r="D21" s="1">
-        <v>13.990196078431373</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5.19</v>
-      </c>
-      <c r="F21" s="1">
-        <v>-0.06563929377820135</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="H21" s="1">
-        <v>75.01</v>
-      </c>
-      <c r="I21" s="1">
-        <v>31.41</v>
-      </c>
-      <c r="J21" s="1">
-        <v>-0.00912194805209317</v>
-      </c>
-      <c r="K21" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>18</v>
-      </c>
-      <c r="M21" s="1">
-        <v>-0.033837095314285914</v>
-      </c>
-      <c r="N21" s="1">
-        <v>8.29202328987655</v>
-      </c>
-      <c r="O21" s="1">
-        <v>53.16455696202531</v>
-      </c>
-      <c r="P21" s="1">
+      <c r="D21" s="2">
+        <v>13.529411764705882</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.05162469064247899</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.61</v>
+      </c>
+      <c r="H21" s="2">
+        <v>49.99</v>
+      </c>
+      <c r="I21" s="2">
+        <v>40.11</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.037330928566145255</v>
+      </c>
+      <c r="K21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>38</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.1184354001368193</v>
+      </c>
+      <c r="N21" s="2">
+        <v>23.87111534062295</v>
+      </c>
+      <c r="O21" s="2">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
-      <c r="Q21" s="1">
-        <v>55.44303797468354</v>
-      </c>
-      <c r="R21" s="1">
-        <v>38.79746835443038</v>
-      </c>
-      <c r="S21" s="1" t="s">
+      <c r="Q21" s="2">
+        <v>64.9367088607595</v>
+      </c>
+      <c r="R21" s="2">
+        <v>52.025316455696206</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T21" s="1">
-        <v>-0.51</v>
+      <c r="T21" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="3">
         <v>8.11</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>70.88607594936708</v>
       </c>
-      <c r="D22" s="1">
-        <v>0.6954377311960543</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-0.22745346460144902</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="H22" s="1">
-        <v>46.93</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-3.08</v>
-      </c>
-      <c r="J22" s="1">
-        <v>-0.014743973448483924</v>
-      </c>
-      <c r="K22" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
-        <v>96</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.18929082644475048</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-7.253349823169911</v>
-      </c>
-      <c r="O22" s="1">
+      <c r="D22" s="3">
+        <v>0.718865598027127</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-1.48</v>
+      </c>
+      <c r="F22" s="3">
+        <v>-0.04307280581540682</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="H22" s="3">
+        <v>63</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10.34</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.014842911779265488</v>
+      </c>
+      <c r="K22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>58</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-0.0014530195730309003</v>
+      </c>
+      <c r="N22" s="3">
+        <v>11.882273369637938</v>
+      </c>
+      <c r="O22" s="3">
+        <v>56.9620253164557</v>
+      </c>
+      <c r="P22" s="3">
+        <v>20.966620085005058</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>60.63291139240506</v>
+      </c>
+      <c r="R22" s="3">
+        <v>47.53164556962025</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>27.51</v>
+      </c>
+      <c r="C23" s="3">
+        <v>97.46835443037975</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-0.7684478371501272</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.2238007118664241</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H23" s="3">
+        <v>34.66</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-13.84</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.0037244957972948725</v>
+      </c>
+      <c r="K23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>23</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-0.19641927354907152</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-7.614352027966116</v>
+      </c>
+      <c r="O23" s="3">
         <v>24.050632911392405</v>
       </c>
-      <c r="P22" s="1">
-        <v>20.966620085005058</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>40.75949367088608</v>
-      </c>
-      <c r="R22" s="1">
-        <v>30.253164556962027</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>27.51</v>
-      </c>
-      <c r="C23" s="1">
-        <v>97.46835443037975</v>
-      </c>
-      <c r="D23" s="1">
-        <v>-0.7593602326426754</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-0.52</v>
-      </c>
-      <c r="F23" s="1">
-        <v>-0.19121337686215006</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="H23" s="1">
-        <v>47.35</v>
-      </c>
-      <c r="I23" s="1">
-        <v>-8.12</v>
-      </c>
-      <c r="J23" s="1">
-        <v>-0.0075053643476327555</v>
-      </c>
-      <c r="K23" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>29</v>
-      </c>
-      <c r="M23" s="1">
-        <v>-0.1657716180910177</v>
-      </c>
-      <c r="N23" s="1">
-        <v>-4.901428987796632</v>
-      </c>
-      <c r="O23" s="1">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="P23" s="1">
+      <c r="P23" s="3">
         <v>28.794141696367475</v>
       </c>
-      <c r="Q23" s="1">
-        <v>45.31645569620253</v>
-      </c>
-      <c r="R23" s="1">
-        <v>31.962025316455694</v>
-      </c>
-      <c r="S23" s="1" t="s">
+      <c r="Q23" s="3">
+        <v>43.291139240506325</v>
+      </c>
+      <c r="R23" s="3">
+        <v>31.51898734177215</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T23" s="1">
-        <v>-0.38</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3500,49 +3497,49 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.3107569721115539</v>
+        <v>-1.089143426294821</v>
       </c>
       <c r="E24" s="1">
-        <v>9.38</v>
+        <v>7.21</v>
       </c>
       <c r="F24" s="1">
-        <v>0.15592581430995772</v>
+        <v>-0.5086884495613566</v>
       </c>
       <c r="G24" s="1">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="H24" s="1">
-        <v>62.41</v>
+        <v>37.22</v>
       </c>
       <c r="I24" s="1">
-        <v>-12.59</v>
+        <v>-36.82</v>
       </c>
       <c r="J24" s="1">
-        <v>0.035040529196603526</v>
+        <v>-0.0031286388148233928</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>33</v>
+        <v>-9</v>
       </c>
       <c r="M24" s="1">
-        <v>0.42836464781749983</v>
+        <v>-0.23268355132244256</v>
       </c>
       <c r="N24" s="1">
-        <v>54.512197603055135</v>
+        <v>-11.240779805303223</v>
       </c>
       <c r="O24" s="1">
-        <v>88.60759493670885</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P24" s="1">
-        <v>40.33904155950217</v>
+        <v>41.129939248308794</v>
       </c>
       <c r="Q24" s="1">
-        <v>31.39240506329114</v>
+        <v>9.746835443037975</v>
       </c>
       <c r="R24" s="1">
-        <v>31.0126582278481</v>
+        <v>3.227848101265824</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>92</v>
@@ -3552,251 +3549,251 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>-2.28</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>11.39240506329114</v>
       </c>
-      <c r="D25" s="3">
-        <v>0.8859649122807016</v>
-      </c>
-      <c r="E25" s="3">
-        <v>11.91</v>
-      </c>
-      <c r="F25" s="3">
-        <v>-0.3761670267637076</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2.23</v>
-      </c>
-      <c r="H25" s="3">
-        <v>50.29</v>
-      </c>
-      <c r="I25" s="3">
-        <v>-49.54</v>
-      </c>
-      <c r="J25" s="3">
-        <v>-0.003975544961099383</v>
-      </c>
-      <c r="K25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <v>48</v>
-      </c>
-      <c r="M25" s="3">
-        <v>-0.24577801306165437</v>
-      </c>
-      <c r="N25" s="3">
-        <v>-12.902068484860301</v>
-      </c>
-      <c r="O25" s="3">
-        <v>16.455696202531644</v>
-      </c>
-      <c r="P25" s="3">
+      <c r="D25" s="1">
+        <v>-7.149122807017544</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11.56</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-0.422333108686368</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2.28</v>
+      </c>
+      <c r="H25" s="1">
+        <v>41.08</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-53.41</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-0.005426020833051525</v>
+      </c>
+      <c r="K25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>42</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-0.2821401445015228</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-16.186439123211244</v>
+      </c>
+      <c r="O25" s="1">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="P25" s="1">
         <v>55.620154465672535</v>
       </c>
-      <c r="Q25" s="3">
-        <v>28.101265822784814</v>
-      </c>
-      <c r="R25" s="3">
-        <v>11.962025316455694</v>
-      </c>
-      <c r="S25" s="3" t="s">
+      <c r="Q25" s="1">
+        <v>12.151898734177216</v>
+      </c>
+      <c r="R25" s="1">
+        <v>-0.37974683544303645</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="T25" s="3">
-        <v>-0.38</v>
+      <c r="T25" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="3">
         <v>-0.17</v>
       </c>
-      <c r="C26" s="1">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="D26" s="1">
-        <v>-2571.7647058823527</v>
-      </c>
-      <c r="E26" s="1">
-        <v>4.67</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.4878708588671728</v>
-      </c>
-      <c r="G26" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="H26" s="1">
-        <v>69.42</v>
-      </c>
-      <c r="I26" s="1">
-        <v>21.77</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.044615350892172945</v>
-      </c>
-      <c r="K26" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>-11</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.7062459549860587</v>
-      </c>
-      <c r="N26" s="1">
-        <v>82.300328319911</v>
-      </c>
-      <c r="O26" s="1">
-        <v>91.13924050632912</v>
-      </c>
-      <c r="P26" s="1">
-        <v>50.63126652197354</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>41.01265822784811</v>
-      </c>
-      <c r="R26" s="1">
-        <v>33.037974683544306</v>
-      </c>
-      <c r="S26" s="1" t="s">
+      <c r="C26" s="3">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="D26" s="3">
+        <v>-2529.3529411764703</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.38957518495318594</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.23</v>
+      </c>
+      <c r="H26" s="3">
+        <v>50</v>
+      </c>
+      <c r="I26" s="3">
+        <v>18.08</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.06421703035469414</v>
+      </c>
+      <c r="K26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-28</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0.6338176147439709</v>
+      </c>
+      <c r="N26" s="3">
+        <v>75.40933680133813</v>
+      </c>
+      <c r="O26" s="3">
+        <v>92.40506329113924</v>
+      </c>
+      <c r="P26" s="3">
+        <v>47.65747922848498</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>39.11392405063292</v>
+      </c>
+      <c r="R26" s="3">
+        <v>33.73417721518988</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T26" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>-1.13</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2.752212389380531</v>
+      </c>
+      <c r="E27" s="1">
+        <v>7.51</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-0.36426584306625975</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.71</v>
+      </c>
+      <c r="H27" s="1">
+        <v>40.05</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-27.28</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.010967630498285301</v>
+      </c>
+      <c r="K27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>39</v>
+      </c>
+      <c r="M27" s="1">
+        <v>-0.1769768049755681</v>
+      </c>
+      <c r="N27" s="1">
+        <v>-5.67010517061578</v>
+      </c>
+      <c r="O27" s="1">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="P27" s="1">
+        <v>48.541802331934534</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>31.77215189873418</v>
+      </c>
+      <c r="R27" s="1">
+        <v>19.87341772151899</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-1.1</v>
+      </c>
+      <c r="C28" s="1">
         <v>13.924050632911392</v>
       </c>
-      <c r="D27" s="3">
-        <v>1.0176991150442478</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-0.20457969183921387</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="H27" s="3">
-        <v>60.75</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-18.72</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0.00800169742756051</v>
-      </c>
-      <c r="K27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>37</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-0.03178774685194008</v>
-      </c>
-      <c r="N27" s="3">
-        <v>8.496958136111138</v>
-      </c>
-      <c r="O27" s="3">
-        <v>54.43037974683544</v>
-      </c>
-      <c r="P27" s="3">
-        <v>51.28834092723359</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>36.58227848101266</v>
-      </c>
-      <c r="R27" s="3">
-        <v>26.392405063291136</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T27" s="3">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-1.1</v>
-      </c>
-      <c r="C28" s="3">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="D28" s="3">
-        <v>7.536363636363636</v>
-      </c>
-      <c r="E28" s="3">
-        <v>-0.68</v>
-      </c>
-      <c r="F28" s="3">
-        <v>-0.3879769225383227</v>
-      </c>
-      <c r="G28" s="3">
-        <v>3.14</v>
-      </c>
-      <c r="H28" s="3">
-        <v>59.66</v>
-      </c>
-      <c r="I28" s="3">
-        <v>-20.69</v>
-      </c>
-      <c r="J28" s="3">
-        <v>-0.010456960261449664</v>
-      </c>
-      <c r="K28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>28</v>
-      </c>
-      <c r="M28" s="3">
-        <v>-0.1611212401623927</v>
-      </c>
-      <c r="N28" s="3">
-        <v>-4.436391194934127</v>
-      </c>
-      <c r="O28" s="3">
-        <v>30.37974683544304</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="D28" s="1">
+        <v>7.899999999999999</v>
+      </c>
+      <c r="E28" s="1">
+        <v>-4.75</v>
+      </c>
+      <c r="F28" s="1">
+        <v>-0.5176828002010445</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3.19</v>
+      </c>
+      <c r="H28" s="1">
+        <v>34.68</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-34.8</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.0023508086237874768</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>-3</v>
+      </c>
+      <c r="M28" s="1">
+        <v>-0.277821400541036</v>
+      </c>
+      <c r="N28" s="1">
+        <v>-15.754564727162565</v>
+      </c>
+      <c r="O28" s="1">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="P28" s="1">
         <v>45.17203183430412</v>
       </c>
-      <c r="Q28" s="3">
-        <v>34.68354430379746</v>
-      </c>
-      <c r="R28" s="3">
-        <v>21.898734177215193</v>
-      </c>
-      <c r="S28" s="3" t="s">
+      <c r="Q28" s="1">
+        <v>31.26582278481013</v>
+      </c>
+      <c r="R28" s="1">
+        <v>17.65822784810127</v>
+      </c>
+      <c r="S28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T28" s="3">
-        <v>-0.38</v>
+      <c r="T28" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3810,49 +3807,49 @@
         <v>34.177215189873415</v>
       </c>
       <c r="D29" s="3">
-        <v>77.04545454545456</v>
+        <v>79.04545454545455</v>
       </c>
       <c r="E29" s="3">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.4139591068760087</v>
+        <v>-0.31376708483042504</v>
       </c>
       <c r="G29" s="3">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="H29" s="3">
-        <v>42.5</v>
+        <v>49.71</v>
       </c>
       <c r="I29" s="3">
-        <v>-32.51</v>
+        <v>-27.45</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.015534149204213981</v>
+        <v>0.0051714150010587585</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-12</v>
+        <v>-68</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.29629097255952164</v>
+        <v>-0.18671721103790906</v>
       </c>
       <c r="N29" s="3">
-        <v>-17.953364434647018</v>
+        <v>-6.644145776849879</v>
       </c>
       <c r="O29" s="3">
-        <v>7.59493670886076</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P29" s="3">
-        <v>48.25819923754261</v>
+        <v>42.700456457951226</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.13924050632911</v>
+        <v>51.26582278481013</v>
       </c>
       <c r="R29" s="3">
-        <v>24.36708860759493</v>
+        <v>34.0506329113924</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
@@ -3862,65 +3859,65 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <v>1.95</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="2">
         <v>46.835443037974684</v>
       </c>
-      <c r="D30" s="1">
-        <v>1656.8153846153846</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2.13</v>
-      </c>
-      <c r="F30" s="1">
-        <v>-0.17095955682866515</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.21</v>
-      </c>
-      <c r="H30" s="1">
-        <v>54.01</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5.44</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0.004296700252854999</v>
-      </c>
-      <c r="K30" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <v>39</v>
-      </c>
-      <c r="M30" s="1">
-        <v>-0.14869801790392434</v>
-      </c>
-      <c r="N30" s="1">
-        <v>-3.1940689690872945</v>
-      </c>
-      <c r="O30" s="1">
-        <v>34.177215189873415</v>
-      </c>
-      <c r="P30" s="1">
+      <c r="D30" s="2">
+        <v>1497.6410256410256</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-0.09853897868270775</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="H30" s="2">
+        <v>48.77</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0.009013675838880993</v>
+      </c>
+      <c r="K30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2">
+        <v>24</v>
+      </c>
+      <c r="M30" s="2">
+        <v>-0.07663382802882568</v>
+      </c>
+      <c r="N30" s="2">
+        <v>4.364192524058455</v>
+      </c>
+      <c r="O30" s="2">
+        <v>48.10126582278481</v>
+      </c>
+      <c r="P30" s="2">
         <v>24.961328061128594</v>
       </c>
-      <c r="Q30" s="1">
-        <v>64.9367088607595</v>
-      </c>
-      <c r="R30" s="1">
-        <v>47.53164556962025</v>
-      </c>
-      <c r="S30" s="1" t="s">
+      <c r="Q30" s="2">
+        <v>64.81012658227849</v>
+      </c>
+      <c r="R30" s="2">
+        <v>51.83544303797468</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="T30" s="1">
-        <v>0.38</v>
+      <c r="T30" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3928,61 +3925,61 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>5.13</v>
+        <v>6.01</v>
       </c>
       <c r="C31" s="2">
-        <v>59.49367088607595</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="D31" s="2">
-        <v>10.688109161793372</v>
+        <v>10.262895174708818</v>
       </c>
       <c r="E31" s="2">
-        <v>0.9</v>
+        <v>-0.64</v>
       </c>
       <c r="F31" s="2">
-        <v>0.14893465812358012</v>
+        <v>0.014210648346719035</v>
       </c>
       <c r="G31" s="2">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="H31" s="2">
-        <v>64.78</v>
+        <v>41.4</v>
       </c>
       <c r="I31" s="2">
-        <v>25.69</v>
+        <v>6.69</v>
       </c>
       <c r="J31" s="2">
-        <v>0.030128371718951562</v>
+        <v>0.020179826792573352</v>
       </c>
       <c r="K31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="M31" s="2">
-        <v>0.19451780925519224</v>
+        <v>0.0656877523833419</v>
       </c>
       <c r="N31" s="2">
-        <v>31.12751374682437</v>
+        <v>18.59635056527523</v>
       </c>
       <c r="O31" s="2">
-        <v>78.48101265822784</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P31" s="2">
-        <v>17.25839209766727</v>
+        <v>22.731897658859403</v>
       </c>
       <c r="Q31" s="2">
-        <v>68.35443037974683</v>
+        <v>61.51898734177215</v>
       </c>
       <c r="R31" s="2">
-        <v>60.822784810126585</v>
+        <v>56.58227848101266</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -3996,117 +3993,117 @@
         <v>10.126582278481013</v>
       </c>
       <c r="D32" s="3">
-        <v>8.178082191780822</v>
+        <v>8.034246575342467</v>
       </c>
       <c r="E32" s="3">
-        <v>1.69</v>
+        <v>-3.39</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.13320749908480836</v>
+        <v>-0.06032165191812297</v>
       </c>
       <c r="G32" s="3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H32" s="3">
-        <v>43.93</v>
+        <v>56.08</v>
       </c>
       <c r="I32" s="3">
-        <v>-4.28</v>
+        <v>7.15</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.006102937885637886</v>
+        <v>0.006695070092382302</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.06854302887484698</v>
+        <v>0.0075843151089114436</v>
       </c>
       <c r="N32" s="3">
-        <v>4.821429933820452</v>
+        <v>12.78600683783217</v>
       </c>
       <c r="O32" s="3">
-        <v>49.36708860759494</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P32" s="3">
-        <v>38.84187494148391</v>
+        <v>27.28297753683016</v>
       </c>
       <c r="Q32" s="3">
-        <v>36.32911392405064</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="R32" s="3">
-        <v>29.36708860759494</v>
+        <v>34.936708860759495</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="3">
         <v>16.79</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="3">
         <v>88.60759493670885</v>
       </c>
-      <c r="D33" s="1">
-        <v>-0.05777248362120303</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="F33" s="1">
-        <v>-0.10754673419165842</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1.09</v>
-      </c>
-      <c r="H33" s="1">
-        <v>50.21</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-11.71</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.0024125422671207788</v>
-      </c>
-      <c r="K33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>84</v>
-      </c>
-      <c r="M33" s="1">
-        <v>-0.09800607465248379</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1.8751253560567682</v>
-      </c>
-      <c r="O33" s="1">
-        <v>43.037974683544306</v>
-      </c>
-      <c r="P33" s="1">
-        <v>26.894390179645494</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>49.62025316455696</v>
-      </c>
-      <c r="R33" s="1">
-        <v>39.9367088607595</v>
-      </c>
-      <c r="S33" s="1" t="s">
+      <c r="D33" s="3">
+        <v>-0.06075044669446097</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1.79</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-0.14667437854757395</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1.13</v>
+      </c>
+      <c r="H33" s="3">
+        <v>37.09</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-13.88</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.008441286927564441</v>
+      </c>
+      <c r="K33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>7</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-0.1324360306225506</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-1.2160277353140274</v>
+      </c>
+      <c r="O33" s="3">
+        <v>36.708860759493675</v>
+      </c>
+      <c r="P33" s="3">
+        <v>25.92446787021105</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>46.58227848101266</v>
+      </c>
+      <c r="R33" s="3">
+        <v>37.911392405063296</v>
+      </c>
+      <c r="S33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T33" s="1">
-        <v>0.38</v>
+      <c r="T33" s="3">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4120,117 +4117,117 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.6453089244851258</v>
+        <v>-0.7360793287566743</v>
       </c>
       <c r="E34" s="2">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0.15231508251016168</v>
+        <v>0.0422329570445851</v>
       </c>
       <c r="G34" s="2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H34" s="2">
-        <v>75.21</v>
+        <v>42.37</v>
       </c>
       <c r="I34" s="2">
-        <v>38.55</v>
+        <v>16.8</v>
       </c>
       <c r="J34" s="2">
-        <v>0.02781949782545467</v>
+        <v>0.021872359169800584</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="M34" s="2">
-        <v>0.17987698784555506</v>
+        <v>0.0696143953619377</v>
       </c>
       <c r="N34" s="2">
-        <v>29.66343160586064</v>
+        <v>18.989014863134802</v>
       </c>
       <c r="O34" s="2">
-        <v>77.21518987341773</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>61.39240506329114</v>
+        <v>53.79746835443038</v>
       </c>
       <c r="R34" s="2">
-        <v>51.139240506329116</v>
+        <v>50.063291139240505</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="2">
-        <v>0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>17.37</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>91.13924050632912</v>
       </c>
-      <c r="D35" s="3">
-        <v>-0.47898675877950486</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-0.96</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-0.3181429691881079</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3">
-        <v>26.9</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-25.05</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-0.024684340384122497</v>
-      </c>
-      <c r="K35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>44</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-0.3181429691881079</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-20.138564097505654</v>
-      </c>
-      <c r="O35" s="3">
-        <v>6.329113924050633</v>
-      </c>
-      <c r="P35" s="3">
-        <v>30.4559601123391</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>32.911392405063296</v>
-      </c>
-      <c r="R35" s="3">
-        <v>21.582278481012658</v>
-      </c>
-      <c r="S35" s="3" t="s">
+      <c r="D35" s="1">
+        <v>-0.47380541162924583</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8.84</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-0.3094808572789003</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="H35" s="1">
+        <v>54.22</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-17.54</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-0.011680687614597451</v>
+      </c>
+      <c r="K35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>20</v>
+      </c>
+      <c r="M35" s="1">
+        <v>-0.3138618874096767</v>
+      </c>
+      <c r="N35" s="1">
+        <v>-19.358613414026642</v>
+      </c>
+      <c r="O35" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P35" s="1">
+        <v>27.295682949534427</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>43.41772151898735</v>
+      </c>
+      <c r="R35" s="1">
+        <v>24.62025316455696</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T35" s="3">
-        <v>-0.38</v>
+      <c r="T35" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4241,58 +4238,58 @@
         <v>11.51</v>
       </c>
       <c r="C36" s="1">
-        <v>82.27848101265823</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="D36" s="1">
-        <v>0.38488271068635965</v>
+        <v>0.3388357949609036</v>
       </c>
       <c r="E36" s="1">
-        <v>-0.97</v>
+        <v>2.32</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.13120568027183452</v>
+        <v>-0.2947040210683217</v>
       </c>
       <c r="G36" s="1">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H36" s="1">
-        <v>38.9</v>
+        <v>39.88</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.19</v>
+        <v>-20.74</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.011964198390205084</v>
+        <v>-0.014443094424291019</v>
       </c>
       <c r="K36" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-19</v>
+        <v>-54</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.11848480088626834</v>
+        <v>-0.2793704156106043</v>
       </c>
       <c r="N36" s="1">
-        <v>-0.17274726732169896</v>
+        <v>-15.909466234119396</v>
       </c>
       <c r="O36" s="1">
-        <v>40.50632911392405</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P36" s="1">
-        <v>32.54334537649318</v>
+        <v>28.98593365092364</v>
       </c>
       <c r="Q36" s="1">
-        <v>39.99999999999999</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="R36" s="1">
-        <v>34.30379746835443</v>
+        <v>25.253164556962023</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4303,52 +4300,52 @@
         <v>5.33</v>
       </c>
       <c r="C37" s="1">
-        <v>63.29113924050633</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="D37" s="1">
-        <v>0.598499061913696</v>
+        <v>0.6003752345215758</v>
       </c>
       <c r="E37" s="1">
-        <v>0.52</v>
+        <v>-4.98</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.0008221176373724437</v>
+        <v>-0.2325702472887173</v>
       </c>
       <c r="G37" s="1">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="H37" s="1">
-        <v>38.49</v>
+        <v>34.53</v>
       </c>
       <c r="I37" s="1">
-        <v>-21.87</v>
+        <v>-25.05</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.0017925280106526717</v>
+        <v>-0.007380376352226501</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-134</v>
+        <v>-215</v>
       </c>
       <c r="M37" s="1">
-        <v>0.039460667083587087</v>
+        <v>-0.1953314911771178</v>
       </c>
       <c r="N37" s="1">
-        <v>15.621799529663857</v>
+        <v>-7.505573790770743</v>
       </c>
       <c r="O37" s="1">
-        <v>62.0253164556962</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P37" s="1">
-        <v>36.27914452259746</v>
+        <v>31.61854630334819</v>
       </c>
       <c r="Q37" s="1">
-        <v>39.11392405063292</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="R37" s="1">
-        <v>38.797468354430386</v>
+        <v>25.316455696202535</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
@@ -4362,55 +4359,55 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>-0.74</v>
+        <v>-0.19</v>
       </c>
       <c r="C38" s="2">
-        <v>16.455696202531644</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="D38" s="2">
-        <v>36.648648648648646</v>
+        <v>139.4736842105263</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.1</v>
+        <v>-1.63</v>
       </c>
       <c r="F38" s="2">
-        <v>0.27827678266224054</v>
+        <v>0.3968131936883785</v>
       </c>
       <c r="G38" s="2">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="H38" s="2">
-        <v>81.02</v>
+        <v>58.72</v>
       </c>
       <c r="I38" s="2">
-        <v>26.02</v>
+        <v>41.01</v>
       </c>
       <c r="J38" s="2">
-        <v>0.038804206935551595</v>
+        <v>0.054287448249601473</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-13</v>
+        <v>-46</v>
       </c>
       <c r="M38" s="2">
-        <v>0.2888775154835457</v>
+        <v>0.42528988953842517</v>
       </c>
       <c r="N38" s="2">
-        <v>40.56348436965971</v>
+        <v>54.55656428078355</v>
       </c>
       <c r="O38" s="2">
-        <v>86.07594936708861</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P38" s="2">
-        <v>28.305323956526895</v>
+        <v>26.51995189252711</v>
       </c>
       <c r="Q38" s="2">
-        <v>64.55696202531647</v>
+        <v>67.46835443037975</v>
       </c>
       <c r="R38" s="2">
-        <v>53.92405063291139</v>
+        <v>57.53164556962025</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
@@ -4420,64 +4417,64 @@
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
-        <v>-0.18</v>
-      </c>
-      <c r="C39" s="2">
-        <v>22.78481012658228</v>
-      </c>
-      <c r="D39" s="2">
-        <v>100</v>
-      </c>
-      <c r="E39" s="2">
-        <v>-7.97</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0.09070062691011735</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="H39" s="2">
-        <v>51.1</v>
-      </c>
-      <c r="I39" s="2">
-        <v>9.01</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0.01990433112361712</v>
-      </c>
-      <c r="K39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="2">
-        <v>-14</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0.12250282537403279</v>
-      </c>
-      <c r="N39" s="2">
-        <v>23.92601535870843</v>
-      </c>
-      <c r="O39" s="2">
-        <v>69.62025316455697</v>
-      </c>
-      <c r="P39" s="2">
-        <v>18.299999237060547</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>57.46835443037974</v>
-      </c>
-      <c r="R39" s="2">
-        <v>53.41772151898734</v>
-      </c>
-      <c r="S39" s="2" t="s">
+      <c r="B39" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="C39" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="D39" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4.83</v>
+      </c>
+      <c r="F39" s="3">
+        <v>-0.15629033779888524</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H39" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="I39" s="3">
+        <v>-11.06</v>
+      </c>
+      <c r="J39" s="3">
+        <v>-0.01940685116622368</v>
+      </c>
+      <c r="K39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3">
+        <v>-4</v>
+      </c>
+      <c r="M39" s="3">
+        <v>-0.13548044467769726</v>
+      </c>
+      <c r="N39" s="3">
+        <v>-1.5204691408286928</v>
+      </c>
+      <c r="O39" s="3">
+        <v>35.44303797468354</v>
+      </c>
+      <c r="P39" s="3">
+        <v>30.28933322215756</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="R39" s="3">
+        <v>30.316455696202535</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4486,247 +4483,247 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>-4.08</v>
+        <v>-6.41</v>
       </c>
       <c r="C40" s="1">
-        <v>5.063291139240507</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>16.730392156862745</v>
+        <v>8.798751950078003</v>
       </c>
       <c r="E40" s="1">
-        <v>12.27</v>
+        <v>0.92</v>
       </c>
       <c r="F40" s="1">
-        <v>0.2721261109960245</v>
+        <v>-0.26771341130198373</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>49.27</v>
+        <v>33.54</v>
       </c>
       <c r="I40" s="1">
-        <v>-10.63</v>
+        <v>-36.42</v>
       </c>
       <c r="J40" s="1">
-        <v>0.02361688973368183</v>
+        <v>-0.021148643287555488</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="M40" s="1">
-        <v>0.1661187827829731</v>
+        <v>-0.37723916457139406</v>
       </c>
       <c r="N40" s="1">
-        <v>28.28761109960246</v>
+        <v>-25.69634113019837</v>
       </c>
       <c r="O40" s="1">
-        <v>74.68354430379746</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P40" s="1">
-        <v>45.29877115964868</v>
+        <v>42.434935391194514</v>
       </c>
       <c r="Q40" s="1">
-        <v>45.18987341772152</v>
+        <v>21.772151898734172</v>
       </c>
       <c r="R40" s="1">
-        <v>40.75949367088608</v>
+        <v>9.93670886075949</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="3">
         <v>-5.03</v>
       </c>
-      <c r="C41" s="1">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="D41" s="1">
-        <v>7.34990059642147</v>
-      </c>
-      <c r="E41" s="1">
-        <v>-1.75</v>
-      </c>
-      <c r="F41" s="1">
-        <v>-0.012992593659218676</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.11</v>
-      </c>
-      <c r="H41" s="1">
-        <v>76.88</v>
-      </c>
-      <c r="I41" s="1">
-        <v>-5.99</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0.016911260218543354</v>
-      </c>
-      <c r="K41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>5</v>
-      </c>
-      <c r="M41" s="1">
-        <v>-0.001331787555783004</v>
-      </c>
-      <c r="N41" s="1">
-        <v>11.542554065726831</v>
-      </c>
-      <c r="O41" s="1">
-        <v>56.9620253164557</v>
-      </c>
-      <c r="P41" s="1">
-        <v>46.4052282234621</v>
-      </c>
-      <c r="Q41" s="1">
+      <c r="C41" s="3">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="D41" s="3">
+        <v>7.013916500994036</v>
+      </c>
+      <c r="E41" s="3">
+        <v>-1.3</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.09601781983879792</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46.08</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-13.15</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0.028988482410286218</v>
+      </c>
+      <c r="K41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0.11354194036190357</v>
+      </c>
+      <c r="N41" s="3">
+        <v>23.381769363131394</v>
+      </c>
+      <c r="O41" s="3">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="P41" s="3">
+        <v>40.794223935469645</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>42.405063291139236</v>
+      </c>
+      <c r="R41" s="3">
+        <v>38.48101265822785</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3">
+        <v>3.61</v>
+      </c>
+      <c r="C42" s="3">
+        <v>53.16455696202531</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1.0664819944598338</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2.2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>-0.10381871794865229</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="H42" s="3">
+        <v>52.05</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-0.005804801745770332</v>
+      </c>
+      <c r="K42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="3">
+        <v>16</v>
+      </c>
+      <c r="M42" s="3">
+        <v>-0.17501045757376898</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-5.473470430435863</v>
+      </c>
+      <c r="O42" s="3">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="P42" s="3">
+        <v>12.159120495183384</v>
+      </c>
+      <c r="Q42" s="3">
         <v>44.30379746835443</v>
       </c>
-      <c r="R41" s="1">
-        <v>30.063291139240505</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1">
-        <v>3.61</v>
-      </c>
-      <c r="C42" s="1">
-        <v>53.16455696202531</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1.0831024930747921</v>
-      </c>
-      <c r="E42" s="1">
-        <v>-0.1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>-0.07152608902469655</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="H42" s="1">
-        <v>37.51</v>
-      </c>
-      <c r="I42" s="1">
-        <v>-0.72</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-0.006280195480516437</v>
-      </c>
-      <c r="K42" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>34</v>
-      </c>
-      <c r="M42" s="1">
-        <v>-0.13937077908104945</v>
-      </c>
-      <c r="N42" s="1">
-        <v>-2.2613450867998</v>
-      </c>
-      <c r="O42" s="1">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="P42" s="1">
-        <v>9.169379043273572</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>42.15189873417721</v>
-      </c>
-      <c r="R42" s="1">
-        <v>38.54430379746835</v>
-      </c>
-      <c r="S42" s="1" t="s">
+      <c r="R42" s="3">
+        <v>34.87341772151899</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T42" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
-        <v>-0.02</v>
-      </c>
-      <c r="C43" s="1">
-        <v>27.848101265822784</v>
-      </c>
-      <c r="D43" s="1">
-        <v>1214</v>
-      </c>
-      <c r="E43" s="1">
-        <v>5.23</v>
-      </c>
-      <c r="F43" s="1">
-        <v>-0.10300963463207322</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="H43" s="1">
-        <v>42.05</v>
-      </c>
-      <c r="I43" s="1">
-        <v>-18.73</v>
-      </c>
-      <c r="J43" s="1">
-        <v>-0.0015476646793928285</v>
-      </c>
-      <c r="K43" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>6</v>
-      </c>
-      <c r="M43" s="1">
-        <v>-0.07438765601454933</v>
-      </c>
-      <c r="N43" s="1">
-        <v>4.236967219850214</v>
-      </c>
-      <c r="O43" s="1">
-        <v>48.10126582278481</v>
-      </c>
-      <c r="P43" s="1">
-        <v>38.87068031431492</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>49.87341772151898</v>
-      </c>
-      <c r="R43" s="1">
-        <v>42.151898734177216</v>
-      </c>
-      <c r="S43" s="1" t="s">
+      <c r="B43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C43" s="3">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="D43" s="3">
+        <v>246.29999999999998</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="F43" s="3">
+        <v>-0.09744959742905798</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="H43" s="3">
+        <v>54.17</v>
+      </c>
+      <c r="I43" s="3">
+        <v>-1.42</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0.006817215206790364</v>
+      </c>
+      <c r="K43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>11</v>
+      </c>
+      <c r="M43" s="3">
+        <v>-0.059115583784764336</v>
+      </c>
+      <c r="N43" s="3">
+        <v>6.116016948464606</v>
+      </c>
+      <c r="O43" s="3">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P43" s="3">
+        <v>30.495842865521038</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>57.34177215189874</v>
+      </c>
+      <c r="R43" s="3">
+        <v>43.924050632911396</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T43" s="1">
-        <v>-0.38</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4740,49 +4737,49 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="3">
-        <v>26.862745098039216</v>
+        <v>26.80392156862745</v>
       </c>
       <c r="E44" s="3">
-        <v>-1.51</v>
+        <v>-2.29</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.4179675723306637</v>
+        <v>-0.4130401822957189</v>
       </c>
       <c r="G44" s="3">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="H44" s="3">
-        <v>32.04</v>
+        <v>46.36</v>
       </c>
       <c r="I44" s="3">
-        <v>-31.9</v>
+        <v>-21.67</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.018572838403102806</v>
+        <v>-0.004878625387168959</v>
       </c>
       <c r="K44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-18</v>
+        <v>-116</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.24941592047191197</v>
+        <v>-0.2399894921300506</v>
       </c>
       <c r="N44" s="3">
-        <v>-13.265859225886054</v>
+        <v>-11.971373886064026</v>
       </c>
       <c r="O44" s="3">
-        <v>13.924050632911392</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P44" s="3">
-        <v>44.155007607957295</v>
+        <v>39.61643255338282</v>
       </c>
       <c r="Q44" s="3">
-        <v>38.60759493670886</v>
+        <v>47.59493670886075</v>
       </c>
       <c r="R44" s="3">
-        <v>26.518987341772146</v>
+        <v>30.949367088607595</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
@@ -4802,49 +4799,49 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.818399044205496</v>
+        <v>0.7323775388291519</v>
       </c>
       <c r="E45" s="2">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2">
-        <v>0.1791686078688256</v>
+        <v>-0.02196012226052682</v>
       </c>
       <c r="G45" s="2">
         <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>65.55</v>
+        <v>34.76</v>
       </c>
       <c r="I45" s="2">
-        <v>17.34</v>
+        <v>2.6</v>
       </c>
       <c r="J45" s="2">
-        <v>0.025585314395313728</v>
+        <v>0.014397334801875173</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.22793197884682925</v>
+        <v>0.028421724243401947</v>
       </c>
       <c r="N45" s="2">
-        <v>34.468930705988065</v>
+        <v>14.86974775128122</v>
       </c>
       <c r="O45" s="2">
-        <v>82.27848101265823</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P45" s="2">
-        <v>19.641850851970627</v>
+        <v>18.755109025385668</v>
       </c>
       <c r="Q45" s="2">
-        <v>62.27848101265823</v>
+        <v>52.65822784810127</v>
       </c>
       <c r="R45" s="2">
-        <v>56.962025316455694</v>
+        <v>50.75949367088607</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
@@ -4861,120 +4858,120 @@
         <v>-0.3</v>
       </c>
       <c r="C46" s="1">
-        <v>21.518987341772153</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="D46" s="1">
-        <v>543.5000000000001</v>
+        <v>548.5333333333334</v>
       </c>
       <c r="E46" s="1">
-        <v>-0.94</v>
+        <v>4.27</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.25626706372444663</v>
+        <v>-0.3705634589208545</v>
       </c>
       <c r="G46" s="1">
         <v>1.51</v>
       </c>
       <c r="H46" s="1">
-        <v>44.66</v>
+        <v>38.93</v>
       </c>
       <c r="I46" s="1">
-        <v>11.33</v>
+        <v>-17.57</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.0062409394148189405</v>
+        <v>-0.015016473512974332</v>
       </c>
       <c r="K46" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.2022033263357904</v>
+        <v>-0.31470532475345525</v>
       </c>
       <c r="N46" s="1">
-        <v>-8.544599812273905</v>
+        <v>-19.442957148404496</v>
       </c>
       <c r="O46" s="1">
-        <v>22.78481012658228</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P46" s="1">
-        <v>40.6204924523832</v>
+        <v>50.613275903697605</v>
       </c>
       <c r="Q46" s="1">
-        <v>51.139240506329116</v>
+        <v>39.746835443037966</v>
       </c>
       <c r="R46" s="1">
-        <v>31.39240506329114</v>
+        <v>21.962025316455694</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="1">
         <v>10.62</v>
       </c>
-      <c r="C47" s="3">
-        <v>81.0126582278481</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="C47" s="1">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="D47" s="1">
         <v>0.8549905838041432</v>
       </c>
-      <c r="E47" s="3">
-        <v>-4.11</v>
-      </c>
-      <c r="F47" s="3">
-        <v>-0.4152563242428725</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1.47</v>
-      </c>
-      <c r="H47" s="3">
-        <v>29.08</v>
-      </c>
-      <c r="I47" s="3">
-        <v>-19.09</v>
-      </c>
-      <c r="J47" s="3">
-        <v>-0.029842556362938727</v>
-      </c>
-      <c r="K47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>17</v>
-      </c>
-      <c r="M47" s="3">
-        <v>-0.3654328799827383</v>
-      </c>
-      <c r="N47" s="3">
-        <v>-24.867555176968693</v>
-      </c>
-      <c r="O47" s="3">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="P47" s="3">
-        <v>29.26623910493363</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>38.607594936708864</v>
-      </c>
-      <c r="R47" s="3">
-        <v>25.759493670886073</v>
-      </c>
-      <c r="S47" s="3" t="s">
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>-0.37390585239131796</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H47" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="I47" s="1">
+        <v>-14.35</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-0.011613039997456574</v>
+      </c>
+      <c r="K47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>11</v>
+      </c>
+      <c r="M47" s="1">
+        <v>-0.3300955510835538</v>
+      </c>
+      <c r="N47" s="1">
+        <v>-20.981979781414356</v>
+      </c>
+      <c r="O47" s="1">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="P47" s="1">
+        <v>33.84253937304741</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>49.11392405063292</v>
+      </c>
+      <c r="R47" s="1">
+        <v>26.139240506329113</v>
+      </c>
+      <c r="S47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T47" s="3">
-        <v>-0.13</v>
+      <c r="T47" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -4988,49 +4985,49 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D48" s="2">
-        <v>7.505025125628141</v>
+        <v>7.977386934673366</v>
       </c>
       <c r="E48" s="2">
-        <v>-1.16</v>
+        <v>3.41</v>
       </c>
       <c r="F48" s="2">
-        <v>0.3550663954606283</v>
+        <v>-0.06535354588389355</v>
       </c>
       <c r="G48" s="2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H48" s="2">
-        <v>71.5</v>
+        <v>44.67</v>
       </c>
       <c r="I48" s="2">
-        <v>85.05</v>
+        <v>37.54</v>
       </c>
       <c r="J48" s="2">
-        <v>0.039067879528610155</v>
+        <v>0.014321123753770508</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="M48" s="2">
-        <v>0.47167445649498485</v>
+        <v>0.04964849504898727</v>
       </c>
       <c r="N48" s="2">
-        <v>58.84317847080362</v>
+        <v>16.992424831839752</v>
       </c>
       <c r="O48" s="2">
-        <v>89.87341772151899</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P48" s="2">
-        <v>15.18684888660459</v>
+        <v>25.31695963070349</v>
       </c>
       <c r="Q48" s="2">
-        <v>69.87341772151898</v>
+        <v>59.87341772151899</v>
       </c>
       <c r="R48" s="2">
-        <v>63.037974683544306</v>
+        <v>50.506329113924046</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>94</v>
@@ -5050,116 +5047,116 @@
         <v>26.582278481012654</v>
       </c>
       <c r="D49" s="2">
-        <v>1710.0000000000002</v>
+        <v>1734.8333333333335</v>
       </c>
       <c r="E49" s="2">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="F49" s="2">
-        <v>0.7888246191322793</v>
+        <v>0.26050081530723546</v>
       </c>
       <c r="G49" s="2">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="H49" s="2">
-        <v>70.19</v>
+        <v>48.3</v>
       </c>
       <c r="I49" s="2">
-        <v>141.75</v>
+        <v>74.32</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06629949146826043</v>
+        <v>0.050836654911211865</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="M49" s="2">
-        <v>1.0856451381288232</v>
+        <v>0.563887151863502</v>
       </c>
       <c r="N49" s="2">
-        <v>120.24024663418746</v>
+        <v>68.41629051329122</v>
       </c>
       <c r="O49" s="2">
-        <v>97.46835443037975</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P49" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q49" s="2">
-        <v>74.55696202531647</v>
+        <v>70</v>
       </c>
       <c r="R49" s="2">
-        <v>63.544303797468345</v>
+        <v>60.25316455696203</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T49" s="2">
-        <v>0.38</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="1">
         <v>-0.13</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="1">
         <v>25.31645569620253</v>
       </c>
-      <c r="D50" s="3">
-        <v>385.61538461538464</v>
-      </c>
-      <c r="E50" s="3">
-        <v>2.75</v>
-      </c>
-      <c r="F50" s="3">
-        <v>-0.436916409525831</v>
-      </c>
-      <c r="G50" s="3">
-        <v>1.53</v>
-      </c>
-      <c r="H50" s="3">
-        <v>39.39</v>
-      </c>
-      <c r="I50" s="3">
-        <v>-23.32</v>
-      </c>
-      <c r="J50" s="3">
-        <v>-0.030364906654603615</v>
-      </c>
-      <c r="K50" s="3" t="b">
+      <c r="D50" s="1">
+        <v>300.1538461538462</v>
+      </c>
+      <c r="E50" s="1">
+        <v>5.32</v>
+      </c>
+      <c r="F50" s="1">
+        <v>-0.493499147921606</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="H50" s="1">
+        <v>42.04</v>
+      </c>
+      <c r="I50" s="1">
+        <v>-26.46</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-0.02662454853740195</v>
+      </c>
+      <c r="K50" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L50" s="3">
-        <v>7</v>
-      </c>
-      <c r="M50" s="3">
-        <v>-0.3807325255729137</v>
-      </c>
-      <c r="N50" s="3">
-        <v>-26.397519735986226</v>
-      </c>
-      <c r="O50" s="3">
+      <c r="L50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="M50" s="1">
+        <v>-0.4376410137542067</v>
+      </c>
+      <c r="N50" s="1">
+        <v>-31.736526048479636</v>
+      </c>
+      <c r="O50" s="1">
         <v>2.5316455696202533</v>
       </c>
-      <c r="P50" s="3">
-        <v>47.64150593279924</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>39.24050632911393</v>
-      </c>
-      <c r="R50" s="3">
-        <v>21.77215189873418</v>
-      </c>
-      <c r="S50" s="3" t="s">
+      <c r="P50" s="1">
+        <v>42.0212746732318</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>40.50632911392405</v>
+      </c>
+      <c r="R50" s="1">
+        <v>22.531645569620252</v>
+      </c>
+      <c r="S50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T50" s="3">
+      <c r="T50" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5171,52 +5168,52 @@
         <v>-3.88</v>
       </c>
       <c r="C51" s="3">
-        <v>7.59493670886076</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="D51" s="3">
-        <v>-6.131443298969073</v>
+        <v>16.3659793814433</v>
       </c>
       <c r="E51" s="3">
-        <v>17.05</v>
+        <v>36.11</v>
       </c>
       <c r="F51" s="3">
-        <v>0.06505664660412691</v>
+        <v>-0.1534588067470235</v>
       </c>
       <c r="G51" s="3">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="H51" s="3">
-        <v>56.45</v>
+        <v>44.08</v>
       </c>
       <c r="I51" s="3">
-        <v>34.3</v>
+        <v>11.61</v>
       </c>
       <c r="J51" s="3">
-        <v>0.03187932043656487</v>
+        <v>0.028904000711836478</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M51" s="3">
-        <v>0.21028668625600733</v>
+        <v>0.009734565624397895</v>
       </c>
       <c r="N51" s="3">
-        <v>32.704401446905884</v>
+        <v>13.001031889380831</v>
       </c>
       <c r="O51" s="3">
-        <v>81.0126582278481</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P51" s="3">
         <v>46.744012320672994</v>
       </c>
       <c r="Q51" s="3">
-        <v>33.67088607594937</v>
+        <v>49.87341772151899</v>
       </c>
       <c r="R51" s="3">
-        <v>26.64556962025317</v>
+        <v>36.39240506329114</v>
       </c>
       <c r="S51" s="3" t="s">
         <v>113</v>
@@ -5233,52 +5230,52 @@
         <v>5.3</v>
       </c>
       <c r="C52" s="2">
-        <v>62.0253164556962</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="D52" s="2">
-        <v>6.496226415094339</v>
+        <v>6.737735849056604</v>
       </c>
       <c r="E52" s="2">
-        <v>0.22</v>
+        <v>-1.41</v>
       </c>
       <c r="F52" s="2">
-        <v>0.09175586852112316</v>
+        <v>0.5185182319425945</v>
       </c>
       <c r="G52" s="2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H52" s="2">
-        <v>66.21</v>
+        <v>68.54</v>
       </c>
       <c r="I52" s="2">
-        <v>64.37</v>
+        <v>79.38</v>
       </c>
       <c r="J52" s="2">
-        <v>0.027550206758726836</v>
+        <v>0.0471794927930525</v>
       </c>
       <c r="K52" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="M52" s="2">
-        <v>0.17974195093795586</v>
+        <v>0.6083293496235109</v>
       </c>
       <c r="N52" s="2">
-        <v>29.649927915100726</v>
+        <v>72.86051028929212</v>
       </c>
       <c r="O52" s="2">
-        <v>75.9493670886076</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P52" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q52" s="2">
-        <v>67.21518987341773</v>
+        <v>69.74683544303798</v>
       </c>
       <c r="R52" s="2">
-        <v>56.77215189873419</v>
+        <v>61.70886075949366</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>94</v>
@@ -5288,65 +5285,65 @@
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="3">
         <v>-0.71</v>
       </c>
-      <c r="C53" s="1">
-        <v>17.72151898734177</v>
-      </c>
-      <c r="D53" s="1">
-        <v>12.042253521126762</v>
-      </c>
-      <c r="E53" s="1">
-        <v>6.97</v>
-      </c>
-      <c r="F53" s="1">
-        <v>-0.1745555804193139</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2.59</v>
-      </c>
-      <c r="H53" s="1">
-        <v>69.25</v>
-      </c>
-      <c r="I53" s="1">
-        <v>-14.45</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0.019469516135453818</v>
-      </c>
-      <c r="K53" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1">
-        <v>25</v>
-      </c>
-      <c r="M53" s="1">
-        <v>-0.0060039285605621995</v>
-      </c>
-      <c r="N53" s="1">
-        <v>11.075339965248917</v>
-      </c>
-      <c r="O53" s="1">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="P53" s="1">
-        <v>48.21894075039502</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>48.734177215189874</v>
-      </c>
-      <c r="R53" s="1">
-        <v>35.12658227848102</v>
-      </c>
-      <c r="S53" s="1" t="s">
+      <c r="C53" s="3">
+        <v>16.455696202531644</v>
+      </c>
+      <c r="D53" s="3">
+        <v>6.873239436619719</v>
+      </c>
+      <c r="E53" s="3">
+        <v>5.43</v>
+      </c>
+      <c r="F53" s="3">
+        <v>-0.24531088377401306</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="H53" s="3">
+        <v>40.1</v>
+      </c>
+      <c r="I53" s="3">
+        <v>-29.77</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0.013374429803373878</v>
+      </c>
+      <c r="K53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3">
+        <v>-13</v>
+      </c>
+      <c r="M53" s="3">
+        <v>-0.06678390594487427</v>
+      </c>
+      <c r="N53" s="3">
+        <v>5.349184732453615</v>
+      </c>
+      <c r="O53" s="3">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="P53" s="3">
+        <v>46.06334900207262</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>36.58227848101265</v>
+      </c>
+      <c r="R53" s="3">
+        <v>30.189873417721515</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T53" s="1">
-        <v>-0.76</v>
+      <c r="T53" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5354,55 +5351,55 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="C54" s="2">
-        <v>35.44303797468354</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="D54" s="2">
-        <v>41.629629629629626</v>
+        <v>34.06060606060606</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.44</v>
+        <v>-2.25</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.00014858383710547596</v>
+        <v>0.002924203187187252</v>
       </c>
       <c r="G54" s="2">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H54" s="2">
-        <v>66.62</v>
+        <v>46.11</v>
       </c>
       <c r="I54" s="2">
-        <v>11.42</v>
+        <v>-4.71</v>
       </c>
       <c r="J54" s="2">
-        <v>0.029728045222307847</v>
+        <v>0.01487390105523656</v>
       </c>
       <c r="K54" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M54" s="2">
-        <v>0.048614787140898175</v>
+        <v>0.05549656475650422</v>
       </c>
       <c r="N54" s="2">
-        <v>16.53721153539496</v>
+        <v>17.577231802591463</v>
       </c>
       <c r="O54" s="2">
-        <v>64.55696202531645</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P54" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q54" s="2">
-        <v>65.69620253164557</v>
+        <v>57.59493670886076</v>
       </c>
       <c r="R54" s="2">
-        <v>52.65822784810126</v>
+        <v>52.21518987341773</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>93</v>
@@ -5412,127 +5409,127 @@
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <v>4.03</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="2">
         <v>56.9620253164557</v>
       </c>
-      <c r="D55" s="1">
-        <v>2.2580645161290325</v>
-      </c>
-      <c r="E55" s="1">
-        <v>-0.7</v>
-      </c>
-      <c r="F55" s="1">
-        <v>-0.18622611726230834</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H55" s="1">
-        <v>39.05</v>
-      </c>
-      <c r="I55" s="1">
-        <v>-3.12</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0.0001009254578829784</v>
-      </c>
-      <c r="K55" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
-        <v>10</v>
-      </c>
-      <c r="M55" s="1">
-        <v>-0.16502465161969804</v>
-      </c>
-      <c r="N55" s="1">
-        <v>-4.826732340664665</v>
-      </c>
-      <c r="O55" s="1">
-        <v>27.848101265822784</v>
-      </c>
-      <c r="P55" s="1">
-        <v>18.39301096820415</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>47.21518987341773</v>
-      </c>
-      <c r="R55" s="1">
-        <v>36.582278481012665</v>
-      </c>
-      <c r="S55" s="1" t="s">
+      <c r="D55" s="2">
+        <v>2.3176178660049627</v>
+      </c>
+      <c r="E55" s="2">
+        <v>-2.09</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0.060163066321827274</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1.17</v>
+      </c>
+      <c r="H55" s="2">
+        <v>71.65</v>
+      </c>
+      <c r="I55" s="2">
+        <v>7.49</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0.012883785857358753</v>
+      </c>
+      <c r="K55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2">
+        <v>-63</v>
+      </c>
+      <c r="M55" s="2">
+        <v>0.07878244437762705</v>
+      </c>
+      <c r="N55" s="2">
+        <v>19.90581976470373</v>
+      </c>
+      <c r="O55" s="2">
+        <v>73.41772151898735</v>
+      </c>
+      <c r="P55" s="2">
+        <v>17.353613604156827</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>57.9746835443038</v>
+      </c>
+      <c r="R55" s="2">
+        <v>51.51898734177216</v>
+      </c>
+      <c r="S55" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T55" s="1">
-        <v>0.38</v>
+      <c r="T55" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="3">
         <v>8.65</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="3">
         <v>74.68354430379746</v>
       </c>
-      <c r="D56" s="1">
-        <v>0.1757225433526011</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="F56" s="1">
-        <v>-0.09903570790419841</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="H56" s="1">
-        <v>51.35</v>
-      </c>
-      <c r="I56" s="1">
-        <v>10.14</v>
-      </c>
-      <c r="J56" s="1">
-        <v>-0.008898279015999048</v>
-      </c>
-      <c r="K56" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>199</v>
-      </c>
-      <c r="M56" s="1">
-        <v>-0.17748113078185646</v>
-      </c>
-      <c r="N56" s="1">
-        <v>-6.07238025688051</v>
-      </c>
-      <c r="O56" s="1">
-        <v>25.31645569620253</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="D56" s="3">
+        <v>0.18843930635838138</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="F56" s="3">
+        <v>-0.03972750715007273</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="H56" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="I56" s="3">
+        <v>12.24</v>
+      </c>
+      <c r="J56" s="3">
+        <v>-0.002064357080070061</v>
+      </c>
+      <c r="K56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3">
+        <v>167</v>
+      </c>
+      <c r="M56" s="3">
+        <v>-0.12296707963482456</v>
+      </c>
+      <c r="N56" s="3">
+        <v>-0.26913263654142544</v>
+      </c>
+      <c r="O56" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="P56" s="3">
         <v>10.95912073621325</v>
       </c>
-      <c r="Q56" s="1">
-        <v>45.063291139240505</v>
-      </c>
-      <c r="R56" s="1">
-        <v>33.98734177215189</v>
-      </c>
-      <c r="S56" s="1" t="s">
+      <c r="Q56" s="3">
+        <v>51.0126582278481</v>
+      </c>
+      <c r="R56" s="3">
+        <v>38.54430379746835</v>
+      </c>
+      <c r="S56" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="T56" s="1">
-        <v>0.13</v>
+      <c r="T56" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5546,37 +5543,37 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.31067044381492</v>
+        <v>2.797450424929179</v>
       </c>
       <c r="E57" s="2">
-        <v>0.39</v>
+        <v>-1.92</v>
       </c>
       <c r="F57" s="2">
-        <v>0.6840401434964034</v>
+        <v>1.0562201784523069</v>
       </c>
       <c r="G57" s="2">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="H57" s="2">
-        <v>79.04</v>
+        <v>60.77</v>
       </c>
       <c r="I57" s="2">
-        <v>160.72</v>
+        <v>157.16</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08503248308634306</v>
+        <v>0.09765329786120983</v>
       </c>
       <c r="K57" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="M57" s="2">
-        <v>0.7900474717094548</v>
+        <v>1.183270052244823</v>
       </c>
       <c r="N57" s="2">
-        <v>90.68047999225062</v>
+        <v>130.35458055142334</v>
       </c>
       <c r="O57" s="2">
         <v>93.67088607594937</v>
@@ -5585,16 +5582,16 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q57" s="2">
-        <v>81.51898734177216</v>
+        <v>80.75949367088607</v>
       </c>
       <c r="R57" s="2">
-        <v>67.34177215189874</v>
+        <v>67.27848101265823</v>
       </c>
       <c r="S57" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T57" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5608,49 +5605,49 @@
         <v>94.9367088607595</v>
       </c>
       <c r="D58" s="2">
-        <v>0.09701492537313429</v>
+        <v>0.09900497512437803</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="F58" s="2">
-        <v>0.021818608106908055</v>
+        <v>0.12718350609419177</v>
       </c>
       <c r="G58" s="2">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H58" s="2">
-        <v>65.53</v>
+        <v>54.56</v>
       </c>
       <c r="I58" s="2">
-        <v>49.13</v>
+        <v>38.02</v>
       </c>
       <c r="J58" s="2">
-        <v>0.02231951880965812</v>
+        <v>0.02369851970661783</v>
       </c>
       <c r="K58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="2">
-        <v>315</v>
+        <v>268</v>
       </c>
       <c r="M58" s="2">
-        <v>0.08754315159899995</v>
+        <v>0.19180370052314388</v>
       </c>
       <c r="N58" s="2">
-        <v>20.430047981205142</v>
+        <v>31.207945379255413</v>
       </c>
       <c r="O58" s="2">
-        <v>67.08860759493672</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P58" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q58" s="2">
-        <v>65.0632911392405</v>
+        <v>65.18987341772151</v>
       </c>
       <c r="R58" s="2">
-        <v>55.31645569620253</v>
+        <v>60</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>105</v>
@@ -5660,188 +5657,188 @@
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="3">
         <v>34.32</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>100</v>
       </c>
-      <c r="D59" s="2">
-        <v>-1.435897435897436</v>
-      </c>
-      <c r="E59" s="2">
-        <v>-2.43</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0.17401162363333672</v>
-      </c>
-      <c r="G59" s="2">
-        <v>1.24</v>
-      </c>
-      <c r="H59" s="2">
-        <v>56.61</v>
-      </c>
-      <c r="I59" s="2">
-        <v>47.17</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0.02141742119672486</v>
-      </c>
-      <c r="K59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>374</v>
-      </c>
-      <c r="M59" s="2">
-        <v>0.19945338240446908</v>
-      </c>
-      <c r="N59" s="2">
-        <v>31.621071061752055</v>
-      </c>
-      <c r="O59" s="2">
-        <v>79.74683544303798</v>
-      </c>
-      <c r="P59" s="2">
-        <v>11.512523311327532</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>59.74683544303798</v>
-      </c>
-      <c r="R59" s="2">
-        <v>56.582278481012665</v>
-      </c>
-      <c r="S59" s="2" t="s">
+      <c r="D59" s="3">
+        <v>-1.4967948717948718</v>
+      </c>
+      <c r="E59" s="3">
+        <v>-1.03</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.030692772753419806</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="H59" s="3">
+        <v>44.11</v>
+      </c>
+      <c r="I59" s="3">
+        <v>23.08</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.005105688176290398</v>
+      </c>
+      <c r="K59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" s="3">
+        <v>367</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0.04821689327652545</v>
+      </c>
+      <c r="N59" s="3">
+        <v>16.849264654593583</v>
+      </c>
+      <c r="O59" s="3">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="P59" s="3">
+        <v>24.570041255395854</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>51.64556962025316</v>
+      </c>
+      <c r="R59" s="3">
+        <v>45.949367088607595</v>
+      </c>
+      <c r="S59" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T59" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="1">
         <v>6.37</v>
       </c>
-      <c r="C60" s="3">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="D60" s="3">
-        <v>-0.1255886970172684</v>
-      </c>
-      <c r="E60" s="3">
-        <v>-0.23</v>
-      </c>
-      <c r="F60" s="3">
-        <v>-0.16126001565497908</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0.38</v>
-      </c>
-      <c r="H60" s="3">
-        <v>38.08</v>
-      </c>
-      <c r="I60" s="3">
-        <v>-0.86</v>
-      </c>
-      <c r="J60" s="3">
-        <v>-0.010130946048307181</v>
-      </c>
-      <c r="K60" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>149</v>
-      </c>
-      <c r="M60" s="3">
-        <v>-0.22698455914707094</v>
-      </c>
-      <c r="N60" s="3">
-        <v>-11.02272309340195</v>
-      </c>
-      <c r="O60" s="3">
-        <v>20.253164556962027</v>
-      </c>
-      <c r="P60" s="3">
-        <v>12.73975043749647</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>36.32911392405063</v>
-      </c>
-      <c r="R60" s="3">
-        <v>28.79746835443038</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="C60" s="1">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="D60" s="1">
+        <v>-0.18210361067503927</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="F60" s="1">
+        <v>-0.14781499880780213</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="H60" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="I60" s="1">
+        <v>-4.03</v>
+      </c>
+      <c r="J60" s="1">
+        <v>-0.007203039194653449</v>
+      </c>
+      <c r="K60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>101</v>
+      </c>
+      <c r="M60" s="1">
+        <v>-0.21791148090022472</v>
+      </c>
+      <c r="N60" s="1">
+        <v>-9.763572763081443</v>
+      </c>
+      <c r="O60" s="1">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="P60" s="1">
+        <v>17.48490342947292</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>37.08860759493671</v>
+      </c>
+      <c r="R60" s="1">
+        <v>28.101265822784814</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T60" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="1">
-        <v>17.74</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B61" s="3">
+        <v>17.65</v>
+      </c>
+      <c r="C61" s="3">
         <v>92.40506329113924</v>
       </c>
-      <c r="D61" s="1">
-        <v>0.6178128523111613</v>
-      </c>
-      <c r="E61" s="1">
-        <v>-0.38</v>
-      </c>
-      <c r="F61" s="1">
-        <v>-0.14291277018514845</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.96</v>
-      </c>
-      <c r="H61" s="1">
-        <v>49.51</v>
-      </c>
-      <c r="I61" s="1">
-        <v>11.77</v>
-      </c>
-      <c r="J61" s="1">
-        <v>-0.006832330097585761</v>
-      </c>
-      <c r="K61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>155</v>
-      </c>
-      <c r="M61" s="1">
-        <v>-0.1471530633136705</v>
-      </c>
-      <c r="N61" s="1">
-        <v>-3.0395735100619077</v>
-      </c>
-      <c r="O61" s="1">
-        <v>35.44303797468354</v>
-      </c>
-      <c r="P61" s="1">
-        <v>16.149676494964734</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>54.050632911392405</v>
-      </c>
-      <c r="R61" s="1">
-        <v>42.848101265822784</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T61" s="1">
+      <c r="D61" s="3">
+        <v>0.46515580736543916</v>
+      </c>
+      <c r="E61" s="3">
+        <v>-1.16</v>
+      </c>
+      <c r="F61" s="3">
+        <v>-0.11045310133014175</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="H61" s="3">
+        <v>54.05</v>
+      </c>
+      <c r="I61" s="3">
+        <v>9.92</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0.0006912634267952529</v>
+      </c>
+      <c r="K61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>171</v>
+      </c>
+      <c r="M61" s="3">
+        <v>-0.12031041912438867</v>
+      </c>
+      <c r="N61" s="3">
+        <v>-0.003466585497835498</v>
+      </c>
+      <c r="O61" s="3">
+        <v>40.50632911392405</v>
+      </c>
+      <c r="P61" s="3">
+        <v>20.131624188012864</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>56.07594936708861</v>
+      </c>
+      <c r="R61" s="3">
+        <v>43.22784810126582</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T61" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5856,55 +5853,55 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D62" s="4">
-        <v>4.831074035453597</v>
+        <v>5.503302050747306</v>
       </c>
       <c r="E62" s="4">
-        <v>-8.63</v>
+        <v>-4.88</v>
       </c>
       <c r="F62" s="4">
-        <v>0.702412030848552</v>
+        <v>1.4420935594906092</v>
       </c>
       <c r="G62" s="4">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="H62" s="4">
-        <v>66.15</v>
+        <v>70.6</v>
       </c>
       <c r="I62" s="4">
-        <v>238.33</v>
+        <v>245.53</v>
       </c>
       <c r="J62" s="4">
-        <v>0.1058386935433432</v>
+        <v>0.09617614977172315</v>
       </c>
       <c r="K62" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="4">
-        <v>413</v>
+        <v>476</v>
       </c>
       <c r="M62" s="4">
-        <v>1.1009995849296252</v>
+        <v>1.872529769839392</v>
       </c>
       <c r="N62" s="4">
-        <v>121.77569131426769</v>
+        <v>199.2805523108802</v>
       </c>
       <c r="O62" s="4">
-        <v>98.73417721518987</v>
+        <v>100</v>
       </c>
       <c r="P62" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q62" s="4">
-        <v>82.27848101265823</v>
+        <v>84.55696202531647</v>
       </c>
       <c r="R62" s="4">
-        <v>72.34177215189874</v>
+        <v>72.59493670886076</v>
       </c>
       <c r="S62" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T62" s="4">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5915,52 +5912,52 @@
         <v>10.54</v>
       </c>
       <c r="C63" s="2">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="D63" s="2">
-        <v>6.3927893738140416</v>
+        <v>6.877609108159394</v>
       </c>
       <c r="E63" s="2">
-        <v>-4.36</v>
+        <v>-2.76</v>
       </c>
       <c r="F63" s="2">
-        <v>0.6347132974900617</v>
+        <v>1.1878522127229045</v>
       </c>
       <c r="G63" s="2">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="H63" s="2">
-        <v>75.15</v>
+        <v>64.28</v>
       </c>
       <c r="I63" s="2">
-        <v>139.96</v>
+        <v>130.29</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0865727164624305</v>
+        <v>0.07212697037883466</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="M63" s="2">
-        <v>0.7439008455495046</v>
+        <v>1.3061400262538676</v>
       </c>
       <c r="N63" s="2">
-        <v>86.06581737625561</v>
+        <v>142.64157795232782</v>
       </c>
       <c r="O63" s="2">
-        <v>92.40506329113924</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P63" s="2">
         <v>20.9978319173529</v>
       </c>
       <c r="Q63" s="2">
-        <v>77.84810126582278</v>
+        <v>77.59493670886076</v>
       </c>
       <c r="R63" s="2">
-        <v>66.96202531645571</v>
+        <v>68.54430379746836</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>107</v>
@@ -5970,313 +5967,313 @@
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="3">
         <v>16.87</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="3">
         <v>89.87341772151899</v>
       </c>
-      <c r="D64" s="1">
-        <v>-0.2691167753408418</v>
-      </c>
-      <c r="E64" s="1">
-        <v>-0.69</v>
-      </c>
-      <c r="F64" s="1">
-        <v>-0.07677209987055884</v>
-      </c>
-      <c r="G64" s="1">
+      <c r="D64" s="3">
+        <v>-0.28986366330764674</v>
+      </c>
+      <c r="E64" s="3">
+        <v>-1.13</v>
+      </c>
+      <c r="F64" s="3">
+        <v>-0.09671219613671744</v>
+      </c>
+      <c r="G64" s="3">
         <v>0.31</v>
       </c>
-      <c r="H64" s="1">
-        <v>59.81</v>
-      </c>
-      <c r="I64" s="1">
-        <v>3.83</v>
-      </c>
-      <c r="J64" s="1">
-        <v>-0.008871724521789534</v>
-      </c>
-      <c r="K64" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>71</v>
-      </c>
-      <c r="M64" s="1">
-        <v>-0.1499171563375643</v>
-      </c>
-      <c r="N64" s="1">
-        <v>-3.315982812451293</v>
-      </c>
-      <c r="O64" s="1">
+      <c r="H64" s="3">
+        <v>53.84</v>
+      </c>
+      <c r="I64" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="J64" s="3">
+        <v>-0.0004284358406020467</v>
+      </c>
+      <c r="K64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>56</v>
+      </c>
+      <c r="M64" s="3">
+        <v>-0.17228496589261055</v>
+      </c>
+      <c r="N64" s="3">
+        <v>-5.2009212623200245</v>
+      </c>
+      <c r="O64" s="3">
         <v>32.91139240506329</v>
       </c>
-      <c r="P64" s="1">
+      <c r="P64" s="3">
         <v>15.211254913322609</v>
       </c>
-      <c r="Q64" s="1">
-        <v>48.22784810126582</v>
-      </c>
-      <c r="R64" s="1">
-        <v>37.40506329113924</v>
-      </c>
-      <c r="S64" s="1" t="s">
+      <c r="Q64" s="3">
+        <v>50.12658227848101</v>
+      </c>
+      <c r="R64" s="3">
+        <v>38.41772151898734</v>
+      </c>
+      <c r="S64" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="T64" s="1">
-        <v>-0.38</v>
+      <c r="T64" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="3">
-        <v>15.41</v>
-      </c>
-      <c r="C65" s="3">
+      <c r="B65" s="1">
+        <v>16.51</v>
+      </c>
+      <c r="C65" s="1">
         <v>87.34177215189874</v>
       </c>
-      <c r="D65" s="3">
-        <v>-0.10837118754055808</v>
-      </c>
-      <c r="E65" s="3">
-        <v>-0.19</v>
-      </c>
-      <c r="F65" s="3">
-        <v>-0.16453528787485666</v>
-      </c>
-      <c r="G65" s="3">
-        <v>1.02</v>
-      </c>
-      <c r="H65" s="3">
-        <v>43.81</v>
-      </c>
-      <c r="I65" s="3">
-        <v>-33.37</v>
-      </c>
-      <c r="J65" s="3">
-        <v>-0.008021649911025294</v>
-      </c>
-      <c r="K65" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3">
-        <v>-153</v>
-      </c>
-      <c r="M65" s="3">
-        <v>-0.16241514131059565</v>
-      </c>
-      <c r="N65" s="3">
-        <v>-4.5657813097544215</v>
-      </c>
-      <c r="O65" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="P65" s="3">
-        <v>48.12800106814908</v>
-      </c>
-      <c r="Q65" s="3">
-        <v>40.75949367088607</v>
-      </c>
-      <c r="R65" s="3">
-        <v>29.050632911392405</v>
-      </c>
-      <c r="S65" s="3" t="s">
+      <c r="D65" s="1">
+        <v>-0.09085402786190197</v>
+      </c>
+      <c r="E65" s="1">
+        <v>-0.08</v>
+      </c>
+      <c r="F65" s="1">
+        <v>-0.49128671708205174</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>32.59</v>
+      </c>
+      <c r="I65" s="1">
+        <v>-47.9</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-0.03690685781363573</v>
+      </c>
+      <c r="K65" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>-199</v>
+      </c>
+      <c r="M65" s="1">
+        <v>-0.49128671708205174</v>
+      </c>
+      <c r="N65" s="1">
+        <v>-37.101096381264135</v>
+      </c>
+      <c r="O65" s="1">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="P65" s="1">
+        <v>50.931782654789714</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>32.27848101265823</v>
+      </c>
+      <c r="R65" s="1">
+        <v>16.89873417721519</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T65" s="3">
-        <v>-0.38</v>
+      <c r="T65" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="3">
         <v>4.01</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="3">
         <v>55.69620253164557</v>
       </c>
-      <c r="D66" s="1">
-        <v>7.0074812967581055</v>
-      </c>
-      <c r="E66" s="1">
-        <v>-0.9</v>
-      </c>
-      <c r="F66" s="1">
-        <v>-0.08084571247327066</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1.15</v>
-      </c>
-      <c r="H66" s="1">
-        <v>48.91</v>
-      </c>
-      <c r="I66" s="1">
-        <v>-11.66</v>
-      </c>
-      <c r="J66" s="1">
-        <v>-0.00043359092444813775</v>
-      </c>
-      <c r="K66" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>-32</v>
-      </c>
-      <c r="M66" s="1">
-        <v>-0.06494461324131295</v>
-      </c>
-      <c r="N66" s="1">
-        <v>5.181271497173847</v>
-      </c>
-      <c r="O66" s="1">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="P66" s="1">
-        <v>21.01837744312229</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>50.12658227848102</v>
-      </c>
-      <c r="R66" s="1">
-        <v>44.11392405063291</v>
-      </c>
-      <c r="S66" s="1" t="s">
+      <c r="D66" s="3">
+        <v>7.221945137157108</v>
+      </c>
+      <c r="E66" s="3">
+        <v>-1.7</v>
+      </c>
+      <c r="F66" s="3">
+        <v>-0.19451257399131322</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H66" s="3">
+        <v>38.78</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-16.57</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-0.001583957620276913</v>
+      </c>
+      <c r="K66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
+        <v>-75</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.18136948359898397</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-6.10937303295736</v>
+      </c>
+      <c r="O66" s="3">
+        <v>27.848101265822784</v>
+      </c>
+      <c r="P66" s="3">
+        <v>19.139656046926937</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>44.68354430379747</v>
+      </c>
+      <c r="R66" s="3">
+        <v>37.911392405063296</v>
+      </c>
+      <c r="S66" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T66" s="1">
-        <v>0.76</v>
+      <c r="T66" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="3">
         <v>7.35</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="3">
         <v>69.62025316455697</v>
       </c>
-      <c r="D67" s="1">
-        <v>84.9795918367347</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F67" s="1">
-        <v>-0.17464350704065426</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H67" s="1">
-        <v>45.64</v>
-      </c>
-      <c r="I67" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="J67" s="1">
-        <v>-0.010596519517794166</v>
-      </c>
-      <c r="K67" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>132</v>
-      </c>
-      <c r="M67" s="1">
-        <v>-0.2456684169433987</v>
-      </c>
-      <c r="N67" s="1">
-        <v>-12.891108873034732</v>
-      </c>
-      <c r="O67" s="1">
+      <c r="D67" s="3">
+        <v>330.17278911564625</v>
+      </c>
+      <c r="E67" s="3">
+        <v>-1.49</v>
+      </c>
+      <c r="F67" s="3">
+        <v>-0.18288640291441538</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="H67" s="3">
+        <v>40.4</v>
+      </c>
+      <c r="I67" s="3">
+        <v>-2.76</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-0.009032533675992323</v>
+      </c>
+      <c r="K67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="3">
+        <v>150</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-0.2540781425395321</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-13.380238927012181</v>
+      </c>
+      <c r="O67" s="3">
         <v>17.72151898734177</v>
       </c>
-      <c r="P67" s="1">
-        <v>18.003852697255347</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>60.37974683544305</v>
-      </c>
-      <c r="R67" s="1">
-        <v>44.936708860759495</v>
-      </c>
-      <c r="S67" s="1" t="s">
+      <c r="P67" s="3">
+        <v>22.02824070768656</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>59.74683544303797</v>
+      </c>
+      <c r="R67" s="3">
+        <v>44.683544303797476</v>
+      </c>
+      <c r="S67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="T67" s="1">
-        <v>0.38</v>
+      <c r="T67" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="1">
         <v>8.24</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="1">
         <v>72.15189873417721</v>
       </c>
-      <c r="D68" s="3">
-        <v>0.6286407766990291</v>
-      </c>
-      <c r="E68" s="3">
-        <v>-0.07</v>
-      </c>
-      <c r="F68" s="3">
-        <v>-0.27315144163343014</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1.49</v>
-      </c>
-      <c r="H68" s="3">
-        <v>36.26</v>
-      </c>
-      <c r="I68" s="3">
-        <v>-13.82</v>
-      </c>
-      <c r="J68" s="3">
-        <v>-0.014530824507100982</v>
-      </c>
-      <c r="K68" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3">
-        <v>-11</v>
-      </c>
-      <c r="M68" s="3">
-        <v>-0.22120785080903493</v>
-      </c>
-      <c r="N68" s="3">
-        <v>-10.445052259598356</v>
-      </c>
-      <c r="O68" s="3">
-        <v>21.518987341772153</v>
-      </c>
-      <c r="P68" s="3">
-        <v>29.145649851223904</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="R68" s="3">
-        <v>27.72151898734177</v>
-      </c>
-      <c r="S68" s="3" t="s">
+      <c r="D68" s="1">
+        <v>0.6152912621359223</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-1.22</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-0.298967640507375</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H68" s="1">
+        <v>40.42</v>
+      </c>
+      <c r="I68" s="1">
+        <v>-16.44</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.009750199688245847</v>
+      </c>
+      <c r="K68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>-69</v>
+      </c>
+      <c r="M68" s="1">
+        <v>-0.2496810515361404</v>
+      </c>
+      <c r="N68" s="1">
+        <v>-12.940529826673005</v>
+      </c>
+      <c r="O68" s="1">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P68" s="1">
+        <v>25.684418695243096</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>40</v>
+      </c>
+      <c r="R68" s="1">
+        <v>28.797468354430375</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T68" s="3">
-        <v>0.13</v>
+      <c r="T68" s="1">
+        <v>0.25</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6290,116 +6287,116 @@
         <v>93.67088607594937</v>
       </c>
       <c r="D69" s="3">
-        <v>-0.47663551401869164</v>
+        <v>-0.4843320505772402</v>
       </c>
       <c r="E69" s="3">
-        <v>1.57</v>
+        <v>-2.56</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.21780123079606967</v>
+        <v>-0.0964299876978872</v>
       </c>
       <c r="G69" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H69" s="3">
-        <v>37.59</v>
+        <v>48.17</v>
       </c>
       <c r="I69" s="3">
-        <v>-14.56</v>
+        <v>-10.81</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.012052150714678567</v>
+        <v>-0.0015674620618146102</v>
       </c>
       <c r="K69" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-34</v>
+        <v>-63</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.23158218346376636</v>
+        <v>-0.10957307809021644</v>
       </c>
       <c r="N69" s="3">
-        <v>-11.4824855250715</v>
+        <v>1.0702675179193921</v>
       </c>
       <c r="O69" s="3">
-        <v>18.9873417721519</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P69" s="3">
-        <v>30.247870785107096</v>
+        <v>31.450467124868602</v>
       </c>
       <c r="Q69" s="3">
-        <v>38.481012658227854</v>
+        <v>46.70886075949367</v>
       </c>
       <c r="R69" s="3">
-        <v>27.72151898734177</v>
+        <v>35.822784810126585</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T69" s="3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="1">
         <v>1.52</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="1">
         <v>45.56962025316456</v>
       </c>
-      <c r="D70" s="3">
-        <v>13.532894736842104</v>
-      </c>
-      <c r="E70" s="3">
-        <v>-0.78</v>
-      </c>
-      <c r="F70" s="3">
-        <v>-0.43529043335779305</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1.11</v>
-      </c>
-      <c r="H70" s="3">
-        <v>31.64</v>
-      </c>
-      <c r="I70" s="3">
-        <v>-32.43</v>
-      </c>
-      <c r="J70" s="3">
-        <v>-0.036819047674802624</v>
-      </c>
-      <c r="K70" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>-65</v>
-      </c>
-      <c r="M70" s="3">
-        <v>-0.4236296272543574</v>
-      </c>
-      <c r="N70" s="3">
-        <v>-30.687229904130596</v>
-      </c>
-      <c r="O70" s="3">
-        <v>1.2658227848101267</v>
-      </c>
-      <c r="P70" s="3">
-        <v>37.53319428279413</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>35.822784810126585</v>
-      </c>
-      <c r="R70" s="3">
-        <v>21.835443037974688</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T70" s="3">
+      <c r="D70" s="1">
+        <v>13.157894736842104</v>
+      </c>
+      <c r="E70" s="1">
+        <v>-1.41</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-0.298883002805443</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H70" s="1">
+        <v>51.57</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-24.36</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.01312031494827248</v>
+      </c>
+      <c r="K70" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>-98</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.28793042747850195</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-16.765467420909165</v>
+      </c>
+      <c r="O70" s="1">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="P70" s="1">
+        <v>36.16826599829714</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>44.68354430379746</v>
+      </c>
+      <c r="R70" s="1">
+        <v>25.822784810126585</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T70" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6411,58 +6408,58 @@
         <v>5.18</v>
       </c>
       <c r="C71" s="3">
-        <v>60.75949367088608</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="D71" s="3">
-        <v>0.7837837837837839</v>
+        <v>0.7702702702702704</v>
       </c>
       <c r="E71" s="3">
-        <v>0.16</v>
+        <v>-0.08</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.2817255110945516</v>
+        <v>-0.0715211144046819</v>
       </c>
       <c r="G71" s="3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3">
-        <v>50.24</v>
+        <v>66.12</v>
       </c>
       <c r="I71" s="3">
-        <v>-7.12</v>
+        <v>0.47</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.011991913113487167</v>
+        <v>0.008550348786368199</v>
       </c>
       <c r="K71" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="3">
-        <v>-20</v>
+        <v>-68</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.28066543781242104</v>
+        <v>-0.0715211144046819</v>
       </c>
       <c r="N71" s="3">
-        <v>-16.39081095993696</v>
+        <v>4.8754638864728355</v>
       </c>
       <c r="O71" s="3">
-        <v>11.39240506329114</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P71" s="3">
         <v>19.13407224404345</v>
       </c>
       <c r="Q71" s="3">
-        <v>40.126582278481</v>
+        <v>54.0506329113924</v>
       </c>
       <c r="R71" s="3">
-        <v>26.202531645569618</v>
+        <v>42.21518987341773</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T71" s="3">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6473,52 +6470,52 @@
         <v>10.42</v>
       </c>
       <c r="C72" s="3">
-        <v>78.48101265822784</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="D72" s="3">
-        <v>0.21305182341650677</v>
+        <v>0.19865642994241844</v>
       </c>
       <c r="E72" s="3">
-        <v>-1.31</v>
+        <v>-1.66</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.30054631759780803</v>
+        <v>-0.1389836947724572</v>
       </c>
       <c r="G72" s="3">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="H72" s="3">
-        <v>39.88</v>
+        <v>56.15</v>
       </c>
       <c r="I72" s="3">
-        <v>-9.12</v>
+        <v>-5.48</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.013340396526671216</v>
+        <v>-0.00307224751560727</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L72" s="3">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.28570529164798086</v>
+        <v>-0.12803111944551615</v>
       </c>
       <c r="N72" s="3">
-        <v>-16.894796343492946</v>
+        <v>-0.7755366176105838</v>
       </c>
       <c r="O72" s="3">
-        <v>10.126582278481013</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P72" s="3">
-        <v>18.537307083411516</v>
+        <v>21.36339366602189</v>
       </c>
       <c r="Q72" s="3">
-        <v>39.24050632911392</v>
+        <v>46.962025316455694</v>
       </c>
       <c r="R72" s="3">
-        <v>27.468354430379748</v>
+        <v>36.07594936708861</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
@@ -6529,58 +6526,58 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B73" s="2">
         <v>0.61</v>
       </c>
       <c r="C73" s="2">
-        <v>36.708860759493675</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="D73" s="2">
-        <v>22.40983606557377</v>
+        <v>20.37704918032787</v>
       </c>
       <c r="E73" s="2">
-        <v>0.1</v>
+        <v>2.89</v>
       </c>
       <c r="F73" s="2">
-        <v>0.2318061407146457</v>
+        <v>0.37784003175339287</v>
       </c>
       <c r="G73" s="2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="H73" s="2">
-        <v>61.8</v>
+        <v>62.3</v>
       </c>
       <c r="I73" s="2">
-        <v>41.61</v>
+        <v>52.02</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03293282383472466</v>
+        <v>0.031672006329449394</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M73" s="2">
-        <v>0.24982738651086445</v>
+        <v>0.39426889474380444</v>
       </c>
       <c r="N73" s="2">
-        <v>36.658471472391575</v>
+        <v>51.454464801321485</v>
       </c>
       <c r="O73" s="2">
-        <v>83.54430379746836</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>65.56962025316456</v>
+        <v>66.32911392405063</v>
       </c>
       <c r="R73" s="2">
-        <v>61.0126582278481</v>
+        <v>60.94936708860761</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
@@ -6591,7 +6588,7 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B74" s="2">
         <v>0.96</v>
@@ -6600,179 +6597,179 @@
         <v>39.24050632911392</v>
       </c>
       <c r="D74" s="2">
-        <v>14.25</v>
+        <v>12.072916666666668</v>
       </c>
       <c r="E74" s="2">
-        <v>2.01</v>
+        <v>0.98</v>
       </c>
       <c r="F74" s="2">
-        <v>0.171837599993916</v>
+        <v>0.07530110050645825</v>
       </c>
       <c r="G74" s="2">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="H74" s="2">
-        <v>83.02</v>
+        <v>71.42</v>
       </c>
       <c r="I74" s="2">
-        <v>32.23</v>
+        <v>26.74</v>
       </c>
       <c r="J74" s="2">
-        <v>0.021742148422753137</v>
+        <v>0.015780199617998404</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.1495760610691752</v>
+        <v>0.051205434787187976</v>
       </c>
       <c r="N74" s="2">
-        <v>26.633338928222656</v>
+        <v>17.14811880565982</v>
       </c>
       <c r="O74" s="2">
-        <v>72.15189873417721</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>65.0632911392405</v>
+        <v>63.41772151898734</v>
       </c>
       <c r="R74" s="2">
-        <v>56.32911392405063</v>
+        <v>53.41772151898735</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="T74" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="3">
         <v>0.44</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="3">
         <v>34.177215189873415</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="3">
         <v>29.204545454545453</v>
       </c>
-      <c r="E75" s="1">
-        <v>-0.71</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0.0822037529066603</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.96</v>
-      </c>
-      <c r="H75" s="1">
-        <v>60.47</v>
-      </c>
-      <c r="I75" s="1">
-        <v>14.82</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0.00564206762993544</v>
-      </c>
-      <c r="K75" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="1">
-        <v>6</v>
-      </c>
-      <c r="M75" s="1">
-        <v>0.07796345977813823</v>
-      </c>
-      <c r="N75" s="1">
-        <v>19.47207879911897</v>
-      </c>
-      <c r="O75" s="1">
-        <v>65.82278481012658</v>
-      </c>
-      <c r="P75" s="1">
-        <v>37.05001195108517</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>58.10126582278481</v>
-      </c>
-      <c r="R75" s="1">
-        <v>46.45569620253164</v>
-      </c>
-      <c r="S75" s="1" t="s">
+      <c r="E75" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="F75" s="3">
+        <v>-0.0194711889625461</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="H75" s="3">
+        <v>34.3</v>
+      </c>
+      <c r="I75" s="3">
+        <v>-2.05</v>
+      </c>
+      <c r="J75" s="3">
+        <v>0.014421107548793829</v>
+      </c>
+      <c r="K75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" s="3">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3">
+        <v>-0.020566446495240198</v>
+      </c>
+      <c r="N75" s="3">
+        <v>9.970930677417016</v>
+      </c>
+      <c r="O75" s="3">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="P75" s="3">
+        <v>36.964149129985884</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>52.40506329113924</v>
+      </c>
+      <c r="R75" s="3">
+        <v>43.67088607594937</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T75" s="1">
+      <c r="T75" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="3">
         <v>2.05</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="3">
         <v>48.10126582278481</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="3">
         <v>0.7170731707317075</v>
       </c>
-      <c r="E76" s="1">
-        <v>2.63</v>
-      </c>
-      <c r="F76" s="1">
-        <v>0.036085675669937756</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="H76" s="1">
-        <v>58.72</v>
-      </c>
-      <c r="I76" s="1">
-        <v>18.77</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0.018217078308452244</v>
-      </c>
-      <c r="K76" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="1">
-        <v>6</v>
-      </c>
-      <c r="M76" s="1">
-        <v>0.006403623770283362</v>
-      </c>
-      <c r="N76" s="1">
-        <v>12.316095198333482</v>
-      </c>
-      <c r="O76" s="1">
-        <v>58.22784810126582</v>
-      </c>
-      <c r="P76" s="1">
-        <v>17.05597509098574</v>
-      </c>
-      <c r="Q76" s="1">
-        <v>50.253164556962034</v>
-      </c>
-      <c r="R76" s="1">
-        <v>42.21518987341772</v>
-      </c>
-      <c r="S76" s="1" t="s">
+      <c r="E76" s="3">
+        <v>-0.21</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0.15929428610072854</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="H76" s="3">
+        <v>67.38</v>
+      </c>
+      <c r="I76" s="3">
+        <v>17.8</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.012413742307556805</v>
+      </c>
+      <c r="K76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
+        <v>0.12205552998912905</v>
+      </c>
+      <c r="N76" s="3">
+        <v>24.233128325853944</v>
+      </c>
+      <c r="O76" s="3">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P76" s="3">
+        <v>16.982798273104898</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>53.16455696202532</v>
+      </c>
+      <c r="R76" s="3">
+        <v>48.60759493670886</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T76" s="1">
-        <v>0.76</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6789,46 +6786,46 @@
         <v>281.33333333333337</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.34</v>
+        <v>2.11</v>
       </c>
       <c r="F77" s="2">
-        <v>0.01240752414840536</v>
+        <v>0.1965352731107456</v>
       </c>
       <c r="G77" s="2">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="H77" s="2">
-        <v>66.79</v>
+        <v>75.62</v>
       </c>
       <c r="I77" s="2">
-        <v>11.55</v>
+        <v>23.47</v>
       </c>
       <c r="J77" s="2">
-        <v>0.008247007365014443</v>
+        <v>0.025525618178329417</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L77" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M77" s="2">
-        <v>0.01028737758414433</v>
+        <v>0.1921542429799692</v>
       </c>
       <c r="N77" s="2">
-        <v>12.70447057971958</v>
+        <v>31.24299962493795</v>
       </c>
       <c r="O77" s="2">
-        <v>59.49367088607595</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>62.91139240506329</v>
+        <v>70.37974683544304</v>
       </c>
       <c r="R77" s="2">
-        <v>54.43037974683545</v>
+        <v>63.0379746835443</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
@@ -6838,64 +6835,64 @@
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="3">
         <v>13.11</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="3">
         <v>84.81012658227847</v>
       </c>
-      <c r="D78" s="1">
-        <v>-0.6414950419527079</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.57</v>
-      </c>
-      <c r="F78" s="1">
-        <v>0.13799643285872165</v>
-      </c>
-      <c r="G78" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="H78" s="1">
-        <v>74.84</v>
-      </c>
-      <c r="I78" s="1">
-        <v>37.38</v>
-      </c>
-      <c r="J78" s="1">
-        <v>0.02693996293552387</v>
-      </c>
-      <c r="K78" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" s="1">
-        <v>144</v>
-      </c>
-      <c r="M78" s="1">
-        <v>0.16555833819411503</v>
-      </c>
-      <c r="N78" s="1">
-        <v>28.23156664071665</v>
-      </c>
-      <c r="O78" s="1">
-        <v>73.41772151898735</v>
-      </c>
-      <c r="P78" s="1">
+      <c r="D78" s="3">
+        <v>-0.7337909992372235</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.041522766450808546</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="H78" s="3">
+        <v>43.44</v>
+      </c>
+      <c r="I78" s="3">
+        <v>16.47</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0.021720040522551956</v>
+      </c>
+      <c r="K78" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="3">
+        <v>59</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0.06780894723546704</v>
+      </c>
+      <c r="N78" s="3">
+        <v>18.80847005048773</v>
+      </c>
+      <c r="O78" s="3">
+        <v>70.88607594936708</v>
+      </c>
+      <c r="P78" s="3">
         <v>20.806025084936465</v>
       </c>
-      <c r="Q78" s="1">
-        <v>60.50632911392405</v>
-      </c>
-      <c r="R78" s="1">
-        <v>49.683544303797476</v>
-      </c>
-      <c r="S78" s="1" t="s">
+      <c r="Q78" s="3">
+        <v>54.177215189873415</v>
+      </c>
+      <c r="R78" s="3">
+        <v>49.620253164556964</v>
+      </c>
+      <c r="S78" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T78" s="1">
+      <c r="T78" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6910,55 +6907,55 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="2">
-        <v>2.4527687296416936</v>
+        <v>2.872964169381108</v>
       </c>
       <c r="E79" s="2">
-        <v>0.82</v>
+        <v>-0.31</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4238631562787893</v>
+        <v>0.42574742614164673</v>
       </c>
       <c r="G79" s="2">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2">
-        <v>87.31</v>
+        <v>59.03</v>
       </c>
       <c r="I79" s="2">
-        <v>50.65</v>
+        <v>48.34</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0276716970655234</v>
+        <v>0.04329447329972292</v>
       </c>
       <c r="K79" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="M79" s="2">
-        <v>0.4164426433038757</v>
+        <v>0.42574742614164673</v>
       </c>
       <c r="N79" s="2">
-        <v>53.31999715169271</v>
+        <v>54.60231794110572</v>
       </c>
       <c r="O79" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>64.55696202531645</v>
+        <v>63.03797468354429</v>
       </c>
       <c r="R79" s="2">
-        <v>58.037974683544306</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6966,61 +6963,61 @@
         <v>127</v>
       </c>
       <c r="B80" s="2">
-        <v>8.72</v>
+        <v>12.58</v>
       </c>
       <c r="C80" s="2">
-        <v>75.9493670886076</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8119266055045871</v>
+        <v>0.6033386327503976</v>
       </c>
       <c r="E80" s="2">
-        <v>5.52</v>
+        <v>-2.26</v>
       </c>
       <c r="F80" s="2">
-        <v>1.0587470216818125</v>
+        <v>1.4536327400417541</v>
       </c>
       <c r="G80" s="2">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="H80" s="2">
-        <v>66.13</v>
+        <v>64.53</v>
       </c>
       <c r="I80" s="2">
-        <v>67.76</v>
+        <v>135.53</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0584419134804722</v>
+        <v>0.09044197812161316</v>
       </c>
       <c r="K80" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>1.0598070949639429</v>
+        <v>1.4886809810879655</v>
       </c>
       <c r="N80" s="2">
-        <v>117.65644231769943</v>
+        <v>160.89567343573756</v>
       </c>
       <c r="O80" s="2">
         <v>96.20253164556962</v>
       </c>
       <c r="P80" s="2">
-        <v>16.957009573963198</v>
+        <v>20.630527651660007</v>
       </c>
       <c r="Q80" s="2">
-        <v>68.60759493670886</v>
+        <v>72.27848101265823</v>
       </c>
       <c r="R80" s="2">
-        <v>64.24050632911393</v>
+        <v>64.30379746835445</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7039,7 +7036,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7047,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32.84810126582278</v>
+        <v>25.379746835443036</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7055,7 +7052,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>64.9367088607595</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7063,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>14.810126582278478</v>
+        <v>43.607594936708864</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7071,7 +7068,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>45.31645569620254</v>
+        <v>45.25316455696203</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7079,7 +7076,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42.08860759493671</v>
+        <v>24.493670886075954</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7087,7 +7084,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.55696202531646</v>
+        <v>53.67088607594937</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7095,7 +7092,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.316455696202524</v>
+        <v>54.43037974683544</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7103,7 +7100,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41.202531645569614</v>
+        <v>31.708860759493664</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7111,7 +7108,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.79746835443038</v>
+        <v>38.291139240506325</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7119,7 +7116,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>46.455696202531655</v>
+        <v>41.139240506329116</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7127,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>20.696202531645564</v>
+        <v>49.36708860759494</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7135,7 +7132,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>15.88607594936709</v>
+        <v>0.6329113924050613</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7143,7 +7140,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>35.189873417721515</v>
+        <v>51.89873417721519</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7151,7 +7148,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>61.962025316455694</v>
+        <v>61.139240506329116</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7159,7 +7156,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36.64556962025316</v>
+        <v>26.518987341772156</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7167,7 +7164,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>23.164556962025316</v>
+        <v>25.443037974683545</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7175,7 +7172,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>30.949367088607595</v>
+        <v>47.34177215189874</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7183,7 +7180,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>40.8860759493671</v>
+        <v>45.31645569620254</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7191,7 +7188,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.405063291139236</v>
+        <v>40.88607594936709</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7199,7 +7196,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>38.79746835443038</v>
+        <v>52.025316455696206</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7207,7 +7204,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.253164556962027</v>
+        <v>47.53164556962025</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7215,7 +7212,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>31.962025316455694</v>
+        <v>31.51898734177215</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7223,7 +7220,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>31.0126582278481</v>
+        <v>3.227848101265824</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7231,7 +7228,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11.962025316455694</v>
+        <v>-0.37974683544303645</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7239,7 +7236,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33.037974683544306</v>
+        <v>33.73417721518988</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7247,7 +7244,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>26.392405063291136</v>
+        <v>19.87341772151899</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7255,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21.898734177215193</v>
+        <v>17.65822784810127</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7263,7 +7260,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>24.36708860759493</v>
+        <v>34.0506329113924</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7271,7 +7268,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>47.53164556962025</v>
+        <v>51.83544303797468</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7279,7 +7276,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>60.822784810126585</v>
+        <v>56.58227848101266</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7287,7 +7284,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>29.36708860759494</v>
+        <v>34.936708860759495</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7295,7 +7292,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>39.9367088607595</v>
+        <v>37.911392405063296</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7303,7 +7300,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>51.139240506329116</v>
+        <v>50.063291139240505</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7311,7 +7308,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>21.582278481012658</v>
+        <v>24.62025316455696</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7319,7 +7316,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>34.30379746835443</v>
+        <v>25.253164556962023</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7327,7 +7324,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>38.797468354430386</v>
+        <v>25.316455696202535</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7335,7 +7332,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>53.92405063291139</v>
+        <v>57.53164556962025</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7343,7 +7340,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>53.41772151898734</v>
+        <v>30.316455696202535</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7351,7 +7348,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>40.75949367088608</v>
+        <v>9.93670886075949</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7359,7 +7356,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>30.063291139240505</v>
+        <v>38.48101265822785</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7367,7 +7364,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.54430379746835</v>
+        <v>34.87341772151899</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7375,7 +7372,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>42.151898734177216</v>
+        <v>43.924050632911396</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7383,7 +7380,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>26.518987341772146</v>
+        <v>30.949367088607595</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7391,7 +7388,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>56.962025316455694</v>
+        <v>50.75949367088607</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7399,7 +7396,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>31.39240506329114</v>
+        <v>21.962025316455694</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7407,7 +7404,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.759493670886073</v>
+        <v>26.139240506329113</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7415,7 +7412,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>63.037974683544306</v>
+        <v>50.506329113924046</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7423,7 +7420,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>63.544303797468345</v>
+        <v>60.25316455696203</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7431,7 +7428,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>21.77215189873418</v>
+        <v>22.531645569620252</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7439,7 +7436,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>26.64556962025317</v>
+        <v>36.39240506329114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7447,7 +7444,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>56.77215189873419</v>
+        <v>61.70886075949366</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7455,7 +7452,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>35.12658227848102</v>
+        <v>30.189873417721515</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7463,7 +7460,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>52.65822784810126</v>
+        <v>52.21518987341773</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7471,7 +7468,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>36.582278481012665</v>
+        <v>51.51898734177216</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7479,7 +7476,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>33.98734177215189</v>
+        <v>38.54430379746835</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7487,7 +7484,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>67.34177215189874</v>
+        <v>67.27848101265823</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7495,7 +7492,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>55.31645569620253</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7503,7 +7500,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>56.582278481012665</v>
+        <v>45.949367088607595</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7511,7 +7508,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>28.79746835443038</v>
+        <v>28.101265822784814</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7519,7 +7516,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>42.848101265822784</v>
+        <v>43.22784810126582</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7527,7 +7524,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>72.34177215189874</v>
+        <v>72.59493670886076</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7535,7 +7532,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>66.96202531645571</v>
+        <v>68.54430379746836</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7543,7 +7540,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>37.40506329113924</v>
+        <v>38.41772151898734</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7551,7 +7548,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>29.050632911392405</v>
+        <v>16.89873417721519</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7559,7 +7556,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>44.11392405063291</v>
+        <v>37.911392405063296</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7567,7 +7564,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>44.936708860759495</v>
+        <v>44.683544303797476</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7575,7 +7572,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>27.72151898734177</v>
+        <v>28.797468354430375</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7583,7 +7580,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.72151898734177</v>
+        <v>35.822784810126585</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7591,7 +7588,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>21.835443037974688</v>
+        <v>25.822784810126585</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7599,7 +7596,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>26.202531645569618</v>
+        <v>42.21518987341773</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7607,23 +7604,23 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>27.468354430379748</v>
+        <v>36.07594936708861</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B73">
-        <v>61.0126582278481</v>
+        <v>60.94936708860761</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B74">
-        <v>56.32911392405063</v>
+        <v>53.41772151898735</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7631,7 +7628,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>46.45569620253164</v>
+        <v>43.67088607594937</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7639,7 +7636,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>42.21518987341772</v>
+        <v>48.60759493670886</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7647,7 +7644,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>54.43037974683545</v>
+        <v>63.0379746835443</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7655,7 +7652,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>49.683544303797476</v>
+        <v>49.620253164556964</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7663,7 +7660,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>58.037974683544306</v>
+        <v>58.9873417721519</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7671,7 +7668,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>64.24050632911393</v>
+        <v>64.30379746835445</v>
       </c>
     </row>
   </sheetData>
@@ -7690,32 +7687,32 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7723,10 +7720,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7734,10 +7731,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7745,82 +7742,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -7839,114 +7836,114 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7965,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7976,10 +7973,10 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7987,10 +7984,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7998,90 +7995,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -8100,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8111,114 +8108,114 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -8234,212 +8231,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" t="s">
         <v>183</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" t="s">
         <v>193</v>
-      </c>
-      <c r="D6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" t="s">
         <v>200</v>
       </c>
-      <c r="C9" t="s">
-        <v>198</v>
-      </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="222">
   <si>
     <t>Ticker</t>
   </si>
@@ -382,19 +382,19 @@
     <t>2026-06-30</t>
   </si>
   <si>
-    <t>ATEN</t>
+    <t>CTS</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>VCEL</t>
   </si>
   <si>
     <t>WSR</t>
   </si>
   <si>
-    <t>OMCL</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>SHO</t>
+    <t>JPM</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-06-14</t>
+    <t>2026-06-16</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -421,9 +421,6 @@
     <t>Last Run</t>
   </si>
   <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
@@ -499,7 +496,7 @@
     <t>Results</t>
   </si>
   <si>
-    <t>5 of 5 qualified</t>
+    <t>4 of 4 qualified</t>
   </si>
   <si>
     <t>Dow Jones 30</t>
@@ -517,24 +514,24 @@
     <t>All sectors</t>
   </si>
   <si>
+    <t>1 of 1 qualified</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>0 of 0 qualified</t>
   </si>
   <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>3 of 3 qualified</t>
-  </si>
-  <si>
     <t>S&amp;P 500 (large-cap subset)</t>
   </si>
   <si>
@@ -547,9 +544,6 @@
     <t>&lt; 40</t>
   </si>
   <si>
-    <t>1 of 1 qualified</t>
-  </si>
-  <si>
     <t>Component</t>
   </si>
   <si>
@@ -676,28 +670,22 @@
     <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1352,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1363,10 +1351,10 @@
         <v>61</v>
       </c>
       <c r="B2">
-        <v>72.59493670886076</v>
+        <v>72.91139240506328</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1374,10 +1362,10 @@
         <v>62</v>
       </c>
       <c r="B3">
-        <v>68.54430379746836</v>
+        <v>68.35443037974684</v>
       </c>
       <c r="C3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1385,10 +1373,10 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <v>67.27848101265823</v>
+        <v>67.53164556962025</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1396,10 +1384,10 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>65</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="C5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1407,109 +1395,109 @@
         <v>127</v>
       </c>
       <c r="B6">
-        <v>64.30379746835445</v>
+        <v>64.74683544303798</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B7">
-        <v>63.0379746835443</v>
+        <v>61.77215189873418</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8">
-        <v>61.70886075949366</v>
+        <v>61.01265822784809</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="B9">
-        <v>61.139240506329116</v>
+        <v>60.9493670886076</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>60.94936708860761</v>
+        <v>60.50632911392406</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="B11">
-        <v>60.25316455696203</v>
+        <v>58.10126582278481</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="B12">
-        <v>60</v>
+        <v>57.72151898734177</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="B13">
-        <v>58.9873417721519</v>
+        <v>57.658227848101255</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>57.53164556962025</v>
+        <v>56.20253164556962</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B15">
-        <v>56.58227848101266</v>
+        <v>54.620253164556964</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1517,76 +1505,76 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>54.43037974683544</v>
+        <v>53.92405063291139</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="B17">
-        <v>53.67088607594937</v>
+        <v>53.417721518987335</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="B18">
-        <v>53.41772151898735</v>
+        <v>52.848101265822784</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>52.21518987341773</v>
+        <v>51.962025316455694</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>52.025316455696206</v>
+        <v>51.8354430379747</v>
       </c>
       <c r="C20" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B21">
-        <v>51.89873417721519</v>
+        <v>51.835443037974684</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="B22">
-        <v>51.83544303797468</v>
+        <v>51.77215189873418</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1594,21 +1582,21 @@
         <v>44</v>
       </c>
       <c r="B23">
-        <v>50.75949367088607</v>
+        <v>51.64556962025317</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B24">
-        <v>50.506329113924046</v>
+        <v>51.455696202531655</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1616,43 +1604,43 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>50.063291139240505</v>
+        <v>50.82278481012659</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B26">
-        <v>49.620253164556964</v>
+        <v>50.31645569620253</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="B27">
-        <v>49.36708860759494</v>
+        <v>49.93670886075949</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>48.60759493670886</v>
+        <v>49.74683544303798</v>
       </c>
       <c r="C28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1660,21 +1648,21 @@
         <v>21</v>
       </c>
       <c r="B29">
-        <v>47.53164556962025</v>
+        <v>49.43037974683545</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="B30">
-        <v>47.34177215189874</v>
+        <v>49.24050632911393</v>
       </c>
       <c r="C30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1682,54 +1670,54 @@
         <v>58</v>
       </c>
       <c r="B31">
-        <v>45.949367088607595</v>
+        <v>48.9873417721519</v>
       </c>
       <c r="C31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B32">
-        <v>45.31645569620254</v>
+        <v>48.60759493670886</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B33">
-        <v>44.683544303797476</v>
+        <v>46.20253164556962</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B34">
-        <v>43.924050632911396</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>43.67088607594937</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1737,142 +1725,142 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>43.607594936708864</v>
+        <v>44.49367088607595</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B37">
-        <v>43.22784810126582</v>
+        <v>43.54430379746835</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="B38">
-        <v>42.21518987341773</v>
+        <v>42.65822784810127</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B39">
-        <v>41.139240506329116</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>40.88607594936709</v>
+        <v>39.936708860759495</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B41">
-        <v>38.54430379746835</v>
+        <v>38.924050632911396</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B42">
-        <v>38.48101265822785</v>
+        <v>38.924050632911396</v>
       </c>
       <c r="C42" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B43">
-        <v>38.41772151898734</v>
+        <v>37.151898734177216</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B44">
-        <v>37.911392405063296</v>
+        <v>36.39240506329114</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B45">
-        <v>36.39240506329114</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B46">
-        <v>36.07594936708861</v>
+        <v>35.88607594936709</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>34.936708860759495</v>
+        <v>34.17721518987342</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B48">
-        <v>34.87341772151899</v>
+        <v>33.417721518987335</v>
       </c>
       <c r="C48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1880,32 +1868,32 @@
         <v>25</v>
       </c>
       <c r="B49">
-        <v>33.73417721518988</v>
+        <v>32.84810126582279</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B50">
-        <v>31.51898734177215</v>
+        <v>30.696202531645575</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B51">
-        <v>28.101265822784814</v>
+        <v>30.18987341772152</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2130,28 +2118,28 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>62.0253164556962</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8853288364249579</v>
+        <v>-1.8870151770657673</v>
       </c>
       <c r="E2" s="1">
         <v>0.38</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.08553141804598512</v>
+        <v>-0.1282834138276514</v>
       </c>
       <c r="G2" s="1">
         <v>0.15</v>
       </c>
       <c r="H2" s="1">
-        <v>43.27</v>
+        <v>35.8</v>
       </c>
       <c r="I2" s="1">
-        <v>9.72</v>
+        <v>5.02</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.012152836818527623</v>
+        <v>-0.01288850034517013</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -2160,28 +2148,28 @@
         <v>295</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.1786283083249839</v>
+        <v>-0.2284684543869019</v>
       </c>
       <c r="N2" s="1">
-        <v>-5.835255505557358</v>
+        <v>-9.985370078778365</v>
       </c>
       <c r="O2" s="1">
-        <v>29.11392405063291</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P2" s="1">
-        <v>15.687871758897787</v>
+        <v>17.46078161093016</v>
       </c>
       <c r="Q2" s="1">
-        <v>32.53164556962025</v>
+        <v>27.341772151898734</v>
       </c>
       <c r="R2" s="1">
-        <v>25.379746835443036</v>
+        <v>22.59493670886076</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>0</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2192,28 +2180,28 @@
         <v>3.05</v>
       </c>
       <c r="C3" s="2">
-        <v>49.36708860759494</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="D3" s="2">
-        <v>24.422950819672135</v>
+        <v>24.462295081967213</v>
       </c>
       <c r="E3" s="2">
         <v>-0.89</v>
       </c>
       <c r="F3" s="2">
-        <v>1.3618073050886133</v>
+        <v>1.4316503850391937</v>
       </c>
       <c r="G3" s="2">
         <v>2.49</v>
       </c>
       <c r="H3" s="2">
-        <v>60.45</v>
+        <v>63.5</v>
       </c>
       <c r="I3" s="2">
-        <v>101.46</v>
+        <v>109.46</v>
       </c>
       <c r="J3" s="2">
-        <v>0.0782117922997919</v>
+        <v>0.07883451212176729</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -2222,28 +2210,28 @@
         <v>108</v>
       </c>
       <c r="M3" s="2">
-        <v>1.5250006774600346</v>
+        <v>1.6072688679018798</v>
       </c>
       <c r="N3" s="2">
-        <v>164.5276430729445</v>
+        <v>173.5883621500998</v>
       </c>
       <c r="O3" s="2">
-        <v>97.46835443037975</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>74.05063291139241</v>
+        <v>74.17721518987342</v>
       </c>
       <c r="R3" s="2">
-        <v>65</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2263,19 +2251,19 @@
         <v>-1.7</v>
       </c>
       <c r="F4" s="3">
-        <v>0.1432166928258231</v>
+        <v>0.1939023829473215</v>
       </c>
       <c r="G4" s="3">
         <v>1.36</v>
       </c>
       <c r="H4" s="3">
-        <v>61.67</v>
+        <v>65.77</v>
       </c>
       <c r="I4" s="3">
-        <v>13.25</v>
+        <v>18.97</v>
       </c>
       <c r="J4" s="3">
-        <v>0.0511211768659595</v>
+        <v>0.0516523291617338</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
@@ -2284,28 +2272,28 @@
         <v>-92</v>
       </c>
       <c r="M4" s="3">
-        <v>0.18264596400281086</v>
+        <v>0.2363336942430041</v>
       </c>
       <c r="N4" s="3">
-        <v>30.292171727222122</v>
+        <v>36.49484478421224</v>
       </c>
       <c r="O4" s="3">
-        <v>79.74683544303798</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P4" s="3">
         <v>43.93055527298539</v>
       </c>
       <c r="Q4" s="3">
-        <v>56.20253164556962</v>
+        <v>57.84810126582278</v>
       </c>
       <c r="R4" s="3">
-        <v>43.607594936708864</v>
+        <v>44.49367088607595</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2316,40 +2304,40 @@
         <v>1.09</v>
       </c>
       <c r="C5" s="3">
-        <v>43.037974683544306</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="D5" s="3">
-        <v>25.027522935779817</v>
+        <v>24.95412844036697</v>
       </c>
       <c r="E5" s="3">
         <v>-0.83</v>
       </c>
       <c r="F5" s="3">
-        <v>-0.17006017171642437</v>
+        <v>-0.19742365337380705</v>
       </c>
       <c r="G5" s="3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="3">
-        <v>48.89</v>
+        <v>50.01</v>
       </c>
       <c r="I5" s="3">
-        <v>-2.23</v>
+        <v>-1.6</v>
       </c>
       <c r="J5" s="3">
-        <v>0.007618231687685116</v>
+        <v>0.008018677495598092</v>
       </c>
       <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>-82</v>
+        <v>-81</v>
       </c>
       <c r="M5" s="3">
-        <v>-0.08134431156820199</v>
+        <v>-0.10313185049451246</v>
       </c>
       <c r="N5" s="3">
-        <v>3.893144170120827</v>
+        <v>2.5482903104605796</v>
       </c>
       <c r="O5" s="3">
         <v>46.835443037974684</v>
@@ -2358,16 +2346,16 @@
         <v>23.613581273496347</v>
       </c>
       <c r="Q5" s="3">
-        <v>56.07594936708862</v>
+        <v>54.177215189873415</v>
       </c>
       <c r="R5" s="3">
-        <v>45.25316455696203</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="3">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2378,7 +2366,7 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>51.89873417721519</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="D6" s="1">
         <v>1.4563106796116505</v>
@@ -2387,49 +2375,49 @@
         <v>0.45</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.3321050615919351</v>
+        <v>-0.3519389498282134</v>
       </c>
       <c r="G6" s="1">
         <v>1.5</v>
       </c>
       <c r="H6" s="1">
-        <v>29.04</v>
+        <v>32.11</v>
       </c>
       <c r="I6" s="1">
-        <v>-19.02</v>
+        <v>-18.85</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.013842094592377854</v>
+        <v>-0.015708665955982654</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.27734218495722995</v>
+        <v>-0.2930065730286543</v>
       </c>
       <c r="N6" s="1">
-        <v>-15.706643168781968</v>
+        <v>-16.439181942953603</v>
       </c>
       <c r="O6" s="1">
-        <v>15.18987341772152</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P6" s="1">
-        <v>25.4661882776573</v>
+        <v>26.199187712619203</v>
       </c>
       <c r="Q6" s="1">
-        <v>32.53164556962025</v>
+        <v>31.392405063291136</v>
       </c>
       <c r="R6" s="1">
-        <v>24.493670886075954</v>
+        <v>22.27848101265823</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>0</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2440,7 +2428,7 @@
         <v>6.53</v>
       </c>
       <c r="C7" s="2">
-        <v>68.35443037974683</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="D7" s="2">
         <v>5.099540581929555</v>
@@ -2449,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.11334325945951962</v>
+        <v>-0.12683662275628715</v>
       </c>
       <c r="G7" s="2">
         <v>2.2</v>
       </c>
       <c r="H7" s="2">
-        <v>45.24</v>
+        <v>48.33</v>
       </c>
       <c r="I7" s="2">
-        <v>8.42</v>
+        <v>10.1</v>
       </c>
       <c r="J7" s="2">
-        <v>0.01702949611879757</v>
+        <v>0.016445065589507906</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2470,28 +2458,28 @@
         <v>107</v>
       </c>
       <c r="M7" s="2">
-        <v>0.018087644463772756</v>
+        <v>0.014601081562654716</v>
       </c>
       <c r="N7" s="2">
-        <v>13.836339773318308</v>
+        <v>14.321583516177297</v>
       </c>
       <c r="O7" s="2">
-        <v>60.75949367088608</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>60.25316455696203</v>
+        <v>58.35443037974684</v>
       </c>
       <c r="R7" s="2">
-        <v>53.67088607594937</v>
+        <v>52.848101265822784</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2502,7 +2490,7 @@
         <v>13.24</v>
       </c>
       <c r="C8" s="2">
-        <v>86.07594936708861</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="D8" s="2">
         <v>0.03398791540785493</v>
@@ -2511,19 +2499,19 @@
         <v>0.55</v>
       </c>
       <c r="F8" s="2">
-        <v>0.36843904917242454</v>
+        <v>0.34523201580338625</v>
       </c>
       <c r="G8" s="2">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H8" s="2">
-        <v>67.94</v>
+        <v>65.34</v>
       </c>
       <c r="I8" s="2">
-        <v>23.2</v>
+        <v>22.49</v>
       </c>
       <c r="J8" s="2">
-        <v>0.040487285904518604</v>
+        <v>0.03976450120742614</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -2532,10 +2520,10 @@
         <v>-220</v>
       </c>
       <c r="M8" s="2">
-        <v>0.3279145204627427</v>
+        <v>0.3028007045077037</v>
       </c>
       <c r="N8" s="2">
-        <v>44.819027373215306</v>
+        <v>43.14154581068219</v>
       </c>
       <c r="O8" s="2">
         <v>83.54430379746836</v>
@@ -2544,16 +2532,16 @@
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>65.82278481012659</v>
+        <v>65.0632911392405</v>
       </c>
       <c r="R8" s="2">
-        <v>54.43037974683544</v>
+        <v>53.92405063291139</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>0</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2564,28 +2552,28 @@
         <v>0.89</v>
       </c>
       <c r="C9" s="3">
-        <v>37.9746835443038</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="D9" s="3">
-        <v>46.82022471910113</v>
+        <v>46.97752808988764</v>
       </c>
       <c r="E9" s="3">
         <v>-0.19</v>
       </c>
       <c r="F9" s="3">
-        <v>-0.333713517588887</v>
+        <v>-0.34758296974318087</v>
       </c>
       <c r="G9" s="3">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H9" s="3">
-        <v>39.31</v>
+        <v>44.99</v>
       </c>
       <c r="I9" s="3">
-        <v>-20.21</v>
+        <v>-17.13</v>
       </c>
       <c r="J9" s="3">
-        <v>-0.00895957584565531</v>
+        <v>-0.01023936657196911</v>
       </c>
       <c r="K9" s="3" t="b">
         <v>0</v>
@@ -2594,28 +2582,28 @@
         <v>-16</v>
       </c>
       <c r="M9" s="3">
-        <v>-0.2723790957580172</v>
+        <v>-0.2851146503356482</v>
       </c>
       <c r="N9" s="3">
-        <v>-15.210334248860697</v>
+        <v>-15.649989673652998</v>
       </c>
       <c r="O9" s="3">
-        <v>16.455696202531644</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P9" s="3">
-        <v>27.71785589333756</v>
+        <v>24.534202088618652</v>
       </c>
       <c r="Q9" s="3">
-        <v>44.55696202531645</v>
+        <v>42.78481012658228</v>
       </c>
       <c r="R9" s="3">
-        <v>31.708860759493664</v>
+        <v>31.202531645569614</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="3">
-        <v>0.13</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2626,7 +2614,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" s="3">
-        <v>65.82278481012658</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="D10" s="3">
         <v>0.5616</v>
@@ -2635,19 +2623,19 @@
         <v>-2.1</v>
       </c>
       <c r="F10" s="3">
-        <v>-0.15434190880290874</v>
+        <v>-0.15486784145139812</v>
       </c>
       <c r="G10" s="3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H10" s="3">
-        <v>44.51</v>
+        <v>48.34</v>
       </c>
       <c r="I10" s="3">
-        <v>-6.9</v>
+        <v>-5.8</v>
       </c>
       <c r="J10" s="3">
-        <v>0.004467231752215964</v>
+        <v>0.0044391076089213</v>
       </c>
       <c r="K10" s="3" t="b">
         <v>0</v>
@@ -2656,28 +2644,28 @@
         <v>-131</v>
       </c>
       <c r="M10" s="3">
-        <v>-0.11272212256053282</v>
+        <v>-0.10890058754774201</v>
       </c>
       <c r="N10" s="3">
-        <v>0.7553630708877476</v>
+        <v>1.9714166051376307</v>
       </c>
       <c r="O10" s="3">
-        <v>41.77215189873418</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P10" s="3">
-        <v>18.508072317589463</v>
+        <v>18.364103068329413</v>
       </c>
       <c r="Q10" s="3">
-        <v>44.177215189873415</v>
+        <v>43.29113924050633</v>
       </c>
       <c r="R10" s="3">
-        <v>38.291139240506325</v>
+        <v>39.620253164556964</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2697,19 +2685,19 @@
         <v>-1.64</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.08111962352263938</v>
+        <v>-0.06520841556972641</v>
       </c>
       <c r="G11" s="3">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="H11" s="3">
-        <v>39.3</v>
+        <v>45.33</v>
       </c>
       <c r="I11" s="3">
-        <v>-4.71</v>
+        <v>-0.67</v>
       </c>
       <c r="J11" s="3">
-        <v>0.01395318334517921</v>
+        <v>0.011870108523928372</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>0</v>
@@ -2718,28 +2706,28 @@
         <v>25</v>
       </c>
       <c r="M11" s="3">
-        <v>-0.09754848651305092</v>
+        <v>-0.08406677614558533</v>
       </c>
       <c r="N11" s="3">
-        <v>2.272726675635934</v>
+        <v>4.454797745353289</v>
       </c>
       <c r="O11" s="3">
-        <v>45.56962025316456</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P11" s="3">
         <v>21.111699887088218</v>
       </c>
       <c r="Q11" s="3">
-        <v>47.721518987341774</v>
+        <v>48.35443037974684</v>
       </c>
       <c r="R11" s="3">
-        <v>41.139240506329116</v>
+        <v>42.65822784810127</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2759,19 +2747,19 @@
         <v>3.03</v>
       </c>
       <c r="F12" s="3">
-        <v>0.10777865138818392</v>
+        <v>0.10743875008006845</v>
       </c>
       <c r="G12" s="3">
         <v>0.97</v>
       </c>
       <c r="H12" s="3">
-        <v>50.22</v>
+        <v>53.85</v>
       </c>
       <c r="I12" s="3">
-        <v>-20.3</v>
+        <v>-17.24</v>
       </c>
       <c r="J12" s="3">
-        <v>0.033289015557999055</v>
+        <v>0.025719847357969342</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>0</v>
@@ -2780,28 +2768,28 @@
         <v>-53</v>
       </c>
       <c r="M12" s="3">
-        <v>0.1044928787901016</v>
+        <v>0.1039028074720949</v>
       </c>
       <c r="N12" s="3">
-        <v>22.476863205951197</v>
+        <v>23.251756107121306</v>
       </c>
       <c r="O12" s="3">
-        <v>74.68354430379746</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P12" s="3">
         <v>49.122344752707264</v>
       </c>
       <c r="Q12" s="3">
-        <v>58.22784810126583</v>
+        <v>57.72151898734178</v>
       </c>
       <c r="R12" s="3">
-        <v>49.36708860759494</v>
+        <v>49.74683544303798</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2821,19 +2809,19 @@
         <v>6.42</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.3877702428136644</v>
+        <v>-0.3363071117835895</v>
       </c>
       <c r="G13" s="1">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H13" s="1">
-        <v>36.7</v>
+        <v>41.9</v>
       </c>
       <c r="I13" s="1">
-        <v>-23.59</v>
+        <v>-19.58</v>
       </c>
       <c r="J13" s="1">
-        <v>-0.013183592823452281</v>
+        <v>-0.016972204534867124</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>0</v>
@@ -2842,28 +2830,28 @@
         <v>12</v>
       </c>
       <c r="M13" s="1">
-        <v>-0.34395994150590026</v>
+        <v>-0.29033985787993344</v>
       </c>
       <c r="N13" s="1">
-        <v>-22.368418823648987</v>
+        <v>-16.17251042808152</v>
       </c>
       <c r="O13" s="1">
-        <v>5.063291139240507</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P13" s="1">
         <v>48.90109995677025</v>
       </c>
       <c r="Q13" s="1">
-        <v>13.797468354430382</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="R13" s="1">
-        <v>0.6329113924050613</v>
+        <v>2.405063291139239</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="1">
-        <v>0</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2874,7 +2862,7 @@
         <v>1.38</v>
       </c>
       <c r="C14" s="2">
-        <v>44.303797468354425</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="D14" s="2">
         <v>6.768115942028986</v>
@@ -2883,19 +2871,19 @@
         <v>4.42</v>
       </c>
       <c r="F14" s="2">
-        <v>0.370679366253922</v>
+        <v>0.3674846041722752</v>
       </c>
       <c r="G14" s="2">
         <v>0.8</v>
       </c>
       <c r="H14" s="2">
-        <v>60.11</v>
+        <v>61.94</v>
       </c>
       <c r="I14" s="2">
-        <v>34.08</v>
+        <v>36.78</v>
       </c>
       <c r="J14" s="2">
-        <v>0.0472651748130161</v>
+        <v>0.04374237461778499</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2904,28 +2892,28 @@
         <v>13</v>
       </c>
       <c r="M14" s="2">
-        <v>0.34877421560003996</v>
+        <v>0.34391165345245156</v>
       </c>
       <c r="N14" s="2">
-        <v>46.90499688694502</v>
+        <v>47.25264070515698</v>
       </c>
       <c r="O14" s="2">
-        <v>84.81012658227847</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P14" s="2">
-        <v>31.5531883466271</v>
+        <v>31.193963552248132</v>
       </c>
       <c r="Q14" s="2">
-        <v>63.037974683544306</v>
+        <v>62.78481012658229</v>
       </c>
       <c r="R14" s="2">
-        <v>51.89873417721519</v>
+        <v>51.8354430379747</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>0.25</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2945,19 +2933,19 @@
         <v>1.71</v>
       </c>
       <c r="F15" s="2">
-        <v>1.4688497883323033</v>
+        <v>1.4639111024804692</v>
       </c>
       <c r="G15" s="2">
         <v>2.21</v>
       </c>
       <c r="H15" s="2">
-        <v>62.43</v>
+        <v>63.06</v>
       </c>
       <c r="I15" s="2">
-        <v>132.83</v>
+        <v>132.31</v>
       </c>
       <c r="J15" s="2">
-        <v>0.07800167121544431</v>
+        <v>0.07876732814006998</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2966,90 +2954,90 @@
         <v>196</v>
       </c>
       <c r="M15" s="2">
-        <v>1.6013759497882898</v>
+        <v>1.6065274543354022</v>
       </c>
       <c r="N15" s="2">
-        <v>172.16517030577003</v>
+        <v>173.51422079345207</v>
       </c>
       <c r="O15" s="2">
-        <v>98.73417721518987</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P15" s="2">
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>68.22784810126582</v>
+        <v>67.72151898734177</v>
       </c>
       <c r="R15" s="2">
-        <v>61.139240506329116</v>
+        <v>60.50632911392406</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T15" s="2">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>-3.53</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="3">
         <v>7.59493670886076</v>
       </c>
-      <c r="D16" s="1">
-        <v>13.059490084985837</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="3">
+        <v>13.056657223796035</v>
+      </c>
+      <c r="E16" s="3">
         <v>4.79</v>
       </c>
-      <c r="F16" s="1">
-        <v>-0.2610273537516778</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="H16" s="1">
-        <v>41.93</v>
-      </c>
-      <c r="I16" s="1">
-        <v>-9.59</v>
-      </c>
-      <c r="J16" s="1">
-        <v>-0.0004547213608892286</v>
-      </c>
-      <c r="K16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="F16" s="3">
+        <v>-0.20139313471465856</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="H16" s="3">
+        <v>52.46</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.0017289255145024785</v>
+      </c>
+      <c r="K16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
         <v>17</v>
       </c>
-      <c r="M16" s="1">
-        <v>-0.1712162360707613</v>
-      </c>
-      <c r="N16" s="1">
-        <v>-5.094048280135099</v>
-      </c>
-      <c r="O16" s="1">
-        <v>34.177215189873415</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="M16" s="3">
+        <v>-0.10710133183536397</v>
+      </c>
+      <c r="N16" s="3">
+        <v>2.1513421763754206</v>
+      </c>
+      <c r="O16" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
-      <c r="Q16" s="1">
-        <v>36.45569620253165</v>
-      </c>
-      <c r="R16" s="1">
-        <v>26.518987341772156</v>
-      </c>
-      <c r="S16" s="1" t="s">
+      <c r="Q16" s="3">
+        <v>41.64556962025317</v>
+      </c>
+      <c r="R16" s="3">
+        <v>30.696202531645575</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="1">
-        <v>0</v>
+      <c r="T16" s="3">
+        <v>4.18</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3069,19 +3057,19 @@
         <v>0.83</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.17759584973496417</v>
+        <v>-0.17456467862415503</v>
       </c>
       <c r="G17" s="1">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H17" s="1">
-        <v>44.73</v>
+        <v>49.1</v>
       </c>
       <c r="I17" s="1">
-        <v>-10.32</v>
+        <v>-7.12</v>
       </c>
       <c r="J17" s="1">
-        <v>0.00710766206262125</v>
+        <v>0.005609888159402101</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
@@ -3090,28 +3078,28 @@
         <v>25</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.09873730738098874</v>
+        <v>-0.09088070356878108</v>
       </c>
       <c r="N17" s="1">
-        <v>2.1538445888421474</v>
+        <v>3.7734050030337087</v>
       </c>
       <c r="O17" s="1">
-        <v>44.303797468354425</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P17" s="1">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="1">
-        <v>33.41772151898734</v>
+        <v>31.518987341772153</v>
       </c>
       <c r="R17" s="1">
-        <v>25.443037974683545</v>
+        <v>26.265822784810123</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.13</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3131,49 +3119,49 @@
         <v>5.96</v>
       </c>
       <c r="F18" s="3">
-        <v>0.036696473844244015</v>
+        <v>-0.006597780522676594</v>
       </c>
       <c r="G18" s="3">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="H18" s="3">
-        <v>62.11</v>
+        <v>63.22</v>
       </c>
       <c r="I18" s="3">
-        <v>6.1</v>
+        <v>7.36</v>
       </c>
       <c r="J18" s="3">
-        <v>0.010037053654593404</v>
+        <v>0.011857727435715955</v>
       </c>
       <c r="K18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>37</v>
       </c>
       <c r="M18" s="3">
-        <v>0.04217276150771454</v>
+        <v>0.007545989909217621</v>
       </c>
       <c r="N18" s="3">
-        <v>16.24485147771248</v>
+        <v>13.616074350833577</v>
       </c>
       <c r="O18" s="3">
-        <v>63.29113924050633</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P18" s="3">
         <v>44.14111512367286</v>
       </c>
       <c r="Q18" s="3">
-        <v>62.78481012658227</v>
+        <v>63.79746835443037</v>
       </c>
       <c r="R18" s="3">
-        <v>47.34177215189874</v>
+        <v>46.20253164556962</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3184,7 +3172,7 @@
         <v>9.32</v>
       </c>
       <c r="C19" s="3">
-        <v>75.9493670886076</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="D19" s="3">
         <v>0.3015021459227468</v>
@@ -3193,43 +3181,43 @@
         <v>-2.17</v>
       </c>
       <c r="F19" s="3">
-        <v>0.07253092317815768</v>
+        <v>0.04380645788563685</v>
       </c>
       <c r="G19" s="3">
         <v>0.17</v>
       </c>
       <c r="H19" s="3">
-        <v>57.57</v>
+        <v>52.74</v>
       </c>
       <c r="I19" s="3">
-        <v>15.33</v>
+        <v>12.83</v>
       </c>
       <c r="J19" s="3">
-        <v>0.006009652808137184</v>
+        <v>0.007929845431286074</v>
       </c>
       <c r="K19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M19" s="3">
-        <v>-0.018375452035452877</v>
+        <v>-0.054021287601631274</v>
       </c>
       <c r="N19" s="3">
-        <v>10.190030123395736</v>
+        <v>7.459346599748695</v>
       </c>
       <c r="O19" s="3">
-        <v>55.69620253164557</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P19" s="3">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="3">
-        <v>53.41772151898735</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="R19" s="3">
-        <v>45.31645569620254</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>106</v>
@@ -3246,7 +3234,7 @@
         <v>6.07</v>
       </c>
       <c r="C20" s="3">
-        <v>64.55696202531645</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="D20" s="3">
         <v>0.6820428336079079</v>
@@ -3255,19 +3243,19 @@
         <v>5.04</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.042081260853274155</v>
+        <v>-0.019064811472597865</v>
       </c>
       <c r="G20" s="3">
         <v>1.09</v>
       </c>
       <c r="H20" s="3">
-        <v>47.92</v>
+        <v>52.21</v>
       </c>
       <c r="I20" s="3">
-        <v>-2.7</v>
+        <v>-0.54</v>
       </c>
       <c r="J20" s="3">
-        <v>0.006295515639365568</v>
+        <v>0.006136780395040876</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>0</v>
@@ -3276,90 +3264,90 @@
         <v>10</v>
       </c>
       <c r="M20" s="3">
-        <v>-0.032223943059027205</v>
+        <v>-0.008456983648677197</v>
       </c>
       <c r="N20" s="3">
-        <v>8.805181021038317</v>
+        <v>12.015776995044106</v>
       </c>
       <c r="O20" s="3">
-        <v>53.16455696202531</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P20" s="3">
-        <v>24.948764656842595</v>
+        <v>22.71709963975286</v>
       </c>
       <c r="Q20" s="3">
-        <v>47.974683544303794</v>
+        <v>48.481012658227854</v>
       </c>
       <c r="R20" s="3">
-        <v>40.88607594936709</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>1.02</v>
       </c>
-      <c r="C21" s="2">
-        <v>41.77215189873418</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="C21" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="D21" s="3">
         <v>13.529411764705882</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>1.52</v>
       </c>
-      <c r="F21" s="2">
-        <v>0.05162469064247899</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1.61</v>
-      </c>
-      <c r="H21" s="2">
-        <v>49.99</v>
-      </c>
-      <c r="I21" s="2">
-        <v>40.11</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.037330928566145255</v>
-      </c>
-      <c r="K21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2">
+      <c r="F21" s="3">
+        <v>-0.0346803510666184</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="H21" s="3">
+        <v>48.03</v>
+      </c>
+      <c r="I21" s="3">
+        <v>34.99</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.038388645609507124</v>
+      </c>
+      <c r="K21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>38</v>
       </c>
-      <c r="M21" s="2">
-        <v>0.1184354001368193</v>
-      </c>
-      <c r="N21" s="2">
-        <v>23.87111534062295</v>
-      </c>
-      <c r="O21" s="2">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="P21" s="2">
+      <c r="M21" s="3">
+        <v>0.03603850109285256</v>
+      </c>
+      <c r="N21" s="3">
+        <v>16.465325469197087</v>
+      </c>
+      <c r="O21" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P21" s="3">
         <v>39.63614933355383</v>
       </c>
-      <c r="Q21" s="2">
-        <v>64.9367088607595</v>
-      </c>
-      <c r="R21" s="2">
-        <v>52.025316455696206</v>
-      </c>
-      <c r="S21" s="2" t="s">
+      <c r="Q21" s="3">
+        <v>61.64556962025317</v>
+      </c>
+      <c r="R21" s="3">
+        <v>48.60759493670886</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T21" s="2">
-        <v>0</v>
+      <c r="T21" s="3">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3370,7 +3358,7 @@
         <v>8.11</v>
       </c>
       <c r="C22" s="3">
-        <v>70.88607594936708</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="D22" s="3">
         <v>0.718865598027127</v>
@@ -3379,19 +3367,19 @@
         <v>-1.48</v>
       </c>
       <c r="F22" s="3">
-        <v>-0.04307280581540682</v>
+        <v>-0.01596096591096488</v>
       </c>
       <c r="G22" s="3">
         <v>1.38</v>
       </c>
       <c r="H22" s="3">
-        <v>63</v>
+        <v>68.69</v>
       </c>
       <c r="I22" s="3">
-        <v>10.34</v>
+        <v>14.75</v>
       </c>
       <c r="J22" s="3">
-        <v>0.014842911779265488</v>
+        <v>0.01707264465093835</v>
       </c>
       <c r="K22" s="3" t="b">
         <v>0</v>
@@ -3400,28 +3388,28 @@
         <v>58</v>
       </c>
       <c r="M22" s="3">
-        <v>-0.0014530195730309003</v>
+        <v>0.028827640456700054</v>
       </c>
       <c r="N22" s="3">
-        <v>11.882273369637938</v>
+        <v>15.744239405581824</v>
       </c>
       <c r="O22" s="3">
-        <v>56.9620253164557</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P22" s="3">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="3">
-        <v>60.63291139240506</v>
+        <v>62.40506329113924</v>
       </c>
       <c r="R22" s="3">
-        <v>47.53164556962025</v>
+        <v>49.43037974683545</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3441,19 +3429,19 @@
         <v>-0.1</v>
       </c>
       <c r="F23" s="3">
-        <v>-0.2238007118664241</v>
+        <v>-0.19500491324233873</v>
       </c>
       <c r="G23" s="3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H23" s="3">
-        <v>34.66</v>
+        <v>49.68</v>
       </c>
       <c r="I23" s="3">
-        <v>-13.84</v>
+        <v>-8.2</v>
       </c>
       <c r="J23" s="3">
-        <v>0.0037244957972948725</v>
+        <v>0.002046324199199352</v>
       </c>
       <c r="K23" s="3" t="b">
         <v>0</v>
@@ -3462,28 +3450,28 @@
         <v>23</v>
       </c>
       <c r="M23" s="3">
-        <v>-0.19641927354907152</v>
+        <v>-0.16671737237855033</v>
       </c>
       <c r="N23" s="3">
-        <v>-7.614352027966116</v>
+        <v>-3.8102618779432094</v>
       </c>
       <c r="O23" s="3">
-        <v>24.050632911392405</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P23" s="3">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="3">
-        <v>43.291139240506325</v>
+        <v>46.58227848101265</v>
       </c>
       <c r="R23" s="3">
-        <v>31.51898734177215</v>
+        <v>33.417721518987335</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3497,25 +3485,25 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="1">
-        <v>-1.089143426294821</v>
+        <v>-0.9205677290836654</v>
       </c>
       <c r="E24" s="1">
         <v>7.21</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.5086884495613566</v>
+        <v>-0.540997176862236</v>
       </c>
       <c r="G24" s="1">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="H24" s="1">
-        <v>37.22</v>
+        <v>42.27</v>
       </c>
       <c r="I24" s="1">
-        <v>-36.82</v>
+        <v>-32.63</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.0031286388148233928</v>
+        <v>-0.0010840395404872125</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3524,28 +3512,28 @@
         <v>-9</v>
       </c>
       <c r="M24" s="1">
-        <v>-0.23268355132244256</v>
+        <v>-0.24751394040043162</v>
       </c>
       <c r="N24" s="1">
-        <v>-11.240779805303223</v>
+        <v>-11.889918680131334</v>
       </c>
       <c r="O24" s="1">
-        <v>21.518987341772153</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P24" s="1">
         <v>41.129939248308794</v>
       </c>
       <c r="Q24" s="1">
-        <v>9.746835443037975</v>
+        <v>10.632911392405067</v>
       </c>
       <c r="R24" s="1">
-        <v>3.227848101265824</v>
+        <v>2.974683544303799</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="1">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3565,19 +3553,19 @@
         <v>11.56</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.422333108686368</v>
+        <v>-0.44397923562155767</v>
       </c>
       <c r="G25" s="1">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H25" s="1">
-        <v>41.08</v>
+        <v>45.02</v>
       </c>
       <c r="I25" s="1">
-        <v>-53.41</v>
+        <v>-50.28</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.005426020833051525</v>
+        <v>-0.0033748606604909193</v>
       </c>
       <c r="K25" s="1" t="b">
         <v>0</v>
@@ -3586,28 +3574,28 @@
         <v>42</v>
       </c>
       <c r="M25" s="1">
-        <v>-0.2821401445015228</v>
+        <v>-0.29782694115865105</v>
       </c>
       <c r="N25" s="1">
-        <v>-16.186439123211244</v>
+        <v>-16.921218755953277</v>
       </c>
       <c r="O25" s="1">
-        <v>11.39240506329114</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P25" s="1">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="1">
-        <v>12.151898734177216</v>
+        <v>11.898734177215193</v>
       </c>
       <c r="R25" s="1">
-        <v>-0.37974683544303645</v>
+        <v>-1.0126582278480996</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3627,19 +3615,19 @@
         <v>2.15</v>
       </c>
       <c r="F26" s="3">
-        <v>0.38957518495318594</v>
+        <v>0.3705636755447685</v>
       </c>
       <c r="G26" s="3">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="H26" s="3">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="I26" s="3">
-        <v>18.08</v>
+        <v>20.6</v>
       </c>
       <c r="J26" s="3">
-        <v>0.06421703035469414</v>
+        <v>0.06218566310977188</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>0</v>
@@ -3648,28 +3636,28 @@
         <v>-28</v>
       </c>
       <c r="M26" s="3">
-        <v>0.6338176147439709</v>
+        <v>0.6298661334628286</v>
       </c>
       <c r="N26" s="3">
-        <v>75.40933680133813</v>
+        <v>75.84808870619469</v>
       </c>
       <c r="O26" s="3">
-        <v>92.40506329113924</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P26" s="3">
-        <v>47.65747922848498</v>
+        <v>47.51283017631868</v>
       </c>
       <c r="Q26" s="3">
-        <v>39.11392405063292</v>
+        <v>38.22784810126583</v>
       </c>
       <c r="R26" s="3">
-        <v>33.73417721518988</v>
+        <v>32.84810126582279</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3689,19 +3677,19 @@
         <v>7.51</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.36426584306625975</v>
+        <v>-0.38421107521853803</v>
       </c>
       <c r="G27" s="1">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="H27" s="1">
-        <v>40.05</v>
+        <v>43.59</v>
       </c>
       <c r="I27" s="1">
-        <v>-27.28</v>
+        <v>-24.69</v>
       </c>
       <c r="J27" s="1">
-        <v>0.010967630498285301</v>
+        <v>0.009760106599280723</v>
       </c>
       <c r="K27" s="1" t="b">
         <v>0</v>
@@ -3710,28 +3698,28 @@
         <v>39</v>
       </c>
       <c r="M27" s="1">
-        <v>-0.1769768049755681</v>
+        <v>-0.18501964163602824</v>
       </c>
       <c r="N27" s="1">
-        <v>-5.67010517061578</v>
+        <v>-5.640488803690999</v>
       </c>
       <c r="O27" s="1">
-        <v>30.37974683544304</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P27" s="1">
-        <v>48.541802331934534</v>
+        <v>46.059783198474584</v>
       </c>
       <c r="Q27" s="1">
         <v>31.77215189873418</v>
       </c>
       <c r="R27" s="1">
-        <v>19.87341772151899</v>
+        <v>19.430379746835442</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="1">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3751,19 +3739,19 @@
         <v>-4.75</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.5176828002010445</v>
+        <v>-0.5302614761180011</v>
       </c>
       <c r="G28" s="1">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="H28" s="1">
-        <v>34.68</v>
+        <v>42.51</v>
       </c>
       <c r="I28" s="1">
-        <v>-34.8</v>
+        <v>-29.72</v>
       </c>
       <c r="J28" s="1">
-        <v>0.0023508086237874768</v>
+        <v>0.00021785781265444356</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3772,28 +3760,28 @@
         <v>-3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.277821400541036</v>
+        <v>-0.27567360834390575</v>
       </c>
       <c r="N28" s="1">
-        <v>-15.754564727162565</v>
+        <v>-14.70588547447875</v>
       </c>
       <c r="O28" s="1">
-        <v>13.924050632911392</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P28" s="1">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="1">
-        <v>31.26582278481013</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="R28" s="1">
-        <v>17.65822784810127</v>
+        <v>18.291139240506332</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="1">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3804,7 +3792,7 @@
         <v>0.44</v>
       </c>
       <c r="C29" s="3">
-        <v>34.177215189873415</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="D29" s="3">
         <v>79.04545454545455</v>
@@ -3813,19 +3801,19 @@
         <v>0.71</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.31376708483042504</v>
+        <v>-0.260444426187111</v>
       </c>
       <c r="G29" s="3">
         <v>2.16</v>
       </c>
       <c r="H29" s="3">
-        <v>49.71</v>
+        <v>57.19</v>
       </c>
       <c r="I29" s="3">
-        <v>-27.45</v>
+        <v>-22.25</v>
       </c>
       <c r="J29" s="3">
-        <v>0.0051714150010587585</v>
+        <v>0.005868927187871581</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
@@ -3834,28 +3822,28 @@
         <v>-68</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.18671721103790906</v>
+        <v>-0.12372131201213388</v>
       </c>
       <c r="N29" s="3">
-        <v>-6.644145776849879</v>
+        <v>0.48934415869842623</v>
       </c>
       <c r="O29" s="3">
-        <v>26.582278481012654</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P29" s="3">
-        <v>42.700456457951226</v>
+        <v>41.93177642803681</v>
       </c>
       <c r="Q29" s="3">
-        <v>51.26582278481013</v>
+        <v>52.911392405063296</v>
       </c>
       <c r="R29" s="3">
-        <v>34.0506329113924</v>
+        <v>37.911392405063296</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>0</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3866,7 +3854,7 @@
         <v>1.95</v>
       </c>
       <c r="C30" s="2">
-        <v>46.835443037974684</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="D30" s="2">
         <v>1497.6410256410256</v>
@@ -3875,19 +3863,19 @@
         <v>0.79</v>
       </c>
       <c r="F30" s="2">
-        <v>-0.09853897868270775</v>
+        <v>-0.08995411839988707</v>
       </c>
       <c r="G30" s="2">
         <v>1.2</v>
       </c>
       <c r="H30" s="2">
-        <v>48.77</v>
+        <v>54.29</v>
       </c>
       <c r="I30" s="2">
-        <v>0.1</v>
+        <v>3.67</v>
       </c>
       <c r="J30" s="2">
-        <v>0.009013675838880993</v>
+        <v>0.008723101725844864</v>
       </c>
       <c r="K30" s="2" t="b">
         <v>0</v>
@@ -3896,28 +3884,28 @@
         <v>24</v>
       </c>
       <c r="M30" s="2">
-        <v>-0.07663382802882568</v>
+        <v>-0.06638116768006341</v>
       </c>
       <c r="N30" s="2">
-        <v>4.364192524058455</v>
+        <v>6.223358591905487</v>
       </c>
       <c r="O30" s="2">
-        <v>48.10126582278481</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P30" s="2">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="2">
-        <v>64.81012658227849</v>
+        <v>64.9367088607595</v>
       </c>
       <c r="R30" s="2">
-        <v>51.83544303797468</v>
+        <v>51.962025316455694</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="2">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3928,7 +3916,7 @@
         <v>6.01</v>
       </c>
       <c r="C31" s="2">
-        <v>63.29113924050633</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="D31" s="2">
         <v>10.262895174708818</v>
@@ -3937,49 +3925,49 @@
         <v>-0.64</v>
       </c>
       <c r="F31" s="2">
-        <v>0.014210648346719035</v>
+        <v>0.0003446817125796475</v>
       </c>
       <c r="G31" s="2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H31" s="2">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="I31" s="2">
-        <v>6.69</v>
+        <v>7.62</v>
       </c>
       <c r="J31" s="2">
-        <v>0.020179826792573352</v>
+        <v>0.019208481201470375</v>
       </c>
       <c r="K31" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2">
         <v>67</v>
       </c>
       <c r="M31" s="2">
-        <v>0.0656877523833419</v>
+        <v>0.05338382083218285</v>
       </c>
       <c r="N31" s="2">
-        <v>18.59635056527523</v>
+        <v>18.199857443130114</v>
       </c>
       <c r="O31" s="2">
-        <v>69.62025316455697</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P31" s="2">
         <v>22.731897658859403</v>
       </c>
       <c r="Q31" s="2">
-        <v>61.51898734177215</v>
+        <v>60.50632911392405</v>
       </c>
       <c r="R31" s="2">
-        <v>56.58227848101266</v>
+        <v>56.20253164556962</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -3999,19 +3987,19 @@
         <v>-3.39</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.06032165191812297</v>
+        <v>-0.1858881192362209</v>
       </c>
       <c r="G32" s="3">
         <v>1.62</v>
       </c>
       <c r="H32" s="3">
-        <v>56.08</v>
+        <v>52.7</v>
       </c>
       <c r="I32" s="3">
-        <v>7.15</v>
+        <v>3.63</v>
       </c>
       <c r="J32" s="3">
-        <v>0.006695070092382302</v>
+        <v>0.0059886439101265905</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
@@ -4020,28 +4008,28 @@
         <v>24</v>
       </c>
       <c r="M32" s="3">
-        <v>0.0075843151089114436</v>
+        <v>-0.11281197200476756</v>
       </c>
       <c r="N32" s="3">
-        <v>12.78600683783217</v>
+        <v>1.5802781594350581</v>
       </c>
       <c r="O32" s="3">
-        <v>58.22784810126582</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P32" s="3">
         <v>27.28297753683016</v>
       </c>
       <c r="Q32" s="3">
-        <v>44.050632911392405</v>
+        <v>42.15189873417721</v>
       </c>
       <c r="R32" s="3">
-        <v>34.936708860759495</v>
+        <v>30.18987341772152</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4052,7 +4040,7 @@
         <v>16.79</v>
       </c>
       <c r="C33" s="3">
-        <v>88.60759493670885</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="D33" s="3">
         <v>-0.06075044669446097</v>
@@ -4061,19 +4049,19 @@
         <v>-1.79</v>
       </c>
       <c r="F33" s="3">
-        <v>-0.14667437854757395</v>
+        <v>-0.1586820808873243</v>
       </c>
       <c r="G33" s="3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="H33" s="3">
-        <v>37.09</v>
+        <v>40.52</v>
       </c>
       <c r="I33" s="3">
-        <v>-13.88</v>
+        <v>-12.8</v>
       </c>
       <c r="J33" s="3">
-        <v>0.008441286927564441</v>
+        <v>0.007145973286055338</v>
       </c>
       <c r="K33" s="3" t="b">
         <v>0</v>
@@ -4082,28 +4070,28 @@
         <v>7</v>
       </c>
       <c r="M33" s="3">
-        <v>-0.1324360306225506</v>
+        <v>-0.14571695799142126</v>
       </c>
       <c r="N33" s="3">
-        <v>-1.2160277353140274</v>
+        <v>-1.7102204392303053</v>
       </c>
       <c r="O33" s="3">
-        <v>36.708860759493675</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P33" s="3">
         <v>25.92446787021105</v>
       </c>
       <c r="Q33" s="3">
-        <v>46.58227848101266</v>
+        <v>45.189873417721515</v>
       </c>
       <c r="R33" s="3">
-        <v>37.911392405063296</v>
+        <v>37.151898734177216</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="3">
-        <v>-0.13</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4114,7 +4102,7 @@
         <v>13.11</v>
       </c>
       <c r="C34" s="2">
-        <v>84.81012658227847</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="D34" s="2">
         <v>-0.7360793287566743</v>
@@ -4123,19 +4111,19 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0.0422329570445851</v>
+        <v>0.05523282741864441</v>
       </c>
       <c r="G34" s="2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H34" s="2">
-        <v>42.37</v>
+        <v>49.52</v>
       </c>
       <c r="I34" s="2">
-        <v>16.8</v>
+        <v>19.17</v>
       </c>
       <c r="J34" s="2">
-        <v>0.021872359169800584</v>
+        <v>0.021334269510778048</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
@@ -4144,28 +4132,28 @@
         <v>36</v>
       </c>
       <c r="M34" s="2">
-        <v>0.0696143953619377</v>
+        <v>0.08352036828243281</v>
       </c>
       <c r="N34" s="2">
-        <v>18.989014863134802</v>
+        <v>21.21351218815511</v>
       </c>
       <c r="O34" s="2">
-        <v>72.15189873417721</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>53.79746835443038</v>
+        <v>53.9240506329114</v>
       </c>
       <c r="R34" s="2">
-        <v>50.063291139240505</v>
+        <v>50.82278481012659</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="2">
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4176,7 +4164,7 @@
         <v>17.37</v>
       </c>
       <c r="C35" s="1">
-        <v>91.13924050632912</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="D35" s="1">
         <v>-0.47380541162924583</v>
@@ -4185,19 +4173,19 @@
         <v>8.84</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.3094808572789003</v>
+        <v>-0.3069178212901955</v>
       </c>
       <c r="G35" s="1">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H35" s="1">
-        <v>54.22</v>
+        <v>50.63</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.54</v>
+        <v>-18.27</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.011680687614597451</v>
+        <v>-0.012000139273407349</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4206,28 +4194,28 @@
         <v>20</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.3138618874096767</v>
+        <v>-0.31045376389816903</v>
       </c>
       <c r="N35" s="1">
-        <v>-19.358613414026642</v>
+        <v>-18.18390102990508</v>
       </c>
       <c r="O35" s="1">
-        <v>8.860759493670885</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P35" s="1">
         <v>27.295682949534427</v>
       </c>
       <c r="Q35" s="1">
-        <v>43.41772151898735</v>
+        <v>39.49367088607595</v>
       </c>
       <c r="R35" s="1">
-        <v>24.62025316455696</v>
+        <v>22.405063291139236</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="1">
-        <v>0</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4238,28 +4226,28 @@
         <v>11.51</v>
       </c>
       <c r="C36" s="1">
-        <v>81.0126582278481</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="D36" s="1">
-        <v>0.3388357949609036</v>
+        <v>0.3596872284969592</v>
       </c>
       <c r="E36" s="1">
         <v>2.32</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.2947040210683217</v>
+        <v>-0.2580770032664025</v>
       </c>
       <c r="G36" s="1">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="H36" s="1">
-        <v>39.88</v>
+        <v>48.95</v>
       </c>
       <c r="I36" s="1">
-        <v>-20.74</v>
+        <v>-15.72</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.014443094424291019</v>
+        <v>-0.008930763070187062</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
@@ -4268,28 +4256,28 @@
         <v>-54</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.2793704156106043</v>
+        <v>-0.24511188037049947</v>
       </c>
       <c r="N36" s="1">
-        <v>-15.909466234119396</v>
+        <v>-11.64971267713813</v>
       </c>
       <c r="O36" s="1">
-        <v>12.658227848101266</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P36" s="1">
-        <v>28.98593365092364</v>
+        <v>27.03345749163471</v>
       </c>
       <c r="Q36" s="1">
-        <v>37.59493670886076</v>
+        <v>41.39240506329113</v>
       </c>
       <c r="R36" s="1">
-        <v>25.253164556962023</v>
+        <v>28.9240506329114</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>0</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4300,7 +4288,7 @@
         <v>5.33</v>
       </c>
       <c r="C37" s="1">
-        <v>60.75949367088608</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="D37" s="1">
         <v>0.6003752345215758</v>
@@ -4309,19 +4297,19 @@
         <v>-4.98</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.2325702472887173</v>
+        <v>-0.22786933516044394</v>
       </c>
       <c r="G37" s="1">
         <v>1.34</v>
       </c>
       <c r="H37" s="1">
-        <v>34.53</v>
+        <v>50.78</v>
       </c>
       <c r="I37" s="1">
-        <v>-25.05</v>
+        <v>-20.52</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.007380376352226501</v>
+        <v>-0.006907274076265041</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
@@ -4330,10 +4318,10 @@
         <v>-215</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.1953314911771178</v>
+        <v>-0.18779531893674373</v>
       </c>
       <c r="N37" s="1">
-        <v>-7.505573790770743</v>
+        <v>-5.918056533762551</v>
       </c>
       <c r="O37" s="1">
         <v>25.31645569620253</v>
@@ -4342,16 +4330,16 @@
         <v>31.61854630334819</v>
       </c>
       <c r="Q37" s="1">
-        <v>33.29113924050633</v>
+        <v>37.974683544303794</v>
       </c>
       <c r="R37" s="1">
-        <v>25.316455696202535</v>
+        <v>25.632911392405063</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4371,19 +4359,19 @@
         <v>-1.63</v>
       </c>
       <c r="F38" s="2">
-        <v>0.3968131936883785</v>
+        <v>0.414588017384123</v>
       </c>
       <c r="G38" s="2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H38" s="2">
-        <v>58.72</v>
+        <v>59.47</v>
       </c>
       <c r="I38" s="2">
-        <v>41.01</v>
+        <v>41.68</v>
       </c>
       <c r="J38" s="2">
-        <v>0.054287448249601473</v>
+        <v>0.05449797535697679</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -4392,28 +4380,28 @@
         <v>-46</v>
       </c>
       <c r="M38" s="2">
-        <v>0.42528988953842517</v>
+        <v>0.44405420578390253</v>
       </c>
       <c r="N38" s="2">
-        <v>54.55656428078355</v>
+        <v>57.26689593830208</v>
       </c>
       <c r="O38" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P38" s="2">
         <v>26.51995189252711</v>
       </c>
       <c r="Q38" s="2">
-        <v>67.46835443037975</v>
+        <v>67.34177215189874</v>
       </c>
       <c r="R38" s="2">
-        <v>57.53164556962025</v>
+        <v>57.658227848101255</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4433,19 +4421,19 @@
         <v>4.83</v>
       </c>
       <c r="F39" s="3">
-        <v>-0.15629033779888524</v>
+        <v>-0.1591001948151601</v>
       </c>
       <c r="G39" s="3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H39" s="3">
-        <v>41.86</v>
+        <v>46.14</v>
       </c>
       <c r="I39" s="3">
-        <v>-11.06</v>
+        <v>-8.77</v>
       </c>
       <c r="J39" s="3">
-        <v>-0.01940685116622368</v>
+        <v>-0.016820409128281557</v>
       </c>
       <c r="K39" s="3" t="b">
         <v>0</v>
@@ -4454,28 +4442,28 @@
         <v>-4</v>
       </c>
       <c r="M39" s="3">
-        <v>-0.13548044467769726</v>
+        <v>-0.13552724409533645</v>
       </c>
       <c r="N39" s="3">
-        <v>-1.5204691408286928</v>
+        <v>-0.6912490496218264</v>
       </c>
       <c r="O39" s="3">
-        <v>35.44303797468354</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P39" s="3">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="3">
-        <v>37.9746835443038</v>
+        <v>37.84810126582279</v>
       </c>
       <c r="R39" s="3">
-        <v>30.316455696202535</v>
+        <v>30.56962025316456</v>
       </c>
       <c r="S39" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4489,25 +4477,25 @@
         <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>8.798751950078003</v>
+        <v>9.173166926677066</v>
       </c>
       <c r="E40" s="1">
         <v>0.92</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.26771341130198373</v>
+        <v>-0.3312951589593636</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>33.54</v>
+        <v>36.03</v>
       </c>
       <c r="I40" s="1">
-        <v>-36.42</v>
+        <v>-35.48</v>
       </c>
       <c r="J40" s="1">
-        <v>-0.021148643287555488</v>
+        <v>-0.0213691326339418</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4516,10 +4504,10 @@
         <v>55</v>
       </c>
       <c r="M40" s="1">
-        <v>-0.37723916457139406</v>
+        <v>-0.44915991255848187</v>
       </c>
       <c r="N40" s="1">
-        <v>-25.69634113019837</v>
+        <v>-32.05451589593636</v>
       </c>
       <c r="O40" s="1">
         <v>3.79746835443038</v>
@@ -4528,16 +4516,16 @@
         <v>42.434935391194514</v>
       </c>
       <c r="Q40" s="1">
-        <v>21.772151898734172</v>
+        <v>22.531645569620252</v>
       </c>
       <c r="R40" s="1">
-        <v>9.93670886075949</v>
+        <v>10.443037974683545</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4557,19 +4545,19 @@
         <v>-1.3</v>
       </c>
       <c r="F41" s="3">
-        <v>0.09601781983879792</v>
+        <v>0.11923562400143034</v>
       </c>
       <c r="G41" s="3">
         <v>1.16</v>
       </c>
       <c r="H41" s="3">
-        <v>46.08</v>
+        <v>56.16</v>
       </c>
       <c r="I41" s="3">
-        <v>-13.15</v>
+        <v>-5.27</v>
       </c>
       <c r="J41" s="3">
-        <v>0.028988482410286218</v>
+        <v>0.027088215580633096</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>0</v>
@@ -4578,28 +4566,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>0.11354194036190357</v>
+        <v>0.13809398457728927</v>
       </c>
       <c r="N41" s="3">
-        <v>23.381769363131394</v>
+        <v>26.67087381764075</v>
       </c>
       <c r="O41" s="3">
-        <v>75.9493670886076</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P41" s="3">
-        <v>40.794223935469645</v>
+        <v>39.70588351306617</v>
       </c>
       <c r="Q41" s="3">
-        <v>42.405063291139236</v>
+        <v>45.44303797468355</v>
       </c>
       <c r="R41" s="3">
-        <v>38.48101265822785</v>
+        <v>39.936708860759495</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4610,7 +4598,7 @@
         <v>3.61</v>
       </c>
       <c r="C42" s="3">
-        <v>53.16455696202531</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="D42" s="3">
         <v>1.0664819944598338</v>
@@ -4619,49 +4607,49 @@
         <v>2.2</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.10381871794865229</v>
+        <v>-0.10131904483173489</v>
       </c>
       <c r="G42" s="3">
         <v>0.35</v>
       </c>
       <c r="H42" s="3">
-        <v>52.05</v>
+        <v>53.83</v>
       </c>
       <c r="I42" s="3">
-        <v>0.02</v>
+        <v>0.57</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.005804801745770332</v>
+        <v>-0.005480313432185138</v>
       </c>
       <c r="K42" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>16</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.17501045757376898</v>
+        <v>-0.17793113467116173</v>
       </c>
       <c r="N42" s="3">
-        <v>-5.473470430435863</v>
+        <v>-4.931638107204353</v>
       </c>
       <c r="O42" s="3">
-        <v>31.645569620253166</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P42" s="3">
         <v>12.159120495183384</v>
       </c>
       <c r="Q42" s="3">
-        <v>44.30379746835443</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="R42" s="3">
-        <v>34.87341772151899</v>
+        <v>34.17721518987342</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="3">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4675,25 +4663,25 @@
         <v>30.37974683544304</v>
       </c>
       <c r="D43" s="3">
-        <v>246.29999999999998</v>
+        <v>246.49999999999997</v>
       </c>
       <c r="E43" s="3">
         <v>10.1</v>
       </c>
       <c r="F43" s="3">
-        <v>-0.09744959742905798</v>
+        <v>-0.20161670338846616</v>
       </c>
       <c r="G43" s="3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H43" s="3">
-        <v>54.17</v>
+        <v>53.53</v>
       </c>
       <c r="I43" s="3">
-        <v>-1.42</v>
+        <v>-1.81</v>
       </c>
       <c r="J43" s="3">
-        <v>0.006817215206790364</v>
+        <v>0.004440131633989671</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>0</v>
@@ -4702,28 +4690,28 @@
         <v>11</v>
       </c>
       <c r="M43" s="3">
-        <v>-0.059115583784764336</v>
+        <v>-0.16154268716476594</v>
       </c>
       <c r="N43" s="3">
-        <v>6.116016948464606</v>
+        <v>-3.2927933565647765</v>
       </c>
       <c r="O43" s="3">
-        <v>51.89873417721519</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P43" s="3">
-        <v>30.495842865521038</v>
+        <v>26.894796563147693</v>
       </c>
       <c r="Q43" s="3">
-        <v>57.34177215189874</v>
+        <v>54.81012658227848</v>
       </c>
       <c r="R43" s="3">
-        <v>43.924050632911396</v>
+        <v>38.924050632911396</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4734,7 +4722,7 @@
         <v>1.02</v>
       </c>
       <c r="C44" s="3">
-        <v>41.77215189873418</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="D44" s="3">
         <v>26.80392156862745</v>
@@ -4743,19 +4731,19 @@
         <v>-2.29</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.4130401822957189</v>
+        <v>-0.4292435058371429</v>
       </c>
       <c r="G44" s="3">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="H44" s="3">
-        <v>46.36</v>
+        <v>52.3</v>
       </c>
       <c r="I44" s="3">
-        <v>-21.67</v>
+        <v>-17.68</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.004878625387168959</v>
+        <v>-0.005779492842713396</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
@@ -4764,28 +4752,28 @@
         <v>-116</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.2399894921300506</v>
+        <v>-0.24183854761454493</v>
       </c>
       <c r="N44" s="3">
-        <v>-11.971373886064026</v>
+        <v>-11.322379401542666</v>
       </c>
       <c r="O44" s="3">
-        <v>20.253164556962027</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P44" s="3">
-        <v>39.61643255338282</v>
+        <v>33.9792376983537</v>
       </c>
       <c r="Q44" s="3">
-        <v>47.59493670886075</v>
+        <v>47.21518987341772</v>
       </c>
       <c r="R44" s="3">
-        <v>30.949367088607595</v>
+        <v>30.886075949367086</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4796,28 +4784,28 @@
         <v>8.37</v>
       </c>
       <c r="C45" s="2">
-        <v>73.41772151898735</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="D45" s="2">
-        <v>0.7323775388291519</v>
+        <v>0.7132616487455199</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2">
-        <v>-0.02196012226052682</v>
+        <v>-0.01630963278402417</v>
       </c>
       <c r="G45" s="2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="2">
-        <v>34.76</v>
+        <v>43.99</v>
       </c>
       <c r="I45" s="2">
-        <v>2.6</v>
+        <v>6.06</v>
       </c>
       <c r="J45" s="2">
-        <v>0.014397334801875173</v>
+        <v>0.014298688620694455</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
@@ -4826,28 +4814,28 @@
         <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.028421724243401947</v>
+        <v>0.03672950633557903</v>
       </c>
       <c r="N45" s="2">
-        <v>14.86974775128122</v>
+        <v>16.53442599346972</v>
       </c>
       <c r="O45" s="2">
-        <v>62.0253164556962</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P45" s="2">
         <v>18.755109025385668</v>
       </c>
       <c r="Q45" s="2">
-        <v>52.65822784810127</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="R45" s="2">
-        <v>50.75949367088607</v>
+        <v>51.64556962025317</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4861,25 +4849,25 @@
         <v>18.9873417721519</v>
       </c>
       <c r="D46" s="1">
-        <v>548.5333333333334</v>
+        <v>564.5333333333334</v>
       </c>
       <c r="E46" s="1">
         <v>4.27</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.3705634589208545</v>
+        <v>-0.35774699407510546</v>
       </c>
       <c r="G46" s="1">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H46" s="1">
-        <v>38.93</v>
+        <v>43.43</v>
       </c>
       <c r="I46" s="1">
-        <v>-17.57</v>
+        <v>-13.13</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.015016473512974332</v>
+        <v>-0.014412624427333395</v>
       </c>
       <c r="K46" s="1" t="b">
         <v>0</v>
@@ -4888,28 +4876,28 @@
         <v>29</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.31470532475345525</v>
+        <v>-0.3011719123475287</v>
       </c>
       <c r="N46" s="1">
-        <v>-19.442957148404496</v>
+        <v>-17.255715874841048</v>
       </c>
       <c r="O46" s="1">
-        <v>7.59493670886076</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P46" s="1">
         <v>50.613275903697605</v>
       </c>
       <c r="Q46" s="1">
-        <v>39.746835443037966</v>
+        <v>40.506329113924046</v>
       </c>
       <c r="R46" s="1">
-        <v>21.962025316455694</v>
+        <v>21.835443037974684</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="1">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4920,7 +4908,7 @@
         <v>10.62</v>
       </c>
       <c r="C47" s="1">
-        <v>79.74683544303798</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="D47" s="1">
         <v>0.8549905838041432</v>
@@ -4929,19 +4917,19 @@
         <v>1</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.37390585239131796</v>
+        <v>-0.3487318651468219</v>
       </c>
       <c r="G47" s="1">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H47" s="1">
-        <v>57.1</v>
+        <v>60.71</v>
       </c>
       <c r="I47" s="1">
-        <v>-14.35</v>
+        <v>-12.35</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.011613039997456574</v>
+        <v>-0.009845944277940756</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -4950,28 +4938,28 @@
         <v>11</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.3300955510835538</v>
+        <v>-0.30040731617118344</v>
       </c>
       <c r="N47" s="1">
-        <v>-20.981979781414356</v>
+        <v>-17.17925625720652</v>
       </c>
       <c r="O47" s="1">
-        <v>6.329113924050633</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P47" s="1">
         <v>33.84253937304741</v>
       </c>
       <c r="Q47" s="1">
-        <v>49.11392405063292</v>
+        <v>48.73417721518988</v>
       </c>
       <c r="R47" s="1">
-        <v>26.139240506329113</v>
+        <v>25.949367088607595</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="1">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -4982,58 +4970,58 @@
         <v>3.98</v>
       </c>
       <c r="C48" s="2">
-        <v>54.43037974683544</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="D48" s="2">
-        <v>7.977386934673366</v>
+        <v>8.06281407035176</v>
       </c>
       <c r="E48" s="2">
         <v>3.41</v>
       </c>
       <c r="F48" s="2">
-        <v>-0.06535354588389355</v>
+        <v>-0.08752660329796674</v>
       </c>
       <c r="G48" s="2">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H48" s="2">
-        <v>44.67</v>
+        <v>48.85</v>
       </c>
       <c r="I48" s="2">
-        <v>37.54</v>
+        <v>40.65</v>
       </c>
       <c r="J48" s="2">
-        <v>0.014321123753770508</v>
+        <v>0.015362358907214027</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M48" s="2">
-        <v>0.04964849504898727</v>
+        <v>0.03505274044511619</v>
       </c>
       <c r="N48" s="2">
-        <v>16.992424831839752</v>
+        <v>16.36674940442345</v>
       </c>
       <c r="O48" s="2">
-        <v>65.82278481012658</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P48" s="2">
         <v>25.31695963070349</v>
       </c>
       <c r="Q48" s="2">
-        <v>59.87341772151899</v>
+        <v>60</v>
       </c>
       <c r="R48" s="2">
-        <v>50.506329113924046</v>
+        <v>50.31645569620253</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T48" s="2">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5053,19 +5041,19 @@
         <v>2.29</v>
       </c>
       <c r="F49" s="2">
-        <v>0.26050081530723546</v>
+        <v>0.3861512497892915</v>
       </c>
       <c r="G49" s="2">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="H49" s="2">
-        <v>48.3</v>
+        <v>56.96</v>
       </c>
       <c r="I49" s="2">
-        <v>74.32</v>
+        <v>93.36</v>
       </c>
       <c r="J49" s="2">
-        <v>0.050836654911211865</v>
+        <v>0.054081015371308744</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5074,28 +5062,28 @@
         <v>207</v>
       </c>
       <c r="M49" s="2">
-        <v>0.563887151863502</v>
+        <v>0.7102793221868666</v>
       </c>
       <c r="N49" s="2">
-        <v>68.41629051329122</v>
+        <v>83.8894075785985</v>
       </c>
       <c r="O49" s="2">
-        <v>89.87341772151899</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P49" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q49" s="2">
-        <v>70</v>
+        <v>72.0253164556962</v>
       </c>
       <c r="R49" s="2">
-        <v>60.25316455696203</v>
+        <v>61.01265822784809</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.25</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5115,31 +5103,31 @@
         <v>5.32</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.493499147921606</v>
+        <v>-0.513158884109552</v>
       </c>
       <c r="G50" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H50" s="1">
-        <v>42.04</v>
+        <v>43.13</v>
       </c>
       <c r="I50" s="1">
-        <v>-26.46</v>
+        <v>-25.98</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.02662454853740195</v>
+        <v>-0.026872051862036873</v>
       </c>
       <c r="K50" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="1">
         <v>-1</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.4376410137542067</v>
+        <v>-0.4518692122380106</v>
       </c>
       <c r="N50" s="1">
-        <v>-31.736526048479636</v>
+        <v>-32.325445863889236</v>
       </c>
       <c r="O50" s="1">
         <v>2.5316455696202533</v>
@@ -5148,16 +5136,16 @@
         <v>42.0212746732318</v>
       </c>
       <c r="Q50" s="1">
-        <v>40.50632911392405</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="R50" s="1">
-        <v>22.531645569620252</v>
+        <v>22.405063291139243</v>
       </c>
       <c r="S50" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T50" s="1">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5177,19 +5165,19 @@
         <v>36.11</v>
       </c>
       <c r="F51" s="3">
-        <v>-0.1534588067470235</v>
+        <v>-0.16242541931150978</v>
       </c>
       <c r="G51" s="3">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="H51" s="3">
-        <v>44.08</v>
+        <v>45.49</v>
       </c>
       <c r="I51" s="3">
-        <v>11.61</v>
+        <v>13.28</v>
       </c>
       <c r="J51" s="3">
-        <v>0.028904000711836478</v>
+        <v>0.030799202986335563</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>0</v>
@@ -5198,19 +5186,19 @@
         <v>96</v>
       </c>
       <c r="M51" s="3">
-        <v>0.009734565624397895</v>
+        <v>0.007299825871220467</v>
       </c>
       <c r="N51" s="3">
-        <v>13.001031889380831</v>
+        <v>13.591457947033861</v>
       </c>
       <c r="O51" s="3">
-        <v>59.49367088607595</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P51" s="3">
         <v>46.744012320672994</v>
       </c>
       <c r="Q51" s="3">
-        <v>49.87341772151899</v>
+        <v>50.25316455696203</v>
       </c>
       <c r="R51" s="3">
         <v>36.39240506329114</v>
@@ -5230,40 +5218,40 @@
         <v>5.3</v>
       </c>
       <c r="C52" s="2">
-        <v>59.49367088607595</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="D52" s="2">
-        <v>6.737735849056604</v>
+        <v>6.766037735849057</v>
       </c>
       <c r="E52" s="2">
         <v>-1.41</v>
       </c>
       <c r="F52" s="2">
-        <v>0.5185182319425945</v>
+        <v>0.556335119489242</v>
       </c>
       <c r="G52" s="2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H52" s="2">
-        <v>68.54</v>
+        <v>71.7</v>
       </c>
       <c r="I52" s="2">
-        <v>79.38</v>
+        <v>86.55</v>
       </c>
       <c r="J52" s="2">
-        <v>0.0471794927930525</v>
+        <v>0.05116104561745051</v>
       </c>
       <c r="K52" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2">
         <v>299</v>
       </c>
       <c r="M52" s="2">
-        <v>0.6083293496235109</v>
+        <v>0.6553415125125013</v>
       </c>
       <c r="N52" s="2">
-        <v>72.86051028929212</v>
+        <v>78.39562661116194</v>
       </c>
       <c r="O52" s="2">
         <v>91.13924050632912</v>
@@ -5272,78 +5260,78 @@
         <v>20.10180966623631</v>
       </c>
       <c r="Q52" s="2">
-        <v>69.74683544303798</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="R52" s="2">
-        <v>61.70886075949366</v>
+        <v>61.77215189873418</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T52" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="1">
         <v>-0.71</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="1">
         <v>16.455696202531644</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="1">
         <v>6.873239436619719</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="1">
         <v>5.43</v>
       </c>
-      <c r="F53" s="3">
-        <v>-0.24531088377401306</v>
-      </c>
-      <c r="G53" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="H53" s="3">
-        <v>40.1</v>
-      </c>
-      <c r="I53" s="3">
-        <v>-29.77</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0.013374429803373878</v>
-      </c>
-      <c r="K53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3">
+      <c r="F53" s="1">
+        <v>-0.3109493603710671</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2.62</v>
+      </c>
+      <c r="H53" s="1">
+        <v>41.32</v>
+      </c>
+      <c r="I53" s="1">
+        <v>-29.04</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.011509910347321772</v>
+      </c>
+      <c r="K53" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
         <v>-13</v>
       </c>
-      <c r="M53" s="3">
-        <v>-0.06678390594487427</v>
-      </c>
-      <c r="N53" s="3">
-        <v>5.349184732453615</v>
-      </c>
-      <c r="O53" s="3">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="P53" s="3">
+      <c r="M53" s="1">
+        <v>-0.12000845954049555</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0.8606294058622744</v>
+      </c>
+      <c r="O53" s="1">
+        <v>40.50632911392405</v>
+      </c>
+      <c r="P53" s="1">
         <v>46.06334900207262</v>
       </c>
-      <c r="Q53" s="3">
-        <v>36.58227848101265</v>
-      </c>
-      <c r="R53" s="3">
-        <v>30.189873417721515</v>
-      </c>
-      <c r="S53" s="3" t="s">
+      <c r="Q53" s="1">
+        <v>35.06329113924051</v>
+      </c>
+      <c r="R53" s="1">
+        <v>27.08860759493671</v>
+      </c>
+      <c r="S53" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="T53" s="3">
-        <v>0</v>
+      <c r="T53" s="1">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5354,7 +5342,7 @@
         <v>0.66</v>
       </c>
       <c r="C54" s="2">
-        <v>36.708860759493675</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="D54" s="2">
         <v>34.06060606060606</v>
@@ -5363,49 +5351,49 @@
         <v>-2.25</v>
       </c>
       <c r="F54" s="2">
-        <v>0.002924203187187252</v>
+        <v>0.00852578710285859</v>
       </c>
       <c r="G54" s="2">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H54" s="2">
-        <v>46.11</v>
+        <v>50.22</v>
       </c>
       <c r="I54" s="2">
-        <v>-4.71</v>
+        <v>-0.29</v>
       </c>
       <c r="J54" s="2">
-        <v>0.01487390105523656</v>
+        <v>0.01582578777085134</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M54" s="2">
-        <v>0.05549656475650422</v>
+        <v>0.06156492622246179</v>
       </c>
       <c r="N54" s="2">
-        <v>17.577231802591463</v>
+        <v>19.01796798215799</v>
       </c>
       <c r="O54" s="2">
-        <v>68.35443037974683</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P54" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q54" s="2">
-        <v>57.59493670886076</v>
+        <v>56.58227848101266</v>
       </c>
       <c r="R54" s="2">
-        <v>52.21518987341773</v>
+        <v>51.455696202531655</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T54" s="2">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5416,7 +5404,7 @@
         <v>4.03</v>
       </c>
       <c r="C55" s="2">
-        <v>56.9620253164557</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="D55" s="2">
         <v>2.3176178660049627</v>
@@ -5425,31 +5413,31 @@
         <v>-2.09</v>
       </c>
       <c r="F55" s="2">
-        <v>0.060163066321827274</v>
+        <v>0.05043589148721053</v>
       </c>
       <c r="G55" s="2">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="H55" s="2">
-        <v>71.65</v>
+        <v>72.52</v>
       </c>
       <c r="I55" s="2">
-        <v>7.49</v>
+        <v>8.21</v>
       </c>
       <c r="J55" s="2">
-        <v>0.012883785857358753</v>
+        <v>0.01354016624185713</v>
       </c>
       <c r="K55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="2">
-        <v>-63</v>
+        <v>-65</v>
       </c>
       <c r="M55" s="2">
-        <v>0.07878244437762705</v>
+        <v>0.07283019467104301</v>
       </c>
       <c r="N55" s="2">
-        <v>19.90581976470373</v>
+        <v>20.14449482701613</v>
       </c>
       <c r="O55" s="2">
         <v>73.41772151898735</v>
@@ -5458,16 +5446,16 @@
         <v>17.353613604156827</v>
       </c>
       <c r="Q55" s="2">
-        <v>57.9746835443038</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="R55" s="2">
-        <v>51.51898734177216</v>
+        <v>51.835443037974684</v>
       </c>
       <c r="S55" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T55" s="2">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5478,7 +5466,7 @@
         <v>8.65</v>
       </c>
       <c r="C56" s="3">
-        <v>74.68354430379746</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="D56" s="3">
         <v>0.18843930635838138</v>
@@ -5487,19 +5475,19 @@
         <v>0.21</v>
       </c>
       <c r="F56" s="3">
-        <v>-0.03972750715007273</v>
+        <v>-0.08088397609813</v>
       </c>
       <c r="G56" s="3">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H56" s="3">
-        <v>66.12</v>
+        <v>50.72</v>
       </c>
       <c r="I56" s="3">
-        <v>12.24</v>
+        <v>7.93</v>
       </c>
       <c r="J56" s="3">
-        <v>-0.002064357080070061</v>
+        <v>-0.0022956135858685878</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>0</v>
@@ -5508,28 +5496,28 @@
         <v>167</v>
       </c>
       <c r="M56" s="3">
-        <v>-0.12296707963482456</v>
+        <v>-0.16928254129746867</v>
       </c>
       <c r="N56" s="3">
-        <v>-0.26913263654142544</v>
+        <v>-4.066778769835045</v>
       </c>
       <c r="O56" s="3">
-        <v>39.24050632911392</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P56" s="3">
         <v>10.95912073621325</v>
       </c>
       <c r="Q56" s="3">
-        <v>51.0126582278481</v>
+        <v>45.189873417721515</v>
       </c>
       <c r="R56" s="3">
-        <v>38.54430379746835</v>
+        <v>35.88607594936709</v>
       </c>
       <c r="S56" s="3" t="s">
         <v>115</v>
       </c>
       <c r="T56" s="3">
-        <v>0</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5543,37 +5531,37 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.797450424929179</v>
+        <v>2.9485363550519357</v>
       </c>
       <c r="E57" s="2">
         <v>-1.92</v>
       </c>
       <c r="F57" s="2">
-        <v>1.0562201784523069</v>
+        <v>1.1899045590932</v>
       </c>
       <c r="G57" s="2">
         <v>2.16</v>
       </c>
       <c r="H57" s="2">
-        <v>60.77</v>
+        <v>66.14</v>
       </c>
       <c r="I57" s="2">
-        <v>157.16</v>
+        <v>176.92</v>
       </c>
       <c r="J57" s="2">
-        <v>0.09765329786120983</v>
+        <v>0.09977261592336065</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M57" s="2">
-        <v>1.183270052244823</v>
+        <v>1.3266276732681772</v>
       </c>
       <c r="N57" s="2">
-        <v>130.35458055142334</v>
+        <v>145.5242426867295</v>
       </c>
       <c r="O57" s="2">
         <v>93.67088607594937</v>
@@ -5582,16 +5570,16 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q57" s="2">
-        <v>80.75949367088607</v>
+        <v>82.15189873417721</v>
       </c>
       <c r="R57" s="2">
-        <v>67.27848101265823</v>
+        <v>67.53164556962025</v>
       </c>
       <c r="S57" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T57" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5602,7 +5590,7 @@
         <v>20.1</v>
       </c>
       <c r="C58" s="2">
-        <v>94.9367088607595</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="D58" s="2">
         <v>0.09900497512437803</v>
@@ -5611,19 +5599,19 @@
         <v>-1</v>
       </c>
       <c r="F58" s="2">
-        <v>0.12718350609419177</v>
+        <v>0.16918926990790614</v>
       </c>
       <c r="G58" s="2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H58" s="2">
-        <v>54.56</v>
+        <v>61.15</v>
       </c>
       <c r="I58" s="2">
-        <v>38.02</v>
+        <v>43.62</v>
       </c>
       <c r="J58" s="2">
-        <v>0.02369851970661783</v>
+        <v>0.02424541368332005</v>
       </c>
       <c r="K58" s="2" t="b">
         <v>0</v>
@@ -5632,28 +5620,28 @@
         <v>268</v>
       </c>
       <c r="M58" s="2">
-        <v>0.19180370052314388</v>
+        <v>0.2399081220673771</v>
       </c>
       <c r="N58" s="2">
-        <v>31.207945379255413</v>
+        <v>36.85228756664954</v>
       </c>
       <c r="O58" s="2">
-        <v>81.0126582278481</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P58" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q58" s="2">
-        <v>65.18987341772151</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="R58" s="2">
-        <v>60</v>
+        <v>60.9493670886076</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T58" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5673,19 +5661,19 @@
         <v>-1.03</v>
       </c>
       <c r="F59" s="3">
-        <v>0.030692772753419806</v>
+        <v>0.0704784520071017</v>
       </c>
       <c r="G59" s="3">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="H59" s="3">
-        <v>44.11</v>
+        <v>53.03</v>
       </c>
       <c r="I59" s="3">
-        <v>23.08</v>
+        <v>30.08</v>
       </c>
       <c r="J59" s="3">
-        <v>0.005105688176290398</v>
+        <v>0.005885000866749586</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
@@ -5694,28 +5682,28 @@
         <v>367</v>
       </c>
       <c r="M59" s="3">
-        <v>0.04821689327652545</v>
+        <v>0.07872898475904</v>
       </c>
       <c r="N59" s="3">
-        <v>16.849264654593583</v>
+        <v>20.73437383581582</v>
       </c>
       <c r="O59" s="3">
-        <v>64.55696202531645</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P59" s="3">
         <v>24.570041255395854</v>
       </c>
       <c r="Q59" s="3">
-        <v>51.64556962025316</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="R59" s="3">
-        <v>45.949367088607595</v>
+        <v>48.9873417721519</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>94</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5726,7 +5714,7 @@
         <v>6.37</v>
       </c>
       <c r="C60" s="1">
-        <v>67.08860759493672</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="D60" s="1">
         <v>-0.18210361067503927</v>
@@ -5735,19 +5723,19 @@
         <v>0.23</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.14781499880780213</v>
+        <v>-0.12254475509947456</v>
       </c>
       <c r="G60" s="1">
         <v>0.36</v>
       </c>
       <c r="H60" s="1">
-        <v>43.2</v>
+        <v>49.19</v>
       </c>
       <c r="I60" s="1">
-        <v>-4.03</v>
+        <v>-2.65</v>
       </c>
       <c r="J60" s="1">
-        <v>-0.007203039194653449</v>
+        <v>-0.007223171177232919</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
@@ -5756,28 +5744,28 @@
         <v>101</v>
       </c>
       <c r="M60" s="1">
-        <v>-0.21791148090022472</v>
+        <v>-0.19797819740291023</v>
       </c>
       <c r="N60" s="1">
-        <v>-9.763572763081443</v>
+        <v>-6.936344380379202</v>
       </c>
       <c r="O60" s="1">
-        <v>22.78481012658228</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P60" s="1">
         <v>17.48490342947292</v>
       </c>
       <c r="Q60" s="1">
-        <v>37.08860759493671</v>
+        <v>36.70886075949367</v>
       </c>
       <c r="R60" s="1">
-        <v>28.101265822784814</v>
+        <v>28.60759493670886</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T60" s="1">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5788,7 +5776,7 @@
         <v>17.65</v>
       </c>
       <c r="C61" s="3">
-        <v>92.40506329113924</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="D61" s="3">
         <v>0.46515580736543916</v>
@@ -5797,19 +5785,19 @@
         <v>-1.16</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.11045310133014175</v>
+        <v>-0.09066052851141675</v>
       </c>
       <c r="G61" s="3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H61" s="3">
-        <v>54.05</v>
+        <v>55.74</v>
       </c>
       <c r="I61" s="3">
-        <v>9.92</v>
+        <v>10.6</v>
       </c>
       <c r="J61" s="3">
-        <v>0.0006912634267952529</v>
+        <v>0.0014107865212750752</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>0</v>
@@ -5818,28 +5806,28 @@
         <v>171</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.12031041912438867</v>
+        <v>-0.1000897087993462</v>
       </c>
       <c r="N61" s="3">
-        <v>-0.003466585497835498</v>
+        <v>2.8525044799772097</v>
       </c>
       <c r="O61" s="3">
-        <v>40.50632911392405</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P61" s="3">
         <v>20.131624188012864</v>
       </c>
       <c r="Q61" s="3">
-        <v>56.07594936708861</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="R61" s="3">
-        <v>43.22784810126582</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5859,19 +5847,19 @@
         <v>-4.88</v>
       </c>
       <c r="F62" s="4">
-        <v>1.4420935594906092</v>
+        <v>1.4170687167277918</v>
       </c>
       <c r="G62" s="4">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="H62" s="4">
-        <v>70.6</v>
+        <v>73.2</v>
       </c>
       <c r="I62" s="4">
-        <v>245.53</v>
+        <v>253.44</v>
       </c>
       <c r="J62" s="4">
-        <v>0.09617614977172315</v>
+        <v>0.10071815716550868</v>
       </c>
       <c r="K62" s="4" t="b">
         <v>0</v>
@@ -5880,10 +5868,10 @@
         <v>476</v>
       </c>
       <c r="M62" s="4">
-        <v>1.872529769839392</v>
+        <v>1.8743839606923707</v>
       </c>
       <c r="N62" s="4">
-        <v>199.2805523108802</v>
+        <v>200.29987142914888</v>
       </c>
       <c r="O62" s="4">
         <v>100</v>
@@ -5892,16 +5880,16 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q62" s="4">
-        <v>84.55696202531647</v>
+        <v>85.44303797468353</v>
       </c>
       <c r="R62" s="4">
-        <v>72.59493670886076</v>
+        <v>72.91139240506328</v>
       </c>
       <c r="S62" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T62" s="4">
-        <v>-0.13</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5912,28 +5900,28 @@
         <v>10.54</v>
       </c>
       <c r="C63" s="2">
-        <v>78.48101265822784</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="D63" s="2">
-        <v>6.877609108159394</v>
+        <v>6.978178368121444</v>
       </c>
       <c r="E63" s="2">
         <v>-2.76</v>
       </c>
       <c r="F63" s="2">
-        <v>1.1878522127229045</v>
+        <v>1.4246922060771565</v>
       </c>
       <c r="G63" s="2">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H63" s="2">
-        <v>64.28</v>
+        <v>73.71</v>
       </c>
       <c r="I63" s="2">
-        <v>130.29</v>
+        <v>158.37</v>
       </c>
       <c r="J63" s="2">
-        <v>0.07212697037883466</v>
+        <v>0.07524095676433057</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
@@ -5942,10 +5930,10 @@
         <v>206</v>
       </c>
       <c r="M63" s="2">
-        <v>1.3061400262538676</v>
+        <v>1.550807492428213</v>
       </c>
       <c r="N63" s="2">
-        <v>142.64157795232782</v>
+        <v>167.94222460273312</v>
       </c>
       <c r="O63" s="2">
         <v>94.9367088607595</v>
@@ -5954,16 +5942,16 @@
         <v>20.9978319173529</v>
       </c>
       <c r="Q63" s="2">
-        <v>77.59493670886076</v>
+        <v>78.73417721518987</v>
       </c>
       <c r="R63" s="2">
-        <v>68.54430379746836</v>
+        <v>68.35443037974684</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T63" s="2">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5974,7 +5962,7 @@
         <v>16.87</v>
       </c>
       <c r="C64" s="3">
-        <v>89.87341772151899</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="D64" s="3">
         <v>-0.28986366330764674</v>
@@ -5983,19 +5971,19 @@
         <v>-1.13</v>
       </c>
       <c r="F64" s="3">
-        <v>-0.09671219613671744</v>
+        <v>-0.07909457868523909</v>
       </c>
       <c r="G64" s="3">
         <v>0.31</v>
       </c>
       <c r="H64" s="3">
-        <v>53.84</v>
+        <v>54.67</v>
       </c>
       <c r="I64" s="3">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="J64" s="3">
-        <v>-0.0004284358406020467</v>
+        <v>0.0006404470192988076</v>
       </c>
       <c r="K64" s="3" t="b">
         <v>0</v>
@@ -6004,28 +5992,28 @@
         <v>56</v>
       </c>
       <c r="M64" s="3">
-        <v>-0.17228496589261055</v>
+        <v>-0.16042125866863066</v>
       </c>
       <c r="N64" s="3">
-        <v>-5.2009212623200245</v>
+        <v>-3.1806505069512445</v>
       </c>
       <c r="O64" s="3">
-        <v>32.91139240506329</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P64" s="3">
         <v>15.211254913322609</v>
       </c>
       <c r="Q64" s="3">
-        <v>50.12658227848101</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R64" s="3">
-        <v>38.41772151898734</v>
+        <v>38.924050632911396</v>
       </c>
       <c r="S64" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="3">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6036,7 +6024,7 @@
         <v>16.51</v>
       </c>
       <c r="C65" s="1">
-        <v>87.34177215189874</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="D65" s="1">
         <v>-0.09085402786190197</v>
@@ -6045,19 +6033,19 @@
         <v>-0.08</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.49128671708205174</v>
+        <v>-0.5140003910942923</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H65" s="1">
-        <v>32.59</v>
+        <v>34.17</v>
       </c>
       <c r="I65" s="1">
-        <v>-47.9</v>
+        <v>-47</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.03690685781363573</v>
+        <v>-0.03813979562715102</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
@@ -6066,10 +6054,10 @@
         <v>-199</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.49128671708205174</v>
+        <v>-0.5163576861662746</v>
       </c>
       <c r="N65" s="1">
-        <v>-37.101096381264135</v>
+        <v>-38.774293256715644</v>
       </c>
       <c r="O65" s="1">
         <v>1.2658227848101267</v>
@@ -6078,7 +6066,7 @@
         <v>50.931782654789714</v>
       </c>
       <c r="Q65" s="1">
-        <v>32.27848101265823</v>
+        <v>32.278481012658226</v>
       </c>
       <c r="R65" s="1">
         <v>16.89873417721519</v>
@@ -6098,7 +6086,7 @@
         <v>4.01</v>
       </c>
       <c r="C66" s="3">
-        <v>55.69620253164557</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="D66" s="3">
         <v>7.221945137157108</v>
@@ -6107,19 +6095,19 @@
         <v>-1.7</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.19451257399131322</v>
+        <v>-0.19591448350607013</v>
       </c>
       <c r="G66" s="3">
         <v>1.12</v>
       </c>
       <c r="H66" s="3">
-        <v>38.78</v>
+        <v>53.72</v>
       </c>
       <c r="I66" s="3">
-        <v>-16.57</v>
+        <v>-10.97</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.001583957620276913</v>
+        <v>-0.001098775231587882</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
@@ -6128,28 +6116,28 @@
         <v>-75</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.18136948359898397</v>
+        <v>-0.18177071307417592</v>
       </c>
       <c r="N66" s="3">
-        <v>-6.10937303295736</v>
+        <v>-5.315595947505765</v>
       </c>
       <c r="O66" s="3">
         <v>27.848101265822784</v>
       </c>
       <c r="P66" s="3">
-        <v>19.139656046926937</v>
+        <v>18.57346443046155</v>
       </c>
       <c r="Q66" s="3">
-        <v>44.68354430379747</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="R66" s="3">
-        <v>37.911392405063296</v>
+        <v>38.41772151898734</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T66" s="3">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6160,58 +6148,58 @@
         <v>7.35</v>
       </c>
       <c r="C67" s="3">
-        <v>69.62025316455697</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="D67" s="3">
-        <v>330.17278911564625</v>
+        <v>331.58775510204083</v>
       </c>
       <c r="E67" s="3">
         <v>-1.49</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.18288640291441538</v>
+        <v>-0.18480245132414647</v>
       </c>
       <c r="G67" s="3">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H67" s="3">
-        <v>40.4</v>
+        <v>41.02</v>
       </c>
       <c r="I67" s="3">
-        <v>-2.76</v>
+        <v>-3.03</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.009032533675992323</v>
+        <v>-0.0098167248810661</v>
       </c>
       <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.2540781425395321</v>
+        <v>-0.2625931886995645</v>
       </c>
       <c r="N67" s="3">
-        <v>-13.380238927012181</v>
+        <v>-13.397843510044623</v>
       </c>
       <c r="O67" s="3">
-        <v>17.72151898734177</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P67" s="3">
         <v>22.02824070768656</v>
       </c>
       <c r="Q67" s="3">
-        <v>59.74683544303797</v>
+        <v>56.32911392405063</v>
       </c>
       <c r="R67" s="3">
-        <v>44.683544303797476</v>
+        <v>43.54430379746835</v>
       </c>
       <c r="S67" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T67" s="3">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6222,28 +6210,28 @@
         <v>8.24</v>
       </c>
       <c r="C68" s="1">
-        <v>72.15189873417721</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="D68" s="1">
-        <v>0.6152912621359223</v>
+        <v>0.54126213592233</v>
       </c>
       <c r="E68" s="1">
         <v>-1.22</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.298967640507375</v>
+        <v>-0.31532576038557225</v>
       </c>
       <c r="G68" s="1">
         <v>1.45</v>
       </c>
       <c r="H68" s="1">
-        <v>40.42</v>
+        <v>45.22</v>
       </c>
       <c r="I68" s="1">
-        <v>-16.44</v>
+        <v>-14.8</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.009750199688245847</v>
+        <v>-0.009023979996625962</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6252,28 +6240,28 @@
         <v>-69</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2496810515361404</v>
+        <v>-0.262286621265969</v>
       </c>
       <c r="N68" s="1">
-        <v>-12.940529826673005</v>
+        <v>-13.367186766685077</v>
       </c>
       <c r="O68" s="1">
-        <v>18.9873417721519</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P68" s="1">
-        <v>25.684418695243096</v>
+        <v>23.92352836551796</v>
       </c>
       <c r="Q68" s="1">
-        <v>40</v>
+        <v>38.35443037974684</v>
       </c>
       <c r="R68" s="1">
-        <v>28.797468354430375</v>
+        <v>28.227848101265828</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T68" s="1">
-        <v>0.25</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6284,7 +6272,7 @@
         <v>18.19</v>
       </c>
       <c r="C69" s="3">
-        <v>93.67088607594937</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="D69" s="3">
         <v>-0.4843320505772402</v>
@@ -6293,19 +6281,19 @@
         <v>-2.56</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.0964299876978872</v>
+        <v>-0.10430077299850737</v>
       </c>
       <c r="G69" s="3">
         <v>0.88</v>
       </c>
       <c r="H69" s="3">
-        <v>48.17</v>
+        <v>51.12</v>
       </c>
       <c r="I69" s="3">
-        <v>-10.81</v>
+        <v>-9.54</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.0015674620618146102</v>
+        <v>-0.0014627186769465284</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
@@ -6314,28 +6302,28 @@
         <v>-63</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.10957307809021644</v>
+        <v>-0.11844454343040156</v>
       </c>
       <c r="N69" s="3">
-        <v>1.0702675179193921</v>
+        <v>1.0170210168716756</v>
       </c>
       <c r="O69" s="3">
-        <v>43.037974683544306</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P69" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q69" s="3">
-        <v>46.70886075949367</v>
+        <v>45.44303797468355</v>
       </c>
       <c r="R69" s="3">
-        <v>35.822784810126585</v>
+        <v>34.93670886075949</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T69" s="3">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6346,7 +6334,7 @@
         <v>1.52</v>
       </c>
       <c r="C70" s="1">
-        <v>45.56962025316456</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="D70" s="1">
         <v>13.157894736842104</v>
@@ -6355,31 +6343,31 @@
         <v>-1.41</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.298883002805443</v>
+        <v>-0.30958501752881185</v>
       </c>
       <c r="G70" s="1">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H70" s="1">
-        <v>51.57</v>
+        <v>54.78</v>
       </c>
       <c r="I70" s="1">
-        <v>-24.36</v>
+        <v>-22.74</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.01312031494827248</v>
+        <v>-0.00858662388860459</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>-98</v>
+        <v>-99</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.28793042747850195</v>
+        <v>-0.29661989463290883</v>
       </c>
       <c r="N70" s="1">
-        <v>-16.765467420909165</v>
+        <v>-16.80051410337906</v>
       </c>
       <c r="O70" s="1">
         <v>10.126582278481013</v>
@@ -6388,16 +6376,16 @@
         <v>36.16826599829714</v>
       </c>
       <c r="Q70" s="1">
-        <v>44.68354430379746</v>
+        <v>46.32911392405064</v>
       </c>
       <c r="R70" s="1">
-        <v>25.822784810126585</v>
+        <v>26.32911392405063</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>119</v>
       </c>
       <c r="T70" s="1">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6408,58 +6396,58 @@
         <v>5.18</v>
       </c>
       <c r="C71" s="3">
-        <v>58.22784810126582</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="D71" s="3">
-        <v>0.7702702702702704</v>
+        <v>0.7953667953667956</v>
       </c>
       <c r="E71" s="3">
         <v>-0.08</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.0715211144046819</v>
+        <v>-0.049428578185401834</v>
       </c>
       <c r="G71" s="3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H71" s="3">
-        <v>66.12</v>
+        <v>70.52</v>
       </c>
       <c r="I71" s="3">
-        <v>0.47</v>
+        <v>2.17</v>
       </c>
       <c r="J71" s="3">
-        <v>0.008550348786368199</v>
+        <v>0.009573891146575371</v>
       </c>
       <c r="K71" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="3">
         <v>-68</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.0715211144046819</v>
+        <v>-0.04824993064941063</v>
       </c>
       <c r="N71" s="3">
-        <v>4.8754638864728355</v>
+        <v>8.036482294970765</v>
       </c>
       <c r="O71" s="3">
-        <v>49.36708860759494</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P71" s="3">
         <v>19.13407224404345</v>
       </c>
       <c r="Q71" s="3">
-        <v>54.0506329113924</v>
+        <v>54.30379746835443</v>
       </c>
       <c r="R71" s="3">
-        <v>42.21518987341773</v>
+        <v>43.79746835443039</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T71" s="3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6470,7 +6458,7 @@
         <v>10.42</v>
       </c>
       <c r="C72" s="3">
-        <v>77.21518987341773</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="D72" s="3">
         <v>0.19865642994241844</v>
@@ -6479,31 +6467,31 @@
         <v>-1.66</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.1389836947724572</v>
+        <v>-0.1412091452908454</v>
       </c>
       <c r="G72" s="3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H72" s="3">
-        <v>56.15</v>
+        <v>59.03</v>
       </c>
       <c r="I72" s="3">
-        <v>-5.48</v>
+        <v>-4.01</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.00307224751560727</v>
+        <v>-0.001489275694968476</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L72" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.12803111944551615</v>
+        <v>-0.1270653748589512</v>
       </c>
       <c r="N72" s="3">
-        <v>-0.7755366176105838</v>
+        <v>0.15493787401670858</v>
       </c>
       <c r="O72" s="3">
         <v>37.9746835443038</v>
@@ -6515,13 +6503,13 @@
         <v>46.962025316455694</v>
       </c>
       <c r="R72" s="3">
-        <v>36.07594936708861</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T72" s="3">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6529,310 +6517,302 @@
         <v>120</v>
       </c>
       <c r="B73" s="2">
-        <v>0.61</v>
+        <v>2.35</v>
       </c>
       <c r="C73" s="2">
-        <v>35.44303797468354</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="D73" s="2">
-        <v>20.37704918032787</v>
+        <v>7.055319148936169</v>
       </c>
       <c r="E73" s="2">
-        <v>2.89</v>
+        <v>5.09</v>
       </c>
       <c r="F73" s="2">
-        <v>0.37784003175339287</v>
+        <v>0.32097408844820413</v>
       </c>
       <c r="G73" s="2">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H73" s="2">
-        <v>62.3</v>
+        <v>61.07</v>
       </c>
       <c r="I73" s="2">
-        <v>52.02</v>
+        <v>37.69</v>
       </c>
       <c r="J73" s="2">
-        <v>0.031672006329449394</v>
+        <v>0.032403048112695954</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M73" s="2">
-        <v>0.39426889474380444</v>
+        <v>0.3256886785921689</v>
       </c>
       <c r="N73" s="2">
-        <v>51.454464801321485</v>
+        <v>45.4303432191287</v>
       </c>
       <c r="O73" s="2">
-        <v>86.07594936708861</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P73" s="2">
-        <v>9.507882188735834</v>
+        <v>20.30977785396255</v>
       </c>
       <c r="Q73" s="2">
-        <v>66.32911392405063</v>
+        <v>64.17721518987341</v>
       </c>
       <c r="R73" s="2">
-        <v>60.94936708860761</v>
+        <v>57.72151898734177</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T73" s="2">
-        <v>0</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="T73" s="2"/>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B74" s="2">
-        <v>0.96</v>
+        <v>17.38</v>
       </c>
       <c r="C74" s="2">
-        <v>39.24050632911392</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="D74" s="2">
-        <v>12.072916666666668</v>
+        <v>-0.4602991944764096</v>
       </c>
       <c r="E74" s="2">
-        <v>0.98</v>
+        <v>1.55</v>
       </c>
       <c r="F74" s="2">
-        <v>0.07530110050645825</v>
+        <v>0.13362137139026073</v>
       </c>
       <c r="G74" s="2">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H74" s="2">
-        <v>71.42</v>
+        <v>61.75</v>
       </c>
       <c r="I74" s="2">
-        <v>26.74</v>
+        <v>9.64</v>
       </c>
       <c r="J74" s="2">
-        <v>0.015780199617998404</v>
+        <v>0.01989175510132392</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="2">
-        <v>13</v>
+        <v>-2</v>
       </c>
       <c r="M74" s="2">
-        <v>0.051205434787187976</v>
+        <v>0.13715731399823428</v>
       </c>
       <c r="N74" s="2">
-        <v>17.14811880565982</v>
+        <v>26.577206759735244</v>
       </c>
       <c r="O74" s="2">
-        <v>67.08860759493672</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P74" s="2">
-        <v>3.6747023875523213</v>
+        <v>23.852303543083593</v>
       </c>
       <c r="Q74" s="2">
-        <v>63.41772151898734</v>
+        <v>60.75949367088607</v>
       </c>
       <c r="R74" s="2">
-        <v>53.41772151898735</v>
+        <v>53.417721518987335</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="T74" s="2">
-        <v>0</v>
-      </c>
+      <c r="T74" s="2"/>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="3">
-        <v>0.44</v>
-      </c>
-      <c r="C75" s="3">
-        <v>34.177215189873415</v>
-      </c>
-      <c r="D75" s="3">
-        <v>29.204545454545453</v>
-      </c>
-      <c r="E75" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F75" s="3">
-        <v>-0.0194711889625461</v>
-      </c>
-      <c r="G75" s="3">
+      <c r="B75" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="C75" s="2">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="D75" s="2">
+        <v>207.90243902439028</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2.71</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0.05476574050182323</v>
+      </c>
+      <c r="G75" s="2">
+        <v>1.11</v>
+      </c>
+      <c r="H75" s="2">
+        <v>63.97</v>
+      </c>
+      <c r="I75" s="2">
+        <v>8.69</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0.017654528845582978</v>
+      </c>
+      <c r="K75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2">
+        <v>11</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0.06773086339772627</v>
+      </c>
+      <c r="N75" s="2">
+        <v>19.634561699684454</v>
+      </c>
+      <c r="O75" s="2">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="P75" s="2">
+        <v>25.0383224064444</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>65.69620253164557</v>
+      </c>
+      <c r="R75" s="2">
+        <v>54.620253164556964</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="T75" s="2"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="C76" s="2">
+        <v>36.708860759493675</v>
+      </c>
+      <c r="D76" s="2">
+        <v>12.072916666666668</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0.05578548121298342</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="H76" s="2">
+        <v>69.77</v>
+      </c>
+      <c r="I76" s="2">
+        <v>26.26</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0.015310849162628181</v>
+      </c>
+      <c r="K76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2">
+        <v>13</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0.029855235421177406</v>
+      </c>
+      <c r="N76" s="2">
+        <v>15.84699890202956</v>
+      </c>
+      <c r="O76" s="2">
+        <v>63.29113924050633</v>
+      </c>
+      <c r="P76" s="2">
+        <v>3.6747023875523213</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>61.898734177215196</v>
+      </c>
+      <c r="R76" s="2">
+        <v>51.77215189873418</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T76" s="2">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="3">
+        <v>20.88</v>
+      </c>
+      <c r="C77" s="3">
+        <v>94.9367088607595</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-0.7102490421455938</v>
+      </c>
+      <c r="E77" s="3">
+        <v>-0.4</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.017325521218239492</v>
+      </c>
+      <c r="G77" s="3">
         <v>0.99</v>
       </c>
-      <c r="H75" s="3">
-        <v>34.3</v>
-      </c>
-      <c r="I75" s="3">
-        <v>-2.05</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0.014421107548793829</v>
-      </c>
-      <c r="K75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L75" s="3">
-        <v>21</v>
-      </c>
-      <c r="M75" s="3">
-        <v>-0.020566446495240198</v>
-      </c>
-      <c r="N75" s="3">
-        <v>9.970930677417016</v>
-      </c>
-      <c r="O75" s="3">
-        <v>54.43037974683544</v>
-      </c>
-      <c r="P75" s="3">
-        <v>36.964149129985884</v>
-      </c>
-      <c r="Q75" s="3">
-        <v>52.40506329113924</v>
-      </c>
-      <c r="R75" s="3">
-        <v>43.67088607594937</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="T75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B76" s="3">
-        <v>2.05</v>
-      </c>
-      <c r="C76" s="3">
-        <v>48.10126582278481</v>
-      </c>
-      <c r="D76" s="3">
-        <v>0.7170731707317075</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-0.21</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0.15929428610072854</v>
-      </c>
-      <c r="G76" s="3">
-        <v>0.66</v>
-      </c>
-      <c r="H76" s="3">
-        <v>67.38</v>
-      </c>
-      <c r="I76" s="3">
-        <v>17.8</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0.012413742307556805</v>
-      </c>
-      <c r="K76" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
-        <v>0.12205552998912905</v>
-      </c>
-      <c r="N76" s="3">
-        <v>24.233128325853944</v>
-      </c>
-      <c r="O76" s="3">
-        <v>78.48101265822784</v>
-      </c>
-      <c r="P76" s="3">
-        <v>16.982798273104898</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>53.16455696202532</v>
-      </c>
-      <c r="R76" s="3">
-        <v>48.60759493670886</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B77" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="C77" s="2">
-        <v>31.645569620253166</v>
-      </c>
-      <c r="D77" s="2">
-        <v>281.33333333333337</v>
-      </c>
-      <c r="E77" s="2">
-        <v>2.11</v>
-      </c>
-      <c r="F77" s="2">
-        <v>0.1965352731107456</v>
-      </c>
-      <c r="G77" s="2">
-        <v>0.96</v>
-      </c>
-      <c r="H77" s="2">
-        <v>75.62</v>
-      </c>
-      <c r="I77" s="2">
-        <v>23.47</v>
-      </c>
-      <c r="J77" s="2">
-        <v>0.025525618178329417</v>
-      </c>
-      <c r="K77" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" s="2">
-        <v>6</v>
-      </c>
-      <c r="M77" s="2">
-        <v>0.1921542429799692</v>
-      </c>
-      <c r="N77" s="2">
-        <v>31.24299962493795</v>
-      </c>
-      <c r="O77" s="2">
-        <v>82.27848101265823</v>
-      </c>
-      <c r="P77" s="2">
-        <v>8.54788795515236</v>
-      </c>
-      <c r="Q77" s="2">
-        <v>70.37974683544304</v>
-      </c>
-      <c r="R77" s="2">
-        <v>63.0379746835443</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="T77" s="2">
-        <v>0</v>
-      </c>
+      <c r="H77" s="3">
+        <v>67.89</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="J77" s="3">
+        <v>0.008725483306200415</v>
+      </c>
+      <c r="K77" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3">
+        <v>25</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0.01614687368224832</v>
+      </c>
+      <c r="N77" s="3">
+        <v>14.476162728136648</v>
+      </c>
+      <c r="O77" s="3">
+        <v>60.75949367088608</v>
+      </c>
+      <c r="P77" s="3">
+        <v>12.27047093905827</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>57.721518987341774</v>
+      </c>
+      <c r="R77" s="3">
+        <v>49.93670886075949</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T77" s="3"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -6842,7 +6822,7 @@
         <v>13.11</v>
       </c>
       <c r="C78" s="3">
-        <v>84.81012658227847</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="D78" s="3">
         <v>-0.7337909992372235</v>
@@ -6851,19 +6831,19 @@
         <v>0</v>
       </c>
       <c r="F78" s="3">
-        <v>0.041522766450808546</v>
+        <v>0.03900179597051556</v>
       </c>
       <c r="G78" s="3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H78" s="3">
-        <v>43.44</v>
+        <v>49.89</v>
       </c>
       <c r="I78" s="3">
-        <v>16.47</v>
+        <v>18.62</v>
       </c>
       <c r="J78" s="3">
-        <v>0.021720040522551956</v>
+        <v>0.02014468829151593</v>
       </c>
       <c r="K78" s="3" t="b">
         <v>0</v>
@@ -6872,10 +6852,10 @@
         <v>59</v>
       </c>
       <c r="M78" s="3">
-        <v>0.06780894723546704</v>
+        <v>0.06611068929831276</v>
       </c>
       <c r="N78" s="3">
-        <v>18.80847005048773</v>
+        <v>19.4725442897431</v>
       </c>
       <c r="O78" s="3">
         <v>70.88607594936708</v>
@@ -6884,16 +6864,16 @@
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="3">
-        <v>54.177215189873415</v>
+        <v>54.05063291139241</v>
       </c>
       <c r="R78" s="3">
-        <v>49.620253164556964</v>
+        <v>49.24050632911393</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="3">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6904,7 +6884,7 @@
         <v>3.07</v>
       </c>
       <c r="C79" s="2">
-        <v>50.63291139240506</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="D79" s="2">
         <v>2.872964169381108</v>
@@ -6913,19 +6893,19 @@
         <v>-0.31</v>
       </c>
       <c r="F79" s="2">
-        <v>0.42574742614164673</v>
+        <v>0.3976209351219777</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
       </c>
       <c r="H79" s="2">
-        <v>59.03</v>
+        <v>57.59</v>
       </c>
       <c r="I79" s="2">
-        <v>48.34</v>
+        <v>46.38</v>
       </c>
       <c r="J79" s="2">
-        <v>0.04329447329972292</v>
+        <v>0.04280599462878057</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6934,28 +6914,28 @@
         <v>83</v>
       </c>
       <c r="M79" s="2">
-        <v>0.42574742614164673</v>
+        <v>0.3976209351219777</v>
       </c>
       <c r="N79" s="2">
-        <v>54.60231794110572</v>
+        <v>52.623568872109594</v>
       </c>
       <c r="O79" s="2">
-        <v>88.60759493670885</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>63.03797468354429</v>
+        <v>61.89873417721519</v>
       </c>
       <c r="R79" s="2">
-        <v>58.9873417721519</v>
+        <v>58.10126582278481</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6966,40 +6946,40 @@
         <v>12.58</v>
       </c>
       <c r="C80" s="2">
-        <v>82.27848101265823</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="D80" s="2">
-        <v>0.6033386327503976</v>
+        <v>0.6025437201907791</v>
       </c>
       <c r="E80" s="2">
         <v>-2.26</v>
       </c>
       <c r="F80" s="2">
-        <v>1.4536327400417541</v>
+        <v>1.5374156575856517</v>
       </c>
       <c r="G80" s="2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H80" s="2">
-        <v>64.53</v>
+        <v>68.02</v>
       </c>
       <c r="I80" s="2">
-        <v>135.53</v>
+        <v>144.83</v>
       </c>
       <c r="J80" s="2">
-        <v>0.09044197812161316</v>
+        <v>0.09050464468130455</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M80" s="2">
-        <v>1.4886809810879655</v>
+        <v>1.5739537312013783</v>
       </c>
       <c r="N80" s="2">
-        <v>160.89567343573756</v>
+        <v>170.25684848004965</v>
       </c>
       <c r="O80" s="2">
         <v>96.20253164556962</v>
@@ -7008,16 +6988,16 @@
         <v>20.630527651660007</v>
       </c>
       <c r="Q80" s="2">
-        <v>72.27848101265823</v>
+        <v>72.78481012658227</v>
       </c>
       <c r="R80" s="2">
-        <v>64.30379746835445</v>
+        <v>64.74683544303798</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>0</v>
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -7044,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25.379746835443036</v>
+        <v>22.59493670886076</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7052,7 +7032,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65</v>
+        <v>64.81012658227849</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7060,7 +7040,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>43.607594936708864</v>
+        <v>44.49367088607595</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7068,7 +7048,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>45.25316455696203</v>
+        <v>45.063291139240505</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7056,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24.493670886075954</v>
+        <v>22.27848101265823</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7064,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>53.67088607594937</v>
+        <v>52.848101265822784</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7072,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>54.43037974683544</v>
+        <v>53.92405063291139</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7080,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31.708860759493664</v>
+        <v>31.202531645569614</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7088,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.291139240506325</v>
+        <v>39.620253164556964</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7096,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>41.139240506329116</v>
+        <v>42.65822784810127</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7104,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>49.36708860759494</v>
+        <v>49.74683544303798</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7112,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.6329113924050613</v>
+        <v>2.405063291139239</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7120,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>51.89873417721519</v>
+        <v>51.8354430379747</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7128,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>61.139240506329116</v>
+        <v>60.50632911392406</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7136,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.518987341772156</v>
+        <v>30.696202531645575</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7164,7 +7144,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25.443037974683545</v>
+        <v>26.265822784810123</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7152,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>47.34177215189874</v>
+        <v>46.20253164556962</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7160,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>45.31645569620254</v>
+        <v>45.31645569620253</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7168,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>40.88607594936709</v>
+        <v>42.53164556962026</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7176,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>52.025316455696206</v>
+        <v>48.60759493670886</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7184,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>47.53164556962025</v>
+        <v>49.43037974683545</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7192,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>31.51898734177215</v>
+        <v>33.417721518987335</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7200,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>3.227848101265824</v>
+        <v>2.974683544303799</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7208,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>-0.37974683544303645</v>
+        <v>-1.0126582278480996</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7216,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33.73417721518988</v>
+        <v>32.84810126582279</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7224,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>19.87341772151899</v>
+        <v>19.430379746835442</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7232,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>17.65822784810127</v>
+        <v>18.291139240506332</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7240,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>34.0506329113924</v>
+        <v>37.911392405063296</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7248,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>51.83544303797468</v>
+        <v>51.962025316455694</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7256,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>56.58227848101266</v>
+        <v>56.20253164556962</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7264,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>34.936708860759495</v>
+        <v>30.18987341772152</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7272,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37.911392405063296</v>
+        <v>37.151898734177216</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7280,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>50.063291139240505</v>
+        <v>50.82278481012659</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7288,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>24.62025316455696</v>
+        <v>22.405063291139236</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7296,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>25.253164556962023</v>
+        <v>28.9240506329114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7304,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>25.316455696202535</v>
+        <v>25.632911392405063</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7312,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>57.53164556962025</v>
+        <v>57.658227848101255</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7320,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>30.316455696202535</v>
+        <v>30.56962025316456</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7328,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>9.93670886075949</v>
+        <v>10.443037974683545</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7336,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>38.48101265822785</v>
+        <v>39.936708860759495</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7344,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>34.87341772151899</v>
+        <v>34.17721518987342</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7352,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>43.924050632911396</v>
+        <v>38.924050632911396</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7360,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>30.949367088607595</v>
+        <v>30.886075949367086</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7368,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>50.75949367088607</v>
+        <v>51.64556962025317</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7376,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>21.962025316455694</v>
+        <v>21.835443037974684</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7384,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>26.139240506329113</v>
+        <v>25.949367088607595</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7392,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>50.506329113924046</v>
+        <v>50.31645569620253</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7400,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>60.25316455696203</v>
+        <v>61.01265822784809</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7408,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>22.531645569620252</v>
+        <v>22.405063291139243</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7444,7 +7424,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>61.70886075949366</v>
+        <v>61.77215189873418</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7432,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>30.189873417721515</v>
+        <v>27.08860759493671</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7460,7 +7440,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>52.21518987341773</v>
+        <v>51.455696202531655</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7448,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>51.51898734177216</v>
+        <v>51.835443037974684</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7456,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>38.54430379746835</v>
+        <v>35.88607594936709</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7464,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>67.27848101265823</v>
+        <v>67.53164556962025</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7472,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>60</v>
+        <v>60.9493670886076</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7480,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>45.949367088607595</v>
+        <v>48.9873417721519</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7488,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>28.101265822784814</v>
+        <v>28.60759493670886</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7516,7 +7496,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>43.22784810126582</v>
+        <v>46.07594936708861</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7504,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>72.59493670886076</v>
+        <v>72.91139240506328</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7512,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>68.54430379746836</v>
+        <v>68.35443037974684</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7520,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>38.41772151898734</v>
+        <v>38.924050632911396</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7556,7 +7536,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>37.911392405063296</v>
+        <v>38.41772151898734</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7544,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>44.683544303797476</v>
+        <v>43.54430379746835</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7552,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>28.797468354430375</v>
+        <v>28.227848101265828</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7560,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>35.822784810126585</v>
+        <v>34.93670886075949</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7568,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>25.822784810126585</v>
+        <v>26.32911392405063</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7576,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>42.21518987341773</v>
+        <v>43.79746835443039</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7584,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>36.07594936708861</v>
+        <v>36.20253164556962</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7612,7 +7592,7 @@
         <v>120</v>
       </c>
       <c r="B73">
-        <v>60.94936708860761</v>
+        <v>57.72151898734177</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7600,7 @@
         <v>121</v>
       </c>
       <c r="B74">
-        <v>53.41772151898735</v>
+        <v>53.417721518987335</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7608,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>43.67088607594937</v>
+        <v>54.620253164556964</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7616,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>48.60759493670886</v>
+        <v>51.77215189873418</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7624,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>63.0379746835443</v>
+        <v>49.93670886075949</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7632,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>49.620253164556964</v>
+        <v>49.24050632911393</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7640,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>58.9873417721519</v>
+        <v>58.10126582278481</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7648,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>64.30379746835445</v>
+        <v>64.74683544303798</v>
       </c>
     </row>
   </sheetData>
@@ -7701,7 +7681,7 @@
         <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7709,10 +7689,10 @@
         <v>121</v>
       </c>
       <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
         <v>134</v>
-      </c>
-      <c r="D3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7720,10 +7700,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" t="s">
         <v>136</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7731,93 +7711,93 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" t="s">
         <v>138</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" t="s">
         <v>140</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" t="s">
         <v>142</v>
-      </c>
-      <c r="D7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
         <v>144</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" t="s">
         <v>146</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" t="s">
         <v>148</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
         <v>150</v>
-      </c>
-      <c r="D11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
         <v>152</v>
-      </c>
-      <c r="D12" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" t="s">
         <v>154</v>
-      </c>
-      <c r="D13" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
         <v>156</v>
-      </c>
-      <c r="D14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" t="s">
         <v>158</v>
-      </c>
-      <c r="D15" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -7842,108 +7822,111 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>124</v>
+      </c>
       <c r="C2" t="s">
         <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" t="s">
         <v>144</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" t="s">
         <v>148</v>
-      </c>
-      <c r="D9" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" t="s">
         <v>150</v>
-      </c>
-      <c r="D10" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" t="s">
         <v>152</v>
-      </c>
-      <c r="D11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
         <v>154</v>
-      </c>
-      <c r="D12" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" t="s">
         <v>156</v>
-      </c>
-      <c r="D13" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7976,7 +7959,7 @@
         <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7984,10 +7967,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7995,90 +7978,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" t="s">
         <v>140</v>
-      </c>
-      <c r="D5" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" t="s">
         <v>144</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" t="s">
         <v>146</v>
-      </c>
-      <c r="D8" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" t="s">
         <v>152</v>
-      </c>
-      <c r="D11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
         <v>154</v>
-      </c>
-      <c r="D12" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" t="s">
         <v>156</v>
-      </c>
-      <c r="D13" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8111,111 +8094,111 @@
         <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
         <v>144</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" t="s">
         <v>146</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" t="s">
         <v>148</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
         <v>150</v>
-      </c>
-      <c r="D11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
         <v>152</v>
-      </c>
-      <c r="D12" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" t="s">
         <v>154</v>
-      </c>
-      <c r="D13" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
         <v>156</v>
-      </c>
-      <c r="D14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8231,212 +8214,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" t="s">
         <v>176</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>177</v>
-      </c>
-      <c r="C1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" t="s">
         <v>180</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>181</v>
-      </c>
-      <c r="C2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" t="s">
         <v>181</v>
-      </c>
-      <c r="C3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
         <v>186</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>187</v>
-      </c>
-      <c r="C4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
         <v>190</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>191</v>
-      </c>
-      <c r="C5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" t="s">
         <v>191</v>
-      </c>
-      <c r="C6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" t="s">
         <v>196</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>197</v>
-      </c>
-      <c r="C7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D7" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="229">
   <si>
     <t>Ticker</t>
   </si>
@@ -301,87 +301,102 @@
     <t>2027-05-05</t>
   </si>
   <si>
-    <t>2026-05-27</t>
+    <t>2027-05-27</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2027-05-20</t>
+  </si>
+  <si>
+    <t>2027-05-04</t>
+  </si>
+  <si>
+    <t>2027-05-06</t>
+  </si>
+  <si>
+    <t>2027-05-28</t>
+  </si>
+  <si>
+    <t>2027-06-02</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2027-05-11</t>
+  </si>
+  <si>
+    <t>2027-04-30</t>
+  </si>
+  <si>
+    <t>2027-04-29</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
+  </si>
+  <si>
+    <t>2027-05-07</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2027-06-03</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2027-05-14</t>
+  </si>
+  <si>
+    <t>2027-04-23</t>
+  </si>
+  <si>
+    <t>2027-06-04</t>
   </si>
   <si>
     <t>2027-04-22</t>
   </si>
   <si>
-    <t>2027-04-16</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
+    <t>2027-05-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2027-05-21</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>2027-04-21</t>
   </si>
   <si>
-    <t>2027-05-04</t>
-  </si>
-  <si>
-    <t>2027-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>2027-03-10</t>
-  </si>
-  <si>
-    <t>2027-04-23</t>
-  </si>
-  <si>
-    <t>2027-05-11</t>
-  </si>
-  <si>
-    <t>2027-04-30</t>
-  </si>
-  <si>
-    <t>2027-04-29</t>
-  </si>
-  <si>
-    <t>2027-04-28</t>
-  </si>
-  <si>
-    <t>2027-05-07</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>2027-04-27</t>
-  </si>
-  <si>
-    <t>2027-05-14</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2027-05-13</t>
-  </si>
-  <si>
-    <t>2027-04-15</t>
-  </si>
-  <si>
-    <t>2027-04-14</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
     <t>CTS</t>
   </si>
   <si>
@@ -409,18 +424,21 @@
     <t>_date_</t>
   </si>
   <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Last Run</t>
+  </si>
+  <si>
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>Criteria</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Last Run</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
@@ -667,25 +685,28 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader</t>
+    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1340,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1351,505 +1372,505 @@
         <v>61</v>
       </c>
       <c r="B2">
-        <v>72.91139240506328</v>
+        <v>70.82278481012659</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B3">
-        <v>68.35443037974684</v>
+        <v>68.98734177215191</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>67.53164556962025</v>
+        <v>68.67088607594937</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="B5">
-        <v>64.81012658227849</v>
+        <v>65.56962025316457</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="B6">
-        <v>64.74683544303798</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="B7">
-        <v>61.77215189873418</v>
+        <v>63.54430379746836</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8">
-        <v>61.01265822784809</v>
+        <v>60.696202531645575</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B9">
-        <v>60.9493670886076</v>
+        <v>60.189873417721515</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="B10">
-        <v>60.50632911392406</v>
+        <v>59.43037974683545</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>58.10126582278481</v>
+        <v>59.36708860759493</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="B12">
-        <v>57.72151898734177</v>
+        <v>59.11392405063292</v>
       </c>
       <c r="C12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="B13">
-        <v>57.658227848101255</v>
+        <v>58.924050632911396</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="B14">
-        <v>56.20253164556962</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>54.620253164556964</v>
+        <v>54.367088607594944</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>53.92405063291139</v>
+        <v>54.240506329113934</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>53.417721518987335</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>52.848101265822784</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B19">
-        <v>51.962025316455694</v>
+        <v>51.01265822784809</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="B20">
-        <v>51.8354430379747</v>
+        <v>50.8860759493671</v>
       </c>
       <c r="C20" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="B21">
-        <v>51.835443037974684</v>
+        <v>49.68354430379747</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B22">
-        <v>51.77215189873418</v>
+        <v>49.55696202531646</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B23">
-        <v>51.64556962025317</v>
+        <v>49.0506329113924</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B24">
-        <v>51.455696202531655</v>
+        <v>48.54430379746836</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>50.82278481012659</v>
+        <v>48.48101265822785</v>
       </c>
       <c r="C25" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>50.31645569620253</v>
+        <v>48.41772151898734</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="B27">
-        <v>49.93670886075949</v>
+        <v>48.35443037974684</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B28">
-        <v>49.74683544303798</v>
+        <v>48.35443037974683</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B29">
-        <v>49.43037974683545</v>
+        <v>46.77215189873418</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="B30">
-        <v>49.24050632911393</v>
+        <v>46.32911392405064</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>48.9873417721519</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="C31" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="B32">
-        <v>48.60759493670886</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>46.20253164556962</v>
+        <v>46.01265822784811</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B34">
-        <v>46.07594936708861</v>
+        <v>46.0126582278481</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B35">
-        <v>45.31645569620253</v>
+        <v>45.31645569620254</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="B36">
-        <v>44.49367088607595</v>
+        <v>45.25316455696203</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B37">
-        <v>43.54430379746835</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B38">
-        <v>42.65822784810127</v>
+        <v>44.17721518987342</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B39">
-        <v>42.53164556962026</v>
+        <v>43.73417721518987</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B40">
-        <v>39.936708860759495</v>
+        <v>43.54430379746836</v>
       </c>
       <c r="C40" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>38.924050632911396</v>
+        <v>42.21518987341773</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B42">
-        <v>38.924050632911396</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B43">
-        <v>37.151898734177216</v>
+        <v>37.974683544303794</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B44">
-        <v>36.39240506329114</v>
+        <v>37.40506329113924</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>36.20253164556962</v>
       </c>
       <c r="C45" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B46">
-        <v>35.88607594936709</v>
+        <v>34.43037974683545</v>
       </c>
       <c r="C46" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B47">
-        <v>34.17721518987342</v>
+        <v>34.1139240506329</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1857,43 +1878,43 @@
         <v>22</v>
       </c>
       <c r="B48">
-        <v>33.417721518987335</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B49">
-        <v>32.84810126582279</v>
+        <v>32.721518987341774</v>
       </c>
       <c r="C49" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B50">
-        <v>30.696202531645575</v>
+        <v>32.08860759493672</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B51">
-        <v>30.18987341772152</v>
+        <v>29.999999999999993</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -2121,55 +2142,55 @@
         <v>59.49367088607595</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8870151770657673</v>
+        <v>-1.5834738617200677</v>
       </c>
       <c r="E2" s="1">
         <v>0.38</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.1282834138276514</v>
+        <v>-0.1858541325339158</v>
       </c>
       <c r="G2" s="1">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="1">
-        <v>35.8</v>
+        <v>35.59</v>
       </c>
       <c r="I2" s="1">
-        <v>5.02</v>
+        <v>0.48</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.01288850034517013</v>
+        <v>-0.008245120065841256</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.2284684543869019</v>
+        <v>-0.30397017046624064</v>
       </c>
       <c r="N2" s="1">
-        <v>-9.985370078778365</v>
+        <v>-15.091169102970472</v>
       </c>
       <c r="O2" s="1">
-        <v>22.78481012658228</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P2" s="1">
-        <v>17.46078161093016</v>
+        <v>20.65084470171101</v>
       </c>
       <c r="Q2" s="1">
-        <v>27.341772151898734</v>
+        <v>29.49367088607595</v>
       </c>
       <c r="R2" s="1">
-        <v>22.59493670886076</v>
+        <v>18.924050632911392</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>-2.78</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2183,55 +2204,55 @@
         <v>46.835443037974684</v>
       </c>
       <c r="D3" s="2">
-        <v>24.462295081967213</v>
+        <v>24.6688524590164</v>
       </c>
       <c r="E3" s="2">
         <v>-0.89</v>
       </c>
       <c r="F3" s="2">
-        <v>1.4316503850391937</v>
+        <v>1.1744858344133393</v>
       </c>
       <c r="G3" s="2">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="H3" s="2">
-        <v>63.5</v>
+        <v>57.35</v>
       </c>
       <c r="I3" s="2">
-        <v>109.46</v>
+        <v>97.06</v>
       </c>
       <c r="J3" s="2">
-        <v>0.07883451212176729</v>
+        <v>0.05973757284423414</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="M3" s="2">
-        <v>1.6072688679018798</v>
+        <v>1.3851023839794125</v>
       </c>
       <c r="N3" s="2">
-        <v>173.5883621500998</v>
+        <v>153.81608634159483</v>
       </c>
       <c r="O3" s="2">
         <v>98.73417721518987</v>
       </c>
       <c r="P3" s="2">
-        <v>26.467189489392297</v>
+        <v>16.611373293216246</v>
       </c>
       <c r="Q3" s="2">
-        <v>74.17721518987342</v>
+        <v>72.53164556962025</v>
       </c>
       <c r="R3" s="2">
-        <v>64.81012658227849</v>
+        <v>68.67088607594937</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.19</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2245,55 +2266,55 @@
         <v>8.860759493670885</v>
       </c>
       <c r="D4" s="3">
-        <v>12.64102564102564</v>
+        <v>12.615384615384617</v>
       </c>
       <c r="E4" s="3">
-        <v>-1.7</v>
+        <v>-1.61</v>
       </c>
       <c r="F4" s="3">
-        <v>0.1939023829473215</v>
+        <v>0.5245361291806449</v>
       </c>
       <c r="G4" s="3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H4" s="3">
-        <v>65.77</v>
+        <v>69.3</v>
       </c>
       <c r="I4" s="3">
-        <v>18.97</v>
+        <v>26.78</v>
       </c>
       <c r="J4" s="3">
-        <v>0.0516523291617338</v>
+        <v>0.05750023529404491</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>-92</v>
+        <v>-88</v>
       </c>
       <c r="M4" s="3">
-        <v>0.2363336942430041</v>
+        <v>0.5729210121890671</v>
       </c>
       <c r="N4" s="3">
-        <v>36.49484478421224</v>
+        <v>72.5979491625603</v>
       </c>
       <c r="O4" s="3">
-        <v>81.0126582278481</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P4" s="3">
-        <v>43.93055527298539</v>
+        <v>33.76175725439266</v>
       </c>
       <c r="Q4" s="3">
-        <v>57.84810126582278</v>
+        <v>59.367088607594944</v>
       </c>
       <c r="R4" s="3">
-        <v>44.49367088607595</v>
+        <v>48.35443037974683</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>0.89</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2307,55 +2328,55 @@
         <v>40.50632911392405</v>
       </c>
       <c r="D5" s="3">
-        <v>24.95412844036697</v>
+        <v>23.678899082568805</v>
       </c>
       <c r="E5" s="3">
-        <v>-0.83</v>
+        <v>-0.89</v>
       </c>
       <c r="F5" s="3">
-        <v>-0.19742365337380705</v>
+        <v>-0.10420845184068017</v>
       </c>
       <c r="G5" s="3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H5" s="3">
-        <v>50.01</v>
+        <v>54.7</v>
       </c>
       <c r="I5" s="3">
-        <v>-1.6</v>
+        <v>0.28</v>
       </c>
       <c r="J5" s="3">
-        <v>0.008018677495598092</v>
+        <v>0.005682802585276467</v>
       </c>
       <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="M5" s="3">
-        <v>-0.10313185049451246</v>
+        <v>0.011061416502913923</v>
       </c>
       <c r="N5" s="3">
-        <v>2.5482903104605796</v>
+        <v>16.411989593944995</v>
       </c>
       <c r="O5" s="3">
-        <v>46.835443037974684</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P5" s="3">
-        <v>23.613581273496347</v>
+        <v>19.851960490969105</v>
       </c>
       <c r="Q5" s="3">
-        <v>54.177215189873415</v>
+        <v>55.9493670886076</v>
       </c>
       <c r="R5" s="3">
-        <v>45.063291139240505</v>
+        <v>47.658227848101276</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="3">
-        <v>-0.19</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2369,117 +2390,117 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4563106796116505</v>
+        <v>1.4854368932038835</v>
       </c>
       <c r="E6" s="1">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.3519389498282134</v>
+        <v>-0.4551108310997908</v>
       </c>
       <c r="G6" s="1">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H6" s="1">
-        <v>32.11</v>
+        <v>43.81</v>
       </c>
       <c r="I6" s="1">
-        <v>-18.85</v>
+        <v>-20.72</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.015708665955982654</v>
+        <v>-0.0262027920733899</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.2930065730286543</v>
+        <v>-0.38253350658715746</v>
       </c>
       <c r="N6" s="1">
-        <v>-16.439181942953603</v>
+        <v>-22.947502715062154</v>
       </c>
       <c r="O6" s="1">
-        <v>11.39240506329114</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P6" s="1">
-        <v>26.199187712619203</v>
+        <v>34.223953127673056</v>
       </c>
       <c r="Q6" s="1">
-        <v>31.392405063291136</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="R6" s="1">
-        <v>22.27848101265823</v>
+        <v>18.417721518987342</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-2.22</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>6.53</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>65.82278481012658</v>
       </c>
-      <c r="D7" s="2">
-        <v>5.099540581929555</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-0.12683662275628715</v>
-      </c>
-      <c r="G7" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="H7" s="2">
-        <v>48.33</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10.1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.016445065589507906</v>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>107</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.014601081562654716</v>
-      </c>
-      <c r="N7" s="2">
-        <v>14.321583516177297</v>
-      </c>
-      <c r="O7" s="2">
-        <v>59.49367088607595</v>
-      </c>
-      <c r="P7" s="2">
-        <v>15.539987609451147</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>58.35443037974684</v>
-      </c>
-      <c r="R7" s="2">
-        <v>52.848101265822784</v>
-      </c>
-      <c r="S7" s="2" t="s">
+      <c r="D7" s="3">
+        <v>5.234303215926493</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-0.2257245863823663</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.23</v>
+      </c>
+      <c r="H7" s="3">
+        <v>41.95</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2.31</v>
+      </c>
+      <c r="J7" s="3">
+        <v>-0.0020420205896341435</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>105</v>
+      </c>
+      <c r="M7" s="3">
+        <v>-0.05068515667542717</v>
+      </c>
+      <c r="N7" s="3">
+        <v>10.237332276110882</v>
+      </c>
+      <c r="O7" s="3">
+        <v>41.77215189873418</v>
+      </c>
+      <c r="P7" s="3">
+        <v>18.329517988884657</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>49.36708860759494</v>
+      </c>
+      <c r="R7" s="3">
+        <v>43.73417721518987</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T7" s="2">
-        <v>-0.82</v>
+      <c r="T7" s="3">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2493,117 +2514,117 @@
         <v>83.54430379746836</v>
       </c>
       <c r="D8" s="2">
-        <v>0.03398791540785493</v>
+        <v>0.04607250755287005</v>
       </c>
       <c r="E8" s="2">
-        <v>0.55</v>
+        <v>0.56</v>
       </c>
       <c r="F8" s="2">
-        <v>0.34523201580338625</v>
+        <v>0.4071696877896948</v>
       </c>
       <c r="G8" s="2">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="2">
-        <v>65.34</v>
+        <v>58.83</v>
       </c>
       <c r="I8" s="2">
-        <v>22.49</v>
+        <v>23.78</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03976450120742614</v>
+        <v>0.023049188226230238</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-220</v>
+        <v>-213</v>
       </c>
       <c r="M8" s="2">
-        <v>0.3028007045077037</v>
+        <v>0.3545155503981765</v>
       </c>
       <c r="N8" s="2">
-        <v>43.14154581068219</v>
+        <v>50.757402983471245</v>
       </c>
       <c r="O8" s="2">
-        <v>83.54430379746836</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P8" s="2">
-        <v>27.294677507005353</v>
+        <v>12.1757720658765</v>
       </c>
       <c r="Q8" s="2">
-        <v>65.0632911392405</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="R8" s="2">
-        <v>53.92405063291139</v>
+        <v>59.36708860759493</v>
       </c>
       <c r="S8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T8" s="2">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="C9" s="1">
+        <v>35.44303797468354</v>
+      </c>
+      <c r="D9" s="1">
+        <v>47.337078651685395</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-0.19</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-0.34283175496477963</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H9" s="1">
+        <v>54.3</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-15.97</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-0.01666318496956814</v>
+      </c>
+      <c r="K9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>-12</v>
+      </c>
+      <c r="M9" s="1">
+        <v>-0.2602928368915888</v>
+      </c>
+      <c r="N9" s="1">
+        <v>-10.723435745505281</v>
+      </c>
+      <c r="O9" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P9" s="1">
+        <v>33.30639201351699</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>46.962025316455694</v>
+      </c>
+      <c r="R9" s="1">
+        <v>27.658227848101262</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T8" s="2">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="C9" s="3">
-        <v>35.44303797468354</v>
-      </c>
-      <c r="D9" s="3">
-        <v>46.97752808988764</v>
-      </c>
-      <c r="E9" s="3">
-        <v>-0.19</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-0.34758296974318087</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1.53</v>
-      </c>
-      <c r="H9" s="3">
-        <v>44.99</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-17.13</v>
-      </c>
-      <c r="J9" s="3">
-        <v>-0.01023936657196911</v>
-      </c>
-      <c r="K9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3">
-        <v>-16</v>
-      </c>
-      <c r="M9" s="3">
-        <v>-0.2851146503356482</v>
-      </c>
-      <c r="N9" s="3">
-        <v>-15.649989673652998</v>
-      </c>
-      <c r="O9" s="3">
-        <v>13.924050632911392</v>
-      </c>
-      <c r="P9" s="3">
-        <v>24.534202088618652</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>42.78481012658228</v>
-      </c>
-      <c r="R9" s="3">
-        <v>31.202531645569614</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="T9" s="3">
-        <v>-0.51</v>
+      <c r="T9" s="1">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2617,179 +2638,179 @@
         <v>63.29113924050633</v>
       </c>
       <c r="D10" s="3">
-        <v>0.5616</v>
+        <v>0.5519999999999999</v>
       </c>
       <c r="E10" s="3">
-        <v>-2.1</v>
+        <v>-2.17</v>
       </c>
       <c r="F10" s="3">
-        <v>-0.15486784145139812</v>
+        <v>-0.20027803859871585</v>
       </c>
       <c r="G10" s="3">
         <v>1.39</v>
       </c>
       <c r="H10" s="3">
-        <v>48.34</v>
+        <v>42.98</v>
       </c>
       <c r="I10" s="3">
-        <v>-5.8</v>
+        <v>-8.31</v>
       </c>
       <c r="J10" s="3">
-        <v>0.0044391076089213</v>
+        <v>-0.00741868766645343</v>
       </c>
       <c r="K10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>-131</v>
+        <v>-136</v>
       </c>
       <c r="M10" s="3">
-        <v>-0.10890058754774201</v>
+        <v>-0.14477773161846685</v>
       </c>
       <c r="N10" s="3">
-        <v>1.9714166051376307</v>
+        <v>0.8280747818068991</v>
       </c>
       <c r="O10" s="3">
-        <v>44.303797468354425</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P10" s="3">
-        <v>18.364103068329413</v>
+        <v>15.951255967229406</v>
       </c>
       <c r="Q10" s="3">
-        <v>43.29113924050633</v>
+        <v>39.49367088607595</v>
       </c>
       <c r="R10" s="3">
-        <v>39.620253164556964</v>
+        <v>34.43037974683545</v>
       </c>
       <c r="S10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T10" s="3">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>-0.95</v>
+      </c>
+      <c r="C11" s="2">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46.22105263157896</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1.62</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.23699359322581803</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="2">
+        <v>68.41</v>
+      </c>
+      <c r="I11" s="2">
+        <v>17.62</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.019742171839279177</v>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>26</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.20853189733851085</v>
+      </c>
+      <c r="N11" s="2">
+        <v>36.15903767750469</v>
+      </c>
+      <c r="O11" s="2">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="P11" s="2">
+        <v>21.2185970476566</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>60.00000000000001</v>
+      </c>
+      <c r="R11" s="2">
+        <v>52.40506329113924</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="T10" s="3">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3">
-        <v>-0.95</v>
-      </c>
-      <c r="C11" s="3">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46.70526315789474</v>
-      </c>
-      <c r="E11" s="3">
-        <v>-1.64</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-0.06520841556972641</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="H11" s="3">
-        <v>45.33</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-0.67</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.011870108523928372</v>
-      </c>
-      <c r="K11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>25</v>
-      </c>
-      <c r="M11" s="3">
-        <v>-0.08406677614558533</v>
-      </c>
-      <c r="N11" s="3">
-        <v>4.454797745353289</v>
-      </c>
-      <c r="O11" s="3">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="P11" s="3">
-        <v>21.111699887088218</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>48.35443037974684</v>
-      </c>
-      <c r="R11" s="3">
-        <v>42.65822784810127</v>
-      </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>-0.15</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="D12" s="2">
+        <v>169</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.30952876191658657</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H12" s="2">
+        <v>67.81</v>
+      </c>
+      <c r="I12" s="2">
+        <v>-1.99</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.03648354343301034</v>
+      </c>
+      <c r="K12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>-55</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.3024133379447598</v>
+      </c>
+      <c r="N12" s="2">
+        <v>45.54718173812957</v>
+      </c>
+      <c r="O12" s="2">
+        <v>83.54430379746836</v>
+      </c>
+      <c r="P12" s="2">
+        <v>40.172518102184526</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>62.531645569620245</v>
+      </c>
+      <c r="R12" s="2">
+        <v>52.65822784810126</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T11" s="3">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3">
-        <v>-0.15</v>
-      </c>
-      <c r="C12" s="3">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="D12" s="3">
-        <v>169</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3.03</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.10743875008006845</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="H12" s="3">
-        <v>53.85</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-17.24</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.025719847357969342</v>
-      </c>
-      <c r="K12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>-53</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0.1039028074720949</v>
-      </c>
-      <c r="N12" s="3">
-        <v>23.251756107121306</v>
-      </c>
-      <c r="O12" s="3">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="P12" s="3">
-        <v>49.122344752707264</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>57.72151898734178</v>
-      </c>
-      <c r="R12" s="3">
-        <v>49.74683544303798</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0.38</v>
+      <c r="T12" s="2">
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2806,52 +2827,52 @@
         <v>-1653.5</v>
       </c>
       <c r="E13" s="1">
-        <v>6.42</v>
+        <v>5.58</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.3363071117835895</v>
+        <v>-0.4471773436712764</v>
       </c>
       <c r="G13" s="1">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="H13" s="1">
-        <v>41.9</v>
+        <v>38.34</v>
       </c>
       <c r="I13" s="1">
-        <v>-19.58</v>
+        <v>-26.44</v>
       </c>
       <c r="J13" s="1">
-        <v>-0.016972204534867124</v>
+        <v>-0.025318627824700554</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M13" s="1">
-        <v>-0.29033985787993344</v>
+        <v>-0.38883086710229664</v>
       </c>
       <c r="N13" s="1">
-        <v>-16.17251042808152</v>
+        <v>-23.577238766576066</v>
       </c>
       <c r="O13" s="1">
-        <v>12.658227848101266</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P13" s="1">
-        <v>48.90109995677025</v>
+        <v>38.374715014440206</v>
       </c>
       <c r="Q13" s="1">
-        <v>12.658227848101266</v>
+        <v>12.531645569620254</v>
       </c>
       <c r="R13" s="1">
-        <v>2.405063291139239</v>
+        <v>1.3924050632911378</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T13" s="1">
-        <v>1.77</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2865,55 +2886,55 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D14" s="2">
-        <v>6.768115942028986</v>
+        <v>6.753623188405798</v>
       </c>
       <c r="E14" s="2">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="F14" s="2">
-        <v>0.3674846041722752</v>
+        <v>0.7327713806648734</v>
       </c>
       <c r="G14" s="2">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="2">
-        <v>61.94</v>
+        <v>78.1</v>
       </c>
       <c r="I14" s="2">
-        <v>36.78</v>
+        <v>66.71</v>
       </c>
       <c r="J14" s="2">
-        <v>0.04374237461778499</v>
+        <v>0.06650440800572771</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="2">
-        <v>0.34391165345245156</v>
+        <v>0.7000404303944701</v>
       </c>
       <c r="N14" s="2">
-        <v>47.25264070515698</v>
+        <v>85.30989098310059</v>
       </c>
       <c r="O14" s="2">
-        <v>86.07594936708861</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P14" s="2">
-        <v>31.193963552248132</v>
+        <v>28.85245621658959</v>
       </c>
       <c r="Q14" s="2">
-        <v>62.78481012658229</v>
+        <v>67.46835443037976</v>
       </c>
       <c r="R14" s="2">
-        <v>51.8354430379747</v>
+        <v>54.367088607594944</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T14" s="2">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2927,55 +2948,55 @@
         <v>17.72151898734177</v>
       </c>
       <c r="D15" s="2">
-        <v>68.11111111111111</v>
+        <v>73.76190476190477</v>
       </c>
       <c r="E15" s="2">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="F15" s="2">
-        <v>1.4639111024804692</v>
+        <v>1.1003138491204965</v>
       </c>
       <c r="G15" s="2">
         <v>2.21</v>
       </c>
       <c r="H15" s="2">
-        <v>63.06</v>
+        <v>50.34</v>
       </c>
       <c r="I15" s="2">
-        <v>132.31</v>
+        <v>100.92</v>
       </c>
       <c r="J15" s="2">
-        <v>0.07876732814006998</v>
+        <v>0.05659218037979602</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="M15" s="2">
-        <v>1.6065274543354022</v>
+        <v>1.2725071092387048</v>
       </c>
       <c r="N15" s="2">
-        <v>173.51422079345207</v>
+        <v>142.55655886752407</v>
       </c>
       <c r="O15" s="2">
-        <v>97.46835443037975</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P15" s="2">
-        <v>24.171577948970977</v>
+        <v>23.3853551464226</v>
       </c>
       <c r="Q15" s="2">
-        <v>67.72151898734177</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="R15" s="2">
-        <v>60.50632911392406</v>
+        <v>59.11392405063292</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T15" s="2">
-        <v>-0.63</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -2992,176 +3013,176 @@
         <v>13.056657223796035</v>
       </c>
       <c r="E16" s="3">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.20139313471465856</v>
+        <v>0.09466139381505068</v>
       </c>
       <c r="G16" s="3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H16" s="3">
-        <v>52.46</v>
+        <v>70.63</v>
       </c>
       <c r="I16" s="3">
-        <v>2.88</v>
+        <v>30.13</v>
       </c>
       <c r="J16" s="3">
-        <v>0.0017289255145024785</v>
+        <v>0.014328315696851569</v>
       </c>
       <c r="K16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
+        <v>19</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.20566200777554866</v>
+      </c>
+      <c r="N16" s="3">
+        <v>35.87204872120846</v>
+      </c>
+      <c r="O16" s="3">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P16" s="3">
+        <v>27.942065176302556</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="R16" s="3">
+        <v>44.68354430379747</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T16" s="3">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-6.21</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.769726247987117</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="F17" s="3">
+        <v>-0.005470059730483645</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.72</v>
+      </c>
+      <c r="H17" s="3">
+        <v>69.35</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11.37</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.0019418392145956062</v>
+      </c>
+      <c r="K17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>25</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.09699204546382223</v>
+      </c>
+      <c r="N17" s="3">
+        <v>25.00505249003583</v>
+      </c>
+      <c r="O17" s="3">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P17" s="3">
+        <v>28.182703357372183</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>40.25316455696203</v>
+      </c>
+      <c r="R17" s="3">
+        <v>32.08860759493672</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M16" s="3">
-        <v>-0.10710133183536397</v>
-      </c>
-      <c r="N16" s="3">
-        <v>2.1513421763754206</v>
-      </c>
-      <c r="O16" s="3">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="P16" s="3">
-        <v>30.2515696939809</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>41.64556962025317</v>
-      </c>
-      <c r="R16" s="3">
-        <v>30.696202531645575</v>
-      </c>
-      <c r="S16" s="3" t="s">
+      <c r="B18" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="C18" s="2">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1387.3333333333335</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5.95</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.14614832605927724</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="H18" s="2">
+        <v>75.57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>28.99</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.014123407320883538</v>
+      </c>
+      <c r="K18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>37</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.15610991961983478</v>
+      </c>
+      <c r="N18" s="2">
+        <v>30.91683990563708</v>
+      </c>
+      <c r="O18" s="2">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="P18" s="2">
+        <v>40.99379037037764</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>69.49367088607595</v>
+      </c>
+      <c r="R18" s="2">
+        <v>51.01265822784809</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="3">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <v>-6.21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="D17" s="1">
-        <v>4.777777777777778</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="F17" s="1">
-        <v>-0.17456467862415503</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="H17" s="1">
-        <v>49.1</v>
-      </c>
-      <c r="I17" s="1">
-        <v>-7.12</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0.005609888159402101</v>
-      </c>
-      <c r="K17" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>25</v>
-      </c>
-      <c r="M17" s="1">
-        <v>-0.09088070356878108</v>
-      </c>
-      <c r="N17" s="1">
-        <v>3.7734050030337087</v>
-      </c>
-      <c r="O17" s="1">
-        <v>49.36708860759494</v>
-      </c>
-      <c r="P17" s="1">
-        <v>28.182703357372183</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>31.518987341772153</v>
-      </c>
-      <c r="R17" s="1">
-        <v>26.265822784810123</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.09</v>
-      </c>
-      <c r="C18" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1446.3333333333333</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5.96</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-0.006597780522676594</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1.12</v>
-      </c>
-      <c r="H18" s="3">
-        <v>63.22</v>
-      </c>
-      <c r="I18" s="3">
-        <v>7.36</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.011857727435715955</v>
-      </c>
-      <c r="K18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>37</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0.007545989909217621</v>
-      </c>
-      <c r="N18" s="3">
-        <v>13.616074350833577</v>
-      </c>
-      <c r="O18" s="3">
-        <v>58.22784810126582</v>
-      </c>
-      <c r="P18" s="3">
-        <v>44.14111512367286</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>63.79746835443037</v>
-      </c>
-      <c r="R18" s="3">
-        <v>46.20253164556962</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1.14</v>
+      <c r="T18" s="2">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3175,55 +3196,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D19" s="3">
-        <v>0.3015021459227468</v>
+        <v>0.3787553648068669</v>
       </c>
       <c r="E19" s="3">
-        <v>-2.17</v>
+        <v>-2.16</v>
       </c>
       <c r="F19" s="3">
-        <v>0.04380645788563685</v>
+        <v>0.14196283015499866</v>
       </c>
       <c r="G19" s="3">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H19" s="3">
-        <v>52.74</v>
+        <v>55.98</v>
       </c>
       <c r="I19" s="3">
-        <v>12.83</v>
+        <v>17.14</v>
       </c>
       <c r="J19" s="3">
-        <v>0.007929845431286074</v>
+        <v>0.0159834734558223</v>
       </c>
       <c r="K19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="3">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M19" s="3">
-        <v>-0.054021287601631274</v>
+        <v>0.02242370742830846</v>
       </c>
       <c r="N19" s="3">
-        <v>7.459346599748695</v>
+        <v>17.54821868648445</v>
       </c>
       <c r="O19" s="3">
-        <v>53.16455696202531</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P19" s="3">
-        <v>14.335419717590279</v>
+        <v>12.304094956687697</v>
       </c>
       <c r="Q19" s="3">
-        <v>52.65822784810126</v>
+        <v>57.848101265822784</v>
       </c>
       <c r="R19" s="3">
-        <v>45.31645569620253</v>
+        <v>48.41772151898734</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T19" s="3">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3240,22 +3261,22 @@
         <v>0.6820428336079079</v>
       </c>
       <c r="E20" s="3">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.019064811472597865</v>
+        <v>-0.1088752671437872</v>
       </c>
       <c r="G20" s="3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H20" s="3">
-        <v>52.21</v>
+        <v>53.77</v>
       </c>
       <c r="I20" s="3">
-        <v>-0.54</v>
+        <v>0.39</v>
       </c>
       <c r="J20" s="3">
-        <v>0.006136780395040876</v>
+        <v>-0.001545128035053975</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>0</v>
@@ -3264,28 +3285,28 @@
         <v>10</v>
       </c>
       <c r="M20" s="3">
-        <v>-0.008456983648677197</v>
+        <v>-0.09891367358322967</v>
       </c>
       <c r="N20" s="3">
-        <v>12.015776995044106</v>
+        <v>5.414480585330635</v>
       </c>
       <c r="O20" s="3">
-        <v>55.69620253164557</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P20" s="3">
-        <v>22.71709963975286</v>
+        <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="3">
-        <v>48.481012658227854</v>
+        <v>47.468354430379755</v>
       </c>
       <c r="R20" s="3">
-        <v>42.53164556962026</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T20" s="3">
-        <v>1.65</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3299,117 +3320,117 @@
         <v>39.24050632911392</v>
       </c>
       <c r="D21" s="3">
-        <v>13.529411764705882</v>
+        <v>13.931372549019608</v>
       </c>
       <c r="E21" s="3">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.0346803510666184</v>
+        <v>0.03448350423695601</v>
       </c>
       <c r="G21" s="3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>48.03</v>
+        <v>40.91</v>
       </c>
       <c r="I21" s="3">
-        <v>34.99</v>
+        <v>12.21</v>
       </c>
       <c r="J21" s="3">
-        <v>0.038388645609507124</v>
+        <v>0.027007860306520536</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M21" s="3">
-        <v>0.03603850109285256</v>
+        <v>0.12271476148760829</v>
       </c>
       <c r="N21" s="3">
-        <v>16.465325469197087</v>
+        <v>27.577324092414436</v>
       </c>
       <c r="O21" s="3">
-        <v>65.82278481012658</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P21" s="3">
-        <v>39.63614933355383</v>
+        <v>40.45347904811993</v>
       </c>
       <c r="Q21" s="3">
-        <v>61.64556962025317</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="R21" s="3">
-        <v>48.60759493670886</v>
+        <v>48.35443037974684</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T21" s="3">
-        <v>-3.42</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>8.11</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>68.35443037974683</v>
       </c>
-      <c r="D22" s="3">
-        <v>0.718865598027127</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="2">
+        <v>0.7410604192355117</v>
+      </c>
+      <c r="E22" s="2">
         <v>-1.48</v>
       </c>
-      <c r="F22" s="3">
-        <v>-0.01596096591096488</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1.38</v>
-      </c>
-      <c r="H22" s="3">
-        <v>68.69</v>
-      </c>
-      <c r="I22" s="3">
-        <v>14.75</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.01707264465093835</v>
-      </c>
-      <c r="K22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>58</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0.028827640456700054</v>
-      </c>
-      <c r="N22" s="3">
-        <v>15.744239405581824</v>
-      </c>
-      <c r="O22" s="3">
-        <v>62.0253164556962</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="F22" s="2">
+        <v>0.14113610896321732</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1.37</v>
+      </c>
+      <c r="H22" s="2">
+        <v>76.42</v>
+      </c>
+      <c r="I22" s="2">
+        <v>22.22</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.02618670776142812</v>
+      </c>
+      <c r="K22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>60</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0.19379024635473563</v>
+      </c>
+      <c r="N22" s="2">
+        <v>34.68487257912715</v>
+      </c>
+      <c r="O22" s="2">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="P22" s="2">
         <v>20.966620085005058</v>
       </c>
-      <c r="Q22" s="3">
-        <v>62.40506329113924</v>
-      </c>
-      <c r="R22" s="3">
-        <v>49.43037974683545</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1.9</v>
+      <c r="Q22" s="2">
+        <v>66.0759493670886</v>
+      </c>
+      <c r="R22" s="2">
+        <v>54.240506329113934</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T22" s="2">
+        <v>1.55</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3420,58 +3441,58 @@
         <v>27.51</v>
       </c>
       <c r="C23" s="3">
-        <v>97.46835443037975</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="D23" s="3">
-        <v>-0.7684478371501272</v>
+        <v>-0.7673573246092329</v>
       </c>
       <c r="E23" s="3">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="F23" s="3">
-        <v>-0.19500491324233873</v>
+        <v>-0.14224862656008772</v>
       </c>
       <c r="G23" s="3">
         <v>1.24</v>
       </c>
       <c r="H23" s="3">
-        <v>49.68</v>
+        <v>53.95</v>
       </c>
       <c r="I23" s="3">
-        <v>-8.2</v>
+        <v>-7.02</v>
       </c>
       <c r="J23" s="3">
-        <v>0.002046324199199352</v>
+        <v>-0.014942118484284332</v>
       </c>
       <c r="K23" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="M23" s="3">
-        <v>-0.16671737237855033</v>
+        <v>-0.10809459149531908</v>
       </c>
       <c r="N23" s="3">
-        <v>-3.8102618779432094</v>
+        <v>4.496388794121688</v>
       </c>
       <c r="O23" s="3">
-        <v>31.645569620253166</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P23" s="3">
-        <v>28.794141696367475</v>
+        <v>22.37087010926521</v>
       </c>
       <c r="Q23" s="3">
-        <v>46.58227848101265</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="R23" s="3">
-        <v>33.417721518987335</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T23" s="3">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3485,55 +3506,55 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.9205677290836654</v>
+        <v>-0.6546314741035859</v>
       </c>
       <c r="E24" s="1">
-        <v>7.21</v>
+        <v>7.1</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.540997176862236</v>
+        <v>-0.6735807245135497</v>
       </c>
       <c r="G24" s="1">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
       <c r="H24" s="1">
-        <v>42.27</v>
+        <v>40.62</v>
       </c>
       <c r="I24" s="1">
-        <v>-32.63</v>
+        <v>-44.05</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.0010840395404872125</v>
+        <v>-0.04717007629350957</v>
       </c>
       <c r="K24" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="M24" s="1">
-        <v>-0.24751394040043162</v>
+        <v>-0.3121171867447483</v>
       </c>
       <c r="N24" s="1">
-        <v>-11.889918680131334</v>
+        <v>-15.90587073082124</v>
       </c>
       <c r="O24" s="1">
-        <v>18.9873417721519</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P24" s="1">
-        <v>41.129939248308794</v>
+        <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>10.632911392405067</v>
+        <v>5.9493670886075956</v>
       </c>
       <c r="R24" s="1">
-        <v>2.974683544303799</v>
+        <v>-3.2278481012658222</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="1">
-        <v>-0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3547,25 +3568,25 @@
         <v>11.39240506329114</v>
       </c>
       <c r="D25" s="1">
-        <v>-7.149122807017544</v>
+        <v>-7.837719298245614</v>
       </c>
       <c r="E25" s="1">
-        <v>11.56</v>
+        <v>11.57</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.44397923562155767</v>
+        <v>-0.3855691322111</v>
       </c>
       <c r="G25" s="1">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H25" s="1">
-        <v>45.02</v>
+        <v>41.43</v>
       </c>
       <c r="I25" s="1">
-        <v>-50.28</v>
+        <v>-50.52</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.0033748606604909193</v>
+        <v>-0.021193606936857956</v>
       </c>
       <c r="K25" s="1" t="b">
         <v>0</v>
@@ -3574,90 +3595,90 @@
         <v>42</v>
       </c>
       <c r="M25" s="1">
-        <v>-0.29782694115865105</v>
+        <v>-0.2062604481210648</v>
       </c>
       <c r="N25" s="1">
-        <v>-16.921218755953277</v>
+        <v>-5.320196868452885</v>
       </c>
       <c r="O25" s="1">
-        <v>8.860759493670885</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P25" s="1">
-        <v>55.620154465672535</v>
+        <v>48.19004700621787</v>
       </c>
       <c r="Q25" s="1">
-        <v>11.898734177215193</v>
+        <v>8.354430379746837</v>
       </c>
       <c r="R25" s="1">
-        <v>-1.0126582278480996</v>
+        <v>1.265822784810128</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T25" s="1">
-        <v>-0.63</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="1">
         <v>-0.17</v>
       </c>
-      <c r="C26" s="3">
-        <v>22.78481012658228</v>
-      </c>
-      <c r="D26" s="3">
-        <v>-2529.3529411764703</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2.15</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0.3705636755447685</v>
-      </c>
-      <c r="G26" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="H26" s="3">
-        <v>51.5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>20.6</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0.06218566310977188</v>
-      </c>
-      <c r="K26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="C26" s="1">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-2336.705882352941</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2.19</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.19324245275038382</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3.26</v>
+      </c>
+      <c r="H26" s="1">
+        <v>40.67</v>
+      </c>
+      <c r="I26" s="1">
+        <v>-1.32</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.00873237443142054</v>
+      </c>
+      <c r="K26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
         <v>-28</v>
       </c>
-      <c r="M26" s="3">
-        <v>0.6298661334628286</v>
-      </c>
-      <c r="N26" s="3">
-        <v>75.84808870619469</v>
-      </c>
-      <c r="O26" s="3">
-        <v>89.87341772151899</v>
-      </c>
-      <c r="P26" s="3">
-        <v>47.51283017631868</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>38.22784810126583</v>
-      </c>
-      <c r="R26" s="3">
-        <v>32.84810126582279</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-0.89</v>
+      <c r="M26" s="1">
+        <v>0.514859616276955</v>
+      </c>
+      <c r="N26" s="1">
+        <v>66.79180957134909</v>
+      </c>
+      <c r="O26" s="1">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="P26" s="1">
+        <v>34.955970015061894</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>23.924050632911392</v>
+      </c>
+      <c r="R26" s="1">
+        <v>29.746835443037977</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T26" s="1">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3674,52 +3695,52 @@
         <v>2.752212389380531</v>
       </c>
       <c r="E27" s="1">
-        <v>7.51</v>
+        <v>7.37</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.38421107521853803</v>
+        <v>-0.3484172903857371</v>
       </c>
       <c r="G27" s="1">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="H27" s="1">
-        <v>43.59</v>
+        <v>43.43</v>
       </c>
       <c r="I27" s="1">
-        <v>-24.69</v>
+        <v>-27.27</v>
       </c>
       <c r="J27" s="1">
-        <v>0.009760106599280723</v>
+        <v>-0.0038101023941875187</v>
       </c>
       <c r="K27" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M27" s="1">
-        <v>-0.18501964163602824</v>
+        <v>-0.10364670575489532</v>
       </c>
       <c r="N27" s="1">
-        <v>-5.640488803690999</v>
+        <v>4.9411773681640625</v>
       </c>
       <c r="O27" s="1">
-        <v>26.582278481012654</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P27" s="1">
-        <v>46.059783198474584</v>
+        <v>30.975612687279728</v>
       </c>
       <c r="Q27" s="1">
-        <v>31.77215189873418</v>
+        <v>28.22784810126582</v>
       </c>
       <c r="R27" s="1">
-        <v>19.430379746835442</v>
+        <v>21.898734177215193</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.44</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3736,52 +3757,52 @@
         <v>7.899999999999999</v>
       </c>
       <c r="E28" s="1">
-        <v>-4.75</v>
+        <v>-4.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.5302614761180011</v>
+        <v>-0.47393917671454994</v>
       </c>
       <c r="G28" s="1">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="H28" s="1">
-        <v>42.51</v>
+        <v>49.45</v>
       </c>
       <c r="I28" s="1">
-        <v>-29.72</v>
+        <v>-28.8</v>
       </c>
       <c r="J28" s="1">
-        <v>0.00021785781265444356</v>
+        <v>-0.01898648761904007</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.27567360834390575</v>
+        <v>-0.16228360674853626</v>
       </c>
       <c r="N28" s="1">
-        <v>-14.70588547447875</v>
+        <v>-0.9225127312000354</v>
       </c>
       <c r="O28" s="1">
-        <v>15.18987341772152</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P28" s="1">
-        <v>45.17203183430412</v>
+        <v>37.76595957169116</v>
       </c>
       <c r="Q28" s="1">
-        <v>31.645569620253166</v>
+        <v>30.379746835443036</v>
       </c>
       <c r="R28" s="1">
-        <v>18.291139240506332</v>
+        <v>20.126582278481013</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T28" s="1">
-        <v>0.63</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3795,25 +3816,25 @@
         <v>32.91139240506329</v>
       </c>
       <c r="D29" s="3">
-        <v>79.04545454545455</v>
+        <v>78.54545454545455</v>
       </c>
       <c r="E29" s="3">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.260444426187111</v>
+        <v>-0.14542689801415637</v>
       </c>
       <c r="G29" s="3">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H29" s="3">
-        <v>57.19</v>
+        <v>61.15</v>
       </c>
       <c r="I29" s="3">
-        <v>-22.25</v>
+        <v>-16.49</v>
       </c>
       <c r="J29" s="3">
-        <v>0.005868927187871581</v>
+        <v>-0.00523760774067895</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
@@ -3822,152 +3843,152 @@
         <v>-68</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.12372131201213388</v>
+        <v>0.021074022926590663</v>
       </c>
       <c r="N29" s="3">
-        <v>0.48934415869842623</v>
+        <v>17.41325023631267</v>
       </c>
       <c r="O29" s="3">
-        <v>39.24050632911392</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P29" s="3">
-        <v>41.93177642803681</v>
+        <v>29.03981570098992</v>
       </c>
       <c r="Q29" s="3">
-        <v>52.911392405063296</v>
+        <v>52.15189873417722</v>
       </c>
       <c r="R29" s="3">
-        <v>37.911392405063296</v>
+        <v>42.72151898734177</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T29" s="3">
-        <v>3.86</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>1.95</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1392.5435897435898</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-0.056538534774211446</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="H30" s="3">
+        <v>62.34</v>
+      </c>
+      <c r="I30" s="3">
+        <v>7.38</v>
+      </c>
+      <c r="J30" s="3">
+        <v>-0.0006259267000878738</v>
+      </c>
+      <c r="K30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>26</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-0.026653754092538895</v>
+      </c>
+      <c r="N30" s="3">
+        <v>12.640472534399693</v>
+      </c>
+      <c r="O30" s="3">
         <v>44.303797468354425</v>
       </c>
-      <c r="D30" s="2">
-        <v>1497.6410256410256</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="F30" s="2">
-        <v>-0.08995411839988707</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="H30" s="2">
-        <v>54.29</v>
-      </c>
-      <c r="I30" s="2">
-        <v>3.67</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0.008723101725844864</v>
-      </c>
-      <c r="K30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2">
-        <v>24</v>
-      </c>
-      <c r="M30" s="2">
-        <v>-0.06638116768006341</v>
-      </c>
-      <c r="N30" s="2">
-        <v>6.223358591905487</v>
-      </c>
-      <c r="O30" s="2">
-        <v>51.89873417721519</v>
-      </c>
-      <c r="P30" s="2">
-        <v>24.961328061128594</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>64.9367088607595</v>
-      </c>
-      <c r="R30" s="2">
-        <v>51.962025316455694</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T30" s="2">
-        <v>0.13</v>
+      <c r="P30" s="3">
+        <v>22.679906206244624</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>64.05063291139241</v>
+      </c>
+      <c r="R30" s="3">
+        <v>48.48101265822785</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0.21</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>6.01</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>60.75949367088608</v>
       </c>
-      <c r="D31" s="2">
-        <v>10.262895174708818</v>
-      </c>
-      <c r="E31" s="2">
-        <v>-0.64</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.0003446817125796475</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1.45</v>
-      </c>
-      <c r="H31" s="2">
-        <v>43.3</v>
-      </c>
-      <c r="I31" s="2">
-        <v>7.62</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0.019208481201470375</v>
-      </c>
-      <c r="K31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2">
-        <v>67</v>
-      </c>
-      <c r="M31" s="2">
-        <v>0.05338382083218285</v>
-      </c>
-      <c r="N31" s="2">
-        <v>18.199857443130114</v>
-      </c>
-      <c r="O31" s="2">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="P31" s="2">
-        <v>22.731897658859403</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>60.50632911392405</v>
-      </c>
-      <c r="R31" s="2">
-        <v>56.20253164556962</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="T31" s="2">
-        <v>-0.38</v>
+      <c r="D31" s="3">
+        <v>10.299500831946755</v>
+      </c>
+      <c r="E31" s="3">
+        <v>-0.61</v>
+      </c>
+      <c r="F31" s="3">
+        <v>-0.03126119356914542</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1.47</v>
+      </c>
+      <c r="H31" s="3">
+        <v>44.72</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="J31" s="3">
+        <v>-0.008523531667344219</v>
+      </c>
+      <c r="K31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>62</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0.03562379176602648</v>
+      </c>
+      <c r="N31" s="3">
+        <v>18.86822712025624</v>
+      </c>
+      <c r="O31" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P31" s="3">
+        <v>25.15106698404559</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>51.265822784810126</v>
+      </c>
+      <c r="R31" s="3">
+        <v>46.07594936708861</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0.82</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -3981,55 +4002,55 @@
         <v>10.126582278481013</v>
       </c>
       <c r="D32" s="3">
-        <v>8.034246575342467</v>
+        <v>7.743150684931507</v>
       </c>
       <c r="E32" s="3">
-        <v>-3.39</v>
+        <v>-3.52</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.1858881192362209</v>
+        <v>0.070771718249906</v>
       </c>
       <c r="G32" s="3">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H32" s="3">
-        <v>52.7</v>
+        <v>70.38</v>
       </c>
       <c r="I32" s="3">
-        <v>3.63</v>
+        <v>27.27</v>
       </c>
       <c r="J32" s="3">
-        <v>0.0059886439101265905</v>
+        <v>0.005369990090877874</v>
       </c>
       <c r="K32" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.11281197200476756</v>
+        <v>0.1547337211174622</v>
       </c>
       <c r="N32" s="3">
-        <v>1.5802781594350581</v>
+        <v>30.779220055399808</v>
       </c>
       <c r="O32" s="3">
-        <v>43.037974683544306</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P32" s="3">
         <v>27.28297753683016</v>
       </c>
       <c r="Q32" s="3">
-        <v>42.15189873417721</v>
+        <v>49.11392405063291</v>
       </c>
       <c r="R32" s="3">
-        <v>30.18987341772152</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="T32" s="3">
-        <v>-4.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4043,117 +4064,117 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D33" s="3">
-        <v>-0.06075044669446097</v>
+        <v>-0.06253722453841566</v>
       </c>
       <c r="E33" s="3">
-        <v>-1.79</v>
+        <v>-1.82</v>
       </c>
       <c r="F33" s="3">
-        <v>-0.1586820808873243</v>
+        <v>-0.13457613563665227</v>
       </c>
       <c r="G33" s="3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H33" s="3">
-        <v>40.52</v>
+        <v>48.11</v>
       </c>
       <c r="I33" s="3">
-        <v>-12.8</v>
+        <v>-13.06</v>
       </c>
       <c r="J33" s="3">
-        <v>0.007145973286055338</v>
+        <v>-0.010467823873542245</v>
       </c>
       <c r="K33" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M33" s="3">
-        <v>-0.14571695799142126</v>
+        <v>-0.11749911810426794</v>
       </c>
       <c r="N33" s="3">
-        <v>-1.7102204392303053</v>
+        <v>3.5559361332268087</v>
       </c>
       <c r="O33" s="3">
-        <v>35.44303797468354</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P33" s="3">
-        <v>25.92446787021105</v>
+        <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="3">
-        <v>45.189873417721515</v>
+        <v>42.65822784810126</v>
       </c>
       <c r="R33" s="3">
-        <v>37.151898734177216</v>
+        <v>34.1139240506329</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T33" s="3">
-        <v>-0.76</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>13.11</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>82.27848101265823</v>
       </c>
-      <c r="D34" s="2">
-        <v>-0.7360793287566743</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.05523282741864441</v>
-      </c>
-      <c r="G34" s="2">
+      <c r="D34" s="3">
+        <v>-0.7597254004576659</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.05179078220618741</v>
+      </c>
+      <c r="G34" s="3">
         <v>1.24</v>
       </c>
-      <c r="H34" s="2">
-        <v>49.52</v>
-      </c>
-      <c r="I34" s="2">
-        <v>19.17</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0.021334269510778048</v>
-      </c>
-      <c r="K34" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2">
-        <v>36</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0.08352036828243281</v>
-      </c>
-      <c r="N34" s="2">
-        <v>21.21351218815511</v>
-      </c>
-      <c r="O34" s="2">
-        <v>75.9493670886076</v>
-      </c>
-      <c r="P34" s="2">
-        <v>20.42247430615109</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>53.9240506329114</v>
-      </c>
-      <c r="R34" s="2">
-        <v>50.82278481012659</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T34" s="2">
-        <v>0.76</v>
+      <c r="H34" s="3">
+        <v>53.65</v>
+      </c>
+      <c r="I34" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.0060588775788692345</v>
+      </c>
+      <c r="K34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>40</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0.08594481727095604</v>
+      </c>
+      <c r="N34" s="3">
+        <v>23.900329670749194</v>
+      </c>
+      <c r="O34" s="3">
+        <v>62.0253164556962</v>
+      </c>
+      <c r="P34" s="3">
+        <v>16.20137630019195</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>49.74683544303797</v>
+      </c>
+      <c r="R34" s="3">
+        <v>45.31645569620254</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T34" s="3">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4167,55 +4188,55 @@
         <v>88.60759493670885</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.47380541162924583</v>
+        <v>-0.4766839378238342</v>
       </c>
       <c r="E35" s="1">
-        <v>8.84</v>
+        <v>8.86</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.3069178212901955</v>
+        <v>-0.32241064265928254</v>
       </c>
       <c r="G35" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H35" s="1">
-        <v>50.63</v>
+        <v>48.9</v>
       </c>
       <c r="I35" s="1">
-        <v>-18.27</v>
+        <v>-19.9</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.012000139273407349</v>
+        <v>-0.02072096608370196</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.31045376389816903</v>
+        <v>-0.328102981836744</v>
       </c>
       <c r="N35" s="1">
-        <v>-18.18390102990508</v>
+        <v>-17.504450240020805</v>
       </c>
       <c r="O35" s="1">
-        <v>5.063291139240507</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P35" s="1">
-        <v>27.295682949534427</v>
+        <v>31.92794275572307</v>
       </c>
       <c r="Q35" s="1">
-        <v>39.49367088607595</v>
+        <v>38.60759493670886</v>
       </c>
       <c r="R35" s="1">
-        <v>22.405063291139236</v>
+        <v>22.278481012658222</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T35" s="1">
-        <v>-2.22</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4229,55 +4250,55 @@
         <v>78.48101265822784</v>
       </c>
       <c r="D36" s="1">
-        <v>0.3596872284969592</v>
+        <v>0.34578627280625546</v>
       </c>
       <c r="E36" s="1">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.2580770032664025</v>
+        <v>-0.2703417042745459</v>
       </c>
       <c r="G36" s="1">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>48.95</v>
+        <v>39.26</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.72</v>
+        <v>-22.31</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.008930763070187062</v>
+        <v>-0.015472933043252417</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.24511188037049947</v>
+        <v>-0.25184160194779626</v>
       </c>
       <c r="N36" s="1">
-        <v>-11.64971267713813</v>
+        <v>-9.878312251126037</v>
       </c>
       <c r="O36" s="1">
-        <v>20.253164556962027</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P36" s="1">
-        <v>27.03345749163471</v>
+        <v>28.780078060741072</v>
       </c>
       <c r="Q36" s="1">
-        <v>41.39240506329113</v>
+        <v>37.21518987341772</v>
       </c>
       <c r="R36" s="1">
-        <v>28.9240506329114</v>
+        <v>25.949367088607598</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T36" s="1">
-        <v>3.67</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4291,55 +4312,55 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D37" s="1">
-        <v>0.6003752345215758</v>
+        <v>0.5347091932457786</v>
       </c>
       <c r="E37" s="1">
-        <v>-4.98</v>
+        <v>-5.96</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.22786933516044394</v>
+        <v>-0.20553417264747517</v>
       </c>
       <c r="G37" s="1">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H37" s="1">
-        <v>50.78</v>
+        <v>57.61</v>
       </c>
       <c r="I37" s="1">
-        <v>-20.52</v>
+        <v>-15.98</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.006907274076265041</v>
+        <v>-0.014092511752628564</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-215</v>
+        <v>-214</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.18779531893674373</v>
+        <v>-0.15857237443341832</v>
       </c>
       <c r="N37" s="1">
-        <v>-5.918056533762551</v>
+        <v>-0.5513894996882364</v>
       </c>
       <c r="O37" s="1">
-        <v>25.31645569620253</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P37" s="1">
-        <v>31.61854630334819</v>
+        <v>20.90944133883571</v>
       </c>
       <c r="Q37" s="1">
-        <v>37.974683544303794</v>
+        <v>39.36708860759494</v>
       </c>
       <c r="R37" s="1">
-        <v>25.632911392405063</v>
+        <v>28.797468354430382</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="T37" s="1">
-        <v>0.32</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4347,123 +4368,123 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>-0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="C38" s="2">
-        <v>21.518987341772153</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="D38" s="2">
-        <v>139.4736842105263</v>
+        <v>528.1999999999999</v>
       </c>
       <c r="E38" s="2">
-        <v>-1.63</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>0.414588017384123</v>
+        <v>0.8109835901490936</v>
       </c>
       <c r="G38" s="2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H38" s="2">
-        <v>59.47</v>
+        <v>74.59</v>
       </c>
       <c r="I38" s="2">
-        <v>41.68</v>
+        <v>58.14</v>
       </c>
       <c r="J38" s="2">
-        <v>0.05449797535697679</v>
+        <v>0.05591146967460016</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-46</v>
+        <v>-41</v>
       </c>
       <c r="M38" s="2">
-        <v>0.44405420578390253</v>
+        <v>0.8451376252138623</v>
       </c>
       <c r="N38" s="2">
-        <v>57.26689593830208</v>
+        <v>99.81961046503982</v>
       </c>
       <c r="O38" s="2">
-        <v>88.60759493670885</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P38" s="2">
-        <v>26.51995189252711</v>
+        <v>18.478263649022576</v>
       </c>
       <c r="Q38" s="2">
-        <v>67.34177215189874</v>
+        <v>73.03797468354429</v>
       </c>
       <c r="R38" s="2">
-        <v>57.658227848101255</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T38" s="2">
-        <v>0.13</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="1">
         <v>-0.25</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="1">
         <v>20.253164556962027</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="1">
         <v>44.4</v>
       </c>
-      <c r="E39" s="3">
-        <v>4.83</v>
-      </c>
-      <c r="F39" s="3">
-        <v>-0.1591001948151601</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46.14</v>
-      </c>
-      <c r="I39" s="3">
-        <v>-8.77</v>
-      </c>
-      <c r="J39" s="3">
-        <v>-0.016820409128281557</v>
-      </c>
-      <c r="K39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3">
-        <v>-4</v>
-      </c>
-      <c r="M39" s="3">
-        <v>-0.13552724409533645</v>
-      </c>
-      <c r="N39" s="3">
-        <v>-0.6912490496218264</v>
-      </c>
-      <c r="O39" s="3">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="P39" s="3">
+      <c r="E39" s="1">
+        <v>4.04</v>
+      </c>
+      <c r="F39" s="1">
+        <v>-0.23946422202207276</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="H39" s="1">
+        <v>55.02</v>
+      </c>
+      <c r="I39" s="1">
+        <v>-1.89</v>
+      </c>
+      <c r="J39" s="1">
+        <v>-0.012590421692770725</v>
+      </c>
+      <c r="K39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>-5</v>
+      </c>
+      <c r="M39" s="1">
+        <v>-0.2138486957234963</v>
+      </c>
+      <c r="N39" s="1">
+        <v>-6.079021628696032</v>
+      </c>
+      <c r="O39" s="1">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
-      <c r="Q39" s="3">
-        <v>37.84810126582279</v>
-      </c>
-      <c r="R39" s="3">
-        <v>30.56962025316456</v>
-      </c>
-      <c r="S39" s="3" t="s">
+      <c r="Q39" s="1">
+        <v>44.556962025316466</v>
+      </c>
+      <c r="R39" s="1">
+        <v>26.392405063291132</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T39" s="3">
-        <v>0.25</v>
+      <c r="T39" s="1">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4480,52 +4501,52 @@
         <v>9.173166926677066</v>
       </c>
       <c r="E40" s="1">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.3312951589593636</v>
+        <v>-0.2802028326881281</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>36.03</v>
+        <v>46.84</v>
       </c>
       <c r="I40" s="1">
-        <v>-35.48</v>
+        <v>-34.68</v>
       </c>
       <c r="J40" s="1">
-        <v>-0.0213691326339418</v>
+        <v>-0.051320290570548946</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M40" s="1">
-        <v>-0.44915991255848187</v>
+        <v>-0.4225113121246641</v>
       </c>
       <c r="N40" s="1">
-        <v>-32.05451589593636</v>
+        <v>-26.94528326881282</v>
       </c>
       <c r="O40" s="1">
-        <v>3.79746835443038</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="P40" s="1">
-        <v>42.434935391194514</v>
+        <v>51.742392838263484</v>
       </c>
       <c r="Q40" s="1">
-        <v>22.531645569620252</v>
+        <v>24.430379746835445</v>
       </c>
       <c r="R40" s="1">
-        <v>10.443037974683545</v>
+        <v>8.417721518987344</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>0.51</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4539,55 +4560,55 @@
         <v>5.063291139240507</v>
       </c>
       <c r="D41" s="3">
-        <v>7.013916500994036</v>
+        <v>6.749502982107356</v>
       </c>
       <c r="E41" s="3">
-        <v>-1.3</v>
+        <v>-1.26</v>
       </c>
       <c r="F41" s="3">
-        <v>0.11923562400143034</v>
+        <v>0.16787716220770937</v>
       </c>
       <c r="G41" s="3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H41" s="3">
-        <v>56.16</v>
+        <v>60.12</v>
       </c>
       <c r="I41" s="3">
-        <v>-5.27</v>
+        <v>-3.67</v>
       </c>
       <c r="J41" s="3">
-        <v>0.027088215580633096</v>
+        <v>0.016759292074575063</v>
       </c>
       <c r="K41" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M41" s="3">
-        <v>0.13809398457728927</v>
+        <v>0.18922343412318976</v>
       </c>
       <c r="N41" s="3">
-        <v>26.67087381764075</v>
+        <v>34.228191355972584</v>
       </c>
       <c r="O41" s="3">
-        <v>79.74683544303798</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P41" s="3">
-        <v>39.70588351306617</v>
+        <v>31.8795444982153</v>
       </c>
       <c r="Q41" s="3">
-        <v>45.44303797468355</v>
+        <v>43.54430379746836</v>
       </c>
       <c r="R41" s="3">
-        <v>39.936708860759495</v>
+        <v>37.40506329113924</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="T41" s="3">
-        <v>1.46</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4601,55 +4622,55 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D42" s="3">
-        <v>1.0664819944598338</v>
+        <v>1.0803324099722993</v>
       </c>
       <c r="E42" s="3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.10131904483173489</v>
+        <v>-0.0882771693683894</v>
       </c>
       <c r="G42" s="3">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H42" s="3">
-        <v>53.83</v>
+        <v>54.9</v>
       </c>
       <c r="I42" s="3">
-        <v>0.57</v>
+        <v>3.29</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.005480313432185138</v>
+        <v>0.00024552284031723287</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.17793113467116173</v>
+        <v>-0.18220076579650313</v>
       </c>
       <c r="N42" s="3">
-        <v>-4.931638107204353</v>
+        <v>-2.9142286359967216</v>
       </c>
       <c r="O42" s="3">
-        <v>29.11392405063291</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P42" s="3">
         <v>12.159120495183384</v>
       </c>
       <c r="Q42" s="3">
-        <v>43.67088607594937</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="R42" s="3">
-        <v>34.17721518987342</v>
+        <v>34.43037974683545</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T42" s="3">
-        <v>-0.7</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4663,55 +4684,55 @@
         <v>30.37974683544304</v>
       </c>
       <c r="D43" s="3">
-        <v>246.49999999999997</v>
+        <v>275.79999999999995</v>
       </c>
       <c r="E43" s="3">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3">
-        <v>-0.20161670338846616</v>
+        <v>-0.03870311839182436</v>
       </c>
       <c r="G43" s="3">
         <v>1.34</v>
       </c>
       <c r="H43" s="3">
-        <v>53.53</v>
+        <v>66.87</v>
       </c>
       <c r="I43" s="3">
-        <v>-1.81</v>
+        <v>11.1</v>
       </c>
       <c r="J43" s="3">
-        <v>0.004440131633989671</v>
+        <v>0.011255044342700209</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M43" s="3">
-        <v>-0.16154268716476594</v>
+        <v>0.009681764616597865</v>
       </c>
       <c r="N43" s="3">
-        <v>-3.2927933565647765</v>
+        <v>16.274024405313376</v>
       </c>
       <c r="O43" s="3">
-        <v>32.91139240506329</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P43" s="3">
         <v>26.894796563147693</v>
       </c>
       <c r="Q43" s="3">
-        <v>54.81012658227848</v>
+        <v>63.41772151898734</v>
       </c>
       <c r="R43" s="3">
-        <v>38.924050632911396</v>
+        <v>46.01265822784811</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="T43" s="3">
-        <v>-5</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4725,117 +4746,117 @@
         <v>39.24050632911392</v>
       </c>
       <c r="D44" s="3">
-        <v>26.80392156862745</v>
+        <v>26.558823529411764</v>
       </c>
       <c r="E44" s="3">
         <v>-2.29</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.4292435058371429</v>
+        <v>-0.36192279542703704</v>
       </c>
       <c r="G44" s="3">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="H44" s="3">
-        <v>52.3</v>
+        <v>58.54</v>
       </c>
       <c r="I44" s="3">
-        <v>-17.68</v>
+        <v>-11.72</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.005779492842713396</v>
+        <v>-0.011761160660354198</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-116</v>
+        <v>-119</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.24183854761454493</v>
+        <v>-0.13707539791731027</v>
       </c>
       <c r="N44" s="3">
-        <v>-11.322379401542666</v>
+        <v>1.5983081519225686</v>
       </c>
       <c r="O44" s="3">
-        <v>21.518987341772153</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P44" s="3">
-        <v>33.9792376983537</v>
+        <v>29.40653991657008</v>
       </c>
       <c r="Q44" s="3">
-        <v>47.21518987341772</v>
+        <v>49.493670886075954</v>
       </c>
       <c r="R44" s="3">
-        <v>30.886075949367086</v>
+        <v>34.303797468354425</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>-0.06</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="3">
         <v>8.37</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <v>70.88607594936708</v>
       </c>
-      <c r="D45" s="2">
-        <v>0.7132616487455199</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>-0.01630963278402417</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1.45</v>
-      </c>
-      <c r="H45" s="2">
-        <v>43.99</v>
-      </c>
-      <c r="I45" s="2">
-        <v>6.06</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0.014298688620694455</v>
-      </c>
-      <c r="K45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
+      <c r="D45" s="3">
+        <v>0.709677419354839</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>-0.05457892653206925</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="H45" s="3">
+        <v>50.05</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4.77</v>
+      </c>
+      <c r="J45" s="3">
+        <v>-0.0036544116075250773</v>
+      </c>
+      <c r="K45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>33</v>
       </c>
-      <c r="M45" s="2">
-        <v>0.03672950633557903</v>
-      </c>
-      <c r="N45" s="2">
-        <v>16.53442599346972</v>
-      </c>
-      <c r="O45" s="2">
-        <v>67.08860759493672</v>
-      </c>
-      <c r="P45" s="2">
-        <v>18.755109025385668</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>52.65822784810126</v>
-      </c>
-      <c r="R45" s="2">
-        <v>51.64556962025317</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T45" s="2">
-        <v>0.89</v>
+      <c r="M45" s="3">
+        <v>0.010882974008737278</v>
+      </c>
+      <c r="N45" s="3">
+        <v>16.39414534452733</v>
+      </c>
+      <c r="O45" s="3">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="P45" s="3">
+        <v>17.44790626256815</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>49.49367088607594</v>
+      </c>
+      <c r="R45" s="3">
+        <v>44.17721518987342</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T45" s="3">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4849,55 +4870,55 @@
         <v>18.9873417721519</v>
       </c>
       <c r="D46" s="1">
-        <v>564.5333333333334</v>
+        <v>671.2333333333333</v>
       </c>
       <c r="E46" s="1">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.35774699407510546</v>
+        <v>-0.451284215066708</v>
       </c>
       <c r="G46" s="1">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="H46" s="1">
-        <v>43.43</v>
+        <v>35.61</v>
       </c>
       <c r="I46" s="1">
-        <v>-13.13</v>
+        <v>-25.34</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.014412624427333395</v>
+        <v>-0.03807576023963544</v>
       </c>
       <c r="K46" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.3011719123475287</v>
+        <v>-0.3772838057597093</v>
       </c>
       <c r="N46" s="1">
-        <v>-17.255715874841048</v>
+        <v>-22.422532632317342</v>
       </c>
       <c r="O46" s="1">
-        <v>6.329113924050633</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P46" s="1">
-        <v>50.613275903697605</v>
+        <v>41.79422060400345</v>
       </c>
       <c r="Q46" s="1">
-        <v>40.506329113924046</v>
+        <v>37.088607594936704</v>
       </c>
       <c r="R46" s="1">
-        <v>21.835443037974684</v>
+        <v>22.21518987341772</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.13</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4914,114 +4935,114 @@
         <v>0.8549905838041432</v>
       </c>
       <c r="E47" s="1">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.3487318651468219</v>
+        <v>-0.31024696725352574</v>
       </c>
       <c r="G47" s="1">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H47" s="1">
-        <v>60.71</v>
+        <v>53.34</v>
       </c>
       <c r="I47" s="1">
-        <v>-12.35</v>
+        <v>-14.36</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.009845944277940756</v>
+        <v>-0.03183408131835473</v>
       </c>
       <c r="K47" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.30040731617118344</v>
+        <v>-0.24905432109581527</v>
       </c>
       <c r="N47" s="1">
-        <v>-17.17925625720652</v>
+        <v>-9.599584165927936</v>
       </c>
       <c r="O47" s="1">
-        <v>7.59493670886076</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P47" s="1">
         <v>33.84253937304741</v>
       </c>
       <c r="Q47" s="1">
-        <v>48.73417721518988</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="R47" s="1">
-        <v>25.949367088607595</v>
+        <v>26.962025316455698</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T47" s="1">
-        <v>-0.19</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="3">
         <v>3.98</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <v>51.89873417721519</v>
       </c>
-      <c r="D48" s="2">
-        <v>8.06281407035176</v>
-      </c>
-      <c r="E48" s="2">
-        <v>3.41</v>
-      </c>
-      <c r="F48" s="2">
-        <v>-0.08752660329796674</v>
-      </c>
-      <c r="G48" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="H48" s="2">
-        <v>48.85</v>
-      </c>
-      <c r="I48" s="2">
-        <v>40.65</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0.015362358907214027</v>
-      </c>
-      <c r="K48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>247</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0.03505274044511619</v>
-      </c>
-      <c r="N48" s="2">
-        <v>16.36674940442345</v>
-      </c>
-      <c r="O48" s="2">
-        <v>64.55696202531645</v>
-      </c>
-      <c r="P48" s="2">
+      <c r="D48" s="3">
+        <v>7.922110552763819</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="F48" s="3">
+        <v>-0.08364511082593934</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.05</v>
+      </c>
+      <c r="H48" s="3">
+        <v>50.48</v>
+      </c>
+      <c r="I48" s="3">
+        <v>36.45</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0.0023912903891721016</v>
+      </c>
+      <c r="K48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>248</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0.06577879258242336</v>
+      </c>
+      <c r="N48" s="3">
+        <v>21.883727201895923</v>
+      </c>
+      <c r="O48" s="3">
+        <v>60.75949367088608</v>
+      </c>
+      <c r="P48" s="3">
         <v>25.31695963070349</v>
       </c>
-      <c r="Q48" s="2">
-        <v>60</v>
-      </c>
-      <c r="R48" s="2">
-        <v>50.31645569620253</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T48" s="2">
-        <v>-0.19</v>
+      <c r="Q48" s="3">
+        <v>57.59493670886076</v>
+      </c>
+      <c r="R48" s="3">
+        <v>46.77215189873418</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="T48" s="3">
+        <v>1.71</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5032,58 +5053,58 @@
         <v>-0.06</v>
       </c>
       <c r="C49" s="2">
-        <v>26.582278481012654</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="D49" s="2">
-        <v>1734.8333333333335</v>
+        <v>1788.6666666666667</v>
       </c>
       <c r="E49" s="2">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="F49" s="2">
-        <v>0.3861512497892915</v>
+        <v>0.6267274511648374</v>
       </c>
       <c r="G49" s="2">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="H49" s="2">
-        <v>56.96</v>
+        <v>52.1</v>
       </c>
       <c r="I49" s="2">
-        <v>93.36</v>
+        <v>77.78</v>
       </c>
       <c r="J49" s="2">
-        <v>0.054081015371308744</v>
+        <v>0.025305338711747616</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M49" s="2">
-        <v>0.7102793221868666</v>
+        <v>1.0223450239984073</v>
       </c>
       <c r="N49" s="2">
-        <v>83.8894075785985</v>
+        <v>117.54035034349431</v>
       </c>
       <c r="O49" s="2">
-        <v>92.40506329113924</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="P49" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q49" s="2">
-        <v>72.0253164556962</v>
+        <v>67.59493670886076</v>
       </c>
       <c r="R49" s="2">
-        <v>61.01265822784809</v>
+        <v>60.189873417721515</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T49" s="2">
-        <v>0.76</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5094,7 +5115,7 @@
         <v>-0.13</v>
       </c>
       <c r="C50" s="1">
-        <v>25.31645569620253</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="D50" s="1">
         <v>300.1538461538462</v>
@@ -5103,19 +5124,19 @@
         <v>5.32</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.513158884109552</v>
+        <v>-0.48221474512597207</v>
       </c>
       <c r="G50" s="1">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H50" s="1">
-        <v>43.13</v>
+        <v>44.69</v>
       </c>
       <c r="I50" s="1">
-        <v>-25.98</v>
+        <v>-26.02</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.026872051862036873</v>
+        <v>-0.02669903068997639</v>
       </c>
       <c r="K50" s="1" t="b">
         <v>0</v>
@@ -5124,28 +5145,28 @@
         <v>-1</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.4518692122380106</v>
+        <v>-0.40963742061333874</v>
       </c>
       <c r="N50" s="1">
-        <v>-32.325445863889236</v>
+        <v>-25.657894117680275</v>
       </c>
       <c r="O50" s="1">
-        <v>2.5316455696202533</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P50" s="1">
-        <v>42.0212746732318</v>
+        <v>43.085103448616955</v>
       </c>
       <c r="Q50" s="1">
-        <v>38.48101265822785</v>
+        <v>40</v>
       </c>
       <c r="R50" s="1">
-        <v>22.405063291139243</v>
+        <v>21.83544303797468</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T50" s="1">
-        <v>-0.13</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5159,55 +5180,55 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D51" s="3">
-        <v>16.3659793814433</v>
+        <v>16.36340206185567</v>
       </c>
       <c r="E51" s="3">
-        <v>36.11</v>
+        <v>22.56</v>
       </c>
       <c r="F51" s="3">
-        <v>-0.16242541931150978</v>
+        <v>-0.1539150887367241</v>
       </c>
       <c r="G51" s="3">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H51" s="3">
-        <v>45.49</v>
+        <v>39.33</v>
       </c>
       <c r="I51" s="3">
-        <v>13.28</v>
+        <v>-4.29</v>
       </c>
       <c r="J51" s="3">
-        <v>0.030799202986335563</v>
+        <v>-0.006719518763636606</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M51" s="3">
-        <v>0.007299825871220467</v>
+        <v>0.062393800006810496</v>
       </c>
       <c r="N51" s="3">
-        <v>13.591457947033861</v>
+        <v>21.545227944334652</v>
       </c>
       <c r="O51" s="3">
-        <v>56.9620253164557</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P51" s="3">
-        <v>46.744012320672994</v>
+        <v>39.29181220981388</v>
       </c>
       <c r="Q51" s="3">
-        <v>50.25316455696203</v>
+        <v>34.936708860759495</v>
       </c>
       <c r="R51" s="3">
-        <v>36.39240506329114</v>
+        <v>32.721518987341774</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="T51" s="3">
-        <v>0</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5221,55 +5242,55 @@
         <v>56.9620253164557</v>
       </c>
       <c r="D52" s="2">
-        <v>6.766037735849057</v>
+        <v>6.983018867924529</v>
       </c>
       <c r="E52" s="2">
-        <v>-1.41</v>
+        <v>-1.43</v>
       </c>
       <c r="F52" s="2">
-        <v>0.556335119489242</v>
+        <v>0.3320117502240813</v>
       </c>
       <c r="G52" s="2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H52" s="2">
-        <v>71.7</v>
+        <v>48.18</v>
       </c>
       <c r="I52" s="2">
-        <v>86.55</v>
+        <v>56.35</v>
       </c>
       <c r="J52" s="2">
-        <v>0.05116104561745051</v>
+        <v>0.040050243203196244</v>
       </c>
       <c r="K52" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="M52" s="2">
-        <v>0.6553415125125013</v>
+        <v>0.4501277881564061</v>
       </c>
       <c r="N52" s="2">
-        <v>78.39562661116194</v>
+        <v>60.31862675929421</v>
       </c>
       <c r="O52" s="2">
-        <v>91.13924050632912</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P52" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q52" s="2">
-        <v>69.62025316455697</v>
+        <v>64.17721518987341</v>
       </c>
       <c r="R52" s="2">
-        <v>61.77215189873418</v>
+        <v>60.696202531645575</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="T52" s="2">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5286,176 +5307,176 @@
         <v>6.873239436619719</v>
       </c>
       <c r="E53" s="1">
-        <v>5.43</v>
+        <v>5.04</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.3109493603710671</v>
+        <v>-0.2495027505178145</v>
       </c>
       <c r="G53" s="1">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="H53" s="1">
-        <v>41.32</v>
+        <v>45.89</v>
       </c>
       <c r="I53" s="1">
-        <v>-29.04</v>
+        <v>-27.64</v>
       </c>
       <c r="J53" s="1">
-        <v>0.011509910347321772</v>
+        <v>0.003788273260567938</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.12000845954049555</v>
+        <v>-0.014693759447530264</v>
       </c>
       <c r="N53" s="1">
-        <v>0.8606294058622744</v>
+        <v>13.836471998900576</v>
       </c>
       <c r="O53" s="1">
-        <v>40.50632911392405</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P53" s="1">
-        <v>46.06334900207262</v>
+        <v>35.00545268745836</v>
       </c>
       <c r="Q53" s="1">
-        <v>35.06329113924051</v>
+        <v>35.31645569620254</v>
       </c>
       <c r="R53" s="1">
-        <v>27.08860759493671</v>
+        <v>28.734177215189874</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="T53" s="1">
-        <v>-3.1</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="3">
         <v>0.66</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3">
         <v>34.177215189873415</v>
       </c>
-      <c r="D54" s="2">
-        <v>34.06060606060606</v>
-      </c>
-      <c r="E54" s="2">
-        <v>-2.25</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0.00852578710285859</v>
-      </c>
-      <c r="G54" s="2">
-        <v>1.45</v>
-      </c>
-      <c r="H54" s="2">
-        <v>50.22</v>
-      </c>
-      <c r="I54" s="2">
-        <v>-0.29</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0.01582578777085134</v>
-      </c>
-      <c r="K54" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2">
-        <v>10</v>
-      </c>
-      <c r="M54" s="2">
-        <v>0.06156492622246179</v>
-      </c>
-      <c r="N54" s="2">
-        <v>19.01796798215799</v>
-      </c>
-      <c r="O54" s="2">
-        <v>69.62025316455697</v>
-      </c>
-      <c r="P54" s="2">
+      <c r="D54" s="3">
+        <v>34.6060606060606</v>
+      </c>
+      <c r="E54" s="3">
+        <v>-1.9</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.025557787859203318</v>
+      </c>
+      <c r="G54" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="H54" s="3">
+        <v>53.69</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0.009917377126776376</v>
+      </c>
+      <c r="K54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3">
+        <v>9</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0.09101968840000985</v>
+      </c>
+      <c r="N54" s="3">
+        <v>24.407816783654585</v>
+      </c>
+      <c r="O54" s="3">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="P54" s="3">
         <v>25.062459708672506</v>
       </c>
-      <c r="Q54" s="2">
-        <v>56.58227848101266</v>
-      </c>
-      <c r="R54" s="2">
-        <v>51.455696202531655</v>
-      </c>
-      <c r="S54" s="2" t="s">
+      <c r="Q54" s="3">
+        <v>57.08860759493672</v>
+      </c>
+      <c r="R54" s="3">
+        <v>49.0506329113924</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T54" s="2">
-        <v>-0.76</v>
+      <c r="T54" s="3">
+        <v>0.85</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="3">
         <v>4.03</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3">
         <v>54.43037974683544</v>
       </c>
-      <c r="D55" s="2">
-        <v>2.3176178660049627</v>
-      </c>
-      <c r="E55" s="2">
-        <v>-2.09</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0.05043589148721053</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1.19</v>
-      </c>
-      <c r="H55" s="2">
-        <v>72.52</v>
-      </c>
-      <c r="I55" s="2">
-        <v>8.21</v>
-      </c>
-      <c r="J55" s="2">
-        <v>0.01354016624185713</v>
-      </c>
-      <c r="K55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>-65</v>
-      </c>
-      <c r="M55" s="2">
-        <v>0.07283019467104301</v>
-      </c>
-      <c r="N55" s="2">
-        <v>20.14449482701613</v>
-      </c>
-      <c r="O55" s="2">
-        <v>73.41772151898735</v>
-      </c>
-      <c r="P55" s="2">
-        <v>17.353613604156827</v>
-      </c>
-      <c r="Q55" s="2">
+      <c r="D55" s="3">
+        <v>2.404466501240695</v>
+      </c>
+      <c r="E55" s="3">
+        <v>-2.1</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.03436771622135912</v>
+      </c>
+      <c r="G55" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="H55" s="3">
+        <v>74.23</v>
+      </c>
+      <c r="I55" s="3">
+        <v>13.83</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0.00895932474010244</v>
+      </c>
+      <c r="K55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3">
+        <v>-64</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0.05998324251993559</v>
+      </c>
+      <c r="N55" s="3">
+        <v>21.30417219564715</v>
+      </c>
+      <c r="O55" s="3">
         <v>58.22784810126582</v>
       </c>
-      <c r="R55" s="2">
-        <v>51.835443037974684</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T55" s="2">
-        <v>0.32</v>
+      <c r="P55" s="3">
+        <v>17.1778029656448</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>58.10126582278481</v>
+      </c>
+      <c r="R55" s="3">
+        <v>47.08860759493671</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T55" s="3">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5469,55 +5490,55 @@
         <v>72.15189873417721</v>
       </c>
       <c r="D56" s="3">
-        <v>0.18843930635838138</v>
+        <v>0.2034682080924855</v>
       </c>
       <c r="E56" s="3">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="F56" s="3">
-        <v>-0.08088397609813</v>
+        <v>0.02354502790658959</v>
       </c>
       <c r="G56" s="3">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H56" s="3">
-        <v>50.72</v>
+        <v>67.84</v>
       </c>
       <c r="I56" s="3">
-        <v>7.93</v>
+        <v>18.23</v>
       </c>
       <c r="J56" s="3">
-        <v>-0.0022956135858685878</v>
+        <v>0.011892994603856162</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="3">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M56" s="3">
-        <v>-0.16928254129746867</v>
+        <v>-0.08603250125954309</v>
       </c>
       <c r="N56" s="3">
-        <v>-4.066778769835045</v>
+        <v>6.70259781769928</v>
       </c>
       <c r="O56" s="3">
-        <v>30.37974683544304</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P56" s="3">
         <v>10.95912073621325</v>
       </c>
       <c r="Q56" s="3">
-        <v>45.189873417721515</v>
+        <v>57.72151898734177</v>
       </c>
       <c r="R56" s="3">
-        <v>35.88607594936709</v>
+        <v>42.21518987341773</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="T56" s="3">
-        <v>-2.66</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5525,61 +5546,61 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>21.18</v>
+        <v>44.17</v>
       </c>
       <c r="C57" s="2">
-        <v>96.20253164556962</v>
+        <v>100</v>
       </c>
       <c r="D57" s="2">
-        <v>2.9485363550519357</v>
+        <v>1.4736246321032376</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.92</v>
+        <v>-1.89</v>
       </c>
       <c r="F57" s="2">
-        <v>1.1899045590932</v>
+        <v>1.367828202513795</v>
       </c>
       <c r="G57" s="2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H57" s="2">
-        <v>66.14</v>
+        <v>49.04</v>
       </c>
       <c r="I57" s="2">
-        <v>176.92</v>
+        <v>119.58</v>
       </c>
       <c r="J57" s="2">
-        <v>0.09977261592336065</v>
+        <v>0.07466484734736409</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M57" s="2">
-        <v>1.3266276732681772</v>
+        <v>1.5357522082489075</v>
       </c>
       <c r="N57" s="2">
-        <v>145.5242426867295</v>
+        <v>168.88106876854437</v>
       </c>
       <c r="O57" s="2">
-        <v>93.67088607594937</v>
+        <v>100</v>
       </c>
       <c r="P57" s="2">
         <v>30.30559414893712</v>
       </c>
       <c r="Q57" s="2">
-        <v>82.15189873417721</v>
+        <v>76.45569620253164</v>
       </c>
       <c r="R57" s="2">
-        <v>67.53164556962025</v>
+        <v>68.98734177215191</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="T57" s="2">
-        <v>0.25</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5593,55 +5614,55 @@
         <v>93.67088607594937</v>
       </c>
       <c r="D58" s="2">
-        <v>0.09900497512437803</v>
+        <v>0.11542288557213931</v>
       </c>
       <c r="E58" s="2">
-        <v>-1</v>
+        <v>-0.98</v>
       </c>
       <c r="F58" s="2">
-        <v>0.16918926990790614</v>
+        <v>0.11531216671472619</v>
       </c>
       <c r="G58" s="2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H58" s="2">
-        <v>61.15</v>
+        <v>51.68</v>
       </c>
       <c r="I58" s="2">
-        <v>43.62</v>
+        <v>38.67</v>
       </c>
       <c r="J58" s="2">
-        <v>0.02424541368332005</v>
+        <v>0.023407444460111584</v>
       </c>
       <c r="K58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M58" s="2">
-        <v>0.2399081220673771</v>
+        <v>0.1992741695822824</v>
       </c>
       <c r="N58" s="2">
-        <v>36.85228756664954</v>
+        <v>35.233264901881824</v>
       </c>
       <c r="O58" s="2">
-        <v>82.27848101265823</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P58" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q58" s="2">
-        <v>67.08860759493672</v>
+        <v>64.30379746835443</v>
       </c>
       <c r="R58" s="2">
-        <v>60.9493670886076</v>
+        <v>59.43037974683545</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T58" s="2">
-        <v>0.95</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5652,58 +5673,58 @@
         <v>34.32</v>
       </c>
       <c r="C59" s="3">
-        <v>100</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="D59" s="3">
-        <v>-1.4967948717948718</v>
+        <v>-1.4458041958041958</v>
       </c>
       <c r="E59" s="3">
-        <v>-1.03</v>
+        <v>-1.06</v>
       </c>
       <c r="F59" s="3">
-        <v>0.0704784520071017</v>
+        <v>0.13044616792085095</v>
       </c>
       <c r="G59" s="3">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="H59" s="3">
-        <v>53.03</v>
+        <v>60.49</v>
       </c>
       <c r="I59" s="3">
-        <v>30.08</v>
+        <v>44.51</v>
       </c>
       <c r="J59" s="3">
-        <v>0.005885000866749586</v>
+        <v>0.011383995972947876</v>
       </c>
       <c r="K59" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="M59" s="3">
-        <v>0.07872898475904</v>
+        <v>0.12902308312648558</v>
       </c>
       <c r="N59" s="3">
-        <v>20.73437383581582</v>
+        <v>28.208156256302146</v>
       </c>
       <c r="O59" s="3">
-        <v>74.68354430379746</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P59" s="3">
         <v>24.570041255395854</v>
       </c>
       <c r="Q59" s="3">
-        <v>54.43037974683544</v>
+        <v>60.632911392405056</v>
       </c>
       <c r="R59" s="3">
-        <v>48.9873417721519</v>
+        <v>48.54430379746836</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>94</v>
       </c>
       <c r="T59" s="3">
-        <v>3.04</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5717,55 +5738,55 @@
         <v>64.55696202531645</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.18210361067503927</v>
+        <v>-0.21193092621664059</v>
       </c>
       <c r="E60" s="1">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.12254475509947456</v>
+        <v>-0.14936403266665277</v>
       </c>
       <c r="G60" s="1">
         <v>0.36</v>
       </c>
       <c r="H60" s="1">
-        <v>49.19</v>
+        <v>49.92</v>
       </c>
       <c r="I60" s="1">
-        <v>-2.65</v>
+        <v>-4.53</v>
       </c>
       <c r="J60" s="1">
-        <v>-0.007223171177232919</v>
+        <v>-0.010619480610974712</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M60" s="1">
-        <v>-0.19797819740291023</v>
+        <v>-0.2404414595060358</v>
       </c>
       <c r="N60" s="1">
-        <v>-6.936344380379202</v>
+        <v>-8.738298006949986</v>
       </c>
       <c r="O60" s="1">
-        <v>24.050632911392405</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P60" s="1">
-        <v>17.48490342947292</v>
+        <v>20.23094761715597</v>
       </c>
       <c r="Q60" s="1">
-        <v>36.70886075949367</v>
+        <v>36.835443037974684</v>
       </c>
       <c r="R60" s="1">
-        <v>28.60759493670886</v>
+        <v>25.18987341772152</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T60" s="1">
-        <v>0.51</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5779,25 +5800,25 @@
         <v>91.13924050632912</v>
       </c>
       <c r="D61" s="3">
-        <v>0.46515580736543916</v>
+        <v>0.44815864022662893</v>
       </c>
       <c r="E61" s="3">
-        <v>-1.16</v>
+        <v>-1.13</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.09066052851141675</v>
+        <v>-0.035424935709090444</v>
       </c>
       <c r="G61" s="3">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H61" s="3">
-        <v>55.74</v>
+        <v>64.67</v>
       </c>
       <c r="I61" s="3">
-        <v>10.6</v>
+        <v>18.82</v>
       </c>
       <c r="J61" s="3">
-        <v>0.0014107865212750752</v>
+        <v>0.0072582355933146015</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>0</v>
@@ -5806,28 +5827,28 @@
         <v>171</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.1000897087993462</v>
+        <v>-0.049655783652744034</v>
       </c>
       <c r="N61" s="3">
-        <v>2.8525044799772097</v>
+        <v>10.340269578379194</v>
       </c>
       <c r="O61" s="3">
-        <v>48.10126582278481</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P61" s="3">
         <v>20.131624188012864</v>
       </c>
       <c r="Q61" s="3">
-        <v>56.9620253164557</v>
+        <v>63.037974683544306</v>
       </c>
       <c r="R61" s="3">
-        <v>46.07594936708861</v>
+        <v>46.32911392405064</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="T61" s="3">
-        <v>2.85</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5838,58 +5859,58 @@
         <v>28.77</v>
       </c>
       <c r="C62" s="4">
-        <v>98.73417721518987</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="D62" s="4">
-        <v>5.503302050747306</v>
+        <v>6.116440736878693</v>
       </c>
       <c r="E62" s="4">
-        <v>-4.88</v>
+        <v>-4.87</v>
       </c>
       <c r="F62" s="4">
-        <v>1.4170687167277918</v>
+        <v>0.7555642635056954</v>
       </c>
       <c r="G62" s="4">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="H62" s="4">
-        <v>73.2</v>
+        <v>46.79</v>
       </c>
       <c r="I62" s="4">
-        <v>253.44</v>
+        <v>145.13</v>
       </c>
       <c r="J62" s="4">
-        <v>0.10071815716550868</v>
+        <v>0.06847855407930967</v>
       </c>
       <c r="K62" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="4">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="M62" s="4">
-        <v>1.8743839606923707</v>
+        <v>1.3333366900180312</v>
       </c>
       <c r="N62" s="4">
-        <v>200.29987142914888</v>
+        <v>148.6395169454567</v>
       </c>
       <c r="O62" s="4">
-        <v>100</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P62" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q62" s="4">
-        <v>85.44303797468353</v>
+        <v>77.34177215189872</v>
       </c>
       <c r="R62" s="4">
-        <v>72.91139240506328</v>
+        <v>70.82278481012659</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T62" s="4">
-        <v>0.32</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5903,55 +5924,55 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D63" s="2">
-        <v>6.978178368121444</v>
+        <v>7.2751423149905134</v>
       </c>
       <c r="E63" s="2">
-        <v>-2.76</v>
+        <v>-2.32</v>
       </c>
       <c r="F63" s="2">
-        <v>1.4246922060771565</v>
+        <v>0.7140444865391655</v>
       </c>
       <c r="G63" s="2">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H63" s="2">
-        <v>73.71</v>
+        <v>46.1</v>
       </c>
       <c r="I63" s="2">
-        <v>158.37</v>
+        <v>88.71</v>
       </c>
       <c r="J63" s="2">
-        <v>0.07524095676433057</v>
+        <v>0.043880745368365205</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M63" s="2">
-        <v>1.550807492428213</v>
+        <v>0.8691607291249897</v>
       </c>
       <c r="N63" s="2">
-        <v>167.94222460273312</v>
+        <v>102.22192085615258</v>
       </c>
       <c r="O63" s="2">
-        <v>94.9367088607595</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P63" s="2">
-        <v>20.9978319173529</v>
+        <v>25.033824735762032</v>
       </c>
       <c r="Q63" s="2">
-        <v>78.73417721518987</v>
+        <v>70.8860759493671</v>
       </c>
       <c r="R63" s="2">
-        <v>68.35443037974684</v>
+        <v>65.56962025316457</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T63" s="2">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5968,52 +5989,52 @@
         <v>-0.28986366330764674</v>
       </c>
       <c r="E64" s="3">
-        <v>-1.13</v>
+        <v>-1.12</v>
       </c>
       <c r="F64" s="3">
-        <v>-0.07909457868523909</v>
+        <v>0.15513341454845112</v>
       </c>
       <c r="G64" s="3">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H64" s="3">
-        <v>54.67</v>
+        <v>81.34</v>
       </c>
       <c r="I64" s="3">
-        <v>1.87</v>
+        <v>19.12</v>
       </c>
       <c r="J64" s="3">
-        <v>0.0006404470192988076</v>
+        <v>0.016385690434724855</v>
       </c>
       <c r="K64" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M64" s="3">
-        <v>-0.16042125866863066</v>
+        <v>0.05409439414851058</v>
       </c>
       <c r="N64" s="3">
-        <v>-3.1806505069512445</v>
+        <v>20.71528735850465</v>
       </c>
       <c r="O64" s="3">
-        <v>34.177215189873415</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P64" s="3">
         <v>15.211254913322609</v>
       </c>
       <c r="Q64" s="3">
-        <v>49.620253164556964</v>
+        <v>63.54430379746836</v>
       </c>
       <c r="R64" s="3">
-        <v>38.924050632911396</v>
+        <v>49.55696202531646</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T64" s="3">
-        <v>0.51</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6027,55 +6048,55 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.09085402786190197</v>
+        <v>-0.09388249545729864</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.5140003910942923</v>
+        <v>-0.5060634564781621</v>
       </c>
       <c r="G65" s="1">
         <v>0.98</v>
       </c>
       <c r="H65" s="1">
-        <v>34.17</v>
+        <v>41.42</v>
       </c>
       <c r="I65" s="1">
-        <v>-47</v>
+        <v>-45.94</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.03813979562715102</v>
+        <v>-0.038260526367539655</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-199</v>
+        <v>-205</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.5163576861662746</v>
+        <v>-0.5089096260668928</v>
       </c>
       <c r="N65" s="1">
-        <v>-38.774293256715644</v>
+        <v>-35.58511466303568</v>
       </c>
       <c r="O65" s="1">
         <v>1.2658227848101267</v>
       </c>
       <c r="P65" s="1">
-        <v>50.931782654789714</v>
+        <v>46.98962940205603</v>
       </c>
       <c r="Q65" s="1">
-        <v>32.278481012658226</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="R65" s="1">
-        <v>16.89873417721519</v>
+        <v>17.40506329113924</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T65" s="1">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6089,55 +6110,55 @@
         <v>53.16455696202531</v>
       </c>
       <c r="D66" s="3">
-        <v>7.221945137157108</v>
+        <v>7.30922693266833</v>
       </c>
       <c r="E66" s="3">
-        <v>-1.7</v>
+        <v>-1.74</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.19591448350607013</v>
+        <v>-0.16348505920453266</v>
       </c>
       <c r="G66" s="3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H66" s="3">
-        <v>53.72</v>
+        <v>49.57</v>
       </c>
       <c r="I66" s="3">
-        <v>-10.97</v>
+        <v>-10.58</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.001098775231587882</v>
+        <v>-0.004561860607385339</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="3">
-        <v>-75</v>
+        <v>-81</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.18177071307417592</v>
+        <v>-0.144984956877783</v>
       </c>
       <c r="N66" s="3">
-        <v>-5.315595947505765</v>
+        <v>0.8073522558752926</v>
       </c>
       <c r="O66" s="3">
         <v>27.848101265822784</v>
       </c>
       <c r="P66" s="3">
-        <v>18.57346443046155</v>
+        <v>13.33838297691908</v>
       </c>
       <c r="Q66" s="3">
-        <v>49.36708860759494</v>
+        <v>47.974683544303794</v>
       </c>
       <c r="R66" s="3">
-        <v>38.41772151898734</v>
+        <v>39.81012658227848</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T66" s="3">
-        <v>0.51</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6151,117 +6172,117 @@
         <v>67.08860759493672</v>
       </c>
       <c r="D67" s="3">
-        <v>331.58775510204083</v>
+        <v>181.49251700680273</v>
       </c>
       <c r="E67" s="3">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.18480245132414647</v>
+        <v>-0.1314275293340424</v>
       </c>
       <c r="G67" s="3">
         <v>0.34</v>
       </c>
       <c r="H67" s="3">
-        <v>41.02</v>
+        <v>53.83</v>
       </c>
       <c r="I67" s="3">
-        <v>-3.03</v>
+        <v>-0.31</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.0098167248810661</v>
+        <v>-0.005944274591974259</v>
       </c>
       <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.2625931886995645</v>
+        <v>-0.2253511257621561</v>
       </c>
       <c r="N67" s="3">
-        <v>-13.397843510044623</v>
+        <v>-7.22926463256202</v>
       </c>
       <c r="O67" s="3">
-        <v>16.455696202531644</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P67" s="3">
         <v>22.02824070768656</v>
       </c>
       <c r="Q67" s="3">
-        <v>56.32911392405063</v>
+        <v>63.037974683544306</v>
       </c>
       <c r="R67" s="3">
-        <v>43.54430379746835</v>
+        <v>43.54430379746836</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T67" s="3">
-        <v>-1.14</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="3">
         <v>8.24</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="3">
         <v>69.62025316455697</v>
       </c>
-      <c r="D68" s="1">
-        <v>0.54126213592233</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="D68" s="3">
+        <v>0.6189320388349514</v>
+      </c>
+      <c r="E68" s="3">
         <v>-1.22</v>
       </c>
-      <c r="F68" s="1">
-        <v>-0.31532576038557225</v>
-      </c>
-      <c r="G68" s="1">
+      <c r="F68" s="3">
+        <v>-0.25965712096269183</v>
+      </c>
+      <c r="G68" s="3">
         <v>1.45</v>
       </c>
-      <c r="H68" s="1">
-        <v>45.22</v>
-      </c>
-      <c r="I68" s="1">
-        <v>-14.8</v>
-      </c>
-      <c r="J68" s="1">
-        <v>-0.009023979996625962</v>
-      </c>
-      <c r="K68" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>-69</v>
-      </c>
-      <c r="M68" s="1">
-        <v>-0.262286621265969</v>
-      </c>
-      <c r="N68" s="1">
-        <v>-13.367186766685077</v>
-      </c>
-      <c r="O68" s="1">
-        <v>17.72151898734177</v>
-      </c>
-      <c r="P68" s="1">
-        <v>23.92352836551796</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>38.35443037974684</v>
-      </c>
-      <c r="R68" s="1">
-        <v>28.227848101265828</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T68" s="1">
-        <v>-0.57</v>
+      <c r="H68" s="3">
+        <v>59.71</v>
+      </c>
+      <c r="I68" s="3">
+        <v>-11.39</v>
+      </c>
+      <c r="J68" s="3">
+        <v>-0.012117242891808658</v>
+      </c>
+      <c r="K68" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>-71</v>
+      </c>
+      <c r="M68" s="3">
+        <v>-0.19561830521625068</v>
+      </c>
+      <c r="N68" s="3">
+        <v>-4.255982577971476</v>
+      </c>
+      <c r="O68" s="3">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="P68" s="3">
+        <v>21.54356280679835</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>45.44303797468355</v>
+      </c>
+      <c r="R68" s="3">
+        <v>30.69620253164557</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="T68" s="3">
+        <v>1.85</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6275,55 +6296,55 @@
         <v>92.40506329113924</v>
       </c>
       <c r="D69" s="3">
-        <v>-0.4843320505772402</v>
+        <v>-0.4821330401319407</v>
       </c>
       <c r="E69" s="3">
-        <v>-2.56</v>
+        <v>-2.6</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.10430077299850737</v>
+        <v>-0.07994686480280469</v>
       </c>
       <c r="G69" s="3">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="H69" s="3">
-        <v>51.12</v>
+        <v>63.37</v>
       </c>
       <c r="I69" s="3">
-        <v>-9.54</v>
+        <v>-1.72</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.0014627186769465284</v>
+        <v>-0.0018980943549039152</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.11844454343040156</v>
+        <v>-0.09987005192391973</v>
       </c>
       <c r="N69" s="3">
-        <v>1.0170210168716756</v>
+        <v>5.318842751261615</v>
       </c>
       <c r="O69" s="3">
-        <v>41.77215189873418</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P69" s="3">
-        <v>31.450467124868602</v>
+        <v>19.82954339952731</v>
       </c>
       <c r="Q69" s="3">
-        <v>45.44303797468355</v>
+        <v>51.392405063291136</v>
       </c>
       <c r="R69" s="3">
-        <v>34.93670886075949</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.89</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6331,61 +6352,61 @@
         <v>69</v>
       </c>
       <c r="B70" s="1">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="C70" s="1">
-        <v>43.037974683544306</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="D70" s="1">
-        <v>13.157894736842104</v>
+        <v>11.352380952380951</v>
       </c>
       <c r="E70" s="1">
-        <v>-1.41</v>
+        <v>-1.43</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.30958501752881185</v>
+        <v>-0.1879474993104786</v>
       </c>
       <c r="G70" s="1">
         <v>1.11</v>
       </c>
       <c r="H70" s="1">
-        <v>54.78</v>
+        <v>49.58</v>
       </c>
       <c r="I70" s="1">
-        <v>-22.74</v>
+        <v>-24.2</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.00858662388860459</v>
+        <v>-0.007821066314249446</v>
       </c>
       <c r="K70" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="1">
-        <v>-99</v>
+        <v>-98</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.29661989463290883</v>
+        <v>-0.17229356657245964</v>
       </c>
       <c r="N70" s="1">
-        <v>-16.80051410337906</v>
+        <v>-1.923508713592365</v>
       </c>
       <c r="O70" s="1">
-        <v>10.126582278481013</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P70" s="1">
-        <v>36.16826599829714</v>
+        <v>37.8905660403687</v>
       </c>
       <c r="Q70" s="1">
-        <v>46.32911392405064</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="R70" s="1">
-        <v>26.32911392405063</v>
+        <v>29.999999999999993</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="T70" s="1">
-        <v>0.51</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6399,55 +6420,55 @@
         <v>55.69620253164557</v>
       </c>
       <c r="D71" s="3">
-        <v>0.7953667953667956</v>
+        <v>0.7992277992277994</v>
       </c>
       <c r="E71" s="3">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.049428578185401834</v>
+        <v>-0.05286882420361361</v>
       </c>
       <c r="G71" s="3">
         <v>1.01</v>
       </c>
       <c r="H71" s="3">
-        <v>70.52</v>
+        <v>51.53</v>
       </c>
       <c r="I71" s="3">
-        <v>2.17</v>
+        <v>0.72</v>
       </c>
       <c r="J71" s="3">
-        <v>0.009573891146575371</v>
+        <v>0.007003088959258054</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-68</v>
+        <v>-62</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.04824993064941063</v>
+        <v>-0.05144573940924824</v>
       </c>
       <c r="N71" s="3">
-        <v>8.036482294970765</v>
+        <v>10.161274002728774</v>
       </c>
       <c r="O71" s="3">
-        <v>54.43037974683544</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P71" s="3">
         <v>19.13407224404345</v>
       </c>
       <c r="Q71" s="3">
-        <v>54.30379746835443</v>
+        <v>49.367088607594944</v>
       </c>
       <c r="R71" s="3">
-        <v>43.79746835443039</v>
+        <v>39.620253164556964</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="T71" s="3">
-        <v>1.58</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6461,120 +6482,122 @@
         <v>74.68354430379746</v>
       </c>
       <c r="D72" s="3">
-        <v>0.19865642994241844</v>
+        <v>0.210172744721689</v>
       </c>
       <c r="E72" s="3">
-        <v>-1.66</v>
+        <v>-1.72</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.1412091452908454</v>
+        <v>-0.06797314547006164</v>
       </c>
       <c r="G72" s="3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="H72" s="3">
-        <v>59.03</v>
+        <v>68.47</v>
       </c>
       <c r="I72" s="3">
-        <v>-4.01</v>
+        <v>4.67</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.001489275694968476</v>
+        <v>0.002759064062136385</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.1270653748589512</v>
+        <v>-0.05516538232077339</v>
       </c>
       <c r="N72" s="3">
-        <v>0.15493787401670858</v>
+        <v>9.789309711576259</v>
       </c>
       <c r="O72" s="3">
-        <v>37.9746835443038</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P72" s="3">
         <v>21.36339366602189</v>
       </c>
       <c r="Q72" s="3">
-        <v>46.962025316455694</v>
+        <v>53.924050632911396</v>
       </c>
       <c r="R72" s="3">
-        <v>36.20253164556962</v>
+        <v>37.974683544303794</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T72" s="3">
-        <v>0.13</v>
+        <v>-0.81</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B73" s="2">
+      <c r="A73" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B73" s="3">
         <v>2.35</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="3">
         <v>45.56962025316456</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="3">
         <v>7.055319148936169</v>
       </c>
-      <c r="E73" s="2">
-        <v>5.09</v>
-      </c>
-      <c r="F73" s="2">
-        <v>0.32097408844820413</v>
-      </c>
-      <c r="G73" s="2">
-        <v>1.04</v>
-      </c>
-      <c r="H73" s="2">
-        <v>61.07</v>
-      </c>
-      <c r="I73" s="2">
-        <v>37.69</v>
-      </c>
-      <c r="J73" s="2">
-        <v>0.032403048112695954</v>
-      </c>
-      <c r="K73" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="2">
-        <v>25</v>
-      </c>
-      <c r="M73" s="2">
-        <v>0.3256886785921689</v>
-      </c>
-      <c r="N73" s="2">
-        <v>45.4303432191287</v>
-      </c>
-      <c r="O73" s="2">
-        <v>84.81012658227847</v>
-      </c>
-      <c r="P73" s="2">
+      <c r="E73" s="3">
+        <v>5.07</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0.0880677176533115</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1.05</v>
+      </c>
+      <c r="H73" s="3">
+        <v>39.85</v>
+      </c>
+      <c r="I73" s="3">
+        <v>20.02</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0.013174703900929499</v>
+      </c>
+      <c r="K73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>27</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0.0951831416251383</v>
+      </c>
+      <c r="N73" s="3">
+        <v>24.824162106167428</v>
+      </c>
+      <c r="O73" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P73" s="3">
         <v>20.30977785396255</v>
       </c>
-      <c r="Q73" s="2">
-        <v>64.17721518987341</v>
-      </c>
-      <c r="R73" s="2">
-        <v>57.72151898734177</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T73" s="2"/>
+      <c r="Q73" s="3">
+        <v>53.164556962025316</v>
+      </c>
+      <c r="R73" s="3">
+        <v>49.68354430379747</v>
+      </c>
+      <c r="S73" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T73" s="3">
+        <v>-2.11</v>
+      </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2">
         <v>17.38</v>
@@ -6586,22 +6609,22 @@
         <v>-0.4602991944764096</v>
       </c>
       <c r="E74" s="2">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="F74" s="2">
-        <v>0.13362137139026073</v>
+        <v>0.1819787886542229</v>
       </c>
       <c r="G74" s="2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H74" s="2">
-        <v>61.75</v>
+        <v>71.44</v>
       </c>
       <c r="I74" s="2">
-        <v>9.64</v>
+        <v>18.18</v>
       </c>
       <c r="J74" s="2">
-        <v>0.01989175510132392</v>
+        <v>0.016065417194350756</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
@@ -6610,31 +6633,33 @@
         <v>-2</v>
       </c>
       <c r="M74" s="2">
-        <v>0.13715731399823428</v>
+        <v>0.18340187344858827</v>
       </c>
       <c r="N74" s="2">
-        <v>26.577206759735244</v>
+        <v>33.64603528851243</v>
       </c>
       <c r="O74" s="2">
-        <v>78.48101265822784</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P74" s="2">
         <v>23.852303543083593</v>
       </c>
       <c r="Q74" s="2">
-        <v>60.75949367088607</v>
+        <v>62.40506329113924</v>
       </c>
       <c r="R74" s="2">
-        <v>53.417721518987335</v>
+        <v>50.8860759493671</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="T74" s="2"/>
+      <c r="T74" s="2">
+        <v>-2.51</v>
+      </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2">
         <v>0.41</v>
@@ -6643,120 +6668,122 @@
         <v>31.645569620253166</v>
       </c>
       <c r="D75" s="2">
-        <v>207.90243902439028</v>
+        <v>208.14634146341464</v>
       </c>
       <c r="E75" s="2">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="F75" s="2">
-        <v>0.05476574050182323</v>
+        <v>0.20077612517766202</v>
       </c>
       <c r="G75" s="2">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="H75" s="2">
-        <v>63.97</v>
+        <v>74.67</v>
       </c>
       <c r="I75" s="2">
-        <v>8.69</v>
+        <v>29.35</v>
       </c>
       <c r="J75" s="2">
-        <v>0.017654528845582978</v>
+        <v>0.030485439368290634</v>
       </c>
       <c r="K75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L75" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M75" s="2">
-        <v>0.06773086339772627</v>
+        <v>0.21073771873821956</v>
       </c>
       <c r="N75" s="2">
-        <v>19.634561699684454</v>
+        <v>36.379619817475565</v>
       </c>
       <c r="O75" s="2">
-        <v>72.15189873417721</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P75" s="2">
-        <v>25.0383224064444</v>
+        <v>23.294117248136235</v>
       </c>
       <c r="Q75" s="2">
-        <v>65.69620253164557</v>
+        <v>71.64556962025317</v>
       </c>
       <c r="R75" s="2">
-        <v>54.620253164556964</v>
+        <v>58.924050632911396</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="T75" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="T75" s="2">
+        <v>-0.43</v>
+      </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B76" s="2">
+      <c r="A76" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="3">
         <v>0.96</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="3">
         <v>36.708860759493675</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="3">
         <v>12.072916666666668</v>
       </c>
-      <c r="E76" s="2">
-        <v>0.98</v>
-      </c>
-      <c r="F76" s="2">
-        <v>0.05578548121298342</v>
-      </c>
-      <c r="G76" s="2">
+      <c r="E76" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0.02239892769488039</v>
+      </c>
+      <c r="G76" s="3">
         <v>0.78</v>
       </c>
-      <c r="H76" s="2">
-        <v>69.77</v>
-      </c>
-      <c r="I76" s="2">
-        <v>26.26</v>
-      </c>
-      <c r="J76" s="2">
-        <v>0.015310849162628181</v>
-      </c>
-      <c r="K76" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="2">
-        <v>13</v>
-      </c>
-      <c r="M76" s="2">
-        <v>0.029855235421177406</v>
-      </c>
-      <c r="N76" s="2">
-        <v>15.84699890202956</v>
-      </c>
-      <c r="O76" s="2">
-        <v>63.29113924050633</v>
-      </c>
-      <c r="P76" s="2">
+      <c r="H76" s="3">
+        <v>52.95</v>
+      </c>
+      <c r="I76" s="3">
+        <v>22.71</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.0001580113949283262</v>
+      </c>
+      <c r="K76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
+        <v>12</v>
+      </c>
+      <c r="M76" s="3">
+        <v>-0.008908937781157533</v>
+      </c>
+      <c r="N76" s="3">
+        <v>14.414954165537846</v>
+      </c>
+      <c r="O76" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P76" s="3">
         <v>3.6747023875523213</v>
       </c>
-      <c r="Q76" s="2">
-        <v>61.898734177215196</v>
-      </c>
-      <c r="R76" s="2">
-        <v>51.77215189873418</v>
-      </c>
-      <c r="S76" s="2" t="s">
+      <c r="Q76" s="3">
+        <v>53.291139240506325</v>
+      </c>
+      <c r="R76" s="3">
+        <v>45.25316455696203</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T76" s="2">
-        <v>-1.65</v>
+      <c r="T76" s="3">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B77" s="3">
         <v>20.88</v>
@@ -6765,58 +6792,60 @@
         <v>94.9367088607595</v>
       </c>
       <c r="D77" s="3">
-        <v>-0.7102490421455938</v>
+        <v>-0.742816091954023</v>
       </c>
       <c r="E77" s="3">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="F77" s="3">
-        <v>0.017325521218239492</v>
+        <v>-0.005267457697742395</v>
       </c>
       <c r="G77" s="3">
         <v>0.99</v>
       </c>
       <c r="H77" s="3">
-        <v>67.89</v>
+        <v>66</v>
       </c>
       <c r="I77" s="3">
-        <v>6.25</v>
+        <v>9.42</v>
       </c>
       <c r="J77" s="3">
-        <v>0.008725483306200415</v>
+        <v>0.006411221374522237</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L77" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M77" s="3">
-        <v>0.01614687368224832</v>
+        <v>-0.006690542492107765</v>
       </c>
       <c r="N77" s="3">
-        <v>14.476162728136648</v>
+        <v>14.636793694442806</v>
       </c>
       <c r="O77" s="3">
-        <v>60.75949367088608</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P77" s="3">
-        <v>12.27047093905827</v>
+        <v>12.188764055163578</v>
       </c>
       <c r="Q77" s="3">
-        <v>57.721518987341774</v>
+        <v>56.708860759493675</v>
       </c>
       <c r="R77" s="3">
-        <v>49.93670886075949</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T77" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="T77" s="3">
+        <v>-0.65</v>
+      </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B78" s="3">
         <v>13.11</v>
@@ -6825,25 +6854,25 @@
         <v>82.27848101265823</v>
       </c>
       <c r="D78" s="3">
-        <v>-0.7337909992372235</v>
+        <v>-0.7574370709382151</v>
       </c>
       <c r="E78" s="3">
         <v>0</v>
       </c>
       <c r="F78" s="3">
-        <v>0.03900179597051556</v>
+        <v>0.053428136296937906</v>
       </c>
       <c r="G78" s="3">
         <v>1.23</v>
       </c>
       <c r="H78" s="3">
-        <v>49.89</v>
+        <v>54</v>
       </c>
       <c r="I78" s="3">
-        <v>18.62</v>
+        <v>15.43</v>
       </c>
       <c r="J78" s="3">
-        <v>0.02014468829151593</v>
+        <v>0.005881114196087425</v>
       </c>
       <c r="K78" s="3" t="b">
         <v>0</v>
@@ -6852,33 +6881,33 @@
         <v>59</v>
       </c>
       <c r="M78" s="3">
-        <v>0.06611068929831276</v>
+        <v>0.08615908656734117</v>
       </c>
       <c r="N78" s="3">
-        <v>19.4725442897431</v>
+        <v>23.921756600387713</v>
       </c>
       <c r="O78" s="3">
-        <v>70.88607594936708</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P78" s="3">
-        <v>20.806025084936465</v>
+        <v>16.126204071156796</v>
       </c>
       <c r="Q78" s="3">
-        <v>54.05063291139241</v>
+        <v>50.37974683544304</v>
       </c>
       <c r="R78" s="3">
-        <v>49.24050632911393</v>
+        <v>46.0126582278481</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T78" s="3">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2">
         <v>3.07</v>
@@ -6887,60 +6916,58 @@
         <v>48.10126582278481</v>
       </c>
       <c r="D79" s="2">
-        <v>2.872964169381108</v>
+        <v>2.8794788273615635</v>
       </c>
       <c r="E79" s="2">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="F79" s="2">
-        <v>0.3976209351219777</v>
+        <v>0.28793818012547534</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H79" s="2">
-        <v>57.59</v>
+        <v>45.71</v>
       </c>
       <c r="I79" s="2">
-        <v>46.38</v>
+        <v>33.86</v>
       </c>
       <c r="J79" s="2">
-        <v>0.04280599462878057</v>
+        <v>0.02592436606426472</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M79" s="2">
-        <v>0.3976209351219777</v>
+        <v>0.2893612649198407</v>
       </c>
       <c r="N79" s="2">
-        <v>52.623568872109594</v>
+        <v>44.24197443563768</v>
       </c>
       <c r="O79" s="2">
-        <v>87.34177215189874</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>61.89873417721519</v>
+        <v>56.32911392405063</v>
       </c>
       <c r="R79" s="2">
-        <v>58.10126582278481</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="T79" s="2">
-        <v>-0.89</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="T79" s="2"/>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2">
         <v>12.58</v>
@@ -6949,55 +6976,55 @@
         <v>79.74683544303798</v>
       </c>
       <c r="D80" s="2">
-        <v>0.6025437201907791</v>
+        <v>0.5985691573926868</v>
       </c>
       <c r="E80" s="2">
-        <v>-2.26</v>
+        <v>-2.29</v>
       </c>
       <c r="F80" s="2">
-        <v>1.5374156575856517</v>
+        <v>1.1630475816143662</v>
       </c>
       <c r="G80" s="2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H80" s="2">
-        <v>68.02</v>
+        <v>56.54</v>
       </c>
       <c r="I80" s="2">
-        <v>144.83</v>
+        <v>118.81</v>
       </c>
       <c r="J80" s="2">
-        <v>0.09050464468130455</v>
+        <v>0.06907704471619198</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M80" s="2">
-        <v>1.5739537312013783</v>
+        <v>1.2085862950340576</v>
       </c>
       <c r="N80" s="2">
-        <v>170.25684848004965</v>
+        <v>136.16447744705934</v>
       </c>
       <c r="O80" s="2">
-        <v>96.20253164556962</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P80" s="2">
         <v>20.630527651660007</v>
       </c>
       <c r="Q80" s="2">
-        <v>72.78481012658227</v>
+        <v>70</v>
       </c>
       <c r="R80" s="2">
-        <v>64.74683544303798</v>
+        <v>63.54430379746836</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T80" s="2">
-        <v>0.44</v>
+        <v>-1.2</v>
       </c>
     </row>
   </sheetData>
@@ -7013,10 +7040,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7024,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22.59493670886076</v>
+        <v>18.924050632911392</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7032,7 +7059,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>64.81012658227849</v>
+        <v>68.67088607594937</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7040,7 +7067,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>44.49367088607595</v>
+        <v>48.35443037974683</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7048,7 +7075,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>45.063291139240505</v>
+        <v>47.658227848101276</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7056,7 +7083,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22.27848101265823</v>
+        <v>18.417721518987342</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7064,7 +7091,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.848101265822784</v>
+        <v>43.73417721518987</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7072,7 +7099,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>53.92405063291139</v>
+        <v>59.36708860759493</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7080,7 +7107,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31.202531645569614</v>
+        <v>27.658227848101262</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7088,7 +7115,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>39.620253164556964</v>
+        <v>34.43037974683545</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7096,7 +7123,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>42.65822784810127</v>
+        <v>52.40506329113924</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7104,7 +7131,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>49.74683544303798</v>
+        <v>52.65822784810126</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7112,7 +7139,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.405063291139239</v>
+        <v>1.3924050632911378</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7120,7 +7147,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>51.8354430379747</v>
+        <v>54.367088607594944</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7128,7 +7155,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>60.50632911392406</v>
+        <v>59.11392405063292</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7136,7 +7163,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>30.696202531645575</v>
+        <v>44.68354430379747</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7144,7 +7171,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>26.265822784810123</v>
+        <v>32.08860759493672</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7152,7 +7179,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>46.20253164556962</v>
+        <v>51.01265822784809</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7160,7 +7187,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>45.31645569620253</v>
+        <v>48.41772151898734</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7168,7 +7195,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>42.53164556962026</v>
+        <v>36.20253164556962</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7176,7 +7203,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48.60759493670886</v>
+        <v>48.35443037974684</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7184,7 +7211,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>49.43037974683545</v>
+        <v>54.240506329113934</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7192,7 +7219,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>33.417721518987335</v>
+        <v>33.164556962025316</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7200,7 +7227,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.974683544303799</v>
+        <v>-3.2278481012658222</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7208,7 +7235,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>-1.0126582278480996</v>
+        <v>1.265822784810128</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7216,7 +7243,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>32.84810126582279</v>
+        <v>29.746835443037977</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7224,7 +7251,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>19.430379746835442</v>
+        <v>21.898734177215193</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7232,7 +7259,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>18.291139240506332</v>
+        <v>20.126582278481013</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7240,7 +7267,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>37.911392405063296</v>
+        <v>42.72151898734177</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7248,7 +7275,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>51.962025316455694</v>
+        <v>48.48101265822785</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7256,7 +7283,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>56.20253164556962</v>
+        <v>46.07594936708861</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7264,7 +7291,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30.18987341772152</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7272,7 +7299,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37.151898734177216</v>
+        <v>34.1139240506329</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7280,7 +7307,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>50.82278481012659</v>
+        <v>45.31645569620254</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7288,7 +7315,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>22.405063291139236</v>
+        <v>22.278481012658222</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7296,7 +7323,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>28.9240506329114</v>
+        <v>25.949367088607598</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7304,7 +7331,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>25.632911392405063</v>
+        <v>28.797468354430382</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7312,7 +7339,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>57.658227848101255</v>
+        <v>64.55696202531645</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7320,7 +7347,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>30.56962025316456</v>
+        <v>26.392405063291132</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7328,7 +7355,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>10.443037974683545</v>
+        <v>8.417721518987344</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7336,7 +7363,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>39.936708860759495</v>
+        <v>37.40506329113924</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7344,7 +7371,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>34.17721518987342</v>
+        <v>34.43037974683545</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7352,7 +7379,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>38.924050632911396</v>
+        <v>46.01265822784811</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7360,7 +7387,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>30.886075949367086</v>
+        <v>34.303797468354425</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7368,7 +7395,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>51.64556962025317</v>
+        <v>44.17721518987342</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7376,7 +7403,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>21.835443037974684</v>
+        <v>22.21518987341772</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7384,7 +7411,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.949367088607595</v>
+        <v>26.962025316455698</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7392,7 +7419,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>50.31645569620253</v>
+        <v>46.77215189873418</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7400,7 +7427,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>61.01265822784809</v>
+        <v>60.189873417721515</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7408,7 +7435,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>22.405063291139243</v>
+        <v>21.83544303797468</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7416,7 +7443,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>36.39240506329114</v>
+        <v>32.721518987341774</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7424,7 +7451,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>61.77215189873418</v>
+        <v>60.696202531645575</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7432,7 +7459,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>27.08860759493671</v>
+        <v>28.734177215189874</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7440,7 +7467,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>51.455696202531655</v>
+        <v>49.0506329113924</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7448,7 +7475,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>51.835443037974684</v>
+        <v>47.08860759493671</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7456,7 +7483,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>35.88607594936709</v>
+        <v>42.21518987341773</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7464,7 +7491,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>67.53164556962025</v>
+        <v>68.98734177215191</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7472,7 +7499,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>60.9493670886076</v>
+        <v>59.43037974683545</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7480,7 +7507,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>48.9873417721519</v>
+        <v>48.54430379746836</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7488,7 +7515,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>28.60759493670886</v>
+        <v>25.18987341772152</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7496,7 +7523,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>46.07594936708861</v>
+        <v>46.32911392405064</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7504,7 +7531,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>72.91139240506328</v>
+        <v>70.82278481012659</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7512,7 +7539,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>68.35443037974684</v>
+        <v>65.56962025316457</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7520,7 +7547,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>38.924050632911396</v>
+        <v>49.55696202531646</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7528,7 +7555,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>16.89873417721519</v>
+        <v>17.40506329113924</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7536,7 +7563,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>38.41772151898734</v>
+        <v>39.81012658227848</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7544,7 +7571,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>43.54430379746835</v>
+        <v>43.54430379746836</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7552,7 +7579,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>28.227848101265828</v>
+        <v>30.69620253164557</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7560,7 +7587,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>34.93670886075949</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7568,7 +7595,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>26.32911392405063</v>
+        <v>29.999999999999993</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7576,7 +7603,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>43.79746835443039</v>
+        <v>39.620253164556964</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7584,71 +7611,71 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>36.20253164556962</v>
+        <v>37.974683544303794</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B73">
-        <v>57.72151898734177</v>
+        <v>49.68354430379747</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B74">
-        <v>53.417721518987335</v>
+        <v>50.8860759493671</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B75">
-        <v>54.620253164556964</v>
+        <v>58.924050632911396</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B76">
-        <v>51.77215189873418</v>
+        <v>45.25316455696203</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B77">
-        <v>49.93670886075949</v>
+        <v>46.07594936708861</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B78">
-        <v>49.24050632911393</v>
+        <v>46.0126582278481</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B79">
-        <v>58.10126582278481</v>
+        <v>56.26582278481013</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B80">
-        <v>64.74683544303798</v>
+        <v>63.54430379746836</v>
       </c>
     </row>
   </sheetData>
@@ -7667,137 +7694,137 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7816,117 +7843,117 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7945,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7956,112 +7983,112 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -8080,125 +8107,125 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -8214,212 +8241,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" t="s">
         <v>204</v>
       </c>
-      <c r="C12" t="s">
-        <v>198</v>
-      </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/data/stocks.xlsx
+++ b/data/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="235">
   <si>
     <t>Ticker</t>
   </si>
@@ -163,27 +163,33 @@
     <t>IDCC</t>
   </si>
   <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>SNAP</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
     <t>VRT</t>
   </si>
   <si>
-    <t>BE</t>
-  </si>
-  <si>
     <t>SMRT</t>
   </si>
   <si>
-    <t>USAR</t>
-  </si>
-  <si>
     <t>LRCX</t>
   </si>
   <si>
     <t>QS</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
     <t>BAC</t>
   </si>
   <si>
@@ -193,9 +199,6 @@
     <t>MU</t>
   </si>
   <si>
-    <t>CAT</t>
-  </si>
-  <si>
     <t>GEV</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
     <t>STX</t>
   </si>
   <si>
-    <t>VRTX</t>
-  </si>
-  <si>
     <t>INTU</t>
   </si>
   <si>
@@ -232,10 +232,10 @@
     <t>NKE</t>
   </si>
   <si>
-    <t>MMM</t>
-  </si>
-  <si>
-    <t>SHW</t>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>BBAI</t>
   </si>
   <si>
     <t>EPS_TTM</t>
@@ -370,61 +370,73 @@
     <t>2027-06-04</t>
   </si>
   <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
     <t>2027-04-22</t>
   </si>
   <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2027-05-21</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>ATEX</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>CBZ</t>
+  </si>
+  <si>
+    <t>ZD</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>ADUS</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
     <t>2027-05-13</t>
   </si>
   <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2027-05-21</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2027-04-21</t>
-  </si>
-  <si>
-    <t>CTS</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>WSR</t>
-  </si>
-  <si>
-    <t>JPM</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>DELL</t>
+    <t>UNP</t>
   </si>
   <si>
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-07-06</t>
+    <t>2026-07-08</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -436,9 +448,6 @@
     <t>Last Run</t>
   </si>
   <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
@@ -514,7 +523,7 @@
     <t>Results</t>
   </si>
   <si>
-    <t>4 of 4 qualified</t>
+    <t>5 of 5 qualified</t>
   </si>
   <si>
     <t>Dow Jones 30</t>
@@ -532,24 +541,24 @@
     <t>All sectors</t>
   </si>
   <si>
+    <t>2 of 2 qualified</t>
+  </si>
+  <si>
+    <t>Nasdaq 100</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
+  </si>
+  <si>
+    <t>0.7 – 1.3</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>1 of 1 qualified</t>
   </si>
   <si>
-    <t>Nasdaq 100</t>
-  </si>
-  <si>
-    <t>&lt; 50</t>
-  </si>
-  <si>
-    <t>0.7 – 1.3</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>0 of 0 qualified</t>
-  </si>
-  <si>
     <t>S&amp;P 500 (large-cap subset)</t>
   </si>
   <si>
@@ -679,7 +688,7 @@
     <t>Triggers</t>
   </si>
   <si>
-    <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Institutional Buying</t>
+    <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
@@ -688,16 +697,25 @@
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
+    <t>Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
@@ -1107,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1343,6 +1361,21 @@
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1361,76 +1394,76 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="B2">
-        <v>70.82278481012659</v>
+        <v>73.71951219512195</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3">
-        <v>68.98734177215191</v>
+        <v>68.96341463414635</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="B4">
-        <v>68.67088607594937</v>
+        <v>68.10975609756098</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>65.56962025316457</v>
+        <v>67.5609756097561</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B6">
-        <v>64.55696202531645</v>
+        <v>65.3658536585366</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="B7">
-        <v>63.54430379746836</v>
+        <v>64.57317073170731</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,43 +1471,43 @@
         <v>51</v>
       </c>
       <c r="B8">
-        <v>60.696202531645575</v>
+        <v>60.54878048780487</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>60.189873417721515</v>
+        <v>60.24390243902438</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>59.43037974683545</v>
+        <v>58.84146341463414</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>59.36708860759493</v>
+        <v>58.47560975609757</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1482,32 +1515,32 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>59.11392405063292</v>
+        <v>58.41463414634147</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="B13">
-        <v>58.924050632911396</v>
+        <v>57.01219512195122</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B14">
-        <v>56.26582278481013</v>
+        <v>55.91463414634147</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1515,10 +1548,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>54.367088607594944</v>
+        <v>55.243902439024396</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1526,10 +1559,10 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>54.240506329113934</v>
+        <v>53.475609756097555</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1537,153 +1570,153 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>52.65822784810126</v>
+        <v>53.109756097560975</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>52.40506329113924</v>
+        <v>52.4390243902439</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>51.01265822784809</v>
+        <v>52.13414634146342</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>50.8860759493671</v>
+        <v>51.34146341463415</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B21">
-        <v>49.68354430379747</v>
+        <v>49.32926829268293</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>49.55696202531646</v>
+        <v>49.26829268292683</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="B23">
-        <v>49.0506329113924</v>
+        <v>49.20731707317073</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B24">
-        <v>48.54430379746836</v>
+        <v>48.47560975609757</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="B25">
-        <v>48.48101265822785</v>
+        <v>48.47560975609756</v>
       </c>
       <c r="C25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>48.41772151898734</v>
+        <v>48.292682926829265</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B27">
-        <v>48.35443037974684</v>
+        <v>48.23170731707318</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>48.35443037974683</v>
+        <v>48.231707317073166</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B29">
-        <v>46.77215189873418</v>
+        <v>47.68292682926829</v>
       </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="B30">
-        <v>46.32911392405064</v>
+        <v>47.5</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,142 +1724,142 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>46.07594936708861</v>
+        <v>47.4390243902439</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>46.07594936708861</v>
+        <v>47.25609756097562</v>
       </c>
       <c r="C32" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="B33">
-        <v>46.01265822784811</v>
+        <v>47.07317073170731</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="B34">
-        <v>46.0126582278481</v>
+        <v>46.70731707317073</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B35">
-        <v>45.31645569620254</v>
+        <v>46.52439024390244</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B36">
-        <v>45.25316455696203</v>
+        <v>46.15853658536586</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="B37">
-        <v>44.68354430379747</v>
+        <v>46.15853658536585</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B38">
-        <v>44.17721518987342</v>
+        <v>45.85365853658537</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B39">
-        <v>43.73417721518987</v>
+        <v>45.85365853658537</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B40">
-        <v>43.54430379746836</v>
+        <v>45.792682926829265</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="B41">
-        <v>42.21518987341773</v>
+        <v>45.24390243902439</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B42">
-        <v>38.734177215189874</v>
+        <v>44.57317073170732</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B43">
-        <v>37.974683544303794</v>
+        <v>43.35365853658536</v>
       </c>
       <c r="C43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1834,10 +1867,10 @@
         <v>40</v>
       </c>
       <c r="B44">
-        <v>37.40506329113924</v>
+        <v>37.987804878048784</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,21 +1878,21 @@
         <v>19</v>
       </c>
       <c r="B45">
-        <v>36.20253164556962</v>
+        <v>35.97560975609757</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>34.43037974683545</v>
+        <v>35.54878048780488</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1867,54 +1900,54 @@
         <v>32</v>
       </c>
       <c r="B47">
-        <v>34.1139240506329</v>
+        <v>35.30487804878049</v>
       </c>
       <c r="C47" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B48">
-        <v>33.164556962025316</v>
+        <v>35.243902439024396</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B49">
-        <v>32.721518987341774</v>
+        <v>33.048780487804876</v>
       </c>
       <c r="C49" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="B50">
-        <v>32.08860759493672</v>
+        <v>30.304878048780488</v>
       </c>
       <c r="C50" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B51">
-        <v>29.999999999999993</v>
+        <v>29.57317073170732</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1935,117 +1968,117 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -2066,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T80"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -2139,58 +2172,58 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>59.49367088607595</v>
+        <v>62.19512195121951</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.5834738617200677</v>
+        <v>-1.585160202360877</v>
       </c>
       <c r="E2" s="1">
         <v>0.38</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.1858541325339158</v>
+        <v>-0.16615084617380577</v>
       </c>
       <c r="G2" s="1">
         <v>0.17</v>
       </c>
       <c r="H2" s="1">
-        <v>35.59</v>
+        <v>48.78</v>
       </c>
       <c r="I2" s="1">
-        <v>0.48</v>
+        <v>4.25</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.008245120065841256</v>
+        <v>-0.007309548914532292</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.30397017046624064</v>
+        <v>-0.27696065069541365</v>
       </c>
       <c r="N2" s="1">
-        <v>-15.091169102970472</v>
+        <v>-13.27048621151632</v>
       </c>
       <c r="O2" s="1">
-        <v>11.39240506329114</v>
+        <v>10.975609756097562</v>
       </c>
       <c r="P2" s="1">
         <v>20.65084470171101</v>
       </c>
       <c r="Q2" s="1">
-        <v>29.49367088607595</v>
+        <v>34.87804878048781</v>
       </c>
       <c r="R2" s="1">
-        <v>18.924050632911392</v>
+        <v>19.451219512195124</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2201,7 +2234,7 @@
         <v>3.05</v>
       </c>
       <c r="C3" s="2">
-        <v>46.835443037974684</v>
+        <v>47.5609756097561</v>
       </c>
       <c r="D3" s="2">
         <v>24.6688524590164</v>
@@ -2210,49 +2243,49 @@
         <v>-0.89</v>
       </c>
       <c r="F3" s="2">
-        <v>1.1744858344133393</v>
+        <v>1.0035274108987613</v>
       </c>
       <c r="G3" s="2">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>57.35</v>
+        <v>51.17</v>
       </c>
       <c r="I3" s="2">
-        <v>97.06</v>
+        <v>83.06</v>
       </c>
       <c r="J3" s="2">
-        <v>0.05973757284423414</v>
+        <v>0.056764423744973674</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="M3" s="2">
-        <v>1.3851023839794125</v>
+        <v>1.1997809201117293</v>
       </c>
       <c r="N3" s="2">
-        <v>153.81608634159483</v>
+        <v>134.40367086919798</v>
       </c>
       <c r="O3" s="2">
-        <v>98.73417721518987</v>
+        <v>97.5609756097561</v>
       </c>
       <c r="P3" s="2">
         <v>16.611373293216246</v>
       </c>
       <c r="Q3" s="2">
-        <v>72.53164556962025</v>
+        <v>70.2439024390244</v>
       </c>
       <c r="R3" s="2">
-        <v>68.67088607594937</v>
+        <v>67.5609756097561</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2263,7 +2296,7 @@
         <v>-3.51</v>
       </c>
       <c r="C4" s="3">
-        <v>8.860759493670885</v>
+        <v>7.317073170731707</v>
       </c>
       <c r="D4" s="3">
         <v>12.615384615384617</v>
@@ -2272,19 +2305,19 @@
         <v>-1.61</v>
       </c>
       <c r="F4" s="3">
-        <v>0.5245361291806449</v>
+        <v>0.5692221164189672</v>
       </c>
       <c r="G4" s="3">
         <v>1.34</v>
       </c>
       <c r="H4" s="3">
-        <v>69.3</v>
+        <v>69.55</v>
       </c>
       <c r="I4" s="3">
-        <v>26.78</v>
+        <v>26.95</v>
       </c>
       <c r="J4" s="3">
-        <v>0.05750023529404491</v>
+        <v>0.05771131692073826</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
@@ -2293,28 +2326,28 @@
         <v>-88</v>
       </c>
       <c r="M4" s="3">
-        <v>0.5729210121890671</v>
+        <v>0.6146140845362524</v>
       </c>
       <c r="N4" s="3">
-        <v>72.5979491625603</v>
+        <v>75.88698731165029</v>
       </c>
       <c r="O4" s="3">
-        <v>88.60759493670885</v>
+        <v>89.02439024390245</v>
       </c>
       <c r="P4" s="3">
         <v>33.76175725439266</v>
       </c>
       <c r="Q4" s="3">
-        <v>59.367088607594944</v>
+        <v>60.121951219512205</v>
       </c>
       <c r="R4" s="3">
-        <v>48.35443037974683</v>
+        <v>48.23170731707318</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2325,58 +2358,58 @@
         <v>1.09</v>
       </c>
       <c r="C5" s="3">
-        <v>40.50632911392405</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="D5" s="3">
-        <v>23.678899082568805</v>
+        <v>23.73394495412844</v>
       </c>
       <c r="E5" s="3">
         <v>-0.89</v>
       </c>
       <c r="F5" s="3">
-        <v>-0.10420845184068017</v>
+        <v>-0.11045345155889336</v>
       </c>
       <c r="G5" s="3">
         <v>1.81</v>
       </c>
       <c r="H5" s="3">
-        <v>54.7</v>
+        <v>49.6</v>
       </c>
       <c r="I5" s="3">
-        <v>0.28</v>
+        <v>-3.72</v>
       </c>
       <c r="J5" s="3">
-        <v>0.005682802585276467</v>
+        <v>0.0059843459170185855</v>
       </c>
       <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>-82</v>
+        <v>-77</v>
       </c>
       <c r="M5" s="3">
-        <v>0.011061416502913923</v>
+        <v>-0.002313762808890507</v>
       </c>
       <c r="N5" s="3">
-        <v>16.411989593944995</v>
+        <v>14.194202577135984</v>
       </c>
       <c r="O5" s="3">
-        <v>51.89873417721519</v>
+        <v>50</v>
       </c>
       <c r="P5" s="3">
         <v>19.851960490969105</v>
       </c>
       <c r="Q5" s="3">
-        <v>55.9493670886076</v>
+        <v>53.048780487804876</v>
       </c>
       <c r="R5" s="3">
-        <v>47.658227848101276</v>
+        <v>45.853658536585364</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="3">
-        <v>5.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2387,7 +2420,7 @@
         <v>3.09</v>
       </c>
       <c r="C6" s="1">
-        <v>49.36708860759494</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1">
         <v>1.4854368932038835</v>
@@ -2396,49 +2429,49 @@
         <v>0.35</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.4551108310997908</v>
+        <v>-0.443639376119203</v>
       </c>
       <c r="G6" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H6" s="1">
-        <v>43.81</v>
+        <v>44.24</v>
       </c>
       <c r="I6" s="1">
-        <v>-20.72</v>
+        <v>-20.35</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.0262027920733899</v>
+        <v>-0.022341262474832237</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.38253350658715746</v>
+        <v>-0.37421636605747277</v>
       </c>
       <c r="N6" s="1">
-        <v>-22.947502715062154</v>
+        <v>-22.99605774772223</v>
       </c>
       <c r="O6" s="1">
-        <v>6.329113924050633</v>
+        <v>8.536585365853659</v>
       </c>
       <c r="P6" s="1">
         <v>34.223953127673056</v>
       </c>
       <c r="Q6" s="1">
-        <v>33.79746835443038</v>
+        <v>35</v>
       </c>
       <c r="R6" s="1">
-        <v>18.417721518987342</v>
+        <v>18.963414634146346</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2449,7 +2482,7 @@
         <v>6.53</v>
       </c>
       <c r="C7" s="3">
-        <v>65.82278481012658</v>
+        <v>68.29268292682927</v>
       </c>
       <c r="D7" s="3">
         <v>5.234303215926493</v>
@@ -2458,49 +2491,49 @@
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>-0.2257245863823663</v>
+        <v>-0.19854248050398182</v>
       </c>
       <c r="G7" s="3">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H7" s="3">
-        <v>41.95</v>
+        <v>43.53</v>
       </c>
       <c r="I7" s="3">
-        <v>2.31</v>
+        <v>2.96</v>
       </c>
       <c r="J7" s="3">
-        <v>-0.0020420205896341435</v>
+        <v>-0.0019788741103188754</v>
       </c>
       <c r="K7" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="M7" s="3">
-        <v>-0.05068515667542717</v>
+        <v>-0.03566541843607629</v>
       </c>
       <c r="N7" s="3">
-        <v>10.237332276110882</v>
+        <v>10.859037014417426</v>
       </c>
       <c r="O7" s="3">
-        <v>41.77215189873418</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="P7" s="3">
         <v>18.329517988884657</v>
       </c>
       <c r="Q7" s="3">
-        <v>49.36708860759494</v>
+        <v>50.97560975609757</v>
       </c>
       <c r="R7" s="3">
-        <v>43.73417721518987</v>
+        <v>45.24390243902439</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="3">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2511,58 +2544,58 @@
         <v>13.24</v>
       </c>
       <c r="C8" s="2">
-        <v>83.54430379746836</v>
+        <v>86.58536585365853</v>
       </c>
       <c r="D8" s="2">
-        <v>0.04607250755287005</v>
+        <v>0.0475830815709969</v>
       </c>
       <c r="E8" s="2">
         <v>0.56</v>
       </c>
       <c r="F8" s="2">
-        <v>0.4071696877896948</v>
+        <v>0.4269995588180243</v>
       </c>
       <c r="G8" s="2">
         <v>0.63</v>
       </c>
       <c r="H8" s="2">
-        <v>58.83</v>
+        <v>63.84</v>
       </c>
       <c r="I8" s="2">
-        <v>23.78</v>
+        <v>26.64</v>
       </c>
       <c r="J8" s="2">
-        <v>0.023049188226230238</v>
+        <v>0.021377774791493668</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-213</v>
+        <v>-200</v>
       </c>
       <c r="M8" s="2">
-        <v>0.3545155503981765</v>
+        <v>0.37760241704333164</v>
       </c>
       <c r="N8" s="2">
-        <v>50.757402983471245</v>
+        <v>52.18582056235821</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>86.58536585365853</v>
       </c>
       <c r="P8" s="2">
         <v>12.1757720658765</v>
       </c>
       <c r="Q8" s="2">
-        <v>62.0253164556962</v>
+        <v>64.02439024390243</v>
       </c>
       <c r="R8" s="2">
-        <v>59.36708860759493</v>
+        <v>60.24390243902438</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2573,7 +2606,7 @@
         <v>0.89</v>
       </c>
       <c r="C9" s="1">
-        <v>35.44303797468354</v>
+        <v>34.146341463414636</v>
       </c>
       <c r="D9" s="1">
         <v>47.337078651685395</v>
@@ -2582,49 +2615,49 @@
         <v>-0.19</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.34283175496477963</v>
+        <v>-0.31335411066961943</v>
       </c>
       <c r="G9" s="1">
         <v>1.58</v>
       </c>
       <c r="H9" s="1">
-        <v>54.3</v>
+        <v>55.83</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.97</v>
+        <v>-14.72</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.01666318496956814</v>
+        <v>-0.013807129818970467</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.2602928368915888</v>
+        <v>-0.23592075329307416</v>
       </c>
       <c r="N9" s="1">
-        <v>-10.723435745505281</v>
+        <v>-9.166496471282365</v>
       </c>
       <c r="O9" s="1">
-        <v>12.658227848101266</v>
+        <v>17.073170731707318</v>
       </c>
       <c r="P9" s="1">
         <v>33.30639201351699</v>
       </c>
       <c r="Q9" s="1">
-        <v>46.962025316455694</v>
+        <v>47.07317073170732</v>
       </c>
       <c r="R9" s="1">
-        <v>27.658227848101262</v>
+        <v>28.10975609756098</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2635,7 +2668,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" s="3">
-        <v>63.29113924050633</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="D10" s="3">
         <v>0.5519999999999999</v>
@@ -2644,49 +2677,49 @@
         <v>-2.17</v>
       </c>
       <c r="F10" s="3">
-        <v>-0.20027803859871585</v>
+        <v>-0.18519440861505942</v>
       </c>
       <c r="G10" s="3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H10" s="3">
-        <v>42.98</v>
+        <v>43.19</v>
       </c>
       <c r="I10" s="3">
-        <v>-8.31</v>
+        <v>-8.16</v>
       </c>
       <c r="J10" s="3">
-        <v>-0.00741868766645343</v>
+        <v>-0.007601731596143749</v>
       </c>
       <c r="K10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>-136</v>
+        <v>-127</v>
       </c>
       <c r="M10" s="3">
-        <v>-0.14477773161846685</v>
+        <v>-0.13179209318295926</v>
       </c>
       <c r="N10" s="3">
-        <v>0.8280747818068991</v>
+        <v>1.2463695397291137</v>
       </c>
       <c r="O10" s="3">
-        <v>29.11392405063291</v>
+        <v>30.48780487804878</v>
       </c>
       <c r="P10" s="3">
         <v>15.951255967229406</v>
       </c>
       <c r="Q10" s="3">
-        <v>39.49367088607595</v>
+        <v>40.48780487804879</v>
       </c>
       <c r="R10" s="3">
-        <v>34.43037974683545</v>
+        <v>34.9390243902439</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T10" s="3">
-        <v>-1.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2697,7 +2730,7 @@
         <v>-0.95</v>
       </c>
       <c r="C11" s="2">
-        <v>15.18987341772152</v>
+        <v>13.414634146341465</v>
       </c>
       <c r="D11" s="2">
         <v>46.22105263157896</v>
@@ -2706,19 +2739,19 @@
         <v>-1.62</v>
       </c>
       <c r="F11" s="2">
-        <v>0.23699359322581803</v>
+        <v>0.2252997664499645</v>
       </c>
       <c r="G11" s="2">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="H11" s="2">
-        <v>68.41</v>
+        <v>68.47</v>
       </c>
       <c r="I11" s="2">
-        <v>17.62</v>
+        <v>17.69</v>
       </c>
       <c r="J11" s="2">
-        <v>0.019742171839279177</v>
+        <v>0.02148949981025138</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2727,28 +2760,28 @@
         <v>26</v>
       </c>
       <c r="M11" s="2">
-        <v>0.20853189733851085</v>
+        <v>0.1999336666197169</v>
       </c>
       <c r="N11" s="2">
-        <v>36.15903767750469</v>
+        <v>34.41894551999673</v>
       </c>
       <c r="O11" s="2">
-        <v>79.74683544303798</v>
+        <v>81.70731707317073</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>60.00000000000001</v>
+        <v>60.73170731707317</v>
       </c>
       <c r="R11" s="2">
-        <v>52.40506329113924</v>
+        <v>52.13414634146342</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T11" s="2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2759,7 +2792,7 @@
         <v>-0.15</v>
       </c>
       <c r="C12" s="2">
-        <v>22.78481012658228</v>
+        <v>23.170731707317074</v>
       </c>
       <c r="D12" s="2">
         <v>169</v>
@@ -2768,49 +2801,49 @@
         <v>2.9</v>
       </c>
       <c r="F12" s="2">
-        <v>0.30952876191658657</v>
+        <v>0.29298250205137943</v>
       </c>
       <c r="G12" s="2">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="H12" s="2">
-        <v>67.81</v>
+        <v>66.29</v>
       </c>
       <c r="I12" s="2">
-        <v>-1.99</v>
+        <v>-2.51</v>
       </c>
       <c r="J12" s="2">
-        <v>0.03648354343301034</v>
+        <v>0.039250177578634575</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="2">
-        <v>-55</v>
+        <v>-54</v>
       </c>
       <c r="M12" s="2">
-        <v>0.3024133379447598</v>
+        <v>0.2876422705081694</v>
       </c>
       <c r="N12" s="2">
-        <v>45.54718173812957</v>
+        <v>43.189805908841976</v>
       </c>
       <c r="O12" s="2">
-        <v>83.54430379746836</v>
+        <v>84.14634146341463</v>
       </c>
       <c r="P12" s="2">
         <v>40.172518102184526</v>
       </c>
       <c r="Q12" s="2">
-        <v>62.531645569620245</v>
+        <v>63.90243902439025</v>
       </c>
       <c r="R12" s="2">
-        <v>52.65822784810126</v>
+        <v>53.109756097560975</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T12" s="2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2821,7 +2854,7 @@
         <v>0.02</v>
       </c>
       <c r="C13" s="1">
-        <v>27.848101265822784</v>
+        <v>28.04878048780488</v>
       </c>
       <c r="D13" s="1">
         <v>-1653.5</v>
@@ -2830,49 +2863,49 @@
         <v>5.58</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.4471773436712764</v>
+        <v>-0.4689656104319249</v>
       </c>
       <c r="G13" s="1">
         <v>1.41</v>
       </c>
       <c r="H13" s="1">
-        <v>38.34</v>
+        <v>32.77</v>
       </c>
       <c r="I13" s="1">
-        <v>-26.44</v>
+        <v>-30.8</v>
       </c>
       <c r="J13" s="1">
-        <v>-0.025318627824700554</v>
+        <v>-0.026317302586635113</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" s="1">
-        <v>-0.38883086710229664</v>
+        <v>-0.41422823711402224</v>
       </c>
       <c r="N13" s="1">
-        <v>-23.577238766576066</v>
+        <v>-26.99724485337718</v>
       </c>
       <c r="O13" s="1">
-        <v>5.063291139240507</v>
+        <v>6.097560975609756</v>
       </c>
       <c r="P13" s="1">
-        <v>38.374715014440206</v>
+        <v>40.180582436698245</v>
       </c>
       <c r="Q13" s="1">
-        <v>12.531645569620254</v>
+        <v>12.195121951219512</v>
       </c>
       <c r="R13" s="1">
-        <v>1.3924050632911378</v>
+        <v>1.2804878048780477</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T13" s="1">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2883,7 +2916,7 @@
         <v>1.38</v>
       </c>
       <c r="C14" s="2">
-        <v>41.77215189873418</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="D14" s="2">
         <v>6.753623188405798</v>
@@ -2892,49 +2925,49 @@
         <v>4.52</v>
       </c>
       <c r="F14" s="2">
-        <v>0.7327713806648734</v>
+        <v>0.7294247945329287</v>
       </c>
       <c r="G14" s="2">
         <v>0.77</v>
       </c>
       <c r="H14" s="2">
-        <v>78.1</v>
+        <v>77.9</v>
       </c>
       <c r="I14" s="2">
-        <v>66.71</v>
+        <v>66.02</v>
       </c>
       <c r="J14" s="2">
-        <v>0.06650440800572771</v>
+        <v>0.06837943735591669</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M14" s="2">
-        <v>0.7000404303944701</v>
+        <v>0.6987184631594712</v>
       </c>
       <c r="N14" s="2">
-        <v>85.30989098310059</v>
+        <v>84.29742517397217</v>
       </c>
       <c r="O14" s="2">
-        <v>89.87341772151899</v>
+        <v>91.46341463414635</v>
       </c>
       <c r="P14" s="2">
         <v>28.85245621658959</v>
       </c>
       <c r="Q14" s="2">
-        <v>67.46835443037976</v>
+        <v>68.17073170731707</v>
       </c>
       <c r="R14" s="2">
-        <v>54.367088607594944</v>
+        <v>55.243902439024396</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T14" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2945,7 +2978,7 @@
         <v>-0.63</v>
       </c>
       <c r="C15" s="2">
-        <v>17.72151898734177</v>
+        <v>17.073170731707318</v>
       </c>
       <c r="D15" s="2">
         <v>73.76190476190477</v>
@@ -2954,49 +2987,49 @@
         <v>1.54</v>
       </c>
       <c r="F15" s="2">
-        <v>1.1003138491204965</v>
+        <v>0.869424662589372</v>
       </c>
       <c r="G15" s="2">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="H15" s="2">
-        <v>50.34</v>
+        <v>43.33</v>
       </c>
       <c r="I15" s="2">
-        <v>100.92</v>
+        <v>80.24</v>
       </c>
       <c r="J15" s="2">
-        <v>0.05659218037979602</v>
+        <v>0.052362782517223726</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M15" s="2">
-        <v>1.2725071092387048</v>
+        <v>1.0296316088856725</v>
       </c>
       <c r="N15" s="2">
-        <v>142.55655886752407</v>
+        <v>117.38873974659232</v>
       </c>
       <c r="O15" s="2">
-        <v>96.20253164556962</v>
+        <v>95.1219512195122</v>
       </c>
       <c r="P15" s="2">
         <v>23.3853551464226</v>
       </c>
       <c r="Q15" s="2">
-        <v>63.29113924050633</v>
+        <v>60.60975609756097</v>
       </c>
       <c r="R15" s="2">
-        <v>59.11392405063292</v>
+        <v>58.41463414634147</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T15" s="2">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3007,28 +3040,28 @@
         <v>-3.53</v>
       </c>
       <c r="C16" s="3">
-        <v>7.59493670886076</v>
+        <v>6.097560975609756</v>
       </c>
       <c r="D16" s="3">
-        <v>13.056657223796035</v>
+        <v>13.6657223796034</v>
       </c>
       <c r="E16" s="3">
         <v>4.82</v>
       </c>
       <c r="F16" s="3">
-        <v>0.09466139381505068</v>
+        <v>0.06213601626796034</v>
       </c>
       <c r="G16" s="3">
         <v>1.78</v>
       </c>
       <c r="H16" s="3">
-        <v>70.63</v>
+        <v>66.27</v>
       </c>
       <c r="I16" s="3">
-        <v>30.13</v>
+        <v>26.91</v>
       </c>
       <c r="J16" s="3">
-        <v>0.014328315696851569</v>
+        <v>0.013003472723877177</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3037,28 +3070,28 @@
         <v>19</v>
       </c>
       <c r="M16" s="3">
-        <v>0.20566200777554866</v>
+        <v>0.1662705313605557</v>
       </c>
       <c r="N16" s="3">
-        <v>35.87204872120846</v>
+        <v>31.05263199408062</v>
       </c>
       <c r="O16" s="3">
-        <v>78.48101265822784</v>
+        <v>79.26829268292683</v>
       </c>
       <c r="P16" s="3">
         <v>27.942065176302556</v>
       </c>
       <c r="Q16" s="3">
-        <v>55.69620253164557</v>
+        <v>54.390243902439025</v>
       </c>
       <c r="R16" s="3">
-        <v>44.68354430379747</v>
+        <v>44.57317073170732</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T16" s="3">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3069,58 +3102,58 @@
         <v>-6.21</v>
       </c>
       <c r="C17" s="3">
-        <v>3.79746835443038</v>
+        <v>3.6585365853658534</v>
       </c>
       <c r="D17" s="3">
-        <v>4.769726247987117</v>
+        <v>4.764895330112721</v>
       </c>
       <c r="E17" s="3">
         <v>0.76</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.005470059730483645</v>
+        <v>-0.003960860302326785</v>
       </c>
       <c r="G17" s="3">
         <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>69.35</v>
+        <v>65.56</v>
       </c>
       <c r="I17" s="3">
-        <v>11.37</v>
+        <v>9.34</v>
       </c>
       <c r="J17" s="3">
-        <v>0.0019418392145956062</v>
+        <v>0.003822084211241451</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" s="3">
-        <v>0.09699204546382223</v>
+        <v>0.09216330747545354</v>
       </c>
       <c r="N17" s="3">
-        <v>25.00505249003583</v>
+        <v>23.641909605570405</v>
       </c>
       <c r="O17" s="3">
-        <v>67.08860759493672</v>
+        <v>69.51219512195121</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>40.25316455696203</v>
+        <v>40.24390243902439</v>
       </c>
       <c r="R17" s="3">
-        <v>32.08860759493672</v>
+        <v>33.048780487804876</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T17" s="3">
-        <v>0.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3131,7 +3164,7 @@
         <v>0.09</v>
       </c>
       <c r="C18" s="2">
-        <v>29.11392405063291</v>
+        <v>29.268292682926827</v>
       </c>
       <c r="D18" s="2">
         <v>1387.3333333333335</v>
@@ -3140,19 +3173,19 @@
         <v>5.95</v>
      